--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{225B1DDE-9531-471C-B325-BE70F37B86B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3BECEC4-E5D1-430E-AAA6-FAF22C2F13D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1736,18 +1736,480 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_058</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 58</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_018</t>
   </si>
   <si>
@@ -1766,40 +2228,94 @@
     <t>connecting solar to buses in cluster 108</t>
   </si>
   <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
   </si>
   <si>
     <t>distr_solelc_spv_056</t>
@@ -1850,126 +2366,6 @@
     <t>connecting solar to buses in cluster 104</t>
   </si>
   <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_052</t>
   </si>
   <si>
@@ -2036,408 +2432,231 @@
     <t>connecting solar to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500</t>
+  </si>
+  <si>
+    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
     <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
   </si>
   <si>
@@ -2450,22 +2669,43 @@
     <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
   </si>
   <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500</t>
-  </si>
-  <si>
-    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
   </si>
   <si>
     <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
@@ -2492,66 +2732,6 @@
     <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
   </si>
   <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
-  </si>
-  <si>
     <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
   </si>
   <si>
@@ -2579,184 +2759,88 @@
     <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
   </si>
   <si>
-    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
   </si>
   <si>
     <t>distr_wonelc_won_060</t>
@@ -2777,6 +2861,228 @@
     <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_012</t>
   </si>
   <si>
@@ -2801,52 +3107,52 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
   </si>
   <si>
     <t>distr_wonelc_won_019</t>
@@ -2867,310 +3173,85 @@
     <t>connecting wind onshore to buses in cluster 46</t>
   </si>
   <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR866-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
   </si>
   <si>
     <t>elc_won_060</t>
@@ -3191,6 +3272,219 @@
     <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
   </si>
   <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
     <t>elc_won_012</t>
   </si>
   <si>
@@ -3215,52 +3509,52 @@
     <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
   </si>
   <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR866-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR400-500</t>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
   </si>
   <si>
     <t>elc_won_019</t>
@@ -3281,298 +3575,142 @@
     <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
   </si>
   <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_069</t>
-  </si>
-  <si>
-    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wofelc_wof_013</t>
@@ -3581,6 +3719,36 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
@@ -3593,172 +3761,136 @@
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR37-500,e_BR42-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
   </si>
   <si>
     <t>elc_wof_013</t>
@@ -3767,6 +3899,33 @@
     <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
   </si>
   <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
@@ -3777,165 +3936,6 @@
   </si>
   <si>
     <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR37-500,e_BR42-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9835,7 +9835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFED6073-879E-4424-B4C1-35C2BEB3A702}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B68C23-490A-418E-8F90-BD7D71D8CC9E}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10073,16 +10073,16 @@
         <v>535</v>
       </c>
       <c r="Y11" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="Z11" t="s">
         <v>769</v>
       </c>
       <c r="AA11">
-        <v>0.99012236069527793</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB11">
-        <v>181.09005391990564</v>
+        <v>470.66510807906917</v>
       </c>
       <c r="AD11" t="s">
         <v>534</v>
@@ -10115,10 +10115,10 @@
         <v>1015</v>
       </c>
       <c r="AO11">
-        <v>0.99445933293330402</v>
+        <v>0.99677419959133018</v>
       </c>
       <c r="AP11">
-        <v>101.57889622275951</v>
+        <v>59.139674158947656</v>
       </c>
       <c r="AR11" t="s">
         <v>534</v>
@@ -10151,10 +10151,10 @@
         <v>1211</v>
       </c>
       <c r="BC11">
-        <v>0.98691003029105739</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD11">
-        <v>239.98277799728109</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10219,16 +10219,16 @@
         <v>539</v>
       </c>
       <c r="Y12" t="s">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="Z12" t="s">
         <v>770</v>
       </c>
       <c r="AA12">
-        <v>0.98990296758392993</v>
+        <v>0.9882282251528024</v>
       </c>
       <c r="AB12">
-        <v>185.11226096128556</v>
+        <v>215.81587219862183</v>
       </c>
       <c r="AD12" t="s">
         <v>534</v>
@@ -10261,10 +10261,10 @@
         <v>1017</v>
       </c>
       <c r="AO12">
-        <v>0.9961850470371636</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP12">
-        <v>69.94080431866837</v>
+        <v>42.750927651225993</v>
       </c>
       <c r="AR12" t="s">
         <v>534</v>
@@ -10294,13 +10294,13 @@
         <v>1212</v>
       </c>
       <c r="BB12" t="s">
-        <v>1213</v>
+        <v>1092</v>
       </c>
       <c r="BC12">
-        <v>0.99032129621526932</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD12">
-        <v>177.44290272006148</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10365,16 +10365,16 @@
         <v>541</v>
       </c>
       <c r="Y13" t="s">
-        <v>456</v>
+        <v>494</v>
       </c>
       <c r="Z13" t="s">
         <v>771</v>
       </c>
       <c r="AA13">
-        <v>0.99377714174527498</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB13">
-        <v>114.08573466995766</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD13" t="s">
         <v>534</v>
@@ -10407,10 +10407,10 @@
         <v>1019</v>
       </c>
       <c r="AO13">
-        <v>0.99710531380540124</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP13">
-        <v>53.069246900976879</v>
+        <v>43.95454940357709</v>
       </c>
       <c r="AR13" t="s">
         <v>534</v>
@@ -10437,16 +10437,16 @@
         <v>1152</v>
       </c>
       <c r="BA13" t="s">
+        <v>1213</v>
+      </c>
+      <c r="BB13" t="s">
         <v>1214</v>
       </c>
-      <c r="BB13" t="s">
-        <v>1215</v>
-      </c>
       <c r="BC13">
-        <v>0.99420451954813838</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD13">
-        <v>106.25047495079694</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10511,16 +10511,16 @@
         <v>543</v>
       </c>
       <c r="Y14" t="s">
-        <v>525</v>
+        <v>427</v>
       </c>
       <c r="Z14" t="s">
         <v>772</v>
       </c>
       <c r="AA14">
-        <v>0.99516685156772267</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB14">
-        <v>88.60772125841865</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD14" t="s">
         <v>534</v>
@@ -10553,10 +10553,10 @@
         <v>1021</v>
       </c>
       <c r="AO14">
-        <v>0.99473480482648013</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP14">
-        <v>96.528578181196991</v>
+        <v>121.72426728897108</v>
       </c>
       <c r="AR14" t="s">
         <v>534</v>
@@ -10583,16 +10583,16 @@
         <v>1154</v>
       </c>
       <c r="BA14" t="s">
+        <v>1215</v>
+      </c>
+      <c r="BB14" t="s">
         <v>1216</v>
       </c>
-      <c r="BB14" t="s">
-        <v>1217</v>
-      </c>
       <c r="BC14">
-        <v>0.9933934749176847</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD14">
-        <v>121.11962650911367</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10657,16 +10657,16 @@
         <v>545</v>
       </c>
       <c r="Y15" t="s">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="Z15" t="s">
         <v>773</v>
       </c>
       <c r="AA15">
-        <v>0.99295369446862825</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB15">
-        <v>129.18226807514921</v>
+        <v>41.695953373122713</v>
       </c>
       <c r="AD15" t="s">
         <v>534</v>
@@ -10699,10 +10699,10 @@
         <v>1023</v>
       </c>
       <c r="AO15">
-        <v>0.99729761494442914</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP15">
-        <v>49.543726018799653</v>
+        <v>44.092000370450322</v>
       </c>
       <c r="AR15" t="s">
         <v>534</v>
@@ -10729,16 +10729,16 @@
         <v>1156</v>
       </c>
       <c r="BA15" t="s">
+        <v>1217</v>
+      </c>
+      <c r="BB15" t="s">
         <v>1218</v>
       </c>
-      <c r="BB15" t="s">
-        <v>1126</v>
-      </c>
       <c r="BC15">
-        <v>0.99418931598784899</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD15">
-        <v>106.52920688943452</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10803,16 +10803,16 @@
         <v>547</v>
       </c>
       <c r="Y16" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="Z16" t="s">
         <v>774</v>
       </c>
       <c r="AA16">
-        <v>0.98571261124433651</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB16">
-        <v>261.93546052049794</v>
+        <v>90.443352439796072</v>
       </c>
       <c r="AD16" t="s">
         <v>534</v>
@@ -10845,10 +10845,10 @@
         <v>1025</v>
       </c>
       <c r="AO16">
-        <v>0.996795372708284</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP16">
-        <v>58.751500348127372</v>
+        <v>138.50582323297994</v>
       </c>
       <c r="AR16" t="s">
         <v>534</v>
@@ -10881,10 +10881,10 @@
         <v>1220</v>
       </c>
       <c r="BC16">
-        <v>0.99834679070917032</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD16">
-        <v>30.308836998544216</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10949,16 +10949,16 @@
         <v>549</v>
       </c>
       <c r="Y17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Z17" t="s">
         <v>775</v>
       </c>
       <c r="AA17">
-        <v>0.9849019911873127</v>
+        <v>0.97537853020161625</v>
       </c>
       <c r="AB17">
-        <v>276.79682823259958</v>
+        <v>451.39361297036953</v>
       </c>
       <c r="AD17" t="s">
         <v>534</v>
@@ -10988,13 +10988,13 @@
         <v>1026</v>
       </c>
       <c r="AN17" t="s">
-        <v>1027</v>
+        <v>775</v>
       </c>
       <c r="AO17">
-        <v>0.99274560110857168</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP17">
-        <v>132.99731300951822</v>
+        <v>473.60023862765331</v>
       </c>
       <c r="AR17" t="s">
         <v>534</v>
@@ -11027,10 +11027,10 @@
         <v>1222</v>
       </c>
       <c r="BC17">
-        <v>0.99401640271965719</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD17">
-        <v>109.69928347295183</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11095,16 +11095,16 @@
         <v>551</v>
       </c>
       <c r="Y18" t="s">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="Z18" t="s">
         <v>776</v>
       </c>
       <c r="AA18">
-        <v>0.99157679714615166</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB18">
-        <v>154.42538565388551</v>
+        <v>106.82211818572355</v>
       </c>
       <c r="AD18" t="s">
         <v>534</v>
@@ -11131,16 +11131,16 @@
         <v>890</v>
       </c>
       <c r="AM18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AN18" t="s">
         <v>1028</v>
       </c>
-      <c r="AN18" t="s">
-        <v>1029</v>
-      </c>
       <c r="AO18">
-        <v>0.99684152237002188</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP18">
-        <v>57.905423216266421</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR18" t="s">
         <v>534</v>
@@ -11173,10 +11173,10 @@
         <v>1224</v>
       </c>
       <c r="BC18">
-        <v>0.98574436213546524</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD18">
-        <v>261.35336084980423</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11241,16 +11241,16 @@
         <v>553</v>
       </c>
       <c r="Y19" t="s">
-        <v>515</v>
+        <v>429</v>
       </c>
       <c r="Z19" t="s">
         <v>777</v>
       </c>
       <c r="AA19">
-        <v>0.99619387577842089</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB19">
-        <v>69.778944062284495</v>
+        <v>62.251070203636829</v>
       </c>
       <c r="AD19" t="s">
         <v>534</v>
@@ -11277,16 +11277,16 @@
         <v>892</v>
       </c>
       <c r="AM19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AN19" t="s">
         <v>1030</v>
       </c>
-      <c r="AN19" t="s">
-        <v>1031</v>
-      </c>
       <c r="AO19">
-        <v>0.99532453653339104</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP19">
-        <v>85.716830221163534</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR19" t="s">
         <v>534</v>
@@ -11319,10 +11319,10 @@
         <v>1226</v>
       </c>
       <c r="BC19">
-        <v>0.98163861082146986</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD19">
-        <v>336.62546827305243</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11387,16 +11387,16 @@
         <v>555</v>
       </c>
       <c r="Y20" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="Z20" t="s">
         <v>778</v>
       </c>
       <c r="AA20">
-        <v>0.99497915241892609</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB20">
-        <v>92.048872319688599</v>
+        <v>54.23617409891024</v>
       </c>
       <c r="AD20" t="s">
         <v>534</v>
@@ -11423,16 +11423,16 @@
         <v>894</v>
       </c>
       <c r="AM20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AN20" t="s">
         <v>1032</v>
       </c>
-      <c r="AN20" t="s">
-        <v>1033</v>
-      </c>
       <c r="AO20">
-        <v>0.99593828267147511</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP20">
-        <v>74.464817689622748</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR20" t="s">
         <v>534</v>
@@ -11465,10 +11465,10 @@
         <v>1228</v>
       </c>
       <c r="BC20">
-        <v>0.95713629889852414</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD20">
-        <v>785.83452019372396</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11533,16 +11533,16 @@
         <v>557</v>
       </c>
       <c r="Y21" t="s">
-        <v>473</v>
+        <v>512</v>
       </c>
       <c r="Z21" t="s">
         <v>779</v>
       </c>
       <c r="AA21">
-        <v>0.97581570155911468</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB21">
-        <v>443.37880474956393</v>
+        <v>154.58276065179118</v>
       </c>
       <c r="AD21" t="s">
         <v>534</v>
@@ -11569,16 +11569,16 @@
         <v>896</v>
       </c>
       <c r="AM21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="AN21" t="s">
         <v>1034</v>
       </c>
-      <c r="AN21" t="s">
-        <v>1035</v>
-      </c>
       <c r="AO21">
-        <v>0.99677419959133018</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP21">
-        <v>59.139674158947656</v>
+        <v>109.31605592223302</v>
       </c>
       <c r="AR21" t="s">
         <v>534</v>
@@ -11611,10 +11611,10 @@
         <v>1230</v>
       </c>
       <c r="BC21">
-        <v>0.98806872821788805</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD21">
-        <v>218.73998267205184</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11679,16 +11679,16 @@
         <v>559</v>
       </c>
       <c r="Y22" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="Z22" t="s">
         <v>780</v>
       </c>
       <c r="AA22">
-        <v>0.99542292233022822</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB22">
-        <v>83.913090612483515</v>
+        <v>49.309812409870183</v>
       </c>
       <c r="AD22" t="s">
         <v>534</v>
@@ -11715,16 +11715,16 @@
         <v>898</v>
       </c>
       <c r="AM22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AN22" t="s">
         <v>1036</v>
       </c>
-      <c r="AN22" t="s">
-        <v>1037</v>
-      </c>
       <c r="AO22">
-        <v>0.99766813121902409</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP22">
-        <v>42.750927651225993</v>
+        <v>163.93514059684662</v>
       </c>
       <c r="AR22" t="s">
         <v>534</v>
@@ -11754,13 +11754,13 @@
         <v>1231</v>
       </c>
       <c r="BB22" t="s">
-        <v>1230</v>
+        <v>1099</v>
       </c>
       <c r="BC22">
-        <v>0.99203097418485064</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD22">
-        <v>146.09880661107059</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11825,16 +11825,16 @@
         <v>561</v>
       </c>
       <c r="Y23" t="s">
-        <v>450</v>
+        <v>514</v>
       </c>
       <c r="Z23" t="s">
         <v>781</v>
       </c>
       <c r="AA23">
-        <v>0.99647584863086869</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB23">
-        <v>64.60944176740837</v>
+        <v>121.27899510281891</v>
       </c>
       <c r="AD23" t="s">
         <v>534</v>
@@ -11861,16 +11861,16 @@
         <v>900</v>
       </c>
       <c r="AM23" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AN23" t="s">
         <v>1038</v>
       </c>
-      <c r="AN23" t="s">
-        <v>1039</v>
-      </c>
       <c r="AO23">
-        <v>0.99760247912344124</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP23">
-        <v>43.95454940357709</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR23" t="s">
         <v>534</v>
@@ -11903,10 +11903,10 @@
         <v>1233</v>
       </c>
       <c r="BC23">
-        <v>0.97821242976023937</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD23">
-        <v>399.43878772894504</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11971,16 +11971,16 @@
         <v>563</v>
       </c>
       <c r="Y24" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="Z24" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="AA24">
-        <v>0.99780983219878738</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB24">
-        <v>40.153076355563911</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD24" t="s">
         <v>534</v>
@@ -12007,16 +12007,16 @@
         <v>902</v>
       </c>
       <c r="AM24" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AN24" t="s">
         <v>1040</v>
       </c>
-      <c r="AN24" t="s">
-        <v>1041</v>
-      </c>
       <c r="AO24">
-        <v>0.99336049451151065</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP24">
-        <v>121.72426728897108</v>
+        <v>85.270745539791065</v>
       </c>
       <c r="AR24" t="s">
         <v>534</v>
@@ -12049,10 +12049,10 @@
         <v>1235</v>
       </c>
       <c r="BC24">
-        <v>0.99665799830099</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD24">
-        <v>61.270031148516708</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12117,16 +12117,16 @@
         <v>565</v>
       </c>
       <c r="Y25" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="Z25" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AA25">
-        <v>0.99724696581141214</v>
+        <v>0.99726809134187266</v>
       </c>
       <c r="AB25">
-        <v>50.472293457444586</v>
+        <v>50.0849920656675</v>
       </c>
       <c r="AD25" t="s">
         <v>534</v>
@@ -12153,16 +12153,16 @@
         <v>904</v>
       </c>
       <c r="AM25" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AN25" t="s">
         <v>1042</v>
       </c>
-      <c r="AN25" t="s">
-        <v>1043</v>
-      </c>
       <c r="AO25">
-        <v>0.99759498179797546</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP25">
-        <v>44.092000370450322</v>
+        <v>101.57889622275951</v>
       </c>
       <c r="AR25" t="s">
         <v>534</v>
@@ -12195,10 +12195,10 @@
         <v>1237</v>
       </c>
       <c r="BC25">
-        <v>0.96863461872110523</v>
+        <v>0.99526086651282741</v>
       </c>
       <c r="BD25">
-        <v>575.0319901130714</v>
+        <v>86.884113931497708</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12263,16 +12263,16 @@
         <v>567</v>
       </c>
       <c r="Y26" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="Z26" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AA26">
-        <v>0.99589550629055523</v>
+        <v>0.97962408753770291</v>
       </c>
       <c r="AB26">
-        <v>75.249051339820184</v>
+        <v>373.55839514211272</v>
       </c>
       <c r="AD26" t="s">
         <v>534</v>
@@ -12299,16 +12299,16 @@
         <v>906</v>
       </c>
       <c r="AM26" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AN26" t="s">
         <v>1044</v>
       </c>
-      <c r="AN26" t="s">
-        <v>1045</v>
-      </c>
       <c r="AO26">
-        <v>0.99503039970536677</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP26">
-        <v>91.109338734942796</v>
+        <v>69.94080431866837</v>
       </c>
       <c r="AR26" t="s">
         <v>534</v>
@@ -12338,13 +12338,13 @@
         <v>1238</v>
       </c>
       <c r="BB26" t="s">
-        <v>1108</v>
+        <v>1239</v>
       </c>
       <c r="BC26">
-        <v>0.99098965084511315</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD26">
-        <v>165.18973450625904</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12409,16 +12409,16 @@
         <v>569</v>
       </c>
       <c r="Y27" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="Z27" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AA27">
-        <v>0.99531156065644533</v>
+        <v>0.99098167665935155</v>
       </c>
       <c r="AB27">
-        <v>85.954721298502818</v>
+        <v>165.33592791188894</v>
       </c>
       <c r="AD27" t="s">
         <v>534</v>
@@ -12445,16 +12445,16 @@
         <v>908</v>
       </c>
       <c r="AM27" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AN27" t="s">
         <v>1046</v>
       </c>
-      <c r="AN27" t="s">
-        <v>1047</v>
-      </c>
       <c r="AO27">
-        <v>0.99544059907537386</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP27">
-        <v>83.589016951479763</v>
+        <v>53.069246900976879</v>
       </c>
       <c r="AR27" t="s">
         <v>534</v>
@@ -12481,16 +12481,16 @@
         <v>1180</v>
       </c>
       <c r="BA27" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="BB27" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="BC27">
-        <v>0.99053278045305837</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD27">
-        <v>173.56569169392964</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12555,16 +12555,16 @@
         <v>571</v>
       </c>
       <c r="Y28" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="Z28" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AA28">
-        <v>0.99706825374988217</v>
+        <v>0.98485684158558628</v>
       </c>
       <c r="AB28">
-        <v>53.748681252160438</v>
+        <v>277.62457093091871</v>
       </c>
       <c r="AD28" t="s">
         <v>534</v>
@@ -12591,16 +12591,16 @@
         <v>910</v>
       </c>
       <c r="AM28" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AN28" t="s">
         <v>1048</v>
       </c>
-      <c r="AN28" t="s">
-        <v>1049</v>
-      </c>
       <c r="AO28">
-        <v>0.98829989485605374</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP28">
-        <v>214.50192763901472</v>
+        <v>341.91992986513412</v>
       </c>
       <c r="AR28" t="s">
         <v>534</v>
@@ -12627,16 +12627,16 @@
         <v>1182</v>
       </c>
       <c r="BA28" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="BB28" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="BC28">
-        <v>0.98488330873784669</v>
+        <v>0.99563011519444145</v>
       </c>
       <c r="BD28">
-        <v>277.13933980614473</v>
+        <v>80.114554768572972</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12701,16 +12701,16 @@
         <v>573</v>
       </c>
       <c r="Y29" t="s">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="Z29" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AA29">
-        <v>0.96520767961718001</v>
+        <v>0.98211145389932475</v>
       </c>
       <c r="AB29">
-        <v>637.85920701836687</v>
+        <v>327.95667851237977</v>
       </c>
       <c r="AD29" t="s">
         <v>534</v>
@@ -12737,16 +12737,16 @@
         <v>912</v>
       </c>
       <c r="AM29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AN29" t="s">
         <v>1050</v>
       </c>
-      <c r="AN29" t="s">
-        <v>1051</v>
-      </c>
       <c r="AO29">
-        <v>0.98134982200735632</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP29">
-        <v>341.91992986513412</v>
+        <v>258.57410995127316</v>
       </c>
       <c r="AR29" t="s">
         <v>534</v>
@@ -12773,16 +12773,16 @@
         <v>1184</v>
       </c>
       <c r="BA29" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="BB29" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="BC29">
-        <v>0.99526086651282741</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD29">
-        <v>86.884113931497708</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12847,16 +12847,16 @@
         <v>575</v>
       </c>
       <c r="Y30" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="Z30" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AA30">
-        <v>0.99344074878931121</v>
+        <v>0.99654205356515035</v>
       </c>
       <c r="AB30">
-        <v>120.25293886262826</v>
+        <v>63.395684638909763</v>
       </c>
       <c r="AD30" t="s">
         <v>534</v>
@@ -12883,16 +12883,16 @@
         <v>914</v>
       </c>
       <c r="AM30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AN30" t="s">
         <v>1052</v>
       </c>
-      <c r="AN30" t="s">
-        <v>1053</v>
-      </c>
       <c r="AO30">
-        <v>0.98589595763902149</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP30">
-        <v>258.57410995127316</v>
+        <v>40.90273458067751</v>
       </c>
       <c r="AR30" t="s">
         <v>534</v>
@@ -12919,16 +12919,16 @@
         <v>1186</v>
       </c>
       <c r="BA30" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="BB30" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="BC30">
-        <v>0.99232494426983575</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD30">
-        <v>140.70935505301131</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12993,16 +12993,16 @@
         <v>577</v>
       </c>
       <c r="Y31" t="s">
-        <v>499</v>
+        <v>460</v>
       </c>
       <c r="Z31" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="AA31">
-        <v>0.99459650548991607</v>
+        <v>0.99504817442297822</v>
       </c>
       <c r="AB31">
-        <v>99.064066018204684</v>
+        <v>90.78346891206678</v>
       </c>
       <c r="AD31" t="s">
         <v>534</v>
@@ -13029,16 +13029,16 @@
         <v>916</v>
       </c>
       <c r="AM31" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AN31" t="s">
         <v>1054</v>
       </c>
-      <c r="AN31" t="s">
-        <v>1055</v>
-      </c>
       <c r="AO31">
-        <v>0.99776894175014486</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP31">
-        <v>40.90273458067751</v>
+        <v>74.530739771815789</v>
       </c>
       <c r="AR31" t="s">
         <v>534</v>
@@ -13065,16 +13065,16 @@
         <v>1188</v>
       </c>
       <c r="BA31" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="BB31" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="BC31">
-        <v>0.98775115723917273</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD31">
-        <v>224.56211728183334</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13139,16 +13139,16 @@
         <v>579</v>
       </c>
       <c r="Y32" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="Z32" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="AA32">
-        <v>0.99655727877565281</v>
+        <v>0.99470247457730832</v>
       </c>
       <c r="AB32">
-        <v>63.116555779697698</v>
+        <v>97.121299416014665</v>
       </c>
       <c r="AD32" t="s">
         <v>534</v>
@@ -13175,16 +13175,16 @@
         <v>918</v>
       </c>
       <c r="AM32" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AN32" t="s">
         <v>1056</v>
       </c>
-      <c r="AN32" t="s">
-        <v>1057</v>
-      </c>
       <c r="AO32">
-        <v>0.9959346869215373</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP32">
-        <v>74.530739771815789</v>
+        <v>546.30069964051177</v>
       </c>
       <c r="AR32" t="s">
         <v>534</v>
@@ -13211,16 +13211,16 @@
         <v>1190</v>
       </c>
       <c r="BA32" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="BB32" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="BC32">
-        <v>0.98890025255868685</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD32">
-        <v>203.49536975740753</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13285,16 +13285,16 @@
         <v>581</v>
       </c>
       <c r="Y33" t="s">
-        <v>488</v>
+        <v>463</v>
       </c>
       <c r="Z33" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AA33">
-        <v>0.99221351039035977</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB33">
-        <v>142.75230951007163</v>
+        <v>82.539922240185263</v>
       </c>
       <c r="AD33" t="s">
         <v>534</v>
@@ -13321,16 +13321,16 @@
         <v>920</v>
       </c>
       <c r="AM33" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AN33" t="s">
         <v>1058</v>
       </c>
-      <c r="AN33" t="s">
-        <v>1059</v>
-      </c>
       <c r="AO33">
-        <v>0.99403730604060547</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP33">
-        <v>109.31605592223302</v>
+        <v>56.159977027506663</v>
       </c>
       <c r="AR33" t="s">
         <v>534</v>
@@ -13357,16 +13357,16 @@
         <v>1192</v>
       </c>
       <c r="BA33" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="BB33" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="BC33">
-        <v>0.99481196273061234</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD33">
-        <v>95.114016605440895</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13431,16 +13431,16 @@
         <v>583</v>
       </c>
       <c r="Y34" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="Z34" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="AA34">
-        <v>0.99067174034238459</v>
+        <v>0.9621480095608167</v>
       </c>
       <c r="AB34">
-        <v>171.01809372294977</v>
+        <v>693.95315805169378</v>
       </c>
       <c r="AD34" t="s">
         <v>534</v>
@@ -13467,16 +13467,16 @@
         <v>922</v>
       </c>
       <c r="AM34" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AN34" t="s">
         <v>1060</v>
       </c>
-      <c r="AN34" t="s">
-        <v>1061</v>
-      </c>
       <c r="AO34">
-        <v>0.99105808324017197</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP34">
-        <v>163.93514059684662</v>
+        <v>95.557874766001078</v>
       </c>
       <c r="AR34" t="s">
         <v>534</v>
@@ -13503,16 +13503,16 @@
         <v>1194</v>
       </c>
       <c r="BA34" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="BB34" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="BC34">
-        <v>0.99374755699184159</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD34">
-        <v>114.62812181623703</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13577,16 +13577,16 @@
         <v>585</v>
       </c>
       <c r="Y35" t="s">
-        <v>418</v>
+        <v>479</v>
       </c>
       <c r="Z35" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="AA35">
-        <v>0.99634417822754895</v>
+        <v>0.98916941127667946</v>
       </c>
       <c r="AB35">
-        <v>67.023399161603095</v>
+        <v>198.56079326087576</v>
       </c>
       <c r="AD35" t="s">
         <v>534</v>
@@ -13613,16 +13613,16 @@
         <v>924</v>
       </c>
       <c r="AM35" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AN35" t="s">
-        <v>1063</v>
+        <v>851</v>
       </c>
       <c r="AO35">
-        <v>0.9974675531234084</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP35">
-        <v>46.428192737512276</v>
+        <v>819.02093721560016</v>
       </c>
       <c r="AR35" t="s">
         <v>534</v>
@@ -13649,16 +13649,16 @@
         <v>1196</v>
       </c>
       <c r="BA35" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="BB35" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="BC35">
-        <v>0.99054926914187857</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD35">
-        <v>173.26339906555947</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13723,16 +13723,16 @@
         <v>587</v>
       </c>
       <c r="Y36" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="Z36" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="AA36">
-        <v>0.98416341622871006</v>
+        <v>0.97159134368321343</v>
       </c>
       <c r="AB36">
-        <v>290.33736914031488</v>
+        <v>520.82536580775354</v>
       </c>
       <c r="AD36" t="s">
         <v>534</v>
@@ -13759,16 +13759,16 @@
         <v>926</v>
       </c>
       <c r="AM36" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="AN36" t="s">
-        <v>1065</v>
+        <v>798</v>
       </c>
       <c r="AO36">
-        <v>0.99534886842510228</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP36">
-        <v>85.270745539791065</v>
+        <v>256.69809569401372</v>
       </c>
       <c r="AR36" t="s">
         <v>534</v>
@@ -13795,16 +13795,16 @@
         <v>1198</v>
       </c>
       <c r="BA36" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="BB36" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="BC36">
-        <v>0.98027195861782945</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD36">
-        <v>361.68075867312689</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13869,16 +13869,16 @@
         <v>589</v>
       </c>
       <c r="Y37" t="s">
-        <v>497</v>
+        <v>449</v>
       </c>
       <c r="Z37" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="AA37">
-        <v>0.99563792883070867</v>
+        <v>0.99359614530212825</v>
       </c>
       <c r="AB37">
-        <v>79.971304770340467</v>
+        <v>117.40400279431638</v>
       </c>
       <c r="AD37" t="s">
         <v>534</v>
@@ -13905,16 +13905,16 @@
         <v>928</v>
       </c>
       <c r="AM37" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="AN37" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="AO37">
-        <v>0.97651207122624506</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP37">
-        <v>430.61202751883985</v>
+        <v>184.02231422223667</v>
       </c>
       <c r="AR37" t="s">
         <v>534</v>
@@ -13941,16 +13941,16 @@
         <v>1200</v>
       </c>
       <c r="BA37" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="BB37" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="BC37">
-        <v>0.98125520899414764</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD37">
-        <v>343.65450177395917</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14015,16 +14015,16 @@
         <v>591</v>
       </c>
       <c r="Y38" t="s">
-        <v>432</v>
+        <v>518</v>
       </c>
       <c r="Z38" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="AA38">
-        <v>0.99558181127270129</v>
+        <v>0.99488082982009873</v>
       </c>
       <c r="AB38">
-        <v>81.000126667143434</v>
+        <v>93.851453298190577</v>
       </c>
       <c r="AD38" t="s">
         <v>534</v>
@@ -14051,16 +14051,16 @@
         <v>930</v>
       </c>
       <c r="AM38" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="AN38" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="AO38">
-        <v>0.9972012891192491</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP38">
-        <v>51.309699480432613</v>
+        <v>69.568618111619969</v>
       </c>
       <c r="AR38" t="s">
         <v>534</v>
@@ -14087,16 +14087,16 @@
         <v>1202</v>
       </c>
       <c r="BA38" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="BB38" t="s">
-        <v>1262</v>
+        <v>1228</v>
       </c>
       <c r="BC38">
-        <v>0.98946506962487613</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD38">
-        <v>193.14039021060518</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14161,16 +14161,16 @@
         <v>593</v>
       </c>
       <c r="Y39" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Z39" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="AA39">
-        <v>0.99390501557434718</v>
+        <v>0.99557743229498485</v>
       </c>
       <c r="AB39">
-        <v>111.7413811369688</v>
+        <v>81.080407925277868</v>
       </c>
       <c r="AD39" t="s">
         <v>534</v>
@@ -14197,16 +14197,16 @@
         <v>932</v>
       </c>
       <c r="AM39" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="AN39" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="AO39">
-        <v>0.99648541839873139</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP39">
-        <v>64.433996023258757</v>
+        <v>114.668395037126</v>
       </c>
       <c r="AR39" t="s">
         <v>534</v>
@@ -14239,10 +14239,10 @@
         <v>1264</v>
       </c>
       <c r="BC39">
-        <v>0.99314574070258299</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD39">
-        <v>125.66142045264445</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14307,16 +14307,16 @@
         <v>595</v>
       </c>
       <c r="Y40" t="s">
-        <v>526</v>
+        <v>455</v>
       </c>
       <c r="Z40" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="AA40">
-        <v>0.93980266520001188</v>
+        <v>0.99401156108202648</v>
       </c>
       <c r="AB40">
-        <v>1103.617804666449</v>
+        <v>109.78804682951412</v>
       </c>
       <c r="AD40" t="s">
         <v>534</v>
@@ -14343,16 +14343,16 @@
         <v>934</v>
       </c>
       <c r="AM40" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="AN40" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="AO40">
-        <v>0.9976540150806753</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP40">
-        <v>43.009723520953628</v>
+        <v>58.41269784431158</v>
       </c>
       <c r="AR40" t="s">
         <v>534</v>
@@ -14385,10 +14385,10 @@
         <v>1266</v>
       </c>
       <c r="BC40">
-        <v>0.9959052853503485</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD40">
-        <v>75.06976857694373</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14453,16 +14453,16 @@
         <v>597</v>
       </c>
       <c r="Y41" t="s">
-        <v>530</v>
+        <v>476</v>
       </c>
       <c r="Z41" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="AA41">
-        <v>0.95679935803281835</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB41">
-        <v>792.01176939833033</v>
+        <v>129.18226807514921</v>
       </c>
       <c r="AD41" t="s">
         <v>534</v>
@@ -14489,16 +14489,16 @@
         <v>936</v>
       </c>
       <c r="AM41" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="AN41" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="AO41">
-        <v>0.99644815774097173</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP41">
-        <v>65.117108082185538</v>
+        <v>86.673039153654699</v>
       </c>
       <c r="AR41" t="s">
         <v>534</v>
@@ -14531,10 +14531,10 @@
         <v>1268</v>
       </c>
       <c r="BC41">
-        <v>0.99563011519444145</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD41">
-        <v>80.114554768572972</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14599,16 +14599,16 @@
         <v>599</v>
       </c>
       <c r="Y42" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="Z42" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="AA42">
-        <v>0.98761622532712257</v>
+        <v>0.98571261124433651</v>
       </c>
       <c r="AB42">
-        <v>227.03586900275366</v>
+        <v>261.93546052049794</v>
       </c>
       <c r="AD42" t="s">
         <v>534</v>
@@ -14635,16 +14635,16 @@
         <v>938</v>
       </c>
       <c r="AM42" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="AN42" t="s">
-        <v>798</v>
+        <v>1074</v>
       </c>
       <c r="AO42">
-        <v>0.95532613069733086</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP42">
-        <v>819.02093721560016</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14709,16 +14709,16 @@
         <v>601</v>
       </c>
       <c r="Y43" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="Z43" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="AA43">
-        <v>0.99003402112096806</v>
+        <v>0.9849019911873127</v>
       </c>
       <c r="AB43">
-        <v>182.70961278225187</v>
+        <v>276.79682823259958</v>
       </c>
       <c r="AD43" t="s">
         <v>534</v>
@@ -14745,16 +14745,16 @@
         <v>940</v>
       </c>
       <c r="AM43" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="AN43" t="s">
-        <v>775</v>
+        <v>1076</v>
       </c>
       <c r="AO43">
-        <v>0.98599828568941739</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP43">
-        <v>256.69809569401372</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14819,16 +14819,16 @@
         <v>603</v>
       </c>
       <c r="Y44" t="s">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="Z44" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="AA44">
-        <v>0.99466062705491098</v>
+        <v>0.99157679714615166</v>
       </c>
       <c r="AB44">
-        <v>97.888503993298116</v>
+        <v>154.42538565388551</v>
       </c>
       <c r="AD44" t="s">
         <v>534</v>
@@ -14855,16 +14855,16 @@
         <v>942</v>
       </c>
       <c r="AM44" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AN44" t="s">
         <v>1078</v>
       </c>
-      <c r="AN44" t="s">
-        <v>1079</v>
-      </c>
       <c r="AO44">
-        <v>0.98996241922424166</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP44">
-        <v>184.02231422223667</v>
+        <v>82.249649925934918</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14929,16 +14929,16 @@
         <v>605</v>
       </c>
       <c r="Y45" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="Z45" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AA45">
-        <v>0.9944598150968682</v>
+        <v>0.99619387577842089</v>
       </c>
       <c r="AB45">
-        <v>101.5700565574154</v>
+        <v>69.778944062284495</v>
       </c>
       <c r="AD45" t="s">
         <v>534</v>
@@ -14965,16 +14965,16 @@
         <v>944</v>
       </c>
       <c r="AM45" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AN45" t="s">
         <v>1080</v>
       </c>
-      <c r="AN45" t="s">
-        <v>1081</v>
-      </c>
       <c r="AO45">
-        <v>0.99620534810300254</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP45">
-        <v>69.568618111619969</v>
+        <v>81.597153048545437</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15039,16 +15039,16 @@
         <v>607</v>
       </c>
       <c r="Y46" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="Z46" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="AA46">
-        <v>0.99494501873633134</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB46">
-        <v>92.674656500591539</v>
+        <v>92.048872319688599</v>
       </c>
       <c r="AD46" t="s">
         <v>534</v>
@@ -15075,16 +15075,16 @@
         <v>946</v>
       </c>
       <c r="AM46" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AN46" t="s">
         <v>1082</v>
       </c>
-      <c r="AN46" t="s">
-        <v>1083</v>
-      </c>
       <c r="AO46">
-        <v>0.99374536027070226</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP46">
-        <v>114.668395037126</v>
+        <v>168.11001279983091</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15149,16 +15149,16 @@
         <v>609</v>
       </c>
       <c r="Y47" t="s">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="Z47" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AA47">
-        <v>0.99438812565699364</v>
+        <v>0.9914627894548943</v>
       </c>
       <c r="AB47">
-        <v>102.88436295511657</v>
+        <v>156.51552666027055</v>
       </c>
       <c r="AD47" t="s">
         <v>534</v>
@@ -15185,16 +15185,16 @@
         <v>948</v>
       </c>
       <c r="AM47" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AN47" t="s">
         <v>1084</v>
       </c>
-      <c r="AN47" t="s">
-        <v>1085</v>
-      </c>
       <c r="AO47">
-        <v>0.99681385284485569</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP47">
-        <v>58.41269784431158</v>
+        <v>43.412641259119624</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15259,16 +15259,16 @@
         <v>611</v>
       </c>
       <c r="Y48" t="s">
-        <v>523</v>
+        <v>500</v>
       </c>
       <c r="Z48" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="AA48">
-        <v>0.99643191679577148</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB48">
-        <v>65.414858744189985</v>
+        <v>409.70769939155917</v>
       </c>
       <c r="AD48" t="s">
         <v>534</v>
@@ -15295,16 +15295,16 @@
         <v>950</v>
       </c>
       <c r="AM48" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AN48" t="s">
         <v>1086</v>
       </c>
-      <c r="AN48" t="s">
-        <v>1087</v>
-      </c>
       <c r="AO48">
-        <v>0.99527237968252791</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP48">
-        <v>86.673039153654699</v>
+        <v>105.47547991621673</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15369,16 +15369,16 @@
         <v>613</v>
       </c>
       <c r="Y49" t="s">
-        <v>469</v>
+        <v>504</v>
       </c>
       <c r="Z49" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="AA49">
-        <v>0.96238190390083644</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB49">
-        <v>689.665095151331</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD49" t="s">
         <v>534</v>
@@ -15405,16 +15405,16 @@
         <v>952</v>
       </c>
       <c r="AM49" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AN49" t="s">
         <v>1088</v>
       </c>
-      <c r="AN49" t="s">
-        <v>1089</v>
-      </c>
       <c r="AO49">
-        <v>0.9917253583369573</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP49">
-        <v>151.70176382244892</v>
+        <v>195.31167947327185</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15479,16 +15479,16 @@
         <v>615</v>
       </c>
       <c r="Y50" t="s">
-        <v>528</v>
+        <v>424</v>
       </c>
       <c r="Z50" t="s">
-        <v>789</v>
+        <v>805</v>
       </c>
       <c r="AA50">
-        <v>0.96316770855847034</v>
+        <v>0.99593583828988941</v>
       </c>
       <c r="AB50">
-        <v>675.25867642804383</v>
+        <v>74.509631352026517</v>
       </c>
       <c r="AD50" t="s">
         <v>534</v>
@@ -15515,16 +15515,16 @@
         <v>954</v>
       </c>
       <c r="AM50" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AN50" t="s">
         <v>1090</v>
       </c>
-      <c r="AN50" t="s">
-        <v>1091</v>
-      </c>
       <c r="AO50">
-        <v>0.99569050067699549</v>
+        <v>0.99499049355022928</v>
       </c>
       <c r="AP50">
-        <v>79.007487588415231</v>
+        <v>91.840951579129481</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15589,16 +15589,16 @@
         <v>617</v>
       </c>
       <c r="Y51" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Z51" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AA51">
-        <v>0.9951089264264793</v>
+        <v>0.98150124893892388</v>
       </c>
       <c r="AB51">
-        <v>89.669682181211982</v>
+        <v>339.14376945306287</v>
       </c>
       <c r="AD51" t="s">
         <v>534</v>
@@ -15625,16 +15625,16 @@
         <v>956</v>
       </c>
       <c r="AM51" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AN51" t="s">
         <v>1092</v>
       </c>
-      <c r="AN51" t="s">
-        <v>1093</v>
-      </c>
       <c r="AO51">
-        <v>0.99567626923235475</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP51">
-        <v>79.268397406829976</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15699,16 +15699,16 @@
         <v>619</v>
       </c>
       <c r="Y52" t="s">
-        <v>434</v>
+        <v>502</v>
       </c>
       <c r="Z52" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AA52">
-        <v>0.98666519734623237</v>
+        <v>0.99523081353776888</v>
       </c>
       <c r="AB52">
-        <v>244.47138198573927</v>
+        <v>87.435085140903482</v>
       </c>
       <c r="AD52" t="s">
         <v>534</v>
@@ -15735,16 +15735,16 @@
         <v>958</v>
       </c>
       <c r="AM52" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AN52" t="s">
         <v>1094</v>
       </c>
-      <c r="AN52" t="s">
-        <v>1095</v>
-      </c>
       <c r="AO52">
-        <v>0.99762284649610655</v>
+        <v>0.99746043308117838</v>
       </c>
       <c r="AP52">
-        <v>43.581147571379539</v>
+        <v>46.558726845063177</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15809,16 +15809,16 @@
         <v>621</v>
       </c>
       <c r="Y53" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="Z53" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AA53">
-        <v>0.99750070245826261</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB53">
-        <v>45.820454931853</v>
+        <v>153.20678909592235</v>
       </c>
       <c r="AD53" t="s">
         <v>534</v>
@@ -15845,16 +15845,16 @@
         <v>960</v>
       </c>
       <c r="AM53" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="AN53" t="s">
-        <v>1097</v>
+        <v>843</v>
       </c>
       <c r="AO53">
-        <v>0.99175391794306234</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP53">
-        <v>151.17817104385733</v>
+        <v>243.0827225935364</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15919,16 +15919,16 @@
         <v>623</v>
       </c>
       <c r="Y54" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z54" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AA54">
-        <v>0.99395341117186964</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB54">
-        <v>110.85412851572337</v>
+        <v>78.81162391526847</v>
       </c>
       <c r="AD54" t="s">
         <v>534</v>
@@ -15955,16 +15955,16 @@
         <v>962</v>
       </c>
       <c r="AM54" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="AN54" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="AO54">
-        <v>0.99688290256322298</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP54">
-        <v>57.146786340912868</v>
+        <v>283.70480651649393</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16029,16 +16029,16 @@
         <v>625</v>
       </c>
       <c r="Y55" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="Z55" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AA55">
-        <v>0.98322732678073066</v>
+        <v>0.99691903985105013</v>
       </c>
       <c r="AB55">
-        <v>307.49900901993823</v>
+        <v>56.484269397415083</v>
       </c>
       <c r="AD55" t="s">
         <v>534</v>
@@ -16065,16 +16065,16 @@
         <v>964</v>
       </c>
       <c r="AM55" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="AN55" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="AO55">
-        <v>0.99488275259079373</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP55">
-        <v>93.81620250211445</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16139,16 +16139,16 @@
         <v>627</v>
       </c>
       <c r="Y56" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="Z56" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AA56">
-        <v>0.9974199781412052</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB56">
-        <v>47.300400744571718</v>
+        <v>263.42178867339101</v>
       </c>
       <c r="AD56" t="s">
         <v>534</v>
@@ -16175,16 +16175,16 @@
         <v>966</v>
       </c>
       <c r="AM56" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AN56" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="AO56">
-        <v>0.99663220850609069</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP56">
-        <v>61.742844055003644</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16249,16 +16249,16 @@
         <v>629</v>
       </c>
       <c r="Y57" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="Z57" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AA57">
-        <v>0.99336837071349593</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB57">
-        <v>121.57987025257442</v>
+        <v>86.308558527470979</v>
       </c>
       <c r="AD57" t="s">
         <v>534</v>
@@ -16285,16 +16285,16 @@
         <v>968</v>
       </c>
       <c r="AM57" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="AN57" t="s">
-        <v>770</v>
+        <v>1103</v>
       </c>
       <c r="AO57">
-        <v>0.98674094240398891</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP57">
-        <v>243.0827225935364</v>
+        <v>430.61202751883985</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16359,16 +16359,16 @@
         <v>631</v>
       </c>
       <c r="Y58" t="s">
-        <v>443</v>
+        <v>511</v>
       </c>
       <c r="Z58" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AA58">
-        <v>0.99379477670057537</v>
+        <v>0.99443562760718263</v>
       </c>
       <c r="AB58">
-        <v>113.7624271561186</v>
+        <v>102.01349386831856</v>
       </c>
       <c r="AD58" t="s">
         <v>534</v>
@@ -16395,16 +16395,16 @@
         <v>970</v>
       </c>
       <c r="AM58" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AN58" t="s">
         <v>1105</v>
       </c>
-      <c r="AN58" t="s">
-        <v>1106</v>
-      </c>
       <c r="AO58">
-        <v>0.98452519237182756</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP58">
-        <v>283.70480651649393</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16469,16 +16469,16 @@
         <v>633</v>
       </c>
       <c r="Y59" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="Z59" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AA59">
-        <v>0.9961866142254362</v>
+        <v>0.99553066735440277</v>
       </c>
       <c r="AB59">
-        <v>69.91207253366963</v>
+        <v>81.937765169281747</v>
       </c>
       <c r="AD59" t="s">
         <v>534</v>
@@ -16505,16 +16505,16 @@
         <v>972</v>
       </c>
       <c r="AM59" t="s">
+        <v>1106</v>
+      </c>
+      <c r="AN59" t="s">
         <v>1107</v>
       </c>
-      <c r="AN59" t="s">
-        <v>1108</v>
-      </c>
       <c r="AO59">
-        <v>0.99679967385551038</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP59">
-        <v>58.672645982308907</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16579,16 +16579,16 @@
         <v>635</v>
       </c>
       <c r="Y60" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="Z60" t="s">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="AA60">
-        <v>0.9621480095608167</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB60">
-        <v>693.95315805169378</v>
+        <v>174.28740880058183</v>
       </c>
       <c r="AD60" t="s">
         <v>534</v>
@@ -16615,16 +16615,16 @@
         <v>974</v>
       </c>
       <c r="AM60" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AN60" t="s">
         <v>1109</v>
       </c>
-      <c r="AN60" t="s">
-        <v>1110</v>
-      </c>
       <c r="AO60">
-        <v>0.99414234808301016</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP60">
-        <v>107.39028514481463</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16689,16 +16689,16 @@
         <v>637</v>
       </c>
       <c r="Y61" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
       <c r="Z61" t="s">
         <v>816</v>
       </c>
       <c r="AA61">
-        <v>0.98916941127667946</v>
+        <v>0.99575157784901702</v>
       </c>
       <c r="AB61">
-        <v>198.56079326087576</v>
+        <v>77.887739434686992</v>
       </c>
       <c r="AD61" t="s">
         <v>534</v>
@@ -16725,16 +16725,16 @@
         <v>976</v>
       </c>
       <c r="AM61" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AN61" t="s">
         <v>1111</v>
       </c>
-      <c r="AN61" t="s">
-        <v>1112</v>
-      </c>
       <c r="AO61">
-        <v>0.99551365545858539</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP61">
-        <v>82.249649925934918</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16799,16 +16799,16 @@
         <v>639</v>
       </c>
       <c r="Y62" t="s">
-        <v>438</v>
+        <v>529</v>
       </c>
       <c r="Z62" t="s">
         <v>817</v>
       </c>
       <c r="AA62">
-        <v>0.97159134368321343</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB62">
-        <v>520.82536580775354</v>
+        <v>637.85920701836687</v>
       </c>
       <c r="AD62" t="s">
         <v>534</v>
@@ -16835,16 +16835,16 @@
         <v>978</v>
       </c>
       <c r="AM62" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AN62" t="s">
         <v>1113</v>
       </c>
-      <c r="AN62" t="s">
-        <v>1114</v>
-      </c>
       <c r="AO62">
-        <v>0.99554924619735208</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP62">
-        <v>81.597153048545437</v>
+        <v>57.905423216266421</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16909,16 +16909,16 @@
         <v>641</v>
       </c>
       <c r="Y63" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="Z63" t="s">
         <v>818</v>
       </c>
       <c r="AA63">
-        <v>0.99359614530212825</v>
+        <v>0.99344074878931121</v>
       </c>
       <c r="AB63">
-        <v>117.40400279431638</v>
+        <v>120.25293886262826</v>
       </c>
       <c r="AD63" t="s">
         <v>534</v>
@@ -16945,16 +16945,16 @@
         <v>980</v>
       </c>
       <c r="AM63" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AN63" t="s">
         <v>1115</v>
       </c>
-      <c r="AN63" t="s">
-        <v>1116</v>
-      </c>
       <c r="AO63">
-        <v>0.99083036293819104</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP63">
-        <v>168.11001279983091</v>
+        <v>85.716830221163534</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17019,16 +17019,16 @@
         <v>643</v>
       </c>
       <c r="Y64" t="s">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="Z64" t="s">
-        <v>819</v>
+        <v>783</v>
       </c>
       <c r="AA64">
-        <v>0.99488082982009873</v>
+        <v>0.99459650548991607</v>
       </c>
       <c r="AB64">
-        <v>93.851453298190577</v>
+        <v>99.064066018204684</v>
       </c>
       <c r="AD64" t="s">
         <v>534</v>
@@ -17055,16 +17055,16 @@
         <v>982</v>
       </c>
       <c r="AM64" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AN64" t="s">
         <v>1117</v>
       </c>
-      <c r="AN64" t="s">
-        <v>1118</v>
-      </c>
       <c r="AO64">
-        <v>0.9976320377495026</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP64">
-        <v>43.412641259119624</v>
+        <v>74.464817689622748</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17129,16 +17129,16 @@
         <v>645</v>
       </c>
       <c r="Y65" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="Z65" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AA65">
-        <v>0.99557743229498485</v>
+        <v>0.99655727877565281</v>
       </c>
       <c r="AB65">
-        <v>81.080407925277868</v>
+        <v>63.116555779697698</v>
       </c>
       <c r="AD65" t="s">
         <v>534</v>
@@ -17165,16 +17165,16 @@
         <v>984</v>
       </c>
       <c r="AM65" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AN65" t="s">
         <v>1119</v>
       </c>
-      <c r="AN65" t="s">
-        <v>1120</v>
-      </c>
       <c r="AO65">
-        <v>0.99424679200457</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP65">
-        <v>105.47547991621673</v>
+        <v>96.528578181196991</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17239,16 +17239,16 @@
         <v>647</v>
       </c>
       <c r="Y66" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="Z66" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AA66">
-        <v>0.99401156108202648</v>
+        <v>0.99221351039035977</v>
       </c>
       <c r="AB66">
-        <v>109.78804682951412</v>
+        <v>142.75230951007163</v>
       </c>
       <c r="AD66" t="s">
         <v>534</v>
@@ -17275,16 +17275,16 @@
         <v>986</v>
       </c>
       <c r="AM66" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AN66" t="s">
         <v>1121</v>
       </c>
-      <c r="AN66" t="s">
-        <v>1122</v>
-      </c>
       <c r="AO66">
-        <v>0.98934663566509429</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP66">
-        <v>195.31167947327185</v>
+        <v>49.543726018799653</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17349,16 +17349,16 @@
         <v>649</v>
       </c>
       <c r="Y67" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="Z67" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="AA67">
-        <v>0.96942910386940295</v>
+        <v>0.99067174034238459</v>
       </c>
       <c r="AB67">
-        <v>560.46642906094564</v>
+        <v>171.01809372294977</v>
       </c>
       <c r="AD67" t="s">
         <v>534</v>
@@ -17385,16 +17385,16 @@
         <v>988</v>
       </c>
       <c r="AM67" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AN67" t="s">
         <v>1123</v>
       </c>
-      <c r="AN67" t="s">
-        <v>1124</v>
-      </c>
       <c r="AO67">
-        <v>0.99499049355022928</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP67">
-        <v>91.840951579129481</v>
+        <v>58.751500348127372</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17459,16 +17459,16 @@
         <v>651</v>
       </c>
       <c r="Y68" t="s">
-        <v>477</v>
+        <v>418</v>
       </c>
       <c r="Z68" t="s">
         <v>822</v>
       </c>
       <c r="AA68">
-        <v>0.99726809134187266</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB68">
-        <v>50.0849920656675</v>
+        <v>67.023399161603095</v>
       </c>
       <c r="AD68" t="s">
         <v>534</v>
@@ -17495,16 +17495,16 @@
         <v>990</v>
       </c>
       <c r="AM68" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AN68" t="s">
         <v>1125</v>
       </c>
-      <c r="AN68" t="s">
-        <v>1126</v>
-      </c>
       <c r="AO68">
-        <v>0.99729205446773184</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP68">
-        <v>49.645668091582088</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17569,16 +17569,16 @@
         <v>653</v>
       </c>
       <c r="Y69" t="s">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="Z69" t="s">
-        <v>789</v>
+        <v>823</v>
       </c>
       <c r="AA69">
-        <v>0.97962408753770291</v>
+        <v>0.98416341622871006</v>
       </c>
       <c r="AB69">
-        <v>373.55839514211272</v>
+        <v>290.33736914031488</v>
       </c>
       <c r="AD69" t="s">
         <v>534</v>
@@ -17605,16 +17605,16 @@
         <v>992</v>
       </c>
       <c r="AM69" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN69" t="s">
         <v>1127</v>
       </c>
-      <c r="AN69" t="s">
-        <v>1128</v>
-      </c>
       <c r="AO69">
-        <v>0.99746043308117838</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP69">
-        <v>46.558726845063177</v>
+        <v>80.747827133859133</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17679,16 +17679,16 @@
         <v>655</v>
       </c>
       <c r="Y70" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z70" t="s">
-        <v>789</v>
+        <v>824</v>
       </c>
       <c r="AA70">
-        <v>0.99098167665935155</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB70">
-        <v>165.33592791188894</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD70" t="s">
         <v>534</v>
@@ -17715,16 +17715,16 @@
         <v>994</v>
       </c>
       <c r="AM70" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AN70" t="s">
         <v>1129</v>
       </c>
-      <c r="AN70" t="s">
-        <v>1130</v>
-      </c>
       <c r="AO70">
-        <v>0.97020178001960844</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP70">
-        <v>546.30069964051177</v>
+        <v>60.189444792275019</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17789,16 +17789,16 @@
         <v>657</v>
       </c>
       <c r="Y71" t="s">
-        <v>503</v>
+        <v>432</v>
       </c>
       <c r="Z71" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="AA71">
-        <v>0.98485684158558628</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB71">
-        <v>277.62457093091871</v>
+        <v>81.000126667143434</v>
       </c>
       <c r="AD71" t="s">
         <v>534</v>
@@ -17825,16 +17825,16 @@
         <v>996</v>
       </c>
       <c r="AM71" t="s">
+        <v>1130</v>
+      </c>
+      <c r="AN71" t="s">
         <v>1131</v>
       </c>
-      <c r="AN71" t="s">
-        <v>1132</v>
-      </c>
       <c r="AO71">
-        <v>0.99693672852577231</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP71">
-        <v>56.159977027506663</v>
+        <v>79.268397406829976</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17899,16 +17899,16 @@
         <v>659</v>
       </c>
       <c r="Y72" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="Z72" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="AA72">
-        <v>0.98211145389932475</v>
+        <v>0.99390501557434718</v>
       </c>
       <c r="AB72">
-        <v>327.95667851237977</v>
+        <v>111.7413811369688</v>
       </c>
       <c r="AD72" t="s">
         <v>534</v>
@@ -17935,16 +17935,16 @@
         <v>998</v>
       </c>
       <c r="AM72" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AN72" t="s">
         <v>1133</v>
       </c>
-      <c r="AN72" t="s">
-        <v>1134</v>
-      </c>
       <c r="AO72">
-        <v>0.99478775228549088</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP72">
-        <v>95.557874766001078</v>
+        <v>43.581147571379539</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18009,16 +18009,16 @@
         <v>661</v>
       </c>
       <c r="Y73" t="s">
-        <v>467</v>
+        <v>527</v>
       </c>
       <c r="Z73" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AA73">
-        <v>0.99654205356515035</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB73">
-        <v>63.395684638909763</v>
+        <v>868.72862240505196</v>
       </c>
       <c r="AD73" t="s">
         <v>534</v>
@@ -18045,16 +18045,16 @@
         <v>1000</v>
       </c>
       <c r="AM73" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AN73" t="s">
         <v>1135</v>
       </c>
-      <c r="AN73" t="s">
-        <v>1136</v>
-      </c>
       <c r="AO73">
-        <v>0.99244513691456471</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP73">
-        <v>138.50582323297994</v>
+        <v>151.17817104385733</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18119,16 +18119,16 @@
         <v>663</v>
       </c>
       <c r="Y74" t="s">
-        <v>460</v>
+        <v>531</v>
       </c>
       <c r="Z74" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AA74">
-        <v>0.99504817442297822</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB74">
-        <v>90.78346891206678</v>
+        <v>475.8705861429753</v>
       </c>
       <c r="AD74" t="s">
         <v>534</v>
@@ -18155,16 +18155,16 @@
         <v>1002</v>
       </c>
       <c r="AM74" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AN74" t="s">
         <v>1137</v>
       </c>
-      <c r="AN74" t="s">
-        <v>839</v>
-      </c>
       <c r="AO74">
-        <v>0.97416725971121887</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP74">
-        <v>473.60023862765331</v>
+        <v>57.146786340912868</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18229,16 +18229,16 @@
         <v>665</v>
       </c>
       <c r="Y75" t="s">
-        <v>507</v>
+        <v>420</v>
       </c>
       <c r="Z75" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AA75">
-        <v>0.99470247457730832</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB75">
-        <v>97.121299416014665</v>
+        <v>226.88936094280919</v>
       </c>
       <c r="AD75" t="s">
         <v>534</v>
@@ -18271,10 +18271,10 @@
         <v>1139</v>
       </c>
       <c r="AO75">
-        <v>0.99760255773158468</v>
+        <v>0.99488275259079373</v>
       </c>
       <c r="AP75">
-        <v>43.953108254279897</v>
+        <v>93.81620250211445</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18339,16 +18339,16 @@
         <v>667</v>
       </c>
       <c r="Y76" t="s">
-        <v>463</v>
+        <v>505</v>
       </c>
       <c r="Z76" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="AA76">
-        <v>0.99549782242326257</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB76">
-        <v>82.539922240185263</v>
+        <v>224.55764046872929</v>
       </c>
       <c r="AD76" t="s">
         <v>534</v>
@@ -18381,10 +18381,10 @@
         <v>1141</v>
       </c>
       <c r="AO76">
-        <v>0.99352359657507616</v>
+        <v>0.99663220850609069</v>
       </c>
       <c r="AP76">
-        <v>118.7340627902709</v>
+        <v>61.742844055003644</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18449,16 +18449,16 @@
         <v>669</v>
       </c>
       <c r="Y77" t="s">
-        <v>527</v>
+        <v>495</v>
       </c>
       <c r="Z77" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="AA77">
-        <v>0.95261480241426988</v>
+        <v>0.99647006537565563</v>
       </c>
       <c r="AB77">
-        <v>868.72862240505196</v>
+        <v>64.715468112981057</v>
       </c>
       <c r="AD77" t="s">
         <v>534</v>
@@ -18491,10 +18491,10 @@
         <v>1143</v>
       </c>
       <c r="AO77">
-        <v>0.99433447571906541</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP77">
-        <v>103.86794515046822</v>
+        <v>91.109338734942796</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18559,16 +18559,16 @@
         <v>671</v>
       </c>
       <c r="Y78" t="s">
-        <v>531</v>
+        <v>492</v>
       </c>
       <c r="Z78" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="AA78">
-        <v>0.97404342257401955</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB78">
-        <v>475.8705861429753</v>
+        <v>645.26520366712316</v>
       </c>
       <c r="AD78" t="s">
         <v>534</v>
@@ -18601,10 +18601,10 @@
         <v>1145</v>
       </c>
       <c r="AO78">
-        <v>0.9955955730654259</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP78">
-        <v>80.747827133859133</v>
+        <v>83.589016951479763</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18669,16 +18669,16 @@
         <v>673</v>
       </c>
       <c r="Y79" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="Z79" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AA79">
-        <v>0.98762421667584677</v>
+        <v>0.99267004448650609</v>
       </c>
       <c r="AB79">
-        <v>226.88936094280919</v>
+        <v>134.38251774738842</v>
       </c>
       <c r="AD79" t="s">
         <v>534</v>
@@ -18711,10 +18711,10 @@
         <v>1147</v>
       </c>
       <c r="AO79">
-        <v>0.99671693937496686</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP79">
-        <v>60.189444792275019</v>
+        <v>214.50192763901472</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18779,16 +18779,16 @@
         <v>675</v>
       </c>
       <c r="Y80" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="Z80" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AA80">
-        <v>0.98775140142897844</v>
+        <v>0.9948848527457459</v>
       </c>
       <c r="AB80">
-        <v>224.55764046872929</v>
+        <v>93.777699661325343</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18853,16 +18853,16 @@
         <v>677</v>
       </c>
       <c r="Y81" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="Z81" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AA81">
-        <v>0.99647006537565563</v>
+        <v>0.9922030648239526</v>
       </c>
       <c r="AB81">
-        <v>64.715468112981057</v>
+        <v>142.94381156086857</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18927,16 +18927,16 @@
         <v>679</v>
       </c>
       <c r="Y82" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="Z82" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="AA82">
-        <v>0.96480371616361149</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB82">
-        <v>645.26520366712316</v>
+        <v>64.274570700309781</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -19001,16 +19001,16 @@
         <v>681</v>
       </c>
       <c r="Y83" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="Z83" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="AA83">
-        <v>0.99267004448650609</v>
+        <v>0.97907421743006762</v>
       </c>
       <c r="AB83">
-        <v>134.38251774738842</v>
+        <v>383.63934711542669</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -19075,16 +19075,16 @@
         <v>683</v>
       </c>
       <c r="Y84" t="s">
-        <v>519</v>
+        <v>426</v>
       </c>
       <c r="Z84" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AA84">
-        <v>0.9948848527457459</v>
+        <v>0.99558768376711515</v>
       </c>
       <c r="AB84">
-        <v>93.777699661325343</v>
+        <v>80.892464269556413</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -19149,16 +19149,16 @@
         <v>685</v>
       </c>
       <c r="Y85" t="s">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="Z85" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AA85">
-        <v>0.9922030648239526</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB85">
-        <v>142.94381156086857</v>
+        <v>123.82892298254488</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19223,16 +19223,16 @@
         <v>687</v>
       </c>
       <c r="Y86" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="Z86" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="AA86">
-        <v>0.99506672623055659</v>
+        <v>0.99419165427276146</v>
       </c>
       <c r="AB86">
-        <v>90.443352439796072</v>
+        <v>106.48633833270691</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19297,16 +19297,16 @@
         <v>689</v>
       </c>
       <c r="Y87" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="Z87" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="AA87">
-        <v>0.97537853020161625</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB87">
-        <v>451.39361297036953</v>
+        <v>146.8618143486346</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19371,16 +19371,16 @@
         <v>691</v>
       </c>
       <c r="Y88" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="Z88" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="AA88">
-        <v>0.99417333900805149</v>
+        <v>0.99012236069527793</v>
       </c>
       <c r="AB88">
-        <v>106.82211818572355</v>
+        <v>181.09005391990564</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19445,16 +19445,16 @@
         <v>693</v>
       </c>
       <c r="Y89" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="Z89" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AA89">
-        <v>0.99660448707980165</v>
+        <v>0.98990296758392993</v>
       </c>
       <c r="AB89">
-        <v>62.251070203636829</v>
+        <v>185.11226096128556</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19519,16 +19519,16 @@
         <v>695</v>
       </c>
       <c r="Y90" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="Z90" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AA90">
-        <v>0.99704166323096854</v>
+        <v>0.99377714174527498</v>
       </c>
       <c r="AB90">
-        <v>54.23617409891024</v>
+        <v>114.08573466995766</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19593,16 +19593,16 @@
         <v>697</v>
       </c>
       <c r="Y91" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="Z91" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AA91">
-        <v>0.99156821305535681</v>
+        <v>0.99516685156772267</v>
       </c>
       <c r="AB91">
-        <v>154.58276065179118</v>
+        <v>88.60772125841865</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19667,16 +19667,16 @@
         <v>699</v>
       </c>
       <c r="Y92" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="Z92" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AA92">
-        <v>0.99731037386855248</v>
+        <v>0.99240925523869494</v>
       </c>
       <c r="AB92">
-        <v>49.309812409870183</v>
+        <v>139.16365395725984</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19741,16 +19741,16 @@
         <v>701</v>
       </c>
       <c r="Y93" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="Z93" t="s">
-        <v>845</v>
+        <v>783</v>
       </c>
       <c r="AA93">
-        <v>0.99338478208530079</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB93">
-        <v>121.27899510281891</v>
+        <v>505.08652809978111</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19815,16 +19815,16 @@
         <v>703</v>
       </c>
       <c r="Y94" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Z94" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AA94">
-        <v>0.99240925523869494</v>
+        <v>0.99172397756136033</v>
       </c>
       <c r="AB94">
-        <v>139.16365395725984</v>
+        <v>151.72707804172813</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19889,16 +19889,16 @@
         <v>705</v>
       </c>
       <c r="Y95" t="s">
-        <v>532</v>
+        <v>451</v>
       </c>
       <c r="Z95" t="s">
-        <v>789</v>
+        <v>848</v>
       </c>
       <c r="AA95">
-        <v>0.97244982574001193</v>
+        <v>0.99431900976645593</v>
       </c>
       <c r="AB95">
-        <v>505.08652809978111</v>
+        <v>104.15148761497397</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19963,16 +19963,16 @@
         <v>707</v>
       </c>
       <c r="Y96" t="s">
-        <v>489</v>
+        <v>430</v>
       </c>
       <c r="Z96" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="AA96">
-        <v>0.99172397756136033</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB96">
-        <v>151.72707804172813</v>
+        <v>98.356996715718111</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -20037,16 +20037,16 @@
         <v>709</v>
       </c>
       <c r="Y97" t="s">
-        <v>451</v>
+        <v>517</v>
       </c>
       <c r="Z97" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AA97">
-        <v>0.99431900976645593</v>
+        <v>0.99343259267015904</v>
       </c>
       <c r="AB97">
-        <v>104.15148761497397</v>
+        <v>120.40246771375152</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -20111,16 +20111,16 @@
         <v>711</v>
       </c>
       <c r="Y98" t="s">
-        <v>430</v>
+        <v>526</v>
       </c>
       <c r="Z98" t="s">
-        <v>849</v>
+        <v>783</v>
       </c>
       <c r="AA98">
-        <v>0.9946350729064154</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB98">
-        <v>98.356996715718111</v>
+        <v>1103.617804666449</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20185,16 +20185,16 @@
         <v>713</v>
       </c>
       <c r="Y99" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="Z99" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AA99">
-        <v>0.99343259267015904</v>
+        <v>0.95679935803281835</v>
       </c>
       <c r="AB99">
-        <v>120.40246771375152</v>
+        <v>792.01176939833033</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20259,16 +20259,16 @@
         <v>715</v>
       </c>
       <c r="Y100" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="Z100" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AA100">
-        <v>0.9914627894548943</v>
+        <v>0.98761622532712257</v>
       </c>
       <c r="AB100">
-        <v>156.51552666027055</v>
+        <v>227.03586900275366</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20333,16 +20333,16 @@
         <v>717</v>
       </c>
       <c r="Y101" t="s">
-        <v>500</v>
+        <v>448</v>
       </c>
       <c r="Z101" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AA101">
-        <v>0.9776523073059149</v>
+        <v>0.99003402112096806</v>
       </c>
       <c r="AB101">
-        <v>409.70769939155917</v>
+        <v>182.70961278225187</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20407,16 +20407,16 @@
         <v>719</v>
       </c>
       <c r="Y102" t="s">
-        <v>504</v>
+        <v>459</v>
       </c>
       <c r="Z102" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AA102">
-        <v>0.98289281118622185</v>
+        <v>0.99466062705491098</v>
       </c>
       <c r="AB102">
-        <v>313.63179491926536</v>
+        <v>97.888503993298116</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20481,16 +20481,16 @@
         <v>721</v>
       </c>
       <c r="Y103" t="s">
-        <v>424</v>
+        <v>508</v>
       </c>
       <c r="Z103" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AA103">
-        <v>0.99593583828988941</v>
+        <v>0.9944598150968682</v>
       </c>
       <c r="AB103">
-        <v>74.509631352026517</v>
+        <v>101.5700565574154</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20555,16 +20555,16 @@
         <v>723</v>
       </c>
       <c r="Y104" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="Z104" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AA104">
-        <v>0.99553066735440277</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB104">
-        <v>81.937765169281747</v>
+        <v>92.674656500591539</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20629,16 +20629,16 @@
         <v>725</v>
       </c>
       <c r="Y105" t="s">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="Z105" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AA105">
-        <v>0.99049341406542279</v>
+        <v>0.99438812565699364</v>
       </c>
       <c r="AB105">
-        <v>174.28740880058183</v>
+        <v>102.88436295511657</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20703,16 +20703,16 @@
         <v>727</v>
       </c>
       <c r="Y106" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Z106" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AA106">
-        <v>0.99575157784901702</v>
+        <v>0.99643191679577148</v>
       </c>
       <c r="AB106">
-        <v>77.887739434686992</v>
+        <v>65.414858744189985</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20777,16 +20777,16 @@
         <v>729</v>
       </c>
       <c r="Y107" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z107" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AA107">
-        <v>0.99649411432543766</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB107">
-        <v>64.274570700309781</v>
+        <v>443.37880474956393</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20851,16 +20851,16 @@
         <v>731</v>
       </c>
       <c r="Y108" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="Z108" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AA108">
-        <v>0.97907421743006762</v>
+        <v>0.99542292233022822</v>
       </c>
       <c r="AB108">
-        <v>383.63934711542669</v>
+        <v>83.913090612483515</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20925,16 +20925,16 @@
         <v>733</v>
       </c>
       <c r="Y109" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="Z109" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AA109">
-        <v>0.99558768376711515</v>
+        <v>0.99647584863086869</v>
       </c>
       <c r="AB109">
-        <v>80.892464269556413</v>
+        <v>64.60944176740837</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20999,16 +20999,16 @@
         <v>735</v>
       </c>
       <c r="Y110" t="s">
-        <v>510</v>
+        <v>431</v>
       </c>
       <c r="Z110" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AA110">
-        <v>0.99324569511004301</v>
+        <v>0.99780983219878738</v>
       </c>
       <c r="AB110">
-        <v>123.82892298254488</v>
+        <v>40.153076355563911</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -21073,16 +21073,16 @@
         <v>737</v>
       </c>
       <c r="Y111" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z111" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AA111">
-        <v>0.99419165427276146</v>
+        <v>0.99724696581141214</v>
       </c>
       <c r="AB111">
-        <v>106.48633833270691</v>
+        <v>50.472293457444586</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -21147,16 +21147,16 @@
         <v>739</v>
       </c>
       <c r="Y112" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="Z112" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AA112">
-        <v>0.99198935558098356</v>
+        <v>0.99589550629055523</v>
       </c>
       <c r="AB112">
-        <v>146.8618143486346</v>
+        <v>75.249051339820184</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21221,16 +21221,16 @@
         <v>741</v>
       </c>
       <c r="Y113" t="s">
-        <v>482</v>
+        <v>520</v>
       </c>
       <c r="Z113" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AA113">
-        <v>0.98150124893892388</v>
+        <v>0.99531156065644533</v>
       </c>
       <c r="AB113">
-        <v>339.14376945306287</v>
+        <v>85.954721298502818</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21295,16 +21295,16 @@
         <v>743</v>
       </c>
       <c r="Y114" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="Z114" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AA114">
-        <v>0.99523081353776888</v>
+        <v>0.99706825374988217</v>
       </c>
       <c r="AB114">
-        <v>87.435085140903482</v>
+        <v>53.748681252160438</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21369,16 +21369,16 @@
         <v>745</v>
       </c>
       <c r="Y115" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="Z115" t="s">
-        <v>866</v>
+        <v>769</v>
       </c>
       <c r="AA115">
-        <v>0.9916432660493133</v>
+        <v>0.96238190390083644</v>
       </c>
       <c r="AB115">
-        <v>153.20678909592235</v>
+        <v>689.665095151331</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21443,16 +21443,16 @@
         <v>747</v>
       </c>
       <c r="Y116" t="s">
-        <v>423</v>
+        <v>528</v>
       </c>
       <c r="Z116" t="s">
-        <v>867</v>
+        <v>783</v>
       </c>
       <c r="AA116">
-        <v>0.99570118415007625</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB116">
-        <v>78.81162391526847</v>
+        <v>675.25867642804383</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21517,16 +21517,16 @@
         <v>749</v>
       </c>
       <c r="Y117" t="s">
-        <v>436</v>
+        <v>484</v>
       </c>
       <c r="Z117" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="AA117">
-        <v>0.99691903985105013</v>
+        <v>0.9951089264264793</v>
       </c>
       <c r="AB117">
-        <v>56.484269397415083</v>
+        <v>89.669682181211982</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21591,16 +21591,16 @@
         <v>751</v>
       </c>
       <c r="Y118" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="Z118" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AA118">
-        <v>0.98563153879963317</v>
+        <v>0.98666519734623237</v>
       </c>
       <c r="AB118">
-        <v>263.42178867339101</v>
+        <v>244.47138198573927</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21665,16 +21665,16 @@
         <v>753</v>
       </c>
       <c r="Y119" t="s">
-        <v>509</v>
+        <v>425</v>
       </c>
       <c r="Z119" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AA119">
-        <v>0.99529226044395613</v>
+        <v>0.99750070245826261</v>
       </c>
       <c r="AB119">
-        <v>86.308558527470979</v>
+        <v>45.820454931853</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21739,16 +21739,16 @@
         <v>755</v>
       </c>
       <c r="Y120" t="s">
-        <v>511</v>
+        <v>422</v>
       </c>
       <c r="Z120" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AA120">
-        <v>0.99443562760718263</v>
+        <v>0.99395341117186964</v>
       </c>
       <c r="AB120">
-        <v>102.01349386831856</v>
+        <v>110.85412851572337</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21813,16 +21813,16 @@
         <v>757</v>
       </c>
       <c r="Y121" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="Z121" t="s">
-        <v>806</v>
+        <v>871</v>
       </c>
       <c r="AA121">
-        <v>0.97432735774114165</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB121">
-        <v>470.66510807906917</v>
+        <v>307.49900901993823</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21887,16 +21887,16 @@
         <v>759</v>
       </c>
       <c r="Y122" t="s">
-        <v>487</v>
+        <v>437</v>
       </c>
       <c r="Z122" t="s">
         <v>872</v>
       </c>
       <c r="AA122">
-        <v>0.9882282251528024</v>
+        <v>0.9974199781412052</v>
       </c>
       <c r="AB122">
-        <v>215.81587219862183</v>
+        <v>47.300400744571718</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21961,16 +21961,16 @@
         <v>761</v>
       </c>
       <c r="Y123" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Z123" t="s">
         <v>873</v>
       </c>
       <c r="AA123">
-        <v>0.99136196456122894</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB123">
-        <v>158.36398304413572</v>
+        <v>121.57987025257442</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -22035,16 +22035,16 @@
         <v>763</v>
       </c>
       <c r="Y124" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="Z124" t="s">
         <v>874</v>
       </c>
       <c r="AA124">
-        <v>0.99658191580238853</v>
+        <v>0.99379477670057537</v>
       </c>
       <c r="AB124">
-        <v>62.664876956210314</v>
+        <v>113.7624271561186</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -22109,16 +22109,16 @@
         <v>765</v>
       </c>
       <c r="Y125" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="Z125" t="s">
         <v>875</v>
       </c>
       <c r="AA125">
-        <v>0.99772567527055689</v>
+        <v>0.9961866142254362</v>
       </c>
       <c r="AB125">
-        <v>41.695953373122713</v>
+        <v>69.91207253366963</v>
       </c>
     </row>
   </sheetData>
@@ -22127,7 +22127,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F097B633-9DD5-4907-ADCE-DB2B33CEE910}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA4439F-62A7-411C-BF51-487DE4C902FA}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22239,7 +22239,7 @@
         <v>1269</v>
       </c>
       <c r="K11" t="s">
-        <v>1135</v>
+        <v>1024</v>
       </c>
       <c r="L11">
         <v>4.7713910333636482</v>
@@ -22272,7 +22272,7 @@
         <v>1407</v>
       </c>
       <c r="X11" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -22307,7 +22307,7 @@
         <v>1271</v>
       </c>
       <c r="K12" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="L12">
         <v>12.404103898825962</v>
@@ -22340,7 +22340,7 @@
         <v>1409</v>
       </c>
       <c r="X12" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -22375,7 +22375,7 @@
         <v>1273</v>
       </c>
       <c r="K13" t="s">
-        <v>1077</v>
+        <v>1062</v>
       </c>
       <c r="L13">
         <v>6.1276234637439133</v>
@@ -22408,7 +22408,7 @@
         <v>1411</v>
       </c>
       <c r="X13" t="s">
-        <v>1255</v>
+        <v>1244</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -22443,7 +22443,7 @@
         <v>1275</v>
       </c>
       <c r="K14" t="s">
-        <v>1066</v>
+        <v>1102</v>
       </c>
       <c r="L14">
         <v>0.85621181691755843</v>
@@ -22476,7 +22476,7 @@
         <v>1413</v>
       </c>
       <c r="X14" t="s">
-        <v>1212</v>
+        <v>1265</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -22511,7 +22511,7 @@
         <v>1277</v>
       </c>
       <c r="K15" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="L15">
         <v>2.2628760328229185</v>
@@ -22544,7 +22544,7 @@
         <v>1415</v>
       </c>
       <c r="X15" t="s">
-        <v>1231</v>
+        <v>1262</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -22579,7 +22579,7 @@
         <v>1279</v>
       </c>
       <c r="K16" t="s">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="L16">
         <v>0.43370118574988076</v>
@@ -22612,7 +22612,7 @@
         <v>1417</v>
       </c>
       <c r="X16" t="s">
-        <v>1263</v>
+        <v>1219</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -22647,7 +22647,7 @@
         <v>1281</v>
       </c>
       <c r="K17" t="s">
-        <v>1121</v>
+        <v>1087</v>
       </c>
       <c r="L17">
         <v>2.5150267058852811</v>
@@ -22680,7 +22680,7 @@
         <v>1419</v>
       </c>
       <c r="X17" t="s">
-        <v>1247</v>
+        <v>1215</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -22715,7 +22715,7 @@
         <v>1283</v>
       </c>
       <c r="K18" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="L18">
         <v>2.885493974180005</v>
@@ -22748,7 +22748,7 @@
         <v>1421</v>
       </c>
       <c r="X18" t="s">
-        <v>1265</v>
+        <v>1240</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -22783,7 +22783,7 @@
         <v>1285</v>
       </c>
       <c r="K19" t="s">
-        <v>1129</v>
+        <v>1055</v>
       </c>
       <c r="L19">
         <v>10.563746678268352</v>
@@ -22816,7 +22816,7 @@
         <v>1423</v>
       </c>
       <c r="X19" t="s">
-        <v>1245</v>
+        <v>1213</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22851,7 +22851,7 @@
         <v>1287</v>
       </c>
       <c r="K20" t="s">
-        <v>1137</v>
+        <v>1026</v>
       </c>
       <c r="L20">
         <v>7.4816578037471135</v>
@@ -22884,7 +22884,7 @@
         <v>1425</v>
       </c>
       <c r="X20" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22919,7 +22919,7 @@
         <v>1289</v>
       </c>
       <c r="K21" t="s">
-        <v>1119</v>
+        <v>1085</v>
       </c>
       <c r="L21">
         <v>11.884376191048085</v>
@@ -22952,7 +22952,7 @@
         <v>1427</v>
       </c>
       <c r="X21" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22987,7 +22987,7 @@
         <v>1291</v>
       </c>
       <c r="K22" t="s">
-        <v>1020</v>
+        <v>1118</v>
       </c>
       <c r="L22">
         <v>12.246676572623375</v>
@@ -23020,7 +23020,7 @@
         <v>1429</v>
       </c>
       <c r="X22" t="s">
-        <v>1261</v>
+        <v>1217</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -23055,7 +23055,7 @@
         <v>1293</v>
       </c>
       <c r="K23" t="s">
-        <v>1058</v>
+        <v>1033</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -23088,7 +23088,7 @@
         <v>1431</v>
       </c>
       <c r="X23" t="s">
-        <v>1210</v>
+        <v>1254</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -23123,7 +23123,7 @@
         <v>1295</v>
       </c>
       <c r="K24" t="s">
-        <v>1078</v>
+        <v>1063</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -23156,7 +23156,7 @@
         <v>1433</v>
       </c>
       <c r="X24" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -23191,7 +23191,7 @@
         <v>1297</v>
       </c>
       <c r="K25" t="s">
-        <v>1131</v>
+        <v>1057</v>
       </c>
       <c r="L25">
         <v>11.221871479411517</v>
@@ -23224,7 +23224,7 @@
         <v>1435</v>
       </c>
       <c r="X25" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -23259,7 +23259,7 @@
         <v>1299</v>
       </c>
       <c r="K26" t="s">
-        <v>1123</v>
+        <v>1089</v>
       </c>
       <c r="L26">
         <v>1.6691823226567941</v>
@@ -23292,7 +23292,7 @@
         <v>1437</v>
       </c>
       <c r="X26" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23327,7 +23327,7 @@
         <v>1301</v>
       </c>
       <c r="K27" t="s">
-        <v>1092</v>
+        <v>1130</v>
       </c>
       <c r="L27">
         <v>3.7614311754340659</v>
@@ -23360,7 +23360,7 @@
         <v>1439</v>
       </c>
       <c r="X27" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -23395,7 +23395,7 @@
         <v>1303</v>
       </c>
       <c r="K28" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="L28">
         <v>0.34625959029864795</v>
@@ -23428,7 +23428,7 @@
         <v>1441</v>
       </c>
       <c r="X28" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="Y28">
         <v>2.6655000000000002</v>
@@ -23463,7 +23463,7 @@
         <v>1305</v>
       </c>
       <c r="K29" t="s">
-        <v>1044</v>
+        <v>1142</v>
       </c>
       <c r="L29">
         <v>0.65440271382024695</v>
@@ -23496,7 +23496,7 @@
         <v>1443</v>
       </c>
       <c r="X29" t="s">
-        <v>1267</v>
+        <v>1242</v>
       </c>
       <c r="Y29">
         <v>8.8432499999999994</v>
@@ -23531,7 +23531,7 @@
         <v>1307</v>
       </c>
       <c r="K30" t="s">
-        <v>1062</v>
+        <v>1037</v>
       </c>
       <c r="L30">
         <v>2.2677057834637031</v>
@@ -23564,7 +23564,7 @@
         <v>1445</v>
       </c>
       <c r="X30" t="s">
-        <v>1225</v>
+        <v>1252</v>
       </c>
       <c r="Y30">
         <v>3.4402499999999998</v>
@@ -23599,7 +23599,7 @@
         <v>1309</v>
       </c>
       <c r="K31" t="s">
-        <v>1080</v>
+        <v>1065</v>
       </c>
       <c r="L31">
         <v>2.4836923620575391</v>
@@ -23632,7 +23632,7 @@
         <v>1447</v>
       </c>
       <c r="X31" t="s">
-        <v>1232</v>
+        <v>1263</v>
       </c>
       <c r="Y31">
         <v>13.389749999999999</v>
@@ -23667,7 +23667,7 @@
         <v>1311</v>
       </c>
       <c r="K32" t="s">
-        <v>1111</v>
+        <v>1077</v>
       </c>
       <c r="L32">
         <v>4.0763322608214585</v>
@@ -23700,7 +23700,7 @@
         <v>1449</v>
       </c>
       <c r="X32" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="Y32">
         <v>6.9757499999999997</v>
@@ -23735,7 +23735,7 @@
         <v>1313</v>
       </c>
       <c r="K33" t="s">
-        <v>1094</v>
+        <v>1132</v>
       </c>
       <c r="L33">
         <v>2.5731779960501728</v>
@@ -23768,7 +23768,7 @@
         <v>1451</v>
       </c>
       <c r="X33" t="s">
-        <v>1223</v>
+        <v>1250</v>
       </c>
       <c r="Y33">
         <v>38.154000000000003</v>
@@ -23803,7 +23803,7 @@
         <v>1315</v>
       </c>
       <c r="K34" t="s">
-        <v>1028</v>
+        <v>1112</v>
       </c>
       <c r="L34">
         <v>4.0509443596880574</v>
@@ -23836,7 +23836,7 @@
         <v>1453</v>
       </c>
       <c r="X34" t="s">
-        <v>1214</v>
+        <v>1267</v>
       </c>
       <c r="Y34">
         <v>26.765999999999998</v>
@@ -23871,7 +23871,7 @@
         <v>1317</v>
       </c>
       <c r="K35" t="s">
-        <v>1034</v>
+        <v>1014</v>
       </c>
       <c r="L35">
         <v>2.4544193550494788</v>
@@ -23904,7 +23904,7 @@
         <v>1455</v>
       </c>
       <c r="X35" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="Y35">
         <v>35.325000000000003</v>
@@ -23939,7 +23939,7 @@
         <v>1319</v>
       </c>
       <c r="K36" t="s">
-        <v>1016</v>
+        <v>1043</v>
       </c>
       <c r="L36">
         <v>0.35051099632091098</v>
@@ -23972,7 +23972,7 @@
         <v>1457</v>
       </c>
       <c r="X36" t="s">
-        <v>1257</v>
+        <v>1246</v>
       </c>
       <c r="Y36">
         <v>38.589750000000002</v>
@@ -24007,7 +24007,7 @@
         <v>1321</v>
       </c>
       <c r="K37" t="s">
-        <v>1142</v>
+        <v>1031</v>
       </c>
       <c r="L37">
         <v>5.5005105319204732</v>
@@ -24040,7 +24040,7 @@
         <v>1459</v>
       </c>
       <c r="X37" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="Y37">
         <v>28.707000000000001</v>
@@ -24075,7 +24075,7 @@
         <v>1323</v>
       </c>
       <c r="K38" t="s">
-        <v>1068</v>
+        <v>1104</v>
       </c>
       <c r="L38">
         <v>1.6757541426674882</v>
@@ -24108,7 +24108,7 @@
         <v>1461</v>
       </c>
       <c r="X38" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="Y38">
         <v>13.428000000000001</v>
@@ -24143,7 +24143,7 @@
         <v>1325</v>
       </c>
       <c r="K39" t="s">
-        <v>1038</v>
+        <v>1018</v>
       </c>
       <c r="L39">
         <v>0.39959553615654331</v>
@@ -24176,7 +24176,7 @@
         <v>1463</v>
       </c>
       <c r="X39" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24211,7 +24211,7 @@
         <v>1327</v>
       </c>
       <c r="K40" t="s">
-        <v>1022</v>
+        <v>1120</v>
       </c>
       <c r="L40">
         <v>1.7832075556426605</v>
@@ -24244,7 +24244,7 @@
         <v>1465</v>
       </c>
       <c r="X40" t="s">
-        <v>1259</v>
+        <v>1248</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24279,7 +24279,7 @@
         <v>1329</v>
       </c>
       <c r="K41" t="s">
-        <v>1018</v>
+        <v>1045</v>
       </c>
       <c r="L41">
         <v>23.427729543154012</v>
@@ -24312,7 +24312,7 @@
         <v>1467</v>
       </c>
       <c r="X41" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24347,7 +24347,7 @@
         <v>1331</v>
       </c>
       <c r="K42" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
       <c r="L42">
         <v>1.4999429400795936</v>
@@ -24382,7 +24382,7 @@
         <v>1333</v>
       </c>
       <c r="K43" t="s">
-        <v>1032</v>
+        <v>1116</v>
       </c>
       <c r="L43">
         <v>55.863958629218203</v>
@@ -24417,7 +24417,7 @@
         <v>1335</v>
       </c>
       <c r="K44" t="s">
-        <v>1086</v>
+        <v>1071</v>
       </c>
       <c r="L44">
         <v>17.068804920122925</v>
@@ -24452,7 +24452,7 @@
         <v>1337</v>
       </c>
       <c r="K45" t="s">
-        <v>1100</v>
+        <v>1138</v>
       </c>
       <c r="L45">
         <v>13.001084297219549</v>
@@ -24487,7 +24487,7 @@
         <v>1339</v>
       </c>
       <c r="K46" t="s">
-        <v>1042</v>
+        <v>1022</v>
       </c>
       <c r="L46">
         <v>3.0756142181007986</v>
@@ -24522,7 +24522,7 @@
         <v>1341</v>
       </c>
       <c r="K47" t="s">
-        <v>1146</v>
+        <v>1128</v>
       </c>
       <c r="L47">
         <v>17.749707845203876</v>
@@ -24557,7 +24557,7 @@
         <v>1343</v>
       </c>
       <c r="K48" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="L48">
         <v>2.3372365278937242</v>
@@ -24592,7 +24592,7 @@
         <v>1345</v>
       </c>
       <c r="K49" t="s">
-        <v>1115</v>
+        <v>1081</v>
       </c>
       <c r="L49">
         <v>4.2648673086521249</v>
@@ -24627,7 +24627,7 @@
         <v>1347</v>
       </c>
       <c r="K50" t="s">
-        <v>1098</v>
+        <v>1136</v>
       </c>
       <c r="L50">
         <v>2.8571480649629004</v>
@@ -24662,7 +24662,7 @@
         <v>1349</v>
       </c>
       <c r="K51" t="s">
-        <v>1102</v>
+        <v>1140</v>
       </c>
       <c r="L51">
         <v>9.5169217846211289</v>
@@ -24697,7 +24697,7 @@
         <v>1351</v>
       </c>
       <c r="K52" t="s">
-        <v>1127</v>
+        <v>1093</v>
       </c>
       <c r="L52">
         <v>33.414563514376454</v>
@@ -24732,7 +24732,7 @@
         <v>1353</v>
       </c>
       <c r="K53" t="s">
-        <v>1074</v>
+        <v>1110</v>
       </c>
       <c r="L53">
         <v>18.904558868579112</v>
@@ -24767,7 +24767,7 @@
         <v>1355</v>
       </c>
       <c r="K54" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="L54">
         <v>15.478330347836801</v>
@@ -24802,7 +24802,7 @@
         <v>1357</v>
       </c>
       <c r="K55" t="s">
-        <v>1076</v>
+        <v>1061</v>
       </c>
       <c r="L55">
         <v>14.176079891703212</v>
@@ -24837,7 +24837,7 @@
         <v>1359</v>
       </c>
       <c r="K56" t="s">
-        <v>1048</v>
+        <v>1146</v>
       </c>
       <c r="L56">
         <v>0.80973624203950822</v>
@@ -24872,7 +24872,7 @@
         <v>1361</v>
       </c>
       <c r="K57" t="s">
-        <v>1026</v>
+        <v>1124</v>
       </c>
       <c r="L57">
         <v>3.2067222321080848</v>
@@ -24907,7 +24907,7 @@
         <v>1363</v>
       </c>
       <c r="K58" t="s">
-        <v>1125</v>
+        <v>1091</v>
       </c>
       <c r="L58">
         <v>0.66271354737797783</v>
@@ -24942,7 +24942,7 @@
         <v>1365</v>
       </c>
       <c r="K59" t="s">
-        <v>1072</v>
+        <v>1108</v>
       </c>
       <c r="L59">
         <v>1.8183767824138508</v>
@@ -24977,7 +24977,7 @@
         <v>1367</v>
       </c>
       <c r="K60" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="L60">
         <v>0.24904319237866104</v>
@@ -25012,7 +25012,7 @@
         <v>1369</v>
       </c>
       <c r="K61" t="s">
-        <v>1117</v>
+        <v>1083</v>
       </c>
       <c r="L61">
         <v>8.2047875916663029E-2</v>
@@ -25047,7 +25047,7 @@
         <v>1371</v>
       </c>
       <c r="K62" t="s">
-        <v>1096</v>
+        <v>1134</v>
       </c>
       <c r="L62">
         <v>11.861012832193515</v>
@@ -25082,7 +25082,7 @@
         <v>1373</v>
       </c>
       <c r="K63" t="s">
-        <v>1070</v>
+        <v>1106</v>
       </c>
       <c r="L63">
         <v>0.74143826937354373</v>
@@ -25117,7 +25117,7 @@
         <v>1375</v>
       </c>
       <c r="K64" t="s">
-        <v>1082</v>
+        <v>1067</v>
       </c>
       <c r="L64">
         <v>5.5201095579611916</v>
@@ -25152,7 +25152,7 @@
         <v>1377</v>
       </c>
       <c r="K65" t="s">
-        <v>1064</v>
+        <v>1039</v>
       </c>
       <c r="L65">
         <v>6.8285247240880329</v>
@@ -25187,7 +25187,7 @@
         <v>1379</v>
       </c>
       <c r="K66" t="s">
-        <v>1133</v>
+        <v>1059</v>
       </c>
       <c r="L66">
         <v>14.065249575687433</v>
@@ -25222,7 +25222,7 @@
         <v>1381</v>
       </c>
       <c r="K67" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="L67">
         <v>9.3799037679336319</v>
@@ -25257,7 +25257,7 @@
         <v>1383</v>
       </c>
       <c r="K68" t="s">
-        <v>1046</v>
+        <v>1144</v>
       </c>
       <c r="L68">
         <v>42.785830383290261</v>
@@ -25292,7 +25292,7 @@
         <v>1385</v>
       </c>
       <c r="K69" t="s">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="L69">
         <v>7.8693705940085819</v>
@@ -25327,7 +25327,7 @@
         <v>1387</v>
       </c>
       <c r="K70" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="L70">
         <v>19.787589902082505</v>
@@ -25362,7 +25362,7 @@
         <v>1389</v>
       </c>
       <c r="K71" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
       <c r="L71">
         <v>18.319832830101969</v>
@@ -25397,7 +25397,7 @@
         <v>1391</v>
       </c>
       <c r="K72" t="s">
-        <v>1084</v>
+        <v>1069</v>
       </c>
       <c r="L72">
         <v>6.7551756478058005</v>
@@ -25432,7 +25432,7 @@
         <v>1393</v>
       </c>
       <c r="K73" t="s">
-        <v>1113</v>
+        <v>1079</v>
       </c>
       <c r="L73">
         <v>3.5275797249830152</v>
@@ -25467,7 +25467,7 @@
         <v>1395</v>
       </c>
       <c r="K74" t="s">
-        <v>1030</v>
+        <v>1114</v>
       </c>
       <c r="L74">
         <v>0.89663971235601181</v>
@@ -25502,7 +25502,7 @@
         <v>1397</v>
       </c>
       <c r="K75" t="s">
-        <v>1024</v>
+        <v>1122</v>
       </c>
       <c r="L75">
         <v>5.9305458091691294</v>
@@ -25537,7 +25537,7 @@
         <v>1399</v>
       </c>
       <c r="K76" t="s">
-        <v>1140</v>
+        <v>1029</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25572,7 +25572,7 @@
         <v>1401</v>
       </c>
       <c r="K77" t="s">
-        <v>1036</v>
+        <v>1016</v>
       </c>
       <c r="L77">
         <v>0.5190595734350465</v>
@@ -25607,7 +25607,7 @@
         <v>1403</v>
       </c>
       <c r="K78" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="L78">
         <v>0.29505146981926272</v>
@@ -25642,7 +25642,7 @@
         <v>1405</v>
       </c>
       <c r="K79" t="s">
-        <v>1138</v>
+        <v>1027</v>
       </c>
       <c r="L79">
         <v>0.28737649325389003</v>
@@ -25657,7 +25657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62816FA7-7CBC-4B37-9E33-1DC2D4496DB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DBC703-DF67-4AA7-B1E6-FC7BF358F2E2}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27126,7 +27126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488606B9-9A43-44A8-9692-B6A0988B3BC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD63786-BB09-473F-8C12-FE13453BC895}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3BECEC4-E5D1-430E-AAA6-FAF22C2F13D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA2EC1FF-F758-4E1B-A486-8B197594AEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1736,18 +1736,396 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_054</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 54</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_070</t>
   </si>
   <si>
@@ -1772,112 +2150,244 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
   </si>
   <si>
     <t>distr_solelc_spv_053</t>
@@ -1922,525 +2432,192 @@
     <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
+  </si>
+  <si>
     <t>e_BR319-230</t>
   </si>
   <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
     <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
   </si>
   <si>
@@ -2453,52 +2630,115 @@
     <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
   </si>
   <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500</t>
+  </si>
+  <si>
+    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
   </si>
   <si>
     <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
@@ -2519,244 +2759,28 @@
     <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
   </si>
   <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500</t>
-  </si>
-  <si>
-    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
-  </si>
-  <si>
-    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
     <t>distr_wonelc_won_025</t>
@@ -2789,6 +2813,96 @@
     <t>connecting wind onshore to buses in cluster 36</t>
   </si>
   <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_001</t>
   </si>
   <si>
@@ -2819,6 +2933,48 @@
     <t>connecting wind onshore to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_013</t>
   </si>
   <si>
@@ -2843,64 +2999,58 @@
     <t>connecting wind onshore to buses in cluster 55</t>
   </si>
   <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
   </si>
   <si>
     <t>distr_wonelc_won_045</t>
@@ -2957,84 +3107,6 @@
     <t>connecting wind onshore to buses in cluster 32</t>
   </si>
   <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_004</t>
   </si>
   <si>
@@ -3065,60 +3137,6 @@
     <t>connecting wind onshore to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_017</t>
   </si>
   <si>
@@ -3155,22 +3173,28 @@
     <t>connecting wind onshore to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
   </si>
   <si>
     <t>elc_won_025</t>
@@ -3203,6 +3227,96 @@
     <t>e_BR412-500,e_BR400-500</t>
   </si>
   <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
     <t>elc_won_001</t>
   </si>
   <si>
@@ -3230,6 +3344,45 @@
     <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
   </si>
   <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+  </si>
+  <si>
     <t>elc_won_013</t>
   </si>
   <si>
@@ -3254,64 +3407,58 @@
     <t>e_BR220-500,e_BR185-500</t>
   </si>
   <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
   </si>
   <si>
     <t>elc_won_045</t>
@@ -3362,81 +3509,6 @@
     <t>e_BR209-500,e_BR208-500</t>
   </si>
   <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
     <t>elc_won_004</t>
   </si>
   <si>
@@ -3467,60 +3539,6 @@
     <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
   </si>
   <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
     <t>elc_won_017</t>
   </si>
   <si>
@@ -3557,22 +3575,136 @@
     <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
   </si>
   <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wofelc_wof_025</t>
@@ -3599,6 +3731,18 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_012</t>
   </si>
   <si>
@@ -3611,154 +3755,139 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_018</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR37-500,e_BR42-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w466973262-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
   </si>
   <si>
     <t>elc_wof_025</t>
@@ -3782,6 +3911,15 @@
     <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
   </si>
   <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
     <t>elc_wof_012</t>
   </si>
   <si>
@@ -3794,148 +3932,10 @@
     <t>e_w108224468-500,e_BR652-500</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR37-500,e_BR42-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
-  </si>
-  <si>
     <t>elc_wof_018</t>
   </si>
   <si>
     <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9835,7 +9835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B68C23-490A-418E-8F90-BD7D71D8CC9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FF7617-A597-4CE1-8882-F68BF9B39F72}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10073,16 +10073,16 @@
         <v>535</v>
       </c>
       <c r="Y11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="Z11" t="s">
         <v>769</v>
       </c>
       <c r="AA11">
-        <v>0.97432735774114165</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB11">
-        <v>470.66510807906917</v>
+        <v>90.443352439796072</v>
       </c>
       <c r="AD11" t="s">
         <v>534</v>
@@ -10115,10 +10115,10 @@
         <v>1015</v>
       </c>
       <c r="AO11">
-        <v>0.99677419959133018</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP11">
-        <v>59.139674158947656</v>
+        <v>96.528578181196991</v>
       </c>
       <c r="AR11" t="s">
         <v>534</v>
@@ -10151,10 +10151,10 @@
         <v>1211</v>
       </c>
       <c r="BC11">
-        <v>0.9933934749176847</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD11">
-        <v>121.11962650911367</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10219,16 +10219,16 @@
         <v>539</v>
       </c>
       <c r="Y12" t="s">
-        <v>487</v>
+        <v>439</v>
       </c>
       <c r="Z12" t="s">
         <v>770</v>
       </c>
       <c r="AA12">
-        <v>0.9882282251528024</v>
+        <v>0.97537853020161625</v>
       </c>
       <c r="AB12">
-        <v>215.81587219862183</v>
+        <v>451.39361297036953</v>
       </c>
       <c r="AD12" t="s">
         <v>534</v>
@@ -10261,10 +10261,10 @@
         <v>1017</v>
       </c>
       <c r="AO12">
-        <v>0.99766813121902409</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP12">
-        <v>42.750927651225993</v>
+        <v>49.543726018799653</v>
       </c>
       <c r="AR12" t="s">
         <v>534</v>
@@ -10294,13 +10294,13 @@
         <v>1212</v>
       </c>
       <c r="BB12" t="s">
-        <v>1092</v>
+        <v>1075</v>
       </c>
       <c r="BC12">
-        <v>0.99418931598784899</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD12">
-        <v>106.52920688943452</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10365,16 +10365,16 @@
         <v>541</v>
       </c>
       <c r="Y13" t="s">
-        <v>494</v>
+        <v>452</v>
       </c>
       <c r="Z13" t="s">
         <v>771</v>
       </c>
       <c r="AA13">
-        <v>0.99136196456122894</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB13">
-        <v>158.36398304413572</v>
+        <v>106.82211818572355</v>
       </c>
       <c r="AD13" t="s">
         <v>534</v>
@@ -10407,10 +10407,10 @@
         <v>1019</v>
       </c>
       <c r="AO13">
-        <v>0.99760247912344124</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP13">
-        <v>43.95454940357709</v>
+        <v>58.751500348127372</v>
       </c>
       <c r="AR13" t="s">
         <v>534</v>
@@ -10443,10 +10443,10 @@
         <v>1214</v>
       </c>
       <c r="BC13">
-        <v>0.99232494426983575</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD13">
-        <v>140.70935505301131</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10511,16 +10511,16 @@
         <v>543</v>
       </c>
       <c r="Y14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Z14" t="s">
         <v>772</v>
       </c>
       <c r="AA14">
-        <v>0.99658191580238853</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB14">
-        <v>62.664876956210314</v>
+        <v>62.251070203636829</v>
       </c>
       <c r="AD14" t="s">
         <v>534</v>
@@ -10553,10 +10553,10 @@
         <v>1021</v>
       </c>
       <c r="AO14">
-        <v>0.99336049451151065</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP14">
-        <v>121.72426728897108</v>
+        <v>132.99731300951822</v>
       </c>
       <c r="AR14" t="s">
         <v>534</v>
@@ -10589,10 +10589,10 @@
         <v>1216</v>
       </c>
       <c r="BC14">
-        <v>0.98775115723917273</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD14">
-        <v>224.56211728183334</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10657,16 +10657,16 @@
         <v>545</v>
       </c>
       <c r="Y15" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="Z15" t="s">
         <v>773</v>
       </c>
       <c r="AA15">
-        <v>0.99772567527055689</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB15">
-        <v>41.695953373122713</v>
+        <v>54.23617409891024</v>
       </c>
       <c r="AD15" t="s">
         <v>534</v>
@@ -10699,10 +10699,10 @@
         <v>1023</v>
       </c>
       <c r="AO15">
-        <v>0.99759498179797546</v>
+        <v>0.99677419959133018</v>
       </c>
       <c r="AP15">
-        <v>44.092000370450322</v>
+        <v>59.139674158947656</v>
       </c>
       <c r="AR15" t="s">
         <v>534</v>
@@ -10735,10 +10735,10 @@
         <v>1218</v>
       </c>
       <c r="BC15">
-        <v>0.98946506962487613</v>
+        <v>0.99526086651282741</v>
       </c>
       <c r="BD15">
-        <v>193.14039021060518</v>
+        <v>86.884113931497708</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10803,16 +10803,16 @@
         <v>547</v>
       </c>
       <c r="Y16" t="s">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="Z16" t="s">
         <v>774</v>
       </c>
       <c r="AA16">
-        <v>0.99506672623055659</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB16">
-        <v>90.443352439796072</v>
+        <v>154.58276065179118</v>
       </c>
       <c r="AD16" t="s">
         <v>534</v>
@@ -10845,10 +10845,10 @@
         <v>1025</v>
       </c>
       <c r="AO16">
-        <v>0.99244513691456471</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP16">
-        <v>138.50582323297994</v>
+        <v>42.750927651225993</v>
       </c>
       <c r="AR16" t="s">
         <v>534</v>
@@ -10881,10 +10881,10 @@
         <v>1220</v>
       </c>
       <c r="BC16">
-        <v>0.99314574070258299</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD16">
-        <v>125.66142045264445</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10949,16 +10949,16 @@
         <v>549</v>
       </c>
       <c r="Y17" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="Z17" t="s">
         <v>775</v>
       </c>
       <c r="AA17">
-        <v>0.97537853020161625</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB17">
-        <v>451.39361297036953</v>
+        <v>49.309812409870183</v>
       </c>
       <c r="AD17" t="s">
         <v>534</v>
@@ -10988,13 +10988,13 @@
         <v>1026</v>
       </c>
       <c r="AN17" t="s">
-        <v>775</v>
+        <v>1027</v>
       </c>
       <c r="AO17">
-        <v>0.97416725971121887</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP17">
-        <v>473.60023862765331</v>
+        <v>43.95454940357709</v>
       </c>
       <c r="AR17" t="s">
         <v>534</v>
@@ -11027,10 +11027,10 @@
         <v>1222</v>
       </c>
       <c r="BC17">
-        <v>0.99834679070917032</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD17">
-        <v>30.308836998544216</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11095,16 +11095,16 @@
         <v>551</v>
       </c>
       <c r="Y18" t="s">
-        <v>452</v>
+        <v>514</v>
       </c>
       <c r="Z18" t="s">
         <v>776</v>
       </c>
       <c r="AA18">
-        <v>0.99417333900805149</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB18">
-        <v>106.82211818572355</v>
+        <v>121.27899510281891</v>
       </c>
       <c r="AD18" t="s">
         <v>534</v>
@@ -11131,16 +11131,16 @@
         <v>890</v>
       </c>
       <c r="AM18" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="AN18" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="AO18">
-        <v>0.99760255773158468</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP18">
-        <v>43.953108254279897</v>
+        <v>121.72426728897108</v>
       </c>
       <c r="AR18" t="s">
         <v>534</v>
@@ -11173,10 +11173,10 @@
         <v>1224</v>
       </c>
       <c r="BC18">
-        <v>0.99401640271965719</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD18">
-        <v>109.69928347295183</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11241,16 +11241,16 @@
         <v>553</v>
       </c>
       <c r="Y19" t="s">
-        <v>429</v>
+        <v>526</v>
       </c>
       <c r="Z19" t="s">
         <v>777</v>
       </c>
       <c r="AA19">
-        <v>0.99660448707980165</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB19">
-        <v>62.251070203636829</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD19" t="s">
         <v>534</v>
@@ -11277,16 +11277,16 @@
         <v>892</v>
       </c>
       <c r="AM19" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="AN19" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AO19">
-        <v>0.99352359657507616</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP19">
-        <v>118.7340627902709</v>
+        <v>44.092000370450322</v>
       </c>
       <c r="AR19" t="s">
         <v>534</v>
@@ -11319,10 +11319,10 @@
         <v>1226</v>
       </c>
       <c r="BC19">
-        <v>0.95713629889852414</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD19">
-        <v>785.83452019372396</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11387,16 +11387,16 @@
         <v>555</v>
       </c>
       <c r="Y20" t="s">
-        <v>433</v>
+        <v>530</v>
       </c>
       <c r="Z20" t="s">
         <v>778</v>
       </c>
       <c r="AA20">
-        <v>0.99704166323096854</v>
+        <v>0.95679935803281835</v>
       </c>
       <c r="AB20">
-        <v>54.23617409891024</v>
+        <v>792.01176939833033</v>
       </c>
       <c r="AD20" t="s">
         <v>534</v>
@@ -11423,16 +11423,16 @@
         <v>894</v>
       </c>
       <c r="AM20" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AN20" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AO20">
-        <v>0.99433447571906541</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP20">
-        <v>103.86794515046822</v>
+        <v>341.91992986513412</v>
       </c>
       <c r="AR20" t="s">
         <v>534</v>
@@ -11465,10 +11465,10 @@
         <v>1228</v>
       </c>
       <c r="BC20">
-        <v>0.98806872821788805</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD20">
-        <v>218.73998267205184</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11533,16 +11533,16 @@
         <v>557</v>
       </c>
       <c r="Y21" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="Z21" t="s">
         <v>779</v>
       </c>
       <c r="AA21">
-        <v>0.99156821305535681</v>
+        <v>0.98761622532712257</v>
       </c>
       <c r="AB21">
-        <v>154.58276065179118</v>
+        <v>227.03586900275366</v>
       </c>
       <c r="AD21" t="s">
         <v>534</v>
@@ -11569,16 +11569,16 @@
         <v>896</v>
       </c>
       <c r="AM21" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="AN21" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AO21">
-        <v>0.99403730604060547</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP21">
-        <v>109.31605592223302</v>
+        <v>258.57410995127316</v>
       </c>
       <c r="AR21" t="s">
         <v>534</v>
@@ -11611,10 +11611,10 @@
         <v>1230</v>
       </c>
       <c r="BC21">
-        <v>0.96863461872110523</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD21">
-        <v>575.0319901130714</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11679,16 +11679,16 @@
         <v>559</v>
       </c>
       <c r="Y22" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="Z22" t="s">
         <v>780</v>
       </c>
       <c r="AA22">
-        <v>0.99731037386855248</v>
+        <v>0.99003402112096806</v>
       </c>
       <c r="AB22">
-        <v>49.309812409870183</v>
+        <v>182.70961278225187</v>
       </c>
       <c r="AD22" t="s">
         <v>534</v>
@@ -11715,16 +11715,16 @@
         <v>898</v>
       </c>
       <c r="AM22" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AN22" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AO22">
-        <v>0.99105808324017197</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP22">
-        <v>163.93514059684662</v>
+        <v>40.90273458067751</v>
       </c>
       <c r="AR22" t="s">
         <v>534</v>
@@ -11754,13 +11754,13 @@
         <v>1231</v>
       </c>
       <c r="BB22" t="s">
-        <v>1099</v>
+        <v>1232</v>
       </c>
       <c r="BC22">
-        <v>0.99098965084511315</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD22">
-        <v>165.18973450625904</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11825,16 +11825,16 @@
         <v>561</v>
       </c>
       <c r="Y23" t="s">
-        <v>514</v>
+        <v>459</v>
       </c>
       <c r="Z23" t="s">
         <v>781</v>
       </c>
       <c r="AA23">
-        <v>0.99338478208530079</v>
+        <v>0.99466062705491098</v>
       </c>
       <c r="AB23">
-        <v>121.27899510281891</v>
+        <v>97.888503993298116</v>
       </c>
       <c r="AD23" t="s">
         <v>534</v>
@@ -11861,16 +11861,16 @@
         <v>900</v>
       </c>
       <c r="AM23" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AN23" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AO23">
-        <v>0.9974675531234084</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP23">
-        <v>46.428192737512276</v>
+        <v>74.530739771815789</v>
       </c>
       <c r="AR23" t="s">
         <v>534</v>
@@ -11897,16 +11897,16 @@
         <v>1172</v>
       </c>
       <c r="BA23" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="BB23" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="BC23">
-        <v>0.99053278045305837</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD23">
-        <v>173.56569169392964</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11971,16 +11971,16 @@
         <v>563</v>
       </c>
       <c r="Y24" t="s">
-        <v>468</v>
+        <v>508</v>
       </c>
       <c r="Z24" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
       <c r="AA24">
-        <v>0.96942910386940295</v>
+        <v>0.9944598150968682</v>
       </c>
       <c r="AB24">
-        <v>560.46642906094564</v>
+        <v>101.5700565574154</v>
       </c>
       <c r="AD24" t="s">
         <v>534</v>
@@ -12007,16 +12007,16 @@
         <v>902</v>
       </c>
       <c r="AM24" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AN24" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="AO24">
-        <v>0.99534886842510228</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP24">
-        <v>85.270745539791065</v>
+        <v>80.747827133859133</v>
       </c>
       <c r="AR24" t="s">
         <v>534</v>
@@ -12043,16 +12043,16 @@
         <v>1174</v>
       </c>
       <c r="BA24" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="BB24" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="BC24">
-        <v>0.98488330873784669</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD24">
-        <v>277.13933980614473</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12117,16 +12117,16 @@
         <v>565</v>
       </c>
       <c r="Y25" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="Z25" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA25">
-        <v>0.99726809134187266</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB25">
-        <v>50.0849920656675</v>
+        <v>92.674656500591539</v>
       </c>
       <c r="AD25" t="s">
         <v>534</v>
@@ -12153,16 +12153,16 @@
         <v>904</v>
       </c>
       <c r="AM25" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AN25" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AO25">
-        <v>0.99445933293330402</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP25">
-        <v>101.57889622275951</v>
+        <v>60.189444792275019</v>
       </c>
       <c r="AR25" t="s">
         <v>534</v>
@@ -12189,16 +12189,16 @@
         <v>1176</v>
       </c>
       <c r="BA25" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="BB25" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="BC25">
-        <v>0.99526086651282741</v>
+        <v>0.99563011519444145</v>
       </c>
       <c r="BD25">
-        <v>86.884113931497708</v>
+        <v>80.114554768572972</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12263,16 +12263,16 @@
         <v>567</v>
       </c>
       <c r="Y26" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="Z26" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AA26">
-        <v>0.97962408753770291</v>
+        <v>0.99438812565699364</v>
       </c>
       <c r="AB26">
-        <v>373.55839514211272</v>
+        <v>102.88436295511657</v>
       </c>
       <c r="AD26" t="s">
         <v>534</v>
@@ -12299,16 +12299,16 @@
         <v>906</v>
       </c>
       <c r="AM26" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AN26" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="AO26">
-        <v>0.9961850470371636</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP26">
-        <v>69.94080431866837</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR26" t="s">
         <v>534</v>
@@ -12335,16 +12335,16 @@
         <v>1178</v>
       </c>
       <c r="BA26" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="BB26" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="BC26">
-        <v>0.99665799830099</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD26">
-        <v>61.270031148516708</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12409,16 +12409,16 @@
         <v>569</v>
       </c>
       <c r="Y27" t="s">
-        <v>498</v>
+        <v>523</v>
       </c>
       <c r="Z27" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AA27">
-        <v>0.99098167665935155</v>
+        <v>0.99643191679577148</v>
       </c>
       <c r="AB27">
-        <v>165.33592791188894</v>
+        <v>65.414858744189985</v>
       </c>
       <c r="AD27" t="s">
         <v>534</v>
@@ -12445,16 +12445,16 @@
         <v>908</v>
       </c>
       <c r="AM27" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AN27" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AO27">
-        <v>0.99710531380540124</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP27">
-        <v>53.069246900976879</v>
+        <v>83.589016951479763</v>
       </c>
       <c r="AR27" t="s">
         <v>534</v>
@@ -12481,16 +12481,16 @@
         <v>1180</v>
       </c>
       <c r="BA27" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="BB27" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="BC27">
-        <v>0.9959052853503485</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD27">
-        <v>75.06976857694373</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12555,16 +12555,16 @@
         <v>571</v>
       </c>
       <c r="Y28" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="Z28" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AA28">
-        <v>0.98485684158558628</v>
+        <v>0.99012236069527793</v>
       </c>
       <c r="AB28">
-        <v>277.62457093091871</v>
+        <v>181.09005391990564</v>
       </c>
       <c r="AD28" t="s">
         <v>534</v>
@@ -12591,16 +12591,16 @@
         <v>910</v>
       </c>
       <c r="AM28" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AN28" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="AO28">
-        <v>0.98134982200735632</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP28">
-        <v>341.91992986513412</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR28" t="s">
         <v>534</v>
@@ -12627,16 +12627,16 @@
         <v>1182</v>
       </c>
       <c r="BA28" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="BB28" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="BC28">
-        <v>0.99563011519444145</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD28">
-        <v>80.114554768572972</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12701,16 +12701,16 @@
         <v>573</v>
       </c>
       <c r="Y29" t="s">
-        <v>493</v>
+        <v>435</v>
       </c>
       <c r="Z29" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AA29">
-        <v>0.98211145389932475</v>
+        <v>0.98990296758392993</v>
       </c>
       <c r="AB29">
-        <v>327.95667851237977</v>
+        <v>185.11226096128556</v>
       </c>
       <c r="AD29" t="s">
         <v>534</v>
@@ -12737,16 +12737,16 @@
         <v>912</v>
       </c>
       <c r="AM29" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AN29" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="AO29">
-        <v>0.98589595763902149</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP29">
-        <v>258.57410995127316</v>
+        <v>57.905423216266421</v>
       </c>
       <c r="AR29" t="s">
         <v>534</v>
@@ -12773,16 +12773,16 @@
         <v>1184</v>
       </c>
       <c r="BA29" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="BB29" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="BC29">
-        <v>0.99054926914187857</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD29">
-        <v>173.26339906555947</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12847,16 +12847,16 @@
         <v>575</v>
       </c>
       <c r="Y30" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="Z30" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AA30">
-        <v>0.99654205356515035</v>
+        <v>0.99377714174527498</v>
       </c>
       <c r="AB30">
-        <v>63.395684638909763</v>
+        <v>114.08573466995766</v>
       </c>
       <c r="AD30" t="s">
         <v>534</v>
@@ -12883,16 +12883,16 @@
         <v>914</v>
       </c>
       <c r="AM30" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AN30" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AO30">
-        <v>0.99776894175014486</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP30">
-        <v>40.90273458067751</v>
+        <v>85.716830221163534</v>
       </c>
       <c r="AR30" t="s">
         <v>534</v>
@@ -12919,16 +12919,16 @@
         <v>1186</v>
       </c>
       <c r="BA30" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="BB30" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="BC30">
-        <v>0.98027195861782945</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD30">
-        <v>361.68075867312689</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12993,16 +12993,16 @@
         <v>577</v>
       </c>
       <c r="Y31" t="s">
-        <v>460</v>
+        <v>525</v>
       </c>
       <c r="Z31" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AA31">
-        <v>0.99504817442297822</v>
+        <v>0.99516685156772267</v>
       </c>
       <c r="AB31">
-        <v>90.78346891206678</v>
+        <v>88.60772125841865</v>
       </c>
       <c r="AD31" t="s">
         <v>534</v>
@@ -13029,16 +13029,16 @@
         <v>916</v>
       </c>
       <c r="AM31" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AN31" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="AO31">
-        <v>0.9959346869215373</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP31">
-        <v>74.530739771815789</v>
+        <v>74.464817689622748</v>
       </c>
       <c r="AR31" t="s">
         <v>534</v>
@@ -13065,16 +13065,16 @@
         <v>1188</v>
       </c>
       <c r="BA31" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="BB31" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="BC31">
-        <v>0.98125520899414764</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD31">
-        <v>343.65450177395917</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13139,16 +13139,16 @@
         <v>579</v>
       </c>
       <c r="Y32" t="s">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="Z32" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AA32">
-        <v>0.99470247457730832</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB32">
-        <v>97.121299416014665</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD32" t="s">
         <v>534</v>
@@ -13175,10 +13175,10 @@
         <v>918</v>
       </c>
       <c r="AM32" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="AN32" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AO32">
         <v>0.97020178001960844</v>
@@ -13211,16 +13211,16 @@
         <v>1190</v>
       </c>
       <c r="BA32" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="BB32" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="BC32">
-        <v>0.98574436213546524</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD32">
-        <v>261.35336084980423</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13285,16 +13285,16 @@
         <v>581</v>
       </c>
       <c r="Y33" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="Z33" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AA33">
-        <v>0.99549782242326257</v>
+        <v>0.99726809134187266</v>
       </c>
       <c r="AB33">
-        <v>82.539922240185263</v>
+        <v>50.0849920656675</v>
       </c>
       <c r="AD33" t="s">
         <v>534</v>
@@ -13321,10 +13321,10 @@
         <v>920</v>
       </c>
       <c r="AM33" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AN33" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="AO33">
         <v>0.99693672852577231</v>
@@ -13357,16 +13357,16 @@
         <v>1192</v>
       </c>
       <c r="BA33" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="BB33" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="BC33">
-        <v>0.98163861082146986</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD33">
-        <v>336.62546827305243</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13431,16 +13431,16 @@
         <v>583</v>
       </c>
       <c r="Y34" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="Z34" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="AA34">
-        <v>0.9621480095608167</v>
+        <v>0.97962408753770291</v>
       </c>
       <c r="AB34">
-        <v>693.95315805169378</v>
+        <v>373.55839514211272</v>
       </c>
       <c r="AD34" t="s">
         <v>534</v>
@@ -13467,10 +13467,10 @@
         <v>922</v>
       </c>
       <c r="AM34" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AN34" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="AO34">
         <v>0.99478775228549088</v>
@@ -13503,16 +13503,16 @@
         <v>1194</v>
       </c>
       <c r="BA34" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="BB34" t="s">
-        <v>1255</v>
+        <v>1107</v>
       </c>
       <c r="BC34">
-        <v>0.98691003029105739</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD34">
-        <v>239.98277799728109</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13577,16 +13577,16 @@
         <v>585</v>
       </c>
       <c r="Y35" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="Z35" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="AA35">
-        <v>0.98916941127667946</v>
+        <v>0.99098167665935155</v>
       </c>
       <c r="AB35">
-        <v>198.56079326087576</v>
+        <v>165.33592791188894</v>
       </c>
       <c r="AD35" t="s">
         <v>534</v>
@@ -13613,16 +13613,16 @@
         <v>924</v>
       </c>
       <c r="AM35" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="AN35" t="s">
-        <v>851</v>
+        <v>1063</v>
       </c>
       <c r="AO35">
-        <v>0.95532613069733086</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP35">
-        <v>819.02093721560016</v>
+        <v>138.50582323297994</v>
       </c>
       <c r="AR35" t="s">
         <v>534</v>
@@ -13655,10 +13655,10 @@
         <v>1257</v>
       </c>
       <c r="BC35">
-        <v>0.98890025255868685</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD35">
-        <v>203.49536975740753</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13723,16 +13723,16 @@
         <v>587</v>
       </c>
       <c r="Y36" t="s">
-        <v>438</v>
+        <v>503</v>
       </c>
       <c r="Z36" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AA36">
-        <v>0.97159134368321343</v>
+        <v>0.98485684158558628</v>
       </c>
       <c r="AB36">
-        <v>520.82536580775354</v>
+        <v>277.62457093091871</v>
       </c>
       <c r="AD36" t="s">
         <v>534</v>
@@ -13759,16 +13759,16 @@
         <v>926</v>
       </c>
       <c r="AM36" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="AN36" t="s">
-        <v>798</v>
+        <v>770</v>
       </c>
       <c r="AO36">
-        <v>0.98599828568941739</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP36">
-        <v>256.69809569401372</v>
+        <v>473.60023862765331</v>
       </c>
       <c r="AR36" t="s">
         <v>534</v>
@@ -13801,10 +13801,10 @@
         <v>1259</v>
       </c>
       <c r="BC36">
-        <v>0.99481196273061234</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD36">
-        <v>95.114016605440895</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13869,16 +13869,16 @@
         <v>589</v>
       </c>
       <c r="Y37" t="s">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="Z37" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AA37">
-        <v>0.99359614530212825</v>
+        <v>0.98211145389932475</v>
       </c>
       <c r="AB37">
-        <v>117.40400279431638</v>
+        <v>327.95667851237977</v>
       </c>
       <c r="AD37" t="s">
         <v>534</v>
@@ -13905,16 +13905,16 @@
         <v>928</v>
       </c>
       <c r="AM37" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="AN37" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="AO37">
-        <v>0.98996241922424166</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP37">
-        <v>184.02231422223667</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR37" t="s">
         <v>534</v>
@@ -13944,13 +13944,13 @@
         <v>1260</v>
       </c>
       <c r="BB37" t="s">
-        <v>1261</v>
+        <v>1222</v>
       </c>
       <c r="BC37">
-        <v>0.99374755699184159</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD37">
-        <v>114.62812181623703</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14015,16 +14015,16 @@
         <v>591</v>
       </c>
       <c r="Y38" t="s">
-        <v>518</v>
+        <v>467</v>
       </c>
       <c r="Z38" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AA38">
-        <v>0.99488082982009873</v>
+        <v>0.99654205356515035</v>
       </c>
       <c r="AB38">
-        <v>93.851453298190577</v>
+        <v>63.395684638909763</v>
       </c>
       <c r="AD38" t="s">
         <v>534</v>
@@ -14051,16 +14051,16 @@
         <v>930</v>
       </c>
       <c r="AM38" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="AN38" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="AO38">
-        <v>0.99620534810300254</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP38">
-        <v>69.568618111619969</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR38" t="s">
         <v>534</v>
@@ -14087,16 +14087,16 @@
         <v>1202</v>
       </c>
       <c r="BA38" t="s">
+        <v>1261</v>
+      </c>
+      <c r="BB38" t="s">
         <v>1262</v>
       </c>
-      <c r="BB38" t="s">
-        <v>1228</v>
-      </c>
       <c r="BC38">
-        <v>0.99203097418485064</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD38">
-        <v>146.09880661107059</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14161,16 +14161,16 @@
         <v>593</v>
       </c>
       <c r="Y39" t="s">
-        <v>513</v>
+        <v>460</v>
       </c>
       <c r="Z39" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AA39">
-        <v>0.99557743229498485</v>
+        <v>0.99504817442297822</v>
       </c>
       <c r="AB39">
-        <v>81.080407925277868</v>
+        <v>90.78346891206678</v>
       </c>
       <c r="AD39" t="s">
         <v>534</v>
@@ -14197,16 +14197,16 @@
         <v>932</v>
       </c>
       <c r="AM39" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="AN39" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AO39">
-        <v>0.99374536027070226</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP39">
-        <v>114.668395037126</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR39" t="s">
         <v>534</v>
@@ -14239,10 +14239,10 @@
         <v>1264</v>
       </c>
       <c r="BC39">
-        <v>0.97821242976023937</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD39">
-        <v>399.43878772894504</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14307,16 +14307,16 @@
         <v>595</v>
       </c>
       <c r="Y40" t="s">
-        <v>455</v>
+        <v>507</v>
       </c>
       <c r="Z40" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AA40">
-        <v>0.99401156108202648</v>
+        <v>0.99470247457730832</v>
       </c>
       <c r="AB40">
-        <v>109.78804682951412</v>
+        <v>97.121299416014665</v>
       </c>
       <c r="AD40" t="s">
         <v>534</v>
@@ -14343,16 +14343,16 @@
         <v>934</v>
       </c>
       <c r="AM40" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="AN40" t="s">
-        <v>1070</v>
+        <v>787</v>
       </c>
       <c r="AO40">
-        <v>0.99681385284485569</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP40">
-        <v>58.41269784431158</v>
+        <v>243.0827225935364</v>
       </c>
       <c r="AR40" t="s">
         <v>534</v>
@@ -14385,10 +14385,10 @@
         <v>1266</v>
       </c>
       <c r="BC40">
-        <v>0.99032129621526932</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD40">
-        <v>177.44290272006148</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14453,16 +14453,16 @@
         <v>597</v>
       </c>
       <c r="Y41" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="Z41" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AA41">
-        <v>0.99295369446862825</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB41">
-        <v>129.18226807514921</v>
+        <v>82.539922240185263</v>
       </c>
       <c r="AD41" t="s">
         <v>534</v>
@@ -14489,16 +14489,16 @@
         <v>936</v>
       </c>
       <c r="AM41" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AN41" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AO41">
-        <v>0.99527237968252791</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP41">
-        <v>86.673039153654699</v>
+        <v>283.70480651649393</v>
       </c>
       <c r="AR41" t="s">
         <v>534</v>
@@ -14531,10 +14531,10 @@
         <v>1268</v>
       </c>
       <c r="BC41">
-        <v>0.99420451954813838</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD41">
-        <v>106.25047495079694</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14599,16 +14599,16 @@
         <v>599</v>
       </c>
       <c r="Y42" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="Z42" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AA42">
-        <v>0.98571261124433651</v>
+        <v>0.9914627894548943</v>
       </c>
       <c r="AB42">
-        <v>261.93546052049794</v>
+        <v>156.51552666027055</v>
       </c>
       <c r="AD42" t="s">
         <v>534</v>
@@ -14635,16 +14635,16 @@
         <v>938</v>
       </c>
       <c r="AM42" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AN42" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AO42">
-        <v>0.9917253583369573</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP42">
-        <v>151.70176382244892</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14709,16 +14709,16 @@
         <v>601</v>
       </c>
       <c r="Y43" t="s">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="Z43" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AA43">
-        <v>0.9849019911873127</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB43">
-        <v>276.79682823259958</v>
+        <v>409.70769939155917</v>
       </c>
       <c r="AD43" t="s">
         <v>534</v>
@@ -14745,16 +14745,16 @@
         <v>940</v>
       </c>
       <c r="AM43" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AN43" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="AO43">
-        <v>0.99569050067699549</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP43">
-        <v>79.007487588415231</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14819,16 +14819,16 @@
         <v>603</v>
       </c>
       <c r="Y44" t="s">
-        <v>419</v>
+        <v>504</v>
       </c>
       <c r="Z44" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AA44">
-        <v>0.99157679714615166</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB44">
-        <v>154.42538565388551</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD44" t="s">
         <v>534</v>
@@ -14855,16 +14855,16 @@
         <v>942</v>
       </c>
       <c r="AM44" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="AN44" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="AO44">
-        <v>0.99551365545858539</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP44">
-        <v>82.249649925934918</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14929,16 +14929,16 @@
         <v>605</v>
       </c>
       <c r="Y45" t="s">
-        <v>515</v>
+        <v>424</v>
       </c>
       <c r="Z45" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AA45">
-        <v>0.99619387577842089</v>
+        <v>0.99593583828988941</v>
       </c>
       <c r="AB45">
-        <v>69.778944062284495</v>
+        <v>74.509631352026517</v>
       </c>
       <c r="AD45" t="s">
         <v>534</v>
@@ -14965,16 +14965,16 @@
         <v>944</v>
       </c>
       <c r="AM45" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AN45" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AO45">
-        <v>0.99554924619735208</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP45">
-        <v>81.597153048545437</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15039,16 +15039,16 @@
         <v>607</v>
       </c>
       <c r="Y46" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="Z46" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AA46">
-        <v>0.99497915241892609</v>
+        <v>0.98150124893892388</v>
       </c>
       <c r="AB46">
-        <v>92.048872319688599</v>
+        <v>339.14376945306287</v>
       </c>
       <c r="AD46" t="s">
         <v>534</v>
@@ -15075,16 +15075,16 @@
         <v>946</v>
       </c>
       <c r="AM46" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="AN46" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AO46">
-        <v>0.99083036293819104</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP46">
-        <v>168.11001279983091</v>
+        <v>53.069246900976879</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15149,16 +15149,16 @@
         <v>609</v>
       </c>
       <c r="Y47" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="Z47" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AA47">
-        <v>0.9914627894548943</v>
+        <v>0.99523081353776888</v>
       </c>
       <c r="AB47">
-        <v>156.51552666027055</v>
+        <v>87.435085140903482</v>
       </c>
       <c r="AD47" t="s">
         <v>534</v>
@@ -15185,16 +15185,16 @@
         <v>948</v>
       </c>
       <c r="AM47" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AN47" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AO47">
-        <v>0.9976320377495026</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP47">
-        <v>43.412641259119624</v>
+        <v>109.31605592223302</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15259,16 +15259,16 @@
         <v>611</v>
       </c>
       <c r="Y48" t="s">
-        <v>500</v>
+        <v>442</v>
       </c>
       <c r="Z48" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AA48">
-        <v>0.9776523073059149</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB48">
-        <v>409.70769939155917</v>
+        <v>153.20678909592235</v>
       </c>
       <c r="AD48" t="s">
         <v>534</v>
@@ -15295,16 +15295,16 @@
         <v>950</v>
       </c>
       <c r="AM48" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="AN48" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="AO48">
-        <v>0.99424679200457</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP48">
-        <v>105.47547991621673</v>
+        <v>163.93514059684662</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15369,16 +15369,16 @@
         <v>613</v>
       </c>
       <c r="Y49" t="s">
-        <v>504</v>
+        <v>423</v>
       </c>
       <c r="Z49" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AA49">
-        <v>0.98289281118622185</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB49">
-        <v>313.63179491926536</v>
+        <v>78.81162391526847</v>
       </c>
       <c r="AD49" t="s">
         <v>534</v>
@@ -15405,16 +15405,16 @@
         <v>952</v>
       </c>
       <c r="AM49" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="AN49" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="AO49">
-        <v>0.98934663566509429</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP49">
-        <v>195.31167947327185</v>
+        <v>46.428192737512276</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15479,16 +15479,16 @@
         <v>615</v>
       </c>
       <c r="Y50" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="Z50" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AA50">
-        <v>0.99593583828988941</v>
+        <v>0.99691903985105013</v>
       </c>
       <c r="AB50">
-        <v>74.509631352026517</v>
+        <v>56.484269397415083</v>
       </c>
       <c r="AD50" t="s">
         <v>534</v>
@@ -15515,16 +15515,16 @@
         <v>954</v>
       </c>
       <c r="AM50" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AN50" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AO50">
-        <v>0.99499049355022928</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP50">
-        <v>91.840951579129481</v>
+        <v>85.270745539791065</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15589,16 +15589,16 @@
         <v>617</v>
       </c>
       <c r="Y51" t="s">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="Z51" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AA51">
-        <v>0.98150124893892388</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB51">
-        <v>339.14376945306287</v>
+        <v>263.42178867339101</v>
       </c>
       <c r="AD51" t="s">
         <v>534</v>
@@ -15625,16 +15625,16 @@
         <v>956</v>
       </c>
       <c r="AM51" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN51" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AO51">
-        <v>0.99729205446773184</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP51">
-        <v>49.645668091582088</v>
+        <v>82.249649925934918</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15699,16 +15699,16 @@
         <v>619</v>
       </c>
       <c r="Y52" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="Z52" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AA52">
-        <v>0.99523081353776888</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB52">
-        <v>87.435085140903482</v>
+        <v>86.308558527470979</v>
       </c>
       <c r="AD52" t="s">
         <v>534</v>
@@ -15735,16 +15735,16 @@
         <v>958</v>
       </c>
       <c r="AM52" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AN52" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AO52">
-        <v>0.99746043308117838</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP52">
-        <v>46.558726845063177</v>
+        <v>81.597153048545437</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15809,16 +15809,16 @@
         <v>621</v>
       </c>
       <c r="Y53" t="s">
-        <v>442</v>
+        <v>511</v>
       </c>
       <c r="Z53" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AA53">
-        <v>0.9916432660493133</v>
+        <v>0.99443562760718263</v>
       </c>
       <c r="AB53">
-        <v>153.20678909592235</v>
+        <v>102.01349386831856</v>
       </c>
       <c r="AD53" t="s">
         <v>534</v>
@@ -15845,16 +15845,16 @@
         <v>960</v>
       </c>
       <c r="AM53" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AN53" t="s">
-        <v>843</v>
+        <v>1097</v>
       </c>
       <c r="AO53">
-        <v>0.98674094240398891</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP53">
-        <v>243.0827225935364</v>
+        <v>168.11001279983091</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15919,16 +15919,16 @@
         <v>623</v>
       </c>
       <c r="Y54" t="s">
-        <v>423</v>
+        <v>529</v>
       </c>
       <c r="Z54" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AA54">
-        <v>0.99570118415007625</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB54">
-        <v>78.81162391526847</v>
+        <v>637.85920701836687</v>
       </c>
       <c r="AD54" t="s">
         <v>534</v>
@@ -15955,16 +15955,16 @@
         <v>962</v>
       </c>
       <c r="AM54" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="AN54" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="AO54">
-        <v>0.98452519237182756</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP54">
-        <v>283.70480651649393</v>
+        <v>43.412641259119624</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16029,16 +16029,16 @@
         <v>625</v>
       </c>
       <c r="Y55" t="s">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="Z55" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AA55">
-        <v>0.99691903985105013</v>
+        <v>0.99344074878931121</v>
       </c>
       <c r="AB55">
-        <v>56.484269397415083</v>
+        <v>120.25293886262826</v>
       </c>
       <c r="AD55" t="s">
         <v>534</v>
@@ -16065,16 +16065,16 @@
         <v>964</v>
       </c>
       <c r="AM55" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="AN55" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="AO55">
-        <v>0.99679967385551038</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP55">
-        <v>58.672645982308907</v>
+        <v>105.47547991621673</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16139,16 +16139,16 @@
         <v>627</v>
       </c>
       <c r="Y56" t="s">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="Z56" t="s">
-        <v>811</v>
+        <v>777</v>
       </c>
       <c r="AA56">
-        <v>0.98563153879963317</v>
+        <v>0.99459650548991607</v>
       </c>
       <c r="AB56">
-        <v>263.42178867339101</v>
+        <v>99.064066018204684</v>
       </c>
       <c r="AD56" t="s">
         <v>534</v>
@@ -16175,16 +16175,16 @@
         <v>966</v>
       </c>
       <c r="AM56" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="AN56" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AO56">
-        <v>0.99414234808301016</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP56">
-        <v>107.39028514481463</v>
+        <v>195.31167947327185</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16249,16 +16249,16 @@
         <v>629</v>
       </c>
       <c r="Y57" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="Z57" t="s">
         <v>812</v>
       </c>
       <c r="AA57">
-        <v>0.99529226044395613</v>
+        <v>0.99655727877565281</v>
       </c>
       <c r="AB57">
-        <v>86.308558527470979</v>
+        <v>63.116555779697698</v>
       </c>
       <c r="AD57" t="s">
         <v>534</v>
@@ -16285,16 +16285,16 @@
         <v>968</v>
       </c>
       <c r="AM57" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="AN57" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AO57">
-        <v>0.97651207122624506</v>
+        <v>0.99499049355022928</v>
       </c>
       <c r="AP57">
-        <v>430.61202751883985</v>
+        <v>91.840951579129481</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16359,16 +16359,16 @@
         <v>631</v>
       </c>
       <c r="Y58" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="Z58" t="s">
         <v>813</v>
       </c>
       <c r="AA58">
-        <v>0.99443562760718263</v>
+        <v>0.99221351039035977</v>
       </c>
       <c r="AB58">
-        <v>102.01349386831856</v>
+        <v>142.75230951007163</v>
       </c>
       <c r="AD58" t="s">
         <v>534</v>
@@ -16395,16 +16395,16 @@
         <v>970</v>
       </c>
       <c r="AM58" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AN58" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="AO58">
-        <v>0.9972012891192491</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP58">
-        <v>51.309699480432613</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16469,16 +16469,16 @@
         <v>633</v>
       </c>
       <c r="Y59" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="Z59" t="s">
         <v>814</v>
       </c>
       <c r="AA59">
-        <v>0.99553066735440277</v>
+        <v>0.99067174034238459</v>
       </c>
       <c r="AB59">
-        <v>81.937765169281747</v>
+        <v>171.01809372294977</v>
       </c>
       <c r="AD59" t="s">
         <v>534</v>
@@ -16505,16 +16505,16 @@
         <v>972</v>
       </c>
       <c r="AM59" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="AN59" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="AO59">
-        <v>0.99648541839873139</v>
+        <v>0.99746043308117838</v>
       </c>
       <c r="AP59">
-        <v>64.433996023258757</v>
+        <v>46.558726845063177</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16579,16 +16579,16 @@
         <v>635</v>
       </c>
       <c r="Y60" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="Z60" t="s">
         <v>815</v>
       </c>
       <c r="AA60">
-        <v>0.99049341406542279</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB60">
-        <v>174.28740880058183</v>
+        <v>67.023399161603095</v>
       </c>
       <c r="AD60" t="s">
         <v>534</v>
@@ -16615,16 +16615,16 @@
         <v>974</v>
       </c>
       <c r="AM60" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AN60" t="s">
-        <v>1109</v>
+        <v>778</v>
       </c>
       <c r="AO60">
-        <v>0.9976540150806753</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP60">
-        <v>43.009723520953628</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16689,16 +16689,16 @@
         <v>637</v>
       </c>
       <c r="Y61" t="s">
-        <v>522</v>
+        <v>453</v>
       </c>
       <c r="Z61" t="s">
         <v>816</v>
       </c>
       <c r="AA61">
-        <v>0.99575157784901702</v>
+        <v>0.98416341622871006</v>
       </c>
       <c r="AB61">
-        <v>77.887739434686992</v>
+        <v>290.33736914031488</v>
       </c>
       <c r="AD61" t="s">
         <v>534</v>
@@ -16725,16 +16725,16 @@
         <v>976</v>
       </c>
       <c r="AM61" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="AN61" t="s">
-        <v>1111</v>
+        <v>835</v>
       </c>
       <c r="AO61">
-        <v>0.99644815774097173</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP61">
-        <v>65.117108082185538</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16799,16 +16799,16 @@
         <v>639</v>
       </c>
       <c r="Y62" t="s">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="Z62" t="s">
         <v>817</v>
       </c>
       <c r="AA62">
-        <v>0.96520767961718001</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB62">
-        <v>637.85920701836687</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD62" t="s">
         <v>534</v>
@@ -16841,10 +16841,10 @@
         <v>1113</v>
       </c>
       <c r="AO62">
-        <v>0.99684152237002188</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP62">
-        <v>57.905423216266421</v>
+        <v>184.02231422223667</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16909,16 +16909,16 @@
         <v>641</v>
       </c>
       <c r="Y63" t="s">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="Z63" t="s">
         <v>818</v>
       </c>
       <c r="AA63">
-        <v>0.99344074878931121</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB63">
-        <v>120.25293886262826</v>
+        <v>81.000126667143434</v>
       </c>
       <c r="AD63" t="s">
         <v>534</v>
@@ -16951,10 +16951,10 @@
         <v>1115</v>
       </c>
       <c r="AO63">
-        <v>0.99532453653339104</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP63">
-        <v>85.716830221163534</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17019,16 +17019,16 @@
         <v>643</v>
       </c>
       <c r="Y64" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="Z64" t="s">
-        <v>783</v>
+        <v>819</v>
       </c>
       <c r="AA64">
-        <v>0.99459650548991607</v>
+        <v>0.99390501557434718</v>
       </c>
       <c r="AB64">
-        <v>99.064066018204684</v>
+        <v>111.7413811369688</v>
       </c>
       <c r="AD64" t="s">
         <v>534</v>
@@ -17061,10 +17061,10 @@
         <v>1117</v>
       </c>
       <c r="AO64">
-        <v>0.99593828267147511</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP64">
-        <v>74.464817689622748</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17129,16 +17129,16 @@
         <v>645</v>
       </c>
       <c r="Y65" t="s">
-        <v>490</v>
+        <v>421</v>
       </c>
       <c r="Z65" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AA65">
-        <v>0.99655727877565281</v>
+        <v>0.99553066735440277</v>
       </c>
       <c r="AB65">
-        <v>63.116555779697698</v>
+        <v>81.937765169281747</v>
       </c>
       <c r="AD65" t="s">
         <v>534</v>
@@ -17171,10 +17171,10 @@
         <v>1119</v>
       </c>
       <c r="AO65">
-        <v>0.99473480482648013</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP65">
-        <v>96.528578181196991</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17239,16 +17239,16 @@
         <v>647</v>
       </c>
       <c r="Y66" t="s">
-        <v>488</v>
+        <v>445</v>
       </c>
       <c r="Z66" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AA66">
-        <v>0.99221351039035977</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB66">
-        <v>142.75230951007163</v>
+        <v>174.28740880058183</v>
       </c>
       <c r="AD66" t="s">
         <v>534</v>
@@ -17281,10 +17281,10 @@
         <v>1121</v>
       </c>
       <c r="AO66">
-        <v>0.99729761494442914</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP66">
-        <v>49.543726018799653</v>
+        <v>86.673039153654699</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17349,16 +17349,16 @@
         <v>649</v>
       </c>
       <c r="Y67" t="s">
-        <v>447</v>
+        <v>522</v>
       </c>
       <c r="Z67" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AA67">
-        <v>0.99067174034238459</v>
+        <v>0.99575157784901702</v>
       </c>
       <c r="AB67">
-        <v>171.01809372294977</v>
+        <v>77.887739434686992</v>
       </c>
       <c r="AD67" t="s">
         <v>534</v>
@@ -17391,10 +17391,10 @@
         <v>1123</v>
       </c>
       <c r="AO67">
-        <v>0.996795372708284</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP67">
-        <v>58.751500348127372</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17459,16 +17459,16 @@
         <v>651</v>
       </c>
       <c r="Y68" t="s">
-        <v>418</v>
+        <v>472</v>
       </c>
       <c r="Z68" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AA68">
-        <v>0.99634417822754895</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB68">
-        <v>67.023399161603095</v>
+        <v>64.274570700309781</v>
       </c>
       <c r="AD68" t="s">
         <v>534</v>
@@ -17501,10 +17501,10 @@
         <v>1125</v>
       </c>
       <c r="AO68">
-        <v>0.99274560110857168</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP68">
-        <v>132.99731300951822</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17569,16 +17569,16 @@
         <v>653</v>
       </c>
       <c r="Y69" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="Z69" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AA69">
-        <v>0.98416341622871006</v>
+        <v>0.97907421743006762</v>
       </c>
       <c r="AB69">
-        <v>290.33736914031488</v>
+        <v>383.63934711542669</v>
       </c>
       <c r="AD69" t="s">
         <v>534</v>
@@ -17611,10 +17611,10 @@
         <v>1127</v>
       </c>
       <c r="AO69">
-        <v>0.9955955730654259</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP69">
-        <v>80.747827133859133</v>
+        <v>430.61202751883985</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17679,16 +17679,16 @@
         <v>655</v>
       </c>
       <c r="Y70" t="s">
-        <v>497</v>
+        <v>426</v>
       </c>
       <c r="Z70" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA70">
-        <v>0.99563792883070867</v>
+        <v>0.99558768376711515</v>
       </c>
       <c r="AB70">
-        <v>79.971304770340467</v>
+        <v>80.892464269556413</v>
       </c>
       <c r="AD70" t="s">
         <v>534</v>
@@ -17721,10 +17721,10 @@
         <v>1129</v>
       </c>
       <c r="AO70">
-        <v>0.99671693937496686</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP70">
-        <v>60.189444792275019</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17789,16 +17789,16 @@
         <v>657</v>
       </c>
       <c r="Y71" t="s">
-        <v>432</v>
+        <v>510</v>
       </c>
       <c r="Z71" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AA71">
-        <v>0.99558181127270129</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB71">
-        <v>81.000126667143434</v>
+        <v>123.82892298254488</v>
       </c>
       <c r="AD71" t="s">
         <v>534</v>
@@ -17831,10 +17831,10 @@
         <v>1131</v>
       </c>
       <c r="AO71">
-        <v>0.99567626923235475</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP71">
-        <v>79.268397406829976</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17899,16 +17899,16 @@
         <v>659</v>
       </c>
       <c r="Y72" t="s">
-        <v>516</v>
+        <v>464</v>
       </c>
       <c r="Z72" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AA72">
-        <v>0.99390501557434718</v>
+        <v>0.99419165427276146</v>
       </c>
       <c r="AB72">
-        <v>111.7413811369688</v>
+        <v>106.48633833270691</v>
       </c>
       <c r="AD72" t="s">
         <v>534</v>
@@ -17941,10 +17941,10 @@
         <v>1133</v>
       </c>
       <c r="AO72">
-        <v>0.99762284649610655</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP72">
-        <v>43.581147571379539</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18009,16 +18009,16 @@
         <v>661</v>
       </c>
       <c r="Y73" t="s">
-        <v>527</v>
+        <v>458</v>
       </c>
       <c r="Z73" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AA73">
-        <v>0.95261480241426988</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB73">
-        <v>868.72862240505196</v>
+        <v>146.8618143486346</v>
       </c>
       <c r="AD73" t="s">
         <v>534</v>
@@ -18051,10 +18051,10 @@
         <v>1135</v>
       </c>
       <c r="AO73">
-        <v>0.99175391794306234</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP73">
-        <v>151.17817104385733</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18119,16 +18119,16 @@
         <v>663</v>
       </c>
       <c r="Y74" t="s">
-        <v>531</v>
+        <v>471</v>
       </c>
       <c r="Z74" t="s">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="AA74">
-        <v>0.97404342257401955</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB74">
-        <v>475.8705861429753</v>
+        <v>470.66510807906917</v>
       </c>
       <c r="AD74" t="s">
         <v>534</v>
@@ -18161,10 +18161,10 @@
         <v>1137</v>
       </c>
       <c r="AO74">
-        <v>0.99688290256322298</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP74">
-        <v>57.146786340912868</v>
+        <v>79.268397406829976</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18229,16 +18229,16 @@
         <v>665</v>
       </c>
       <c r="Y75" t="s">
-        <v>420</v>
+        <v>487</v>
       </c>
       <c r="Z75" t="s">
         <v>829</v>
       </c>
       <c r="AA75">
-        <v>0.98762421667584677</v>
+        <v>0.9882282251528024</v>
       </c>
       <c r="AB75">
-        <v>226.88936094280919</v>
+        <v>215.81587219862183</v>
       </c>
       <c r="AD75" t="s">
         <v>534</v>
@@ -18271,10 +18271,10 @@
         <v>1139</v>
       </c>
       <c r="AO75">
-        <v>0.99488275259079373</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP75">
-        <v>93.81620250211445</v>
+        <v>43.581147571379539</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18339,16 +18339,16 @@
         <v>667</v>
       </c>
       <c r="Y76" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="Z76" t="s">
         <v>830</v>
       </c>
       <c r="AA76">
-        <v>0.98775140142897844</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB76">
-        <v>224.55764046872929</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD76" t="s">
         <v>534</v>
@@ -18381,10 +18381,10 @@
         <v>1141</v>
       </c>
       <c r="AO76">
-        <v>0.99663220850609069</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP76">
-        <v>61.742844055003644</v>
+        <v>151.17817104385733</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18449,16 +18449,16 @@
         <v>669</v>
       </c>
       <c r="Y77" t="s">
-        <v>495</v>
+        <v>427</v>
       </c>
       <c r="Z77" t="s">
         <v>831</v>
       </c>
       <c r="AA77">
-        <v>0.99647006537565563</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB77">
-        <v>64.715468112981057</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD77" t="s">
         <v>534</v>
@@ -18491,10 +18491,10 @@
         <v>1143</v>
       </c>
       <c r="AO77">
-        <v>0.99503039970536677</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP77">
-        <v>91.109338734942796</v>
+        <v>57.146786340912868</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18559,16 +18559,16 @@
         <v>671</v>
       </c>
       <c r="Y78" t="s">
-        <v>492</v>
+        <v>428</v>
       </c>
       <c r="Z78" t="s">
         <v>832</v>
       </c>
       <c r="AA78">
-        <v>0.96480371616361149</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB78">
-        <v>645.26520366712316</v>
+        <v>41.695953373122713</v>
       </c>
       <c r="AD78" t="s">
         <v>534</v>
@@ -18601,10 +18601,10 @@
         <v>1145</v>
       </c>
       <c r="AO78">
-        <v>0.99544059907537386</v>
+        <v>0.99488275259079373</v>
       </c>
       <c r="AP78">
-        <v>83.589016951479763</v>
+        <v>93.81620250211445</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18669,16 +18669,16 @@
         <v>673</v>
       </c>
       <c r="Y79" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="Z79" t="s">
         <v>833</v>
       </c>
       <c r="AA79">
-        <v>0.99267004448650609</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB79">
-        <v>134.38251774738842</v>
+        <v>129.18226807514921</v>
       </c>
       <c r="AD79" t="s">
         <v>534</v>
@@ -18711,10 +18711,10 @@
         <v>1147</v>
       </c>
       <c r="AO79">
-        <v>0.98829989485605374</v>
+        <v>0.99663220850609069</v>
       </c>
       <c r="AP79">
-        <v>214.50192763901472</v>
+        <v>61.742844055003644</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18779,16 +18779,16 @@
         <v>675</v>
       </c>
       <c r="Y80" t="s">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="Z80" t="s">
         <v>834</v>
       </c>
       <c r="AA80">
-        <v>0.9948848527457459</v>
+        <v>0.98571261124433651</v>
       </c>
       <c r="AB80">
-        <v>93.777699661325343</v>
+        <v>261.93546052049794</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18853,16 +18853,16 @@
         <v>677</v>
       </c>
       <c r="Y81" t="s">
-        <v>524</v>
+        <v>440</v>
       </c>
       <c r="Z81" t="s">
         <v>835</v>
       </c>
       <c r="AA81">
-        <v>0.9922030648239526</v>
+        <v>0.9849019911873127</v>
       </c>
       <c r="AB81">
-        <v>142.94381156086857</v>
+        <v>276.79682823259958</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18927,16 +18927,16 @@
         <v>679</v>
       </c>
       <c r="Y82" t="s">
-        <v>472</v>
+        <v>419</v>
       </c>
       <c r="Z82" t="s">
         <v>836</v>
       </c>
       <c r="AA82">
-        <v>0.99649411432543766</v>
+        <v>0.99157679714615166</v>
       </c>
       <c r="AB82">
-        <v>64.274570700309781</v>
+        <v>154.42538565388551</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -19001,16 +19001,16 @@
         <v>681</v>
       </c>
       <c r="Y83" t="s">
-        <v>480</v>
+        <v>515</v>
       </c>
       <c r="Z83" t="s">
         <v>837</v>
       </c>
       <c r="AA83">
-        <v>0.97907421743006762</v>
+        <v>0.99619387577842089</v>
       </c>
       <c r="AB83">
-        <v>383.63934711542669</v>
+        <v>69.778944062284495</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -19075,16 +19075,16 @@
         <v>683</v>
       </c>
       <c r="Y84" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="Z84" t="s">
         <v>838</v>
       </c>
       <c r="AA84">
-        <v>0.99558768376711515</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB84">
-        <v>80.892464269556413</v>
+        <v>92.048872319688599</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -19149,16 +19149,16 @@
         <v>685</v>
       </c>
       <c r="Y85" t="s">
-        <v>510</v>
+        <v>473</v>
       </c>
       <c r="Z85" t="s">
         <v>839</v>
       </c>
       <c r="AA85">
-        <v>0.99324569511004301</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB85">
-        <v>123.82892298254488</v>
+        <v>443.37880474956393</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19223,16 +19223,16 @@
         <v>687</v>
       </c>
       <c r="Y86" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="Z86" t="s">
         <v>840</v>
       </c>
       <c r="AA86">
-        <v>0.99419165427276146</v>
+        <v>0.99542292233022822</v>
       </c>
       <c r="AB86">
-        <v>106.48633833270691</v>
+        <v>83.913090612483515</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19297,16 +19297,16 @@
         <v>689</v>
       </c>
       <c r="Y87" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="Z87" t="s">
         <v>841</v>
       </c>
       <c r="AA87">
-        <v>0.99198935558098356</v>
+        <v>0.99647584863086869</v>
       </c>
       <c r="AB87">
-        <v>146.8618143486346</v>
+        <v>64.60944176740837</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19371,16 +19371,16 @@
         <v>691</v>
       </c>
       <c r="Y88" t="s">
-        <v>475</v>
+        <v>431</v>
       </c>
       <c r="Z88" t="s">
         <v>842</v>
       </c>
       <c r="AA88">
-        <v>0.99012236069527793</v>
+        <v>0.99780983219878738</v>
       </c>
       <c r="AB88">
-        <v>181.09005391990564</v>
+        <v>40.153076355563911</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19445,16 +19445,16 @@
         <v>693</v>
       </c>
       <c r="Y89" t="s">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="Z89" t="s">
         <v>843</v>
       </c>
       <c r="AA89">
-        <v>0.98990296758392993</v>
+        <v>0.99724696581141214</v>
       </c>
       <c r="AB89">
-        <v>185.11226096128556</v>
+        <v>50.472293457444586</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19519,16 +19519,16 @@
         <v>695</v>
       </c>
       <c r="Y90" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="Z90" t="s">
         <v>844</v>
       </c>
       <c r="AA90">
-        <v>0.99377714174527498</v>
+        <v>0.99589550629055523</v>
       </c>
       <c r="AB90">
-        <v>114.08573466995766</v>
+        <v>75.249051339820184</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19593,16 +19593,16 @@
         <v>697</v>
       </c>
       <c r="Y91" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="Z91" t="s">
         <v>845</v>
       </c>
       <c r="AA91">
-        <v>0.99516685156772267</v>
+        <v>0.99531156065644533</v>
       </c>
       <c r="AB91">
-        <v>88.60772125841865</v>
+        <v>85.954721298502818</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19667,16 +19667,16 @@
         <v>699</v>
       </c>
       <c r="Y92" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="Z92" t="s">
         <v>846</v>
       </c>
       <c r="AA92">
-        <v>0.99240925523869494</v>
+        <v>0.99706825374988217</v>
       </c>
       <c r="AB92">
-        <v>139.16365395725984</v>
+        <v>53.748681252160438</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19741,16 +19741,16 @@
         <v>701</v>
       </c>
       <c r="Y93" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="Z93" t="s">
-        <v>783</v>
+        <v>847</v>
       </c>
       <c r="AA93">
-        <v>0.97244982574001193</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB93">
-        <v>505.08652809978111</v>
+        <v>868.72862240505196</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19815,16 +19815,16 @@
         <v>703</v>
       </c>
       <c r="Y94" t="s">
-        <v>489</v>
+        <v>531</v>
       </c>
       <c r="Z94" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AA94">
-        <v>0.99172397756136033</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB94">
-        <v>151.72707804172813</v>
+        <v>475.8705861429753</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19889,16 +19889,16 @@
         <v>705</v>
       </c>
       <c r="Y95" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="Z95" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AA95">
-        <v>0.99431900976645593</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB95">
-        <v>104.15148761497397</v>
+        <v>226.88936094280919</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19963,16 +19963,16 @@
         <v>707</v>
       </c>
       <c r="Y96" t="s">
-        <v>430</v>
+        <v>505</v>
       </c>
       <c r="Z96" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AA96">
-        <v>0.9946350729064154</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB96">
-        <v>98.356996715718111</v>
+        <v>224.55764046872929</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -20037,16 +20037,16 @@
         <v>709</v>
       </c>
       <c r="Y97" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="Z97" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AA97">
-        <v>0.99343259267015904</v>
+        <v>0.99647006537565563</v>
       </c>
       <c r="AB97">
-        <v>120.40246771375152</v>
+        <v>64.715468112981057</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -20111,16 +20111,16 @@
         <v>711</v>
       </c>
       <c r="Y98" t="s">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="Z98" t="s">
-        <v>783</v>
+        <v>852</v>
       </c>
       <c r="AA98">
-        <v>0.93980266520001188</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB98">
-        <v>1103.617804666449</v>
+        <v>645.26520366712316</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20185,16 +20185,16 @@
         <v>713</v>
       </c>
       <c r="Y99" t="s">
-        <v>530</v>
+        <v>446</v>
       </c>
       <c r="Z99" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AA99">
-        <v>0.95679935803281835</v>
+        <v>0.99267004448650609</v>
       </c>
       <c r="AB99">
-        <v>792.01176939833033</v>
+        <v>134.38251774738842</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20259,16 +20259,16 @@
         <v>715</v>
       </c>
       <c r="Y100" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="Z100" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AA100">
-        <v>0.98761622532712257</v>
+        <v>0.9948848527457459</v>
       </c>
       <c r="AB100">
-        <v>227.03586900275366</v>
+        <v>93.777699661325343</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20333,16 +20333,16 @@
         <v>717</v>
       </c>
       <c r="Y101" t="s">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="Z101" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="AA101">
-        <v>0.99003402112096806</v>
+        <v>0.9922030648239526</v>
       </c>
       <c r="AB101">
-        <v>182.70961278225187</v>
+        <v>142.94381156086857</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20407,16 +20407,16 @@
         <v>719</v>
       </c>
       <c r="Y102" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="Z102" t="s">
-        <v>854</v>
+        <v>790</v>
       </c>
       <c r="AA102">
-        <v>0.99466062705491098</v>
+        <v>0.96238190390083644</v>
       </c>
       <c r="AB102">
-        <v>97.888503993298116</v>
+        <v>689.665095151331</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20481,16 +20481,16 @@
         <v>721</v>
       </c>
       <c r="Y103" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="Z103" t="s">
-        <v>855</v>
+        <v>777</v>
       </c>
       <c r="AA103">
-        <v>0.9944598150968682</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB103">
-        <v>101.5700565574154</v>
+        <v>675.25867642804383</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20555,16 +20555,16 @@
         <v>723</v>
       </c>
       <c r="Y104" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="Z104" t="s">
         <v>856</v>
       </c>
       <c r="AA104">
-        <v>0.99494501873633134</v>
+        <v>0.9951089264264793</v>
       </c>
       <c r="AB104">
-        <v>92.674656500591539</v>
+        <v>89.669682181211982</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20629,16 +20629,16 @@
         <v>725</v>
       </c>
       <c r="Y105" t="s">
-        <v>506</v>
+        <v>434</v>
       </c>
       <c r="Z105" t="s">
         <v>857</v>
       </c>
       <c r="AA105">
-        <v>0.99438812565699364</v>
+        <v>0.98666519734623237</v>
       </c>
       <c r="AB105">
-        <v>102.88436295511657</v>
+        <v>244.47138198573927</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20703,16 +20703,16 @@
         <v>727</v>
       </c>
       <c r="Y106" t="s">
-        <v>523</v>
+        <v>425</v>
       </c>
       <c r="Z106" t="s">
         <v>858</v>
       </c>
       <c r="AA106">
-        <v>0.99643191679577148</v>
+        <v>0.99750070245826261</v>
       </c>
       <c r="AB106">
-        <v>65.414858744189985</v>
+        <v>45.820454931853</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20777,16 +20777,16 @@
         <v>729</v>
       </c>
       <c r="Y107" t="s">
-        <v>473</v>
+        <v>422</v>
       </c>
       <c r="Z107" t="s">
         <v>859</v>
       </c>
       <c r="AA107">
-        <v>0.97581570155911468</v>
+        <v>0.99395341117186964</v>
       </c>
       <c r="AB107">
-        <v>443.37880474956393</v>
+        <v>110.85412851572337</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20851,16 +20851,16 @@
         <v>731</v>
       </c>
       <c r="Y108" t="s">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="Z108" t="s">
         <v>860</v>
       </c>
       <c r="AA108">
-        <v>0.99542292233022822</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB108">
-        <v>83.913090612483515</v>
+        <v>307.49900901993823</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20925,16 +20925,16 @@
         <v>733</v>
       </c>
       <c r="Y109" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="Z109" t="s">
         <v>861</v>
       </c>
       <c r="AA109">
-        <v>0.99647584863086869</v>
+        <v>0.9974199781412052</v>
       </c>
       <c r="AB109">
-        <v>64.60944176740837</v>
+        <v>47.300400744571718</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20999,16 +20999,16 @@
         <v>735</v>
       </c>
       <c r="Y110" t="s">
-        <v>431</v>
+        <v>496</v>
       </c>
       <c r="Z110" t="s">
         <v>862</v>
       </c>
       <c r="AA110">
-        <v>0.99780983219878738</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB110">
-        <v>40.153076355563911</v>
+        <v>121.57987025257442</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -21073,16 +21073,16 @@
         <v>737</v>
       </c>
       <c r="Y111" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
       <c r="Z111" t="s">
         <v>863</v>
       </c>
       <c r="AA111">
-        <v>0.99724696581141214</v>
+        <v>0.99379477670057537</v>
       </c>
       <c r="AB111">
-        <v>50.472293457444586</v>
+        <v>113.7624271561186</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -21147,16 +21147,16 @@
         <v>739</v>
       </c>
       <c r="Y112" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="Z112" t="s">
         <v>864</v>
       </c>
       <c r="AA112">
-        <v>0.99589550629055523</v>
+        <v>0.9961866142254362</v>
       </c>
       <c r="AB112">
-        <v>75.249051339820184</v>
+        <v>69.91207253366963</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21221,16 +21221,16 @@
         <v>741</v>
       </c>
       <c r="Y113" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="Z113" t="s">
         <v>865</v>
       </c>
       <c r="AA113">
-        <v>0.99531156065644533</v>
+        <v>0.99240925523869494</v>
       </c>
       <c r="AB113">
-        <v>85.954721298502818</v>
+        <v>139.16365395725984</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21295,16 +21295,16 @@
         <v>743</v>
       </c>
       <c r="Y114" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="Z114" t="s">
-        <v>866</v>
+        <v>777</v>
       </c>
       <c r="AA114">
-        <v>0.99706825374988217</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB114">
-        <v>53.748681252160438</v>
+        <v>505.08652809978111</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21369,16 +21369,16 @@
         <v>745</v>
       </c>
       <c r="Y115" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="Z115" t="s">
-        <v>769</v>
+        <v>866</v>
       </c>
       <c r="AA115">
-        <v>0.96238190390083644</v>
+        <v>0.99172397756136033</v>
       </c>
       <c r="AB115">
-        <v>689.665095151331</v>
+        <v>151.72707804172813</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21443,16 +21443,16 @@
         <v>747</v>
       </c>
       <c r="Y116" t="s">
-        <v>528</v>
+        <v>451</v>
       </c>
       <c r="Z116" t="s">
-        <v>783</v>
+        <v>867</v>
       </c>
       <c r="AA116">
-        <v>0.96316770855847034</v>
+        <v>0.99431900976645593</v>
       </c>
       <c r="AB116">
-        <v>675.25867642804383</v>
+        <v>104.15148761497397</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21517,16 +21517,16 @@
         <v>749</v>
       </c>
       <c r="Y117" t="s">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="Z117" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AA117">
-        <v>0.9951089264264793</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB117">
-        <v>89.669682181211982</v>
+        <v>98.356996715718111</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21591,16 +21591,16 @@
         <v>751</v>
       </c>
       <c r="Y118" t="s">
-        <v>434</v>
+        <v>517</v>
       </c>
       <c r="Z118" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AA118">
-        <v>0.98666519734623237</v>
+        <v>0.99343259267015904</v>
       </c>
       <c r="AB118">
-        <v>244.47138198573927</v>
+        <v>120.40246771375152</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21665,16 +21665,16 @@
         <v>753</v>
       </c>
       <c r="Y119" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="Z119" t="s">
-        <v>869</v>
+        <v>790</v>
       </c>
       <c r="AA119">
-        <v>0.99750070245826261</v>
+        <v>0.9621480095608167</v>
       </c>
       <c r="AB119">
-        <v>45.820454931853</v>
+        <v>693.95315805169378</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21739,16 +21739,16 @@
         <v>755</v>
       </c>
       <c r="Y120" t="s">
-        <v>422</v>
+        <v>479</v>
       </c>
       <c r="Z120" t="s">
         <v>870</v>
       </c>
       <c r="AA120">
-        <v>0.99395341117186964</v>
+        <v>0.98916941127667946</v>
       </c>
       <c r="AB120">
-        <v>110.85412851572337</v>
+        <v>198.56079326087576</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21813,16 +21813,16 @@
         <v>757</v>
       </c>
       <c r="Y121" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="Z121" t="s">
         <v>871</v>
       </c>
       <c r="AA121">
-        <v>0.98322732678073066</v>
+        <v>0.97159134368321343</v>
       </c>
       <c r="AB121">
-        <v>307.49900901993823</v>
+        <v>520.82536580775354</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21887,16 +21887,16 @@
         <v>759</v>
       </c>
       <c r="Y122" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="Z122" t="s">
         <v>872</v>
       </c>
       <c r="AA122">
-        <v>0.9974199781412052</v>
+        <v>0.99359614530212825</v>
       </c>
       <c r="AB122">
-        <v>47.300400744571718</v>
+        <v>117.40400279431638</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21961,16 +21961,16 @@
         <v>761</v>
       </c>
       <c r="Y123" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="Z123" t="s">
         <v>873</v>
       </c>
       <c r="AA123">
-        <v>0.99336837071349593</v>
+        <v>0.99488082982009873</v>
       </c>
       <c r="AB123">
-        <v>121.57987025257442</v>
+        <v>93.851453298190577</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -22035,16 +22035,16 @@
         <v>763</v>
       </c>
       <c r="Y124" t="s">
-        <v>443</v>
+        <v>513</v>
       </c>
       <c r="Z124" t="s">
         <v>874</v>
       </c>
       <c r="AA124">
-        <v>0.99379477670057537</v>
+        <v>0.99557743229498485</v>
       </c>
       <c r="AB124">
-        <v>113.7624271561186</v>
+        <v>81.080407925277868</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -22109,16 +22109,16 @@
         <v>765</v>
       </c>
       <c r="Y125" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z125" t="s">
         <v>875</v>
       </c>
       <c r="AA125">
-        <v>0.9961866142254362</v>
+        <v>0.99401156108202648</v>
       </c>
       <c r="AB125">
-        <v>69.91207253366963</v>
+        <v>109.78804682951412</v>
       </c>
     </row>
   </sheetData>
@@ -22127,7 +22127,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA4439F-62A7-411C-BF51-487DE4C902FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1091732-646A-43DB-8CA2-0454984A53E0}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22239,7 +22239,7 @@
         <v>1269</v>
       </c>
       <c r="K11" t="s">
-        <v>1024</v>
+        <v>1062</v>
       </c>
       <c r="L11">
         <v>4.7713910333636482</v>
@@ -22272,7 +22272,7 @@
         <v>1407</v>
       </c>
       <c r="X11" t="s">
-        <v>1256</v>
+        <v>1223</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -22307,7 +22307,7 @@
         <v>1271</v>
       </c>
       <c r="K12" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="L12">
         <v>12.404103898825962</v>
@@ -22340,7 +22340,7 @@
         <v>1409</v>
       </c>
       <c r="X12" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -22375,7 +22375,7 @@
         <v>1273</v>
       </c>
       <c r="K13" t="s">
-        <v>1062</v>
+        <v>1111</v>
       </c>
       <c r="L13">
         <v>6.1276234637439133</v>
@@ -22408,7 +22408,7 @@
         <v>1411</v>
       </c>
       <c r="X13" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -22443,7 +22443,7 @@
         <v>1275</v>
       </c>
       <c r="K14" t="s">
-        <v>1102</v>
+        <v>1126</v>
       </c>
       <c r="L14">
         <v>0.85621181691755843</v>
@@ -22476,7 +22476,7 @@
         <v>1413</v>
       </c>
       <c r="X14" t="s">
-        <v>1265</v>
+        <v>1249</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -22511,7 +22511,7 @@
         <v>1277</v>
       </c>
       <c r="K15" t="s">
-        <v>1096</v>
+        <v>1072</v>
       </c>
       <c r="L15">
         <v>2.2628760328229185</v>
@@ -22544,7 +22544,7 @@
         <v>1415</v>
       </c>
       <c r="X15" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -22579,7 +22579,7 @@
         <v>1279</v>
       </c>
       <c r="K16" t="s">
-        <v>1035</v>
+        <v>1086</v>
       </c>
       <c r="L16">
         <v>0.43370118574988076</v>
@@ -22612,7 +22612,7 @@
         <v>1417</v>
       </c>
       <c r="X16" t="s">
-        <v>1219</v>
+        <v>1265</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -22647,7 +22647,7 @@
         <v>1281</v>
       </c>
       <c r="K17" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="L17">
         <v>2.5150267058852811</v>
@@ -22680,7 +22680,7 @@
         <v>1419</v>
       </c>
       <c r="X17" t="s">
-        <v>1215</v>
+        <v>1258</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -22715,7 +22715,7 @@
         <v>1283</v>
       </c>
       <c r="K18" t="s">
-        <v>1095</v>
+        <v>1071</v>
       </c>
       <c r="L18">
         <v>2.885493974180005</v>
@@ -22748,7 +22748,7 @@
         <v>1421</v>
       </c>
       <c r="X18" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -22783,7 +22783,7 @@
         <v>1285</v>
       </c>
       <c r="K19" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="L19">
         <v>10.563746678268352</v>
@@ -22816,7 +22816,7 @@
         <v>1423</v>
       </c>
       <c r="X19" t="s">
-        <v>1213</v>
+        <v>1256</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22851,7 +22851,7 @@
         <v>1287</v>
       </c>
       <c r="K20" t="s">
-        <v>1026</v>
+        <v>1064</v>
       </c>
       <c r="L20">
         <v>7.4816578037471135</v>
@@ -22884,7 +22884,7 @@
         <v>1425</v>
       </c>
       <c r="X20" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22919,7 +22919,7 @@
         <v>1289</v>
       </c>
       <c r="K21" t="s">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="L21">
         <v>11.884376191048085</v>
@@ -22952,7 +22952,7 @@
         <v>1427</v>
       </c>
       <c r="X21" t="s">
-        <v>1231</v>
+        <v>1212</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22987,7 +22987,7 @@
         <v>1291</v>
       </c>
       <c r="K22" t="s">
-        <v>1118</v>
+        <v>1014</v>
       </c>
       <c r="L22">
         <v>12.246676572623375</v>
@@ -23020,7 +23020,7 @@
         <v>1429</v>
       </c>
       <c r="X22" t="s">
-        <v>1217</v>
+        <v>1263</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -23055,7 +23055,7 @@
         <v>1293</v>
       </c>
       <c r="K23" t="s">
-        <v>1033</v>
+        <v>1084</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -23088,7 +23088,7 @@
         <v>1431</v>
       </c>
       <c r="X23" t="s">
-        <v>1254</v>
+        <v>1233</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -23123,7 +23123,7 @@
         <v>1295</v>
       </c>
       <c r="K24" t="s">
-        <v>1063</v>
+        <v>1112</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -23156,7 +23156,7 @@
         <v>1433</v>
       </c>
       <c r="X24" t="s">
-        <v>1232</v>
+        <v>1213</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -23191,7 +23191,7 @@
         <v>1297</v>
       </c>
       <c r="K25" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="L25">
         <v>11.221871479411517</v>
@@ -23224,7 +23224,7 @@
         <v>1435</v>
       </c>
       <c r="X25" t="s">
-        <v>1258</v>
+        <v>1225</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -23259,7 +23259,7 @@
         <v>1299</v>
       </c>
       <c r="K26" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="L26">
         <v>1.6691823226567941</v>
@@ -23292,7 +23292,7 @@
         <v>1437</v>
       </c>
       <c r="X26" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23327,7 +23327,7 @@
         <v>1301</v>
       </c>
       <c r="K27" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="L27">
         <v>3.7614311754340659</v>
@@ -23360,7 +23360,7 @@
         <v>1439</v>
       </c>
       <c r="X27" t="s">
-        <v>1229</v>
+        <v>1210</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -23395,7 +23395,7 @@
         <v>1303</v>
       </c>
       <c r="K28" t="s">
-        <v>1051</v>
+        <v>1036</v>
       </c>
       <c r="L28">
         <v>0.34625959029864795</v>
@@ -23428,7 +23428,7 @@
         <v>1441</v>
       </c>
       <c r="X28" t="s">
-        <v>1238</v>
+        <v>1267</v>
       </c>
       <c r="Y28">
         <v>2.6655000000000002</v>
@@ -23463,7 +23463,7 @@
         <v>1305</v>
       </c>
       <c r="K29" t="s">
-        <v>1142</v>
+        <v>1044</v>
       </c>
       <c r="L29">
         <v>0.65440271382024695</v>
@@ -23496,7 +23496,7 @@
         <v>1443</v>
       </c>
       <c r="X29" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="Y29">
         <v>8.8432499999999994</v>
@@ -23531,7 +23531,7 @@
         <v>1307</v>
       </c>
       <c r="K30" t="s">
-        <v>1037</v>
+        <v>1088</v>
       </c>
       <c r="L30">
         <v>2.2677057834637031</v>
@@ -23564,7 +23564,7 @@
         <v>1445</v>
       </c>
       <c r="X30" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="Y30">
         <v>3.4402499999999998</v>
@@ -23599,7 +23599,7 @@
         <v>1309</v>
       </c>
       <c r="K31" t="s">
-        <v>1065</v>
+        <v>1114</v>
       </c>
       <c r="L31">
         <v>2.4836923620575391</v>
@@ -23632,7 +23632,7 @@
         <v>1447</v>
       </c>
       <c r="X31" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="Y31">
         <v>13.389749999999999</v>
@@ -23667,7 +23667,7 @@
         <v>1311</v>
       </c>
       <c r="K32" t="s">
-        <v>1077</v>
+        <v>1092</v>
       </c>
       <c r="L32">
         <v>4.0763322608214585</v>
@@ -23700,7 +23700,7 @@
         <v>1449</v>
       </c>
       <c r="X32" t="s">
-        <v>1212</v>
+        <v>1255</v>
       </c>
       <c r="Y32">
         <v>6.9757499999999997</v>
@@ -23735,7 +23735,7 @@
         <v>1313</v>
       </c>
       <c r="K33" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="L33">
         <v>2.5731779960501728</v>
@@ -23768,7 +23768,7 @@
         <v>1451</v>
       </c>
       <c r="X33" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="Y33">
         <v>38.154000000000003</v>
@@ -23803,7 +23803,7 @@
         <v>1315</v>
       </c>
       <c r="K34" t="s">
-        <v>1112</v>
+        <v>1050</v>
       </c>
       <c r="L34">
         <v>4.0509443596880574</v>
@@ -23836,7 +23836,7 @@
         <v>1453</v>
       </c>
       <c r="X34" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
       <c r="Y34">
         <v>26.765999999999998</v>
@@ -23871,7 +23871,7 @@
         <v>1317</v>
       </c>
       <c r="K35" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="L35">
         <v>2.4544193550494788</v>
@@ -23904,7 +23904,7 @@
         <v>1455</v>
       </c>
       <c r="X35" t="s">
-        <v>1210</v>
+        <v>1253</v>
       </c>
       <c r="Y35">
         <v>35.325000000000003</v>
@@ -23939,7 +23939,7 @@
         <v>1319</v>
       </c>
       <c r="K36" t="s">
-        <v>1043</v>
+        <v>1080</v>
       </c>
       <c r="L36">
         <v>0.35051099632091098</v>
@@ -23972,7 +23972,7 @@
         <v>1457</v>
       </c>
       <c r="X36" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="Y36">
         <v>38.589750000000002</v>
@@ -24007,7 +24007,7 @@
         <v>1321</v>
       </c>
       <c r="K37" t="s">
-        <v>1031</v>
+        <v>1069</v>
       </c>
       <c r="L37">
         <v>5.5005105319204732</v>
@@ -24040,7 +24040,7 @@
         <v>1459</v>
       </c>
       <c r="X37" t="s">
-        <v>1234</v>
+        <v>1215</v>
       </c>
       <c r="Y37">
         <v>28.707000000000001</v>
@@ -24075,7 +24075,7 @@
         <v>1323</v>
       </c>
       <c r="K38" t="s">
-        <v>1104</v>
+        <v>1128</v>
       </c>
       <c r="L38">
         <v>1.6757541426674882</v>
@@ -24108,7 +24108,7 @@
         <v>1461</v>
       </c>
       <c r="X38" t="s">
-        <v>1236</v>
+        <v>1217</v>
       </c>
       <c r="Y38">
         <v>13.428000000000001</v>
@@ -24143,7 +24143,7 @@
         <v>1325</v>
       </c>
       <c r="K39" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="L39">
         <v>0.39959553615654331</v>
@@ -24176,7 +24176,7 @@
         <v>1463</v>
       </c>
       <c r="X39" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24211,7 +24211,7 @@
         <v>1327</v>
       </c>
       <c r="K40" t="s">
-        <v>1120</v>
+        <v>1016</v>
       </c>
       <c r="L40">
         <v>1.7832075556426605</v>
@@ -24244,7 +24244,7 @@
         <v>1465</v>
       </c>
       <c r="X40" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24279,7 +24279,7 @@
         <v>1329</v>
       </c>
       <c r="K41" t="s">
-        <v>1045</v>
+        <v>1082</v>
       </c>
       <c r="L41">
         <v>23.427729543154012</v>
@@ -24312,7 +24312,7 @@
         <v>1467</v>
       </c>
       <c r="X41" t="s">
-        <v>1260</v>
+        <v>1227</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24347,7 +24347,7 @@
         <v>1331</v>
       </c>
       <c r="K42" t="s">
-        <v>1075</v>
+        <v>1124</v>
       </c>
       <c r="L42">
         <v>1.4999429400795936</v>
@@ -24382,7 +24382,7 @@
         <v>1333</v>
       </c>
       <c r="K43" t="s">
-        <v>1116</v>
+        <v>1054</v>
       </c>
       <c r="L43">
         <v>55.863958629218203</v>
@@ -24417,7 +24417,7 @@
         <v>1335</v>
       </c>
       <c r="K44" t="s">
-        <v>1071</v>
+        <v>1120</v>
       </c>
       <c r="L44">
         <v>17.068804920122925</v>
@@ -24452,7 +24452,7 @@
         <v>1337</v>
       </c>
       <c r="K45" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="L45">
         <v>13.001084297219549</v>
@@ -24487,7 +24487,7 @@
         <v>1339</v>
       </c>
       <c r="K46" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="L46">
         <v>3.0756142181007986</v>
@@ -24522,7 +24522,7 @@
         <v>1341</v>
       </c>
       <c r="K47" t="s">
-        <v>1128</v>
+        <v>1042</v>
       </c>
       <c r="L47">
         <v>17.749707845203876</v>
@@ -24557,7 +24557,7 @@
         <v>1343</v>
       </c>
       <c r="K48" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="L48">
         <v>2.3372365278937242</v>
@@ -24592,7 +24592,7 @@
         <v>1345</v>
       </c>
       <c r="K49" t="s">
-        <v>1081</v>
+        <v>1096</v>
       </c>
       <c r="L49">
         <v>4.2648673086521249</v>
@@ -24627,7 +24627,7 @@
         <v>1347</v>
       </c>
       <c r="K50" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="L50">
         <v>2.8571480649629004</v>
@@ -24662,7 +24662,7 @@
         <v>1349</v>
       </c>
       <c r="K51" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="L51">
         <v>9.5169217846211289</v>
@@ -24697,7 +24697,7 @@
         <v>1351</v>
       </c>
       <c r="K52" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="L52">
         <v>33.414563514376454</v>
@@ -24732,7 +24732,7 @@
         <v>1353</v>
       </c>
       <c r="K53" t="s">
-        <v>1110</v>
+        <v>1134</v>
       </c>
       <c r="L53">
         <v>18.904558868579112</v>
@@ -24767,7 +24767,7 @@
         <v>1355</v>
       </c>
       <c r="K54" t="s">
-        <v>1073</v>
+        <v>1122</v>
       </c>
       <c r="L54">
         <v>15.478330347836801</v>
@@ -24802,7 +24802,7 @@
         <v>1357</v>
       </c>
       <c r="K55" t="s">
-        <v>1061</v>
+        <v>1110</v>
       </c>
       <c r="L55">
         <v>14.176079891703212</v>
@@ -24837,7 +24837,7 @@
         <v>1359</v>
       </c>
       <c r="K56" t="s">
-        <v>1146</v>
+        <v>1048</v>
       </c>
       <c r="L56">
         <v>0.80973624203950822</v>
@@ -24872,7 +24872,7 @@
         <v>1361</v>
       </c>
       <c r="K57" t="s">
-        <v>1124</v>
+        <v>1020</v>
       </c>
       <c r="L57">
         <v>3.2067222321080848</v>
@@ -24907,7 +24907,7 @@
         <v>1363</v>
       </c>
       <c r="K58" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="L58">
         <v>0.66271354737797783</v>
@@ -24942,7 +24942,7 @@
         <v>1365</v>
       </c>
       <c r="K59" t="s">
-        <v>1108</v>
+        <v>1132</v>
       </c>
       <c r="L59">
         <v>1.8183767824138508</v>
@@ -24977,7 +24977,7 @@
         <v>1367</v>
       </c>
       <c r="K60" t="s">
-        <v>1098</v>
+        <v>1074</v>
       </c>
       <c r="L60">
         <v>0.24904319237866104</v>
@@ -25012,7 +25012,7 @@
         <v>1369</v>
       </c>
       <c r="K61" t="s">
-        <v>1083</v>
+        <v>1098</v>
       </c>
       <c r="L61">
         <v>8.2047875916663029E-2</v>
@@ -25047,7 +25047,7 @@
         <v>1371</v>
       </c>
       <c r="K62" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="L62">
         <v>11.861012832193515</v>
@@ -25082,7 +25082,7 @@
         <v>1373</v>
       </c>
       <c r="K63" t="s">
-        <v>1106</v>
+        <v>1130</v>
       </c>
       <c r="L63">
         <v>0.74143826937354373</v>
@@ -25117,7 +25117,7 @@
         <v>1375</v>
       </c>
       <c r="K64" t="s">
-        <v>1067</v>
+        <v>1116</v>
       </c>
       <c r="L64">
         <v>5.5201095579611916</v>
@@ -25152,7 +25152,7 @@
         <v>1377</v>
       </c>
       <c r="K65" t="s">
-        <v>1039</v>
+        <v>1090</v>
       </c>
       <c r="L65">
         <v>6.8285247240880329</v>
@@ -25187,7 +25187,7 @@
         <v>1379</v>
       </c>
       <c r="K66" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L66">
         <v>14.065249575687433</v>
@@ -25222,7 +25222,7 @@
         <v>1381</v>
       </c>
       <c r="K67" t="s">
-        <v>1100</v>
+        <v>1076</v>
       </c>
       <c r="L67">
         <v>9.3799037679336319</v>
@@ -25257,7 +25257,7 @@
         <v>1383</v>
       </c>
       <c r="K68" t="s">
-        <v>1144</v>
+        <v>1046</v>
       </c>
       <c r="L68">
         <v>42.785830383290261</v>
@@ -25292,7 +25292,7 @@
         <v>1385</v>
       </c>
       <c r="K69" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="L69">
         <v>7.8693705940085819</v>
@@ -25327,7 +25327,7 @@
         <v>1387</v>
       </c>
       <c r="K70" t="s">
-        <v>1041</v>
+        <v>1078</v>
       </c>
       <c r="L70">
         <v>19.787589902082505</v>
@@ -25362,7 +25362,7 @@
         <v>1389</v>
       </c>
       <c r="K71" t="s">
-        <v>1126</v>
+        <v>1040</v>
       </c>
       <c r="L71">
         <v>18.319832830101969</v>
@@ -25397,7 +25397,7 @@
         <v>1391</v>
       </c>
       <c r="K72" t="s">
-        <v>1069</v>
+        <v>1118</v>
       </c>
       <c r="L72">
         <v>6.7551756478058005</v>
@@ -25432,7 +25432,7 @@
         <v>1393</v>
       </c>
       <c r="K73" t="s">
-        <v>1079</v>
+        <v>1094</v>
       </c>
       <c r="L73">
         <v>3.5275797249830152</v>
@@ -25467,7 +25467,7 @@
         <v>1395</v>
       </c>
       <c r="K74" t="s">
-        <v>1114</v>
+        <v>1052</v>
       </c>
       <c r="L74">
         <v>0.89663971235601181</v>
@@ -25502,7 +25502,7 @@
         <v>1397</v>
       </c>
       <c r="K75" t="s">
-        <v>1122</v>
+        <v>1018</v>
       </c>
       <c r="L75">
         <v>5.9305458091691294</v>
@@ -25537,7 +25537,7 @@
         <v>1399</v>
       </c>
       <c r="K76" t="s">
-        <v>1029</v>
+        <v>1067</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25572,7 +25572,7 @@
         <v>1401</v>
       </c>
       <c r="K77" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="L77">
         <v>0.5190595734350465</v>
@@ -25607,7 +25607,7 @@
         <v>1403</v>
       </c>
       <c r="K78" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="L78">
         <v>0.29505146981926272</v>
@@ -25642,7 +25642,7 @@
         <v>1405</v>
       </c>
       <c r="K79" t="s">
-        <v>1027</v>
+        <v>1065</v>
       </c>
       <c r="L79">
         <v>0.28737649325389003</v>
@@ -25657,7 +25657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DBC703-DF67-4AA7-B1E6-FC7BF358F2E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54750754-E0F4-474D-82A6-BF271D6393B6}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27126,7 +27126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD63786-BB09-473F-8C12-FE13453BC895}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480870E1-D7C1-4A4E-8176-A3B520762C7F}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA2EC1FF-F758-4E1B-A486-8B197594AEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6440EE8D-B4B7-4804-9164-E93802DE4D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1736,18 +1736,552 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_057</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 57</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_022</t>
   </si>
   <si>
@@ -1790,214 +2324,46 @@
     <t>connecting solar to buses in cluster 97</t>
   </si>
   <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
     <t>distr_solelc_spv_112</t>
@@ -2066,378 +2432,261 @@
     <t>connecting solar to buses in cluster 99</t>
   </si>
   <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500</t>
+  </si>
+  <si>
+    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
+  </si>
+  <si>
     <t>e_BR319-230,e_BR318-230</t>
   </si>
   <si>
@@ -2462,103 +2711,22 @@
     <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
   </si>
   <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
   </si>
   <si>
     <t>e_BR274-500,e_w304646981-500</t>
@@ -2591,172 +2759,34 @@
     <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
   </si>
   <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500</t>
-  </si>
-  <si>
-    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
   </si>
   <si>
     <t>distr_wonelc_won_012</t>
@@ -2783,6 +2813,198 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_025</t>
   </si>
   <si>
@@ -2813,76 +3035,100 @@
     <t>connecting wind onshore to buses in cluster 36</t>
   </si>
   <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -2903,36 +3149,6 @@
     <t>connecting wind onshore to buses in cluster 56</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_008</t>
   </si>
   <si>
@@ -2957,220 +3173,31 @@
     <t>connecting wind onshore to buses in cluster 57</t>
   </si>
   <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
   </si>
   <si>
     <t>elc_won_012</t>
@@ -3197,6 +3224,198 @@
     <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
   </si>
   <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
+  </si>
+  <si>
     <t>elc_won_025</t>
   </si>
   <si>
@@ -3227,76 +3446,94 @@
     <t>e_BR412-500,e_BR400-500</t>
   </si>
   <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
   </si>
   <si>
     <t>elc_won_009</t>
@@ -3317,33 +3554,6 @@
     <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_069</t>
-  </si>
-  <si>
-    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
     <t>elc_won_008</t>
   </si>
   <si>
@@ -3365,214 +3575,28 @@
     <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
   </si>
   <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_017</t>
@@ -3617,6 +3641,42 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
@@ -3635,34 +3695,46 @@
     <t>connecting wind offshore to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wofelc_wof_003</t>
@@ -3683,84 +3755,36 @@
     <t>connecting wind offshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_018</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
     <t>elc_wof_017</t>
   </si>
   <si>
@@ -3800,6 +3824,39 @@
     <t>e_BR992-525,e_BR886-500</t>
   </si>
   <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
@@ -3818,34 +3875,43 @@
     <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
-  </si>
-  <si>
     <t>elc_wof_013</t>
   </si>
   <si>
     <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
   </si>
   <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w466973262-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
   </si>
   <si>
     <t>elc_wof_003</t>
@@ -3864,72 +3930,6 @@
   </si>
   <si>
     <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
   </si>
   <si>
     <t>elc_wof_018</t>
@@ -9835,7 +9835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47FF7617-A597-4CE1-8882-F68BF9B39F72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D9EE51-467A-4E69-9233-24C1C5B04268}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10073,16 +10073,16 @@
         <v>535</v>
       </c>
       <c r="Y11" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Z11" t="s">
         <v>769</v>
       </c>
       <c r="AA11">
-        <v>0.99506672623055659</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB11">
-        <v>90.443352439796072</v>
+        <v>129.18226807514921</v>
       </c>
       <c r="AD11" t="s">
         <v>534</v>
@@ -10115,10 +10115,10 @@
         <v>1015</v>
       </c>
       <c r="AO11">
-        <v>0.99473480482648013</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP11">
-        <v>96.528578181196991</v>
+        <v>138.50582323297994</v>
       </c>
       <c r="AR11" t="s">
         <v>534</v>
@@ -10151,10 +10151,10 @@
         <v>1211</v>
       </c>
       <c r="BC11">
-        <v>0.96863461872110523</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD11">
-        <v>575.0319901130714</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10219,16 +10219,16 @@
         <v>539</v>
       </c>
       <c r="Y12" t="s">
-        <v>439</v>
+        <v>486</v>
       </c>
       <c r="Z12" t="s">
         <v>770</v>
       </c>
       <c r="AA12">
-        <v>0.97537853020161625</v>
+        <v>0.98571261124433651</v>
       </c>
       <c r="AB12">
-        <v>451.39361297036953</v>
+        <v>261.93546052049794</v>
       </c>
       <c r="AD12" t="s">
         <v>534</v>
@@ -10258,13 +10258,13 @@
         <v>1016</v>
       </c>
       <c r="AN12" t="s">
-        <v>1017</v>
+        <v>853</v>
       </c>
       <c r="AO12">
-        <v>0.99729761494442914</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP12">
-        <v>49.543726018799653</v>
+        <v>473.60023862765331</v>
       </c>
       <c r="AR12" t="s">
         <v>534</v>
@@ -10294,13 +10294,13 @@
         <v>1212</v>
       </c>
       <c r="BB12" t="s">
-        <v>1075</v>
+        <v>1213</v>
       </c>
       <c r="BC12">
-        <v>0.99098965084511315</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD12">
-        <v>165.18973450625904</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10365,16 +10365,16 @@
         <v>541</v>
       </c>
       <c r="Y13" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="Z13" t="s">
         <v>771</v>
       </c>
       <c r="AA13">
-        <v>0.99417333900805149</v>
+        <v>0.9849019911873127</v>
       </c>
       <c r="AB13">
-        <v>106.82211818572355</v>
+        <v>276.79682823259958</v>
       </c>
       <c r="AD13" t="s">
         <v>534</v>
@@ -10401,16 +10401,16 @@
         <v>880</v>
       </c>
       <c r="AM13" t="s">
+        <v>1017</v>
+      </c>
+      <c r="AN13" t="s">
         <v>1018</v>
       </c>
-      <c r="AN13" t="s">
-        <v>1019</v>
-      </c>
       <c r="AO13">
-        <v>0.996795372708284</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP13">
-        <v>58.751500348127372</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR13" t="s">
         <v>534</v>
@@ -10437,16 +10437,16 @@
         <v>1152</v>
       </c>
       <c r="BA13" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="BB13" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="BC13">
-        <v>0.99053278045305837</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD13">
-        <v>173.56569169392964</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10511,16 +10511,16 @@
         <v>543</v>
       </c>
       <c r="Y14" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="Z14" t="s">
         <v>772</v>
       </c>
       <c r="AA14">
-        <v>0.99660448707980165</v>
+        <v>0.99157679714615166</v>
       </c>
       <c r="AB14">
-        <v>62.251070203636829</v>
+        <v>154.42538565388551</v>
       </c>
       <c r="AD14" t="s">
         <v>534</v>
@@ -10547,16 +10547,16 @@
         <v>882</v>
       </c>
       <c r="AM14" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AN14" t="s">
         <v>1020</v>
       </c>
-      <c r="AN14" t="s">
-        <v>1021</v>
-      </c>
       <c r="AO14">
-        <v>0.99274560110857168</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP14">
-        <v>132.99731300951822</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR14" t="s">
         <v>534</v>
@@ -10583,16 +10583,16 @@
         <v>1154</v>
       </c>
       <c r="BA14" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="BB14" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="BC14">
-        <v>0.98488330873784669</v>
+        <v>0.99563011519444145</v>
       </c>
       <c r="BD14">
-        <v>277.13933980614473</v>
+        <v>80.114554768572972</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10657,16 +10657,16 @@
         <v>545</v>
       </c>
       <c r="Y15" t="s">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="Z15" t="s">
         <v>773</v>
       </c>
       <c r="AA15">
-        <v>0.99704166323096854</v>
+        <v>0.99619387577842089</v>
       </c>
       <c r="AB15">
-        <v>54.23617409891024</v>
+        <v>69.778944062284495</v>
       </c>
       <c r="AD15" t="s">
         <v>534</v>
@@ -10693,16 +10693,16 @@
         <v>884</v>
       </c>
       <c r="AM15" t="s">
+        <v>1021</v>
+      </c>
+      <c r="AN15" t="s">
         <v>1022</v>
       </c>
-      <c r="AN15" t="s">
-        <v>1023</v>
-      </c>
       <c r="AO15">
-        <v>0.99677419959133018</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP15">
-        <v>59.139674158947656</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR15" t="s">
         <v>534</v>
@@ -10729,16 +10729,16 @@
         <v>1156</v>
       </c>
       <c r="BA15" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="BB15" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="BC15">
-        <v>0.99526086651282741</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD15">
-        <v>86.884113931497708</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10803,16 +10803,16 @@
         <v>547</v>
       </c>
       <c r="Y16" t="s">
-        <v>512</v>
+        <v>457</v>
       </c>
       <c r="Z16" t="s">
         <v>774</v>
       </c>
       <c r="AA16">
-        <v>0.99156821305535681</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB16">
-        <v>154.58276065179118</v>
+        <v>92.048872319688599</v>
       </c>
       <c r="AD16" t="s">
         <v>534</v>
@@ -10839,16 +10839,16 @@
         <v>886</v>
       </c>
       <c r="AM16" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AN16" t="s">
         <v>1024</v>
       </c>
-      <c r="AN16" t="s">
-        <v>1025</v>
-      </c>
       <c r="AO16">
-        <v>0.99766813121902409</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP16">
-        <v>42.750927651225993</v>
+        <v>96.528578181196991</v>
       </c>
       <c r="AR16" t="s">
         <v>534</v>
@@ -10875,16 +10875,16 @@
         <v>1158</v>
       </c>
       <c r="BA16" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="BB16" t="s">
-        <v>1220</v>
+        <v>1145</v>
       </c>
       <c r="BC16">
-        <v>0.95713629889852414</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD16">
-        <v>785.83452019372396</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10949,16 +10949,16 @@
         <v>549</v>
       </c>
       <c r="Y17" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="Z17" t="s">
         <v>775</v>
       </c>
       <c r="AA17">
-        <v>0.99731037386855248</v>
+        <v>0.98150124893892388</v>
       </c>
       <c r="AB17">
-        <v>49.309812409870183</v>
+        <v>339.14376945306287</v>
       </c>
       <c r="AD17" t="s">
         <v>534</v>
@@ -10985,16 +10985,16 @@
         <v>888</v>
       </c>
       <c r="AM17" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AN17" t="s">
         <v>1026</v>
       </c>
-      <c r="AN17" t="s">
-        <v>1027</v>
-      </c>
       <c r="AO17">
-        <v>0.99760247912344124</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP17">
-        <v>43.95454940357709</v>
+        <v>49.543726018799653</v>
       </c>
       <c r="AR17" t="s">
         <v>534</v>
@@ -11027,10 +11027,10 @@
         <v>1222</v>
       </c>
       <c r="BC17">
-        <v>0.98806872821788805</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD17">
-        <v>218.73998267205184</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11095,16 +11095,16 @@
         <v>551</v>
       </c>
       <c r="Y18" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="Z18" t="s">
         <v>776</v>
       </c>
       <c r="AA18">
-        <v>0.99338478208530079</v>
+        <v>0.99523081353776888</v>
       </c>
       <c r="AB18">
-        <v>121.27899510281891</v>
+        <v>87.435085140903482</v>
       </c>
       <c r="AD18" t="s">
         <v>534</v>
@@ -11131,16 +11131,16 @@
         <v>890</v>
       </c>
       <c r="AM18" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AN18" t="s">
         <v>1028</v>
       </c>
-      <c r="AN18" t="s">
-        <v>1029</v>
-      </c>
       <c r="AO18">
-        <v>0.99336049451151065</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP18">
-        <v>121.72426728897108</v>
+        <v>58.751500348127372</v>
       </c>
       <c r="AR18" t="s">
         <v>534</v>
@@ -11173,10 +11173,10 @@
         <v>1224</v>
       </c>
       <c r="BC18">
-        <v>0.98890025255868685</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD18">
-        <v>203.49536975740753</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11241,16 +11241,16 @@
         <v>553</v>
       </c>
       <c r="Y19" t="s">
-        <v>526</v>
+        <v>442</v>
       </c>
       <c r="Z19" t="s">
         <v>777</v>
       </c>
       <c r="AA19">
-        <v>0.93980266520001188</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB19">
-        <v>1103.617804666449</v>
+        <v>153.20678909592235</v>
       </c>
       <c r="AD19" t="s">
         <v>534</v>
@@ -11277,16 +11277,16 @@
         <v>892</v>
       </c>
       <c r="AM19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AN19" t="s">
         <v>1030</v>
       </c>
-      <c r="AN19" t="s">
-        <v>1031</v>
-      </c>
       <c r="AO19">
-        <v>0.99759498179797546</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP19">
-        <v>44.092000370450322</v>
+        <v>132.99731300951822</v>
       </c>
       <c r="AR19" t="s">
         <v>534</v>
@@ -11319,10 +11319,10 @@
         <v>1226</v>
       </c>
       <c r="BC19">
-        <v>0.99481196273061234</v>
+        <v>0.99526086651282741</v>
       </c>
       <c r="BD19">
-        <v>95.114016605440895</v>
+        <v>86.884113931497708</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11387,16 +11387,16 @@
         <v>555</v>
       </c>
       <c r="Y20" t="s">
-        <v>530</v>
+        <v>423</v>
       </c>
       <c r="Z20" t="s">
         <v>778</v>
       </c>
       <c r="AA20">
-        <v>0.95679935803281835</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB20">
-        <v>792.01176939833033</v>
+        <v>78.81162391526847</v>
       </c>
       <c r="AD20" t="s">
         <v>534</v>
@@ -11423,16 +11423,16 @@
         <v>894</v>
       </c>
       <c r="AM20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AN20" t="s">
         <v>1032</v>
       </c>
-      <c r="AN20" t="s">
-        <v>1033</v>
-      </c>
       <c r="AO20">
-        <v>0.98134982200735632</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP20">
-        <v>341.91992986513412</v>
+        <v>109.31605592223302</v>
       </c>
       <c r="AR20" t="s">
         <v>534</v>
@@ -11465,10 +11465,10 @@
         <v>1228</v>
       </c>
       <c r="BC20">
-        <v>0.99374755699184159</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD20">
-        <v>114.62812181623703</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11533,16 +11533,16 @@
         <v>557</v>
       </c>
       <c r="Y21" t="s">
-        <v>501</v>
+        <v>436</v>
       </c>
       <c r="Z21" t="s">
         <v>779</v>
       </c>
       <c r="AA21">
-        <v>0.98761622532712257</v>
+        <v>0.99691903985105013</v>
       </c>
       <c r="AB21">
-        <v>227.03586900275366</v>
+        <v>56.484269397415083</v>
       </c>
       <c r="AD21" t="s">
         <v>534</v>
@@ -11569,16 +11569,16 @@
         <v>896</v>
       </c>
       <c r="AM21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="AN21" t="s">
         <v>1034</v>
       </c>
-      <c r="AN21" t="s">
-        <v>1035</v>
-      </c>
       <c r="AO21">
-        <v>0.98589595763902149</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP21">
-        <v>258.57410995127316</v>
+        <v>163.93514059684662</v>
       </c>
       <c r="AR21" t="s">
         <v>534</v>
@@ -11611,10 +11611,10 @@
         <v>1230</v>
       </c>
       <c r="BC21">
-        <v>0.99834679070917032</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD21">
-        <v>30.308836998544216</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11679,16 +11679,16 @@
         <v>559</v>
       </c>
       <c r="Y22" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="Z22" t="s">
         <v>780</v>
       </c>
       <c r="AA22">
-        <v>0.99003402112096806</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB22">
-        <v>182.70961278225187</v>
+        <v>263.42178867339101</v>
       </c>
       <c r="AD22" t="s">
         <v>534</v>
@@ -11715,16 +11715,16 @@
         <v>898</v>
       </c>
       <c r="AM22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AN22" t="s">
         <v>1036</v>
       </c>
-      <c r="AN22" t="s">
-        <v>1037</v>
-      </c>
       <c r="AO22">
-        <v>0.99776894175014486</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP22">
-        <v>40.90273458067751</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR22" t="s">
         <v>534</v>
@@ -11757,10 +11757,10 @@
         <v>1232</v>
       </c>
       <c r="BC22">
-        <v>0.99401640271965719</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD22">
-        <v>109.69928347295183</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11825,16 +11825,16 @@
         <v>561</v>
       </c>
       <c r="Y23" t="s">
-        <v>459</v>
+        <v>509</v>
       </c>
       <c r="Z23" t="s">
         <v>781</v>
       </c>
       <c r="AA23">
-        <v>0.99466062705491098</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB23">
-        <v>97.888503993298116</v>
+        <v>86.308558527470979</v>
       </c>
       <c r="AD23" t="s">
         <v>534</v>
@@ -11861,16 +11861,16 @@
         <v>900</v>
       </c>
       <c r="AM23" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AN23" t="s">
         <v>1038</v>
       </c>
-      <c r="AN23" t="s">
-        <v>1039</v>
-      </c>
       <c r="AO23">
-        <v>0.9959346869215373</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP23">
-        <v>74.530739771815789</v>
+        <v>85.270745539791065</v>
       </c>
       <c r="AR23" t="s">
         <v>534</v>
@@ -11903,10 +11903,10 @@
         <v>1234</v>
       </c>
       <c r="BC23">
-        <v>0.98691003029105739</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD23">
-        <v>239.98277799728109</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11971,16 +11971,16 @@
         <v>563</v>
       </c>
       <c r="Y24" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="Z24" t="s">
         <v>782</v>
       </c>
       <c r="AA24">
-        <v>0.9944598150968682</v>
+        <v>0.99443562760718263</v>
       </c>
       <c r="AB24">
-        <v>101.5700565574154</v>
+        <v>102.01349386831856</v>
       </c>
       <c r="AD24" t="s">
         <v>534</v>
@@ -12007,16 +12007,16 @@
         <v>902</v>
       </c>
       <c r="AM24" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AN24" t="s">
         <v>1040</v>
       </c>
-      <c r="AN24" t="s">
-        <v>1041</v>
-      </c>
       <c r="AO24">
-        <v>0.9955955730654259</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP24">
-        <v>80.747827133859133</v>
+        <v>79.268397406829976</v>
       </c>
       <c r="AR24" t="s">
         <v>534</v>
@@ -12049,10 +12049,10 @@
         <v>1236</v>
       </c>
       <c r="BC24">
-        <v>0.9959052853503485</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD24">
-        <v>75.06976857694373</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12117,16 +12117,16 @@
         <v>565</v>
       </c>
       <c r="Y25" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="Z25" t="s">
         <v>783</v>
       </c>
       <c r="AA25">
-        <v>0.99494501873633134</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB25">
-        <v>92.674656500591539</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD25" t="s">
         <v>534</v>
@@ -12153,16 +12153,16 @@
         <v>904</v>
       </c>
       <c r="AM25" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AN25" t="s">
         <v>1042</v>
       </c>
-      <c r="AN25" t="s">
-        <v>1043</v>
-      </c>
       <c r="AO25">
-        <v>0.99671693937496686</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP25">
-        <v>60.189444792275019</v>
+        <v>43.581147571379539</v>
       </c>
       <c r="AR25" t="s">
         <v>534</v>
@@ -12192,13 +12192,13 @@
         <v>1237</v>
       </c>
       <c r="BB25" t="s">
-        <v>1238</v>
+        <v>1078</v>
       </c>
       <c r="BC25">
-        <v>0.99563011519444145</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD25">
-        <v>80.114554768572972</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12263,16 +12263,16 @@
         <v>567</v>
       </c>
       <c r="Y26" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="Z26" t="s">
         <v>784</v>
       </c>
       <c r="AA26">
-        <v>0.99438812565699364</v>
+        <v>0.99726809134187266</v>
       </c>
       <c r="AB26">
-        <v>102.88436295511657</v>
+        <v>50.0849920656675</v>
       </c>
       <c r="AD26" t="s">
         <v>534</v>
@@ -12299,16 +12299,16 @@
         <v>906</v>
       </c>
       <c r="AM26" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AN26" t="s">
         <v>1044</v>
       </c>
-      <c r="AN26" t="s">
-        <v>1045</v>
-      </c>
       <c r="AO26">
-        <v>0.99503039970536677</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP26">
-        <v>91.109338734942796</v>
+        <v>151.17817104385733</v>
       </c>
       <c r="AR26" t="s">
         <v>534</v>
@@ -12335,16 +12335,16 @@
         <v>1178</v>
       </c>
       <c r="BA26" t="s">
+        <v>1238</v>
+      </c>
+      <c r="BB26" t="s">
         <v>1239</v>
       </c>
-      <c r="BB26" t="s">
-        <v>1240</v>
-      </c>
       <c r="BC26">
-        <v>0.99054926914187857</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD26">
-        <v>173.26339906555947</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12409,16 +12409,16 @@
         <v>569</v>
       </c>
       <c r="Y27" t="s">
-        <v>523</v>
+        <v>481</v>
       </c>
       <c r="Z27" t="s">
         <v>785</v>
       </c>
       <c r="AA27">
-        <v>0.99643191679577148</v>
+        <v>0.97962408753770291</v>
       </c>
       <c r="AB27">
-        <v>65.414858744189985</v>
+        <v>373.55839514211272</v>
       </c>
       <c r="AD27" t="s">
         <v>534</v>
@@ -12445,16 +12445,16 @@
         <v>908</v>
       </c>
       <c r="AM27" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AN27" t="s">
         <v>1046</v>
       </c>
-      <c r="AN27" t="s">
-        <v>1047</v>
-      </c>
       <c r="AO27">
-        <v>0.99544059907537386</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP27">
-        <v>83.589016951479763</v>
+        <v>57.146786340912868</v>
       </c>
       <c r="AR27" t="s">
         <v>534</v>
@@ -12481,16 +12481,16 @@
         <v>1180</v>
       </c>
       <c r="BA27" t="s">
+        <v>1240</v>
+      </c>
+      <c r="BB27" t="s">
         <v>1241</v>
       </c>
-      <c r="BB27" t="s">
-        <v>1242</v>
-      </c>
       <c r="BC27">
-        <v>0.98027195861782945</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD27">
-        <v>361.68075867312689</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12555,16 +12555,16 @@
         <v>571</v>
       </c>
       <c r="Y28" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="Z28" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA28">
-        <v>0.99012236069527793</v>
+        <v>0.99098167665935155</v>
       </c>
       <c r="AB28">
-        <v>181.09005391990564</v>
+        <v>165.33592791188894</v>
       </c>
       <c r="AD28" t="s">
         <v>534</v>
@@ -12591,16 +12591,16 @@
         <v>910</v>
       </c>
       <c r="AM28" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AN28" t="s">
         <v>1048</v>
       </c>
-      <c r="AN28" t="s">
-        <v>1049</v>
-      </c>
       <c r="AO28">
-        <v>0.98829989485605374</v>
+        <v>0.99488275259079373</v>
       </c>
       <c r="AP28">
-        <v>214.50192763901472</v>
+        <v>93.81620250211445</v>
       </c>
       <c r="AR28" t="s">
         <v>534</v>
@@ -12627,16 +12627,16 @@
         <v>1182</v>
       </c>
       <c r="BA28" t="s">
+        <v>1242</v>
+      </c>
+      <c r="BB28" t="s">
         <v>1243</v>
       </c>
-      <c r="BB28" t="s">
-        <v>1244</v>
-      </c>
       <c r="BC28">
-        <v>0.98125520899414764</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD28">
-        <v>343.65450177395917</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12701,16 +12701,16 @@
         <v>573</v>
       </c>
       <c r="Y29" t="s">
-        <v>435</v>
+        <v>503</v>
       </c>
       <c r="Z29" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AA29">
-        <v>0.98990296758392993</v>
+        <v>0.98485684158558628</v>
       </c>
       <c r="AB29">
-        <v>185.11226096128556</v>
+        <v>277.62457093091871</v>
       </c>
       <c r="AD29" t="s">
         <v>534</v>
@@ -12737,16 +12737,16 @@
         <v>912</v>
       </c>
       <c r="AM29" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AN29" t="s">
         <v>1050</v>
       </c>
-      <c r="AN29" t="s">
-        <v>1051</v>
-      </c>
       <c r="AO29">
-        <v>0.99684152237002188</v>
+        <v>0.99663220850609069</v>
       </c>
       <c r="AP29">
-        <v>57.905423216266421</v>
+        <v>61.742844055003644</v>
       </c>
       <c r="AR29" t="s">
         <v>534</v>
@@ -12773,16 +12773,16 @@
         <v>1184</v>
       </c>
       <c r="BA29" t="s">
+        <v>1244</v>
+      </c>
+      <c r="BB29" t="s">
         <v>1245</v>
       </c>
-      <c r="BB29" t="s">
-        <v>1246</v>
-      </c>
       <c r="BC29">
-        <v>0.98574436213546524</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD29">
-        <v>261.35336084980423</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12847,16 +12847,16 @@
         <v>575</v>
       </c>
       <c r="Y30" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="Z30" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA30">
-        <v>0.99377714174527498</v>
+        <v>0.98211145389932475</v>
       </c>
       <c r="AB30">
-        <v>114.08573466995766</v>
+        <v>327.95667851237977</v>
       </c>
       <c r="AD30" t="s">
         <v>534</v>
@@ -12883,16 +12883,16 @@
         <v>914</v>
       </c>
       <c r="AM30" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AN30" t="s">
         <v>1052</v>
       </c>
-      <c r="AN30" t="s">
-        <v>1053</v>
-      </c>
       <c r="AO30">
-        <v>0.99532453653339104</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP30">
-        <v>85.716830221163534</v>
+        <v>341.91992986513412</v>
       </c>
       <c r="AR30" t="s">
         <v>534</v>
@@ -12919,16 +12919,16 @@
         <v>1186</v>
       </c>
       <c r="BA30" t="s">
+        <v>1246</v>
+      </c>
+      <c r="BB30" t="s">
         <v>1247</v>
       </c>
-      <c r="BB30" t="s">
-        <v>1248</v>
-      </c>
       <c r="BC30">
-        <v>0.98163861082146986</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD30">
-        <v>336.62546827305243</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12993,16 +12993,16 @@
         <v>577</v>
       </c>
       <c r="Y31" t="s">
-        <v>525</v>
+        <v>467</v>
       </c>
       <c r="Z31" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AA31">
-        <v>0.99516685156772267</v>
+        <v>0.99654205356515035</v>
       </c>
       <c r="AB31">
-        <v>88.60772125841865</v>
+        <v>63.395684638909763</v>
       </c>
       <c r="AD31" t="s">
         <v>534</v>
@@ -13029,16 +13029,16 @@
         <v>916</v>
       </c>
       <c r="AM31" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AN31" t="s">
         <v>1054</v>
       </c>
-      <c r="AN31" t="s">
-        <v>1055</v>
-      </c>
       <c r="AO31">
-        <v>0.99593828267147511</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP31">
-        <v>74.464817689622748</v>
+        <v>258.57410995127316</v>
       </c>
       <c r="AR31" t="s">
         <v>534</v>
@@ -13065,16 +13065,16 @@
         <v>1188</v>
       </c>
       <c r="BA31" t="s">
+        <v>1248</v>
+      </c>
+      <c r="BB31" t="s">
         <v>1249</v>
       </c>
-      <c r="BB31" t="s">
-        <v>1250</v>
-      </c>
       <c r="BC31">
-        <v>0.99032129621526932</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD31">
-        <v>177.44290272006148</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13139,16 +13139,16 @@
         <v>579</v>
       </c>
       <c r="Y32" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="Z32" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AA32">
-        <v>0.96942910386940295</v>
+        <v>0.99504817442297822</v>
       </c>
       <c r="AB32">
-        <v>560.46642906094564</v>
+        <v>90.78346891206678</v>
       </c>
       <c r="AD32" t="s">
         <v>534</v>
@@ -13175,16 +13175,16 @@
         <v>918</v>
       </c>
       <c r="AM32" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AN32" t="s">
         <v>1056</v>
       </c>
-      <c r="AN32" t="s">
-        <v>1057</v>
-      </c>
       <c r="AO32">
-        <v>0.97020178001960844</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP32">
-        <v>546.30069964051177</v>
+        <v>40.90273458067751</v>
       </c>
       <c r="AR32" t="s">
         <v>534</v>
@@ -13211,16 +13211,16 @@
         <v>1190</v>
       </c>
       <c r="BA32" t="s">
+        <v>1250</v>
+      </c>
+      <c r="BB32" t="s">
         <v>1251</v>
       </c>
-      <c r="BB32" t="s">
-        <v>1252</v>
-      </c>
       <c r="BC32">
-        <v>0.99420451954813838</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD32">
-        <v>106.25047495079694</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13285,16 +13285,16 @@
         <v>581</v>
       </c>
       <c r="Y33" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="Z33" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AA33">
-        <v>0.99726809134187266</v>
+        <v>0.99470247457730832</v>
       </c>
       <c r="AB33">
-        <v>50.0849920656675</v>
+        <v>97.121299416014665</v>
       </c>
       <c r="AD33" t="s">
         <v>534</v>
@@ -13321,16 +13321,16 @@
         <v>920</v>
       </c>
       <c r="AM33" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AN33" t="s">
         <v>1058</v>
       </c>
-      <c r="AN33" t="s">
-        <v>1059</v>
-      </c>
       <c r="AO33">
-        <v>0.99693672852577231</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP33">
-        <v>56.159977027506663</v>
+        <v>74.530739771815789</v>
       </c>
       <c r="AR33" t="s">
         <v>534</v>
@@ -13357,16 +13357,16 @@
         <v>1192</v>
       </c>
       <c r="BA33" t="s">
+        <v>1252</v>
+      </c>
+      <c r="BB33" t="s">
         <v>1253</v>
       </c>
-      <c r="BB33" t="s">
-        <v>1254</v>
-      </c>
       <c r="BC33">
-        <v>0.9933934749176847</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD33">
-        <v>121.11962650911367</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13431,16 +13431,16 @@
         <v>583</v>
       </c>
       <c r="Y34" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="Z34" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="AA34">
-        <v>0.97962408753770291</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB34">
-        <v>373.55839514211272</v>
+        <v>82.539922240185263</v>
       </c>
       <c r="AD34" t="s">
         <v>534</v>
@@ -13467,16 +13467,16 @@
         <v>922</v>
       </c>
       <c r="AM34" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AN34" t="s">
         <v>1060</v>
       </c>
-      <c r="AN34" t="s">
-        <v>1061</v>
-      </c>
       <c r="AO34">
-        <v>0.99478775228549088</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP34">
-        <v>95.557874766001078</v>
+        <v>57.905423216266421</v>
       </c>
       <c r="AR34" t="s">
         <v>534</v>
@@ -13503,16 +13503,16 @@
         <v>1194</v>
       </c>
       <c r="BA34" t="s">
+        <v>1254</v>
+      </c>
+      <c r="BB34" t="s">
         <v>1255</v>
       </c>
-      <c r="BB34" t="s">
-        <v>1107</v>
-      </c>
       <c r="BC34">
-        <v>0.99418931598784899</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD34">
-        <v>106.52920688943452</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13577,16 +13577,16 @@
         <v>585</v>
       </c>
       <c r="Y35" t="s">
-        <v>498</v>
+        <v>527</v>
       </c>
       <c r="Z35" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="AA35">
-        <v>0.99098167665935155</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB35">
-        <v>165.33592791188894</v>
+        <v>868.72862240505196</v>
       </c>
       <c r="AD35" t="s">
         <v>534</v>
@@ -13613,16 +13613,16 @@
         <v>924</v>
       </c>
       <c r="AM35" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AN35" t="s">
         <v>1062</v>
       </c>
-      <c r="AN35" t="s">
-        <v>1063</v>
-      </c>
       <c r="AO35">
-        <v>0.99244513691456471</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP35">
-        <v>138.50582323297994</v>
+        <v>85.716830221163534</v>
       </c>
       <c r="AR35" t="s">
         <v>534</v>
@@ -13655,10 +13655,10 @@
         <v>1257</v>
       </c>
       <c r="BC35">
-        <v>0.99232494426983575</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD35">
-        <v>140.70935505301131</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13723,16 +13723,16 @@
         <v>587</v>
       </c>
       <c r="Y36" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
       <c r="Z36" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AA36">
-        <v>0.98485684158558628</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB36">
-        <v>277.62457093091871</v>
+        <v>475.8705861429753</v>
       </c>
       <c r="AD36" t="s">
         <v>534</v>
@@ -13759,16 +13759,16 @@
         <v>926</v>
       </c>
       <c r="AM36" t="s">
+        <v>1063</v>
+      </c>
+      <c r="AN36" t="s">
         <v>1064</v>
       </c>
-      <c r="AN36" t="s">
-        <v>770</v>
-      </c>
       <c r="AO36">
-        <v>0.97416725971121887</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP36">
-        <v>473.60023862765331</v>
+        <v>74.464817689622748</v>
       </c>
       <c r="AR36" t="s">
         <v>534</v>
@@ -13798,13 +13798,13 @@
         <v>1258</v>
       </c>
       <c r="BB36" t="s">
-        <v>1259</v>
+        <v>1230</v>
       </c>
       <c r="BC36">
-        <v>0.98775115723917273</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD36">
-        <v>224.56211728183334</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13869,16 +13869,16 @@
         <v>589</v>
       </c>
       <c r="Y37" t="s">
-        <v>493</v>
+        <v>420</v>
       </c>
       <c r="Z37" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AA37">
-        <v>0.98211145389932475</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB37">
-        <v>327.95667851237977</v>
+        <v>226.88936094280919</v>
       </c>
       <c r="AD37" t="s">
         <v>534</v>
@@ -13911,10 +13911,10 @@
         <v>1066</v>
       </c>
       <c r="AO37">
-        <v>0.99760255773158468</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP37">
-        <v>43.953108254279897</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR37" t="s">
         <v>534</v>
@@ -13941,16 +13941,16 @@
         <v>1200</v>
       </c>
       <c r="BA37" t="s">
+        <v>1259</v>
+      </c>
+      <c r="BB37" t="s">
         <v>1260</v>
       </c>
-      <c r="BB37" t="s">
-        <v>1222</v>
-      </c>
       <c r="BC37">
-        <v>0.99203097418485064</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD37">
-        <v>146.09880661107059</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14015,16 +14015,16 @@
         <v>591</v>
       </c>
       <c r="Y38" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="Z38" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AA38">
-        <v>0.99654205356515035</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB38">
-        <v>63.395684638909763</v>
+        <v>224.55764046872929</v>
       </c>
       <c r="AD38" t="s">
         <v>534</v>
@@ -14057,10 +14057,10 @@
         <v>1068</v>
       </c>
       <c r="AO38">
-        <v>0.99352359657507616</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP38">
-        <v>118.7340627902709</v>
+        <v>83.589016951479763</v>
       </c>
       <c r="AR38" t="s">
         <v>534</v>
@@ -14093,10 +14093,10 @@
         <v>1262</v>
       </c>
       <c r="BC38">
-        <v>0.97821242976023937</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD38">
-        <v>399.43878772894504</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14161,16 +14161,16 @@
         <v>593</v>
       </c>
       <c r="Y39" t="s">
-        <v>460</v>
+        <v>495</v>
       </c>
       <c r="Z39" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AA39">
-        <v>0.99504817442297822</v>
+        <v>0.99647006537565563</v>
       </c>
       <c r="AB39">
-        <v>90.78346891206678</v>
+        <v>64.715468112981057</v>
       </c>
       <c r="AD39" t="s">
         <v>534</v>
@@ -14203,10 +14203,10 @@
         <v>1070</v>
       </c>
       <c r="AO39">
-        <v>0.99433447571906541</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP39">
-        <v>103.86794515046822</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR39" t="s">
         <v>534</v>
@@ -14239,10 +14239,10 @@
         <v>1264</v>
       </c>
       <c r="BC39">
-        <v>0.98946506962487613</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD39">
-        <v>193.14039021060518</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14307,16 +14307,16 @@
         <v>595</v>
       </c>
       <c r="Y40" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="Z40" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AA40">
-        <v>0.99470247457730832</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB40">
-        <v>97.121299416014665</v>
+        <v>645.26520366712316</v>
       </c>
       <c r="AD40" t="s">
         <v>534</v>
@@ -14346,13 +14346,13 @@
         <v>1071</v>
       </c>
       <c r="AN40" t="s">
-        <v>787</v>
+        <v>1072</v>
       </c>
       <c r="AO40">
-        <v>0.98674094240398891</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP40">
-        <v>243.0827225935364</v>
+        <v>105.47547991621673</v>
       </c>
       <c r="AR40" t="s">
         <v>534</v>
@@ -14385,10 +14385,10 @@
         <v>1266</v>
       </c>
       <c r="BC40">
-        <v>0.99314574070258299</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD40">
-        <v>125.66142045264445</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14453,16 +14453,16 @@
         <v>597</v>
       </c>
       <c r="Y41" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="Z41" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AA41">
-        <v>0.99549782242326257</v>
+        <v>0.99267004448650609</v>
       </c>
       <c r="AB41">
-        <v>82.539922240185263</v>
+        <v>134.38251774738842</v>
       </c>
       <c r="AD41" t="s">
         <v>534</v>
@@ -14489,16 +14489,16 @@
         <v>936</v>
       </c>
       <c r="AM41" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AN41" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AO41">
-        <v>0.98452519237182756</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP41">
-        <v>283.70480651649393</v>
+        <v>195.31167947327185</v>
       </c>
       <c r="AR41" t="s">
         <v>534</v>
@@ -14599,16 +14599,16 @@
         <v>599</v>
       </c>
       <c r="Y42" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="Z42" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AA42">
-        <v>0.9914627894548943</v>
+        <v>0.9948848527457459</v>
       </c>
       <c r="AB42">
-        <v>156.51552666027055</v>
+        <v>93.777699661325343</v>
       </c>
       <c r="AD42" t="s">
         <v>534</v>
@@ -14635,16 +14635,16 @@
         <v>938</v>
       </c>
       <c r="AM42" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AN42" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AO42">
-        <v>0.99679967385551038</v>
+        <v>0.99499049355022928</v>
       </c>
       <c r="AP42">
-        <v>58.672645982308907</v>
+        <v>91.840951579129481</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14709,16 +14709,16 @@
         <v>601</v>
       </c>
       <c r="Y43" t="s">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="Z43" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AA43">
-        <v>0.9776523073059149</v>
+        <v>0.9922030648239526</v>
       </c>
       <c r="AB43">
-        <v>409.70769939155917</v>
+        <v>142.94381156086857</v>
       </c>
       <c r="AD43" t="s">
         <v>534</v>
@@ -14745,16 +14745,16 @@
         <v>940</v>
       </c>
       <c r="AM43" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="AN43" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="AO43">
-        <v>0.99414234808301016</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP43">
-        <v>107.39028514481463</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14819,16 +14819,16 @@
         <v>603</v>
       </c>
       <c r="Y44" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="Z44" t="s">
-        <v>800</v>
+        <v>783</v>
       </c>
       <c r="AA44">
-        <v>0.98289281118622185</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB44">
-        <v>313.63179491926536</v>
+        <v>470.66510807906917</v>
       </c>
       <c r="AD44" t="s">
         <v>534</v>
@@ -14855,16 +14855,16 @@
         <v>942</v>
       </c>
       <c r="AM44" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="AN44" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AO44">
-        <v>0.99445933293330402</v>
+        <v>0.99746043308117838</v>
       </c>
       <c r="AP44">
-        <v>101.57889622275951</v>
+        <v>46.558726845063177</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14929,16 +14929,16 @@
         <v>605</v>
       </c>
       <c r="Y45" t="s">
-        <v>424</v>
+        <v>487</v>
       </c>
       <c r="Z45" t="s">
         <v>801</v>
       </c>
       <c r="AA45">
-        <v>0.99593583828988941</v>
+        <v>0.9882282251528024</v>
       </c>
       <c r="AB45">
-        <v>74.509631352026517</v>
+        <v>215.81587219862183</v>
       </c>
       <c r="AD45" t="s">
         <v>534</v>
@@ -14965,16 +14965,16 @@
         <v>944</v>
       </c>
       <c r="AM45" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AN45" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="AO45">
-        <v>0.9961850470371636</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP45">
-        <v>69.94080431866837</v>
+        <v>80.747827133859133</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15039,16 +15039,16 @@
         <v>607</v>
       </c>
       <c r="Y46" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="Z46" t="s">
         <v>802</v>
       </c>
       <c r="AA46">
-        <v>0.98150124893892388</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB46">
-        <v>339.14376945306287</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD46" t="s">
         <v>534</v>
@@ -15075,16 +15075,16 @@
         <v>946</v>
       </c>
       <c r="AM46" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AN46" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AO46">
-        <v>0.99710531380540124</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP46">
-        <v>53.069246900976879</v>
+        <v>60.189444792275019</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15149,16 +15149,16 @@
         <v>609</v>
       </c>
       <c r="Y47" t="s">
-        <v>502</v>
+        <v>427</v>
       </c>
       <c r="Z47" t="s">
         <v>803</v>
       </c>
       <c r="AA47">
-        <v>0.99523081353776888</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB47">
-        <v>87.435085140903482</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD47" t="s">
         <v>534</v>
@@ -15185,16 +15185,16 @@
         <v>948</v>
       </c>
       <c r="AM47" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AN47" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="AO47">
-        <v>0.99403730604060547</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP47">
-        <v>109.31605592223302</v>
+        <v>430.61202751883985</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15259,16 +15259,16 @@
         <v>611</v>
       </c>
       <c r="Y48" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="Z48" t="s">
         <v>804</v>
       </c>
       <c r="AA48">
-        <v>0.9916432660493133</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB48">
-        <v>153.20678909592235</v>
+        <v>41.695953373122713</v>
       </c>
       <c r="AD48" t="s">
         <v>534</v>
@@ -15295,16 +15295,16 @@
         <v>950</v>
       </c>
       <c r="AM48" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="AN48" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="AO48">
-        <v>0.99105808324017197</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP48">
-        <v>163.93514059684662</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15369,16 +15369,16 @@
         <v>613</v>
       </c>
       <c r="Y49" t="s">
-        <v>423</v>
+        <v>475</v>
       </c>
       <c r="Z49" t="s">
         <v>805</v>
       </c>
       <c r="AA49">
-        <v>0.99570118415007625</v>
+        <v>0.99012236069527793</v>
       </c>
       <c r="AB49">
-        <v>78.81162391526847</v>
+        <v>181.09005391990564</v>
       </c>
       <c r="AD49" t="s">
         <v>534</v>
@@ -15405,16 +15405,16 @@
         <v>952</v>
       </c>
       <c r="AM49" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="AN49" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AO49">
-        <v>0.9974675531234084</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP49">
-        <v>46.428192737512276</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15479,16 +15479,16 @@
         <v>615</v>
       </c>
       <c r="Y50" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Z50" t="s">
         <v>806</v>
       </c>
       <c r="AA50">
-        <v>0.99691903985105013</v>
+        <v>0.98990296758392993</v>
       </c>
       <c r="AB50">
-        <v>56.484269397415083</v>
+        <v>185.11226096128556</v>
       </c>
       <c r="AD50" t="s">
         <v>534</v>
@@ -15515,16 +15515,16 @@
         <v>954</v>
       </c>
       <c r="AM50" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AN50" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AO50">
-        <v>0.99534886842510228</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP50">
-        <v>85.270745539791065</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15589,16 +15589,16 @@
         <v>617</v>
       </c>
       <c r="Y51" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="Z51" t="s">
         <v>807</v>
       </c>
       <c r="AA51">
-        <v>0.98563153879963317</v>
+        <v>0.99377714174527498</v>
       </c>
       <c r="AB51">
-        <v>263.42178867339101</v>
+        <v>114.08573466995766</v>
       </c>
       <c r="AD51" t="s">
         <v>534</v>
@@ -15625,16 +15625,16 @@
         <v>956</v>
       </c>
       <c r="AM51" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AN51" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AO51">
-        <v>0.99551365545858539</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP51">
-        <v>82.249649925934918</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15699,16 +15699,16 @@
         <v>619</v>
       </c>
       <c r="Y52" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="Z52" t="s">
         <v>808</v>
       </c>
       <c r="AA52">
-        <v>0.99529226044395613</v>
+        <v>0.99516685156772267</v>
       </c>
       <c r="AB52">
-        <v>86.308558527470979</v>
+        <v>88.60772125841865</v>
       </c>
       <c r="AD52" t="s">
         <v>534</v>
@@ -15735,16 +15735,16 @@
         <v>958</v>
       </c>
       <c r="AM52" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AN52" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AO52">
-        <v>0.99554924619735208</v>
+        <v>0.99677419959133018</v>
       </c>
       <c r="AP52">
-        <v>81.597153048545437</v>
+        <v>59.139674158947656</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15809,16 +15809,16 @@
         <v>621</v>
       </c>
       <c r="Y53" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="Z53" t="s">
         <v>809</v>
       </c>
       <c r="AA53">
-        <v>0.99443562760718263</v>
+        <v>0.99240925523869494</v>
       </c>
       <c r="AB53">
-        <v>102.01349386831856</v>
+        <v>139.16365395725984</v>
       </c>
       <c r="AD53" t="s">
         <v>534</v>
@@ -15845,16 +15845,16 @@
         <v>960</v>
       </c>
       <c r="AM53" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AN53" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AO53">
-        <v>0.99083036293819104</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP53">
-        <v>168.11001279983091</v>
+        <v>42.750927651225993</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15919,16 +15919,16 @@
         <v>623</v>
       </c>
       <c r="Y54" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="Z54" t="s">
-        <v>810</v>
+        <v>785</v>
       </c>
       <c r="AA54">
-        <v>0.96520767961718001</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB54">
-        <v>637.85920701836687</v>
+        <v>505.08652809978111</v>
       </c>
       <c r="AD54" t="s">
         <v>534</v>
@@ -15955,16 +15955,16 @@
         <v>962</v>
       </c>
       <c r="AM54" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="AN54" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AO54">
-        <v>0.9976320377495026</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP54">
-        <v>43.412641259119624</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16029,16 +16029,16 @@
         <v>625</v>
       </c>
       <c r="Y55" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="Z55" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AA55">
-        <v>0.99344074878931121</v>
+        <v>0.99172397756136033</v>
       </c>
       <c r="AB55">
-        <v>120.25293886262826</v>
+        <v>151.72707804172813</v>
       </c>
       <c r="AD55" t="s">
         <v>534</v>
@@ -16065,16 +16065,16 @@
         <v>964</v>
       </c>
       <c r="AM55" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="AN55" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AO55">
-        <v>0.99424679200457</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP55">
-        <v>105.47547991621673</v>
+        <v>121.72426728897108</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16139,16 +16139,16 @@
         <v>627</v>
       </c>
       <c r="Y56" t="s">
-        <v>499</v>
+        <v>451</v>
       </c>
       <c r="Z56" t="s">
-        <v>777</v>
+        <v>811</v>
       </c>
       <c r="AA56">
-        <v>0.99459650548991607</v>
+        <v>0.99431900976645593</v>
       </c>
       <c r="AB56">
-        <v>99.064066018204684</v>
+        <v>104.15148761497397</v>
       </c>
       <c r="AD56" t="s">
         <v>534</v>
@@ -16175,16 +16175,16 @@
         <v>966</v>
       </c>
       <c r="AM56" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AN56" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AO56">
-        <v>0.98934663566509429</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP56">
-        <v>195.31167947327185</v>
+        <v>44.092000370450322</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16249,16 +16249,16 @@
         <v>629</v>
       </c>
       <c r="Y57" t="s">
-        <v>490</v>
+        <v>430</v>
       </c>
       <c r="Z57" t="s">
         <v>812</v>
       </c>
       <c r="AA57">
-        <v>0.99655727877565281</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB57">
-        <v>63.116555779697698</v>
+        <v>98.356996715718111</v>
       </c>
       <c r="AD57" t="s">
         <v>534</v>
@@ -16285,16 +16285,16 @@
         <v>968</v>
       </c>
       <c r="AM57" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="AN57" t="s">
-        <v>1105</v>
+        <v>841</v>
       </c>
       <c r="AO57">
-        <v>0.99499049355022928</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP57">
-        <v>91.840951579129481</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16359,16 +16359,16 @@
         <v>631</v>
       </c>
       <c r="Y58" t="s">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="Z58" t="s">
         <v>813</v>
       </c>
       <c r="AA58">
-        <v>0.99221351039035977</v>
+        <v>0.99343259267015904</v>
       </c>
       <c r="AB58">
-        <v>142.75230951007163</v>
+        <v>120.40246771375152</v>
       </c>
       <c r="AD58" t="s">
         <v>534</v>
@@ -16398,13 +16398,13 @@
         <v>1106</v>
       </c>
       <c r="AN58" t="s">
-        <v>1107</v>
+        <v>771</v>
       </c>
       <c r="AO58">
-        <v>0.99729205446773184</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP58">
-        <v>49.645668091582088</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16469,16 +16469,16 @@
         <v>633</v>
       </c>
       <c r="Y59" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="Z59" t="s">
         <v>814</v>
       </c>
       <c r="AA59">
-        <v>0.99067174034238459</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB59">
-        <v>171.01809372294977</v>
+        <v>443.37880474956393</v>
       </c>
       <c r="AD59" t="s">
         <v>534</v>
@@ -16505,16 +16505,16 @@
         <v>972</v>
       </c>
       <c r="AM59" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AN59" t="s">
         <v>1108</v>
       </c>
-      <c r="AN59" t="s">
-        <v>1109</v>
-      </c>
       <c r="AO59">
-        <v>0.99746043308117838</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP59">
-        <v>46.558726845063177</v>
+        <v>184.02231422223667</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16579,16 +16579,16 @@
         <v>635</v>
       </c>
       <c r="Y60" t="s">
-        <v>418</v>
+        <v>485</v>
       </c>
       <c r="Z60" t="s">
         <v>815</v>
       </c>
       <c r="AA60">
-        <v>0.99634417822754895</v>
+        <v>0.99542292233022822</v>
       </c>
       <c r="AB60">
-        <v>67.023399161603095</v>
+        <v>83.913090612483515</v>
       </c>
       <c r="AD60" t="s">
         <v>534</v>
@@ -16615,16 +16615,16 @@
         <v>974</v>
       </c>
       <c r="AM60" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AN60" t="s">
         <v>1110</v>
       </c>
-      <c r="AN60" t="s">
-        <v>778</v>
-      </c>
       <c r="AO60">
-        <v>0.95532613069733086</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP60">
-        <v>819.02093721560016</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16689,16 +16689,16 @@
         <v>637</v>
       </c>
       <c r="Y61" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="Z61" t="s">
         <v>816</v>
       </c>
       <c r="AA61">
-        <v>0.98416341622871006</v>
+        <v>0.99647584863086869</v>
       </c>
       <c r="AB61">
-        <v>290.33736914031488</v>
+        <v>64.60944176740837</v>
       </c>
       <c r="AD61" t="s">
         <v>534</v>
@@ -16728,13 +16728,13 @@
         <v>1111</v>
       </c>
       <c r="AN61" t="s">
-        <v>835</v>
+        <v>1112</v>
       </c>
       <c r="AO61">
-        <v>0.98599828568941739</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP61">
-        <v>256.69809569401372</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16799,16 +16799,16 @@
         <v>639</v>
       </c>
       <c r="Y62" t="s">
-        <v>497</v>
+        <v>431</v>
       </c>
       <c r="Z62" t="s">
         <v>817</v>
       </c>
       <c r="AA62">
-        <v>0.99563792883070867</v>
+        <v>0.99780983219878738</v>
       </c>
       <c r="AB62">
-        <v>79.971304770340467</v>
+        <v>40.153076355563911</v>
       </c>
       <c r="AD62" t="s">
         <v>534</v>
@@ -16835,16 +16835,16 @@
         <v>978</v>
       </c>
       <c r="AM62" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="AN62" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="AO62">
-        <v>0.98996241922424166</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP62">
-        <v>184.02231422223667</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16909,16 +16909,16 @@
         <v>641</v>
       </c>
       <c r="Y63" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="Z63" t="s">
         <v>818</v>
       </c>
       <c r="AA63">
-        <v>0.99558181127270129</v>
+        <v>0.99724696581141214</v>
       </c>
       <c r="AB63">
-        <v>81.000126667143434</v>
+        <v>50.472293457444586</v>
       </c>
       <c r="AD63" t="s">
         <v>534</v>
@@ -16945,16 +16945,16 @@
         <v>980</v>
       </c>
       <c r="AM63" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AN63" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="AO63">
-        <v>0.99620534810300254</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP63">
-        <v>69.568618111619969</v>
+        <v>86.673039153654699</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17019,16 +17019,16 @@
         <v>643</v>
       </c>
       <c r="Y64" t="s">
-        <v>516</v>
+        <v>461</v>
       </c>
       <c r="Z64" t="s">
         <v>819</v>
       </c>
       <c r="AA64">
-        <v>0.99390501557434718</v>
+        <v>0.99589550629055523</v>
       </c>
       <c r="AB64">
-        <v>111.7413811369688</v>
+        <v>75.249051339820184</v>
       </c>
       <c r="AD64" t="s">
         <v>534</v>
@@ -17055,16 +17055,16 @@
         <v>982</v>
       </c>
       <c r="AM64" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="AN64" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AO64">
-        <v>0.99374536027070226</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP64">
-        <v>114.668395037126</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17129,16 +17129,16 @@
         <v>645</v>
       </c>
       <c r="Y65" t="s">
-        <v>421</v>
+        <v>520</v>
       </c>
       <c r="Z65" t="s">
         <v>820</v>
       </c>
       <c r="AA65">
-        <v>0.99553066735440277</v>
+        <v>0.99531156065644533</v>
       </c>
       <c r="AB65">
-        <v>81.937765169281747</v>
+        <v>85.954721298502818</v>
       </c>
       <c r="AD65" t="s">
         <v>534</v>
@@ -17165,16 +17165,16 @@
         <v>984</v>
       </c>
       <c r="AM65" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AN65" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AO65">
-        <v>0.99681385284485569</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP65">
-        <v>58.41269784431158</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17239,16 +17239,16 @@
         <v>647</v>
       </c>
       <c r="Y66" t="s">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="Z66" t="s">
         <v>821</v>
       </c>
       <c r="AA66">
-        <v>0.99049341406542279</v>
+        <v>0.99706825374988217</v>
       </c>
       <c r="AB66">
-        <v>174.28740880058183</v>
+        <v>53.748681252160438</v>
       </c>
       <c r="AD66" t="s">
         <v>534</v>
@@ -17275,16 +17275,16 @@
         <v>986</v>
       </c>
       <c r="AM66" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="AN66" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="AO66">
-        <v>0.99527237968252791</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP66">
-        <v>86.673039153654699</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17349,16 +17349,16 @@
         <v>649</v>
       </c>
       <c r="Y67" t="s">
-        <v>522</v>
+        <v>469</v>
       </c>
       <c r="Z67" t="s">
-        <v>822</v>
+        <v>783</v>
       </c>
       <c r="AA67">
-        <v>0.99575157784901702</v>
+        <v>0.96238190390083644</v>
       </c>
       <c r="AB67">
-        <v>77.887739434686992</v>
+        <v>689.665095151331</v>
       </c>
       <c r="AD67" t="s">
         <v>534</v>
@@ -17385,16 +17385,16 @@
         <v>988</v>
       </c>
       <c r="AM67" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AN67" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="AO67">
-        <v>0.9917253583369573</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP67">
-        <v>151.70176382244892</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17459,16 +17459,16 @@
         <v>651</v>
       </c>
       <c r="Y68" t="s">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="Z68" t="s">
-        <v>823</v>
+        <v>785</v>
       </c>
       <c r="AA68">
-        <v>0.99649411432543766</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB68">
-        <v>64.274570700309781</v>
+        <v>675.25867642804383</v>
       </c>
       <c r="AD68" t="s">
         <v>534</v>
@@ -17495,16 +17495,16 @@
         <v>990</v>
       </c>
       <c r="AM68" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="AN68" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="AO68">
-        <v>0.99569050067699549</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP68">
-        <v>79.007487588415231</v>
+        <v>53.069246900976879</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17569,16 +17569,16 @@
         <v>653</v>
       </c>
       <c r="Y69" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="Z69" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="AA69">
-        <v>0.97907421743006762</v>
+        <v>0.9951089264264793</v>
       </c>
       <c r="AB69">
-        <v>383.63934711542669</v>
+        <v>89.669682181211982</v>
       </c>
       <c r="AD69" t="s">
         <v>534</v>
@@ -17605,16 +17605,16 @@
         <v>992</v>
       </c>
       <c r="AM69" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="AN69" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="AO69">
-        <v>0.97651207122624506</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP69">
-        <v>430.61202751883985</v>
+        <v>82.249649925934918</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17679,16 +17679,16 @@
         <v>655</v>
       </c>
       <c r="Y70" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="Z70" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AA70">
-        <v>0.99558768376711515</v>
+        <v>0.98666519734623237</v>
       </c>
       <c r="AB70">
-        <v>80.892464269556413</v>
+        <v>244.47138198573927</v>
       </c>
       <c r="AD70" t="s">
         <v>534</v>
@@ -17715,16 +17715,16 @@
         <v>994</v>
       </c>
       <c r="AM70" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="AN70" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="AO70">
-        <v>0.9972012891192491</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP70">
-        <v>51.309699480432613</v>
+        <v>81.597153048545437</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17789,16 +17789,16 @@
         <v>657</v>
       </c>
       <c r="Y71" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="Z71" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AA71">
-        <v>0.99324569511004301</v>
+        <v>0.99750070245826261</v>
       </c>
       <c r="AB71">
-        <v>123.82892298254488</v>
+        <v>45.820454931853</v>
       </c>
       <c r="AD71" t="s">
         <v>534</v>
@@ -17825,16 +17825,16 @@
         <v>996</v>
       </c>
       <c r="AM71" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="AN71" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AO71">
-        <v>0.99648541839873139</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP71">
-        <v>64.433996023258757</v>
+        <v>168.11001279983091</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17899,16 +17899,16 @@
         <v>659</v>
       </c>
       <c r="Y72" t="s">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="Z72" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="AA72">
-        <v>0.99419165427276146</v>
+        <v>0.99395341117186964</v>
       </c>
       <c r="AB72">
-        <v>106.48633833270691</v>
+        <v>110.85412851572337</v>
       </c>
       <c r="AD72" t="s">
         <v>534</v>
@@ -17935,16 +17935,16 @@
         <v>998</v>
       </c>
       <c r="AM72" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AN72" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="AO72">
-        <v>0.9976540150806753</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP72">
-        <v>43.009723520953628</v>
+        <v>43.412641259119624</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18009,16 +18009,16 @@
         <v>661</v>
       </c>
       <c r="Y73" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="Z73" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AA73">
-        <v>0.99198935558098356</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB73">
-        <v>146.8618143486346</v>
+        <v>307.49900901993823</v>
       </c>
       <c r="AD73" t="s">
         <v>534</v>
@@ -18045,16 +18045,16 @@
         <v>1000</v>
       </c>
       <c r="AM73" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="AN73" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="AO73">
-        <v>0.99644815774097173</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP73">
-        <v>65.117108082185538</v>
+        <v>546.30069964051177</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18119,16 +18119,16 @@
         <v>663</v>
       </c>
       <c r="Y74" t="s">
-        <v>471</v>
+        <v>437</v>
       </c>
       <c r="Z74" t="s">
-        <v>790</v>
+        <v>827</v>
       </c>
       <c r="AA74">
-        <v>0.97432735774114165</v>
+        <v>0.9974199781412052</v>
       </c>
       <c r="AB74">
-        <v>470.66510807906917</v>
+        <v>47.300400744571718</v>
       </c>
       <c r="AD74" t="s">
         <v>534</v>
@@ -18155,16 +18155,16 @@
         <v>1002</v>
       </c>
       <c r="AM74" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AN74" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AO74">
-        <v>0.99567626923235475</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP74">
-        <v>79.268397406829976</v>
+        <v>56.159977027506663</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18229,16 +18229,16 @@
         <v>665</v>
       </c>
       <c r="Y75" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="Z75" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AA75">
-        <v>0.9882282251528024</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB75">
-        <v>215.81587219862183</v>
+        <v>121.57987025257442</v>
       </c>
       <c r="AD75" t="s">
         <v>534</v>
@@ -18265,16 +18265,16 @@
         <v>1004</v>
       </c>
       <c r="AM75" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="AN75" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AO75">
-        <v>0.99762284649610655</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP75">
-        <v>43.581147571379539</v>
+        <v>95.557874766001078</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18339,16 +18339,16 @@
         <v>667</v>
       </c>
       <c r="Y76" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="Z76" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AA76">
-        <v>0.99136196456122894</v>
+        <v>0.99379477670057537</v>
       </c>
       <c r="AB76">
-        <v>158.36398304413572</v>
+        <v>113.7624271561186</v>
       </c>
       <c r="AD76" t="s">
         <v>534</v>
@@ -18375,16 +18375,16 @@
         <v>1006</v>
       </c>
       <c r="AM76" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="AN76" t="s">
-        <v>1141</v>
+        <v>806</v>
       </c>
       <c r="AO76">
-        <v>0.99175391794306234</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP76">
-        <v>151.17817104385733</v>
+        <v>243.0827225935364</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18449,16 +18449,16 @@
         <v>669</v>
       </c>
       <c r="Y77" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="Z77" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AA77">
-        <v>0.99658191580238853</v>
+        <v>0.9961866142254362</v>
       </c>
       <c r="AB77">
-        <v>62.664876956210314</v>
+        <v>69.91207253366963</v>
       </c>
       <c r="AD77" t="s">
         <v>534</v>
@@ -18491,10 +18491,10 @@
         <v>1143</v>
       </c>
       <c r="AO77">
-        <v>0.99688290256322298</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP77">
-        <v>57.146786340912868</v>
+        <v>283.70480651649393</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18559,16 +18559,16 @@
         <v>671</v>
       </c>
       <c r="Y78" t="s">
-        <v>428</v>
+        <v>483</v>
       </c>
       <c r="Z78" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AA78">
-        <v>0.99772567527055689</v>
+        <v>0.9914627894548943</v>
       </c>
       <c r="AB78">
-        <v>41.695953373122713</v>
+        <v>156.51552666027055</v>
       </c>
       <c r="AD78" t="s">
         <v>534</v>
@@ -18601,10 +18601,10 @@
         <v>1145</v>
       </c>
       <c r="AO78">
-        <v>0.99488275259079373</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP78">
-        <v>93.81620250211445</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18669,16 +18669,16 @@
         <v>673</v>
       </c>
       <c r="Y79" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="Z79" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AA79">
-        <v>0.99295369446862825</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB79">
-        <v>129.18226807514921</v>
+        <v>409.70769939155917</v>
       </c>
       <c r="AD79" t="s">
         <v>534</v>
@@ -18711,10 +18711,10 @@
         <v>1147</v>
       </c>
       <c r="AO79">
-        <v>0.99663220850609069</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP79">
-        <v>61.742844055003644</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18779,16 +18779,16 @@
         <v>675</v>
       </c>
       <c r="Y80" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="Z80" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AA80">
-        <v>0.98571261124433651</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB80">
-        <v>261.93546052049794</v>
+        <v>313.63179491926536</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18853,16 +18853,16 @@
         <v>677</v>
       </c>
       <c r="Y81" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="Z81" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AA81">
-        <v>0.9849019911873127</v>
+        <v>0.99593583828988941</v>
       </c>
       <c r="AB81">
-        <v>276.79682823259958</v>
+        <v>74.509631352026517</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18927,16 +18927,16 @@
         <v>679</v>
       </c>
       <c r="Y82" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="Z82" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AA82">
-        <v>0.99157679714615166</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB82">
-        <v>154.42538565388551</v>
+        <v>64.274570700309781</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -19001,16 +19001,16 @@
         <v>681</v>
       </c>
       <c r="Y83" t="s">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="Z83" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="AA83">
-        <v>0.99619387577842089</v>
+        <v>0.97907421743006762</v>
       </c>
       <c r="AB83">
-        <v>69.778944062284495</v>
+        <v>383.63934711542669</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -19075,16 +19075,16 @@
         <v>683</v>
       </c>
       <c r="Y84" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="Z84" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AA84">
-        <v>0.99497915241892609</v>
+        <v>0.99558768376711515</v>
       </c>
       <c r="AB84">
-        <v>92.048872319688599</v>
+        <v>80.892464269556413</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -19149,16 +19149,16 @@
         <v>685</v>
       </c>
       <c r="Y85" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="Z85" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AA85">
-        <v>0.97581570155911468</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB85">
-        <v>443.37880474956393</v>
+        <v>123.82892298254488</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19223,16 +19223,16 @@
         <v>687</v>
       </c>
       <c r="Y86" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="Z86" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA86">
-        <v>0.99542292233022822</v>
+        <v>0.99419165427276146</v>
       </c>
       <c r="AB86">
-        <v>83.913090612483515</v>
+        <v>106.48633833270691</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19297,16 +19297,16 @@
         <v>689</v>
       </c>
       <c r="Y87" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="Z87" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AA87">
-        <v>0.99647584863086869</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB87">
-        <v>64.60944176740837</v>
+        <v>146.8618143486346</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19371,16 +19371,16 @@
         <v>691</v>
       </c>
       <c r="Y88" t="s">
-        <v>431</v>
+        <v>526</v>
       </c>
       <c r="Z88" t="s">
-        <v>842</v>
+        <v>785</v>
       </c>
       <c r="AA88">
-        <v>0.99780983219878738</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB88">
-        <v>40.153076355563911</v>
+        <v>1103.617804666449</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19445,16 +19445,16 @@
         <v>693</v>
       </c>
       <c r="Y89" t="s">
-        <v>466</v>
+        <v>530</v>
       </c>
       <c r="Z89" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="AA89">
-        <v>0.99724696581141214</v>
+        <v>0.95679935803281835</v>
       </c>
       <c r="AB89">
-        <v>50.472293457444586</v>
+        <v>792.01176939833033</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19519,16 +19519,16 @@
         <v>695</v>
       </c>
       <c r="Y90" t="s">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="Z90" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="AA90">
-        <v>0.99589550629055523</v>
+        <v>0.98761622532712257</v>
       </c>
       <c r="AB90">
-        <v>75.249051339820184</v>
+        <v>227.03586900275366</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19593,16 +19593,16 @@
         <v>697</v>
       </c>
       <c r="Y91" t="s">
-        <v>520</v>
+        <v>448</v>
       </c>
       <c r="Z91" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="AA91">
-        <v>0.99531156065644533</v>
+        <v>0.99003402112096806</v>
       </c>
       <c r="AB91">
-        <v>85.954721298502818</v>
+        <v>182.70961278225187</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19667,16 +19667,16 @@
         <v>699</v>
       </c>
       <c r="Y92" t="s">
-        <v>521</v>
+        <v>459</v>
       </c>
       <c r="Z92" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="AA92">
-        <v>0.99706825374988217</v>
+        <v>0.99466062705491098</v>
       </c>
       <c r="AB92">
-        <v>53.748681252160438</v>
+        <v>97.888503993298116</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19741,16 +19741,16 @@
         <v>701</v>
       </c>
       <c r="Y93" t="s">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="Z93" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="AA93">
-        <v>0.95261480241426988</v>
+        <v>0.9944598150968682</v>
       </c>
       <c r="AB93">
-        <v>868.72862240505196</v>
+        <v>101.5700565574154</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19815,16 +19815,16 @@
         <v>703</v>
       </c>
       <c r="Y94" t="s">
-        <v>531</v>
+        <v>462</v>
       </c>
       <c r="Z94" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="AA94">
-        <v>0.97404342257401955</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB94">
-        <v>475.8705861429753</v>
+        <v>92.674656500591539</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19889,16 +19889,16 @@
         <v>705</v>
       </c>
       <c r="Y95" t="s">
-        <v>420</v>
+        <v>506</v>
       </c>
       <c r="Z95" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="AA95">
-        <v>0.98762421667584677</v>
+        <v>0.99438812565699364</v>
       </c>
       <c r="AB95">
-        <v>226.88936094280919</v>
+        <v>102.88436295511657</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19963,16 +19963,16 @@
         <v>707</v>
       </c>
       <c r="Y96" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="Z96" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="AA96">
-        <v>0.98775140142897844</v>
+        <v>0.99643191679577148</v>
       </c>
       <c r="AB96">
-        <v>224.55764046872929</v>
+        <v>65.414858744189985</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -20037,16 +20037,16 @@
         <v>709</v>
       </c>
       <c r="Y97" t="s">
-        <v>495</v>
+        <v>421</v>
       </c>
       <c r="Z97" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="AA97">
-        <v>0.99647006537565563</v>
+        <v>0.99553066735440277</v>
       </c>
       <c r="AB97">
-        <v>64.715468112981057</v>
+        <v>81.937765169281747</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -20111,16 +20111,16 @@
         <v>711</v>
       </c>
       <c r="Y98" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="Z98" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="AA98">
-        <v>0.96480371616361149</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB98">
-        <v>645.26520366712316</v>
+        <v>174.28740880058183</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20185,16 +20185,16 @@
         <v>713</v>
       </c>
       <c r="Y99" t="s">
-        <v>446</v>
+        <v>522</v>
       </c>
       <c r="Z99" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="AA99">
-        <v>0.99267004448650609</v>
+        <v>0.99575157784901702</v>
       </c>
       <c r="AB99">
-        <v>134.38251774738842</v>
+        <v>77.887739434686992</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20259,16 +20259,16 @@
         <v>715</v>
       </c>
       <c r="Y100" t="s">
-        <v>519</v>
+        <v>474</v>
       </c>
       <c r="Z100" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="AA100">
-        <v>0.9948848527457459</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB100">
-        <v>93.777699661325343</v>
+        <v>90.443352439796072</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20333,16 +20333,16 @@
         <v>717</v>
       </c>
       <c r="Y101" t="s">
-        <v>524</v>
+        <v>439</v>
       </c>
       <c r="Z101" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="AA101">
-        <v>0.9922030648239526</v>
+        <v>0.97537853020161625</v>
       </c>
       <c r="AB101">
-        <v>142.94381156086857</v>
+        <v>451.39361297036953</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20407,16 +20407,16 @@
         <v>719</v>
       </c>
       <c r="Y102" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="Z102" t="s">
-        <v>790</v>
+        <v>854</v>
       </c>
       <c r="AA102">
-        <v>0.96238190390083644</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB102">
-        <v>689.665095151331</v>
+        <v>106.82211818572355</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20481,16 +20481,16 @@
         <v>721</v>
       </c>
       <c r="Y103" t="s">
-        <v>528</v>
+        <v>429</v>
       </c>
       <c r="Z103" t="s">
-        <v>777</v>
+        <v>855</v>
       </c>
       <c r="AA103">
-        <v>0.96316770855847034</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB103">
-        <v>675.25867642804383</v>
+        <v>62.251070203636829</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20555,16 +20555,16 @@
         <v>723</v>
       </c>
       <c r="Y104" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="Z104" t="s">
         <v>856</v>
       </c>
       <c r="AA104">
-        <v>0.9951089264264793</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB104">
-        <v>89.669682181211982</v>
+        <v>54.23617409891024</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20629,16 +20629,16 @@
         <v>725</v>
       </c>
       <c r="Y105" t="s">
-        <v>434</v>
+        <v>512</v>
       </c>
       <c r="Z105" t="s">
         <v>857</v>
       </c>
       <c r="AA105">
-        <v>0.98666519734623237</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB105">
-        <v>244.47138198573927</v>
+        <v>154.58276065179118</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20703,16 +20703,16 @@
         <v>727</v>
       </c>
       <c r="Y106" t="s">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="Z106" t="s">
         <v>858</v>
       </c>
       <c r="AA106">
-        <v>0.99750070245826261</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB106">
-        <v>45.820454931853</v>
+        <v>49.309812409870183</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20777,16 +20777,16 @@
         <v>729</v>
       </c>
       <c r="Y107" t="s">
-        <v>422</v>
+        <v>514</v>
       </c>
       <c r="Z107" t="s">
         <v>859</v>
       </c>
       <c r="AA107">
-        <v>0.99395341117186964</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB107">
-        <v>110.85412851572337</v>
+        <v>121.27899510281891</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20851,16 +20851,16 @@
         <v>731</v>
       </c>
       <c r="Y108" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="Z108" t="s">
-        <v>860</v>
+        <v>783</v>
       </c>
       <c r="AA108">
-        <v>0.98322732678073066</v>
+        <v>0.9621480095608167</v>
       </c>
       <c r="AB108">
-        <v>307.49900901993823</v>
+        <v>693.95315805169378</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20925,16 +20925,16 @@
         <v>733</v>
       </c>
       <c r="Y109" t="s">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="Z109" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AA109">
-        <v>0.9974199781412052</v>
+        <v>0.98916941127667946</v>
       </c>
       <c r="AB109">
-        <v>47.300400744571718</v>
+        <v>198.56079326087576</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20999,16 +20999,16 @@
         <v>735</v>
       </c>
       <c r="Y110" t="s">
-        <v>496</v>
+        <v>438</v>
       </c>
       <c r="Z110" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AA110">
-        <v>0.99336837071349593</v>
+        <v>0.97159134368321343</v>
       </c>
       <c r="AB110">
-        <v>121.57987025257442</v>
+        <v>520.82536580775354</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -21073,16 +21073,16 @@
         <v>737</v>
       </c>
       <c r="Y111" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="Z111" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AA111">
-        <v>0.99379477670057537</v>
+        <v>0.99359614530212825</v>
       </c>
       <c r="AB111">
-        <v>113.7624271561186</v>
+        <v>117.40400279431638</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -21147,16 +21147,16 @@
         <v>739</v>
       </c>
       <c r="Y112" t="s">
-        <v>454</v>
+        <v>518</v>
       </c>
       <c r="Z112" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AA112">
-        <v>0.9961866142254362</v>
+        <v>0.99488082982009873</v>
       </c>
       <c r="AB112">
-        <v>69.91207253366963</v>
+        <v>93.851453298190577</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21221,16 +21221,16 @@
         <v>741</v>
       </c>
       <c r="Y113" t="s">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="Z113" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="AA113">
-        <v>0.99240925523869494</v>
+        <v>0.99557743229498485</v>
       </c>
       <c r="AB113">
-        <v>139.16365395725984</v>
+        <v>81.080407925277868</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21295,16 +21295,16 @@
         <v>743</v>
       </c>
       <c r="Y114" t="s">
-        <v>532</v>
+        <v>455</v>
       </c>
       <c r="Z114" t="s">
-        <v>777</v>
+        <v>865</v>
       </c>
       <c r="AA114">
-        <v>0.97244982574001193</v>
+        <v>0.99401156108202648</v>
       </c>
       <c r="AB114">
-        <v>505.08652809978111</v>
+        <v>109.78804682951412</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21369,16 +21369,16 @@
         <v>745</v>
       </c>
       <c r="Y115" t="s">
-        <v>489</v>
+        <v>529</v>
       </c>
       <c r="Z115" t="s">
         <v>866</v>
       </c>
       <c r="AA115">
-        <v>0.99172397756136033</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB115">
-        <v>151.72707804172813</v>
+        <v>637.85920701836687</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21443,16 +21443,16 @@
         <v>747</v>
       </c>
       <c r="Y116" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="Z116" t="s">
         <v>867</v>
       </c>
       <c r="AA116">
-        <v>0.99431900976645593</v>
+        <v>0.99344074878931121</v>
       </c>
       <c r="AB116">
-        <v>104.15148761497397</v>
+        <v>120.25293886262826</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21517,16 +21517,16 @@
         <v>749</v>
       </c>
       <c r="Y117" t="s">
-        <v>430</v>
+        <v>499</v>
       </c>
       <c r="Z117" t="s">
-        <v>868</v>
+        <v>785</v>
       </c>
       <c r="AA117">
-        <v>0.9946350729064154</v>
+        <v>0.99459650548991607</v>
       </c>
       <c r="AB117">
-        <v>98.356996715718111</v>
+        <v>99.064066018204684</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21591,16 +21591,16 @@
         <v>751</v>
       </c>
       <c r="Y118" t="s">
-        <v>517</v>
+        <v>490</v>
       </c>
       <c r="Z118" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AA118">
-        <v>0.99343259267015904</v>
+        <v>0.99655727877565281</v>
       </c>
       <c r="AB118">
-        <v>120.40246771375152</v>
+        <v>63.116555779697698</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21665,16 +21665,16 @@
         <v>753</v>
       </c>
       <c r="Y119" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="Z119" t="s">
-        <v>790</v>
+        <v>869</v>
       </c>
       <c r="AA119">
-        <v>0.9621480095608167</v>
+        <v>0.99221351039035977</v>
       </c>
       <c r="AB119">
-        <v>693.95315805169378</v>
+        <v>142.75230951007163</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21739,16 +21739,16 @@
         <v>755</v>
       </c>
       <c r="Y120" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="Z120" t="s">
         <v>870</v>
       </c>
       <c r="AA120">
-        <v>0.98916941127667946</v>
+        <v>0.99067174034238459</v>
       </c>
       <c r="AB120">
-        <v>198.56079326087576</v>
+        <v>171.01809372294977</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21813,16 +21813,16 @@
         <v>757</v>
       </c>
       <c r="Y121" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="Z121" t="s">
         <v>871</v>
       </c>
       <c r="AA121">
-        <v>0.97159134368321343</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB121">
-        <v>520.82536580775354</v>
+        <v>67.023399161603095</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21887,16 +21887,16 @@
         <v>759</v>
       </c>
       <c r="Y122" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="Z122" t="s">
         <v>872</v>
       </c>
       <c r="AA122">
-        <v>0.99359614530212825</v>
+        <v>0.98416341622871006</v>
       </c>
       <c r="AB122">
-        <v>117.40400279431638</v>
+        <v>290.33736914031488</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21961,16 +21961,16 @@
         <v>761</v>
       </c>
       <c r="Y123" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="Z123" t="s">
         <v>873</v>
       </c>
       <c r="AA123">
-        <v>0.99488082982009873</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB123">
-        <v>93.851453298190577</v>
+        <v>79.971304770340467</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -22035,16 +22035,16 @@
         <v>763</v>
       </c>
       <c r="Y124" t="s">
-        <v>513</v>
+        <v>432</v>
       </c>
       <c r="Z124" t="s">
         <v>874</v>
       </c>
       <c r="AA124">
-        <v>0.99557743229498485</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB124">
-        <v>81.080407925277868</v>
+        <v>81.000126667143434</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -22109,16 +22109,16 @@
         <v>765</v>
       </c>
       <c r="Y125" t="s">
-        <v>455</v>
+        <v>516</v>
       </c>
       <c r="Z125" t="s">
         <v>875</v>
       </c>
       <c r="AA125">
-        <v>0.99401156108202648</v>
+        <v>0.99390501557434718</v>
       </c>
       <c r="AB125">
-        <v>109.78804682951412</v>
+        <v>111.7413811369688</v>
       </c>
     </row>
   </sheetData>
@@ -22127,7 +22127,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1091732-646A-43DB-8CA2-0454984A53E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240DCCA3-74E6-4A1F-9AF5-527495DFCF3E}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22239,7 +22239,7 @@
         <v>1269</v>
       </c>
       <c r="K11" t="s">
-        <v>1062</v>
+        <v>1014</v>
       </c>
       <c r="L11">
         <v>4.7713910333636482</v>
@@ -22272,7 +22272,7 @@
         <v>1407</v>
       </c>
       <c r="X11" t="s">
-        <v>1223</v>
+        <v>1242</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -22307,7 +22307,7 @@
         <v>1271</v>
       </c>
       <c r="K12" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="L12">
         <v>12.404103898825962</v>
@@ -22340,7 +22340,7 @@
         <v>1409</v>
       </c>
       <c r="X12" t="s">
-        <v>1229</v>
+        <v>1210</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -22375,7 +22375,7 @@
         <v>1273</v>
       </c>
       <c r="K13" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="L13">
         <v>6.1276234637439133</v>
@@ -22408,7 +22408,7 @@
         <v>1411</v>
       </c>
       <c r="X13" t="s">
-        <v>1239</v>
+        <v>1261</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -22443,7 +22443,7 @@
         <v>1275</v>
       </c>
       <c r="K14" t="s">
-        <v>1126</v>
+        <v>1085</v>
       </c>
       <c r="L14">
         <v>0.85621181691755843</v>
@@ -22476,7 +22476,7 @@
         <v>1413</v>
       </c>
       <c r="X14" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -22511,7 +22511,7 @@
         <v>1277</v>
       </c>
       <c r="K15" t="s">
-        <v>1072</v>
+        <v>1142</v>
       </c>
       <c r="L15">
         <v>2.2628760328229185</v>
@@ -22544,7 +22544,7 @@
         <v>1415</v>
       </c>
       <c r="X15" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -22579,7 +22579,7 @@
         <v>1279</v>
       </c>
       <c r="K16" t="s">
-        <v>1086</v>
+        <v>1033</v>
       </c>
       <c r="L16">
         <v>0.43370118574988076</v>
@@ -22612,7 +22612,7 @@
         <v>1417</v>
       </c>
       <c r="X16" t="s">
-        <v>1265</v>
+        <v>1252</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -22647,7 +22647,7 @@
         <v>1281</v>
       </c>
       <c r="K17" t="s">
-        <v>1102</v>
+        <v>1073</v>
       </c>
       <c r="L17">
         <v>2.5150267058852811</v>
@@ -22680,7 +22680,7 @@
         <v>1419</v>
       </c>
       <c r="X17" t="s">
-        <v>1258</v>
+        <v>1240</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -22715,7 +22715,7 @@
         <v>1283</v>
       </c>
       <c r="K18" t="s">
-        <v>1071</v>
+        <v>1141</v>
       </c>
       <c r="L18">
         <v>2.885493974180005</v>
@@ -22748,7 +22748,7 @@
         <v>1421</v>
       </c>
       <c r="X18" t="s">
-        <v>1235</v>
+        <v>1214</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -22783,7 +22783,7 @@
         <v>1285</v>
       </c>
       <c r="K19" t="s">
-        <v>1056</v>
+        <v>1135</v>
       </c>
       <c r="L19">
         <v>10.563746678268352</v>
@@ -22816,7 +22816,7 @@
         <v>1423</v>
       </c>
       <c r="X19" t="s">
-        <v>1256</v>
+        <v>1238</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22851,7 +22851,7 @@
         <v>1287</v>
       </c>
       <c r="K20" t="s">
-        <v>1064</v>
+        <v>1016</v>
       </c>
       <c r="L20">
         <v>7.4816578037471135</v>
@@ -22884,7 +22884,7 @@
         <v>1425</v>
       </c>
       <c r="X20" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22919,7 +22919,7 @@
         <v>1289</v>
       </c>
       <c r="K21" t="s">
-        <v>1100</v>
+        <v>1071</v>
       </c>
       <c r="L21">
         <v>11.884376191048085</v>
@@ -22952,7 +22952,7 @@
         <v>1427</v>
       </c>
       <c r="X21" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22987,7 +22987,7 @@
         <v>1291</v>
       </c>
       <c r="K22" t="s">
-        <v>1014</v>
+        <v>1023</v>
       </c>
       <c r="L22">
         <v>12.246676572623375</v>
@@ -23020,7 +23020,7 @@
         <v>1429</v>
       </c>
       <c r="X22" t="s">
-        <v>1263</v>
+        <v>1250</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -23055,7 +23055,7 @@
         <v>1293</v>
       </c>
       <c r="K23" t="s">
-        <v>1084</v>
+        <v>1031</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -23088,7 +23088,7 @@
         <v>1431</v>
       </c>
       <c r="X23" t="s">
-        <v>1233</v>
+        <v>1248</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -23123,7 +23123,7 @@
         <v>1295</v>
       </c>
       <c r="K24" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -23156,7 +23156,7 @@
         <v>1433</v>
       </c>
       <c r="X24" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -23191,7 +23191,7 @@
         <v>1297</v>
       </c>
       <c r="K25" t="s">
-        <v>1058</v>
+        <v>1137</v>
       </c>
       <c r="L25">
         <v>11.221871479411517</v>
@@ -23224,7 +23224,7 @@
         <v>1435</v>
       </c>
       <c r="X25" t="s">
-        <v>1225</v>
+        <v>1244</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -23259,7 +23259,7 @@
         <v>1299</v>
       </c>
       <c r="K26" t="s">
-        <v>1104</v>
+        <v>1075</v>
       </c>
       <c r="L26">
         <v>1.6691823226567941</v>
@@ -23292,7 +23292,7 @@
         <v>1437</v>
       </c>
       <c r="X26" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23327,7 +23327,7 @@
         <v>1301</v>
       </c>
       <c r="K27" t="s">
-        <v>1136</v>
+        <v>1039</v>
       </c>
       <c r="L27">
         <v>3.7614311754340659</v>
@@ -23360,7 +23360,7 @@
         <v>1439</v>
       </c>
       <c r="X27" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -23395,7 +23395,7 @@
         <v>1303</v>
       </c>
       <c r="K28" t="s">
-        <v>1036</v>
+        <v>1055</v>
       </c>
       <c r="L28">
         <v>0.34625959029864795</v>
@@ -23463,7 +23463,7 @@
         <v>1305</v>
       </c>
       <c r="K29" t="s">
-        <v>1044</v>
+        <v>1065</v>
       </c>
       <c r="L29">
         <v>0.65440271382024695</v>
@@ -23496,7 +23496,7 @@
         <v>1443</v>
       </c>
       <c r="X29" t="s">
-        <v>1237</v>
+        <v>1216</v>
       </c>
       <c r="Y29">
         <v>8.8432499999999994</v>
@@ -23531,7 +23531,7 @@
         <v>1307</v>
       </c>
       <c r="K30" t="s">
-        <v>1088</v>
+        <v>1035</v>
       </c>
       <c r="L30">
         <v>2.2677057834637031</v>
@@ -23564,7 +23564,7 @@
         <v>1445</v>
       </c>
       <c r="X30" t="s">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="Y30">
         <v>3.4402499999999998</v>
@@ -23599,7 +23599,7 @@
         <v>1309</v>
       </c>
       <c r="K31" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="L31">
         <v>2.4836923620575391</v>
@@ -23632,7 +23632,7 @@
         <v>1447</v>
       </c>
       <c r="X31" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="Y31">
         <v>13.389749999999999</v>
@@ -23667,7 +23667,7 @@
         <v>1311</v>
       </c>
       <c r="K32" t="s">
-        <v>1092</v>
+        <v>1127</v>
       </c>
       <c r="L32">
         <v>4.0763322608214585</v>
@@ -23700,7 +23700,7 @@
         <v>1449</v>
       </c>
       <c r="X32" t="s">
-        <v>1255</v>
+        <v>1237</v>
       </c>
       <c r="Y32">
         <v>6.9757499999999997</v>
@@ -23735,7 +23735,7 @@
         <v>1313</v>
       </c>
       <c r="K33" t="s">
-        <v>1138</v>
+        <v>1041</v>
       </c>
       <c r="L33">
         <v>2.5731779960501728</v>
@@ -23768,7 +23768,7 @@
         <v>1451</v>
       </c>
       <c r="X33" t="s">
-        <v>1245</v>
+        <v>1231</v>
       </c>
       <c r="Y33">
         <v>38.154000000000003</v>
@@ -23803,7 +23803,7 @@
         <v>1315</v>
       </c>
       <c r="K34" t="s">
-        <v>1050</v>
+        <v>1059</v>
       </c>
       <c r="L34">
         <v>4.0509443596880574</v>
@@ -23836,7 +23836,7 @@
         <v>1453</v>
       </c>
       <c r="X34" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="Y34">
         <v>26.765999999999998</v>
@@ -23871,7 +23871,7 @@
         <v>1317</v>
       </c>
       <c r="K35" t="s">
-        <v>1022</v>
+        <v>1095</v>
       </c>
       <c r="L35">
         <v>2.4544193550494788</v>
@@ -23904,7 +23904,7 @@
         <v>1455</v>
       </c>
       <c r="X35" t="s">
-        <v>1253</v>
+        <v>1235</v>
       </c>
       <c r="Y35">
         <v>35.325000000000003</v>
@@ -23939,7 +23939,7 @@
         <v>1319</v>
       </c>
       <c r="K36" t="s">
-        <v>1080</v>
+        <v>1123</v>
       </c>
       <c r="L36">
         <v>0.35051099632091098</v>
@@ -23972,7 +23972,7 @@
         <v>1457</v>
       </c>
       <c r="X36" t="s">
-        <v>1241</v>
+        <v>1263</v>
       </c>
       <c r="Y36">
         <v>38.589750000000002</v>
@@ -24007,7 +24007,7 @@
         <v>1321</v>
       </c>
       <c r="K37" t="s">
-        <v>1069</v>
+        <v>1021</v>
       </c>
       <c r="L37">
         <v>5.5005105319204732</v>
@@ -24040,7 +24040,7 @@
         <v>1459</v>
       </c>
       <c r="X37" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="Y37">
         <v>28.707000000000001</v>
@@ -24075,7 +24075,7 @@
         <v>1323</v>
       </c>
       <c r="K38" t="s">
-        <v>1128</v>
+        <v>1087</v>
       </c>
       <c r="L38">
         <v>1.6757541426674882</v>
@@ -24108,7 +24108,7 @@
         <v>1461</v>
       </c>
       <c r="X38" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="Y38">
         <v>13.428000000000001</v>
@@ -24143,7 +24143,7 @@
         <v>1325</v>
       </c>
       <c r="K39" t="s">
-        <v>1026</v>
+        <v>1099</v>
       </c>
       <c r="L39">
         <v>0.39959553615654331</v>
@@ -24176,7 +24176,7 @@
         <v>1463</v>
       </c>
       <c r="X39" t="s">
-        <v>1231</v>
+        <v>1212</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24211,7 +24211,7 @@
         <v>1327</v>
       </c>
       <c r="K40" t="s">
-        <v>1016</v>
+        <v>1025</v>
       </c>
       <c r="L40">
         <v>1.7832075556426605</v>
@@ -24244,7 +24244,7 @@
         <v>1465</v>
       </c>
       <c r="X40" t="s">
-        <v>1243</v>
+        <v>1265</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24279,7 +24279,7 @@
         <v>1329</v>
       </c>
       <c r="K41" t="s">
-        <v>1082</v>
+        <v>1125</v>
       </c>
       <c r="L41">
         <v>23.427729543154012</v>
@@ -24312,7 +24312,7 @@
         <v>1467</v>
       </c>
       <c r="X41" t="s">
-        <v>1227</v>
+        <v>1246</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24347,7 +24347,7 @@
         <v>1331</v>
       </c>
       <c r="K42" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="L42">
         <v>1.4999429400795936</v>
@@ -24382,7 +24382,7 @@
         <v>1333</v>
       </c>
       <c r="K43" t="s">
-        <v>1054</v>
+        <v>1063</v>
       </c>
       <c r="L43">
         <v>55.863958629218203</v>
@@ -24417,7 +24417,7 @@
         <v>1335</v>
       </c>
       <c r="K44" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="L44">
         <v>17.068804920122925</v>
@@ -24452,7 +24452,7 @@
         <v>1337</v>
       </c>
       <c r="K45" t="s">
-        <v>1144</v>
+        <v>1047</v>
       </c>
       <c r="L45">
         <v>13.001084297219549</v>
@@ -24487,7 +24487,7 @@
         <v>1339</v>
       </c>
       <c r="K46" t="s">
-        <v>1030</v>
+        <v>1103</v>
       </c>
       <c r="L46">
         <v>3.0756142181007986</v>
@@ -24522,7 +24522,7 @@
         <v>1341</v>
       </c>
       <c r="K47" t="s">
-        <v>1042</v>
+        <v>1083</v>
       </c>
       <c r="L47">
         <v>17.749707845203876</v>
@@ -24557,7 +24557,7 @@
         <v>1343</v>
       </c>
       <c r="K48" t="s">
-        <v>1034</v>
+        <v>1053</v>
       </c>
       <c r="L48">
         <v>2.3372365278937242</v>
@@ -24592,7 +24592,7 @@
         <v>1345</v>
       </c>
       <c r="K49" t="s">
-        <v>1096</v>
+        <v>1131</v>
       </c>
       <c r="L49">
         <v>4.2648673086521249</v>
@@ -24627,7 +24627,7 @@
         <v>1347</v>
       </c>
       <c r="K50" t="s">
-        <v>1142</v>
+        <v>1045</v>
       </c>
       <c r="L50">
         <v>2.8571480649629004</v>
@@ -24662,7 +24662,7 @@
         <v>1349</v>
       </c>
       <c r="K51" t="s">
-        <v>1146</v>
+        <v>1049</v>
       </c>
       <c r="L51">
         <v>9.5169217846211289</v>
@@ -24697,7 +24697,7 @@
         <v>1351</v>
       </c>
       <c r="K52" t="s">
-        <v>1108</v>
+        <v>1079</v>
       </c>
       <c r="L52">
         <v>33.414563514376454</v>
@@ -24732,7 +24732,7 @@
         <v>1353</v>
       </c>
       <c r="K53" t="s">
-        <v>1134</v>
+        <v>1093</v>
       </c>
       <c r="L53">
         <v>18.904558868579112</v>
@@ -24767,7 +24767,7 @@
         <v>1355</v>
       </c>
       <c r="K54" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="L54">
         <v>15.478330347836801</v>
@@ -24802,7 +24802,7 @@
         <v>1357</v>
       </c>
       <c r="K55" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="L55">
         <v>14.176079891703212</v>
@@ -24837,7 +24837,7 @@
         <v>1359</v>
       </c>
       <c r="K56" t="s">
-        <v>1048</v>
+        <v>1069</v>
       </c>
       <c r="L56">
         <v>0.80973624203950822</v>
@@ -24872,7 +24872,7 @@
         <v>1361</v>
       </c>
       <c r="K57" t="s">
-        <v>1020</v>
+        <v>1029</v>
       </c>
       <c r="L57">
         <v>3.2067222321080848</v>
@@ -24907,7 +24907,7 @@
         <v>1363</v>
       </c>
       <c r="K58" t="s">
-        <v>1106</v>
+        <v>1077</v>
       </c>
       <c r="L58">
         <v>0.66271354737797783</v>
@@ -24942,7 +24942,7 @@
         <v>1365</v>
       </c>
       <c r="K59" t="s">
-        <v>1132</v>
+        <v>1091</v>
       </c>
       <c r="L59">
         <v>1.8183767824138508</v>
@@ -24977,7 +24977,7 @@
         <v>1367</v>
       </c>
       <c r="K60" t="s">
-        <v>1074</v>
+        <v>1144</v>
       </c>
       <c r="L60">
         <v>0.24904319237866104</v>
@@ -25012,7 +25012,7 @@
         <v>1369</v>
       </c>
       <c r="K61" t="s">
-        <v>1098</v>
+        <v>1133</v>
       </c>
       <c r="L61">
         <v>8.2047875916663029E-2</v>
@@ -25047,7 +25047,7 @@
         <v>1371</v>
       </c>
       <c r="K62" t="s">
-        <v>1140</v>
+        <v>1043</v>
       </c>
       <c r="L62">
         <v>11.861012832193515</v>
@@ -25082,7 +25082,7 @@
         <v>1373</v>
       </c>
       <c r="K63" t="s">
-        <v>1130</v>
+        <v>1089</v>
       </c>
       <c r="L63">
         <v>0.74143826937354373</v>
@@ -25117,7 +25117,7 @@
         <v>1375</v>
       </c>
       <c r="K64" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="L64">
         <v>5.5201095579611916</v>
@@ -25152,7 +25152,7 @@
         <v>1377</v>
       </c>
       <c r="K65" t="s">
-        <v>1090</v>
+        <v>1037</v>
       </c>
       <c r="L65">
         <v>6.8285247240880329</v>
@@ -25187,7 +25187,7 @@
         <v>1379</v>
       </c>
       <c r="K66" t="s">
-        <v>1060</v>
+        <v>1139</v>
       </c>
       <c r="L66">
         <v>14.065249575687433</v>
@@ -25222,7 +25222,7 @@
         <v>1381</v>
       </c>
       <c r="K67" t="s">
-        <v>1076</v>
+        <v>1146</v>
       </c>
       <c r="L67">
         <v>9.3799037679336319</v>
@@ -25257,7 +25257,7 @@
         <v>1383</v>
       </c>
       <c r="K68" t="s">
-        <v>1046</v>
+        <v>1067</v>
       </c>
       <c r="L68">
         <v>42.785830383290261</v>
@@ -25292,7 +25292,7 @@
         <v>1385</v>
       </c>
       <c r="K69" t="s">
-        <v>1028</v>
+        <v>1101</v>
       </c>
       <c r="L69">
         <v>7.8693705940085819</v>
@@ -25327,7 +25327,7 @@
         <v>1387</v>
       </c>
       <c r="K70" t="s">
-        <v>1078</v>
+        <v>1121</v>
       </c>
       <c r="L70">
         <v>19.787589902082505</v>
@@ -25362,7 +25362,7 @@
         <v>1389</v>
       </c>
       <c r="K71" t="s">
-        <v>1040</v>
+        <v>1081</v>
       </c>
       <c r="L71">
         <v>18.319832830101969</v>
@@ -25397,7 +25397,7 @@
         <v>1391</v>
       </c>
       <c r="K72" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="L72">
         <v>6.7551756478058005</v>
@@ -25432,7 +25432,7 @@
         <v>1393</v>
       </c>
       <c r="K73" t="s">
-        <v>1094</v>
+        <v>1129</v>
       </c>
       <c r="L73">
         <v>3.5275797249830152</v>
@@ -25467,7 +25467,7 @@
         <v>1395</v>
       </c>
       <c r="K74" t="s">
-        <v>1052</v>
+        <v>1061</v>
       </c>
       <c r="L74">
         <v>0.89663971235601181</v>
@@ -25502,7 +25502,7 @@
         <v>1397</v>
       </c>
       <c r="K75" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="L75">
         <v>5.9305458091691294</v>
@@ -25537,7 +25537,7 @@
         <v>1399</v>
       </c>
       <c r="K76" t="s">
-        <v>1067</v>
+        <v>1019</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25572,7 +25572,7 @@
         <v>1401</v>
       </c>
       <c r="K77" t="s">
-        <v>1024</v>
+        <v>1097</v>
       </c>
       <c r="L77">
         <v>0.5190595734350465</v>
@@ -25607,7 +25607,7 @@
         <v>1403</v>
       </c>
       <c r="K78" t="s">
-        <v>1038</v>
+        <v>1057</v>
       </c>
       <c r="L78">
         <v>0.29505146981926272</v>
@@ -25642,7 +25642,7 @@
         <v>1405</v>
       </c>
       <c r="K79" t="s">
-        <v>1065</v>
+        <v>1017</v>
       </c>
       <c r="L79">
         <v>0.28737649325389003</v>
@@ -25657,7 +25657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54750754-E0F4-474D-82A6-BF271D6393B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424E33F8-80C7-42DD-A00D-EDB9A0602F79}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27126,7 +27126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480870E1-D7C1-4A4E-8176-A3B520762C7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767C7947-3428-49D6-9477-F1BF57EE6E4D}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6440EE8D-B4B7-4804-9164-E93802DE4D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7CABA30-ECEF-4E2B-AE30-882F07B31A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1736,18 +1736,672 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_059</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 59</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_069</t>
   </si>
   <si>
@@ -1778,666 +2432,315 @@
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
+  </si>
+  <si>
     <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
   </si>
   <si>
@@ -2456,307 +2759,130 @@
     <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
   </si>
   <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
-  </si>
-  <si>
-    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
     <t>distr_wonelc_won_001</t>
@@ -2789,28 +2915,46 @@
     <t>connecting wind onshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -2837,6 +2981,162 @@
     <t>connecting wind onshore to buses in cluster 55</t>
   </si>
   <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_017</t>
   </si>
   <si>
@@ -2873,304 +3173,130 @@
     <t>connecting wind onshore to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR866-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
   </si>
   <si>
     <t>elc_won_001</t>
@@ -3200,28 +3326,43 @@
     <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
   </si>
   <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -3248,6 +3389,156 @@
     <t>e_BR220-500,e_BR185-500</t>
   </si>
   <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
+  </si>
+  <si>
     <t>elc_won_017</t>
   </si>
   <si>
@@ -3284,295 +3575,118 @@
     <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
   </si>
   <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR866-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_002</t>
@@ -3587,6 +3701,24 @@
     <t>connecting wind offshore to buses in cluster 29</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
@@ -3599,34 +3731,22 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wofelc_wof_016</t>
@@ -3641,124 +3761,112 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w466973262-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR37-500,e_BR42-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
   </si>
   <si>
     <t>elc_wof_002</t>
@@ -3773,6 +3881,24 @@
     <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
   </si>
   <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
@@ -3785,31 +3911,22 @@
     <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
   </si>
   <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR37-500,e_BR42-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
   </si>
   <si>
     <t>elc_wof_016</t>
@@ -3819,123 +3936,6 @@
   </si>
   <si>
     <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9835,7 +9835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D9EE51-467A-4E69-9233-24C1C5B04268}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D784C0C-E48D-4599-95B4-E9DEF55BCF33}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10073,16 +10073,16 @@
         <v>535</v>
       </c>
       <c r="Y11" t="s">
-        <v>476</v>
+        <v>526</v>
       </c>
       <c r="Z11" t="s">
         <v>769</v>
       </c>
       <c r="AA11">
-        <v>0.99295369446862825</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB11">
-        <v>129.18226807514921</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD11" t="s">
         <v>534</v>
@@ -10115,10 +10115,10 @@
         <v>1015</v>
       </c>
       <c r="AO11">
-        <v>0.99244513691456471</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP11">
-        <v>138.50582323297994</v>
+        <v>96.528578181196991</v>
       </c>
       <c r="AR11" t="s">
         <v>534</v>
@@ -10151,10 +10151,10 @@
         <v>1211</v>
       </c>
       <c r="BC11">
-        <v>0.99834679070917032</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD11">
-        <v>30.308836998544216</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10219,16 +10219,16 @@
         <v>539</v>
       </c>
       <c r="Y12" t="s">
-        <v>486</v>
+        <v>530</v>
       </c>
       <c r="Z12" t="s">
         <v>770</v>
       </c>
       <c r="AA12">
-        <v>0.98571261124433651</v>
+        <v>0.95679935803281835</v>
       </c>
       <c r="AB12">
-        <v>261.93546052049794</v>
+        <v>792.01176939833033</v>
       </c>
       <c r="AD12" t="s">
         <v>534</v>
@@ -10258,13 +10258,13 @@
         <v>1016</v>
       </c>
       <c r="AN12" t="s">
-        <v>853</v>
+        <v>1017</v>
       </c>
       <c r="AO12">
-        <v>0.97416725971121887</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP12">
-        <v>473.60023862765331</v>
+        <v>49.543726018799653</v>
       </c>
       <c r="AR12" t="s">
         <v>534</v>
@@ -10297,10 +10297,10 @@
         <v>1213</v>
       </c>
       <c r="BC12">
-        <v>0.99401640271965719</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD12">
-        <v>109.69928347295183</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10365,16 +10365,16 @@
         <v>541</v>
       </c>
       <c r="Y13" t="s">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="Z13" t="s">
         <v>771</v>
       </c>
       <c r="AA13">
-        <v>0.9849019911873127</v>
+        <v>0.98761622532712257</v>
       </c>
       <c r="AB13">
-        <v>276.79682823259958</v>
+        <v>227.03586900275366</v>
       </c>
       <c r="AD13" t="s">
         <v>534</v>
@@ -10401,16 +10401,16 @@
         <v>880</v>
       </c>
       <c r="AM13" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="AN13" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AO13">
-        <v>0.99760255773158468</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP13">
-        <v>43.953108254279897</v>
+        <v>58.751500348127372</v>
       </c>
       <c r="AR13" t="s">
         <v>534</v>
@@ -10443,10 +10443,10 @@
         <v>1215</v>
       </c>
       <c r="BC13">
-        <v>0.9959052853503485</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD13">
-        <v>75.06976857694373</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10511,16 +10511,16 @@
         <v>543</v>
       </c>
       <c r="Y14" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="Z14" t="s">
         <v>772</v>
       </c>
       <c r="AA14">
-        <v>0.99157679714615166</v>
+        <v>0.99003402112096806</v>
       </c>
       <c r="AB14">
-        <v>154.42538565388551</v>
+        <v>182.70961278225187</v>
       </c>
       <c r="AD14" t="s">
         <v>534</v>
@@ -10547,16 +10547,16 @@
         <v>882</v>
       </c>
       <c r="AM14" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AN14" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AO14">
-        <v>0.99352359657507616</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP14">
-        <v>118.7340627902709</v>
+        <v>132.99731300951822</v>
       </c>
       <c r="AR14" t="s">
         <v>534</v>
@@ -10589,10 +10589,10 @@
         <v>1217</v>
       </c>
       <c r="BC14">
-        <v>0.99563011519444145</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD14">
-        <v>80.114554768572972</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10657,16 +10657,16 @@
         <v>545</v>
       </c>
       <c r="Y15" t="s">
-        <v>515</v>
+        <v>459</v>
       </c>
       <c r="Z15" t="s">
         <v>773</v>
       </c>
       <c r="AA15">
-        <v>0.99619387577842089</v>
+        <v>0.99466062705491098</v>
       </c>
       <c r="AB15">
-        <v>69.778944062284495</v>
+        <v>97.888503993298116</v>
       </c>
       <c r="AD15" t="s">
         <v>534</v>
@@ -10693,16 +10693,16 @@
         <v>884</v>
       </c>
       <c r="AM15" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AN15" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="AO15">
-        <v>0.99433447571906541</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP15">
-        <v>103.86794515046822</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR15" t="s">
         <v>534</v>
@@ -10735,10 +10735,10 @@
         <v>1219</v>
       </c>
       <c r="BC15">
-        <v>0.96863461872110523</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD15">
-        <v>575.0319901130714</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10803,16 +10803,16 @@
         <v>547</v>
       </c>
       <c r="Y16" t="s">
-        <v>457</v>
+        <v>508</v>
       </c>
       <c r="Z16" t="s">
         <v>774</v>
       </c>
       <c r="AA16">
-        <v>0.99497915241892609</v>
+        <v>0.9944598150968682</v>
       </c>
       <c r="AB16">
-        <v>92.048872319688599</v>
+        <v>101.5700565574154</v>
       </c>
       <c r="AD16" t="s">
         <v>534</v>
@@ -10839,16 +10839,16 @@
         <v>886</v>
       </c>
       <c r="AM16" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AN16" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AO16">
-        <v>0.99473480482648013</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP16">
-        <v>96.528578181196991</v>
+        <v>83.589016951479763</v>
       </c>
       <c r="AR16" t="s">
         <v>534</v>
@@ -10878,13 +10878,13 @@
         <v>1220</v>
       </c>
       <c r="BB16" t="s">
-        <v>1145</v>
+        <v>1221</v>
       </c>
       <c r="BC16">
-        <v>0.99098965084511315</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD16">
-        <v>165.18973450625904</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10949,16 +10949,16 @@
         <v>549</v>
       </c>
       <c r="Y17" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="Z17" t="s">
         <v>775</v>
       </c>
       <c r="AA17">
-        <v>0.98150124893892388</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB17">
-        <v>339.14376945306287</v>
+        <v>92.674656500591539</v>
       </c>
       <c r="AD17" t="s">
         <v>534</v>
@@ -10985,16 +10985,16 @@
         <v>888</v>
       </c>
       <c r="AM17" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="AN17" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AO17">
-        <v>0.99729761494442914</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP17">
-        <v>49.543726018799653</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR17" t="s">
         <v>534</v>
@@ -11021,16 +11021,16 @@
         <v>1160</v>
       </c>
       <c r="BA17" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="BB17" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="BC17">
-        <v>0.99053278045305837</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD17">
-        <v>173.56569169392964</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11095,16 +11095,16 @@
         <v>551</v>
       </c>
       <c r="Y18" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="Z18" t="s">
         <v>776</v>
       </c>
       <c r="AA18">
-        <v>0.99523081353776888</v>
+        <v>0.99438812565699364</v>
       </c>
       <c r="AB18">
-        <v>87.435085140903482</v>
+        <v>102.88436295511657</v>
       </c>
       <c r="AD18" t="s">
         <v>534</v>
@@ -11131,16 +11131,16 @@
         <v>890</v>
       </c>
       <c r="AM18" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="AN18" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="AO18">
-        <v>0.996795372708284</v>
+        <v>0.99677419959133018</v>
       </c>
       <c r="AP18">
-        <v>58.751500348127372</v>
+        <v>59.139674158947656</v>
       </c>
       <c r="AR18" t="s">
         <v>534</v>
@@ -11167,16 +11167,16 @@
         <v>1162</v>
       </c>
       <c r="BA18" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="BB18" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="BC18">
-        <v>0.98488330873784669</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD18">
-        <v>277.13933980614473</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11241,16 +11241,16 @@
         <v>553</v>
       </c>
       <c r="Y19" t="s">
-        <v>442</v>
+        <v>523</v>
       </c>
       <c r="Z19" t="s">
         <v>777</v>
       </c>
       <c r="AA19">
-        <v>0.9916432660493133</v>
+        <v>0.99643191679577148</v>
       </c>
       <c r="AB19">
-        <v>153.20678909592235</v>
+        <v>65.414858744189985</v>
       </c>
       <c r="AD19" t="s">
         <v>534</v>
@@ -11277,16 +11277,16 @@
         <v>892</v>
       </c>
       <c r="AM19" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="AN19" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AO19">
-        <v>0.99274560110857168</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP19">
-        <v>132.99731300951822</v>
+        <v>42.750927651225993</v>
       </c>
       <c r="AR19" t="s">
         <v>534</v>
@@ -11313,16 +11313,16 @@
         <v>1164</v>
       </c>
       <c r="BA19" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="BB19" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="BC19">
-        <v>0.99526086651282741</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD19">
-        <v>86.884113931497708</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11387,16 +11387,16 @@
         <v>555</v>
       </c>
       <c r="Y20" t="s">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="Z20" t="s">
         <v>778</v>
       </c>
       <c r="AA20">
-        <v>0.99570118415007625</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB20">
-        <v>78.81162391526847</v>
+        <v>64.274570700309781</v>
       </c>
       <c r="AD20" t="s">
         <v>534</v>
@@ -11423,16 +11423,16 @@
         <v>894</v>
       </c>
       <c r="AM20" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AN20" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AO20">
-        <v>0.99403730604060547</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP20">
-        <v>109.31605592223302</v>
+        <v>43.95454940357709</v>
       </c>
       <c r="AR20" t="s">
         <v>534</v>
@@ -11459,16 +11459,16 @@
         <v>1166</v>
       </c>
       <c r="BA20" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="BB20" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="BC20">
-        <v>0.95713629889852414</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD20">
-        <v>785.83452019372396</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11533,16 +11533,16 @@
         <v>557</v>
       </c>
       <c r="Y21" t="s">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="Z21" t="s">
         <v>779</v>
       </c>
       <c r="AA21">
-        <v>0.99691903985105013</v>
+        <v>0.97907421743006762</v>
       </c>
       <c r="AB21">
-        <v>56.484269397415083</v>
+        <v>383.63934711542669</v>
       </c>
       <c r="AD21" t="s">
         <v>534</v>
@@ -11569,16 +11569,16 @@
         <v>896</v>
       </c>
       <c r="AM21" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="AN21" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AO21">
-        <v>0.99105808324017197</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP21">
-        <v>163.93514059684662</v>
+        <v>121.72426728897108</v>
       </c>
       <c r="AR21" t="s">
         <v>534</v>
@@ -11605,16 +11605,16 @@
         <v>1168</v>
       </c>
       <c r="BA21" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="BB21" t="s">
-        <v>1230</v>
+        <v>1075</v>
       </c>
       <c r="BC21">
-        <v>0.98806872821788805</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD21">
-        <v>218.73998267205184</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11679,16 +11679,16 @@
         <v>559</v>
       </c>
       <c r="Y22" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="Z22" t="s">
         <v>780</v>
       </c>
       <c r="AA22">
-        <v>0.98563153879963317</v>
+        <v>0.99558768376711515</v>
       </c>
       <c r="AB22">
-        <v>263.42178867339101</v>
+        <v>80.892464269556413</v>
       </c>
       <c r="AD22" t="s">
         <v>534</v>
@@ -11715,16 +11715,16 @@
         <v>898</v>
       </c>
       <c r="AM22" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AN22" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AO22">
-        <v>0.9974675531234084</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP22">
-        <v>46.428192737512276</v>
+        <v>44.092000370450322</v>
       </c>
       <c r="AR22" t="s">
         <v>534</v>
@@ -11757,10 +11757,10 @@
         <v>1232</v>
       </c>
       <c r="BC22">
-        <v>0.98574436213546524</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD22">
-        <v>261.35336084980423</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11825,16 +11825,16 @@
         <v>561</v>
       </c>
       <c r="Y23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z23" t="s">
         <v>781</v>
       </c>
       <c r="AA23">
-        <v>0.99529226044395613</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB23">
-        <v>86.308558527470979</v>
+        <v>123.82892298254488</v>
       </c>
       <c r="AD23" t="s">
         <v>534</v>
@@ -11861,16 +11861,16 @@
         <v>900</v>
       </c>
       <c r="AM23" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AN23" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AO23">
-        <v>0.99534886842510228</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP23">
-        <v>85.270745539791065</v>
+        <v>82.249649925934918</v>
       </c>
       <c r="AR23" t="s">
         <v>534</v>
@@ -11903,10 +11903,10 @@
         <v>1234</v>
       </c>
       <c r="BC23">
-        <v>0.98163861082146986</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD23">
-        <v>336.62546827305243</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11971,16 +11971,16 @@
         <v>563</v>
       </c>
       <c r="Y24" t="s">
-        <v>511</v>
+        <v>464</v>
       </c>
       <c r="Z24" t="s">
         <v>782</v>
       </c>
       <c r="AA24">
-        <v>0.99443562760718263</v>
+        <v>0.99419165427276146</v>
       </c>
       <c r="AB24">
-        <v>102.01349386831856</v>
+        <v>106.48633833270691</v>
       </c>
       <c r="AD24" t="s">
         <v>534</v>
@@ -12007,16 +12007,16 @@
         <v>902</v>
       </c>
       <c r="AM24" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AN24" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="AO24">
-        <v>0.99567626923235475</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP24">
-        <v>79.268397406829976</v>
+        <v>81.597153048545437</v>
       </c>
       <c r="AR24" t="s">
         <v>534</v>
@@ -12049,10 +12049,10 @@
         <v>1236</v>
       </c>
       <c r="BC24">
-        <v>0.9933934749176847</v>
+        <v>0.99526086651282741</v>
       </c>
       <c r="BD24">
-        <v>121.11962650911367</v>
+        <v>86.884113931497708</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12117,16 +12117,16 @@
         <v>565</v>
       </c>
       <c r="Y25" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="Z25" t="s">
         <v>783</v>
       </c>
       <c r="AA25">
-        <v>0.96942910386940295</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB25">
-        <v>560.46642906094564</v>
+        <v>146.8618143486346</v>
       </c>
       <c r="AD25" t="s">
         <v>534</v>
@@ -12153,16 +12153,16 @@
         <v>904</v>
       </c>
       <c r="AM25" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AN25" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AO25">
-        <v>0.99762284649610655</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP25">
-        <v>43.581147571379539</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR25" t="s">
         <v>534</v>
@@ -12192,13 +12192,13 @@
         <v>1237</v>
       </c>
       <c r="BB25" t="s">
-        <v>1078</v>
+        <v>1238</v>
       </c>
       <c r="BC25">
-        <v>0.99418931598784899</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD25">
-        <v>106.52920688943452</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12263,16 +12263,16 @@
         <v>567</v>
       </c>
       <c r="Y26" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="Z26" t="s">
         <v>784</v>
       </c>
       <c r="AA26">
-        <v>0.99726809134187266</v>
+        <v>0.96238190390083644</v>
       </c>
       <c r="AB26">
-        <v>50.0849920656675</v>
+        <v>689.665095151331</v>
       </c>
       <c r="AD26" t="s">
         <v>534</v>
@@ -12299,16 +12299,16 @@
         <v>906</v>
       </c>
       <c r="AM26" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AN26" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="AO26">
-        <v>0.99175391794306234</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP26">
-        <v>151.17817104385733</v>
+        <v>43.412641259119624</v>
       </c>
       <c r="AR26" t="s">
         <v>534</v>
@@ -12335,16 +12335,16 @@
         <v>1178</v>
       </c>
       <c r="BA26" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="BB26" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="BC26">
-        <v>0.99232494426983575</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD26">
-        <v>140.70935505301131</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12409,16 +12409,16 @@
         <v>569</v>
       </c>
       <c r="Y27" t="s">
-        <v>481</v>
+        <v>528</v>
       </c>
       <c r="Z27" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="AA27">
-        <v>0.97962408753770291</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB27">
-        <v>373.55839514211272</v>
+        <v>675.25867642804383</v>
       </c>
       <c r="AD27" t="s">
         <v>534</v>
@@ -12445,16 +12445,16 @@
         <v>908</v>
       </c>
       <c r="AM27" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AN27" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AO27">
-        <v>0.99688290256322298</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP27">
-        <v>57.146786340912868</v>
+        <v>57.905423216266421</v>
       </c>
       <c r="AR27" t="s">
         <v>534</v>
@@ -12481,16 +12481,16 @@
         <v>1180</v>
       </c>
       <c r="BA27" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="BB27" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="BC27">
-        <v>0.98775115723917273</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD27">
-        <v>224.56211728183334</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12555,16 +12555,16 @@
         <v>571</v>
       </c>
       <c r="Y28" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="Z28" t="s">
         <v>785</v>
       </c>
       <c r="AA28">
-        <v>0.99098167665935155</v>
+        <v>0.9951089264264793</v>
       </c>
       <c r="AB28">
-        <v>165.33592791188894</v>
+        <v>89.669682181211982</v>
       </c>
       <c r="AD28" t="s">
         <v>534</v>
@@ -12591,16 +12591,16 @@
         <v>910</v>
       </c>
       <c r="AM28" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AN28" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="AO28">
-        <v>0.99488275259079373</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP28">
-        <v>93.81620250211445</v>
+        <v>85.716830221163534</v>
       </c>
       <c r="AR28" t="s">
         <v>534</v>
@@ -12627,16 +12627,16 @@
         <v>1182</v>
       </c>
       <c r="BA28" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="BB28" t="s">
-        <v>1243</v>
+        <v>1099</v>
       </c>
       <c r="BC28">
-        <v>0.98890025255868685</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD28">
-        <v>203.49536975740753</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12701,16 +12701,16 @@
         <v>573</v>
       </c>
       <c r="Y29" t="s">
-        <v>503</v>
+        <v>434</v>
       </c>
       <c r="Z29" t="s">
         <v>786</v>
       </c>
       <c r="AA29">
-        <v>0.98485684158558628</v>
+        <v>0.98666519734623237</v>
       </c>
       <c r="AB29">
-        <v>277.62457093091871</v>
+        <v>244.47138198573927</v>
       </c>
       <c r="AD29" t="s">
         <v>534</v>
@@ -12737,16 +12737,16 @@
         <v>912</v>
       </c>
       <c r="AM29" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AN29" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="AO29">
-        <v>0.99663220850609069</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP29">
-        <v>61.742844055003644</v>
+        <v>74.464817689622748</v>
       </c>
       <c r="AR29" t="s">
         <v>534</v>
@@ -12779,10 +12779,10 @@
         <v>1245</v>
       </c>
       <c r="BC29">
-        <v>0.99481196273061234</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD29">
-        <v>95.114016605440895</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12847,16 +12847,16 @@
         <v>575</v>
       </c>
       <c r="Y30" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="Z30" t="s">
         <v>787</v>
       </c>
       <c r="AA30">
-        <v>0.98211145389932475</v>
+        <v>0.99750070245826261</v>
       </c>
       <c r="AB30">
-        <v>327.95667851237977</v>
+        <v>45.820454931853</v>
       </c>
       <c r="AD30" t="s">
         <v>534</v>
@@ -12883,16 +12883,16 @@
         <v>914</v>
       </c>
       <c r="AM30" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AN30" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AO30">
-        <v>0.98134982200735632</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP30">
-        <v>341.91992986513412</v>
+        <v>80.747827133859133</v>
       </c>
       <c r="AR30" t="s">
         <v>534</v>
@@ -12925,10 +12925,10 @@
         <v>1247</v>
       </c>
       <c r="BC30">
-        <v>0.99374755699184159</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD30">
-        <v>114.62812181623703</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12993,16 +12993,16 @@
         <v>577</v>
       </c>
       <c r="Y31" t="s">
-        <v>467</v>
+        <v>422</v>
       </c>
       <c r="Z31" t="s">
         <v>788</v>
       </c>
       <c r="AA31">
-        <v>0.99654205356515035</v>
+        <v>0.99395341117186964</v>
       </c>
       <c r="AB31">
-        <v>63.395684638909763</v>
+        <v>110.85412851572337</v>
       </c>
       <c r="AD31" t="s">
         <v>534</v>
@@ -13029,16 +13029,16 @@
         <v>916</v>
       </c>
       <c r="AM31" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AN31" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="AO31">
-        <v>0.98589595763902149</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP31">
-        <v>258.57410995127316</v>
+        <v>60.189444792275019</v>
       </c>
       <c r="AR31" t="s">
         <v>534</v>
@@ -13071,10 +13071,10 @@
         <v>1249</v>
       </c>
       <c r="BC31">
-        <v>0.98691003029105739</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD31">
-        <v>239.98277799728109</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13139,16 +13139,16 @@
         <v>579</v>
       </c>
       <c r="Y32" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="Z32" t="s">
         <v>789</v>
       </c>
       <c r="AA32">
-        <v>0.99504817442297822</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB32">
-        <v>90.78346891206678</v>
+        <v>307.49900901993823</v>
       </c>
       <c r="AD32" t="s">
         <v>534</v>
@@ -13175,16 +13175,16 @@
         <v>918</v>
       </c>
       <c r="AM32" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="AN32" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AO32">
-        <v>0.99776894175014486</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP32">
-        <v>40.90273458067751</v>
+        <v>138.50582323297994</v>
       </c>
       <c r="AR32" t="s">
         <v>534</v>
@@ -13217,10 +13217,10 @@
         <v>1251</v>
       </c>
       <c r="BC32">
-        <v>0.98946506962487613</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD32">
-        <v>193.14039021060518</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13285,16 +13285,16 @@
         <v>581</v>
       </c>
       <c r="Y33" t="s">
-        <v>507</v>
+        <v>437</v>
       </c>
       <c r="Z33" t="s">
         <v>790</v>
       </c>
       <c r="AA33">
-        <v>0.99470247457730832</v>
+        <v>0.9974199781412052</v>
       </c>
       <c r="AB33">
-        <v>97.121299416014665</v>
+        <v>47.300400744571718</v>
       </c>
       <c r="AD33" t="s">
         <v>534</v>
@@ -13321,16 +13321,16 @@
         <v>920</v>
       </c>
       <c r="AM33" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AN33" t="s">
-        <v>1058</v>
+        <v>842</v>
       </c>
       <c r="AO33">
-        <v>0.9959346869215373</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP33">
-        <v>74.530739771815789</v>
+        <v>473.60023862765331</v>
       </c>
       <c r="AR33" t="s">
         <v>534</v>
@@ -13363,10 +13363,10 @@
         <v>1253</v>
       </c>
       <c r="BC33">
-        <v>0.99314574070258299</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD33">
-        <v>125.66142045264445</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13431,16 +13431,16 @@
         <v>583</v>
       </c>
       <c r="Y34" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="Z34" t="s">
         <v>791</v>
       </c>
       <c r="AA34">
-        <v>0.99549782242326257</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB34">
-        <v>82.539922240185263</v>
+        <v>121.57987025257442</v>
       </c>
       <c r="AD34" t="s">
         <v>534</v>
@@ -13473,10 +13473,10 @@
         <v>1060</v>
       </c>
       <c r="AO34">
-        <v>0.99684152237002188</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP34">
-        <v>57.905423216266421</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR34" t="s">
         <v>534</v>
@@ -13509,10 +13509,10 @@
         <v>1255</v>
       </c>
       <c r="BC34">
-        <v>0.99032129621526932</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD34">
-        <v>177.44290272006148</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13577,16 +13577,16 @@
         <v>585</v>
       </c>
       <c r="Y35" t="s">
-        <v>527</v>
+        <v>443</v>
       </c>
       <c r="Z35" t="s">
         <v>792</v>
       </c>
       <c r="AA35">
-        <v>0.95261480241426988</v>
+        <v>0.99379477670057537</v>
       </c>
       <c r="AB35">
-        <v>868.72862240505196</v>
+        <v>113.7624271561186</v>
       </c>
       <c r="AD35" t="s">
         <v>534</v>
@@ -13619,10 +13619,10 @@
         <v>1062</v>
       </c>
       <c r="AO35">
-        <v>0.99532453653339104</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP35">
-        <v>85.716830221163534</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR35" t="s">
         <v>534</v>
@@ -13655,10 +13655,10 @@
         <v>1257</v>
       </c>
       <c r="BC35">
-        <v>0.99420451954813838</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD35">
-        <v>106.25047495079694</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13723,16 +13723,16 @@
         <v>587</v>
       </c>
       <c r="Y36" t="s">
-        <v>531</v>
+        <v>454</v>
       </c>
       <c r="Z36" t="s">
         <v>793</v>
       </c>
       <c r="AA36">
-        <v>0.97404342257401955</v>
+        <v>0.9961866142254362</v>
       </c>
       <c r="AB36">
-        <v>475.8705861429753</v>
+        <v>69.91207253366963</v>
       </c>
       <c r="AD36" t="s">
         <v>534</v>
@@ -13765,10 +13765,10 @@
         <v>1064</v>
       </c>
       <c r="AO36">
-        <v>0.99593828267147511</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP36">
-        <v>74.464817689622748</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR36" t="s">
         <v>534</v>
@@ -13798,13 +13798,13 @@
         <v>1258</v>
       </c>
       <c r="BB36" t="s">
-        <v>1230</v>
+        <v>1259</v>
       </c>
       <c r="BC36">
-        <v>0.99203097418485064</v>
+        <v>0.99563011519444145</v>
       </c>
       <c r="BD36">
-        <v>146.09880661107059</v>
+        <v>80.114554768572972</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13869,16 +13869,16 @@
         <v>589</v>
       </c>
       <c r="Y37" t="s">
-        <v>420</v>
+        <v>491</v>
       </c>
       <c r="Z37" t="s">
         <v>794</v>
       </c>
       <c r="AA37">
-        <v>0.98762421667584677</v>
+        <v>0.99240925523869494</v>
       </c>
       <c r="AB37">
-        <v>226.88936094280919</v>
+        <v>139.16365395725984</v>
       </c>
       <c r="AD37" t="s">
         <v>534</v>
@@ -13911,10 +13911,10 @@
         <v>1066</v>
       </c>
       <c r="AO37">
-        <v>0.99503039970536677</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP37">
-        <v>91.109338734942796</v>
+        <v>546.30069964051177</v>
       </c>
       <c r="AR37" t="s">
         <v>534</v>
@@ -13941,16 +13941,16 @@
         <v>1200</v>
       </c>
       <c r="BA37" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="BB37" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="BC37">
-        <v>0.97821242976023937</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD37">
-        <v>399.43878772894504</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14015,16 +14015,16 @@
         <v>591</v>
       </c>
       <c r="Y38" t="s">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="Z38" t="s">
-        <v>795</v>
+        <v>769</v>
       </c>
       <c r="AA38">
-        <v>0.98775140142897844</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB38">
-        <v>224.55764046872929</v>
+        <v>505.08652809978111</v>
       </c>
       <c r="AD38" t="s">
         <v>534</v>
@@ -14057,10 +14057,10 @@
         <v>1068</v>
       </c>
       <c r="AO38">
-        <v>0.99544059907537386</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP38">
-        <v>83.589016951479763</v>
+        <v>56.159977027506663</v>
       </c>
       <c r="AR38" t="s">
         <v>534</v>
@@ -14087,16 +14087,16 @@
         <v>1202</v>
       </c>
       <c r="BA38" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="BB38" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="BC38">
-        <v>0.99054926914187857</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD38">
-        <v>173.26339906555947</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14161,16 +14161,16 @@
         <v>593</v>
       </c>
       <c r="Y39" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="Z39" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA39">
-        <v>0.99647006537565563</v>
+        <v>0.99172397756136033</v>
       </c>
       <c r="AB39">
-        <v>64.715468112981057</v>
+        <v>151.72707804172813</v>
       </c>
       <c r="AD39" t="s">
         <v>534</v>
@@ -14203,10 +14203,10 @@
         <v>1070</v>
       </c>
       <c r="AO39">
-        <v>0.98829989485605374</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP39">
-        <v>214.50192763901472</v>
+        <v>95.557874766001078</v>
       </c>
       <c r="AR39" t="s">
         <v>534</v>
@@ -14233,16 +14233,16 @@
         <v>1204</v>
       </c>
       <c r="BA39" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="BB39" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="BC39">
-        <v>0.98027195861782945</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD39">
-        <v>361.68075867312689</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14307,16 +14307,16 @@
         <v>595</v>
       </c>
       <c r="Y40" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="Z40" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA40">
-        <v>0.96480371616361149</v>
+        <v>0.99431900976645593</v>
       </c>
       <c r="AB40">
-        <v>645.26520366712316</v>
+        <v>104.15148761497397</v>
       </c>
       <c r="AD40" t="s">
         <v>534</v>
@@ -14346,13 +14346,13 @@
         <v>1071</v>
       </c>
       <c r="AN40" t="s">
-        <v>1072</v>
+        <v>838</v>
       </c>
       <c r="AO40">
-        <v>0.99424679200457</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP40">
-        <v>105.47547991621673</v>
+        <v>243.0827225935364</v>
       </c>
       <c r="AR40" t="s">
         <v>534</v>
@@ -14379,16 +14379,16 @@
         <v>1206</v>
       </c>
       <c r="BA40" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="BB40" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="BC40">
-        <v>0.98125520899414764</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD40">
-        <v>343.65450177395917</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14453,16 +14453,16 @@
         <v>597</v>
       </c>
       <c r="Y41" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="Z41" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AA41">
-        <v>0.99267004448650609</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB41">
-        <v>134.38251774738842</v>
+        <v>98.356996715718111</v>
       </c>
       <c r="AD41" t="s">
         <v>534</v>
@@ -14489,16 +14489,16 @@
         <v>936</v>
       </c>
       <c r="AM41" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AN41" t="s">
         <v>1073</v>
       </c>
-      <c r="AN41" t="s">
-        <v>1074</v>
-      </c>
       <c r="AO41">
-        <v>0.98934663566509429</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP41">
-        <v>195.31167947327185</v>
+        <v>283.70480651649393</v>
       </c>
       <c r="AR41" t="s">
         <v>534</v>
@@ -14525,16 +14525,16 @@
         <v>1208</v>
       </c>
       <c r="BA41" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="BB41" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="BC41">
-        <v>0.99665799830099</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD41">
-        <v>61.270031148516708</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14599,16 +14599,16 @@
         <v>599</v>
       </c>
       <c r="Y42" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Z42" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AA42">
-        <v>0.9948848527457459</v>
+        <v>0.99343259267015904</v>
       </c>
       <c r="AB42">
-        <v>93.777699661325343</v>
+        <v>120.40246771375152</v>
       </c>
       <c r="AD42" t="s">
         <v>534</v>
@@ -14635,16 +14635,16 @@
         <v>938</v>
       </c>
       <c r="AM42" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AN42" t="s">
         <v>1075</v>
       </c>
-      <c r="AN42" t="s">
-        <v>1076</v>
-      </c>
       <c r="AO42">
-        <v>0.99499049355022928</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP42">
-        <v>91.840951579129481</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14709,16 +14709,16 @@
         <v>601</v>
       </c>
       <c r="Y43" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="Z43" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AA43">
-        <v>0.9922030648239526</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB43">
-        <v>142.94381156086857</v>
+        <v>868.72862240505196</v>
       </c>
       <c r="AD43" t="s">
         <v>534</v>
@@ -14745,16 +14745,16 @@
         <v>940</v>
       </c>
       <c r="AM43" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AN43" t="s">
         <v>1077</v>
       </c>
-      <c r="AN43" t="s">
-        <v>1078</v>
-      </c>
       <c r="AO43">
-        <v>0.99729205446773184</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP43">
-        <v>49.645668091582088</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14819,16 +14819,16 @@
         <v>603</v>
       </c>
       <c r="Y44" t="s">
-        <v>471</v>
+        <v>531</v>
       </c>
       <c r="Z44" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="AA44">
-        <v>0.97432735774114165</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB44">
-        <v>470.66510807906917</v>
+        <v>475.8705861429753</v>
       </c>
       <c r="AD44" t="s">
         <v>534</v>
@@ -14855,16 +14855,16 @@
         <v>942</v>
       </c>
       <c r="AM44" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AN44" t="s">
         <v>1079</v>
       </c>
-      <c r="AN44" t="s">
-        <v>1080</v>
-      </c>
       <c r="AO44">
-        <v>0.99746043308117838</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP44">
-        <v>46.558726845063177</v>
+        <v>109.31605592223302</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14929,16 +14929,16 @@
         <v>605</v>
       </c>
       <c r="Y45" t="s">
-        <v>487</v>
+        <v>420</v>
       </c>
       <c r="Z45" t="s">
         <v>801</v>
       </c>
       <c r="AA45">
-        <v>0.9882282251528024</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB45">
-        <v>215.81587219862183</v>
+        <v>226.88936094280919</v>
       </c>
       <c r="AD45" t="s">
         <v>534</v>
@@ -14965,16 +14965,16 @@
         <v>944</v>
       </c>
       <c r="AM45" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AN45" t="s">
         <v>1081</v>
       </c>
-      <c r="AN45" t="s">
-        <v>1082</v>
-      </c>
       <c r="AO45">
-        <v>0.9955955730654259</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP45">
-        <v>80.747827133859133</v>
+        <v>163.93514059684662</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15039,16 +15039,16 @@
         <v>607</v>
       </c>
       <c r="Y46" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="Z46" t="s">
         <v>802</v>
       </c>
       <c r="AA46">
-        <v>0.99136196456122894</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB46">
-        <v>158.36398304413572</v>
+        <v>224.55764046872929</v>
       </c>
       <c r="AD46" t="s">
         <v>534</v>
@@ -15075,16 +15075,16 @@
         <v>946</v>
       </c>
       <c r="AM46" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AN46" t="s">
         <v>1083</v>
       </c>
-      <c r="AN46" t="s">
-        <v>1084</v>
-      </c>
       <c r="AO46">
-        <v>0.99671693937496686</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP46">
-        <v>60.189444792275019</v>
+        <v>46.428192737512276</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15149,16 +15149,16 @@
         <v>609</v>
       </c>
       <c r="Y47" t="s">
-        <v>427</v>
+        <v>495</v>
       </c>
       <c r="Z47" t="s">
         <v>803</v>
       </c>
       <c r="AA47">
-        <v>0.99658191580238853</v>
+        <v>0.99647006537565563</v>
       </c>
       <c r="AB47">
-        <v>62.664876956210314</v>
+        <v>64.715468112981057</v>
       </c>
       <c r="AD47" t="s">
         <v>534</v>
@@ -15185,16 +15185,16 @@
         <v>948</v>
       </c>
       <c r="AM47" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AN47" t="s">
         <v>1085</v>
       </c>
-      <c r="AN47" t="s">
-        <v>1086</v>
-      </c>
       <c r="AO47">
-        <v>0.97651207122624506</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP47">
-        <v>430.61202751883985</v>
+        <v>85.270745539791065</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15259,16 +15259,16 @@
         <v>611</v>
       </c>
       <c r="Y48" t="s">
-        <v>428</v>
+        <v>492</v>
       </c>
       <c r="Z48" t="s">
         <v>804</v>
       </c>
       <c r="AA48">
-        <v>0.99772567527055689</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB48">
-        <v>41.695953373122713</v>
+        <v>645.26520366712316</v>
       </c>
       <c r="AD48" t="s">
         <v>534</v>
@@ -15295,16 +15295,16 @@
         <v>950</v>
       </c>
       <c r="AM48" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AN48" t="s">
         <v>1087</v>
       </c>
-      <c r="AN48" t="s">
-        <v>1088</v>
-      </c>
       <c r="AO48">
-        <v>0.9972012891192491</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP48">
-        <v>51.309699480432613</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15369,16 +15369,16 @@
         <v>613</v>
       </c>
       <c r="Y49" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="Z49" t="s">
         <v>805</v>
       </c>
       <c r="AA49">
-        <v>0.99012236069527793</v>
+        <v>0.99267004448650609</v>
       </c>
       <c r="AB49">
-        <v>181.09005391990564</v>
+        <v>134.38251774738842</v>
       </c>
       <c r="AD49" t="s">
         <v>534</v>
@@ -15405,16 +15405,16 @@
         <v>952</v>
       </c>
       <c r="AM49" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AN49" t="s">
         <v>1089</v>
       </c>
-      <c r="AN49" t="s">
-        <v>1090</v>
-      </c>
       <c r="AO49">
-        <v>0.99648541839873139</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP49">
-        <v>64.433996023258757</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15479,16 +15479,16 @@
         <v>615</v>
       </c>
       <c r="Y50" t="s">
-        <v>435</v>
+        <v>519</v>
       </c>
       <c r="Z50" t="s">
         <v>806</v>
       </c>
       <c r="AA50">
-        <v>0.98990296758392993</v>
+        <v>0.9948848527457459</v>
       </c>
       <c r="AB50">
-        <v>185.11226096128556</v>
+        <v>93.777699661325343</v>
       </c>
       <c r="AD50" t="s">
         <v>534</v>
@@ -15515,16 +15515,16 @@
         <v>954</v>
       </c>
       <c r="AM50" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AN50" t="s">
         <v>1091</v>
       </c>
-      <c r="AN50" t="s">
-        <v>1092</v>
-      </c>
       <c r="AO50">
-        <v>0.9976540150806753</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP50">
-        <v>43.009723520953628</v>
+        <v>53.069246900976879</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15589,16 +15589,16 @@
         <v>617</v>
       </c>
       <c r="Y51" t="s">
-        <v>456</v>
+        <v>524</v>
       </c>
       <c r="Z51" t="s">
         <v>807</v>
       </c>
       <c r="AA51">
-        <v>0.99377714174527498</v>
+        <v>0.9922030648239526</v>
       </c>
       <c r="AB51">
-        <v>114.08573466995766</v>
+        <v>142.94381156086857</v>
       </c>
       <c r="AD51" t="s">
         <v>534</v>
@@ -15625,16 +15625,16 @@
         <v>956</v>
       </c>
       <c r="AM51" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AN51" t="s">
         <v>1093</v>
       </c>
-      <c r="AN51" t="s">
-        <v>1094</v>
-      </c>
       <c r="AO51">
-        <v>0.99644815774097173</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP51">
-        <v>65.117108082185538</v>
+        <v>105.47547991621673</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15699,16 +15699,16 @@
         <v>619</v>
       </c>
       <c r="Y52" t="s">
-        <v>525</v>
+        <v>468</v>
       </c>
       <c r="Z52" t="s">
-        <v>808</v>
+        <v>784</v>
       </c>
       <c r="AA52">
-        <v>0.99516685156772267</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB52">
-        <v>88.60772125841865</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD52" t="s">
         <v>534</v>
@@ -15735,16 +15735,16 @@
         <v>958</v>
       </c>
       <c r="AM52" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AN52" t="s">
         <v>1095</v>
       </c>
-      <c r="AN52" t="s">
-        <v>1096</v>
-      </c>
       <c r="AO52">
-        <v>0.99677419959133018</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP52">
-        <v>59.139674158947656</v>
+        <v>195.31167947327185</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15809,16 +15809,16 @@
         <v>621</v>
       </c>
       <c r="Y53" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="Z53" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AA53">
-        <v>0.99240925523869494</v>
+        <v>0.99726809134187266</v>
       </c>
       <c r="AB53">
-        <v>139.16365395725984</v>
+        <v>50.0849920656675</v>
       </c>
       <c r="AD53" t="s">
         <v>534</v>
@@ -15845,16 +15845,16 @@
         <v>960</v>
       </c>
       <c r="AM53" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AN53" t="s">
         <v>1097</v>
       </c>
-      <c r="AN53" t="s">
-        <v>1098</v>
-      </c>
       <c r="AO53">
-        <v>0.99766813121902409</v>
+        <v>0.99499049355022928</v>
       </c>
       <c r="AP53">
-        <v>42.750927651225993</v>
+        <v>91.840951579129481</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15919,16 +15919,16 @@
         <v>623</v>
       </c>
       <c r="Y54" t="s">
-        <v>532</v>
+        <v>481</v>
       </c>
       <c r="Z54" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="AA54">
-        <v>0.97244982574001193</v>
+        <v>0.97962408753770291</v>
       </c>
       <c r="AB54">
-        <v>505.08652809978111</v>
+        <v>373.55839514211272</v>
       </c>
       <c r="AD54" t="s">
         <v>534</v>
@@ -15955,16 +15955,16 @@
         <v>962</v>
       </c>
       <c r="AM54" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AN54" t="s">
         <v>1099</v>
       </c>
-      <c r="AN54" t="s">
-        <v>1100</v>
-      </c>
       <c r="AO54">
-        <v>0.99760247912344124</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP54">
-        <v>43.95454940357709</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16029,16 +16029,16 @@
         <v>625</v>
       </c>
       <c r="Y55" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="Z55" t="s">
-        <v>810</v>
+        <v>769</v>
       </c>
       <c r="AA55">
-        <v>0.99172397756136033</v>
+        <v>0.99098167665935155</v>
       </c>
       <c r="AB55">
-        <v>151.72707804172813</v>
+        <v>165.33592791188894</v>
       </c>
       <c r="AD55" t="s">
         <v>534</v>
@@ -16065,16 +16065,16 @@
         <v>964</v>
       </c>
       <c r="AM55" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AN55" t="s">
         <v>1101</v>
       </c>
-      <c r="AN55" t="s">
-        <v>1102</v>
-      </c>
       <c r="AO55">
-        <v>0.99336049451151065</v>
+        <v>0.99746043308117838</v>
       </c>
       <c r="AP55">
-        <v>121.72426728897108</v>
+        <v>46.558726845063177</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16139,16 +16139,16 @@
         <v>627</v>
       </c>
       <c r="Y56" t="s">
-        <v>451</v>
+        <v>503</v>
       </c>
       <c r="Z56" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="AA56">
-        <v>0.99431900976645593</v>
+        <v>0.98485684158558628</v>
       </c>
       <c r="AB56">
-        <v>104.15148761497397</v>
+        <v>277.62457093091871</v>
       </c>
       <c r="AD56" t="s">
         <v>534</v>
@@ -16175,16 +16175,16 @@
         <v>966</v>
       </c>
       <c r="AM56" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AN56" t="s">
         <v>1103</v>
       </c>
-      <c r="AN56" t="s">
-        <v>1104</v>
-      </c>
       <c r="AO56">
-        <v>0.99759498179797546</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP56">
-        <v>44.092000370450322</v>
+        <v>341.91992986513412</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16249,16 +16249,16 @@
         <v>629</v>
       </c>
       <c r="Y57" t="s">
-        <v>430</v>
+        <v>493</v>
       </c>
       <c r="Z57" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="AA57">
-        <v>0.9946350729064154</v>
+        <v>0.98211145389932475</v>
       </c>
       <c r="AB57">
-        <v>98.356996715718111</v>
+        <v>327.95667851237977</v>
       </c>
       <c r="AD57" t="s">
         <v>534</v>
@@ -16285,16 +16285,16 @@
         <v>968</v>
       </c>
       <c r="AM57" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AN57" t="s">
         <v>1105</v>
       </c>
-      <c r="AN57" t="s">
-        <v>841</v>
-      </c>
       <c r="AO57">
-        <v>0.95532613069733086</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP57">
-        <v>819.02093721560016</v>
+        <v>258.57410995127316</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16359,16 +16359,16 @@
         <v>631</v>
       </c>
       <c r="Y58" t="s">
-        <v>517</v>
+        <v>467</v>
       </c>
       <c r="Z58" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="AA58">
-        <v>0.99343259267015904</v>
+        <v>0.99654205356515035</v>
       </c>
       <c r="AB58">
-        <v>120.40246771375152</v>
+        <v>63.395684638909763</v>
       </c>
       <c r="AD58" t="s">
         <v>534</v>
@@ -16398,13 +16398,13 @@
         <v>1106</v>
       </c>
       <c r="AN58" t="s">
-        <v>771</v>
+        <v>1107</v>
       </c>
       <c r="AO58">
-        <v>0.98599828568941739</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP58">
-        <v>256.69809569401372</v>
+        <v>40.90273458067751</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16469,16 +16469,16 @@
         <v>633</v>
       </c>
       <c r="Y59" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="Z59" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="AA59">
-        <v>0.97581570155911468</v>
+        <v>0.99504817442297822</v>
       </c>
       <c r="AB59">
-        <v>443.37880474956393</v>
+        <v>90.78346891206678</v>
       </c>
       <c r="AD59" t="s">
         <v>534</v>
@@ -16505,16 +16505,16 @@
         <v>972</v>
       </c>
       <c r="AM59" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AN59" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AO59">
-        <v>0.98996241922424166</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP59">
-        <v>184.02231422223667</v>
+        <v>74.530739771815789</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16579,16 +16579,16 @@
         <v>635</v>
       </c>
       <c r="Y60" t="s">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="Z60" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="AA60">
-        <v>0.99542292233022822</v>
+        <v>0.99470247457730832</v>
       </c>
       <c r="AB60">
-        <v>83.913090612483515</v>
+        <v>97.121299416014665</v>
       </c>
       <c r="AD60" t="s">
         <v>534</v>
@@ -16615,16 +16615,16 @@
         <v>974</v>
       </c>
       <c r="AM60" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AN60" t="s">
-        <v>1110</v>
+        <v>770</v>
       </c>
       <c r="AO60">
-        <v>0.99620534810300254</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP60">
-        <v>69.568618111619969</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16689,16 +16689,16 @@
         <v>637</v>
       </c>
       <c r="Y61" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="Z61" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="AA61">
-        <v>0.99647584863086869</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB61">
-        <v>64.60944176740837</v>
+        <v>82.539922240185263</v>
       </c>
       <c r="AD61" t="s">
         <v>534</v>
@@ -16728,13 +16728,13 @@
         <v>1111</v>
       </c>
       <c r="AN61" t="s">
-        <v>1112</v>
+        <v>872</v>
       </c>
       <c r="AO61">
-        <v>0.99374536027070226</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP61">
-        <v>114.668395037126</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16799,16 +16799,16 @@
         <v>639</v>
       </c>
       <c r="Y62" t="s">
-        <v>431</v>
+        <v>471</v>
       </c>
       <c r="Z62" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="AA62">
-        <v>0.99780983219878738</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB62">
-        <v>40.153076355563911</v>
+        <v>470.66510807906917</v>
       </c>
       <c r="AD62" t="s">
         <v>534</v>
@@ -16835,16 +16835,16 @@
         <v>978</v>
       </c>
       <c r="AM62" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AN62" t="s">
         <v>1113</v>
       </c>
-      <c r="AN62" t="s">
-        <v>1114</v>
-      </c>
       <c r="AO62">
-        <v>0.99681385284485569</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP62">
-        <v>58.41269784431158</v>
+        <v>184.02231422223667</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16909,16 +16909,16 @@
         <v>641</v>
       </c>
       <c r="Y63" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="Z63" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="AA63">
-        <v>0.99724696581141214</v>
+        <v>0.9882282251528024</v>
       </c>
       <c r="AB63">
-        <v>50.472293457444586</v>
+        <v>215.81587219862183</v>
       </c>
       <c r="AD63" t="s">
         <v>534</v>
@@ -16945,16 +16945,16 @@
         <v>980</v>
       </c>
       <c r="AM63" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AN63" t="s">
         <v>1115</v>
       </c>
-      <c r="AN63" t="s">
-        <v>1116</v>
-      </c>
       <c r="AO63">
-        <v>0.99527237968252791</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP63">
-        <v>86.673039153654699</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17019,16 +17019,16 @@
         <v>643</v>
       </c>
       <c r="Y64" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="Z64" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="AA64">
-        <v>0.99589550629055523</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB64">
-        <v>75.249051339820184</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD64" t="s">
         <v>534</v>
@@ -17055,16 +17055,16 @@
         <v>982</v>
       </c>
       <c r="AM64" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AN64" t="s">
         <v>1117</v>
       </c>
-      <c r="AN64" t="s">
-        <v>1118</v>
-      </c>
       <c r="AO64">
-        <v>0.9917253583369573</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP64">
-        <v>151.70176382244892</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17129,16 +17129,16 @@
         <v>645</v>
       </c>
       <c r="Y65" t="s">
-        <v>520</v>
+        <v>427</v>
       </c>
       <c r="Z65" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="AA65">
-        <v>0.99531156065644533</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB65">
-        <v>85.954721298502818</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD65" t="s">
         <v>534</v>
@@ -17165,16 +17165,16 @@
         <v>984</v>
       </c>
       <c r="AM65" t="s">
+        <v>1118</v>
+      </c>
+      <c r="AN65" t="s">
         <v>1119</v>
       </c>
-      <c r="AN65" t="s">
-        <v>1120</v>
-      </c>
       <c r="AO65">
-        <v>0.99569050067699549</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP65">
-        <v>79.007487588415231</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17239,16 +17239,16 @@
         <v>647</v>
       </c>
       <c r="Y66" t="s">
-        <v>521</v>
+        <v>428</v>
       </c>
       <c r="Z66" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="AA66">
-        <v>0.99706825374988217</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB66">
-        <v>53.748681252160438</v>
+        <v>41.695953373122713</v>
       </c>
       <c r="AD66" t="s">
         <v>534</v>
@@ -17275,16 +17275,16 @@
         <v>986</v>
       </c>
       <c r="AM66" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AN66" t="s">
         <v>1121</v>
       </c>
-      <c r="AN66" t="s">
-        <v>1122</v>
-      </c>
       <c r="AO66">
-        <v>0.99445933293330402</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP66">
-        <v>101.57889622275951</v>
+        <v>86.673039153654699</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17349,16 +17349,16 @@
         <v>649</v>
       </c>
       <c r="Y67" t="s">
-        <v>469</v>
+        <v>529</v>
       </c>
       <c r="Z67" t="s">
-        <v>783</v>
+        <v>819</v>
       </c>
       <c r="AA67">
-        <v>0.96238190390083644</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB67">
-        <v>689.665095151331</v>
+        <v>637.85920701836687</v>
       </c>
       <c r="AD67" t="s">
         <v>534</v>
@@ -17385,16 +17385,16 @@
         <v>988</v>
       </c>
       <c r="AM67" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AN67" t="s">
         <v>1123</v>
       </c>
-      <c r="AN67" t="s">
-        <v>1124</v>
-      </c>
       <c r="AO67">
-        <v>0.9961850470371636</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP67">
-        <v>69.94080431866837</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17459,16 +17459,16 @@
         <v>651</v>
       </c>
       <c r="Y68" t="s">
-        <v>528</v>
+        <v>478</v>
       </c>
       <c r="Z68" t="s">
-        <v>785</v>
+        <v>820</v>
       </c>
       <c r="AA68">
-        <v>0.96316770855847034</v>
+        <v>0.99344074878931121</v>
       </c>
       <c r="AB68">
-        <v>675.25867642804383</v>
+        <v>120.25293886262826</v>
       </c>
       <c r="AD68" t="s">
         <v>534</v>
@@ -17495,16 +17495,16 @@
         <v>990</v>
       </c>
       <c r="AM68" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AN68" t="s">
         <v>1125</v>
       </c>
-      <c r="AN68" t="s">
-        <v>1126</v>
-      </c>
       <c r="AO68">
-        <v>0.99710531380540124</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP68">
-        <v>53.069246900976879</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17569,16 +17569,16 @@
         <v>653</v>
       </c>
       <c r="Y69" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="Z69" t="s">
-        <v>822</v>
+        <v>769</v>
       </c>
       <c r="AA69">
-        <v>0.9951089264264793</v>
+        <v>0.99459650548991607</v>
       </c>
       <c r="AB69">
-        <v>89.669682181211982</v>
+        <v>99.064066018204684</v>
       </c>
       <c r="AD69" t="s">
         <v>534</v>
@@ -17605,16 +17605,16 @@
         <v>992</v>
       </c>
       <c r="AM69" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AN69" t="s">
         <v>1127</v>
       </c>
-      <c r="AN69" t="s">
-        <v>1128</v>
-      </c>
       <c r="AO69">
-        <v>0.99551365545858539</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP69">
-        <v>82.249649925934918</v>
+        <v>430.61202751883985</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17679,16 +17679,16 @@
         <v>655</v>
       </c>
       <c r="Y70" t="s">
-        <v>434</v>
+        <v>490</v>
       </c>
       <c r="Z70" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AA70">
-        <v>0.98666519734623237</v>
+        <v>0.99655727877565281</v>
       </c>
       <c r="AB70">
-        <v>244.47138198573927</v>
+        <v>63.116555779697698</v>
       </c>
       <c r="AD70" t="s">
         <v>534</v>
@@ -17715,16 +17715,16 @@
         <v>994</v>
       </c>
       <c r="AM70" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AN70" t="s">
         <v>1129</v>
       </c>
-      <c r="AN70" t="s">
-        <v>1130</v>
-      </c>
       <c r="AO70">
-        <v>0.99554924619735208</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP70">
-        <v>81.597153048545437</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17789,16 +17789,16 @@
         <v>657</v>
       </c>
       <c r="Y71" t="s">
-        <v>425</v>
+        <v>488</v>
       </c>
       <c r="Z71" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="AA71">
-        <v>0.99750070245826261</v>
+        <v>0.99221351039035977</v>
       </c>
       <c r="AB71">
-        <v>45.820454931853</v>
+        <v>142.75230951007163</v>
       </c>
       <c r="AD71" t="s">
         <v>534</v>
@@ -17825,16 +17825,16 @@
         <v>996</v>
       </c>
       <c r="AM71" t="s">
+        <v>1130</v>
+      </c>
+      <c r="AN71" t="s">
         <v>1131</v>
       </c>
-      <c r="AN71" t="s">
-        <v>1132</v>
-      </c>
       <c r="AO71">
-        <v>0.99083036293819104</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP71">
-        <v>168.11001279983091</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17899,16 +17899,16 @@
         <v>659</v>
       </c>
       <c r="Y72" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="Z72" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AA72">
-        <v>0.99395341117186964</v>
+        <v>0.99067174034238459</v>
       </c>
       <c r="AB72">
-        <v>110.85412851572337</v>
+        <v>171.01809372294977</v>
       </c>
       <c r="AD72" t="s">
         <v>534</v>
@@ -17935,16 +17935,16 @@
         <v>998</v>
       </c>
       <c r="AM72" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AN72" t="s">
         <v>1133</v>
       </c>
-      <c r="AN72" t="s">
-        <v>1134</v>
-      </c>
       <c r="AO72">
-        <v>0.9976320377495026</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP72">
-        <v>43.412641259119624</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18009,16 +18009,16 @@
         <v>661</v>
       </c>
       <c r="Y73" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="Z73" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AA73">
-        <v>0.98322732678073066</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB73">
-        <v>307.49900901993823</v>
+        <v>67.023399161603095</v>
       </c>
       <c r="AD73" t="s">
         <v>534</v>
@@ -18045,16 +18045,16 @@
         <v>1000</v>
       </c>
       <c r="AM73" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AN73" t="s">
         <v>1135</v>
       </c>
-      <c r="AN73" t="s">
-        <v>1136</v>
-      </c>
       <c r="AO73">
-        <v>0.97020178001960844</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP73">
-        <v>546.30069964051177</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18119,16 +18119,16 @@
         <v>663</v>
       </c>
       <c r="Y74" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="Z74" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="AA74">
-        <v>0.9974199781412052</v>
+        <v>0.98416341622871006</v>
       </c>
       <c r="AB74">
-        <v>47.300400744571718</v>
+        <v>290.33736914031488</v>
       </c>
       <c r="AD74" t="s">
         <v>534</v>
@@ -18155,16 +18155,16 @@
         <v>1002</v>
       </c>
       <c r="AM74" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AN74" t="s">
         <v>1137</v>
       </c>
-      <c r="AN74" t="s">
-        <v>1138</v>
-      </c>
       <c r="AO74">
-        <v>0.99693672852577231</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP74">
-        <v>56.159977027506663</v>
+        <v>79.268397406829976</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18229,16 +18229,16 @@
         <v>665</v>
       </c>
       <c r="Y75" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z75" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AA75">
-        <v>0.99336837071349593</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB75">
-        <v>121.57987025257442</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD75" t="s">
         <v>534</v>
@@ -18265,16 +18265,16 @@
         <v>1004</v>
       </c>
       <c r="AM75" t="s">
+        <v>1138</v>
+      </c>
+      <c r="AN75" t="s">
         <v>1139</v>
       </c>
-      <c r="AN75" t="s">
-        <v>1140</v>
-      </c>
       <c r="AO75">
-        <v>0.99478775228549088</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP75">
-        <v>95.557874766001078</v>
+        <v>43.581147571379539</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18339,16 +18339,16 @@
         <v>667</v>
       </c>
       <c r="Y76" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="Z76" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AA76">
-        <v>0.99379477670057537</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB76">
-        <v>113.7624271561186</v>
+        <v>81.000126667143434</v>
       </c>
       <c r="AD76" t="s">
         <v>534</v>
@@ -18375,16 +18375,16 @@
         <v>1006</v>
       </c>
       <c r="AM76" t="s">
+        <v>1140</v>
+      </c>
+      <c r="AN76" t="s">
         <v>1141</v>
       </c>
-      <c r="AN76" t="s">
-        <v>806</v>
-      </c>
       <c r="AO76">
-        <v>0.98674094240398891</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP76">
-        <v>243.0827225935364</v>
+        <v>151.17817104385733</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18449,16 +18449,16 @@
         <v>669</v>
       </c>
       <c r="Y77" t="s">
-        <v>454</v>
+        <v>516</v>
       </c>
       <c r="Z77" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="AA77">
-        <v>0.9961866142254362</v>
+        <v>0.99390501557434718</v>
       </c>
       <c r="AB77">
-        <v>69.91207253366963</v>
+        <v>111.7413811369688</v>
       </c>
       <c r="AD77" t="s">
         <v>534</v>
@@ -18491,10 +18491,10 @@
         <v>1143</v>
       </c>
       <c r="AO77">
-        <v>0.98452519237182756</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP77">
-        <v>283.70480651649393</v>
+        <v>57.146786340912868</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18559,16 +18559,16 @@
         <v>671</v>
       </c>
       <c r="Y78" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="Z78" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="AA78">
-        <v>0.9914627894548943</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB78">
-        <v>156.51552666027055</v>
+        <v>443.37880474956393</v>
       </c>
       <c r="AD78" t="s">
         <v>534</v>
@@ -18601,10 +18601,10 @@
         <v>1145</v>
       </c>
       <c r="AO78">
-        <v>0.99679967385551038</v>
+        <v>0.99488275259079373</v>
       </c>
       <c r="AP78">
-        <v>58.672645982308907</v>
+        <v>93.81620250211445</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18669,16 +18669,16 @@
         <v>673</v>
       </c>
       <c r="Y79" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="Z79" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="AA79">
-        <v>0.9776523073059149</v>
+        <v>0.99542292233022822</v>
       </c>
       <c r="AB79">
-        <v>409.70769939155917</v>
+        <v>83.913090612483515</v>
       </c>
       <c r="AD79" t="s">
         <v>534</v>
@@ -18711,10 +18711,10 @@
         <v>1147</v>
       </c>
       <c r="AO79">
-        <v>0.99414234808301016</v>
+        <v>0.99663220850609069</v>
       </c>
       <c r="AP79">
-        <v>107.39028514481463</v>
+        <v>61.742844055003644</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18779,16 +18779,16 @@
         <v>675</v>
       </c>
       <c r="Y80" t="s">
-        <v>504</v>
+        <v>450</v>
       </c>
       <c r="Z80" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="AA80">
-        <v>0.98289281118622185</v>
+        <v>0.99647584863086869</v>
       </c>
       <c r="AB80">
-        <v>313.63179491926536</v>
+        <v>64.60944176740837</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18853,16 +18853,16 @@
         <v>677</v>
       </c>
       <c r="Y81" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="Z81" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AA81">
-        <v>0.99593583828988941</v>
+        <v>0.99780983219878738</v>
       </c>
       <c r="AB81">
-        <v>74.509631352026517</v>
+        <v>40.153076355563911</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18927,16 +18927,16 @@
         <v>679</v>
       </c>
       <c r="Y82" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="Z82" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="AA82">
-        <v>0.99649411432543766</v>
+        <v>0.99724696581141214</v>
       </c>
       <c r="AB82">
-        <v>64.274570700309781</v>
+        <v>50.472293457444586</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -19001,16 +19001,16 @@
         <v>681</v>
       </c>
       <c r="Y83" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="Z83" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="AA83">
-        <v>0.97907421743006762</v>
+        <v>0.99589550629055523</v>
       </c>
       <c r="AB83">
-        <v>383.63934711542669</v>
+        <v>75.249051339820184</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -19075,16 +19075,16 @@
         <v>683</v>
       </c>
       <c r="Y84" t="s">
-        <v>426</v>
+        <v>520</v>
       </c>
       <c r="Z84" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="AA84">
-        <v>0.99558768376711515</v>
+        <v>0.99531156065644533</v>
       </c>
       <c r="AB84">
-        <v>80.892464269556413</v>
+        <v>85.954721298502818</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -19149,16 +19149,16 @@
         <v>685</v>
       </c>
       <c r="Y85" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="Z85" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="AA85">
-        <v>0.99324569511004301</v>
+        <v>0.99706825374988217</v>
       </c>
       <c r="AB85">
-        <v>123.82892298254488</v>
+        <v>53.748681252160438</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19223,16 +19223,16 @@
         <v>687</v>
       </c>
       <c r="Y86" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="Z86" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AA86">
-        <v>0.99419165427276146</v>
+        <v>0.99012236069527793</v>
       </c>
       <c r="AB86">
-        <v>106.48633833270691</v>
+        <v>181.09005391990564</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19297,16 +19297,16 @@
         <v>689</v>
       </c>
       <c r="Y87" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="Z87" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="AA87">
-        <v>0.99198935558098356</v>
+        <v>0.98990296758392993</v>
       </c>
       <c r="AB87">
-        <v>146.8618143486346</v>
+        <v>185.11226096128556</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19371,16 +19371,16 @@
         <v>691</v>
       </c>
       <c r="Y88" t="s">
-        <v>526</v>
+        <v>456</v>
       </c>
       <c r="Z88" t="s">
-        <v>785</v>
+        <v>839</v>
       </c>
       <c r="AA88">
-        <v>0.93980266520001188</v>
+        <v>0.99377714174527498</v>
       </c>
       <c r="AB88">
-        <v>1103.617804666449</v>
+        <v>114.08573466995766</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19445,16 +19445,16 @@
         <v>693</v>
       </c>
       <c r="Y89" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Z89" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AA89">
-        <v>0.95679935803281835</v>
+        <v>0.99516685156772267</v>
       </c>
       <c r="AB89">
-        <v>792.01176939833033</v>
+        <v>88.60772125841865</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19519,16 +19519,16 @@
         <v>695</v>
       </c>
       <c r="Y90" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="Z90" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AA90">
-        <v>0.98761622532712257</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB90">
-        <v>227.03586900275366</v>
+        <v>90.443352439796072</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19593,16 +19593,16 @@
         <v>697</v>
       </c>
       <c r="Y91" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="Z91" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AA91">
-        <v>0.99003402112096806</v>
+        <v>0.97537853020161625</v>
       </c>
       <c r="AB91">
-        <v>182.70961278225187</v>
+        <v>451.39361297036953</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19667,16 +19667,16 @@
         <v>699</v>
       </c>
       <c r="Y92" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="Z92" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AA92">
-        <v>0.99466062705491098</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB92">
-        <v>97.888503993298116</v>
+        <v>106.82211818572355</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19741,16 +19741,16 @@
         <v>701</v>
       </c>
       <c r="Y93" t="s">
-        <v>508</v>
+        <v>429</v>
       </c>
       <c r="Z93" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AA93">
-        <v>0.9944598150968682</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB93">
-        <v>101.5700565574154</v>
+        <v>62.251070203636829</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19815,16 +19815,16 @@
         <v>703</v>
       </c>
       <c r="Y94" t="s">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="Z94" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AA94">
-        <v>0.99494501873633134</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB94">
-        <v>92.674656500591539</v>
+        <v>54.23617409891024</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19889,16 +19889,16 @@
         <v>705</v>
       </c>
       <c r="Y95" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="Z95" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AA95">
-        <v>0.99438812565699364</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB95">
-        <v>102.88436295511657</v>
+        <v>154.58276065179118</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19963,16 +19963,16 @@
         <v>707</v>
       </c>
       <c r="Y96" t="s">
-        <v>523</v>
+        <v>465</v>
       </c>
       <c r="Z96" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AA96">
-        <v>0.99643191679577148</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB96">
-        <v>65.414858744189985</v>
+        <v>49.309812409870183</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -20037,16 +20037,16 @@
         <v>709</v>
       </c>
       <c r="Y97" t="s">
-        <v>421</v>
+        <v>514</v>
       </c>
       <c r="Z97" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AA97">
-        <v>0.99553066735440277</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB97">
-        <v>81.937765169281747</v>
+        <v>121.27899510281891</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -20111,16 +20111,16 @@
         <v>711</v>
       </c>
       <c r="Y98" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="Z98" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AA98">
-        <v>0.99049341406542279</v>
+        <v>0.98150124893892388</v>
       </c>
       <c r="AB98">
-        <v>174.28740880058183</v>
+        <v>339.14376945306287</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20185,16 +20185,16 @@
         <v>713</v>
       </c>
       <c r="Y99" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="Z99" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AA99">
-        <v>0.99575157784901702</v>
+        <v>0.99523081353776888</v>
       </c>
       <c r="AB99">
-        <v>77.887739434686992</v>
+        <v>87.435085140903482</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20259,16 +20259,16 @@
         <v>715</v>
       </c>
       <c r="Y100" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="Z100" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AA100">
-        <v>0.99506672623055659</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB100">
-        <v>90.443352439796072</v>
+        <v>153.20678909592235</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20333,16 +20333,16 @@
         <v>717</v>
       </c>
       <c r="Y101" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="Z101" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AA101">
-        <v>0.97537853020161625</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB101">
-        <v>451.39361297036953</v>
+        <v>78.81162391526847</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20407,16 +20407,16 @@
         <v>719</v>
       </c>
       <c r="Y102" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="Z102" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AA102">
-        <v>0.99417333900805149</v>
+        <v>0.99691903985105013</v>
       </c>
       <c r="AB102">
-        <v>106.82211818572355</v>
+        <v>56.484269397415083</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20481,16 +20481,16 @@
         <v>721</v>
       </c>
       <c r="Y103" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="Z103" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AA103">
-        <v>0.99660448707980165</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB103">
-        <v>62.251070203636829</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20555,16 +20555,16 @@
         <v>723</v>
       </c>
       <c r="Y104" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="Z104" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AA104">
-        <v>0.99704166323096854</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB104">
-        <v>54.23617409891024</v>
+        <v>86.308558527470979</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20629,16 +20629,16 @@
         <v>725</v>
       </c>
       <c r="Y105" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Z105" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AA105">
-        <v>0.99156821305535681</v>
+        <v>0.99443562760718263</v>
       </c>
       <c r="AB105">
-        <v>154.58276065179118</v>
+        <v>102.01349386831856</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20703,16 +20703,16 @@
         <v>727</v>
       </c>
       <c r="Y106" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="Z106" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AA106">
-        <v>0.99731037386855248</v>
+        <v>0.9914627894548943</v>
       </c>
       <c r="AB106">
-        <v>49.309812409870183</v>
+        <v>156.51552666027055</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20777,16 +20777,16 @@
         <v>729</v>
       </c>
       <c r="Y107" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="Z107" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AA107">
-        <v>0.99338478208530079</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB107">
-        <v>121.27899510281891</v>
+        <v>409.70769939155917</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20851,16 +20851,16 @@
         <v>731</v>
       </c>
       <c r="Y108" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="Z108" t="s">
-        <v>783</v>
+        <v>859</v>
       </c>
       <c r="AA108">
-        <v>0.9621480095608167</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB108">
-        <v>693.95315805169378</v>
+        <v>313.63179491926536</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20925,16 +20925,16 @@
         <v>733</v>
       </c>
       <c r="Y109" t="s">
-        <v>479</v>
+        <v>424</v>
       </c>
       <c r="Z109" t="s">
         <v>860</v>
       </c>
       <c r="AA109">
-        <v>0.98916941127667946</v>
+        <v>0.99593583828988941</v>
       </c>
       <c r="AB109">
-        <v>198.56079326087576</v>
+        <v>74.509631352026517</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20999,16 +20999,16 @@
         <v>735</v>
       </c>
       <c r="Y110" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="Z110" t="s">
         <v>861</v>
       </c>
       <c r="AA110">
-        <v>0.97159134368321343</v>
+        <v>0.99553066735440277</v>
       </c>
       <c r="AB110">
-        <v>520.82536580775354</v>
+        <v>81.937765169281747</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -21073,16 +21073,16 @@
         <v>737</v>
       </c>
       <c r="Y111" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="Z111" t="s">
         <v>862</v>
       </c>
       <c r="AA111">
-        <v>0.99359614530212825</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB111">
-        <v>117.40400279431638</v>
+        <v>174.28740880058183</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -21147,16 +21147,16 @@
         <v>739</v>
       </c>
       <c r="Y112" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="Z112" t="s">
         <v>863</v>
       </c>
       <c r="AA112">
-        <v>0.99488082982009873</v>
+        <v>0.99575157784901702</v>
       </c>
       <c r="AB112">
-        <v>93.851453298190577</v>
+        <v>77.887739434686992</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21221,16 +21221,16 @@
         <v>741</v>
       </c>
       <c r="Y113" t="s">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="Z113" t="s">
-        <v>864</v>
+        <v>784</v>
       </c>
       <c r="AA113">
-        <v>0.99557743229498485</v>
+        <v>0.9621480095608167</v>
       </c>
       <c r="AB113">
-        <v>81.080407925277868</v>
+        <v>693.95315805169378</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21295,16 +21295,16 @@
         <v>743</v>
       </c>
       <c r="Y114" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="Z114" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="AA114">
-        <v>0.99401156108202648</v>
+        <v>0.98916941127667946</v>
       </c>
       <c r="AB114">
-        <v>109.78804682951412</v>
+        <v>198.56079326087576</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21369,16 +21369,16 @@
         <v>745</v>
       </c>
       <c r="Y115" t="s">
-        <v>529</v>
+        <v>438</v>
       </c>
       <c r="Z115" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="AA115">
-        <v>0.96520767961718001</v>
+        <v>0.97159134368321343</v>
       </c>
       <c r="AB115">
-        <v>637.85920701836687</v>
+        <v>520.82536580775354</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21443,16 +21443,16 @@
         <v>747</v>
       </c>
       <c r="Y116" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="Z116" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AA116">
-        <v>0.99344074878931121</v>
+        <v>0.99359614530212825</v>
       </c>
       <c r="AB116">
-        <v>120.25293886262826</v>
+        <v>117.40400279431638</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21517,16 +21517,16 @@
         <v>749</v>
       </c>
       <c r="Y117" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="Z117" t="s">
-        <v>785</v>
+        <v>867</v>
       </c>
       <c r="AA117">
-        <v>0.99459650548991607</v>
+        <v>0.99488082982009873</v>
       </c>
       <c r="AB117">
-        <v>99.064066018204684</v>
+        <v>93.851453298190577</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21591,16 +21591,16 @@
         <v>751</v>
       </c>
       <c r="Y118" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="Z118" t="s">
         <v>868</v>
       </c>
       <c r="AA118">
-        <v>0.99655727877565281</v>
+        <v>0.99557743229498485</v>
       </c>
       <c r="AB118">
-        <v>63.116555779697698</v>
+        <v>81.080407925277868</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21665,16 +21665,16 @@
         <v>753</v>
       </c>
       <c r="Y119" t="s">
-        <v>488</v>
+        <v>455</v>
       </c>
       <c r="Z119" t="s">
         <v>869</v>
       </c>
       <c r="AA119">
-        <v>0.99221351039035977</v>
+        <v>0.99401156108202648</v>
       </c>
       <c r="AB119">
-        <v>142.75230951007163</v>
+        <v>109.78804682951412</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21739,16 +21739,16 @@
         <v>755</v>
       </c>
       <c r="Y120" t="s">
-        <v>447</v>
+        <v>476</v>
       </c>
       <c r="Z120" t="s">
         <v>870</v>
       </c>
       <c r="AA120">
-        <v>0.99067174034238459</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB120">
-        <v>171.01809372294977</v>
+        <v>129.18226807514921</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21813,16 +21813,16 @@
         <v>757</v>
       </c>
       <c r="Y121" t="s">
-        <v>418</v>
+        <v>486</v>
       </c>
       <c r="Z121" t="s">
         <v>871</v>
       </c>
       <c r="AA121">
-        <v>0.99634417822754895</v>
+        <v>0.98571261124433651</v>
       </c>
       <c r="AB121">
-        <v>67.023399161603095</v>
+        <v>261.93546052049794</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21887,16 +21887,16 @@
         <v>759</v>
       </c>
       <c r="Y122" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="Z122" t="s">
         <v>872</v>
       </c>
       <c r="AA122">
-        <v>0.98416341622871006</v>
+        <v>0.9849019911873127</v>
       </c>
       <c r="AB122">
-        <v>290.33736914031488</v>
+        <v>276.79682823259958</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21961,16 +21961,16 @@
         <v>761</v>
       </c>
       <c r="Y123" t="s">
-        <v>497</v>
+        <v>419</v>
       </c>
       <c r="Z123" t="s">
         <v>873</v>
       </c>
       <c r="AA123">
-        <v>0.99563792883070867</v>
+        <v>0.99157679714615166</v>
       </c>
       <c r="AB123">
-        <v>79.971304770340467</v>
+        <v>154.42538565388551</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -22035,16 +22035,16 @@
         <v>763</v>
       </c>
       <c r="Y124" t="s">
-        <v>432</v>
+        <v>515</v>
       </c>
       <c r="Z124" t="s">
         <v>874</v>
       </c>
       <c r="AA124">
-        <v>0.99558181127270129</v>
+        <v>0.99619387577842089</v>
       </c>
       <c r="AB124">
-        <v>81.000126667143434</v>
+        <v>69.778944062284495</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -22109,16 +22109,16 @@
         <v>765</v>
       </c>
       <c r="Y125" t="s">
-        <v>516</v>
+        <v>457</v>
       </c>
       <c r="Z125" t="s">
         <v>875</v>
       </c>
       <c r="AA125">
-        <v>0.99390501557434718</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB125">
-        <v>111.7413811369688</v>
+        <v>92.048872319688599</v>
       </c>
     </row>
   </sheetData>
@@ -22127,7 +22127,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240DCCA3-74E6-4A1F-9AF5-527495DFCF3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394B6F6F-2920-41A3-BE71-2A46C2CAE5E7}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22239,7 +22239,7 @@
         <v>1269</v>
       </c>
       <c r="K11" t="s">
-        <v>1014</v>
+        <v>1056</v>
       </c>
       <c r="L11">
         <v>4.7713910333636482</v>
@@ -22272,7 +22272,7 @@
         <v>1407</v>
       </c>
       <c r="X11" t="s">
-        <v>1242</v>
+        <v>1214</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -22307,7 +22307,7 @@
         <v>1271</v>
       </c>
       <c r="K12" t="s">
-        <v>1051</v>
+        <v>1102</v>
       </c>
       <c r="L12">
         <v>12.404103898825962</v>
@@ -22340,7 +22340,7 @@
         <v>1409</v>
       </c>
       <c r="X12" t="s">
-        <v>1210</v>
+        <v>1246</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -22375,7 +22375,7 @@
         <v>1273</v>
       </c>
       <c r="K13" t="s">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="L13">
         <v>6.1276234637439133</v>
@@ -22408,7 +22408,7 @@
         <v>1411</v>
       </c>
       <c r="X13" t="s">
-        <v>1261</v>
+        <v>1250</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -22443,7 +22443,7 @@
         <v>1275</v>
       </c>
       <c r="K14" t="s">
-        <v>1085</v>
+        <v>1126</v>
       </c>
       <c r="L14">
         <v>0.85621181691755843</v>
@@ -22476,7 +22476,7 @@
         <v>1413</v>
       </c>
       <c r="X14" t="s">
-        <v>1254</v>
+        <v>1224</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -22511,7 +22511,7 @@
         <v>1277</v>
       </c>
       <c r="K15" t="s">
-        <v>1142</v>
+        <v>1072</v>
       </c>
       <c r="L15">
         <v>2.2628760328229185</v>
@@ -22544,7 +22544,7 @@
         <v>1415</v>
       </c>
       <c r="X15" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -22579,7 +22579,7 @@
         <v>1279</v>
       </c>
       <c r="K16" t="s">
-        <v>1033</v>
+        <v>1080</v>
       </c>
       <c r="L16">
         <v>0.43370118574988076</v>
@@ -22612,7 +22612,7 @@
         <v>1417</v>
       </c>
       <c r="X16" t="s">
-        <v>1252</v>
+        <v>1239</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -22647,7 +22647,7 @@
         <v>1281</v>
       </c>
       <c r="K17" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
       <c r="L17">
         <v>2.5150267058852811</v>
@@ -22680,7 +22680,7 @@
         <v>1419</v>
       </c>
       <c r="X17" t="s">
-        <v>1240</v>
+        <v>1222</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -22715,7 +22715,7 @@
         <v>1283</v>
       </c>
       <c r="K18" t="s">
-        <v>1141</v>
+        <v>1071</v>
       </c>
       <c r="L18">
         <v>2.885493974180005</v>
@@ -22748,7 +22748,7 @@
         <v>1421</v>
       </c>
       <c r="X18" t="s">
-        <v>1214</v>
+        <v>1256</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -22783,7 +22783,7 @@
         <v>1285</v>
       </c>
       <c r="K19" t="s">
-        <v>1135</v>
+        <v>1065</v>
       </c>
       <c r="L19">
         <v>10.563746678268352</v>
@@ -22816,7 +22816,7 @@
         <v>1423</v>
       </c>
       <c r="X19" t="s">
-        <v>1238</v>
+        <v>1220</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22851,7 +22851,7 @@
         <v>1287</v>
       </c>
       <c r="K20" t="s">
-        <v>1016</v>
+        <v>1058</v>
       </c>
       <c r="L20">
         <v>7.4816578037471135</v>
@@ -22884,7 +22884,7 @@
         <v>1425</v>
       </c>
       <c r="X20" t="s">
-        <v>1229</v>
+        <v>1268</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22919,7 +22919,7 @@
         <v>1289</v>
       </c>
       <c r="K21" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="L21">
         <v>11.884376191048085</v>
@@ -22952,7 +22952,7 @@
         <v>1427</v>
       </c>
       <c r="X21" t="s">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22987,7 +22987,7 @@
         <v>1291</v>
       </c>
       <c r="K22" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="L22">
         <v>12.246676572623375</v>
@@ -23020,7 +23020,7 @@
         <v>1429</v>
       </c>
       <c r="X22" t="s">
-        <v>1250</v>
+        <v>1237</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -23055,7 +23055,7 @@
         <v>1293</v>
       </c>
       <c r="K23" t="s">
-        <v>1031</v>
+        <v>1078</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -23088,7 +23088,7 @@
         <v>1431</v>
       </c>
       <c r="X23" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -23123,7 +23123,7 @@
         <v>1295</v>
       </c>
       <c r="K24" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -23156,7 +23156,7 @@
         <v>1433</v>
       </c>
       <c r="X24" t="s">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -23191,7 +23191,7 @@
         <v>1297</v>
       </c>
       <c r="K25" t="s">
-        <v>1137</v>
+        <v>1067</v>
       </c>
       <c r="L25">
         <v>11.221871479411517</v>
@@ -23224,7 +23224,7 @@
         <v>1435</v>
       </c>
       <c r="X25" t="s">
-        <v>1244</v>
+        <v>1216</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -23259,7 +23259,7 @@
         <v>1299</v>
       </c>
       <c r="K26" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="L26">
         <v>1.6691823226567941</v>
@@ -23292,7 +23292,7 @@
         <v>1437</v>
       </c>
       <c r="X26" t="s">
-        <v>1227</v>
+        <v>1266</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23327,7 +23327,7 @@
         <v>1301</v>
       </c>
       <c r="K27" t="s">
-        <v>1039</v>
+        <v>1136</v>
       </c>
       <c r="L27">
         <v>3.7614311754340659</v>
@@ -23360,7 +23360,7 @@
         <v>1439</v>
       </c>
       <c r="X27" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -23395,7 +23395,7 @@
         <v>1303</v>
       </c>
       <c r="K28" t="s">
-        <v>1055</v>
+        <v>1106</v>
       </c>
       <c r="L28">
         <v>0.34625959029864795</v>
@@ -23428,7 +23428,7 @@
         <v>1441</v>
       </c>
       <c r="X28" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
       <c r="Y28">
         <v>2.6655000000000002</v>
@@ -23463,7 +23463,7 @@
         <v>1305</v>
       </c>
       <c r="K29" t="s">
-        <v>1065</v>
+        <v>1022</v>
       </c>
       <c r="L29">
         <v>0.65440271382024695</v>
@@ -23496,7 +23496,7 @@
         <v>1443</v>
       </c>
       <c r="X29" t="s">
-        <v>1216</v>
+        <v>1258</v>
       </c>
       <c r="Y29">
         <v>8.8432499999999994</v>
@@ -23531,7 +23531,7 @@
         <v>1307</v>
       </c>
       <c r="K30" t="s">
-        <v>1035</v>
+        <v>1082</v>
       </c>
       <c r="L30">
         <v>2.2677057834637031</v>
@@ -23564,7 +23564,7 @@
         <v>1445</v>
       </c>
       <c r="X30" t="s">
-        <v>1233</v>
+        <v>1212</v>
       </c>
       <c r="Y30">
         <v>3.4402499999999998</v>
@@ -23599,7 +23599,7 @@
         <v>1309</v>
       </c>
       <c r="K31" t="s">
-        <v>1109</v>
+        <v>1114</v>
       </c>
       <c r="L31">
         <v>2.4836923620575391</v>
@@ -23632,7 +23632,7 @@
         <v>1447</v>
       </c>
       <c r="X31" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="Y31">
         <v>13.389749999999999</v>
@@ -23667,7 +23667,7 @@
         <v>1311</v>
       </c>
       <c r="K32" t="s">
-        <v>1127</v>
+        <v>1038</v>
       </c>
       <c r="L32">
         <v>4.0763322608214585</v>
@@ -23700,7 +23700,7 @@
         <v>1449</v>
       </c>
       <c r="X32" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="Y32">
         <v>6.9757499999999997</v>
@@ -23735,7 +23735,7 @@
         <v>1313</v>
       </c>
       <c r="K33" t="s">
-        <v>1041</v>
+        <v>1138</v>
       </c>
       <c r="L33">
         <v>2.5731779960501728</v>
@@ -23768,7 +23768,7 @@
         <v>1451</v>
       </c>
       <c r="X33" t="s">
-        <v>1231</v>
+        <v>1210</v>
       </c>
       <c r="Y33">
         <v>38.154000000000003</v>
@@ -23803,7 +23803,7 @@
         <v>1315</v>
       </c>
       <c r="K34" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="L34">
         <v>4.0509443596880574</v>
@@ -23836,7 +23836,7 @@
         <v>1453</v>
       </c>
       <c r="X34" t="s">
-        <v>1256</v>
+        <v>1226</v>
       </c>
       <c r="Y34">
         <v>26.765999999999998</v>
@@ -23871,7 +23871,7 @@
         <v>1317</v>
       </c>
       <c r="K35" t="s">
-        <v>1095</v>
+        <v>1028</v>
       </c>
       <c r="L35">
         <v>2.4544193550494788</v>
@@ -23904,7 +23904,7 @@
         <v>1455</v>
       </c>
       <c r="X35" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="Y35">
         <v>35.325000000000003</v>
@@ -23939,7 +23939,7 @@
         <v>1319</v>
       </c>
       <c r="K36" t="s">
-        <v>1123</v>
+        <v>1088</v>
       </c>
       <c r="L36">
         <v>0.35051099632091098</v>
@@ -23972,7 +23972,7 @@
         <v>1457</v>
       </c>
       <c r="X36" t="s">
-        <v>1263</v>
+        <v>1252</v>
       </c>
       <c r="Y36">
         <v>38.589750000000002</v>
@@ -24007,7 +24007,7 @@
         <v>1321</v>
       </c>
       <c r="K37" t="s">
-        <v>1021</v>
+        <v>1063</v>
       </c>
       <c r="L37">
         <v>5.5005105319204732</v>
@@ -24040,7 +24040,7 @@
         <v>1459</v>
       </c>
       <c r="X37" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="Y37">
         <v>28.707000000000001</v>
@@ -24075,7 +24075,7 @@
         <v>1323</v>
       </c>
       <c r="K38" t="s">
-        <v>1087</v>
+        <v>1128</v>
       </c>
       <c r="L38">
         <v>1.6757541426674882</v>
@@ -24108,7 +24108,7 @@
         <v>1461</v>
       </c>
       <c r="X38" t="s">
-        <v>1225</v>
+        <v>1235</v>
       </c>
       <c r="Y38">
         <v>13.428000000000001</v>
@@ -24143,7 +24143,7 @@
         <v>1325</v>
       </c>
       <c r="K39" t="s">
-        <v>1099</v>
+        <v>1032</v>
       </c>
       <c r="L39">
         <v>0.39959553615654331</v>
@@ -24176,7 +24176,7 @@
         <v>1463</v>
       </c>
       <c r="X39" t="s">
-        <v>1212</v>
+        <v>1248</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24211,7 +24211,7 @@
         <v>1327</v>
       </c>
       <c r="K40" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="L40">
         <v>1.7832075556426605</v>
@@ -24244,7 +24244,7 @@
         <v>1465</v>
       </c>
       <c r="X40" t="s">
-        <v>1265</v>
+        <v>1254</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24279,7 +24279,7 @@
         <v>1329</v>
       </c>
       <c r="K41" t="s">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="L41">
         <v>23.427729543154012</v>
@@ -24312,7 +24312,7 @@
         <v>1467</v>
       </c>
       <c r="X41" t="s">
-        <v>1246</v>
+        <v>1218</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24347,7 +24347,7 @@
         <v>1331</v>
       </c>
       <c r="K42" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="L42">
         <v>1.4999429400795936</v>
@@ -24382,7 +24382,7 @@
         <v>1333</v>
       </c>
       <c r="K43" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
       <c r="L43">
         <v>55.863958629218203</v>
@@ -24417,7 +24417,7 @@
         <v>1335</v>
       </c>
       <c r="K44" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
       <c r="L44">
         <v>17.068804920122925</v>
@@ -24452,7 +24452,7 @@
         <v>1337</v>
       </c>
       <c r="K45" t="s">
-        <v>1047</v>
+        <v>1144</v>
       </c>
       <c r="L45">
         <v>13.001084297219549</v>
@@ -24487,7 +24487,7 @@
         <v>1339</v>
       </c>
       <c r="K46" t="s">
-        <v>1103</v>
+        <v>1036</v>
       </c>
       <c r="L46">
         <v>3.0756142181007986</v>
@@ -24522,7 +24522,7 @@
         <v>1341</v>
       </c>
       <c r="K47" t="s">
-        <v>1083</v>
+        <v>1054</v>
       </c>
       <c r="L47">
         <v>17.749707845203876</v>
@@ -24557,7 +24557,7 @@
         <v>1343</v>
       </c>
       <c r="K48" t="s">
-        <v>1053</v>
+        <v>1104</v>
       </c>
       <c r="L48">
         <v>2.3372365278937242</v>
@@ -24592,7 +24592,7 @@
         <v>1345</v>
       </c>
       <c r="K49" t="s">
-        <v>1131</v>
+        <v>1042</v>
       </c>
       <c r="L49">
         <v>4.2648673086521249</v>
@@ -24627,7 +24627,7 @@
         <v>1347</v>
       </c>
       <c r="K50" t="s">
-        <v>1045</v>
+        <v>1142</v>
       </c>
       <c r="L50">
         <v>2.8571480649629004</v>
@@ -24662,7 +24662,7 @@
         <v>1349</v>
       </c>
       <c r="K51" t="s">
-        <v>1049</v>
+        <v>1146</v>
       </c>
       <c r="L51">
         <v>9.5169217846211289</v>
@@ -24697,7 +24697,7 @@
         <v>1351</v>
       </c>
       <c r="K52" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="L52">
         <v>33.414563514376454</v>
@@ -24732,7 +24732,7 @@
         <v>1353</v>
       </c>
       <c r="K53" t="s">
-        <v>1093</v>
+        <v>1134</v>
       </c>
       <c r="L53">
         <v>18.904558868579112</v>
@@ -24767,7 +24767,7 @@
         <v>1355</v>
       </c>
       <c r="K54" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="L54">
         <v>15.478330347836801</v>
@@ -24802,7 +24802,7 @@
         <v>1357</v>
       </c>
       <c r="K55" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="L55">
         <v>14.176079891703212</v>
@@ -24837,7 +24837,7 @@
         <v>1359</v>
       </c>
       <c r="K56" t="s">
-        <v>1069</v>
+        <v>1026</v>
       </c>
       <c r="L56">
         <v>0.80973624203950822</v>
@@ -24872,7 +24872,7 @@
         <v>1361</v>
       </c>
       <c r="K57" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
       <c r="L57">
         <v>3.2067222321080848</v>
@@ -24907,7 +24907,7 @@
         <v>1363</v>
       </c>
       <c r="K58" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="L58">
         <v>0.66271354737797783</v>
@@ -24942,7 +24942,7 @@
         <v>1365</v>
       </c>
       <c r="K59" t="s">
-        <v>1091</v>
+        <v>1132</v>
       </c>
       <c r="L59">
         <v>1.8183767824138508</v>
@@ -24977,7 +24977,7 @@
         <v>1367</v>
       </c>
       <c r="K60" t="s">
-        <v>1144</v>
+        <v>1074</v>
       </c>
       <c r="L60">
         <v>0.24904319237866104</v>
@@ -25012,7 +25012,7 @@
         <v>1369</v>
       </c>
       <c r="K61" t="s">
-        <v>1133</v>
+        <v>1044</v>
       </c>
       <c r="L61">
         <v>8.2047875916663029E-2</v>
@@ -25047,7 +25047,7 @@
         <v>1371</v>
       </c>
       <c r="K62" t="s">
-        <v>1043</v>
+        <v>1140</v>
       </c>
       <c r="L62">
         <v>11.861012832193515</v>
@@ -25082,7 +25082,7 @@
         <v>1373</v>
       </c>
       <c r="K63" t="s">
-        <v>1089</v>
+        <v>1130</v>
       </c>
       <c r="L63">
         <v>0.74143826937354373</v>
@@ -25117,7 +25117,7 @@
         <v>1375</v>
       </c>
       <c r="K64" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="L64">
         <v>5.5201095579611916</v>
@@ -25152,7 +25152,7 @@
         <v>1377</v>
       </c>
       <c r="K65" t="s">
-        <v>1037</v>
+        <v>1084</v>
       </c>
       <c r="L65">
         <v>6.8285247240880329</v>
@@ -25187,7 +25187,7 @@
         <v>1379</v>
       </c>
       <c r="K66" t="s">
-        <v>1139</v>
+        <v>1069</v>
       </c>
       <c r="L66">
         <v>14.065249575687433</v>
@@ -25222,7 +25222,7 @@
         <v>1381</v>
       </c>
       <c r="K67" t="s">
-        <v>1146</v>
+        <v>1076</v>
       </c>
       <c r="L67">
         <v>9.3799037679336319</v>
@@ -25257,7 +25257,7 @@
         <v>1383</v>
       </c>
       <c r="K68" t="s">
-        <v>1067</v>
+        <v>1024</v>
       </c>
       <c r="L68">
         <v>42.785830383290261</v>
@@ -25292,7 +25292,7 @@
         <v>1385</v>
       </c>
       <c r="K69" t="s">
-        <v>1101</v>
+        <v>1034</v>
       </c>
       <c r="L69">
         <v>7.8693705940085819</v>
@@ -25327,7 +25327,7 @@
         <v>1387</v>
       </c>
       <c r="K70" t="s">
-        <v>1121</v>
+        <v>1086</v>
       </c>
       <c r="L70">
         <v>19.787589902082505</v>
@@ -25362,7 +25362,7 @@
         <v>1389</v>
       </c>
       <c r="K71" t="s">
-        <v>1081</v>
+        <v>1052</v>
       </c>
       <c r="L71">
         <v>18.319832830101969</v>
@@ -25397,7 +25397,7 @@
         <v>1391</v>
       </c>
       <c r="K72" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="L72">
         <v>6.7551756478058005</v>
@@ -25432,7 +25432,7 @@
         <v>1393</v>
       </c>
       <c r="K73" t="s">
-        <v>1129</v>
+        <v>1040</v>
       </c>
       <c r="L73">
         <v>3.5275797249830152</v>
@@ -25467,7 +25467,7 @@
         <v>1395</v>
       </c>
       <c r="K74" t="s">
-        <v>1061</v>
+        <v>1048</v>
       </c>
       <c r="L74">
         <v>0.89663971235601181</v>
@@ -25502,7 +25502,7 @@
         <v>1397</v>
       </c>
       <c r="K75" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="L75">
         <v>5.9305458091691294</v>
@@ -25537,7 +25537,7 @@
         <v>1399</v>
       </c>
       <c r="K76" t="s">
-        <v>1019</v>
+        <v>1061</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25572,7 +25572,7 @@
         <v>1401</v>
       </c>
       <c r="K77" t="s">
-        <v>1097</v>
+        <v>1030</v>
       </c>
       <c r="L77">
         <v>0.5190595734350465</v>
@@ -25607,7 +25607,7 @@
         <v>1403</v>
       </c>
       <c r="K78" t="s">
-        <v>1057</v>
+        <v>1108</v>
       </c>
       <c r="L78">
         <v>0.29505146981926272</v>
@@ -25642,7 +25642,7 @@
         <v>1405</v>
       </c>
       <c r="K79" t="s">
-        <v>1017</v>
+        <v>1059</v>
       </c>
       <c r="L79">
         <v>0.28737649325389003</v>
@@ -25657,7 +25657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424E33F8-80C7-42DD-A00D-EDB9A0602F79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E283625-3DA9-473B-8CD5-341626B04925}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27126,7 +27126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767C7947-3428-49D6-9477-F1BF57EE6E4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B48EB99D-AB33-4734-8AF9-339D0B93A115}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7CABA30-ECEF-4E2B-AE30-882F07B31A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47372631-D139-4CD6-994D-400CA65F7701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1736,18 +1736,372 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_109</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 109</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_113</t>
   </si>
   <si>
@@ -1796,40 +2150,172 @@
     <t>connecting solar to buses in cluster 106</t>
   </si>
   <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
   </si>
   <si>
     <t>distr_solelc_spv_052</t>
@@ -1898,372 +2384,6 @@
     <t>connecting solar to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_065</t>
   </si>
   <si>
@@ -2312,135 +2432,174 @@
     <t>connecting solar to buses in cluster 94</t>
   </si>
   <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
     <t>e_w304646981-500</t>
   </si>
   <si>
+    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500</t>
+  </si>
+  <si>
+    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
     <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
   </si>
   <si>
@@ -2465,25 +2624,88 @@
     <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
   </si>
   <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
   </si>
   <si>
     <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
@@ -2513,171 +2735,6 @@
     <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
   </si>
   <si>
-    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
     <t>e_BR270-230,e_w304646981-500</t>
   </si>
   <si>
@@ -2702,63 +2759,6 @@
     <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
   </si>
   <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_w953014442-500,e_BR309-500,e_BR220-500,e_BR373-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR387-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR337-500,e_BR276-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500</t>
-  </si>
-  <si>
-    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_012</t>
   </si>
   <si>
@@ -2783,6 +2783,150 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_019</t>
   </si>
   <si>
@@ -2831,28 +2975,184 @@
     <t>connecting wind onshore to buses in cluster 36</t>
   </si>
   <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_wonelc_won_024</t>
@@ -2873,306 +3173,6 @@
     <t>connecting wind onshore to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
     <t>elc_won_012</t>
   </si>
   <si>
@@ -3197,6 +3197,144 @@
     <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
   </si>
   <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+  </si>
+  <si>
     <t>elc_won_019</t>
   </si>
   <si>
@@ -3245,28 +3383,178 @@
     <t>e_BR412-500,e_BR400-500</t>
   </si>
   <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
   </si>
   <si>
     <t>elc_won_024</t>
@@ -3287,292 +3575,142 @@
     <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
   </si>
   <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_069</t>
-  </si>
-  <si>
-    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_023</t>
@@ -3587,22 +3725,28 @@
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_009</t>
@@ -3617,148 +3761,136 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR37-500,e_BR42-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w466973262-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
   </si>
   <si>
     <t>elc_wof_023</t>
@@ -3773,22 +3905,25 @@
     <t>e_BR459-500</t>
   </si>
   <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
   </si>
   <si>
     <t>elc_wof_009</t>
@@ -3801,141 +3936,6 @@
   </si>
   <si>
     <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR37-500,e_BR42-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6969,7 +6969,7 @@
         <v>19</v>
       </c>
       <c r="L11">
-        <v>103.874</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:14">
@@ -7001,7 +7001,7 @@
         <v>19</v>
       </c>
       <c r="L12">
-        <v>35.629296975962831</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -9835,7 +9835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D784C0C-E48D-4599-95B4-E9DEF55BCF33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A753BE09-DC28-4125-A2B1-404D49A3F433}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10073,16 +10073,16 @@
         <v>535</v>
       </c>
       <c r="Y11" t="s">
-        <v>526</v>
+        <v>491</v>
       </c>
       <c r="Z11" t="s">
         <v>769</v>
       </c>
       <c r="AA11">
-        <v>0.93980266520001188</v>
+        <v>0.99240925523869494</v>
       </c>
       <c r="AB11">
-        <v>1103.617804666449</v>
+        <v>139.16365395725984</v>
       </c>
       <c r="AD11" t="s">
         <v>534</v>
@@ -10151,10 +10151,10 @@
         <v>1211</v>
       </c>
       <c r="BC11">
-        <v>0.98574436213546524</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD11">
-        <v>261.35336084980423</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10219,16 +10219,16 @@
         <v>539</v>
       </c>
       <c r="Y12" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="Z12" t="s">
         <v>770</v>
       </c>
       <c r="AA12">
-        <v>0.95679935803281835</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB12">
-        <v>792.01176939833033</v>
+        <v>505.08652809978111</v>
       </c>
       <c r="AD12" t="s">
         <v>534</v>
@@ -10297,10 +10297,10 @@
         <v>1213</v>
       </c>
       <c r="BC12">
-        <v>0.98163861082146986</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD12">
-        <v>336.62546827305243</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10365,16 +10365,16 @@
         <v>541</v>
       </c>
       <c r="Y13" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="Z13" t="s">
         <v>771</v>
       </c>
       <c r="AA13">
-        <v>0.98761622532712257</v>
+        <v>0.99172397756136033</v>
       </c>
       <c r="AB13">
-        <v>227.03586900275366</v>
+        <v>151.72707804172813</v>
       </c>
       <c r="AD13" t="s">
         <v>534</v>
@@ -10443,10 +10443,10 @@
         <v>1215</v>
       </c>
       <c r="BC13">
-        <v>0.98890025255868685</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD13">
-        <v>203.49536975740753</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10511,16 +10511,16 @@
         <v>543</v>
       </c>
       <c r="Y14" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="Z14" t="s">
         <v>772</v>
       </c>
       <c r="AA14">
-        <v>0.99003402112096806</v>
+        <v>0.99431900976645593</v>
       </c>
       <c r="AB14">
-        <v>182.70961278225187</v>
+        <v>104.15148761497397</v>
       </c>
       <c r="AD14" t="s">
         <v>534</v>
@@ -10589,10 +10589,10 @@
         <v>1217</v>
       </c>
       <c r="BC14">
-        <v>0.99481196273061234</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD14">
-        <v>95.114016605440895</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10657,16 +10657,16 @@
         <v>545</v>
       </c>
       <c r="Y15" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="Z15" t="s">
         <v>773</v>
       </c>
       <c r="AA15">
-        <v>0.99466062705491098</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB15">
-        <v>97.888503993298116</v>
+        <v>98.356996715718111</v>
       </c>
       <c r="AD15" t="s">
         <v>534</v>
@@ -10699,10 +10699,10 @@
         <v>1023</v>
       </c>
       <c r="AO15">
-        <v>0.99503039970536677</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP15">
-        <v>91.109338734942796</v>
+        <v>82.249649925934918</v>
       </c>
       <c r="AR15" t="s">
         <v>534</v>
@@ -10732,13 +10732,13 @@
         <v>1218</v>
       </c>
       <c r="BB15" t="s">
-        <v>1219</v>
+        <v>1037</v>
       </c>
       <c r="BC15">
-        <v>0.99374755699184159</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD15">
-        <v>114.62812181623703</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10803,16 +10803,16 @@
         <v>547</v>
       </c>
       <c r="Y16" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="Z16" t="s">
         <v>774</v>
       </c>
       <c r="AA16">
-        <v>0.9944598150968682</v>
+        <v>0.99343259267015904</v>
       </c>
       <c r="AB16">
-        <v>101.5700565574154</v>
+        <v>120.40246771375152</v>
       </c>
       <c r="AD16" t="s">
         <v>534</v>
@@ -10845,10 +10845,10 @@
         <v>1025</v>
       </c>
       <c r="AO16">
-        <v>0.99544059907537386</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP16">
-        <v>83.589016951479763</v>
+        <v>81.597153048545437</v>
       </c>
       <c r="AR16" t="s">
         <v>534</v>
@@ -10875,16 +10875,16 @@
         <v>1158</v>
       </c>
       <c r="BA16" t="s">
+        <v>1219</v>
+      </c>
+      <c r="BB16" t="s">
         <v>1220</v>
       </c>
-      <c r="BB16" t="s">
-        <v>1221</v>
-      </c>
       <c r="BC16">
-        <v>0.99232494426983575</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD16">
-        <v>140.70935505301131</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10949,16 +10949,16 @@
         <v>549</v>
       </c>
       <c r="Y17" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="Z17" t="s">
         <v>775</v>
       </c>
       <c r="AA17">
-        <v>0.99494501873633134</v>
+        <v>0.99012236069527793</v>
       </c>
       <c r="AB17">
-        <v>92.674656500591539</v>
+        <v>181.09005391990564</v>
       </c>
       <c r="AD17" t="s">
         <v>534</v>
@@ -10991,10 +10991,10 @@
         <v>1027</v>
       </c>
       <c r="AO17">
-        <v>0.98829989485605374</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP17">
-        <v>214.50192763901472</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR17" t="s">
         <v>534</v>
@@ -11021,16 +11021,16 @@
         <v>1160</v>
       </c>
       <c r="BA17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="BB17" t="s">
         <v>1222</v>
       </c>
-      <c r="BB17" t="s">
-        <v>1223</v>
-      </c>
       <c r="BC17">
-        <v>0.98775115723917273</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD17">
-        <v>224.56211728183334</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11095,16 +11095,16 @@
         <v>551</v>
       </c>
       <c r="Y18" t="s">
-        <v>506</v>
+        <v>435</v>
       </c>
       <c r="Z18" t="s">
         <v>776</v>
       </c>
       <c r="AA18">
-        <v>0.99438812565699364</v>
+        <v>0.98990296758392993</v>
       </c>
       <c r="AB18">
-        <v>102.88436295511657</v>
+        <v>185.11226096128556</v>
       </c>
       <c r="AD18" t="s">
         <v>534</v>
@@ -11137,10 +11137,10 @@
         <v>1029</v>
       </c>
       <c r="AO18">
-        <v>0.99677419959133018</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP18">
-        <v>59.139674158947656</v>
+        <v>43.412641259119624</v>
       </c>
       <c r="AR18" t="s">
         <v>534</v>
@@ -11167,16 +11167,16 @@
         <v>1162</v>
       </c>
       <c r="BA18" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="BB18" t="s">
-        <v>1225</v>
+        <v>1097</v>
       </c>
       <c r="BC18">
-        <v>0.99032129621526932</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD18">
-        <v>177.44290272006148</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11241,16 +11241,16 @@
         <v>553</v>
       </c>
       <c r="Y19" t="s">
-        <v>523</v>
+        <v>456</v>
       </c>
       <c r="Z19" t="s">
         <v>777</v>
       </c>
       <c r="AA19">
-        <v>0.99643191679577148</v>
+        <v>0.99377714174527498</v>
       </c>
       <c r="AB19">
-        <v>65.414858744189985</v>
+        <v>114.08573466995766</v>
       </c>
       <c r="AD19" t="s">
         <v>534</v>
@@ -11283,10 +11283,10 @@
         <v>1031</v>
       </c>
       <c r="AO19">
-        <v>0.99766813121902409</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP19">
-        <v>42.750927651225993</v>
+        <v>105.47547991621673</v>
       </c>
       <c r="AR19" t="s">
         <v>534</v>
@@ -11313,16 +11313,16 @@
         <v>1164</v>
       </c>
       <c r="BA19" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="BB19" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="BC19">
-        <v>0.99420451954813838</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD19">
-        <v>106.25047495079694</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11387,16 +11387,16 @@
         <v>555</v>
       </c>
       <c r="Y20" t="s">
-        <v>472</v>
+        <v>525</v>
       </c>
       <c r="Z20" t="s">
         <v>778</v>
       </c>
       <c r="AA20">
-        <v>0.99649411432543766</v>
+        <v>0.99516685156772267</v>
       </c>
       <c r="AB20">
-        <v>64.274570700309781</v>
+        <v>88.60772125841865</v>
       </c>
       <c r="AD20" t="s">
         <v>534</v>
@@ -11429,10 +11429,10 @@
         <v>1033</v>
       </c>
       <c r="AO20">
-        <v>0.99760247912344124</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP20">
-        <v>43.95454940357709</v>
+        <v>195.31167947327185</v>
       </c>
       <c r="AR20" t="s">
         <v>534</v>
@@ -11459,16 +11459,16 @@
         <v>1166</v>
       </c>
       <c r="BA20" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="BB20" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="BC20">
-        <v>0.96863461872110523</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD20">
-        <v>575.0319901130714</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11533,16 +11533,16 @@
         <v>557</v>
       </c>
       <c r="Y21" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="Z21" t="s">
         <v>779</v>
       </c>
       <c r="AA21">
-        <v>0.97907421743006762</v>
+        <v>0.9914627894548943</v>
       </c>
       <c r="AB21">
-        <v>383.63934711542669</v>
+        <v>156.51552666027055</v>
       </c>
       <c r="AD21" t="s">
         <v>534</v>
@@ -11575,10 +11575,10 @@
         <v>1035</v>
       </c>
       <c r="AO21">
-        <v>0.99336049451151065</v>
+        <v>0.99499049355022928</v>
       </c>
       <c r="AP21">
-        <v>121.72426728897108</v>
+        <v>91.840951579129481</v>
       </c>
       <c r="AR21" t="s">
         <v>534</v>
@@ -11605,16 +11605,16 @@
         <v>1168</v>
       </c>
       <c r="BA21" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="BB21" t="s">
-        <v>1075</v>
+        <v>1229</v>
       </c>
       <c r="BC21">
-        <v>0.99098965084511315</v>
+        <v>0.99526086651282741</v>
       </c>
       <c r="BD21">
-        <v>165.18973450625904</v>
+        <v>86.884113931497708</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11679,16 +11679,16 @@
         <v>559</v>
       </c>
       <c r="Y22" t="s">
-        <v>426</v>
+        <v>500</v>
       </c>
       <c r="Z22" t="s">
         <v>780</v>
       </c>
       <c r="AA22">
-        <v>0.99558768376711515</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB22">
-        <v>80.892464269556413</v>
+        <v>409.70769939155917</v>
       </c>
       <c r="AD22" t="s">
         <v>534</v>
@@ -11721,10 +11721,10 @@
         <v>1037</v>
       </c>
       <c r="AO22">
-        <v>0.99759498179797546</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP22">
-        <v>44.092000370450322</v>
+        <v>49.645668091582088</v>
       </c>
       <c r="AR22" t="s">
         <v>534</v>
@@ -11751,16 +11751,16 @@
         <v>1170</v>
       </c>
       <c r="BA22" t="s">
+        <v>1230</v>
+      </c>
+      <c r="BB22" t="s">
         <v>1231</v>
       </c>
-      <c r="BB22" t="s">
-        <v>1232</v>
-      </c>
       <c r="BC22">
-        <v>0.99053278045305837</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD22">
-        <v>173.56569169392964</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11825,16 +11825,16 @@
         <v>561</v>
       </c>
       <c r="Y23" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="Z23" t="s">
         <v>781</v>
       </c>
       <c r="AA23">
-        <v>0.99324569511004301</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB23">
-        <v>123.82892298254488</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD23" t="s">
         <v>534</v>
@@ -11867,10 +11867,10 @@
         <v>1039</v>
       </c>
       <c r="AO23">
-        <v>0.99551365545858539</v>
+        <v>0.99746043308117838</v>
       </c>
       <c r="AP23">
-        <v>82.249649925934918</v>
+        <v>46.558726845063177</v>
       </c>
       <c r="AR23" t="s">
         <v>534</v>
@@ -11897,16 +11897,16 @@
         <v>1172</v>
       </c>
       <c r="BA23" t="s">
+        <v>1232</v>
+      </c>
+      <c r="BB23" t="s">
         <v>1233</v>
       </c>
-      <c r="BB23" t="s">
-        <v>1234</v>
-      </c>
       <c r="BC23">
-        <v>0.98488330873784669</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD23">
-        <v>277.13933980614473</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11971,16 +11971,16 @@
         <v>563</v>
       </c>
       <c r="Y24" t="s">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="Z24" t="s">
         <v>782</v>
       </c>
       <c r="AA24">
-        <v>0.99419165427276146</v>
+        <v>0.99593583828988941</v>
       </c>
       <c r="AB24">
-        <v>106.48633833270691</v>
+        <v>74.509631352026517</v>
       </c>
       <c r="AD24" t="s">
         <v>534</v>
@@ -12010,13 +12010,13 @@
         <v>1040</v>
       </c>
       <c r="AN24" t="s">
-        <v>1041</v>
+        <v>823</v>
       </c>
       <c r="AO24">
-        <v>0.99554924619735208</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP24">
-        <v>81.597153048545437</v>
+        <v>819.02093721560016</v>
       </c>
       <c r="AR24" t="s">
         <v>534</v>
@@ -12043,16 +12043,16 @@
         <v>1174</v>
       </c>
       <c r="BA24" t="s">
+        <v>1234</v>
+      </c>
+      <c r="BB24" t="s">
         <v>1235</v>
       </c>
-      <c r="BB24" t="s">
-        <v>1236</v>
-      </c>
       <c r="BC24">
-        <v>0.99526086651282741</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD24">
-        <v>86.884113931497708</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12117,16 +12117,16 @@
         <v>565</v>
       </c>
       <c r="Y25" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="Z25" t="s">
         <v>783</v>
       </c>
       <c r="AA25">
-        <v>0.99198935558098356</v>
+        <v>0.9621480095608167</v>
       </c>
       <c r="AB25">
-        <v>146.8618143486346</v>
+        <v>693.95315805169378</v>
       </c>
       <c r="AD25" t="s">
         <v>534</v>
@@ -12153,16 +12153,16 @@
         <v>904</v>
       </c>
       <c r="AM25" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="AN25" t="s">
-        <v>1043</v>
+        <v>819</v>
       </c>
       <c r="AO25">
-        <v>0.99083036293819104</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP25">
-        <v>168.11001279983091</v>
+        <v>256.69809569401372</v>
       </c>
       <c r="AR25" t="s">
         <v>534</v>
@@ -12189,16 +12189,16 @@
         <v>1176</v>
       </c>
       <c r="BA25" t="s">
+        <v>1236</v>
+      </c>
+      <c r="BB25" t="s">
         <v>1237</v>
       </c>
-      <c r="BB25" t="s">
-        <v>1238</v>
-      </c>
       <c r="BC25">
-        <v>0.98946506962487613</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD25">
-        <v>193.14039021060518</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12263,16 +12263,16 @@
         <v>567</v>
       </c>
       <c r="Y26" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="Z26" t="s">
         <v>784</v>
       </c>
       <c r="AA26">
-        <v>0.96238190390083644</v>
+        <v>0.98916941127667946</v>
       </c>
       <c r="AB26">
-        <v>689.665095151331</v>
+        <v>198.56079326087576</v>
       </c>
       <c r="AD26" t="s">
         <v>534</v>
@@ -12299,16 +12299,16 @@
         <v>906</v>
       </c>
       <c r="AM26" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="AN26" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="AO26">
-        <v>0.9976320377495026</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP26">
-        <v>43.412641259119624</v>
+        <v>184.02231422223667</v>
       </c>
       <c r="AR26" t="s">
         <v>534</v>
@@ -12335,16 +12335,16 @@
         <v>1178</v>
       </c>
       <c r="BA26" t="s">
+        <v>1238</v>
+      </c>
+      <c r="BB26" t="s">
         <v>1239</v>
       </c>
-      <c r="BB26" t="s">
-        <v>1240</v>
-      </c>
       <c r="BC26">
-        <v>0.99314574070258299</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD26">
-        <v>125.66142045264445</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12409,16 +12409,16 @@
         <v>569</v>
       </c>
       <c r="Y27" t="s">
-        <v>528</v>
+        <v>438</v>
       </c>
       <c r="Z27" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="AA27">
-        <v>0.96316770855847034</v>
+        <v>0.97159134368321343</v>
       </c>
       <c r="AB27">
-        <v>675.25867642804383</v>
+        <v>520.82536580775354</v>
       </c>
       <c r="AD27" t="s">
         <v>534</v>
@@ -12445,16 +12445,16 @@
         <v>908</v>
       </c>
       <c r="AM27" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="AN27" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="AO27">
-        <v>0.99684152237002188</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP27">
-        <v>57.905423216266421</v>
+        <v>69.568618111619969</v>
       </c>
       <c r="AR27" t="s">
         <v>534</v>
@@ -12481,16 +12481,16 @@
         <v>1180</v>
       </c>
       <c r="BA27" t="s">
+        <v>1240</v>
+      </c>
+      <c r="BB27" t="s">
         <v>1241</v>
       </c>
-      <c r="BB27" t="s">
-        <v>1242</v>
-      </c>
       <c r="BC27">
-        <v>0.9933934749176847</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD27">
-        <v>121.11962650911367</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12555,16 +12555,16 @@
         <v>571</v>
       </c>
       <c r="Y28" t="s">
-        <v>484</v>
+        <v>449</v>
       </c>
       <c r="Z28" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AA28">
-        <v>0.9951089264264793</v>
+        <v>0.99359614530212825</v>
       </c>
       <c r="AB28">
-        <v>89.669682181211982</v>
+        <v>117.40400279431638</v>
       </c>
       <c r="AD28" t="s">
         <v>534</v>
@@ -12591,16 +12591,16 @@
         <v>910</v>
       </c>
       <c r="AM28" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="AN28" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="AO28">
-        <v>0.99532453653339104</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP28">
-        <v>85.716830221163534</v>
+        <v>114.668395037126</v>
       </c>
       <c r="AR28" t="s">
         <v>534</v>
@@ -12627,16 +12627,16 @@
         <v>1182</v>
       </c>
       <c r="BA28" t="s">
+        <v>1242</v>
+      </c>
+      <c r="BB28" t="s">
         <v>1243</v>
       </c>
-      <c r="BB28" t="s">
-        <v>1099</v>
-      </c>
       <c r="BC28">
-        <v>0.99418931598784899</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD28">
-        <v>106.52920688943452</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12701,16 +12701,16 @@
         <v>573</v>
       </c>
       <c r="Y29" t="s">
-        <v>434</v>
+        <v>518</v>
       </c>
       <c r="Z29" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AA29">
-        <v>0.98666519734623237</v>
+        <v>0.99488082982009873</v>
       </c>
       <c r="AB29">
-        <v>244.47138198573927</v>
+        <v>93.851453298190577</v>
       </c>
       <c r="AD29" t="s">
         <v>534</v>
@@ -12737,16 +12737,16 @@
         <v>912</v>
       </c>
       <c r="AM29" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AN29" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="AO29">
-        <v>0.99593828267147511</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP29">
-        <v>74.464817689622748</v>
+        <v>58.41269784431158</v>
       </c>
       <c r="AR29" t="s">
         <v>534</v>
@@ -12779,10 +12779,10 @@
         <v>1245</v>
       </c>
       <c r="BC29">
-        <v>0.98691003029105739</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD29">
-        <v>239.98277799728109</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12847,16 +12847,16 @@
         <v>575</v>
       </c>
       <c r="Y30" t="s">
-        <v>425</v>
+        <v>513</v>
       </c>
       <c r="Z30" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA30">
-        <v>0.99750070245826261</v>
+        <v>0.99557743229498485</v>
       </c>
       <c r="AB30">
-        <v>45.820454931853</v>
+        <v>81.080407925277868</v>
       </c>
       <c r="AD30" t="s">
         <v>534</v>
@@ -12883,16 +12883,16 @@
         <v>914</v>
       </c>
       <c r="AM30" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="AN30" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="AO30">
-        <v>0.9955955730654259</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP30">
-        <v>80.747827133859133</v>
+        <v>86.673039153654699</v>
       </c>
       <c r="AR30" t="s">
         <v>534</v>
@@ -12925,10 +12925,10 @@
         <v>1247</v>
       </c>
       <c r="BC30">
-        <v>0.99834679070917032</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD30">
-        <v>30.308836998544216</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12993,16 +12993,16 @@
         <v>577</v>
       </c>
       <c r="Y31" t="s">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="Z31" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AA31">
-        <v>0.99395341117186964</v>
+        <v>0.99401156108202648</v>
       </c>
       <c r="AB31">
-        <v>110.85412851572337</v>
+        <v>109.78804682951412</v>
       </c>
       <c r="AD31" t="s">
         <v>534</v>
@@ -13029,16 +13029,16 @@
         <v>916</v>
       </c>
       <c r="AM31" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="AN31" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="AO31">
-        <v>0.99671693937496686</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP31">
-        <v>60.189444792275019</v>
+        <v>151.70176382244892</v>
       </c>
       <c r="AR31" t="s">
         <v>534</v>
@@ -13071,10 +13071,10 @@
         <v>1249</v>
       </c>
       <c r="BC31">
-        <v>0.99401640271965719</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD31">
-        <v>109.69928347295183</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13139,16 +13139,16 @@
         <v>579</v>
       </c>
       <c r="Y32" t="s">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="Z32" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="AA32">
-        <v>0.98322732678073066</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB32">
-        <v>307.49900901993823</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD32" t="s">
         <v>534</v>
@@ -13175,16 +13175,16 @@
         <v>918</v>
       </c>
       <c r="AM32" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="AN32" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="AO32">
-        <v>0.99244513691456471</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP32">
-        <v>138.50582323297994</v>
+        <v>79.007487588415231</v>
       </c>
       <c r="AR32" t="s">
         <v>534</v>
@@ -13217,10 +13217,10 @@
         <v>1251</v>
       </c>
       <c r="BC32">
-        <v>0.99054926914187857</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD32">
-        <v>173.26339906555947</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13285,16 +13285,16 @@
         <v>581</v>
       </c>
       <c r="Y33" t="s">
-        <v>437</v>
+        <v>477</v>
       </c>
       <c r="Z33" t="s">
         <v>790</v>
       </c>
       <c r="AA33">
-        <v>0.9974199781412052</v>
+        <v>0.99726809134187266</v>
       </c>
       <c r="AB33">
-        <v>47.300400744571718</v>
+        <v>50.0849920656675</v>
       </c>
       <c r="AD33" t="s">
         <v>534</v>
@@ -13321,16 +13321,16 @@
         <v>920</v>
       </c>
       <c r="AM33" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="AN33" t="s">
-        <v>842</v>
+        <v>1057</v>
       </c>
       <c r="AO33">
-        <v>0.97416725971121887</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP33">
-        <v>473.60023862765331</v>
+        <v>79.268397406829976</v>
       </c>
       <c r="AR33" t="s">
         <v>534</v>
@@ -13363,10 +13363,10 @@
         <v>1253</v>
       </c>
       <c r="BC33">
-        <v>0.98027195861782945</v>
+        <v>0.99563011519444145</v>
       </c>
       <c r="BD33">
-        <v>361.68075867312689</v>
+        <v>80.114554768572972</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13431,16 +13431,16 @@
         <v>583</v>
       </c>
       <c r="Y34" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="Z34" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="AA34">
-        <v>0.99336837071349593</v>
+        <v>0.97962408753770291</v>
       </c>
       <c r="AB34">
-        <v>121.57987025257442</v>
+        <v>373.55839514211272</v>
       </c>
       <c r="AD34" t="s">
         <v>534</v>
@@ -13467,16 +13467,16 @@
         <v>922</v>
       </c>
       <c r="AM34" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AN34" t="s">
         <v>1059</v>
       </c>
-      <c r="AN34" t="s">
-        <v>1060</v>
-      </c>
       <c r="AO34">
-        <v>0.99760255773158468</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP34">
-        <v>43.953108254279897</v>
+        <v>43.581147571379539</v>
       </c>
       <c r="AR34" t="s">
         <v>534</v>
@@ -13509,10 +13509,10 @@
         <v>1255</v>
       </c>
       <c r="BC34">
-        <v>0.98125520899414764</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD34">
-        <v>343.65450177395917</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13577,16 +13577,16 @@
         <v>585</v>
       </c>
       <c r="Y35" t="s">
-        <v>443</v>
+        <v>498</v>
       </c>
       <c r="Z35" t="s">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="AA35">
-        <v>0.99379477670057537</v>
+        <v>0.99098167665935155</v>
       </c>
       <c r="AB35">
-        <v>113.7624271561186</v>
+        <v>165.33592791188894</v>
       </c>
       <c r="AD35" t="s">
         <v>534</v>
@@ -13613,16 +13613,16 @@
         <v>924</v>
       </c>
       <c r="AM35" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AN35" t="s">
         <v>1061</v>
       </c>
-      <c r="AN35" t="s">
-        <v>1062</v>
-      </c>
       <c r="AO35">
-        <v>0.99352359657507616</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP35">
-        <v>118.7340627902709</v>
+        <v>151.17817104385733</v>
       </c>
       <c r="AR35" t="s">
         <v>534</v>
@@ -13655,10 +13655,10 @@
         <v>1257</v>
       </c>
       <c r="BC35">
-        <v>0.9959052853503485</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD35">
-        <v>75.06976857694373</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13723,16 +13723,16 @@
         <v>587</v>
       </c>
       <c r="Y36" t="s">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="Z36" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="AA36">
-        <v>0.9961866142254362</v>
+        <v>0.98485684158558628</v>
       </c>
       <c r="AB36">
-        <v>69.91207253366963</v>
+        <v>277.62457093091871</v>
       </c>
       <c r="AD36" t="s">
         <v>534</v>
@@ -13759,16 +13759,16 @@
         <v>926</v>
       </c>
       <c r="AM36" t="s">
+        <v>1062</v>
+      </c>
+      <c r="AN36" t="s">
         <v>1063</v>
       </c>
-      <c r="AN36" t="s">
-        <v>1064</v>
-      </c>
       <c r="AO36">
-        <v>0.99433447571906541</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP36">
-        <v>103.86794515046822</v>
+        <v>57.146786340912868</v>
       </c>
       <c r="AR36" t="s">
         <v>534</v>
@@ -13801,10 +13801,10 @@
         <v>1259</v>
       </c>
       <c r="BC36">
-        <v>0.99563011519444145</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD36">
-        <v>80.114554768572972</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13869,16 +13869,16 @@
         <v>589</v>
       </c>
       <c r="Y37" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Z37" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="AA37">
-        <v>0.99240925523869494</v>
+        <v>0.98211145389932475</v>
       </c>
       <c r="AB37">
-        <v>139.16365395725984</v>
+        <v>327.95667851237977</v>
       </c>
       <c r="AD37" t="s">
         <v>534</v>
@@ -13905,16 +13905,16 @@
         <v>928</v>
       </c>
       <c r="AM37" t="s">
+        <v>1064</v>
+      </c>
+      <c r="AN37" t="s">
         <v>1065</v>
       </c>
-      <c r="AN37" t="s">
-        <v>1066</v>
-      </c>
       <c r="AO37">
-        <v>0.97020178001960844</v>
+        <v>0.99488275259079373</v>
       </c>
       <c r="AP37">
-        <v>546.30069964051177</v>
+        <v>93.81620250211445</v>
       </c>
       <c r="AR37" t="s">
         <v>534</v>
@@ -13944,13 +13944,13 @@
         <v>1260</v>
       </c>
       <c r="BB37" t="s">
-        <v>1261</v>
+        <v>1247</v>
       </c>
       <c r="BC37">
-        <v>0.99665799830099</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD37">
-        <v>61.270031148516708</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14015,16 +14015,16 @@
         <v>591</v>
       </c>
       <c r="Y38" t="s">
-        <v>532</v>
+        <v>467</v>
       </c>
       <c r="Z38" t="s">
-        <v>769</v>
+        <v>793</v>
       </c>
       <c r="AA38">
-        <v>0.97244982574001193</v>
+        <v>0.99654205356515035</v>
       </c>
       <c r="AB38">
-        <v>505.08652809978111</v>
+        <v>63.395684638909763</v>
       </c>
       <c r="AD38" t="s">
         <v>534</v>
@@ -14051,16 +14051,16 @@
         <v>930</v>
       </c>
       <c r="AM38" t="s">
+        <v>1066</v>
+      </c>
+      <c r="AN38" t="s">
         <v>1067</v>
       </c>
-      <c r="AN38" t="s">
-        <v>1068</v>
-      </c>
       <c r="AO38">
-        <v>0.99693672852577231</v>
+        <v>0.99663220850609069</v>
       </c>
       <c r="AP38">
-        <v>56.159977027506663</v>
+        <v>61.742844055003644</v>
       </c>
       <c r="AR38" t="s">
         <v>534</v>
@@ -14087,16 +14087,16 @@
         <v>1202</v>
       </c>
       <c r="BA38" t="s">
+        <v>1261</v>
+      </c>
+      <c r="BB38" t="s">
         <v>1262</v>
       </c>
-      <c r="BB38" t="s">
-        <v>1263</v>
-      </c>
       <c r="BC38">
-        <v>0.99203097418485064</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD38">
-        <v>146.09880661107059</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14161,16 +14161,16 @@
         <v>593</v>
       </c>
       <c r="Y39" t="s">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="Z39" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AA39">
-        <v>0.99172397756136033</v>
+        <v>0.99504817442297822</v>
       </c>
       <c r="AB39">
-        <v>151.72707804172813</v>
+        <v>90.78346891206678</v>
       </c>
       <c r="AD39" t="s">
         <v>534</v>
@@ -14197,16 +14197,16 @@
         <v>932</v>
       </c>
       <c r="AM39" t="s">
+        <v>1068</v>
+      </c>
+      <c r="AN39" t="s">
         <v>1069</v>
       </c>
-      <c r="AN39" t="s">
-        <v>1070</v>
-      </c>
       <c r="AO39">
-        <v>0.99478775228549088</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP39">
-        <v>95.557874766001078</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR39" t="s">
         <v>534</v>
@@ -14233,16 +14233,16 @@
         <v>1204</v>
       </c>
       <c r="BA39" t="s">
+        <v>1263</v>
+      </c>
+      <c r="BB39" t="s">
         <v>1264</v>
       </c>
-      <c r="BB39" t="s">
-        <v>1265</v>
-      </c>
       <c r="BC39">
-        <v>0.97821242976023937</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD39">
-        <v>399.43878772894504</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14307,16 +14307,16 @@
         <v>595</v>
       </c>
       <c r="Y40" t="s">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="Z40" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA40">
-        <v>0.99431900976645593</v>
+        <v>0.99470247457730832</v>
       </c>
       <c r="AB40">
-        <v>104.15148761497397</v>
+        <v>97.121299416014665</v>
       </c>
       <c r="AD40" t="s">
         <v>534</v>
@@ -14343,16 +14343,16 @@
         <v>934</v>
       </c>
       <c r="AM40" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AN40" t="s">
         <v>1071</v>
       </c>
-      <c r="AN40" t="s">
-        <v>838</v>
-      </c>
       <c r="AO40">
-        <v>0.98674094240398891</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP40">
-        <v>243.0827225935364</v>
+        <v>83.589016951479763</v>
       </c>
       <c r="AR40" t="s">
         <v>534</v>
@@ -14379,16 +14379,16 @@
         <v>1206</v>
       </c>
       <c r="BA40" t="s">
+        <v>1265</v>
+      </c>
+      <c r="BB40" t="s">
         <v>1266</v>
       </c>
-      <c r="BB40" t="s">
-        <v>1267</v>
-      </c>
       <c r="BC40">
-        <v>0.95713629889852414</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD40">
-        <v>785.83452019372396</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14453,16 +14453,16 @@
         <v>597</v>
       </c>
       <c r="Y41" t="s">
-        <v>430</v>
+        <v>463</v>
       </c>
       <c r="Z41" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA41">
-        <v>0.9946350729064154</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB41">
-        <v>98.356996715718111</v>
+        <v>82.539922240185263</v>
       </c>
       <c r="AD41" t="s">
         <v>534</v>
@@ -14495,10 +14495,10 @@
         <v>1073</v>
       </c>
       <c r="AO41">
-        <v>0.98452519237182756</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP41">
-        <v>283.70480651649393</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR41" t="s">
         <v>534</v>
@@ -14525,16 +14525,16 @@
         <v>1208</v>
       </c>
       <c r="BA41" t="s">
+        <v>1267</v>
+      </c>
+      <c r="BB41" t="s">
         <v>1268</v>
       </c>
-      <c r="BB41" t="s">
-        <v>1263</v>
-      </c>
       <c r="BC41">
-        <v>0.98806872821788805</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD41">
-        <v>218.73998267205184</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14599,16 +14599,16 @@
         <v>599</v>
       </c>
       <c r="Y42" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="Z42" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AA42">
-        <v>0.99343259267015904</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB42">
-        <v>120.40246771375152</v>
+        <v>637.85920701836687</v>
       </c>
       <c r="AD42" t="s">
         <v>534</v>
@@ -14641,10 +14641,10 @@
         <v>1075</v>
       </c>
       <c r="AO42">
-        <v>0.99679967385551038</v>
+        <v>0.99677419959133018</v>
       </c>
       <c r="AP42">
-        <v>58.672645982308907</v>
+        <v>59.139674158947656</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14709,16 +14709,16 @@
         <v>601</v>
       </c>
       <c r="Y43" t="s">
-        <v>527</v>
+        <v>478</v>
       </c>
       <c r="Z43" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AA43">
-        <v>0.95261480241426988</v>
+        <v>0.99344074878931121</v>
       </c>
       <c r="AB43">
-        <v>868.72862240505196</v>
+        <v>120.25293886262826</v>
       </c>
       <c r="AD43" t="s">
         <v>534</v>
@@ -14751,10 +14751,10 @@
         <v>1077</v>
       </c>
       <c r="AO43">
-        <v>0.99414234808301016</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP43">
-        <v>107.39028514481463</v>
+        <v>42.750927651225993</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14819,16 +14819,16 @@
         <v>603</v>
       </c>
       <c r="Y44" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="Z44" t="s">
-        <v>800</v>
+        <v>770</v>
       </c>
       <c r="AA44">
-        <v>0.97404342257401955</v>
+        <v>0.99459650548991607</v>
       </c>
       <c r="AB44">
-        <v>475.8705861429753</v>
+        <v>99.064066018204684</v>
       </c>
       <c r="AD44" t="s">
         <v>534</v>
@@ -14861,10 +14861,10 @@
         <v>1079</v>
       </c>
       <c r="AO44">
-        <v>0.99403730604060547</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP44">
-        <v>109.31605592223302</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14929,16 +14929,16 @@
         <v>605</v>
       </c>
       <c r="Y45" t="s">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="Z45" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="AA45">
-        <v>0.98762421667584677</v>
+        <v>0.99655727877565281</v>
       </c>
       <c r="AB45">
-        <v>226.88936094280919</v>
+        <v>63.116555779697698</v>
       </c>
       <c r="AD45" t="s">
         <v>534</v>
@@ -14971,10 +14971,10 @@
         <v>1081</v>
       </c>
       <c r="AO45">
-        <v>0.99105808324017197</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP45">
-        <v>163.93514059684662</v>
+        <v>121.72426728897108</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15039,16 +15039,16 @@
         <v>607</v>
       </c>
       <c r="Y46" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="Z46" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AA46">
-        <v>0.98775140142897844</v>
+        <v>0.99221351039035977</v>
       </c>
       <c r="AB46">
-        <v>224.55764046872929</v>
+        <v>142.75230951007163</v>
       </c>
       <c r="AD46" t="s">
         <v>534</v>
@@ -15081,10 +15081,10 @@
         <v>1083</v>
       </c>
       <c r="AO46">
-        <v>0.9974675531234084</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP46">
-        <v>46.428192737512276</v>
+        <v>44.092000370450322</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15149,16 +15149,16 @@
         <v>609</v>
       </c>
       <c r="Y47" t="s">
-        <v>495</v>
+        <v>447</v>
       </c>
       <c r="Z47" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="AA47">
-        <v>0.99647006537565563</v>
+        <v>0.99067174034238459</v>
       </c>
       <c r="AB47">
-        <v>64.715468112981057</v>
+        <v>171.01809372294977</v>
       </c>
       <c r="AD47" t="s">
         <v>534</v>
@@ -15191,10 +15191,10 @@
         <v>1085</v>
       </c>
       <c r="AO47">
-        <v>0.99534886842510228</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP47">
-        <v>85.270745539791065</v>
+        <v>138.50582323297994</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15259,16 +15259,16 @@
         <v>611</v>
       </c>
       <c r="Y48" t="s">
-        <v>492</v>
+        <v>418</v>
       </c>
       <c r="Z48" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AA48">
-        <v>0.96480371616361149</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB48">
-        <v>645.26520366712316</v>
+        <v>67.023399161603095</v>
       </c>
       <c r="AD48" t="s">
         <v>534</v>
@@ -15298,13 +15298,13 @@
         <v>1086</v>
       </c>
       <c r="AN48" t="s">
-        <v>1087</v>
+        <v>844</v>
       </c>
       <c r="AO48">
-        <v>0.99445933293330402</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP48">
-        <v>101.57889622275951</v>
+        <v>473.60023862765331</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15369,16 +15369,16 @@
         <v>613</v>
       </c>
       <c r="Y49" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="Z49" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="AA49">
-        <v>0.99267004448650609</v>
+        <v>0.98416341622871006</v>
       </c>
       <c r="AB49">
-        <v>134.38251774738842</v>
+        <v>290.33736914031488</v>
       </c>
       <c r="AD49" t="s">
         <v>534</v>
@@ -15405,16 +15405,16 @@
         <v>952</v>
       </c>
       <c r="AM49" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AN49" t="s">
         <v>1088</v>
       </c>
-      <c r="AN49" t="s">
-        <v>1089</v>
-      </c>
       <c r="AO49">
-        <v>0.9961850470371636</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP49">
-        <v>69.94080431866837</v>
+        <v>43.953108254279897</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15479,16 +15479,16 @@
         <v>615</v>
       </c>
       <c r="Y50" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="Z50" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="AA50">
-        <v>0.9948848527457459</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB50">
-        <v>93.777699661325343</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD50" t="s">
         <v>534</v>
@@ -15515,16 +15515,16 @@
         <v>954</v>
       </c>
       <c r="AM50" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AN50" t="s">
         <v>1090</v>
       </c>
-      <c r="AN50" t="s">
-        <v>1091</v>
-      </c>
       <c r="AO50">
-        <v>0.99710531380540124</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP50">
-        <v>53.069246900976879</v>
+        <v>118.7340627902709</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15589,16 +15589,16 @@
         <v>617</v>
       </c>
       <c r="Y51" t="s">
-        <v>524</v>
+        <v>432</v>
       </c>
       <c r="Z51" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="AA51">
-        <v>0.9922030648239526</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB51">
-        <v>142.94381156086857</v>
+        <v>81.000126667143434</v>
       </c>
       <c r="AD51" t="s">
         <v>534</v>
@@ -15625,16 +15625,16 @@
         <v>956</v>
       </c>
       <c r="AM51" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AN51" t="s">
         <v>1092</v>
       </c>
-      <c r="AN51" t="s">
-        <v>1093</v>
-      </c>
       <c r="AO51">
-        <v>0.99424679200457</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP51">
-        <v>105.47547991621673</v>
+        <v>103.86794515046822</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15699,16 +15699,16 @@
         <v>619</v>
       </c>
       <c r="Y52" t="s">
-        <v>468</v>
+        <v>516</v>
       </c>
       <c r="Z52" t="s">
-        <v>784</v>
+        <v>806</v>
       </c>
       <c r="AA52">
-        <v>0.96942910386940295</v>
+        <v>0.99390501557434718</v>
       </c>
       <c r="AB52">
-        <v>560.46642906094564</v>
+        <v>111.7413811369688</v>
       </c>
       <c r="AD52" t="s">
         <v>534</v>
@@ -15735,16 +15735,16 @@
         <v>958</v>
       </c>
       <c r="AM52" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="AN52" t="s">
-        <v>1095</v>
+        <v>776</v>
       </c>
       <c r="AO52">
-        <v>0.98934663566509429</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP52">
-        <v>195.31167947327185</v>
+        <v>243.0827225935364</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15809,16 +15809,16 @@
         <v>621</v>
       </c>
       <c r="Y53" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="Z53" t="s">
-        <v>808</v>
+        <v>783</v>
       </c>
       <c r="AA53">
-        <v>0.99726809134187266</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB53">
-        <v>50.0849920656675</v>
+        <v>470.66510807906917</v>
       </c>
       <c r="AD53" t="s">
         <v>534</v>
@@ -15845,16 +15845,16 @@
         <v>960</v>
       </c>
       <c r="AM53" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="AN53" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="AO53">
-        <v>0.99499049355022928</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP53">
-        <v>91.840951579129481</v>
+        <v>283.70480651649393</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15919,16 +15919,16 @@
         <v>623</v>
       </c>
       <c r="Y54" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="Z54" t="s">
-        <v>769</v>
+        <v>807</v>
       </c>
       <c r="AA54">
-        <v>0.97962408753770291</v>
+        <v>0.9882282251528024</v>
       </c>
       <c r="AB54">
-        <v>373.55839514211272</v>
+        <v>215.81587219862183</v>
       </c>
       <c r="AD54" t="s">
         <v>534</v>
@@ -15955,16 +15955,16 @@
         <v>962</v>
       </c>
       <c r="AM54" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="AN54" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="AO54">
-        <v>0.99729205446773184</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP54">
-        <v>49.645668091582088</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16029,16 +16029,16 @@
         <v>625</v>
       </c>
       <c r="Y55" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="Z55" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
       <c r="AA55">
-        <v>0.99098167665935155</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB55">
-        <v>165.33592791188894</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD55" t="s">
         <v>534</v>
@@ -16065,16 +16065,16 @@
         <v>964</v>
       </c>
       <c r="AM55" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="AN55" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="AO55">
-        <v>0.99746043308117838</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP55">
-        <v>46.558726845063177</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16139,16 +16139,16 @@
         <v>627</v>
       </c>
       <c r="Y56" t="s">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="Z56" t="s">
         <v>809</v>
       </c>
       <c r="AA56">
-        <v>0.98485684158558628</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB56">
-        <v>277.62457093091871</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD56" t="s">
         <v>534</v>
@@ -16175,10 +16175,10 @@
         <v>966</v>
       </c>
       <c r="AM56" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="AN56" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="AO56">
         <v>0.98134982200735632</v>
@@ -16249,16 +16249,16 @@
         <v>629</v>
       </c>
       <c r="Y57" t="s">
-        <v>493</v>
+        <v>428</v>
       </c>
       <c r="Z57" t="s">
         <v>810</v>
       </c>
       <c r="AA57">
-        <v>0.98211145389932475</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB57">
-        <v>327.95667851237977</v>
+        <v>41.695953373122713</v>
       </c>
       <c r="AD57" t="s">
         <v>534</v>
@@ -16285,10 +16285,10 @@
         <v>968</v>
       </c>
       <c r="AM57" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="AN57" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="AO57">
         <v>0.98589595763902149</v>
@@ -16359,16 +16359,16 @@
         <v>631</v>
       </c>
       <c r="Y58" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="Z58" t="s">
         <v>811</v>
       </c>
       <c r="AA58">
-        <v>0.99654205356515035</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB58">
-        <v>63.395684638909763</v>
+        <v>64.274570700309781</v>
       </c>
       <c r="AD58" t="s">
         <v>534</v>
@@ -16395,10 +16395,10 @@
         <v>970</v>
       </c>
       <c r="AM58" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="AN58" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="AO58">
         <v>0.99776894175014486</v>
@@ -16469,16 +16469,16 @@
         <v>633</v>
       </c>
       <c r="Y59" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="Z59" t="s">
         <v>812</v>
       </c>
       <c r="AA59">
-        <v>0.99504817442297822</v>
+        <v>0.97907421743006762</v>
       </c>
       <c r="AB59">
-        <v>90.78346891206678</v>
+        <v>383.63934711542669</v>
       </c>
       <c r="AD59" t="s">
         <v>534</v>
@@ -16505,10 +16505,10 @@
         <v>972</v>
       </c>
       <c r="AM59" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="AN59" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="AO59">
         <v>0.9959346869215373</v>
@@ -16579,16 +16579,16 @@
         <v>635</v>
       </c>
       <c r="Y60" t="s">
-        <v>507</v>
+        <v>426</v>
       </c>
       <c r="Z60" t="s">
         <v>813</v>
       </c>
       <c r="AA60">
-        <v>0.99470247457730832</v>
+        <v>0.99558768376711515</v>
       </c>
       <c r="AB60">
-        <v>97.121299416014665</v>
+        <v>80.892464269556413</v>
       </c>
       <c r="AD60" t="s">
         <v>534</v>
@@ -16615,16 +16615,16 @@
         <v>974</v>
       </c>
       <c r="AM60" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="AN60" t="s">
-        <v>770</v>
+        <v>1109</v>
       </c>
       <c r="AO60">
-        <v>0.95532613069733086</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP60">
-        <v>819.02093721560016</v>
+        <v>80.747827133859133</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16689,16 +16689,16 @@
         <v>637</v>
       </c>
       <c r="Y61" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="Z61" t="s">
         <v>814</v>
       </c>
       <c r="AA61">
-        <v>0.99549782242326257</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB61">
-        <v>82.539922240185263</v>
+        <v>123.82892298254488</v>
       </c>
       <c r="AD61" t="s">
         <v>534</v>
@@ -16725,16 +16725,16 @@
         <v>976</v>
       </c>
       <c r="AM61" t="s">
+        <v>1110</v>
+      </c>
+      <c r="AN61" t="s">
         <v>1111</v>
       </c>
-      <c r="AN61" t="s">
-        <v>872</v>
-      </c>
       <c r="AO61">
-        <v>0.98599828568941739</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP61">
-        <v>256.69809569401372</v>
+        <v>60.189444792275019</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16799,16 +16799,16 @@
         <v>639</v>
       </c>
       <c r="Y62" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="Z62" t="s">
-        <v>784</v>
+        <v>815</v>
       </c>
       <c r="AA62">
-        <v>0.97432735774114165</v>
+        <v>0.99419165427276146</v>
       </c>
       <c r="AB62">
-        <v>470.66510807906917</v>
+        <v>106.48633833270691</v>
       </c>
       <c r="AD62" t="s">
         <v>534</v>
@@ -16841,10 +16841,10 @@
         <v>1113</v>
       </c>
       <c r="AO62">
-        <v>0.98996241922424166</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP62">
-        <v>184.02231422223667</v>
+        <v>109.31605592223302</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16909,16 +16909,16 @@
         <v>641</v>
       </c>
       <c r="Y63" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="Z63" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AA63">
-        <v>0.9882282251528024</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB63">
-        <v>215.81587219862183</v>
+        <v>146.8618143486346</v>
       </c>
       <c r="AD63" t="s">
         <v>534</v>
@@ -16951,10 +16951,10 @@
         <v>1115</v>
       </c>
       <c r="AO63">
-        <v>0.99620534810300254</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP63">
-        <v>69.568618111619969</v>
+        <v>163.93514059684662</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17019,16 +17019,16 @@
         <v>643</v>
       </c>
       <c r="Y64" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="Z64" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AA64">
-        <v>0.99136196456122894</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB64">
-        <v>158.36398304413572</v>
+        <v>129.18226807514921</v>
       </c>
       <c r="AD64" t="s">
         <v>534</v>
@@ -17061,10 +17061,10 @@
         <v>1117</v>
       </c>
       <c r="AO64">
-        <v>0.99374536027070226</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP64">
-        <v>114.668395037126</v>
+        <v>46.428192737512276</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17129,16 +17129,16 @@
         <v>645</v>
       </c>
       <c r="Y65" t="s">
-        <v>427</v>
+        <v>486</v>
       </c>
       <c r="Z65" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AA65">
-        <v>0.99658191580238853</v>
+        <v>0.98571261124433651</v>
       </c>
       <c r="AB65">
-        <v>62.664876956210314</v>
+        <v>261.93546052049794</v>
       </c>
       <c r="AD65" t="s">
         <v>534</v>
@@ -17171,10 +17171,10 @@
         <v>1119</v>
       </c>
       <c r="AO65">
-        <v>0.99681385284485569</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP65">
-        <v>58.41269784431158</v>
+        <v>85.270745539791065</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17239,16 +17239,16 @@
         <v>647</v>
       </c>
       <c r="Y66" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="Z66" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AA66">
-        <v>0.99772567527055689</v>
+        <v>0.9849019911873127</v>
       </c>
       <c r="AB66">
-        <v>41.695953373122713</v>
+        <v>276.79682823259958</v>
       </c>
       <c r="AD66" t="s">
         <v>534</v>
@@ -17281,10 +17281,10 @@
         <v>1121</v>
       </c>
       <c r="AO66">
-        <v>0.99527237968252791</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP66">
-        <v>86.673039153654699</v>
+        <v>546.30069964051177</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17349,16 +17349,16 @@
         <v>649</v>
       </c>
       <c r="Y67" t="s">
-        <v>529</v>
+        <v>419</v>
       </c>
       <c r="Z67" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AA67">
-        <v>0.96520767961718001</v>
+        <v>0.99157679714615166</v>
       </c>
       <c r="AB67">
-        <v>637.85920701836687</v>
+        <v>154.42538565388551</v>
       </c>
       <c r="AD67" t="s">
         <v>534</v>
@@ -17391,10 +17391,10 @@
         <v>1123</v>
       </c>
       <c r="AO67">
-        <v>0.9917253583369573</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP67">
-        <v>151.70176382244892</v>
+        <v>56.159977027506663</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17459,16 +17459,16 @@
         <v>651</v>
       </c>
       <c r="Y68" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="Z68" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AA68">
-        <v>0.99344074878931121</v>
+        <v>0.99619387577842089</v>
       </c>
       <c r="AB68">
-        <v>120.25293886262826</v>
+        <v>69.778944062284495</v>
       </c>
       <c r="AD68" t="s">
         <v>534</v>
@@ -17501,10 +17501,10 @@
         <v>1125</v>
       </c>
       <c r="AO68">
-        <v>0.99569050067699549</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP68">
-        <v>79.007487588415231</v>
+        <v>95.557874766001078</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17569,16 +17569,16 @@
         <v>653</v>
       </c>
       <c r="Y69" t="s">
-        <v>499</v>
+        <v>457</v>
       </c>
       <c r="Z69" t="s">
-        <v>769</v>
+        <v>822</v>
       </c>
       <c r="AA69">
-        <v>0.99459650548991607</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB69">
-        <v>99.064066018204684</v>
+        <v>92.048872319688599</v>
       </c>
       <c r="AD69" t="s">
         <v>534</v>
@@ -17679,16 +17679,16 @@
         <v>655</v>
       </c>
       <c r="Y70" t="s">
-        <v>490</v>
+        <v>526</v>
       </c>
       <c r="Z70" t="s">
-        <v>821</v>
+        <v>770</v>
       </c>
       <c r="AA70">
-        <v>0.99655727877565281</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB70">
-        <v>63.116555779697698</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD70" t="s">
         <v>534</v>
@@ -17789,16 +17789,16 @@
         <v>657</v>
       </c>
       <c r="Y71" t="s">
-        <v>488</v>
+        <v>530</v>
       </c>
       <c r="Z71" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AA71">
-        <v>0.99221351039035977</v>
+        <v>0.95679935803281835</v>
       </c>
       <c r="AB71">
-        <v>142.75230951007163</v>
+        <v>792.01176939833033</v>
       </c>
       <c r="AD71" t="s">
         <v>534</v>
@@ -17899,16 +17899,16 @@
         <v>659</v>
       </c>
       <c r="Y72" t="s">
-        <v>447</v>
+        <v>501</v>
       </c>
       <c r="Z72" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AA72">
-        <v>0.99067174034238459</v>
+        <v>0.98761622532712257</v>
       </c>
       <c r="AB72">
-        <v>171.01809372294977</v>
+        <v>227.03586900275366</v>
       </c>
       <c r="AD72" t="s">
         <v>534</v>
@@ -18009,16 +18009,16 @@
         <v>661</v>
       </c>
       <c r="Y73" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="Z73" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA73">
-        <v>0.99634417822754895</v>
+        <v>0.99003402112096806</v>
       </c>
       <c r="AB73">
-        <v>67.023399161603095</v>
+        <v>182.70961278225187</v>
       </c>
       <c r="AD73" t="s">
         <v>534</v>
@@ -18119,16 +18119,16 @@
         <v>663</v>
       </c>
       <c r="Y74" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="Z74" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AA74">
-        <v>0.98416341622871006</v>
+        <v>0.99466062705491098</v>
       </c>
       <c r="AB74">
-        <v>290.33736914031488</v>
+        <v>97.888503993298116</v>
       </c>
       <c r="AD74" t="s">
         <v>534</v>
@@ -18161,10 +18161,10 @@
         <v>1137</v>
       </c>
       <c r="AO74">
-        <v>0.99567626923235475</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP74">
-        <v>79.268397406829976</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18229,16 +18229,16 @@
         <v>665</v>
       </c>
       <c r="Y75" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="Z75" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AA75">
-        <v>0.99563792883070867</v>
+        <v>0.9944598150968682</v>
       </c>
       <c r="AB75">
-        <v>79.971304770340467</v>
+        <v>101.5700565574154</v>
       </c>
       <c r="AD75" t="s">
         <v>534</v>
@@ -18271,10 +18271,10 @@
         <v>1139</v>
       </c>
       <c r="AO75">
-        <v>0.99762284649610655</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP75">
-        <v>43.581147571379539</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18339,16 +18339,16 @@
         <v>667</v>
       </c>
       <c r="Y76" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
       <c r="Z76" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AA76">
-        <v>0.99558181127270129</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB76">
-        <v>81.000126667143434</v>
+        <v>92.674656500591539</v>
       </c>
       <c r="AD76" t="s">
         <v>534</v>
@@ -18381,10 +18381,10 @@
         <v>1141</v>
       </c>
       <c r="AO76">
-        <v>0.99175391794306234</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP76">
-        <v>151.17817104385733</v>
+        <v>53.069246900976879</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18449,16 +18449,16 @@
         <v>669</v>
       </c>
       <c r="Y77" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="Z77" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AA77">
-        <v>0.99390501557434718</v>
+        <v>0.99438812565699364</v>
       </c>
       <c r="AB77">
-        <v>111.7413811369688</v>
+        <v>102.88436295511657</v>
       </c>
       <c r="AD77" t="s">
         <v>534</v>
@@ -18491,10 +18491,10 @@
         <v>1143</v>
       </c>
       <c r="AO77">
-        <v>0.99688290256322298</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP77">
-        <v>57.146786340912868</v>
+        <v>57.905423216266421</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18559,16 +18559,16 @@
         <v>671</v>
       </c>
       <c r="Y78" t="s">
-        <v>473</v>
+        <v>523</v>
       </c>
       <c r="Z78" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AA78">
-        <v>0.97581570155911468</v>
+        <v>0.99643191679577148</v>
       </c>
       <c r="AB78">
-        <v>443.37880474956393</v>
+        <v>65.414858744189985</v>
       </c>
       <c r="AD78" t="s">
         <v>534</v>
@@ -18601,10 +18601,10 @@
         <v>1145</v>
       </c>
       <c r="AO78">
-        <v>0.99488275259079373</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP78">
-        <v>93.81620250211445</v>
+        <v>85.716830221163534</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18669,16 +18669,16 @@
         <v>673</v>
       </c>
       <c r="Y79" t="s">
-        <v>485</v>
+        <v>421</v>
       </c>
       <c r="Z79" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AA79">
-        <v>0.99542292233022822</v>
+        <v>0.99553066735440277</v>
       </c>
       <c r="AB79">
-        <v>83.913090612483515</v>
+        <v>81.937765169281747</v>
       </c>
       <c r="AD79" t="s">
         <v>534</v>
@@ -18711,10 +18711,10 @@
         <v>1147</v>
       </c>
       <c r="AO79">
-        <v>0.99663220850609069</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP79">
-        <v>61.742844055003644</v>
+        <v>74.464817689622748</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18779,16 +18779,16 @@
         <v>675</v>
       </c>
       <c r="Y80" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="Z80" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AA80">
-        <v>0.99647584863086869</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB80">
-        <v>64.60944176740837</v>
+        <v>174.28740880058183</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18853,16 +18853,16 @@
         <v>677</v>
       </c>
       <c r="Y81" t="s">
-        <v>431</v>
+        <v>522</v>
       </c>
       <c r="Z81" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AA81">
-        <v>0.99780983219878738</v>
+        <v>0.99575157784901702</v>
       </c>
       <c r="AB81">
-        <v>40.153076355563911</v>
+        <v>77.887739434686992</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18927,16 +18927,16 @@
         <v>679</v>
       </c>
       <c r="Y82" t="s">
-        <v>466</v>
+        <v>527</v>
       </c>
       <c r="Z82" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AA82">
-        <v>0.99724696581141214</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB82">
-        <v>50.472293457444586</v>
+        <v>868.72862240505196</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -19001,16 +19001,16 @@
         <v>681</v>
       </c>
       <c r="Y83" t="s">
-        <v>461</v>
+        <v>531</v>
       </c>
       <c r="Z83" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AA83">
-        <v>0.99589550629055523</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB83">
-        <v>75.249051339820184</v>
+        <v>475.8705861429753</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -19075,16 +19075,16 @@
         <v>683</v>
       </c>
       <c r="Y84" t="s">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="Z84" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AA84">
-        <v>0.99531156065644533</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB84">
-        <v>85.954721298502818</v>
+        <v>226.88936094280919</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -19149,16 +19149,16 @@
         <v>685</v>
       </c>
       <c r="Y85" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="Z85" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AA85">
-        <v>0.99706825374988217</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB85">
-        <v>53.748681252160438</v>
+        <v>224.55764046872929</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19223,16 +19223,16 @@
         <v>687</v>
       </c>
       <c r="Y86" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="Z86" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AA86">
-        <v>0.99012236069527793</v>
+        <v>0.99647006537565563</v>
       </c>
       <c r="AB86">
-        <v>181.09005391990564</v>
+        <v>64.715468112981057</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19297,16 +19297,16 @@
         <v>689</v>
       </c>
       <c r="Y87" t="s">
-        <v>435</v>
+        <v>492</v>
       </c>
       <c r="Z87" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AA87">
-        <v>0.98990296758392993</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB87">
-        <v>185.11226096128556</v>
+        <v>645.26520366712316</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19371,16 +19371,16 @@
         <v>691</v>
       </c>
       <c r="Y88" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="Z88" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AA88">
-        <v>0.99377714174527498</v>
+        <v>0.99267004448650609</v>
       </c>
       <c r="AB88">
-        <v>114.08573466995766</v>
+        <v>134.38251774738842</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19445,16 +19445,16 @@
         <v>693</v>
       </c>
       <c r="Y89" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="Z89" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AA89">
-        <v>0.99516685156772267</v>
+        <v>0.9948848527457459</v>
       </c>
       <c r="AB89">
-        <v>88.60772125841865</v>
+        <v>93.777699661325343</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19519,16 +19519,16 @@
         <v>695</v>
       </c>
       <c r="Y90" t="s">
-        <v>474</v>
+        <v>524</v>
       </c>
       <c r="Z90" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="AA90">
-        <v>0.99506672623055659</v>
+        <v>0.9922030648239526</v>
       </c>
       <c r="AB90">
-        <v>90.443352439796072</v>
+        <v>142.94381156086857</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19593,16 +19593,16 @@
         <v>697</v>
       </c>
       <c r="Y91" t="s">
-        <v>439</v>
+        <v>474</v>
       </c>
       <c r="Z91" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AA91">
-        <v>0.97537853020161625</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB91">
-        <v>451.39361297036953</v>
+        <v>90.443352439796072</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19667,16 +19667,16 @@
         <v>699</v>
       </c>
       <c r="Y92" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="Z92" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AA92">
-        <v>0.99417333900805149</v>
+        <v>0.97537853020161625</v>
       </c>
       <c r="AB92">
-        <v>106.82211818572355</v>
+        <v>451.39361297036953</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19741,16 +19741,16 @@
         <v>701</v>
       </c>
       <c r="Y93" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="Z93" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AA93">
-        <v>0.99660448707980165</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB93">
-        <v>62.251070203636829</v>
+        <v>106.82211818572355</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19815,16 +19815,16 @@
         <v>703</v>
       </c>
       <c r="Y94" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="Z94" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AA94">
-        <v>0.99704166323096854</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB94">
-        <v>54.23617409891024</v>
+        <v>62.251070203636829</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19889,16 +19889,16 @@
         <v>705</v>
       </c>
       <c r="Y95" t="s">
-        <v>512</v>
+        <v>433</v>
       </c>
       <c r="Z95" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AA95">
-        <v>0.99156821305535681</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB95">
-        <v>154.58276065179118</v>
+        <v>54.23617409891024</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19963,16 +19963,16 @@
         <v>707</v>
       </c>
       <c r="Y96" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="Z96" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AA96">
-        <v>0.99731037386855248</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB96">
-        <v>49.309812409870183</v>
+        <v>154.58276065179118</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -20037,16 +20037,16 @@
         <v>709</v>
       </c>
       <c r="Y97" t="s">
-        <v>514</v>
+        <v>465</v>
       </c>
       <c r="Z97" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AA97">
-        <v>0.99338478208530079</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB97">
-        <v>121.27899510281891</v>
+        <v>49.309812409870183</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -20111,16 +20111,16 @@
         <v>711</v>
       </c>
       <c r="Y98" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="Z98" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AA98">
-        <v>0.98150124893892388</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB98">
-        <v>339.14376945306287</v>
+        <v>121.27899510281891</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20185,16 +20185,16 @@
         <v>713</v>
       </c>
       <c r="Y99" t="s">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="Z99" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AA99">
-        <v>0.99523081353776888</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB99">
-        <v>87.435085140903482</v>
+        <v>443.37880474956393</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20259,16 +20259,16 @@
         <v>715</v>
       </c>
       <c r="Y100" t="s">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="Z100" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AA100">
-        <v>0.9916432660493133</v>
+        <v>0.99542292233022822</v>
       </c>
       <c r="AB100">
-        <v>153.20678909592235</v>
+        <v>83.913090612483515</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20333,16 +20333,16 @@
         <v>717</v>
       </c>
       <c r="Y101" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="Z101" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AA101">
-        <v>0.99570118415007625</v>
+        <v>0.99647584863086869</v>
       </c>
       <c r="AB101">
-        <v>78.81162391526847</v>
+        <v>64.60944176740837</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20407,16 +20407,16 @@
         <v>719</v>
       </c>
       <c r="Y102" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="Z102" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AA102">
-        <v>0.99691903985105013</v>
+        <v>0.99780983219878738</v>
       </c>
       <c r="AB102">
-        <v>56.484269397415083</v>
+        <v>40.153076355563911</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20481,16 +20481,16 @@
         <v>721</v>
       </c>
       <c r="Y103" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="Z103" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AA103">
-        <v>0.98563153879963317</v>
+        <v>0.99724696581141214</v>
       </c>
       <c r="AB103">
-        <v>263.42178867339101</v>
+        <v>50.472293457444586</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20555,16 +20555,16 @@
         <v>723</v>
       </c>
       <c r="Y104" t="s">
-        <v>509</v>
+        <v>461</v>
       </c>
       <c r="Z104" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AA104">
-        <v>0.99529226044395613</v>
+        <v>0.99589550629055523</v>
       </c>
       <c r="AB104">
-        <v>86.308558527470979</v>
+        <v>75.249051339820184</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20629,16 +20629,16 @@
         <v>725</v>
       </c>
       <c r="Y105" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="Z105" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AA105">
-        <v>0.99443562760718263</v>
+        <v>0.99531156065644533</v>
       </c>
       <c r="AB105">
-        <v>102.01349386831856</v>
+        <v>85.954721298502818</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20703,16 +20703,16 @@
         <v>727</v>
       </c>
       <c r="Y106" t="s">
-        <v>483</v>
+        <v>521</v>
       </c>
       <c r="Z106" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AA106">
-        <v>0.9914627894548943</v>
+        <v>0.99706825374988217</v>
       </c>
       <c r="AB106">
-        <v>156.51552666027055</v>
+        <v>53.748681252160438</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20777,16 +20777,16 @@
         <v>729</v>
       </c>
       <c r="Y107" t="s">
-        <v>500</v>
+        <v>469</v>
       </c>
       <c r="Z107" t="s">
-        <v>858</v>
+        <v>783</v>
       </c>
       <c r="AA107">
-        <v>0.9776523073059149</v>
+        <v>0.96238190390083644</v>
       </c>
       <c r="AB107">
-        <v>409.70769939155917</v>
+        <v>689.665095151331</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20851,16 +20851,16 @@
         <v>731</v>
       </c>
       <c r="Y108" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="Z108" t="s">
-        <v>859</v>
+        <v>770</v>
       </c>
       <c r="AA108">
-        <v>0.98289281118622185</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB108">
-        <v>313.63179491926536</v>
+        <v>675.25867642804383</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20925,16 +20925,16 @@
         <v>733</v>
       </c>
       <c r="Y109" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="Z109" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AA109">
-        <v>0.99593583828988941</v>
+        <v>0.9951089264264793</v>
       </c>
       <c r="AB109">
-        <v>74.509631352026517</v>
+        <v>89.669682181211982</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20999,16 +20999,16 @@
         <v>735</v>
       </c>
       <c r="Y110" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="Z110" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AA110">
-        <v>0.99553066735440277</v>
+        <v>0.98666519734623237</v>
       </c>
       <c r="AB110">
-        <v>81.937765169281747</v>
+        <v>244.47138198573927</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -21073,16 +21073,16 @@
         <v>737</v>
       </c>
       <c r="Y111" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="Z111" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AA111">
-        <v>0.99049341406542279</v>
+        <v>0.99750070245826261</v>
       </c>
       <c r="AB111">
-        <v>174.28740880058183</v>
+        <v>45.820454931853</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -21147,16 +21147,16 @@
         <v>739</v>
       </c>
       <c r="Y112" t="s">
-        <v>522</v>
+        <v>422</v>
       </c>
       <c r="Z112" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="AA112">
-        <v>0.99575157784901702</v>
+        <v>0.99395341117186964</v>
       </c>
       <c r="AB112">
-        <v>77.887739434686992</v>
+        <v>110.85412851572337</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21221,16 +21221,16 @@
         <v>741</v>
       </c>
       <c r="Y113" t="s">
-        <v>470</v>
+        <v>441</v>
       </c>
       <c r="Z113" t="s">
-        <v>784</v>
+        <v>863</v>
       </c>
       <c r="AA113">
-        <v>0.9621480095608167</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB113">
-        <v>693.95315805169378</v>
+        <v>307.49900901993823</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21295,16 +21295,16 @@
         <v>743</v>
       </c>
       <c r="Y114" t="s">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="Z114" t="s">
         <v>864</v>
       </c>
       <c r="AA114">
-        <v>0.98916941127667946</v>
+        <v>0.9974199781412052</v>
       </c>
       <c r="AB114">
-        <v>198.56079326087576</v>
+        <v>47.300400744571718</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21369,16 +21369,16 @@
         <v>745</v>
       </c>
       <c r="Y115" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="Z115" t="s">
         <v>865</v>
       </c>
       <c r="AA115">
-        <v>0.97159134368321343</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB115">
-        <v>520.82536580775354</v>
+        <v>121.57987025257442</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21443,16 +21443,16 @@
         <v>747</v>
       </c>
       <c r="Y116" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="Z116" t="s">
         <v>866</v>
       </c>
       <c r="AA116">
-        <v>0.99359614530212825</v>
+        <v>0.99379477670057537</v>
       </c>
       <c r="AB116">
-        <v>117.40400279431638</v>
+        <v>113.7624271561186</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21517,16 +21517,16 @@
         <v>749</v>
       </c>
       <c r="Y117" t="s">
-        <v>518</v>
+        <v>454</v>
       </c>
       <c r="Z117" t="s">
         <v>867</v>
       </c>
       <c r="AA117">
-        <v>0.99488082982009873</v>
+        <v>0.9961866142254362</v>
       </c>
       <c r="AB117">
-        <v>93.851453298190577</v>
+        <v>69.91207253366963</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21591,16 +21591,16 @@
         <v>751</v>
       </c>
       <c r="Y118" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="Z118" t="s">
         <v>868</v>
       </c>
       <c r="AA118">
-        <v>0.99557743229498485</v>
+        <v>0.98150124893892388</v>
       </c>
       <c r="AB118">
-        <v>81.080407925277868</v>
+        <v>339.14376945306287</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21665,16 +21665,16 @@
         <v>753</v>
       </c>
       <c r="Y119" t="s">
-        <v>455</v>
+        <v>502</v>
       </c>
       <c r="Z119" t="s">
         <v>869</v>
       </c>
       <c r="AA119">
-        <v>0.99401156108202648</v>
+        <v>0.99523081353776888</v>
       </c>
       <c r="AB119">
-        <v>109.78804682951412</v>
+        <v>87.435085140903482</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21739,16 +21739,16 @@
         <v>755</v>
       </c>
       <c r="Y120" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="Z120" t="s">
         <v>870</v>
       </c>
       <c r="AA120">
-        <v>0.99295369446862825</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB120">
-        <v>129.18226807514921</v>
+        <v>153.20678909592235</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21813,16 +21813,16 @@
         <v>757</v>
       </c>
       <c r="Y121" t="s">
-        <v>486</v>
+        <v>423</v>
       </c>
       <c r="Z121" t="s">
         <v>871</v>
       </c>
       <c r="AA121">
-        <v>0.98571261124433651</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB121">
-        <v>261.93546052049794</v>
+        <v>78.81162391526847</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21887,16 +21887,16 @@
         <v>759</v>
       </c>
       <c r="Y122" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="Z122" t="s">
         <v>872</v>
       </c>
       <c r="AA122">
-        <v>0.9849019911873127</v>
+        <v>0.99691903985105013</v>
       </c>
       <c r="AB122">
-        <v>276.79682823259958</v>
+        <v>56.484269397415083</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21961,16 +21961,16 @@
         <v>761</v>
       </c>
       <c r="Y123" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="Z123" t="s">
         <v>873</v>
       </c>
       <c r="AA123">
-        <v>0.99157679714615166</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB123">
-        <v>154.42538565388551</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -22035,16 +22035,16 @@
         <v>763</v>
       </c>
       <c r="Y124" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="Z124" t="s">
         <v>874</v>
       </c>
       <c r="AA124">
-        <v>0.99619387577842089</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB124">
-        <v>69.778944062284495</v>
+        <v>86.308558527470979</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -22109,16 +22109,16 @@
         <v>765</v>
       </c>
       <c r="Y125" t="s">
-        <v>457</v>
+        <v>511</v>
       </c>
       <c r="Z125" t="s">
         <v>875</v>
       </c>
       <c r="AA125">
-        <v>0.99497915241892609</v>
+        <v>0.99443562760718263</v>
       </c>
       <c r="AB125">
-        <v>92.048872319688599</v>
+        <v>102.01349386831856</v>
       </c>
     </row>
   </sheetData>
@@ -22127,7 +22127,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394B6F6F-2920-41A3-BE71-2A46C2CAE5E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCABACA-A93F-4787-97ED-B948EA785FDB}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22239,7 +22239,7 @@
         <v>1269</v>
       </c>
       <c r="K11" t="s">
-        <v>1056</v>
+        <v>1084</v>
       </c>
       <c r="L11">
         <v>4.7713910333636482</v>
@@ -22272,7 +22272,7 @@
         <v>1407</v>
       </c>
       <c r="X11" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -22307,7 +22307,7 @@
         <v>1271</v>
       </c>
       <c r="K12" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="L12">
         <v>12.404103898825962</v>
@@ -22340,7 +22340,7 @@
         <v>1409</v>
       </c>
       <c r="X12" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -22375,7 +22375,7 @@
         <v>1273</v>
       </c>
       <c r="K13" t="s">
-        <v>1111</v>
+        <v>1041</v>
       </c>
       <c r="L13">
         <v>6.1276234637439133</v>
@@ -22408,7 +22408,7 @@
         <v>1411</v>
       </c>
       <c r="X13" t="s">
-        <v>1250</v>
+        <v>1230</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -22476,7 +22476,7 @@
         <v>1413</v>
       </c>
       <c r="X14" t="s">
-        <v>1224</v>
+        <v>1242</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -22511,7 +22511,7 @@
         <v>1277</v>
       </c>
       <c r="K15" t="s">
-        <v>1072</v>
+        <v>1094</v>
       </c>
       <c r="L15">
         <v>2.2628760328229185</v>
@@ -22544,7 +22544,7 @@
         <v>1415</v>
       </c>
       <c r="X15" t="s">
-        <v>1262</v>
+        <v>1246</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -22579,7 +22579,7 @@
         <v>1279</v>
       </c>
       <c r="K16" t="s">
-        <v>1080</v>
+        <v>1114</v>
       </c>
       <c r="L16">
         <v>0.43370118574988076</v>
@@ -22612,7 +22612,7 @@
         <v>1417</v>
       </c>
       <c r="X16" t="s">
-        <v>1239</v>
+        <v>1263</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -22647,7 +22647,7 @@
         <v>1281</v>
       </c>
       <c r="K17" t="s">
-        <v>1094</v>
+        <v>1032</v>
       </c>
       <c r="L17">
         <v>2.5150267058852811</v>
@@ -22680,7 +22680,7 @@
         <v>1419</v>
       </c>
       <c r="X17" t="s">
-        <v>1222</v>
+        <v>1267</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -22715,7 +22715,7 @@
         <v>1283</v>
       </c>
       <c r="K18" t="s">
-        <v>1071</v>
+        <v>1093</v>
       </c>
       <c r="L18">
         <v>2.885493974180005</v>
@@ -22748,7 +22748,7 @@
         <v>1421</v>
       </c>
       <c r="X18" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -22783,7 +22783,7 @@
         <v>1285</v>
       </c>
       <c r="K19" t="s">
-        <v>1065</v>
+        <v>1120</v>
       </c>
       <c r="L19">
         <v>10.563746678268352</v>
@@ -22816,7 +22816,7 @@
         <v>1423</v>
       </c>
       <c r="X19" t="s">
-        <v>1220</v>
+        <v>1265</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22851,7 +22851,7 @@
         <v>1287</v>
       </c>
       <c r="K20" t="s">
-        <v>1058</v>
+        <v>1086</v>
       </c>
       <c r="L20">
         <v>7.4816578037471135</v>
@@ -22884,7 +22884,7 @@
         <v>1425</v>
       </c>
       <c r="X20" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22919,7 +22919,7 @@
         <v>1289</v>
       </c>
       <c r="K21" t="s">
-        <v>1092</v>
+        <v>1030</v>
       </c>
       <c r="L21">
         <v>11.884376191048085</v>
@@ -22952,7 +22952,7 @@
         <v>1427</v>
       </c>
       <c r="X21" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -23020,7 +23020,7 @@
         <v>1429</v>
       </c>
       <c r="X22" t="s">
-        <v>1237</v>
+        <v>1261</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -23055,7 +23055,7 @@
         <v>1293</v>
       </c>
       <c r="K23" t="s">
-        <v>1078</v>
+        <v>1112</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -23088,7 +23088,7 @@
         <v>1431</v>
       </c>
       <c r="X23" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -23123,7 +23123,7 @@
         <v>1295</v>
       </c>
       <c r="K24" t="s">
-        <v>1112</v>
+        <v>1042</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -23156,7 +23156,7 @@
         <v>1433</v>
       </c>
       <c r="X24" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -23191,7 +23191,7 @@
         <v>1297</v>
       </c>
       <c r="K25" t="s">
-        <v>1067</v>
+        <v>1122</v>
       </c>
       <c r="L25">
         <v>11.221871479411517</v>
@@ -23224,7 +23224,7 @@
         <v>1435</v>
       </c>
       <c r="X25" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -23259,7 +23259,7 @@
         <v>1299</v>
       </c>
       <c r="K26" t="s">
-        <v>1096</v>
+        <v>1034</v>
       </c>
       <c r="L26">
         <v>1.6691823226567941</v>
@@ -23292,7 +23292,7 @@
         <v>1437</v>
       </c>
       <c r="X26" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23327,7 +23327,7 @@
         <v>1301</v>
       </c>
       <c r="K27" t="s">
-        <v>1136</v>
+        <v>1056</v>
       </c>
       <c r="L27">
         <v>3.7614311754340659</v>
@@ -23360,7 +23360,7 @@
         <v>1439</v>
       </c>
       <c r="X27" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -23395,7 +23395,7 @@
         <v>1303</v>
       </c>
       <c r="K28" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="L28">
         <v>0.34625959029864795</v>
@@ -23428,7 +23428,7 @@
         <v>1441</v>
       </c>
       <c r="X28" t="s">
-        <v>1260</v>
+        <v>1219</v>
       </c>
       <c r="Y28">
         <v>2.6655000000000002</v>
@@ -23463,7 +23463,7 @@
         <v>1305</v>
       </c>
       <c r="K29" t="s">
-        <v>1022</v>
+        <v>1068</v>
       </c>
       <c r="L29">
         <v>0.65440271382024695</v>
@@ -23496,7 +23496,7 @@
         <v>1443</v>
       </c>
       <c r="X29" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="Y29">
         <v>8.8432499999999994</v>
@@ -23531,7 +23531,7 @@
         <v>1307</v>
       </c>
       <c r="K30" t="s">
-        <v>1082</v>
+        <v>1116</v>
       </c>
       <c r="L30">
         <v>2.2677057834637031</v>
@@ -23564,7 +23564,7 @@
         <v>1445</v>
       </c>
       <c r="X30" t="s">
-        <v>1212</v>
+        <v>1256</v>
       </c>
       <c r="Y30">
         <v>3.4402499999999998</v>
@@ -23599,7 +23599,7 @@
         <v>1309</v>
       </c>
       <c r="K31" t="s">
-        <v>1114</v>
+        <v>1044</v>
       </c>
       <c r="L31">
         <v>2.4836923620575391</v>
@@ -23632,7 +23632,7 @@
         <v>1447</v>
       </c>
       <c r="X31" t="s">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="Y31">
         <v>13.389749999999999</v>
@@ -23667,7 +23667,7 @@
         <v>1311</v>
       </c>
       <c r="K32" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="L32">
         <v>4.0763322608214585</v>
@@ -23700,7 +23700,7 @@
         <v>1449</v>
       </c>
       <c r="X32" t="s">
-        <v>1243</v>
+        <v>1218</v>
       </c>
       <c r="Y32">
         <v>6.9757499999999997</v>
@@ -23735,7 +23735,7 @@
         <v>1313</v>
       </c>
       <c r="K33" t="s">
-        <v>1138</v>
+        <v>1058</v>
       </c>
       <c r="L33">
         <v>2.5731779960501728</v>
@@ -23768,7 +23768,7 @@
         <v>1451</v>
       </c>
       <c r="X33" t="s">
-        <v>1210</v>
+        <v>1254</v>
       </c>
       <c r="Y33">
         <v>38.154000000000003</v>
@@ -23803,7 +23803,7 @@
         <v>1315</v>
       </c>
       <c r="K34" t="s">
-        <v>1046</v>
+        <v>1142</v>
       </c>
       <c r="L34">
         <v>4.0509443596880574</v>
@@ -23836,7 +23836,7 @@
         <v>1453</v>
       </c>
       <c r="X34" t="s">
-        <v>1226</v>
+        <v>1244</v>
       </c>
       <c r="Y34">
         <v>26.765999999999998</v>
@@ -23871,7 +23871,7 @@
         <v>1317</v>
       </c>
       <c r="K35" t="s">
-        <v>1028</v>
+        <v>1074</v>
       </c>
       <c r="L35">
         <v>2.4544193550494788</v>
@@ -23904,7 +23904,7 @@
         <v>1455</v>
       </c>
       <c r="X35" t="s">
-        <v>1241</v>
+        <v>1216</v>
       </c>
       <c r="Y35">
         <v>35.325000000000003</v>
@@ -23939,7 +23939,7 @@
         <v>1319</v>
       </c>
       <c r="K36" t="s">
-        <v>1088</v>
+        <v>1138</v>
       </c>
       <c r="L36">
         <v>0.35051099632091098</v>
@@ -23972,7 +23972,7 @@
         <v>1457</v>
       </c>
       <c r="X36" t="s">
-        <v>1252</v>
+        <v>1232</v>
       </c>
       <c r="Y36">
         <v>38.589750000000002</v>
@@ -24007,7 +24007,7 @@
         <v>1321</v>
       </c>
       <c r="K37" t="s">
-        <v>1063</v>
+        <v>1091</v>
       </c>
       <c r="L37">
         <v>5.5005105319204732</v>
@@ -24040,7 +24040,7 @@
         <v>1459</v>
       </c>
       <c r="X37" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
       <c r="Y37">
         <v>28.707000000000001</v>
@@ -24108,7 +24108,7 @@
         <v>1461</v>
       </c>
       <c r="X38" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
       <c r="Y38">
         <v>13.428000000000001</v>
@@ -24143,7 +24143,7 @@
         <v>1325</v>
       </c>
       <c r="K39" t="s">
-        <v>1032</v>
+        <v>1078</v>
       </c>
       <c r="L39">
         <v>0.39959553615654331</v>
@@ -24176,7 +24176,7 @@
         <v>1463</v>
       </c>
       <c r="X39" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24244,7 +24244,7 @@
         <v>1465</v>
       </c>
       <c r="X40" t="s">
-        <v>1254</v>
+        <v>1234</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24279,7 +24279,7 @@
         <v>1329</v>
       </c>
       <c r="K41" t="s">
-        <v>1090</v>
+        <v>1140</v>
       </c>
       <c r="L41">
         <v>23.427729543154012</v>
@@ -24312,7 +24312,7 @@
         <v>1467</v>
       </c>
       <c r="X41" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24347,7 +24347,7 @@
         <v>1331</v>
       </c>
       <c r="K42" t="s">
-        <v>1124</v>
+        <v>1054</v>
       </c>
       <c r="L42">
         <v>1.4999429400795936</v>
@@ -24382,7 +24382,7 @@
         <v>1333</v>
       </c>
       <c r="K43" t="s">
-        <v>1050</v>
+        <v>1146</v>
       </c>
       <c r="L43">
         <v>55.863958629218203</v>
@@ -24417,7 +24417,7 @@
         <v>1335</v>
       </c>
       <c r="K44" t="s">
-        <v>1120</v>
+        <v>1050</v>
       </c>
       <c r="L44">
         <v>17.068804920122925</v>
@@ -24452,7 +24452,7 @@
         <v>1337</v>
       </c>
       <c r="K45" t="s">
-        <v>1144</v>
+        <v>1064</v>
       </c>
       <c r="L45">
         <v>13.001084297219549</v>
@@ -24487,7 +24487,7 @@
         <v>1339</v>
       </c>
       <c r="K46" t="s">
-        <v>1036</v>
+        <v>1082</v>
       </c>
       <c r="L46">
         <v>3.0756142181007986</v>
@@ -24522,7 +24522,7 @@
         <v>1341</v>
       </c>
       <c r="K47" t="s">
-        <v>1054</v>
+        <v>1110</v>
       </c>
       <c r="L47">
         <v>17.749707845203876</v>
@@ -24557,7 +24557,7 @@
         <v>1343</v>
       </c>
       <c r="K48" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="L48">
         <v>2.3372365278937242</v>
@@ -24592,7 +24592,7 @@
         <v>1345</v>
       </c>
       <c r="K49" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="L49">
         <v>4.2648673086521249</v>
@@ -24627,7 +24627,7 @@
         <v>1347</v>
       </c>
       <c r="K50" t="s">
-        <v>1142</v>
+        <v>1062</v>
       </c>
       <c r="L50">
         <v>2.8571480649629004</v>
@@ -24662,7 +24662,7 @@
         <v>1349</v>
       </c>
       <c r="K51" t="s">
-        <v>1146</v>
+        <v>1066</v>
       </c>
       <c r="L51">
         <v>9.5169217846211289</v>
@@ -24697,7 +24697,7 @@
         <v>1351</v>
       </c>
       <c r="K52" t="s">
-        <v>1100</v>
+        <v>1038</v>
       </c>
       <c r="L52">
         <v>33.414563514376454</v>
@@ -24767,7 +24767,7 @@
         <v>1355</v>
       </c>
       <c r="K54" t="s">
-        <v>1122</v>
+        <v>1052</v>
       </c>
       <c r="L54">
         <v>15.478330347836801</v>
@@ -24802,7 +24802,7 @@
         <v>1357</v>
       </c>
       <c r="K55" t="s">
-        <v>1110</v>
+        <v>1040</v>
       </c>
       <c r="L55">
         <v>14.176079891703212</v>
@@ -24837,7 +24837,7 @@
         <v>1359</v>
       </c>
       <c r="K56" t="s">
-        <v>1026</v>
+        <v>1072</v>
       </c>
       <c r="L56">
         <v>0.80973624203950822</v>
@@ -24907,7 +24907,7 @@
         <v>1363</v>
       </c>
       <c r="K58" t="s">
-        <v>1098</v>
+        <v>1036</v>
       </c>
       <c r="L58">
         <v>0.66271354737797783</v>
@@ -24977,7 +24977,7 @@
         <v>1367</v>
       </c>
       <c r="K60" t="s">
-        <v>1074</v>
+        <v>1096</v>
       </c>
       <c r="L60">
         <v>0.24904319237866104</v>
@@ -25012,7 +25012,7 @@
         <v>1369</v>
       </c>
       <c r="K61" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="L61">
         <v>8.2047875916663029E-2</v>
@@ -25047,7 +25047,7 @@
         <v>1371</v>
       </c>
       <c r="K62" t="s">
-        <v>1140</v>
+        <v>1060</v>
       </c>
       <c r="L62">
         <v>11.861012832193515</v>
@@ -25117,7 +25117,7 @@
         <v>1375</v>
       </c>
       <c r="K64" t="s">
-        <v>1116</v>
+        <v>1046</v>
       </c>
       <c r="L64">
         <v>5.5201095579611916</v>
@@ -25152,7 +25152,7 @@
         <v>1377</v>
       </c>
       <c r="K65" t="s">
-        <v>1084</v>
+        <v>1118</v>
       </c>
       <c r="L65">
         <v>6.8285247240880329</v>
@@ -25187,7 +25187,7 @@
         <v>1379</v>
       </c>
       <c r="K66" t="s">
-        <v>1069</v>
+        <v>1124</v>
       </c>
       <c r="L66">
         <v>14.065249575687433</v>
@@ -25222,7 +25222,7 @@
         <v>1381</v>
       </c>
       <c r="K67" t="s">
-        <v>1076</v>
+        <v>1098</v>
       </c>
       <c r="L67">
         <v>9.3799037679336319</v>
@@ -25257,7 +25257,7 @@
         <v>1383</v>
       </c>
       <c r="K68" t="s">
-        <v>1024</v>
+        <v>1070</v>
       </c>
       <c r="L68">
         <v>42.785830383290261</v>
@@ -25292,7 +25292,7 @@
         <v>1385</v>
       </c>
       <c r="K69" t="s">
-        <v>1034</v>
+        <v>1080</v>
       </c>
       <c r="L69">
         <v>7.8693705940085819</v>
@@ -25327,7 +25327,7 @@
         <v>1387</v>
       </c>
       <c r="K70" t="s">
-        <v>1086</v>
+        <v>1136</v>
       </c>
       <c r="L70">
         <v>19.787589902082505</v>
@@ -25362,7 +25362,7 @@
         <v>1389</v>
       </c>
       <c r="K71" t="s">
-        <v>1052</v>
+        <v>1108</v>
       </c>
       <c r="L71">
         <v>18.319832830101969</v>
@@ -25397,7 +25397,7 @@
         <v>1391</v>
       </c>
       <c r="K72" t="s">
-        <v>1118</v>
+        <v>1048</v>
       </c>
       <c r="L72">
         <v>6.7551756478058005</v>
@@ -25432,7 +25432,7 @@
         <v>1393</v>
       </c>
       <c r="K73" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="L73">
         <v>3.5275797249830152</v>
@@ -25467,7 +25467,7 @@
         <v>1395</v>
       </c>
       <c r="K74" t="s">
-        <v>1048</v>
+        <v>1144</v>
       </c>
       <c r="L74">
         <v>0.89663971235601181</v>
@@ -25537,7 +25537,7 @@
         <v>1399</v>
       </c>
       <c r="K76" t="s">
-        <v>1061</v>
+        <v>1089</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25572,7 +25572,7 @@
         <v>1401</v>
       </c>
       <c r="K77" t="s">
-        <v>1030</v>
+        <v>1076</v>
       </c>
       <c r="L77">
         <v>0.5190595734350465</v>
@@ -25607,7 +25607,7 @@
         <v>1403</v>
       </c>
       <c r="K78" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="L78">
         <v>0.29505146981926272</v>
@@ -25642,7 +25642,7 @@
         <v>1405</v>
       </c>
       <c r="K79" t="s">
-        <v>1059</v>
+        <v>1087</v>
       </c>
       <c r="L79">
         <v>0.28737649325389003</v>
@@ -25657,7 +25657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E283625-3DA9-473B-8CD5-341626B04925}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2EE1D31-28D2-4445-AE62-0FFCF9E92A3C}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27126,7 +27126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B48EB99D-AB33-4734-8AF9-339D0B93A115}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F523B850-7BD9-4DE9-AE7B-7AA3E32BAED3}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47372631-D139-4CD6-994D-400CA65F7701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D926484B-D8AC-4893-9553-CEA92C28E777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1736,18 +1736,342 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_074</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 74</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_115</t>
   </si>
   <si>
@@ -1778,28 +2102,82 @@
     <t>connecting solar to buses in cluster 100</t>
   </si>
   <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_solelc_spv_066</t>
@@ -1826,6 +2204,192 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_053</t>
   </si>
   <si>
@@ -1868,582 +2432,162 @@
     <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
     <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
   </si>
   <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
     <t>e_w168904844-500,e_BR411-230,e_w168904844-230,e_w168664395-500</t>
   </si>
   <si>
@@ -2456,16 +2600,40 @@
     <t>e_BR310-500,e_BR300-500,e_w271191830-500,e_BR184-500,e_w953014442-500,e_BR309-500,e_BR220-500</t>
   </si>
   <si>
-    <t>e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
   </si>
   <si>
     <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
@@ -2480,7 +2648,97 @@
     <t>e_BR777-500,e_BR803-500,e_BR787-525,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
   </si>
   <si>
-    <t>e_BR319-230</t>
+    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR878-500</t>
+  </si>
+  <si>
+    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
   </si>
   <si>
     <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
@@ -2501,262 +2759,196 @@
     <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
   </si>
   <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR550-500,e_BR592-500,e_BR602-500,e_BR556-500,e_BR580-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR596-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR610-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR433-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w307168542-230,e_BR290-500,e_BR283-500,e_BR371-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR61-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500</t>
-  </si>
-  <si>
-    <t>e_BR482-500,e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR506-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>e_BR141-500,e_BR125-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR254-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR282-500,e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR302-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR292-500,e_BR204-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR221-500,e_BR72-500,e_BR105-500,e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_BR290-500,e_w453724535-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w306104018-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR550-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR493-500,e_BR485-500,e_BR500-500,e_BR475-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>e_BR371-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_w150728360-500,e_BR833-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR878-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR662-440,e_w206109551-500,e_BR639-440,e_BR732-500,e_BR673-440,e_BR676-440,e_BR676-500,e_w174017677-440,e_BR646-440,e_BR663-440</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_w271191830-500,e_BR300-500,e_BR171-500</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR558-500,e_BR535-500,e_BR587-500,e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w302901044-440,e_BR609-440,e_BR626-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR125-500,e_BR61-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
   </si>
   <si>
     <t>distr_wonelc_won_012</t>
@@ -2783,58 +2975,148 @@
     <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
   </si>
   <si>
     <t>distr_wonelc_won_045</t>
@@ -2891,286 +3173,193 @@
     <t>connecting wind onshore to buses in cluster 32</t>
   </si>
   <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
   </si>
   <si>
     <t>elc_won_012</t>
@@ -3197,58 +3386,145 @@
     <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
   </si>
   <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500,e_BR866-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR866-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
   </si>
   <si>
     <t>elc_won_045</t>
@@ -3299,280 +3575,16 @@
     <t>e_BR209-500,e_BR208-500</t>
   </si>
   <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR866-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_069</t>
-  </si>
-  <si>
-    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -3593,6 +3605,78 @@
     <t>connecting wind offshore to buses in cluster 31</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_025</t>
   </si>
   <si>
@@ -3605,40 +3689,28 @@
     <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wofelc_wof_003</t>
@@ -3659,106 +3731,46 @@
     <t>connecting wind offshore to buses in cluster 30</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
   </si>
   <si>
     <t>elc_wof_001</t>
@@ -3779,6 +3791,75 @@
     <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
   </si>
   <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR37-500,e_BR42-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
     <t>elc_wof_025</t>
   </si>
   <si>
@@ -3788,37 +3869,28 @@
     <t>elc_wof_022</t>
   </si>
   <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR37-500,e_BR42-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_BR292-500,e_BR258-500,e_w1090304792-500,e_BR154-500,e_w348815398-500</t>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w466973262-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
   </si>
   <si>
     <t>elc_wof_003</t>
@@ -3839,103 +3911,31 @@
     <t>e_BR154-500</t>
   </si>
   <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
     <t>elc_wof_013</t>
   </si>
   <si>
     <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9835,7 +9835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A753BE09-DC28-4125-A2B1-404D49A3F433}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F50B663-C9B6-4B78-8194-4608859DF72B}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10073,16 +10073,16 @@
         <v>535</v>
       </c>
       <c r="Y11" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="Z11" t="s">
         <v>769</v>
       </c>
       <c r="AA11">
-        <v>0.99240925523869494</v>
+        <v>0.96238190390083644</v>
       </c>
       <c r="AB11">
-        <v>139.16365395725984</v>
+        <v>689.665095151331</v>
       </c>
       <c r="AD11" t="s">
         <v>534</v>
@@ -10115,10 +10115,10 @@
         <v>1015</v>
       </c>
       <c r="AO11">
-        <v>0.99473480482648013</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP11">
-        <v>96.528578181196991</v>
+        <v>105.47547991621673</v>
       </c>
       <c r="AR11" t="s">
         <v>534</v>
@@ -10151,10 +10151,10 @@
         <v>1211</v>
       </c>
       <c r="BC11">
-        <v>0.98890025255868685</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD11">
-        <v>203.49536975740753</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10219,16 +10219,16 @@
         <v>539</v>
       </c>
       <c r="Y12" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="Z12" t="s">
         <v>770</v>
       </c>
       <c r="AA12">
-        <v>0.97244982574001193</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB12">
-        <v>505.08652809978111</v>
+        <v>675.25867642804383</v>
       </c>
       <c r="AD12" t="s">
         <v>534</v>
@@ -10261,10 +10261,10 @@
         <v>1017</v>
       </c>
       <c r="AO12">
-        <v>0.99729761494442914</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP12">
-        <v>49.543726018799653</v>
+        <v>195.31167947327185</v>
       </c>
       <c r="AR12" t="s">
         <v>534</v>
@@ -10297,10 +10297,10 @@
         <v>1213</v>
       </c>
       <c r="BC12">
-        <v>0.99481196273061234</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD12">
-        <v>95.114016605440895</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10365,16 +10365,16 @@
         <v>541</v>
       </c>
       <c r="Y13" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="Z13" t="s">
         <v>771</v>
       </c>
       <c r="AA13">
-        <v>0.99172397756136033</v>
+        <v>0.9951089264264793</v>
       </c>
       <c r="AB13">
-        <v>151.72707804172813</v>
+        <v>89.669682181211982</v>
       </c>
       <c r="AD13" t="s">
         <v>534</v>
@@ -10407,10 +10407,10 @@
         <v>1019</v>
       </c>
       <c r="AO13">
-        <v>0.996795372708284</v>
+        <v>0.99499049355022928</v>
       </c>
       <c r="AP13">
-        <v>58.751500348127372</v>
+        <v>91.840951579129481</v>
       </c>
       <c r="AR13" t="s">
         <v>534</v>
@@ -10443,10 +10443,10 @@
         <v>1215</v>
       </c>
       <c r="BC13">
-        <v>0.99374755699184159</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD13">
-        <v>114.62812181623703</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10511,16 +10511,16 @@
         <v>543</v>
       </c>
       <c r="Y14" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="Z14" t="s">
         <v>772</v>
       </c>
       <c r="AA14">
-        <v>0.99431900976645593</v>
+        <v>0.98666519734623237</v>
       </c>
       <c r="AB14">
-        <v>104.15148761497397</v>
+        <v>244.47138198573927</v>
       </c>
       <c r="AD14" t="s">
         <v>534</v>
@@ -10553,10 +10553,10 @@
         <v>1021</v>
       </c>
       <c r="AO14">
-        <v>0.99274560110857168</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP14">
-        <v>132.99731300951822</v>
+        <v>49.645668091582088</v>
       </c>
       <c r="AR14" t="s">
         <v>534</v>
@@ -10589,10 +10589,10 @@
         <v>1217</v>
       </c>
       <c r="BC14">
-        <v>0.9933934749176847</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD14">
-        <v>121.11962650911367</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10657,16 +10657,16 @@
         <v>545</v>
       </c>
       <c r="Y15" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="Z15" t="s">
         <v>773</v>
       </c>
       <c r="AA15">
-        <v>0.9946350729064154</v>
+        <v>0.99750070245826261</v>
       </c>
       <c r="AB15">
-        <v>98.356996715718111</v>
+        <v>45.820454931853</v>
       </c>
       <c r="AD15" t="s">
         <v>534</v>
@@ -10699,10 +10699,10 @@
         <v>1023</v>
       </c>
       <c r="AO15">
-        <v>0.99551365545858539</v>
+        <v>0.99746043308117838</v>
       </c>
       <c r="AP15">
-        <v>82.249649925934918</v>
+        <v>46.558726845063177</v>
       </c>
       <c r="AR15" t="s">
         <v>534</v>
@@ -10732,13 +10732,13 @@
         <v>1218</v>
       </c>
       <c r="BB15" t="s">
-        <v>1037</v>
+        <v>1219</v>
       </c>
       <c r="BC15">
-        <v>0.99418931598784899</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD15">
-        <v>106.52920688943452</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10803,16 +10803,16 @@
         <v>547</v>
       </c>
       <c r="Y16" t="s">
-        <v>517</v>
+        <v>422</v>
       </c>
       <c r="Z16" t="s">
         <v>774</v>
       </c>
       <c r="AA16">
-        <v>0.99343259267015904</v>
+        <v>0.99395341117186964</v>
       </c>
       <c r="AB16">
-        <v>120.40246771375152</v>
+        <v>110.85412851572337</v>
       </c>
       <c r="AD16" t="s">
         <v>534</v>
@@ -10845,10 +10845,10 @@
         <v>1025</v>
       </c>
       <c r="AO16">
-        <v>0.99554924619735208</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP16">
-        <v>81.597153048545437</v>
+        <v>341.91992986513412</v>
       </c>
       <c r="AR16" t="s">
         <v>534</v>
@@ -10875,16 +10875,16 @@
         <v>1158</v>
       </c>
       <c r="BA16" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="BB16" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="BC16">
-        <v>0.99665799830099</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD16">
-        <v>61.270031148516708</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10949,16 +10949,16 @@
         <v>549</v>
       </c>
       <c r="Y17" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="Z17" t="s">
         <v>775</v>
       </c>
       <c r="AA17">
-        <v>0.99012236069527793</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB17">
-        <v>181.09005391990564</v>
+        <v>307.49900901993823</v>
       </c>
       <c r="AD17" t="s">
         <v>534</v>
@@ -10991,10 +10991,10 @@
         <v>1027</v>
       </c>
       <c r="AO17">
-        <v>0.99083036293819104</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP17">
-        <v>168.11001279983091</v>
+        <v>258.57410995127316</v>
       </c>
       <c r="AR17" t="s">
         <v>534</v>
@@ -11021,16 +11021,16 @@
         <v>1160</v>
       </c>
       <c r="BA17" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="BB17" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="BC17">
-        <v>0.96863461872110523</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD17">
-        <v>575.0319901130714</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11095,16 +11095,16 @@
         <v>551</v>
       </c>
       <c r="Y18" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Z18" t="s">
         <v>776</v>
       </c>
       <c r="AA18">
-        <v>0.98990296758392993</v>
+        <v>0.9974199781412052</v>
       </c>
       <c r="AB18">
-        <v>185.11226096128556</v>
+        <v>47.300400744571718</v>
       </c>
       <c r="AD18" t="s">
         <v>534</v>
@@ -11137,10 +11137,10 @@
         <v>1029</v>
       </c>
       <c r="AO18">
-        <v>0.9976320377495026</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP18">
-        <v>43.412641259119624</v>
+        <v>40.90273458067751</v>
       </c>
       <c r="AR18" t="s">
         <v>534</v>
@@ -11167,16 +11167,16 @@
         <v>1162</v>
       </c>
       <c r="BA18" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="BB18" t="s">
-        <v>1097</v>
+        <v>1225</v>
       </c>
       <c r="BC18">
-        <v>0.99098965084511315</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD18">
-        <v>165.18973450625904</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11241,16 +11241,16 @@
         <v>553</v>
       </c>
       <c r="Y19" t="s">
-        <v>456</v>
+        <v>496</v>
       </c>
       <c r="Z19" t="s">
         <v>777</v>
       </c>
       <c r="AA19">
-        <v>0.99377714174527498</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB19">
-        <v>114.08573466995766</v>
+        <v>121.57987025257442</v>
       </c>
       <c r="AD19" t="s">
         <v>534</v>
@@ -11283,10 +11283,10 @@
         <v>1031</v>
       </c>
       <c r="AO19">
-        <v>0.99424679200457</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP19">
-        <v>105.47547991621673</v>
+        <v>74.530739771815789</v>
       </c>
       <c r="AR19" t="s">
         <v>534</v>
@@ -11313,16 +11313,16 @@
         <v>1164</v>
       </c>
       <c r="BA19" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="BB19" t="s">
-        <v>1225</v>
+        <v>1123</v>
       </c>
       <c r="BC19">
-        <v>0.99053278045305837</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD19">
-        <v>173.56569169392964</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11387,16 +11387,16 @@
         <v>555</v>
       </c>
       <c r="Y20" t="s">
-        <v>525</v>
+        <v>443</v>
       </c>
       <c r="Z20" t="s">
         <v>778</v>
       </c>
       <c r="AA20">
-        <v>0.99516685156772267</v>
+        <v>0.99379477670057537</v>
       </c>
       <c r="AB20">
-        <v>88.60772125841865</v>
+        <v>113.7624271561186</v>
       </c>
       <c r="AD20" t="s">
         <v>534</v>
@@ -11429,10 +11429,10 @@
         <v>1033</v>
       </c>
       <c r="AO20">
-        <v>0.98934663566509429</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP20">
-        <v>195.31167947327185</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR20" t="s">
         <v>534</v>
@@ -11459,16 +11459,16 @@
         <v>1166</v>
       </c>
       <c r="BA20" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="BB20" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="BC20">
-        <v>0.98488330873784669</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD20">
-        <v>277.13933980614473</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11533,16 +11533,16 @@
         <v>557</v>
       </c>
       <c r="Y21" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="Z21" t="s">
         <v>779</v>
       </c>
       <c r="AA21">
-        <v>0.9914627894548943</v>
+        <v>0.9961866142254362</v>
       </c>
       <c r="AB21">
-        <v>156.51552666027055</v>
+        <v>69.91207253366963</v>
       </c>
       <c r="AD21" t="s">
         <v>534</v>
@@ -11575,10 +11575,10 @@
         <v>1035</v>
       </c>
       <c r="AO21">
-        <v>0.99499049355022928</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP21">
-        <v>91.840951579129481</v>
+        <v>83.589016951479763</v>
       </c>
       <c r="AR21" t="s">
         <v>534</v>
@@ -11605,16 +11605,16 @@
         <v>1168</v>
       </c>
       <c r="BA21" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="BB21" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="BC21">
-        <v>0.99526086651282741</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD21">
-        <v>86.884113931497708</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11679,16 +11679,16 @@
         <v>559</v>
       </c>
       <c r="Y22" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="Z22" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="AA22">
-        <v>0.9776523073059149</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB22">
-        <v>409.70769939155917</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD22" t="s">
         <v>534</v>
@@ -11721,10 +11721,10 @@
         <v>1037</v>
       </c>
       <c r="AO22">
-        <v>0.99729205446773184</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP22">
-        <v>49.645668091582088</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR22" t="s">
         <v>534</v>
@@ -11751,16 +11751,16 @@
         <v>1170</v>
       </c>
       <c r="BA22" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="BB22" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="BC22">
-        <v>0.99054926914187857</v>
+        <v>0.99526086651282741</v>
       </c>
       <c r="BD22">
-        <v>173.26339906555947</v>
+        <v>86.884113931497708</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11825,16 +11825,16 @@
         <v>561</v>
       </c>
       <c r="Y23" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="Z23" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AA23">
-        <v>0.98289281118622185</v>
+        <v>0.99726809134187266</v>
       </c>
       <c r="AB23">
-        <v>313.63179491926536</v>
+        <v>50.0849920656675</v>
       </c>
       <c r="AD23" t="s">
         <v>534</v>
@@ -11867,10 +11867,10 @@
         <v>1039</v>
       </c>
       <c r="AO23">
-        <v>0.99746043308117838</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP23">
-        <v>46.558726845063177</v>
+        <v>138.50582323297994</v>
       </c>
       <c r="AR23" t="s">
         <v>534</v>
@@ -11897,16 +11897,16 @@
         <v>1172</v>
       </c>
       <c r="BA23" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="BB23" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="BC23">
-        <v>0.98027195861782945</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD23">
-        <v>361.68075867312689</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11971,16 +11971,16 @@
         <v>563</v>
       </c>
       <c r="Y24" t="s">
-        <v>424</v>
+        <v>481</v>
       </c>
       <c r="Z24" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="AA24">
-        <v>0.99593583828988941</v>
+        <v>0.97962408753770291</v>
       </c>
       <c r="AB24">
-        <v>74.509631352026517</v>
+        <v>373.55839514211272</v>
       </c>
       <c r="AD24" t="s">
         <v>534</v>
@@ -12010,13 +12010,13 @@
         <v>1040</v>
       </c>
       <c r="AN24" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AO24">
-        <v>0.95532613069733086</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP24">
-        <v>819.02093721560016</v>
+        <v>473.60023862765331</v>
       </c>
       <c r="AR24" t="s">
         <v>534</v>
@@ -12043,16 +12043,16 @@
         <v>1174</v>
       </c>
       <c r="BA24" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="BB24" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="BC24">
-        <v>0.98125520899414764</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD24">
-        <v>343.65450177395917</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12117,16 +12117,16 @@
         <v>565</v>
       </c>
       <c r="Y25" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="Z25" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="AA25">
-        <v>0.9621480095608167</v>
+        <v>0.99098167665935155</v>
       </c>
       <c r="AB25">
-        <v>693.95315805169378</v>
+        <v>165.33592791188894</v>
       </c>
       <c r="AD25" t="s">
         <v>534</v>
@@ -12156,13 +12156,13 @@
         <v>1041</v>
       </c>
       <c r="AN25" t="s">
-        <v>819</v>
+        <v>1042</v>
       </c>
       <c r="AO25">
-        <v>0.98599828568941739</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP25">
-        <v>256.69809569401372</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR25" t="s">
         <v>534</v>
@@ -12189,16 +12189,16 @@
         <v>1176</v>
       </c>
       <c r="BA25" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="BB25" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="BC25">
-        <v>0.98691003029105739</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD25">
-        <v>239.98277799728109</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12263,16 +12263,16 @@
         <v>567</v>
       </c>
       <c r="Y26" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="Z26" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="AA26">
-        <v>0.98916941127667946</v>
+        <v>0.98485684158558628</v>
       </c>
       <c r="AB26">
-        <v>198.56079326087576</v>
+        <v>277.62457093091871</v>
       </c>
       <c r="AD26" t="s">
         <v>534</v>
@@ -12299,16 +12299,16 @@
         <v>906</v>
       </c>
       <c r="AM26" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AN26" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AO26">
-        <v>0.98996241922424166</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP26">
-        <v>184.02231422223667</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR26" t="s">
         <v>534</v>
@@ -12335,16 +12335,16 @@
         <v>1178</v>
       </c>
       <c r="BA26" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="BB26" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="BC26">
-        <v>0.99834679070917032</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD26">
-        <v>30.308836998544216</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12409,16 +12409,16 @@
         <v>569</v>
       </c>
       <c r="Y27" t="s">
-        <v>438</v>
+        <v>493</v>
       </c>
       <c r="Z27" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="AA27">
-        <v>0.97159134368321343</v>
+        <v>0.98211145389932475</v>
       </c>
       <c r="AB27">
-        <v>520.82536580775354</v>
+        <v>327.95667851237977</v>
       </c>
       <c r="AD27" t="s">
         <v>534</v>
@@ -12445,16 +12445,16 @@
         <v>908</v>
       </c>
       <c r="AM27" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="AN27" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AO27">
-        <v>0.99620534810300254</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP27">
-        <v>69.568618111619969</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR27" t="s">
         <v>534</v>
@@ -12481,16 +12481,16 @@
         <v>1180</v>
       </c>
       <c r="BA27" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="BB27" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="BC27">
-        <v>0.99401640271965719</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD27">
-        <v>109.69928347295183</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12555,16 +12555,16 @@
         <v>571</v>
       </c>
       <c r="Y28" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="Z28" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="AA28">
-        <v>0.99359614530212825</v>
+        <v>0.99654205356515035</v>
       </c>
       <c r="AB28">
-        <v>117.40400279431638</v>
+        <v>63.395684638909763</v>
       </c>
       <c r="AD28" t="s">
         <v>534</v>
@@ -12591,16 +12591,16 @@
         <v>910</v>
       </c>
       <c r="AM28" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AN28" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AO28">
-        <v>0.99374536027070226</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP28">
-        <v>114.668395037126</v>
+        <v>80.747827133859133</v>
       </c>
       <c r="AR28" t="s">
         <v>534</v>
@@ -12627,16 +12627,16 @@
         <v>1182</v>
       </c>
       <c r="BA28" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="BB28" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="BC28">
-        <v>0.99032129621526932</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD28">
-        <v>177.44290272006148</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12701,16 +12701,16 @@
         <v>573</v>
       </c>
       <c r="Y29" t="s">
-        <v>518</v>
+        <v>460</v>
       </c>
       <c r="Z29" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="AA29">
-        <v>0.99488082982009873</v>
+        <v>0.99504817442297822</v>
       </c>
       <c r="AB29">
-        <v>93.851453298190577</v>
+        <v>90.78346891206678</v>
       </c>
       <c r="AD29" t="s">
         <v>534</v>
@@ -12737,16 +12737,16 @@
         <v>912</v>
       </c>
       <c r="AM29" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="AN29" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AO29">
-        <v>0.99681385284485569</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP29">
-        <v>58.41269784431158</v>
+        <v>60.189444792275019</v>
       </c>
       <c r="AR29" t="s">
         <v>534</v>
@@ -12773,16 +12773,16 @@
         <v>1184</v>
       </c>
       <c r="BA29" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="BB29" t="s">
-        <v>1245</v>
+        <v>1021</v>
       </c>
       <c r="BC29">
-        <v>0.99420451954813838</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD29">
-        <v>106.25047495079694</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12847,16 +12847,16 @@
         <v>575</v>
       </c>
       <c r="Y30" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="Z30" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="AA30">
-        <v>0.99557743229498485</v>
+        <v>0.99470247457730832</v>
       </c>
       <c r="AB30">
-        <v>81.080407925277868</v>
+        <v>97.121299416014665</v>
       </c>
       <c r="AD30" t="s">
         <v>534</v>
@@ -12883,16 +12883,16 @@
         <v>914</v>
       </c>
       <c r="AM30" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="AN30" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AO30">
-        <v>0.99527237968252791</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP30">
-        <v>86.673039153654699</v>
+        <v>82.249649925934918</v>
       </c>
       <c r="AR30" t="s">
         <v>534</v>
@@ -12925,10 +12925,10 @@
         <v>1247</v>
       </c>
       <c r="BC30">
-        <v>0.99203097418485064</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD30">
-        <v>146.09880661107059</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12993,16 +12993,16 @@
         <v>577</v>
       </c>
       <c r="Y31" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="Z31" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="AA31">
-        <v>0.99401156108202648</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB31">
-        <v>109.78804682951412</v>
+        <v>82.539922240185263</v>
       </c>
       <c r="AD31" t="s">
         <v>534</v>
@@ -13029,16 +13029,16 @@
         <v>916</v>
       </c>
       <c r="AM31" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AN31" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AO31">
-        <v>0.9917253583369573</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP31">
-        <v>151.70176382244892</v>
+        <v>81.597153048545437</v>
       </c>
       <c r="AR31" t="s">
         <v>534</v>
@@ -13071,10 +13071,10 @@
         <v>1249</v>
       </c>
       <c r="BC31">
-        <v>0.97821242976023937</v>
+        <v>0.99563011519444145</v>
       </c>
       <c r="BD31">
-        <v>399.43878772894504</v>
+        <v>80.114554768572972</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13139,16 +13139,16 @@
         <v>579</v>
       </c>
       <c r="Y32" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="Z32" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="AA32">
-        <v>0.96942910386940295</v>
+        <v>0.99012236069527793</v>
       </c>
       <c r="AB32">
-        <v>560.46642906094564</v>
+        <v>181.09005391990564</v>
       </c>
       <c r="AD32" t="s">
         <v>534</v>
@@ -13175,16 +13175,16 @@
         <v>918</v>
       </c>
       <c r="AM32" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="AN32" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="AO32">
-        <v>0.99569050067699549</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP32">
-        <v>79.007487588415231</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR32" t="s">
         <v>534</v>
@@ -13217,10 +13217,10 @@
         <v>1251</v>
       </c>
       <c r="BC32">
-        <v>0.9959052853503485</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD32">
-        <v>75.06976857694373</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13285,16 +13285,16 @@
         <v>581</v>
       </c>
       <c r="Y33" t="s">
-        <v>477</v>
+        <v>435</v>
       </c>
       <c r="Z33" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="AA33">
-        <v>0.99726809134187266</v>
+        <v>0.98990296758392993</v>
       </c>
       <c r="AB33">
-        <v>50.0849920656675</v>
+        <v>185.11226096128556</v>
       </c>
       <c r="AD33" t="s">
         <v>534</v>
@@ -13321,16 +13321,16 @@
         <v>920</v>
       </c>
       <c r="AM33" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AN33" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AO33">
-        <v>0.99567626923235475</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP33">
-        <v>79.268397406829976</v>
+        <v>43.412641259119624</v>
       </c>
       <c r="AR33" t="s">
         <v>534</v>
@@ -13363,10 +13363,10 @@
         <v>1253</v>
       </c>
       <c r="BC33">
-        <v>0.99563011519444145</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD33">
-        <v>80.114554768572972</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13431,16 +13431,16 @@
         <v>583</v>
       </c>
       <c r="Y34" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="Z34" t="s">
-        <v>770</v>
+        <v>789</v>
       </c>
       <c r="AA34">
-        <v>0.97962408753770291</v>
+        <v>0.99377714174527498</v>
       </c>
       <c r="AB34">
-        <v>373.55839514211272</v>
+        <v>114.08573466995766</v>
       </c>
       <c r="AD34" t="s">
         <v>534</v>
@@ -13467,16 +13467,16 @@
         <v>922</v>
       </c>
       <c r="AM34" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="AN34" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="AO34">
-        <v>0.99762284649610655</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP34">
-        <v>43.581147571379539</v>
+        <v>109.31605592223302</v>
       </c>
       <c r="AR34" t="s">
         <v>534</v>
@@ -13509,10 +13509,10 @@
         <v>1255</v>
       </c>
       <c r="BC34">
-        <v>0.98574436213546524</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD34">
-        <v>261.35336084980423</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13577,16 +13577,16 @@
         <v>585</v>
       </c>
       <c r="Y35" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="Z35" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="AA35">
-        <v>0.99098167665935155</v>
+        <v>0.99516685156772267</v>
       </c>
       <c r="AB35">
-        <v>165.33592791188894</v>
+        <v>88.60772125841865</v>
       </c>
       <c r="AD35" t="s">
         <v>534</v>
@@ -13613,16 +13613,16 @@
         <v>924</v>
       </c>
       <c r="AM35" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="AN35" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="AO35">
-        <v>0.99175391794306234</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP35">
-        <v>151.17817104385733</v>
+        <v>163.93514059684662</v>
       </c>
       <c r="AR35" t="s">
         <v>534</v>
@@ -13655,10 +13655,10 @@
         <v>1257</v>
       </c>
       <c r="BC35">
-        <v>0.98163861082146986</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD35">
-        <v>336.62546827305243</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13723,16 +13723,16 @@
         <v>587</v>
       </c>
       <c r="Y36" t="s">
-        <v>503</v>
+        <v>421</v>
       </c>
       <c r="Z36" t="s">
         <v>791</v>
       </c>
       <c r="AA36">
-        <v>0.98485684158558628</v>
+        <v>0.99553066735440277</v>
       </c>
       <c r="AB36">
-        <v>277.62457093091871</v>
+        <v>81.937765169281747</v>
       </c>
       <c r="AD36" t="s">
         <v>534</v>
@@ -13759,16 +13759,16 @@
         <v>926</v>
       </c>
       <c r="AM36" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AN36" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="AO36">
-        <v>0.99688290256322298</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP36">
-        <v>57.146786340912868</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR36" t="s">
         <v>534</v>
@@ -13801,10 +13801,10 @@
         <v>1259</v>
       </c>
       <c r="BC36">
-        <v>0.95713629889852414</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD36">
-        <v>785.83452019372396</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13869,16 +13869,16 @@
         <v>589</v>
       </c>
       <c r="Y37" t="s">
-        <v>493</v>
+        <v>445</v>
       </c>
       <c r="Z37" t="s">
         <v>792</v>
       </c>
       <c r="AA37">
-        <v>0.98211145389932475</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB37">
-        <v>327.95667851237977</v>
+        <v>174.28740880058183</v>
       </c>
       <c r="AD37" t="s">
         <v>534</v>
@@ -13905,16 +13905,16 @@
         <v>928</v>
       </c>
       <c r="AM37" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AN37" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="AO37">
-        <v>0.99488275259079373</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP37">
-        <v>93.81620250211445</v>
+        <v>85.270745539791065</v>
       </c>
       <c r="AR37" t="s">
         <v>534</v>
@@ -13944,13 +13944,13 @@
         <v>1260</v>
       </c>
       <c r="BB37" t="s">
-        <v>1247</v>
+        <v>1261</v>
       </c>
       <c r="BC37">
-        <v>0.98806872821788805</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD37">
-        <v>218.73998267205184</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14015,16 +14015,16 @@
         <v>591</v>
       </c>
       <c r="Y38" t="s">
-        <v>467</v>
+        <v>522</v>
       </c>
       <c r="Z38" t="s">
         <v>793</v>
       </c>
       <c r="AA38">
-        <v>0.99654205356515035</v>
+        <v>0.99575157784901702</v>
       </c>
       <c r="AB38">
-        <v>63.395684638909763</v>
+        <v>77.887739434686992</v>
       </c>
       <c r="AD38" t="s">
         <v>534</v>
@@ -14051,16 +14051,16 @@
         <v>930</v>
       </c>
       <c r="AM38" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AN38" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AO38">
-        <v>0.99663220850609069</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP38">
-        <v>61.742844055003644</v>
+        <v>430.61202751883985</v>
       </c>
       <c r="AR38" t="s">
         <v>534</v>
@@ -14087,16 +14087,16 @@
         <v>1202</v>
       </c>
       <c r="BA38" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="BB38" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="BC38">
-        <v>0.98946506962487613</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD38">
-        <v>193.14039021060518</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14161,16 +14161,16 @@
         <v>593</v>
       </c>
       <c r="Y39" t="s">
-        <v>460</v>
+        <v>526</v>
       </c>
       <c r="Z39" t="s">
-        <v>794</v>
+        <v>770</v>
       </c>
       <c r="AA39">
-        <v>0.99504817442297822</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB39">
-        <v>90.78346891206678</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD39" t="s">
         <v>534</v>
@@ -14197,16 +14197,16 @@
         <v>932</v>
       </c>
       <c r="AM39" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AN39" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AO39">
-        <v>0.99503039970536677</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP39">
-        <v>91.109338734942796</v>
+        <v>51.309699480432613</v>
       </c>
       <c r="AR39" t="s">
         <v>534</v>
@@ -14233,16 +14233,16 @@
         <v>1204</v>
       </c>
       <c r="BA39" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="BB39" t="s">
-        <v>1264</v>
+        <v>1223</v>
       </c>
       <c r="BC39">
-        <v>0.99314574070258299</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD39">
-        <v>125.66142045264445</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14307,16 +14307,16 @@
         <v>595</v>
       </c>
       <c r="Y40" t="s">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="Z40" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AA40">
-        <v>0.99470247457730832</v>
+        <v>0.95679935803281835</v>
       </c>
       <c r="AB40">
-        <v>97.121299416014665</v>
+        <v>792.01176939833033</v>
       </c>
       <c r="AD40" t="s">
         <v>534</v>
@@ -14343,16 +14343,16 @@
         <v>934</v>
       </c>
       <c r="AM40" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="AN40" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AO40">
-        <v>0.99544059907537386</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP40">
-        <v>83.589016951479763</v>
+        <v>64.433996023258757</v>
       </c>
       <c r="AR40" t="s">
         <v>534</v>
@@ -14385,10 +14385,10 @@
         <v>1266</v>
       </c>
       <c r="BC40">
-        <v>0.99232494426983575</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD40">
-        <v>140.70935505301131</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14453,16 +14453,16 @@
         <v>597</v>
       </c>
       <c r="Y41" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="Z41" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA41">
-        <v>0.99549782242326257</v>
+        <v>0.98761622532712257</v>
       </c>
       <c r="AB41">
-        <v>82.539922240185263</v>
+        <v>227.03586900275366</v>
       </c>
       <c r="AD41" t="s">
         <v>534</v>
@@ -14489,16 +14489,16 @@
         <v>936</v>
       </c>
       <c r="AM41" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AN41" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AO41">
-        <v>0.98829989485605374</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP41">
-        <v>214.50192763901472</v>
+        <v>43.009723520953628</v>
       </c>
       <c r="AR41" t="s">
         <v>534</v>
@@ -14531,10 +14531,10 @@
         <v>1268</v>
       </c>
       <c r="BC41">
-        <v>0.98775115723917273</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD41">
-        <v>224.56211728183334</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14599,16 +14599,16 @@
         <v>599</v>
       </c>
       <c r="Y42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="Z42" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA42">
-        <v>0.96520767961718001</v>
+        <v>0.99003402112096806</v>
       </c>
       <c r="AB42">
-        <v>637.85920701836687</v>
+        <v>182.70961278225187</v>
       </c>
       <c r="AD42" t="s">
         <v>534</v>
@@ -14635,16 +14635,16 @@
         <v>938</v>
       </c>
       <c r="AM42" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AN42" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AO42">
-        <v>0.99677419959133018</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP42">
-        <v>59.139674158947656</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14709,16 +14709,16 @@
         <v>601</v>
       </c>
       <c r="Y43" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="Z43" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AA43">
-        <v>0.99344074878931121</v>
+        <v>0.99466062705491098</v>
       </c>
       <c r="AB43">
-        <v>120.25293886262826</v>
+        <v>97.888503993298116</v>
       </c>
       <c r="AD43" t="s">
         <v>534</v>
@@ -14745,16 +14745,16 @@
         <v>940</v>
       </c>
       <c r="AM43" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="AN43" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="AO43">
-        <v>0.99766813121902409</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP43">
-        <v>42.750927651225993</v>
+        <v>96.528578181196991</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14819,16 +14819,16 @@
         <v>603</v>
       </c>
       <c r="Y44" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="Z44" t="s">
-        <v>770</v>
+        <v>798</v>
       </c>
       <c r="AA44">
-        <v>0.99459650548991607</v>
+        <v>0.9944598150968682</v>
       </c>
       <c r="AB44">
-        <v>99.064066018204684</v>
+        <v>101.5700565574154</v>
       </c>
       <c r="AD44" t="s">
         <v>534</v>
@@ -14855,16 +14855,16 @@
         <v>942</v>
       </c>
       <c r="AM44" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="AN44" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AO44">
-        <v>0.99760247912344124</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP44">
-        <v>43.95454940357709</v>
+        <v>49.543726018799653</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14929,16 +14929,16 @@
         <v>605</v>
       </c>
       <c r="Y45" t="s">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="Z45" t="s">
         <v>799</v>
       </c>
       <c r="AA45">
-        <v>0.99655727877565281</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB45">
-        <v>63.116555779697698</v>
+        <v>92.674656500591539</v>
       </c>
       <c r="AD45" t="s">
         <v>534</v>
@@ -14965,16 +14965,16 @@
         <v>944</v>
       </c>
       <c r="AM45" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AN45" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="AO45">
-        <v>0.99336049451151065</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP45">
-        <v>121.72426728897108</v>
+        <v>58.751500348127372</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15039,16 +15039,16 @@
         <v>607</v>
       </c>
       <c r="Y46" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="Z46" t="s">
         <v>800</v>
       </c>
       <c r="AA46">
-        <v>0.99221351039035977</v>
+        <v>0.99438812565699364</v>
       </c>
       <c r="AB46">
-        <v>142.75230951007163</v>
+        <v>102.88436295511657</v>
       </c>
       <c r="AD46" t="s">
         <v>534</v>
@@ -15075,16 +15075,16 @@
         <v>946</v>
       </c>
       <c r="AM46" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AN46" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AO46">
-        <v>0.99759498179797546</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP46">
-        <v>44.092000370450322</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15149,16 +15149,16 @@
         <v>609</v>
       </c>
       <c r="Y47" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
       <c r="Z47" t="s">
         <v>801</v>
       </c>
       <c r="AA47">
-        <v>0.99067174034238459</v>
+        <v>0.99643191679577148</v>
       </c>
       <c r="AB47">
-        <v>171.01809372294977</v>
+        <v>65.414858744189985</v>
       </c>
       <c r="AD47" t="s">
         <v>534</v>
@@ -15185,16 +15185,16 @@
         <v>948</v>
       </c>
       <c r="AM47" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AN47" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="AO47">
-        <v>0.99244513691456471</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP47">
-        <v>138.50582323297994</v>
+        <v>57.905423216266421</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15259,16 +15259,16 @@
         <v>611</v>
       </c>
       <c r="Y48" t="s">
-        <v>418</v>
+        <v>529</v>
       </c>
       <c r="Z48" t="s">
         <v>802</v>
       </c>
       <c r="AA48">
-        <v>0.99634417822754895</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB48">
-        <v>67.023399161603095</v>
+        <v>637.85920701836687</v>
       </c>
       <c r="AD48" t="s">
         <v>534</v>
@@ -15295,16 +15295,16 @@
         <v>950</v>
       </c>
       <c r="AM48" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="AN48" t="s">
-        <v>844</v>
+        <v>1088</v>
       </c>
       <c r="AO48">
-        <v>0.97416725971121887</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP48">
-        <v>473.60023862765331</v>
+        <v>85.716830221163534</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15369,16 +15369,16 @@
         <v>613</v>
       </c>
       <c r="Y49" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="Z49" t="s">
         <v>803</v>
       </c>
       <c r="AA49">
-        <v>0.98416341622871006</v>
+        <v>0.99344074878931121</v>
       </c>
       <c r="AB49">
-        <v>290.33736914031488</v>
+        <v>120.25293886262826</v>
       </c>
       <c r="AD49" t="s">
         <v>534</v>
@@ -15405,16 +15405,16 @@
         <v>952</v>
       </c>
       <c r="AM49" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="AN49" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="AO49">
-        <v>0.99760255773158468</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP49">
-        <v>43.953108254279897</v>
+        <v>74.464817689622748</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15479,16 +15479,16 @@
         <v>615</v>
       </c>
       <c r="Y50" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Z50" t="s">
-        <v>804</v>
+        <v>770</v>
       </c>
       <c r="AA50">
-        <v>0.99563792883070867</v>
+        <v>0.99459650548991607</v>
       </c>
       <c r="AB50">
-        <v>79.971304770340467</v>
+        <v>99.064066018204684</v>
       </c>
       <c r="AD50" t="s">
         <v>534</v>
@@ -15515,16 +15515,16 @@
         <v>954</v>
       </c>
       <c r="AM50" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="AN50" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="AO50">
-        <v>0.99352359657507616</v>
+        <v>0.99677419959133018</v>
       </c>
       <c r="AP50">
-        <v>118.7340627902709</v>
+        <v>59.139674158947656</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15589,16 +15589,16 @@
         <v>617</v>
       </c>
       <c r="Y51" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
       <c r="Z51" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AA51">
-        <v>0.99558181127270129</v>
+        <v>0.99655727877565281</v>
       </c>
       <c r="AB51">
-        <v>81.000126667143434</v>
+        <v>63.116555779697698</v>
       </c>
       <c r="AD51" t="s">
         <v>534</v>
@@ -15625,16 +15625,16 @@
         <v>956</v>
       </c>
       <c r="AM51" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="AN51" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="AO51">
-        <v>0.99433447571906541</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP51">
-        <v>103.86794515046822</v>
+        <v>42.750927651225993</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15699,16 +15699,16 @@
         <v>619</v>
       </c>
       <c r="Y52" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
       <c r="Z52" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AA52">
-        <v>0.99390501557434718</v>
+        <v>0.99221351039035977</v>
       </c>
       <c r="AB52">
-        <v>111.7413811369688</v>
+        <v>142.75230951007163</v>
       </c>
       <c r="AD52" t="s">
         <v>534</v>
@@ -15735,16 +15735,16 @@
         <v>958</v>
       </c>
       <c r="AM52" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AN52" t="s">
-        <v>776</v>
+        <v>1096</v>
       </c>
       <c r="AO52">
-        <v>0.98674094240398891</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP52">
-        <v>243.0827225935364</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15809,16 +15809,16 @@
         <v>621</v>
       </c>
       <c r="Y53" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="Z53" t="s">
-        <v>783</v>
+        <v>806</v>
       </c>
       <c r="AA53">
-        <v>0.97432735774114165</v>
+        <v>0.99067174034238459</v>
       </c>
       <c r="AB53">
-        <v>470.66510807906917</v>
+        <v>171.01809372294977</v>
       </c>
       <c r="AD53" t="s">
         <v>534</v>
@@ -15845,16 +15845,16 @@
         <v>960</v>
       </c>
       <c r="AM53" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="AN53" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="AO53">
-        <v>0.98452519237182756</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP53">
-        <v>283.70480651649393</v>
+        <v>121.72426728897108</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15919,16 +15919,16 @@
         <v>623</v>
       </c>
       <c r="Y54" t="s">
-        <v>487</v>
+        <v>418</v>
       </c>
       <c r="Z54" t="s">
         <v>807</v>
       </c>
       <c r="AA54">
-        <v>0.9882282251528024</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB54">
-        <v>215.81587219862183</v>
+        <v>67.023399161603095</v>
       </c>
       <c r="AD54" t="s">
         <v>534</v>
@@ -15955,16 +15955,16 @@
         <v>962</v>
       </c>
       <c r="AM54" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="AN54" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="AO54">
-        <v>0.99679967385551038</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP54">
-        <v>58.672645982308907</v>
+        <v>44.092000370450322</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16029,16 +16029,16 @@
         <v>625</v>
       </c>
       <c r="Y55" t="s">
-        <v>494</v>
+        <v>453</v>
       </c>
       <c r="Z55" t="s">
         <v>808</v>
       </c>
       <c r="AA55">
-        <v>0.99136196456122894</v>
+        <v>0.98416341622871006</v>
       </c>
       <c r="AB55">
-        <v>158.36398304413572</v>
+        <v>290.33736914031488</v>
       </c>
       <c r="AD55" t="s">
         <v>534</v>
@@ -16065,16 +16065,16 @@
         <v>964</v>
       </c>
       <c r="AM55" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="AN55" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="AO55">
-        <v>0.99414234808301016</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP55">
-        <v>107.39028514481463</v>
+        <v>79.268397406829976</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16139,16 +16139,16 @@
         <v>627</v>
       </c>
       <c r="Y56" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="Z56" t="s">
         <v>809</v>
       </c>
       <c r="AA56">
-        <v>0.99658191580238853</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB56">
-        <v>62.664876956210314</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD56" t="s">
         <v>534</v>
@@ -16175,16 +16175,16 @@
         <v>966</v>
       </c>
       <c r="AM56" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="AN56" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="AO56">
-        <v>0.98134982200735632</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP56">
-        <v>341.91992986513412</v>
+        <v>43.581147571379539</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16249,16 +16249,16 @@
         <v>629</v>
       </c>
       <c r="Y57" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="Z57" t="s">
         <v>810</v>
       </c>
       <c r="AA57">
-        <v>0.99772567527055689</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB57">
-        <v>41.695953373122713</v>
+        <v>81.000126667143434</v>
       </c>
       <c r="AD57" t="s">
         <v>534</v>
@@ -16285,16 +16285,16 @@
         <v>968</v>
       </c>
       <c r="AM57" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="AN57" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="AO57">
-        <v>0.98589595763902149</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP57">
-        <v>258.57410995127316</v>
+        <v>151.17817104385733</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16359,16 +16359,16 @@
         <v>631</v>
       </c>
       <c r="Y58" t="s">
-        <v>472</v>
+        <v>516</v>
       </c>
       <c r="Z58" t="s">
         <v>811</v>
       </c>
       <c r="AA58">
-        <v>0.99649411432543766</v>
+        <v>0.99390501557434718</v>
       </c>
       <c r="AB58">
-        <v>64.274570700309781</v>
+        <v>111.7413811369688</v>
       </c>
       <c r="AD58" t="s">
         <v>534</v>
@@ -16395,16 +16395,16 @@
         <v>970</v>
       </c>
       <c r="AM58" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="AN58" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="AO58">
-        <v>0.99776894175014486</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP58">
-        <v>40.90273458067751</v>
+        <v>57.146786340912868</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16469,16 +16469,16 @@
         <v>633</v>
       </c>
       <c r="Y59" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="Z59" t="s">
         <v>812</v>
       </c>
       <c r="AA59">
-        <v>0.97907421743006762</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB59">
-        <v>383.63934711542669</v>
+        <v>64.274570700309781</v>
       </c>
       <c r="AD59" t="s">
         <v>534</v>
@@ -16505,16 +16505,16 @@
         <v>972</v>
       </c>
       <c r="AM59" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="AN59" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="AO59">
-        <v>0.9959346869215373</v>
+        <v>0.99488275259079373</v>
       </c>
       <c r="AP59">
-        <v>74.530739771815789</v>
+        <v>93.81620250211445</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16579,16 +16579,16 @@
         <v>635</v>
       </c>
       <c r="Y60" t="s">
-        <v>426</v>
+        <v>480</v>
       </c>
       <c r="Z60" t="s">
         <v>813</v>
       </c>
       <c r="AA60">
-        <v>0.99558768376711515</v>
+        <v>0.97907421743006762</v>
       </c>
       <c r="AB60">
-        <v>80.892464269556413</v>
+        <v>383.63934711542669</v>
       </c>
       <c r="AD60" t="s">
         <v>534</v>
@@ -16615,16 +16615,16 @@
         <v>974</v>
       </c>
       <c r="AM60" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="AN60" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="AO60">
-        <v>0.9955955730654259</v>
+        <v>0.99663220850609069</v>
       </c>
       <c r="AP60">
-        <v>80.747827133859133</v>
+        <v>61.742844055003644</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16689,16 +16689,16 @@
         <v>637</v>
       </c>
       <c r="Y61" t="s">
-        <v>510</v>
+        <v>426</v>
       </c>
       <c r="Z61" t="s">
         <v>814</v>
       </c>
       <c r="AA61">
-        <v>0.99324569511004301</v>
+        <v>0.99558768376711515</v>
       </c>
       <c r="AB61">
-        <v>123.82892298254488</v>
+        <v>80.892464269556413</v>
       </c>
       <c r="AD61" t="s">
         <v>534</v>
@@ -16725,16 +16725,16 @@
         <v>976</v>
       </c>
       <c r="AM61" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="AN61" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="AO61">
-        <v>0.99671693937496686</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP61">
-        <v>60.189444792275019</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16799,16 +16799,16 @@
         <v>639</v>
       </c>
       <c r="Y62" t="s">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="Z62" t="s">
         <v>815</v>
       </c>
       <c r="AA62">
-        <v>0.99419165427276146</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB62">
-        <v>106.48633833270691</v>
+        <v>123.82892298254488</v>
       </c>
       <c r="AD62" t="s">
         <v>534</v>
@@ -16835,16 +16835,16 @@
         <v>978</v>
       </c>
       <c r="AM62" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="AN62" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="AO62">
-        <v>0.99403730604060547</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP62">
-        <v>109.31605592223302</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16909,16 +16909,16 @@
         <v>641</v>
       </c>
       <c r="Y63" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="Z63" t="s">
         <v>816</v>
       </c>
       <c r="AA63">
-        <v>0.99198935558098356</v>
+        <v>0.99419165427276146</v>
       </c>
       <c r="AB63">
-        <v>146.8618143486346</v>
+        <v>106.48633833270691</v>
       </c>
       <c r="AD63" t="s">
         <v>534</v>
@@ -16945,16 +16945,16 @@
         <v>980</v>
       </c>
       <c r="AM63" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="AN63" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="AO63">
-        <v>0.99105808324017197</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP63">
-        <v>163.93514059684662</v>
+        <v>53.069246900976879</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17019,16 +17019,16 @@
         <v>643</v>
       </c>
       <c r="Y64" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="Z64" t="s">
         <v>817</v>
       </c>
       <c r="AA64">
-        <v>0.99295369446862825</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB64">
-        <v>129.18226807514921</v>
+        <v>146.8618143486346</v>
       </c>
       <c r="AD64" t="s">
         <v>534</v>
@@ -17055,16 +17055,16 @@
         <v>982</v>
       </c>
       <c r="AM64" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="AN64" t="s">
-        <v>1117</v>
+        <v>788</v>
       </c>
       <c r="AO64">
-        <v>0.9974675531234084</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP64">
-        <v>46.428192737512276</v>
+        <v>243.0827225935364</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17129,16 +17129,16 @@
         <v>645</v>
       </c>
       <c r="Y65" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="Z65" t="s">
         <v>818</v>
       </c>
       <c r="AA65">
-        <v>0.98571261124433651</v>
+        <v>0.99240925523869494</v>
       </c>
       <c r="AB65">
-        <v>261.93546052049794</v>
+        <v>139.16365395725984</v>
       </c>
       <c r="AD65" t="s">
         <v>534</v>
@@ -17165,16 +17165,16 @@
         <v>984</v>
       </c>
       <c r="AM65" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="AN65" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AO65">
-        <v>0.99534886842510228</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP65">
-        <v>85.270745539791065</v>
+        <v>283.70480651649393</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17239,16 +17239,16 @@
         <v>647</v>
       </c>
       <c r="Y66" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="Z66" t="s">
-        <v>819</v>
+        <v>770</v>
       </c>
       <c r="AA66">
-        <v>0.9849019911873127</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB66">
-        <v>276.79682823259958</v>
+        <v>505.08652809978111</v>
       </c>
       <c r="AD66" t="s">
         <v>534</v>
@@ -17275,16 +17275,16 @@
         <v>986</v>
       </c>
       <c r="AM66" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="AN66" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="AO66">
-        <v>0.97020178001960844</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP66">
-        <v>546.30069964051177</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17349,16 +17349,16 @@
         <v>649</v>
       </c>
       <c r="Y67" t="s">
-        <v>419</v>
+        <v>489</v>
       </c>
       <c r="Z67" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AA67">
-        <v>0.99157679714615166</v>
+        <v>0.99172397756136033</v>
       </c>
       <c r="AB67">
-        <v>154.42538565388551</v>
+        <v>151.72707804172813</v>
       </c>
       <c r="AD67" t="s">
         <v>534</v>
@@ -17385,16 +17385,16 @@
         <v>988</v>
       </c>
       <c r="AM67" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="AN67" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AO67">
-        <v>0.99693672852577231</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP67">
-        <v>56.159977027506663</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17459,16 +17459,16 @@
         <v>651</v>
       </c>
       <c r="Y68" t="s">
-        <v>515</v>
+        <v>451</v>
       </c>
       <c r="Z68" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AA68">
-        <v>0.99619387577842089</v>
+        <v>0.99431900976645593</v>
       </c>
       <c r="AB68">
-        <v>69.778944062284495</v>
+        <v>104.15148761497397</v>
       </c>
       <c r="AD68" t="s">
         <v>534</v>
@@ -17495,16 +17495,16 @@
         <v>990</v>
       </c>
       <c r="AM68" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AN68" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="AO68">
-        <v>0.99478775228549088</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP68">
-        <v>95.557874766001078</v>
+        <v>546.30069964051177</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17569,16 +17569,16 @@
         <v>653</v>
       </c>
       <c r="Y69" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="Z69" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AA69">
-        <v>0.99497915241892609</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB69">
-        <v>92.048872319688599</v>
+        <v>98.356996715718111</v>
       </c>
       <c r="AD69" t="s">
         <v>534</v>
@@ -17605,16 +17605,16 @@
         <v>992</v>
       </c>
       <c r="AM69" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="AN69" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="AO69">
-        <v>0.97651207122624506</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP69">
-        <v>430.61202751883985</v>
+        <v>56.159977027506663</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17679,16 +17679,16 @@
         <v>655</v>
       </c>
       <c r="Y70" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="Z70" t="s">
-        <v>770</v>
+        <v>822</v>
       </c>
       <c r="AA70">
-        <v>0.93980266520001188</v>
+        <v>0.99343259267015904</v>
       </c>
       <c r="AB70">
-        <v>1103.617804666449</v>
+        <v>120.40246771375152</v>
       </c>
       <c r="AD70" t="s">
         <v>534</v>
@@ -17715,16 +17715,16 @@
         <v>994</v>
       </c>
       <c r="AM70" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="AN70" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="AO70">
-        <v>0.9972012891192491</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP70">
-        <v>51.309699480432613</v>
+        <v>95.557874766001078</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17789,16 +17789,16 @@
         <v>657</v>
       </c>
       <c r="Y71" t="s">
-        <v>530</v>
+        <v>474</v>
       </c>
       <c r="Z71" t="s">
         <v>823</v>
       </c>
       <c r="AA71">
-        <v>0.95679935803281835</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB71">
-        <v>792.01176939833033</v>
+        <v>90.443352439796072</v>
       </c>
       <c r="AD71" t="s">
         <v>534</v>
@@ -17825,16 +17825,16 @@
         <v>996</v>
       </c>
       <c r="AM71" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="AN71" t="s">
-        <v>1131</v>
+        <v>794</v>
       </c>
       <c r="AO71">
-        <v>0.99648541839873139</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP71">
-        <v>64.433996023258757</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17899,16 +17899,16 @@
         <v>659</v>
       </c>
       <c r="Y72" t="s">
-        <v>501</v>
+        <v>439</v>
       </c>
       <c r="Z72" t="s">
         <v>824</v>
       </c>
       <c r="AA72">
-        <v>0.98761622532712257</v>
+        <v>0.97537853020161625</v>
       </c>
       <c r="AB72">
-        <v>227.03586900275366</v>
+        <v>451.39361297036953</v>
       </c>
       <c r="AD72" t="s">
         <v>534</v>
@@ -17935,16 +17935,16 @@
         <v>998</v>
       </c>
       <c r="AM72" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AN72" t="s">
-        <v>1133</v>
+        <v>857</v>
       </c>
       <c r="AO72">
-        <v>0.9976540150806753</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP72">
-        <v>43.009723520953628</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18009,16 +18009,16 @@
         <v>661</v>
       </c>
       <c r="Y73" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="Z73" t="s">
         <v>825</v>
       </c>
       <c r="AA73">
-        <v>0.99003402112096806</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB73">
-        <v>182.70961278225187</v>
+        <v>106.82211818572355</v>
       </c>
       <c r="AD73" t="s">
         <v>534</v>
@@ -18051,10 +18051,10 @@
         <v>1135</v>
       </c>
       <c r="AO73">
-        <v>0.99644815774097173</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP73">
-        <v>65.117108082185538</v>
+        <v>184.02231422223667</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18119,16 +18119,16 @@
         <v>663</v>
       </c>
       <c r="Y74" t="s">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="Z74" t="s">
         <v>826</v>
       </c>
       <c r="AA74">
-        <v>0.99466062705491098</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB74">
-        <v>97.888503993298116</v>
+        <v>62.251070203636829</v>
       </c>
       <c r="AD74" t="s">
         <v>534</v>
@@ -18161,10 +18161,10 @@
         <v>1137</v>
       </c>
       <c r="AO74">
-        <v>0.99445933293330402</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP74">
-        <v>101.57889622275951</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18229,16 +18229,16 @@
         <v>665</v>
       </c>
       <c r="Y75" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="Z75" t="s">
         <v>827</v>
       </c>
       <c r="AA75">
-        <v>0.9944598150968682</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB75">
-        <v>101.5700565574154</v>
+        <v>54.23617409891024</v>
       </c>
       <c r="AD75" t="s">
         <v>534</v>
@@ -18271,10 +18271,10 @@
         <v>1139</v>
       </c>
       <c r="AO75">
-        <v>0.9961850470371636</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP75">
-        <v>69.94080431866837</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18339,16 +18339,16 @@
         <v>667</v>
       </c>
       <c r="Y76" t="s">
-        <v>462</v>
+        <v>512</v>
       </c>
       <c r="Z76" t="s">
         <v>828</v>
       </c>
       <c r="AA76">
-        <v>0.99494501873633134</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB76">
-        <v>92.674656500591539</v>
+        <v>154.58276065179118</v>
       </c>
       <c r="AD76" t="s">
         <v>534</v>
@@ -18381,10 +18381,10 @@
         <v>1141</v>
       </c>
       <c r="AO76">
-        <v>0.99710531380540124</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP76">
-        <v>53.069246900976879</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18449,16 +18449,16 @@
         <v>669</v>
       </c>
       <c r="Y77" t="s">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="Z77" t="s">
         <v>829</v>
       </c>
       <c r="AA77">
-        <v>0.99438812565699364</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB77">
-        <v>102.88436295511657</v>
+        <v>49.309812409870183</v>
       </c>
       <c r="AD77" t="s">
         <v>534</v>
@@ -18491,10 +18491,10 @@
         <v>1143</v>
       </c>
       <c r="AO77">
-        <v>0.99684152237002188</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP77">
-        <v>57.905423216266421</v>
+        <v>86.673039153654699</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18559,16 +18559,16 @@
         <v>671</v>
       </c>
       <c r="Y78" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="Z78" t="s">
         <v>830</v>
       </c>
       <c r="AA78">
-        <v>0.99643191679577148</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB78">
-        <v>65.414858744189985</v>
+        <v>121.27899510281891</v>
       </c>
       <c r="AD78" t="s">
         <v>534</v>
@@ -18601,10 +18601,10 @@
         <v>1145</v>
       </c>
       <c r="AO78">
-        <v>0.99532453653339104</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP78">
-        <v>85.716830221163534</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18669,16 +18669,16 @@
         <v>673</v>
       </c>
       <c r="Y79" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="Z79" t="s">
-        <v>831</v>
+        <v>769</v>
       </c>
       <c r="AA79">
-        <v>0.99553066735440277</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB79">
-        <v>81.937765169281747</v>
+        <v>470.66510807906917</v>
       </c>
       <c r="AD79" t="s">
         <v>534</v>
@@ -18711,10 +18711,10 @@
         <v>1147</v>
       </c>
       <c r="AO79">
-        <v>0.99593828267147511</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP79">
-        <v>74.464817689622748</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18779,16 +18779,16 @@
         <v>675</v>
       </c>
       <c r="Y80" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="Z80" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AA80">
-        <v>0.99049341406542279</v>
+        <v>0.9882282251528024</v>
       </c>
       <c r="AB80">
-        <v>174.28740880058183</v>
+        <v>215.81587219862183</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18853,16 +18853,16 @@
         <v>677</v>
       </c>
       <c r="Y81" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
       <c r="Z81" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AA81">
-        <v>0.99575157784901702</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB81">
-        <v>77.887739434686992</v>
+        <v>158.36398304413572</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18927,16 +18927,16 @@
         <v>679</v>
       </c>
       <c r="Y82" t="s">
-        <v>527</v>
+        <v>427</v>
       </c>
       <c r="Z82" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AA82">
-        <v>0.95261480241426988</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB82">
-        <v>868.72862240505196</v>
+        <v>62.664876956210314</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -19001,16 +19001,16 @@
         <v>681</v>
       </c>
       <c r="Y83" t="s">
-        <v>531</v>
+        <v>428</v>
       </c>
       <c r="Z83" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AA83">
-        <v>0.97404342257401955</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB83">
-        <v>475.8705861429753</v>
+        <v>41.695953373122713</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -19075,16 +19075,16 @@
         <v>683</v>
       </c>
       <c r="Y84" t="s">
-        <v>420</v>
+        <v>483</v>
       </c>
       <c r="Z84" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AA84">
-        <v>0.98762421667584677</v>
+        <v>0.9914627894548943</v>
       </c>
       <c r="AB84">
-        <v>226.88936094280919</v>
+        <v>156.51552666027055</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -19149,16 +19149,16 @@
         <v>685</v>
       </c>
       <c r="Y85" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="Z85" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="AA85">
-        <v>0.98775140142897844</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB85">
-        <v>224.55764046872929</v>
+        <v>409.70769939155917</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19223,16 +19223,16 @@
         <v>687</v>
       </c>
       <c r="Y86" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="Z86" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AA86">
-        <v>0.99647006537565563</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB86">
-        <v>64.715468112981057</v>
+        <v>313.63179491926536</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19297,16 +19297,16 @@
         <v>689</v>
       </c>
       <c r="Y87" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="Z87" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AA87">
-        <v>0.96480371616361149</v>
+        <v>0.99593583828988941</v>
       </c>
       <c r="AB87">
-        <v>645.26520366712316</v>
+        <v>74.509631352026517</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19371,16 +19371,16 @@
         <v>691</v>
       </c>
       <c r="Y88" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="Z88" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AA88">
-        <v>0.99267004448650609</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB88">
-        <v>134.38251774738842</v>
+        <v>443.37880474956393</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19445,16 +19445,16 @@
         <v>693</v>
       </c>
       <c r="Y89" t="s">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="Z89" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AA89">
-        <v>0.9948848527457459</v>
+        <v>0.99542292233022822</v>
       </c>
       <c r="AB89">
-        <v>93.777699661325343</v>
+        <v>83.913090612483515</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19519,16 +19519,16 @@
         <v>695</v>
       </c>
       <c r="Y90" t="s">
-        <v>524</v>
+        <v>450</v>
       </c>
       <c r="Z90" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AA90">
-        <v>0.9922030648239526</v>
+        <v>0.99647584863086869</v>
       </c>
       <c r="AB90">
-        <v>142.94381156086857</v>
+        <v>64.60944176740837</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19593,16 +19593,16 @@
         <v>697</v>
       </c>
       <c r="Y91" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="Z91" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AA91">
-        <v>0.99506672623055659</v>
+        <v>0.99780983219878738</v>
       </c>
       <c r="AB91">
-        <v>90.443352439796072</v>
+        <v>40.153076355563911</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19667,16 +19667,16 @@
         <v>699</v>
       </c>
       <c r="Y92" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="Z92" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AA92">
-        <v>0.97537853020161625</v>
+        <v>0.99724696581141214</v>
       </c>
       <c r="AB92">
-        <v>451.39361297036953</v>
+        <v>50.472293457444586</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19741,16 +19741,16 @@
         <v>701</v>
       </c>
       <c r="Y93" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="Z93" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="AA93">
-        <v>0.99417333900805149</v>
+        <v>0.99589550629055523</v>
       </c>
       <c r="AB93">
-        <v>106.82211818572355</v>
+        <v>75.249051339820184</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19815,16 +19815,16 @@
         <v>703</v>
       </c>
       <c r="Y94" t="s">
-        <v>429</v>
+        <v>520</v>
       </c>
       <c r="Z94" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AA94">
-        <v>0.99660448707980165</v>
+        <v>0.99531156065644533</v>
       </c>
       <c r="AB94">
-        <v>62.251070203636829</v>
+        <v>85.954721298502818</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19889,16 +19889,16 @@
         <v>705</v>
       </c>
       <c r="Y95" t="s">
-        <v>433</v>
+        <v>521</v>
       </c>
       <c r="Z95" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AA95">
-        <v>0.99704166323096854</v>
+        <v>0.99706825374988217</v>
       </c>
       <c r="AB95">
-        <v>54.23617409891024</v>
+        <v>53.748681252160438</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19963,16 +19963,16 @@
         <v>707</v>
       </c>
       <c r="Y96" t="s">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="Z96" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AA96">
-        <v>0.99156821305535681</v>
+        <v>0.98150124893892388</v>
       </c>
       <c r="AB96">
-        <v>154.58276065179118</v>
+        <v>339.14376945306287</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -20037,16 +20037,16 @@
         <v>709</v>
       </c>
       <c r="Y97" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="Z97" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AA97">
-        <v>0.99731037386855248</v>
+        <v>0.99523081353776888</v>
       </c>
       <c r="AB97">
-        <v>49.309812409870183</v>
+        <v>87.435085140903482</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -20111,16 +20111,16 @@
         <v>711</v>
       </c>
       <c r="Y98" t="s">
-        <v>514</v>
+        <v>442</v>
       </c>
       <c r="Z98" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AA98">
-        <v>0.99338478208530079</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB98">
-        <v>121.27899510281891</v>
+        <v>153.20678909592235</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20185,16 +20185,16 @@
         <v>713</v>
       </c>
       <c r="Y99" t="s">
-        <v>473</v>
+        <v>423</v>
       </c>
       <c r="Z99" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AA99">
-        <v>0.97581570155911468</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB99">
-        <v>443.37880474956393</v>
+        <v>78.81162391526847</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20259,16 +20259,16 @@
         <v>715</v>
       </c>
       <c r="Y100" t="s">
-        <v>485</v>
+        <v>436</v>
       </c>
       <c r="Z100" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AA100">
-        <v>0.99542292233022822</v>
+        <v>0.99691903985105013</v>
       </c>
       <c r="AB100">
-        <v>83.913090612483515</v>
+        <v>56.484269397415083</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20333,16 +20333,16 @@
         <v>717</v>
       </c>
       <c r="Y101" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="Z101" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AA101">
-        <v>0.99647584863086869</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB101">
-        <v>64.60944176740837</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20407,16 +20407,16 @@
         <v>719</v>
       </c>
       <c r="Y102" t="s">
-        <v>431</v>
+        <v>509</v>
       </c>
       <c r="Z102" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AA102">
-        <v>0.99780983219878738</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB102">
-        <v>40.153076355563911</v>
+        <v>86.308558527470979</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20481,16 +20481,16 @@
         <v>721</v>
       </c>
       <c r="Y103" t="s">
-        <v>466</v>
+        <v>511</v>
       </c>
       <c r="Z103" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AA103">
-        <v>0.99724696581141214</v>
+        <v>0.99443562760718263</v>
       </c>
       <c r="AB103">
-        <v>50.472293457444586</v>
+        <v>102.01349386831856</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20555,16 +20555,16 @@
         <v>723</v>
       </c>
       <c r="Y104" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="Z104" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AA104">
-        <v>0.99589550629055523</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB104">
-        <v>75.249051339820184</v>
+        <v>129.18226807514921</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20629,16 +20629,16 @@
         <v>725</v>
       </c>
       <c r="Y105" t="s">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="Z105" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AA105">
-        <v>0.99531156065644533</v>
+        <v>0.98571261124433651</v>
       </c>
       <c r="AB105">
-        <v>85.954721298502818</v>
+        <v>261.93546052049794</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20703,16 +20703,16 @@
         <v>727</v>
       </c>
       <c r="Y106" t="s">
-        <v>521</v>
+        <v>440</v>
       </c>
       <c r="Z106" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AA106">
-        <v>0.99706825374988217</v>
+        <v>0.9849019911873127</v>
       </c>
       <c r="AB106">
-        <v>53.748681252160438</v>
+        <v>276.79682823259958</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20777,16 +20777,16 @@
         <v>729</v>
       </c>
       <c r="Y107" t="s">
-        <v>469</v>
+        <v>419</v>
       </c>
       <c r="Z107" t="s">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="AA107">
-        <v>0.96238190390083644</v>
+        <v>0.99157679714615166</v>
       </c>
       <c r="AB107">
-        <v>689.665095151331</v>
+        <v>154.42538565388551</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20851,16 +20851,16 @@
         <v>731</v>
       </c>
       <c r="Y108" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="Z108" t="s">
-        <v>770</v>
+        <v>859</v>
       </c>
       <c r="AA108">
-        <v>0.96316770855847034</v>
+        <v>0.99619387577842089</v>
       </c>
       <c r="AB108">
-        <v>675.25867642804383</v>
+        <v>69.778944062284495</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20925,16 +20925,16 @@
         <v>733</v>
       </c>
       <c r="Y109" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="Z109" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AA109">
-        <v>0.9951089264264793</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB109">
-        <v>89.669682181211982</v>
+        <v>92.048872319688599</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20999,16 +20999,16 @@
         <v>735</v>
       </c>
       <c r="Y110" t="s">
-        <v>434</v>
+        <v>527</v>
       </c>
       <c r="Z110" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AA110">
-        <v>0.98666519734623237</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB110">
-        <v>244.47138198573927</v>
+        <v>868.72862240505196</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -21073,16 +21073,16 @@
         <v>737</v>
       </c>
       <c r="Y111" t="s">
-        <v>425</v>
+        <v>531</v>
       </c>
       <c r="Z111" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AA111">
-        <v>0.99750070245826261</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB111">
-        <v>45.820454931853</v>
+        <v>475.8705861429753</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -21147,16 +21147,16 @@
         <v>739</v>
       </c>
       <c r="Y112" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="Z112" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AA112">
-        <v>0.99395341117186964</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB112">
-        <v>110.85412851572337</v>
+        <v>226.88936094280919</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21221,16 +21221,16 @@
         <v>741</v>
       </c>
       <c r="Y113" t="s">
-        <v>441</v>
+        <v>505</v>
       </c>
       <c r="Z113" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AA113">
-        <v>0.98322732678073066</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB113">
-        <v>307.49900901993823</v>
+        <v>224.55764046872929</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21295,16 +21295,16 @@
         <v>743</v>
       </c>
       <c r="Y114" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="Z114" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AA114">
-        <v>0.9974199781412052</v>
+        <v>0.99647006537565563</v>
       </c>
       <c r="AB114">
-        <v>47.300400744571718</v>
+        <v>64.715468112981057</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21369,16 +21369,16 @@
         <v>745</v>
       </c>
       <c r="Y115" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="Z115" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AA115">
-        <v>0.99336837071349593</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB115">
-        <v>121.57987025257442</v>
+        <v>645.26520366712316</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21443,16 +21443,16 @@
         <v>747</v>
       </c>
       <c r="Y116" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="Z116" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AA116">
-        <v>0.99379477670057537</v>
+        <v>0.99267004448650609</v>
       </c>
       <c r="AB116">
-        <v>113.7624271561186</v>
+        <v>134.38251774738842</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21517,16 +21517,16 @@
         <v>749</v>
       </c>
       <c r="Y117" t="s">
-        <v>454</v>
+        <v>519</v>
       </c>
       <c r="Z117" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AA117">
-        <v>0.9961866142254362</v>
+        <v>0.9948848527457459</v>
       </c>
       <c r="AB117">
-        <v>69.91207253366963</v>
+        <v>93.777699661325343</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21591,16 +21591,16 @@
         <v>751</v>
       </c>
       <c r="Y118" t="s">
-        <v>482</v>
+        <v>524</v>
       </c>
       <c r="Z118" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AA118">
-        <v>0.98150124893892388</v>
+        <v>0.9922030648239526</v>
       </c>
       <c r="AB118">
-        <v>339.14376945306287</v>
+        <v>142.94381156086857</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21665,16 +21665,16 @@
         <v>753</v>
       </c>
       <c r="Y119" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="Z119" t="s">
-        <v>869</v>
+        <v>769</v>
       </c>
       <c r="AA119">
-        <v>0.99523081353776888</v>
+        <v>0.9621480095608167</v>
       </c>
       <c r="AB119">
-        <v>87.435085140903482</v>
+        <v>693.95315805169378</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21739,16 +21739,16 @@
         <v>755</v>
       </c>
       <c r="Y120" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="Z120" t="s">
         <v>870</v>
       </c>
       <c r="AA120">
-        <v>0.9916432660493133</v>
+        <v>0.98916941127667946</v>
       </c>
       <c r="AB120">
-        <v>153.20678909592235</v>
+        <v>198.56079326087576</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21813,16 +21813,16 @@
         <v>757</v>
       </c>
       <c r="Y121" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="Z121" t="s">
         <v>871</v>
       </c>
       <c r="AA121">
-        <v>0.99570118415007625</v>
+        <v>0.97159134368321343</v>
       </c>
       <c r="AB121">
-        <v>78.81162391526847</v>
+        <v>520.82536580775354</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21887,16 +21887,16 @@
         <v>759</v>
       </c>
       <c r="Y122" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="Z122" t="s">
         <v>872</v>
       </c>
       <c r="AA122">
-        <v>0.99691903985105013</v>
+        <v>0.99359614530212825</v>
       </c>
       <c r="AB122">
-        <v>56.484269397415083</v>
+        <v>117.40400279431638</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21961,16 +21961,16 @@
         <v>761</v>
       </c>
       <c r="Y123" t="s">
-        <v>444</v>
+        <v>518</v>
       </c>
       <c r="Z123" t="s">
         <v>873</v>
       </c>
       <c r="AA123">
-        <v>0.98563153879963317</v>
+        <v>0.99488082982009873</v>
       </c>
       <c r="AB123">
-        <v>263.42178867339101</v>
+        <v>93.851453298190577</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -22035,16 +22035,16 @@
         <v>763</v>
       </c>
       <c r="Y124" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="Z124" t="s">
         <v>874</v>
       </c>
       <c r="AA124">
-        <v>0.99529226044395613</v>
+        <v>0.99557743229498485</v>
       </c>
       <c r="AB124">
-        <v>86.308558527470979</v>
+        <v>81.080407925277868</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -22109,16 +22109,16 @@
         <v>765</v>
       </c>
       <c r="Y125" t="s">
-        <v>511</v>
+        <v>455</v>
       </c>
       <c r="Z125" t="s">
         <v>875</v>
       </c>
       <c r="AA125">
-        <v>0.99443562760718263</v>
+        <v>0.99401156108202648</v>
       </c>
       <c r="AB125">
-        <v>102.01349386831856</v>
+        <v>109.78804682951412</v>
       </c>
     </row>
   </sheetData>
@@ -22127,7 +22127,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCABACA-A93F-4787-97ED-B948EA785FDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB656114-575F-45C7-9C06-8B4176CC0979}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22239,7 +22239,7 @@
         <v>1269</v>
       </c>
       <c r="K11" t="s">
-        <v>1084</v>
+        <v>1038</v>
       </c>
       <c r="L11">
         <v>4.7713910333636482</v>
@@ -22272,7 +22272,7 @@
         <v>1407</v>
       </c>
       <c r="X11" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -22307,7 +22307,7 @@
         <v>1271</v>
       </c>
       <c r="K12" t="s">
-        <v>1100</v>
+        <v>1024</v>
       </c>
       <c r="L12">
         <v>12.404103898825962</v>
@@ -22340,7 +22340,7 @@
         <v>1409</v>
       </c>
       <c r="X12" t="s">
-        <v>1238</v>
+        <v>1210</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -22375,7 +22375,7 @@
         <v>1273</v>
       </c>
       <c r="K13" t="s">
-        <v>1041</v>
+        <v>1133</v>
       </c>
       <c r="L13">
         <v>6.1276234637439133</v>
@@ -22408,7 +22408,7 @@
         <v>1411</v>
       </c>
       <c r="X13" t="s">
-        <v>1230</v>
+        <v>1254</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -22443,7 +22443,7 @@
         <v>1275</v>
       </c>
       <c r="K14" t="s">
-        <v>1126</v>
+        <v>1067</v>
       </c>
       <c r="L14">
         <v>0.85621181691755843</v>
@@ -22476,7 +22476,7 @@
         <v>1413</v>
       </c>
       <c r="X14" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -22511,7 +22511,7 @@
         <v>1277</v>
       </c>
       <c r="K15" t="s">
-        <v>1094</v>
+        <v>1120</v>
       </c>
       <c r="L15">
         <v>2.2628760328229185</v>
@@ -22544,7 +22544,7 @@
         <v>1415</v>
       </c>
       <c r="X15" t="s">
-        <v>1246</v>
+        <v>1264</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -22579,7 +22579,7 @@
         <v>1279</v>
       </c>
       <c r="K16" t="s">
-        <v>1114</v>
+        <v>1061</v>
       </c>
       <c r="L16">
         <v>0.43370118574988076</v>
@@ -22612,7 +22612,7 @@
         <v>1417</v>
       </c>
       <c r="X16" t="s">
-        <v>1263</v>
+        <v>1241</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -22647,7 +22647,7 @@
         <v>1281</v>
       </c>
       <c r="K17" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="L17">
         <v>2.5150267058852811</v>
@@ -22680,7 +22680,7 @@
         <v>1419</v>
       </c>
       <c r="X17" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -22715,7 +22715,7 @@
         <v>1283</v>
       </c>
       <c r="K18" t="s">
-        <v>1093</v>
+        <v>1119</v>
       </c>
       <c r="L18">
         <v>2.885493974180005</v>
@@ -22748,7 +22748,7 @@
         <v>1421</v>
       </c>
       <c r="X18" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -22783,7 +22783,7 @@
         <v>1285</v>
       </c>
       <c r="K19" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="L19">
         <v>10.563746678268352</v>
@@ -22816,7 +22816,7 @@
         <v>1423</v>
       </c>
       <c r="X19" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22851,7 +22851,7 @@
         <v>1287</v>
       </c>
       <c r="K20" t="s">
-        <v>1086</v>
+        <v>1040</v>
       </c>
       <c r="L20">
         <v>7.4816578037471135</v>
@@ -22884,7 +22884,7 @@
         <v>1425</v>
       </c>
       <c r="X20" t="s">
-        <v>1260</v>
+        <v>1222</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22919,7 +22919,7 @@
         <v>1289</v>
       </c>
       <c r="K21" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="L21">
         <v>11.884376191048085</v>
@@ -22952,7 +22952,7 @@
         <v>1427</v>
       </c>
       <c r="X21" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22987,7 +22987,7 @@
         <v>1291</v>
       </c>
       <c r="K22" t="s">
-        <v>1014</v>
+        <v>1077</v>
       </c>
       <c r="L22">
         <v>12.246676572623375</v>
@@ -23020,7 +23020,7 @@
         <v>1429</v>
       </c>
       <c r="X22" t="s">
-        <v>1261</v>
+        <v>1239</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -23055,7 +23055,7 @@
         <v>1293</v>
       </c>
       <c r="K23" t="s">
-        <v>1112</v>
+        <v>1059</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -23088,7 +23088,7 @@
         <v>1431</v>
       </c>
       <c r="X23" t="s">
-        <v>1236</v>
+        <v>1267</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -23123,7 +23123,7 @@
         <v>1295</v>
       </c>
       <c r="K24" t="s">
-        <v>1042</v>
+        <v>1134</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -23156,7 +23156,7 @@
         <v>1433</v>
       </c>
       <c r="X24" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -23191,7 +23191,7 @@
         <v>1297</v>
       </c>
       <c r="K25" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="L25">
         <v>11.221871479411517</v>
@@ -23224,7 +23224,7 @@
         <v>1435</v>
       </c>
       <c r="X25" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -23259,7 +23259,7 @@
         <v>1299</v>
       </c>
       <c r="K26" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="L26">
         <v>1.6691823226567941</v>
@@ -23292,7 +23292,7 @@
         <v>1437</v>
       </c>
       <c r="X26" t="s">
-        <v>1258</v>
+        <v>1220</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23327,7 +23327,7 @@
         <v>1301</v>
       </c>
       <c r="K27" t="s">
-        <v>1056</v>
+        <v>1101</v>
       </c>
       <c r="L27">
         <v>3.7614311754340659</v>
@@ -23360,7 +23360,7 @@
         <v>1439</v>
       </c>
       <c r="X27" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -23395,7 +23395,7 @@
         <v>1303</v>
       </c>
       <c r="K28" t="s">
-        <v>1104</v>
+        <v>1028</v>
       </c>
       <c r="L28">
         <v>0.34625959029864795</v>
@@ -23428,7 +23428,7 @@
         <v>1441</v>
       </c>
       <c r="X28" t="s">
-        <v>1219</v>
+        <v>1237</v>
       </c>
       <c r="Y28">
         <v>2.6655000000000002</v>
@@ -23463,7 +23463,7 @@
         <v>1305</v>
       </c>
       <c r="K29" t="s">
-        <v>1068</v>
+        <v>1032</v>
       </c>
       <c r="L29">
         <v>0.65440271382024695</v>
@@ -23496,7 +23496,7 @@
         <v>1443</v>
       </c>
       <c r="X29" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="Y29">
         <v>8.8432499999999994</v>
@@ -23531,7 +23531,7 @@
         <v>1307</v>
       </c>
       <c r="K30" t="s">
-        <v>1116</v>
+        <v>1063</v>
       </c>
       <c r="L30">
         <v>2.2677057834637031</v>
@@ -23564,7 +23564,7 @@
         <v>1445</v>
       </c>
       <c r="X30" t="s">
-        <v>1256</v>
+        <v>1235</v>
       </c>
       <c r="Y30">
         <v>3.4402499999999998</v>
@@ -23599,7 +23599,7 @@
         <v>1309</v>
       </c>
       <c r="K31" t="s">
-        <v>1044</v>
+        <v>1136</v>
       </c>
       <c r="L31">
         <v>2.4836923620575391</v>
@@ -23632,7 +23632,7 @@
         <v>1447</v>
       </c>
       <c r="X31" t="s">
-        <v>1248</v>
+        <v>1265</v>
       </c>
       <c r="Y31">
         <v>13.389749999999999</v>
@@ -23667,7 +23667,7 @@
         <v>1311</v>
       </c>
       <c r="K32" t="s">
-        <v>1022</v>
+        <v>1051</v>
       </c>
       <c r="L32">
         <v>4.0763322608214585</v>
@@ -23700,7 +23700,7 @@
         <v>1449</v>
       </c>
       <c r="X32" t="s">
-        <v>1218</v>
+        <v>1245</v>
       </c>
       <c r="Y32">
         <v>6.9757499999999997</v>
@@ -23735,7 +23735,7 @@
         <v>1313</v>
       </c>
       <c r="K33" t="s">
-        <v>1058</v>
+        <v>1103</v>
       </c>
       <c r="L33">
         <v>2.5731779960501728</v>
@@ -23768,7 +23768,7 @@
         <v>1451</v>
       </c>
       <c r="X33" t="s">
-        <v>1254</v>
+        <v>1233</v>
       </c>
       <c r="Y33">
         <v>38.154000000000003</v>
@@ -23803,7 +23803,7 @@
         <v>1315</v>
       </c>
       <c r="K34" t="s">
-        <v>1142</v>
+        <v>1085</v>
       </c>
       <c r="L34">
         <v>4.0509443596880574</v>
@@ -23836,7 +23836,7 @@
         <v>1453</v>
       </c>
       <c r="X34" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="Y34">
         <v>26.765999999999998</v>
@@ -23871,7 +23871,7 @@
         <v>1317</v>
       </c>
       <c r="K35" t="s">
-        <v>1074</v>
+        <v>1091</v>
       </c>
       <c r="L35">
         <v>2.4544193550494788</v>
@@ -23904,7 +23904,7 @@
         <v>1455</v>
       </c>
       <c r="X35" t="s">
-        <v>1216</v>
+        <v>1243</v>
       </c>
       <c r="Y35">
         <v>35.325000000000003</v>
@@ -23939,7 +23939,7 @@
         <v>1319</v>
       </c>
       <c r="K36" t="s">
-        <v>1138</v>
+        <v>1115</v>
       </c>
       <c r="L36">
         <v>0.35051099632091098</v>
@@ -23972,7 +23972,7 @@
         <v>1457</v>
       </c>
       <c r="X36" t="s">
-        <v>1232</v>
+        <v>1256</v>
       </c>
       <c r="Y36">
         <v>38.589750000000002</v>
@@ -24007,7 +24007,7 @@
         <v>1321</v>
       </c>
       <c r="K37" t="s">
-        <v>1091</v>
+        <v>1045</v>
       </c>
       <c r="L37">
         <v>5.5005105319204732</v>
@@ -24040,7 +24040,7 @@
         <v>1459</v>
       </c>
       <c r="X37" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="Y37">
         <v>28.707000000000001</v>
@@ -24075,7 +24075,7 @@
         <v>1323</v>
       </c>
       <c r="K38" t="s">
-        <v>1128</v>
+        <v>1069</v>
       </c>
       <c r="L38">
         <v>1.6757541426674882</v>
@@ -24108,7 +24108,7 @@
         <v>1461</v>
       </c>
       <c r="X38" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="Y38">
         <v>13.428000000000001</v>
@@ -24143,7 +24143,7 @@
         <v>1325</v>
       </c>
       <c r="K39" t="s">
-        <v>1078</v>
+        <v>1095</v>
       </c>
       <c r="L39">
         <v>0.39959553615654331</v>
@@ -24176,7 +24176,7 @@
         <v>1463</v>
       </c>
       <c r="X39" t="s">
-        <v>1240</v>
+        <v>1212</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24211,7 +24211,7 @@
         <v>1327</v>
       </c>
       <c r="K40" t="s">
-        <v>1016</v>
+        <v>1079</v>
       </c>
       <c r="L40">
         <v>1.7832075556426605</v>
@@ -24244,7 +24244,7 @@
         <v>1465</v>
       </c>
       <c r="X40" t="s">
-        <v>1234</v>
+        <v>1258</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24279,7 +24279,7 @@
         <v>1329</v>
       </c>
       <c r="K41" t="s">
-        <v>1140</v>
+        <v>1117</v>
       </c>
       <c r="L41">
         <v>23.427729543154012</v>
@@ -24312,7 +24312,7 @@
         <v>1467</v>
       </c>
       <c r="X41" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24347,7 +24347,7 @@
         <v>1331</v>
       </c>
       <c r="K42" t="s">
-        <v>1054</v>
+        <v>1146</v>
       </c>
       <c r="L42">
         <v>1.4999429400795936</v>
@@ -24382,7 +24382,7 @@
         <v>1333</v>
       </c>
       <c r="K43" t="s">
-        <v>1146</v>
+        <v>1089</v>
       </c>
       <c r="L43">
         <v>55.863958629218203</v>
@@ -24417,7 +24417,7 @@
         <v>1335</v>
       </c>
       <c r="K44" t="s">
-        <v>1050</v>
+        <v>1142</v>
       </c>
       <c r="L44">
         <v>17.068804920122925</v>
@@ -24452,7 +24452,7 @@
         <v>1337</v>
       </c>
       <c r="K45" t="s">
-        <v>1064</v>
+        <v>1109</v>
       </c>
       <c r="L45">
         <v>13.001084297219549</v>
@@ -24487,7 +24487,7 @@
         <v>1339</v>
       </c>
       <c r="K46" t="s">
-        <v>1082</v>
+        <v>1099</v>
       </c>
       <c r="L46">
         <v>3.0756142181007986</v>
@@ -24522,7 +24522,7 @@
         <v>1341</v>
       </c>
       <c r="K47" t="s">
-        <v>1110</v>
+        <v>1049</v>
       </c>
       <c r="L47">
         <v>17.749707845203876</v>
@@ -24557,7 +24557,7 @@
         <v>1343</v>
       </c>
       <c r="K48" t="s">
-        <v>1102</v>
+        <v>1026</v>
       </c>
       <c r="L48">
         <v>2.3372365278937242</v>
@@ -24592,7 +24592,7 @@
         <v>1345</v>
       </c>
       <c r="K49" t="s">
-        <v>1026</v>
+        <v>1055</v>
       </c>
       <c r="L49">
         <v>4.2648673086521249</v>
@@ -24627,7 +24627,7 @@
         <v>1347</v>
       </c>
       <c r="K50" t="s">
-        <v>1062</v>
+        <v>1107</v>
       </c>
       <c r="L50">
         <v>2.8571480649629004</v>
@@ -24662,7 +24662,7 @@
         <v>1349</v>
       </c>
       <c r="K51" t="s">
-        <v>1066</v>
+        <v>1111</v>
       </c>
       <c r="L51">
         <v>9.5169217846211289</v>
@@ -24697,7 +24697,7 @@
         <v>1351</v>
       </c>
       <c r="K52" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="L52">
         <v>33.414563514376454</v>
@@ -24732,7 +24732,7 @@
         <v>1353</v>
       </c>
       <c r="K53" t="s">
-        <v>1134</v>
+        <v>1075</v>
       </c>
       <c r="L53">
         <v>18.904558868579112</v>
@@ -24767,7 +24767,7 @@
         <v>1355</v>
       </c>
       <c r="K54" t="s">
-        <v>1052</v>
+        <v>1144</v>
       </c>
       <c r="L54">
         <v>15.478330347836801</v>
@@ -24802,7 +24802,7 @@
         <v>1357</v>
       </c>
       <c r="K55" t="s">
-        <v>1040</v>
+        <v>1132</v>
       </c>
       <c r="L55">
         <v>14.176079891703212</v>
@@ -24837,7 +24837,7 @@
         <v>1359</v>
       </c>
       <c r="K56" t="s">
-        <v>1072</v>
+        <v>1036</v>
       </c>
       <c r="L56">
         <v>0.80973624203950822</v>
@@ -24872,7 +24872,7 @@
         <v>1361</v>
       </c>
       <c r="K57" t="s">
-        <v>1020</v>
+        <v>1083</v>
       </c>
       <c r="L57">
         <v>3.2067222321080848</v>
@@ -24907,7 +24907,7 @@
         <v>1363</v>
       </c>
       <c r="K58" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
       <c r="L58">
         <v>0.66271354737797783</v>
@@ -24942,7 +24942,7 @@
         <v>1365</v>
       </c>
       <c r="K59" t="s">
-        <v>1132</v>
+        <v>1073</v>
       </c>
       <c r="L59">
         <v>1.8183767824138508</v>
@@ -24977,7 +24977,7 @@
         <v>1367</v>
       </c>
       <c r="K60" t="s">
-        <v>1096</v>
+        <v>1122</v>
       </c>
       <c r="L60">
         <v>0.24904319237866104</v>
@@ -25012,7 +25012,7 @@
         <v>1369</v>
       </c>
       <c r="K61" t="s">
-        <v>1028</v>
+        <v>1057</v>
       </c>
       <c r="L61">
         <v>8.2047875916663029E-2</v>
@@ -25047,7 +25047,7 @@
         <v>1371</v>
       </c>
       <c r="K62" t="s">
-        <v>1060</v>
+        <v>1105</v>
       </c>
       <c r="L62">
         <v>11.861012832193515</v>
@@ -25082,7 +25082,7 @@
         <v>1373</v>
       </c>
       <c r="K63" t="s">
-        <v>1130</v>
+        <v>1071</v>
       </c>
       <c r="L63">
         <v>0.74143826937354373</v>
@@ -25117,7 +25117,7 @@
         <v>1375</v>
       </c>
       <c r="K64" t="s">
-        <v>1046</v>
+        <v>1138</v>
       </c>
       <c r="L64">
         <v>5.5201095579611916</v>
@@ -25152,7 +25152,7 @@
         <v>1377</v>
       </c>
       <c r="K65" t="s">
-        <v>1118</v>
+        <v>1065</v>
       </c>
       <c r="L65">
         <v>6.8285247240880329</v>
@@ -25187,7 +25187,7 @@
         <v>1379</v>
       </c>
       <c r="K66" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="L66">
         <v>14.065249575687433</v>
@@ -25222,7 +25222,7 @@
         <v>1381</v>
       </c>
       <c r="K67" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="L67">
         <v>9.3799037679336319</v>
@@ -25257,7 +25257,7 @@
         <v>1383</v>
       </c>
       <c r="K68" t="s">
-        <v>1070</v>
+        <v>1034</v>
       </c>
       <c r="L68">
         <v>42.785830383290261</v>
@@ -25292,7 +25292,7 @@
         <v>1385</v>
       </c>
       <c r="K69" t="s">
-        <v>1080</v>
+        <v>1097</v>
       </c>
       <c r="L69">
         <v>7.8693705940085819</v>
@@ -25327,7 +25327,7 @@
         <v>1387</v>
       </c>
       <c r="K70" t="s">
-        <v>1136</v>
+        <v>1113</v>
       </c>
       <c r="L70">
         <v>19.787589902082505</v>
@@ -25362,7 +25362,7 @@
         <v>1389</v>
       </c>
       <c r="K71" t="s">
-        <v>1108</v>
+        <v>1047</v>
       </c>
       <c r="L71">
         <v>18.319832830101969</v>
@@ -25397,7 +25397,7 @@
         <v>1391</v>
       </c>
       <c r="K72" t="s">
-        <v>1048</v>
+        <v>1140</v>
       </c>
       <c r="L72">
         <v>6.7551756478058005</v>
@@ -25432,7 +25432,7 @@
         <v>1393</v>
       </c>
       <c r="K73" t="s">
-        <v>1024</v>
+        <v>1053</v>
       </c>
       <c r="L73">
         <v>3.5275797249830152</v>
@@ -25467,7 +25467,7 @@
         <v>1395</v>
       </c>
       <c r="K74" t="s">
-        <v>1144</v>
+        <v>1087</v>
       </c>
       <c r="L74">
         <v>0.89663971235601181</v>
@@ -25502,7 +25502,7 @@
         <v>1397</v>
       </c>
       <c r="K75" t="s">
-        <v>1018</v>
+        <v>1081</v>
       </c>
       <c r="L75">
         <v>5.9305458091691294</v>
@@ -25537,7 +25537,7 @@
         <v>1399</v>
       </c>
       <c r="K76" t="s">
-        <v>1089</v>
+        <v>1043</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25572,7 +25572,7 @@
         <v>1401</v>
       </c>
       <c r="K77" t="s">
-        <v>1076</v>
+        <v>1093</v>
       </c>
       <c r="L77">
         <v>0.5190595734350465</v>
@@ -25607,7 +25607,7 @@
         <v>1403</v>
       </c>
       <c r="K78" t="s">
-        <v>1106</v>
+        <v>1030</v>
       </c>
       <c r="L78">
         <v>0.29505146981926272</v>
@@ -25642,7 +25642,7 @@
         <v>1405</v>
       </c>
       <c r="K79" t="s">
-        <v>1087</v>
+        <v>1041</v>
       </c>
       <c r="L79">
         <v>0.28737649325389003</v>
@@ -25657,7 +25657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2EE1D31-28D2-4445-AE62-0FFCF9E92A3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E0E4DDC-B9B2-4331-A327-9B7D3C7B8787}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27126,7 +27126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F523B850-7BD9-4DE9-AE7B-7AA3E32BAED3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89A7E2B-750A-4247-9EFB-C1A78FB8C274}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6EA96B6-6B23-4071-A093-BF0E3548A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45DAC686-5BF3-474F-B951-A62D466480D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1736,18 +1736,450 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_025</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_047</t>
   </si>
   <si>
@@ -1790,298 +2222,64 @@
     <t>connecting solar to buses in cluster 87</t>
   </si>
   <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
   </si>
   <si>
     <t>distr_solelc_spv_028</t>
@@ -2114,6 +2312,84 @@
     <t>connecting solar to buses in cluster 85</t>
   </si>
   <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_103</t>
   </si>
   <si>
@@ -2156,288 +2432,213 @@
     <t>connecting solar to buses in cluster 83</t>
   </si>
   <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_BR283-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR367-500,e_BR381-500,e_BR435-500</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_BR21-500,e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR744-440,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440,e_BR685-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR246-500,e_BR254-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR337-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w626452961-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR558-500,e_BR535-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR141-500,e_BR125-500,e_BR61-500,e_BR122-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR446-500,e_BR487-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR487-500,e_BR515-500,e_w306104018-500,e_r6844204-500,e_BR490-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR475-500,e_BR433-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_BR290-500,e_BR347-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500,e_BR310-500</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR528-500,e_BR483-500,e_BR571-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR221-500,e_BR209-500,e_BR321-500,e_BR282-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_BR305-230,e_w284868411-230,e_BR303-230,e_BR284-500,e_BR285-500,e_w201470687-230,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_w603494578-500,e_BR292-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_BR387-500,e_BR354-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR343-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR283-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR777-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w150728360-500,e_BR833-500</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_BR171-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>e_BR248-500,e_BR221-500,e_BR122-500,e_BR72-500,e_BR105-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500</t>
+  </si>
+  <si>
+    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
+  </si>
+  <si>
+    <t>e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR669-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR437-500,e_BR483-500,e_BR478-500,e_BR464-500,e_w954122148-500,e_w596594961-500</t>
+  </si>
+  <si>
     <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
   </si>
   <si>
@@ -2462,154 +2663,34 @@
     <t>e_BR528-500,e_w954122148-500,e_BR499-500,e_BR535-500,e_BR579-500</t>
   </si>
   <si>
-    <t>e_BR283-500,e_BR290-500,e_BR347-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500,e_BR310-500</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR528-500,e_BR483-500,e_BR571-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR221-500,e_BR209-500,e_BR321-500,e_BR282-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR141-500,e_BR125-500,e_BR61-500,e_BR122-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_BR305-230,e_w284868411-230,e_BR303-230,e_BR284-500,e_BR285-500,e_w201470687-230,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_w603494578-500,e_BR292-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_BR21-500,e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR744-440,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440,e_BR685-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR246-500,e_BR254-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR337-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR283-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR777-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w150728360-500,e_BR833-500</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_BR171-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>e_BR248-500,e_BR221-500,e_BR122-500,e_BR72-500,e_BR105-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_BR283-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR367-500,e_BR381-500,e_BR435-500</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR347-500,e_BR446-500,e_BR353-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR446-500,e_BR487-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR487-500,e_BR515-500,e_w306104018-500,e_r6844204-500,e_BR490-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR475-500,e_BR433-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w284868411-230,e_BR327-230,e_BR315-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR411-230,e_BR283-500,e_BR290-500,e_BR371-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500</t>
+  </si>
+  <si>
+    <t>e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
   </si>
   <si>
     <t>e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR525-500,e_BR500-500,e_BR550-500,e_BR473-500</t>
@@ -2621,6 +2702,39 @@
     <t>e_BR355-500,e_BR321-500,e_BR412-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
   </si>
   <si>
+    <t>e_w168904844-230,e_w168664395-500,e_BR657-440,e_BR626-440</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR435-500,e_BR367-500,e_w306104018-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR52-500,e_BR171-500,e_BR143-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_w521542011-500,e_BR903-500,e_BR866-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_w215284729-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_w302931307-440,e_BR544-500,e_BR541-500,e_BR515-500,e_BR632-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_r6844204-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR428-500,e_BR382-500,e_BR387-500,e_BR354-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500,e_BR355-500</t>
+  </si>
+  <si>
     <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
   </si>
   <si>
@@ -2642,118 +2756,106 @@
     <t>e_BR209-500,e_BR208-500,e_BR190-500,e_BR103-500,e_BR282-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR204-500,e_BR164-500,e_BR142-500,e_BR292-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
   </si>
   <si>
-    <t>e_BR342-230,e_BR327-230,e_BR315-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w626452961-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR558-500,e_BR535-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500</t>
-  </si>
-  <si>
-    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
-  </si>
-  <si>
-    <t>e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500,e_w521542011-500,e_BR858-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_BR387-500,e_BR354-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR343-500</t>
-  </si>
-  <si>
-    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR669-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR437-500,e_BR483-500,e_BR478-500,e_BR464-500,e_w954122148-500,e_w596594961-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w284868411-230,e_BR327-230,e_BR315-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR411-230,e_BR283-500,e_BR290-500,e_BR371-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500</t>
-  </si>
-  <si>
-    <t>e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR63-500,e_BR208-500,e_BR80-500,e_BR78-500,e_BR103-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500,e_BR657-440,e_BR626-440</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR435-500,e_BR367-500,e_w306104018-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR52-500,e_BR171-500,e_BR143-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_w521542011-500,e_BR903-500,e_BR866-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_w215284729-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_w302931307-440,e_BR544-500,e_BR541-500,e_BR515-500,e_BR632-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_r6844204-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR428-500,e_BR382-500,e_BR387-500,e_BR354-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR337-500,e_BR459-500,e_BR412-500,e_BR304-500,e_BR355-500</t>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wonelc_won_022</t>
@@ -2780,10 +2882,88 @@
     <t>connecting wind onshore to buses in cluster 32</t>
   </si>
   <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
   </si>
   <si>
     <t>distr_wonelc_won_016</t>
@@ -2810,28 +2990,100 @@
     <t>connecting wind onshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
   </si>
   <si>
     <t>distr_wonelc_won_013</t>
@@ -2858,6 +3110,36 @@
     <t>connecting wind onshore to buses in cluster 53</t>
   </si>
   <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_019</t>
   </si>
   <si>
@@ -2888,286 +3170,103 @@
     <t>connecting wind onshore to buses in cluster 62</t>
   </si>
   <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_BR732-500,e_BR673-440,e_BR676-440,e_w202622375-765,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR663-440,e_BR661-440</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR302-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w306104018-500</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_w596594961-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
   </si>
   <si>
     <t>elc_won_022</t>
@@ -3194,10 +3293,85 @@
     <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
   </si>
   <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR344-500,e_BR340-500,e_BR302-500,e_w603494578-500,e_BR292-500,e_w532354815-500,e_BR204-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w168664395-500,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w202622375-765,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
   </si>
   <si>
     <t>elc_won_016</t>
@@ -3224,28 +3398,100 @@
     <t>e_BR412-500,e_BR400-500,e_BR360-500</t>
   </si>
   <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w168664395-500,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w202622375-765,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR609-440,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
   </si>
   <si>
     <t>elc_won_013</t>
@@ -3272,6 +3518,36 @@
     <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
   </si>
   <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_BR833-500,e_w150728360-500,e_BR838-500,e_BR837-525,e_BR832-500,e_w125761912-500,e_w125761912-765,e_BR788-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
+  </si>
+  <si>
     <t>elc_won_019</t>
   </si>
   <si>
@@ -3299,304 +3575,172 @@
     <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
   </si>
   <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR609-440,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_BR732-500,e_BR673-440,e_BR676-440,e_w202622375-765,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR663-440,e_BR661-440</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR302-500</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR344-500,e_BR340-500,e_BR302-500,e_w603494578-500,e_BR292-500,e_w532354815-500,e_BR204-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_w596594961-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w306104018-500</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_BR833-500,e_w150728360-500,e_BR838-500,e_BR837-525,e_BR832-500,e_w125761912-500,e_w125761912-765,e_BR788-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500</t>
-  </si>
-  <si>
-    <t>elc_won_069</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_025</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
     <t>distr_wofelc_wof_005</t>
@@ -3617,169 +3761,160 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
     <t>elc_wof_025</t>
   </si>
   <si>
     <t>e_BR37-500,e_BR42-500</t>
   </si>
   <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w466973262-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_BR764-440,e_BR758-440,e_BR755-500</t>
+  </si>
+  <si>
     <t>elc_wof_013</t>
   </si>
   <si>
     <t>e_BR764-440</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
   </si>
   <si>
     <t>elc_wof_005</t>
@@ -3798,141 +3933,6 @@
   </si>
   <si>
     <t>e_BR652-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_BR764-440,e_BR758-440,e_BR755-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_BR1014-525,e_w466973262-525,e_BR1013-525</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9832,7 +9832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84A731A-3B4B-433B-960A-44AA28B9EDD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50C5381B-907C-4CB2-9622-34537447EE72}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10070,16 +10070,16 @@
         <v>535</v>
       </c>
       <c r="Y11" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="Z11" t="s">
         <v>769</v>
       </c>
       <c r="AA11">
-        <v>0.96988338866662871</v>
+        <v>0.9565626086601956</v>
       </c>
       <c r="AB11">
-        <v>552.13787444514003</v>
+        <v>796.35217456308078</v>
       </c>
       <c r="AD11" t="s">
         <v>534</v>
@@ -10112,10 +10112,10 @@
         <v>1014</v>
       </c>
       <c r="AO11">
-        <v>0.97416725971121887</v>
+        <v>0.99453968761366496</v>
       </c>
       <c r="AP11">
-        <v>473.60023862765331</v>
+        <v>100.10572708280816</v>
       </c>
       <c r="AR11" t="s">
         <v>534</v>
@@ -10216,16 +10216,16 @@
         <v>539</v>
       </c>
       <c r="Y12" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="Z12" t="s">
         <v>770</v>
       </c>
       <c r="AA12">
-        <v>0.98061830542009054</v>
+        <v>0.98644915759239105</v>
       </c>
       <c r="AB12">
-        <v>355.3310672983406</v>
+        <v>248.43211080616339</v>
       </c>
       <c r="AD12" t="s">
         <v>534</v>
@@ -10258,10 +10258,10 @@
         <v>1016</v>
       </c>
       <c r="AO12">
-        <v>0.99693672852577231</v>
+        <v>0.99675446210163643</v>
       </c>
       <c r="AP12">
-        <v>56.159977027506663</v>
+        <v>59.501528136664533</v>
       </c>
       <c r="AR12" t="s">
         <v>534</v>
@@ -10294,10 +10294,10 @@
         <v>1213</v>
       </c>
       <c r="BC12">
-        <v>0.99027261546287559</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD12">
-        <v>178.33538318061403</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10362,16 +10362,16 @@
         <v>541</v>
       </c>
       <c r="Y13" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="Z13" t="s">
         <v>771</v>
       </c>
       <c r="AA13">
-        <v>0.99621118265687969</v>
+        <v>0.9946911823559148</v>
       </c>
       <c r="AB13">
-        <v>69.461651290538995</v>
+        <v>97.32832347489618</v>
       </c>
       <c r="AD13" t="s">
         <v>534</v>
@@ -10404,10 +10404,10 @@
         <v>1018</v>
       </c>
       <c r="AO13">
-        <v>0.99706157261604222</v>
+        <v>0.99589340828485295</v>
       </c>
       <c r="AP13">
-        <v>53.871168705893545</v>
+        <v>75.287514777696231</v>
       </c>
       <c r="AR13" t="s">
         <v>534</v>
@@ -10437,13 +10437,13 @@
         <v>1214</v>
       </c>
       <c r="BB13" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="BC13">
-        <v>0.99203097418485064</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD13">
-        <v>146.09880661107059</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10508,16 +10508,16 @@
         <v>543</v>
       </c>
       <c r="Y14" t="s">
-        <v>429</v>
+        <v>512</v>
       </c>
       <c r="Z14" t="s">
         <v>772</v>
       </c>
       <c r="AA14">
-        <v>0.99720399169001062</v>
+        <v>0.99040896044606685</v>
       </c>
       <c r="AB14">
-        <v>51.260152349805715</v>
+        <v>175.83572515544165</v>
       </c>
       <c r="AD14" t="s">
         <v>534</v>
@@ -10550,10 +10550,10 @@
         <v>1020</v>
       </c>
       <c r="AO14">
-        <v>0.99760255773158468</v>
+        <v>0.98030817163892847</v>
       </c>
       <c r="AP14">
-        <v>43.953108254279897</v>
+        <v>361.01685328631117</v>
       </c>
       <c r="AR14" t="s">
         <v>534</v>
@@ -10580,16 +10580,16 @@
         <v>1154</v>
       </c>
       <c r="BA14" t="s">
+        <v>1215</v>
+      </c>
+      <c r="BB14" t="s">
         <v>1216</v>
       </c>
-      <c r="BB14" t="s">
-        <v>1215</v>
-      </c>
       <c r="BC14">
-        <v>0.98806872821788805</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD14">
-        <v>218.73998267205184</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10654,16 +10654,16 @@
         <v>545</v>
       </c>
       <c r="Y15" t="s">
-        <v>497</v>
+        <v>435</v>
       </c>
       <c r="Z15" t="s">
         <v>773</v>
       </c>
       <c r="AA15">
-        <v>0.99546059111776786</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB15">
-        <v>83.222496174256221</v>
+        <v>98.356996715718111</v>
       </c>
       <c r="AD15" t="s">
         <v>534</v>
@@ -10696,10 +10696,10 @@
         <v>1022</v>
       </c>
       <c r="AO15">
-        <v>0.9854553870197319</v>
+        <v>0.99429886321911398</v>
       </c>
       <c r="AP15">
-        <v>266.65123797158259</v>
+        <v>104.52084098291034</v>
       </c>
       <c r="AR15" t="s">
         <v>534</v>
@@ -10732,10 +10732,10 @@
         <v>1218</v>
       </c>
       <c r="BC15">
-        <v>0.99043684613816729</v>
+        <v>0.98990297941208016</v>
       </c>
       <c r="BD15">
-        <v>175.324487466932</v>
+        <v>185.11204411186426</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10800,16 +10800,16 @@
         <v>547</v>
       </c>
       <c r="Y16" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="Z16" t="s">
         <v>774</v>
       </c>
       <c r="AA16">
-        <v>0.99324569511004301</v>
+        <v>0.99431447054153432</v>
       </c>
       <c r="AB16">
-        <v>123.82892298254488</v>
+        <v>104.23470673853728</v>
       </c>
       <c r="AD16" t="s">
         <v>534</v>
@@ -10839,13 +10839,13 @@
         <v>1023</v>
       </c>
       <c r="AN16" t="s">
-        <v>1024</v>
+        <v>812</v>
       </c>
       <c r="AO16">
-        <v>0.99403730604060547</v>
+        <v>0.99406127396234245</v>
       </c>
       <c r="AP16">
-        <v>109.31605592223302</v>
+        <v>108.87664402372108</v>
       </c>
       <c r="AR16" t="s">
         <v>534</v>
@@ -10878,10 +10878,10 @@
         <v>1220</v>
       </c>
       <c r="BC16">
-        <v>0.99401640271965719</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD16">
-        <v>109.69928347295183</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10946,16 +10946,16 @@
         <v>549</v>
       </c>
       <c r="Y17" t="s">
-        <v>489</v>
+        <v>443</v>
       </c>
       <c r="Z17" t="s">
         <v>775</v>
       </c>
       <c r="AA17">
-        <v>0.99337606666931988</v>
+        <v>0.98823673546715696</v>
       </c>
       <c r="AB17">
-        <v>121.43877772913534</v>
+        <v>215.65984976878829</v>
       </c>
       <c r="AD17" t="s">
         <v>534</v>
@@ -10982,16 +10982,16 @@
         <v>887</v>
       </c>
       <c r="AM17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AN17" t="s">
         <v>1025</v>
       </c>
-      <c r="AN17" t="s">
-        <v>1026</v>
-      </c>
       <c r="AO17">
-        <v>0.99648541839873139</v>
+        <v>0.99314072847128088</v>
       </c>
       <c r="AP17">
-        <v>64.433996023258757</v>
+        <v>125.75331135985151</v>
       </c>
       <c r="AR17" t="s">
         <v>534</v>
@@ -11024,10 +11024,10 @@
         <v>1222</v>
       </c>
       <c r="BC17">
-        <v>0.9933934749176847</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD17">
-        <v>121.11962650911367</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -11092,16 +11092,16 @@
         <v>551</v>
       </c>
       <c r="Y18" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="Z18" t="s">
         <v>776</v>
       </c>
       <c r="AA18">
-        <v>0.99373081730832413</v>
+        <v>0.97910116787740509</v>
       </c>
       <c r="AB18">
-        <v>114.93501601405842</v>
+        <v>383.14525558090747</v>
       </c>
       <c r="AD18" t="s">
         <v>534</v>
@@ -11128,16 +11128,16 @@
         <v>889</v>
       </c>
       <c r="AM18" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AN18" t="s">
         <v>1027</v>
       </c>
-      <c r="AN18" t="s">
-        <v>1028</v>
-      </c>
       <c r="AO18">
-        <v>0.99564187507480328</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP18">
-        <v>79.898956961940044</v>
+        <v>81.597153048545437</v>
       </c>
       <c r="AR18" t="s">
         <v>534</v>
@@ -11170,10 +11170,10 @@
         <v>1224</v>
       </c>
       <c r="BC18">
-        <v>0.99314574070258299</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD18">
-        <v>125.66142045264445</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11238,16 +11238,16 @@
         <v>553</v>
       </c>
       <c r="Y19" t="s">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="Z19" t="s">
         <v>777</v>
       </c>
       <c r="AA19">
-        <v>0.99525157031553801</v>
+        <v>0.99053217900479729</v>
       </c>
       <c r="AB19">
-        <v>87.054544215136644</v>
+        <v>173.5767182453834</v>
       </c>
       <c r="AD19" t="s">
         <v>534</v>
@@ -11274,16 +11274,16 @@
         <v>891</v>
       </c>
       <c r="AM19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AN19" t="s">
         <v>1029</v>
       </c>
-      <c r="AN19" t="s">
-        <v>1030</v>
-      </c>
       <c r="AO19">
-        <v>0.99724271030877243</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP19">
-        <v>50.550311005838999</v>
+        <v>43.95454940357709</v>
       </c>
       <c r="AR19" t="s">
         <v>534</v>
@@ -11316,10 +11316,10 @@
         <v>1226</v>
       </c>
       <c r="BC19">
-        <v>0.98815917778868734</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD19">
-        <v>217.08174054073277</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11384,16 +11384,16 @@
         <v>555</v>
       </c>
       <c r="Y20" t="s">
-        <v>510</v>
+        <v>466</v>
       </c>
       <c r="Z20" t="s">
         <v>778</v>
       </c>
       <c r="AA20">
-        <v>0.98322732678073066</v>
+        <v>0.98938039552710522</v>
       </c>
       <c r="AB20">
-        <v>307.49900901993823</v>
+        <v>194.69274866973731</v>
       </c>
       <c r="AD20" t="s">
         <v>534</v>
@@ -11420,16 +11420,16 @@
         <v>893</v>
       </c>
       <c r="AM20" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AN20" t="s">
         <v>1031</v>
       </c>
-      <c r="AN20" t="s">
-        <v>1032</v>
-      </c>
       <c r="AO20">
-        <v>0.9819559893726687</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP20">
-        <v>330.80686150107323</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR20" t="s">
         <v>534</v>
@@ -11462,10 +11462,10 @@
         <v>1228</v>
       </c>
       <c r="BC20">
-        <v>0.98696067665321152</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD20">
-        <v>239.0542613577889</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11530,16 +11530,16 @@
         <v>557</v>
       </c>
       <c r="Y21" t="s">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="Z21" t="s">
         <v>779</v>
       </c>
       <c r="AA21">
-        <v>0.99147725599972802</v>
+        <v>0.99104477607780261</v>
       </c>
       <c r="AB21">
-        <v>156.25030667165251</v>
+        <v>164.17910524028503</v>
       </c>
       <c r="AD21" t="s">
         <v>534</v>
@@ -11566,16 +11566,16 @@
         <v>895</v>
       </c>
       <c r="AM21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AN21" t="s">
         <v>1033</v>
       </c>
-      <c r="AN21" t="s">
-        <v>1034</v>
-      </c>
       <c r="AO21">
-        <v>0.99758444956716208</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP21">
-        <v>44.285091268695631</v>
+        <v>49.645668091582088</v>
       </c>
       <c r="AR21" t="s">
         <v>534</v>
@@ -11608,10 +11608,10 @@
         <v>1230</v>
       </c>
       <c r="BC21">
-        <v>0.99420451954813838</v>
+        <v>0.98926566233528401</v>
       </c>
       <c r="BD21">
-        <v>106.25047495079694</v>
+        <v>196.79619051979324</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11676,16 +11676,16 @@
         <v>559</v>
       </c>
       <c r="Y22" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="Z22" t="s">
         <v>780</v>
       </c>
       <c r="AA22">
-        <v>0.99489602087782958</v>
+        <v>0.99850371228061685</v>
       </c>
       <c r="AB22">
-        <v>93.572950573123947</v>
+        <v>27.431941522024111</v>
       </c>
       <c r="AD22" t="s">
         <v>534</v>
@@ -11712,16 +11712,16 @@
         <v>897</v>
       </c>
       <c r="AM22" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AN22" t="s">
         <v>1035</v>
       </c>
-      <c r="AN22" t="s">
-        <v>1036</v>
-      </c>
       <c r="AO22">
-        <v>0.99414234808301016</v>
+        <v>0.99776348189506514</v>
       </c>
       <c r="AP22">
-        <v>107.39028514481463</v>
+        <v>41.002831923804749</v>
       </c>
       <c r="AR22" t="s">
         <v>534</v>
@@ -11754,10 +11754,10 @@
         <v>1232</v>
       </c>
       <c r="BC22">
-        <v>0.98163861082146986</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD22">
-        <v>336.62546827305243</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11822,16 +11822,16 @@
         <v>561</v>
       </c>
       <c r="Y23" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="Z23" t="s">
         <v>781</v>
       </c>
       <c r="AA23">
-        <v>0.99497915241892609</v>
+        <v>0.99570852190480352</v>
       </c>
       <c r="AB23">
-        <v>92.048872319688599</v>
+        <v>78.677098411934551</v>
       </c>
       <c r="AD23" t="s">
         <v>534</v>
@@ -11858,16 +11858,16 @@
         <v>899</v>
       </c>
       <c r="AM23" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AN23" t="s">
         <v>1037</v>
       </c>
-      <c r="AN23" t="s">
-        <v>1038</v>
-      </c>
       <c r="AO23">
-        <v>0.99569050067699549</v>
+        <v>0.99601995941081189</v>
       </c>
       <c r="AP23">
-        <v>79.007487588415231</v>
+        <v>72.967410801782407</v>
       </c>
       <c r="AR23" t="s">
         <v>534</v>
@@ -11900,10 +11900,10 @@
         <v>1234</v>
       </c>
       <c r="BC23">
-        <v>0.98990297941208016</v>
+        <v>0.98879241442000787</v>
       </c>
       <c r="BD23">
-        <v>185.11204411186426</v>
+        <v>205.47240229985658</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11968,16 +11968,16 @@
         <v>563</v>
       </c>
       <c r="Y24" t="s">
-        <v>501</v>
+        <v>444</v>
       </c>
       <c r="Z24" t="s">
         <v>782</v>
       </c>
       <c r="AA24">
-        <v>0.99539217974285599</v>
+        <v>0.96184233910767591</v>
       </c>
       <c r="AB24">
-        <v>84.476704714307601</v>
+        <v>699.55711635927571</v>
       </c>
       <c r="AD24" t="s">
         <v>534</v>
@@ -12004,16 +12004,16 @@
         <v>901</v>
       </c>
       <c r="AM24" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AN24" t="s">
         <v>1039</v>
       </c>
-      <c r="AN24" t="s">
-        <v>1040</v>
-      </c>
       <c r="AO24">
-        <v>0.99424679200457</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP24">
-        <v>105.47547991621673</v>
+        <v>95.557874766001078</v>
       </c>
       <c r="AR24" t="s">
         <v>534</v>
@@ -12046,10 +12046,10 @@
         <v>1236</v>
       </c>
       <c r="BC24">
-        <v>0.99665799830099</v>
+        <v>0.99542890407822671</v>
       </c>
       <c r="BD24">
-        <v>61.270031148516708</v>
+        <v>83.803425232511387</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -12114,16 +12114,16 @@
         <v>565</v>
       </c>
       <c r="Y25" t="s">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="Z25" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AA25">
-        <v>0.95261480241426988</v>
+        <v>0.9751195525863231</v>
       </c>
       <c r="AB25">
-        <v>868.72862240505196</v>
+        <v>456.14153591741012</v>
       </c>
       <c r="AD25" t="s">
         <v>534</v>
@@ -12150,16 +12150,16 @@
         <v>903</v>
       </c>
       <c r="AM25" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AN25" t="s">
         <v>1041</v>
       </c>
-      <c r="AN25" t="s">
-        <v>1042</v>
-      </c>
       <c r="AO25">
-        <v>0.99688290256322298</v>
+        <v>0.99562494976668181</v>
       </c>
       <c r="AP25">
-        <v>57.146786340912868</v>
+        <v>80.209254277501145</v>
       </c>
       <c r="AR25" t="s">
         <v>534</v>
@@ -12192,10 +12192,10 @@
         <v>1238</v>
       </c>
       <c r="BC25">
-        <v>0.98125520899414764</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD25">
-        <v>343.65450177395917</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12260,16 +12260,16 @@
         <v>567</v>
       </c>
       <c r="Y26" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="Z26" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AA26">
-        <v>0.98900080273824509</v>
+        <v>0.9922188892109014</v>
       </c>
       <c r="AB26">
-        <v>201.65194979884086</v>
+        <v>142.65369780014009</v>
       </c>
       <c r="AD26" t="s">
         <v>534</v>
@@ -12296,16 +12296,16 @@
         <v>905</v>
       </c>
       <c r="AM26" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AN26" t="s">
         <v>1043</v>
       </c>
-      <c r="AN26" t="s">
-        <v>1044</v>
-      </c>
       <c r="AO26">
-        <v>0.99568455481208962</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP26">
-        <v>79.11649511169017</v>
+        <v>151.70176382244892</v>
       </c>
       <c r="AR26" t="s">
         <v>534</v>
@@ -12335,13 +12335,13 @@
         <v>1239</v>
       </c>
       <c r="BB26" t="s">
-        <v>1226</v>
+        <v>1240</v>
       </c>
       <c r="BC26">
-        <v>0.99481196273061234</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD26">
-        <v>95.114016605440895</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12406,16 +12406,16 @@
         <v>569</v>
       </c>
       <c r="Y27" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="Z27" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AA27">
-        <v>0.97307980230740565</v>
+        <v>0.993866858424726</v>
       </c>
       <c r="AB27">
-        <v>493.53695769756274</v>
+        <v>112.44092888002339</v>
       </c>
       <c r="AD27" t="s">
         <v>534</v>
@@ -12442,16 +12442,16 @@
         <v>907</v>
       </c>
       <c r="AM27" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AN27" t="s">
         <v>1045</v>
       </c>
-      <c r="AN27" t="s">
-        <v>1046</v>
-      </c>
       <c r="AO27">
-        <v>0.9976540150806753</v>
+        <v>0.9854553870197319</v>
       </c>
       <c r="AP27">
-        <v>43.009723520953628</v>
+        <v>266.65123797158259</v>
       </c>
       <c r="AR27" t="s">
         <v>534</v>
@@ -12478,16 +12478,16 @@
         <v>1180</v>
       </c>
       <c r="BA27" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="BB27" t="s">
-        <v>1143</v>
+        <v>1242</v>
       </c>
       <c r="BC27">
-        <v>0.99098965084511315</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD27">
-        <v>165.18973450625904</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12552,16 +12552,16 @@
         <v>571</v>
       </c>
       <c r="Y28" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="Z28" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA28">
-        <v>0.99416973031683098</v>
+        <v>0.97539876358704702</v>
       </c>
       <c r="AB28">
-        <v>106.88827752476594</v>
+        <v>451.02266757080491</v>
       </c>
       <c r="AD28" t="s">
         <v>534</v>
@@ -12588,16 +12588,16 @@
         <v>909</v>
       </c>
       <c r="AM28" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AN28" t="s">
         <v>1047</v>
       </c>
-      <c r="AN28" t="s">
-        <v>1048</v>
-      </c>
       <c r="AO28">
-        <v>0.97020178001960844</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP28">
-        <v>546.30069964051177</v>
+        <v>473.60023862765331</v>
       </c>
       <c r="AR28" t="s">
         <v>534</v>
@@ -12624,16 +12624,16 @@
         <v>1182</v>
       </c>
       <c r="BA28" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="BB28" t="s">
-        <v>1242</v>
+        <v>1033</v>
       </c>
       <c r="BC28">
-        <v>0.98027195861782945</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD28">
-        <v>361.68075867312689</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12698,16 +12698,16 @@
         <v>573</v>
       </c>
       <c r="Y29" t="s">
-        <v>447</v>
+        <v>491</v>
       </c>
       <c r="Z29" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AA29">
-        <v>0.9955587546015936</v>
+        <v>0.99462766772169342</v>
       </c>
       <c r="AB29">
-        <v>81.422832304117264</v>
+        <v>98.492758435621411</v>
       </c>
       <c r="AD29" t="s">
         <v>534</v>
@@ -12734,16 +12734,16 @@
         <v>911</v>
       </c>
       <c r="AM29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AN29" t="s">
         <v>1049</v>
       </c>
-      <c r="AN29" t="s">
-        <v>791</v>
-      </c>
       <c r="AO29">
-        <v>0.98461822034848479</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP29">
-        <v>281.99929361111151</v>
+        <v>56.159977027506663</v>
       </c>
       <c r="AR29" t="s">
         <v>534</v>
@@ -12770,16 +12770,16 @@
         <v>1184</v>
       </c>
       <c r="BA29" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="BB29" t="s">
-        <v>1244</v>
+        <v>1100</v>
       </c>
       <c r="BC29">
-        <v>0.98574436213546524</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD29">
-        <v>261.35336084980423</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12844,16 +12844,16 @@
         <v>575</v>
       </c>
       <c r="Y30" t="s">
-        <v>441</v>
+        <v>505</v>
       </c>
       <c r="Z30" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA30">
-        <v>0.99543850973825376</v>
+        <v>0.99572841681824009</v>
       </c>
       <c r="AB30">
-        <v>83.627321465346881</v>
+        <v>78.312358332265575</v>
       </c>
       <c r="AD30" t="s">
         <v>534</v>
@@ -12886,10 +12886,10 @@
         <v>1051</v>
       </c>
       <c r="AO30">
-        <v>0.99732946028719993</v>
+        <v>0.99706157261604222</v>
       </c>
       <c r="AP30">
-        <v>48.959894734666925</v>
+        <v>53.871168705893545</v>
       </c>
       <c r="AR30" t="s">
         <v>534</v>
@@ -12922,10 +12922,10 @@
         <v>1246</v>
       </c>
       <c r="BC30">
-        <v>0.97821242976023937</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD30">
-        <v>399.43878772894504</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12990,16 +12990,16 @@
         <v>577</v>
       </c>
       <c r="Y31" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="Z31" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AA31">
-        <v>0.99463967358156791</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB31">
-        <v>98.272651004588909</v>
+        <v>868.72862240505196</v>
       </c>
       <c r="AD31" t="s">
         <v>534</v>
@@ -13032,10 +13032,10 @@
         <v>1053</v>
       </c>
       <c r="AO31">
-        <v>0.9976383201876905</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP31">
-        <v>43.297463225673241</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR31" t="s">
         <v>534</v>
@@ -13068,10 +13068,10 @@
         <v>1248</v>
       </c>
       <c r="BC31">
-        <v>0.99538398111052984</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD31">
-        <v>84.627012973619784</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -13136,16 +13136,16 @@
         <v>579</v>
       </c>
       <c r="Y32" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="Z32" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AA32">
-        <v>0.99485953599356114</v>
+        <v>0.98900080273824509</v>
       </c>
       <c r="AB32">
-        <v>94.241840118045246</v>
+        <v>201.65194979884086</v>
       </c>
       <c r="AD32" t="s">
         <v>534</v>
@@ -13175,13 +13175,13 @@
         <v>1054</v>
       </c>
       <c r="AN32" t="s">
-        <v>1055</v>
+        <v>769</v>
       </c>
       <c r="AO32">
-        <v>0.99544059907537386</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP32">
-        <v>83.589016951479763</v>
+        <v>819.02093721560016</v>
       </c>
       <c r="AR32" t="s">
         <v>534</v>
@@ -13214,10 +13214,10 @@
         <v>1250</v>
       </c>
       <c r="BC32">
-        <v>0.99374755699184159</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD32">
-        <v>114.62812181623703</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13282,16 +13282,16 @@
         <v>581</v>
       </c>
       <c r="Y33" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Z33" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AA33">
-        <v>0.99114422924909706</v>
+        <v>0.97307980230740565</v>
       </c>
       <c r="AB33">
-        <v>162.3557970998875</v>
+        <v>493.53695769756274</v>
       </c>
       <c r="AD33" t="s">
         <v>534</v>
@@ -13318,16 +13318,16 @@
         <v>919</v>
       </c>
       <c r="AM33" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AN33" t="s">
         <v>1056</v>
       </c>
-      <c r="AN33" t="s">
-        <v>1057</v>
-      </c>
       <c r="AO33">
-        <v>0.98996241922424166</v>
+        <v>0.99723686803477207</v>
       </c>
       <c r="AP33">
-        <v>184.02231422223667</v>
+        <v>50.657419362511995</v>
       </c>
       <c r="AR33" t="s">
         <v>534</v>
@@ -13360,10 +13360,10 @@
         <v>1252</v>
       </c>
       <c r="BC33">
-        <v>0.95713629889852414</v>
+        <v>0.99538398111052984</v>
       </c>
       <c r="BD33">
-        <v>785.83452019372396</v>
+        <v>84.627012973619784</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13428,16 +13428,16 @@
         <v>583</v>
       </c>
       <c r="Y34" t="s">
-        <v>428</v>
+        <v>499</v>
       </c>
       <c r="Z34" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AA34">
-        <v>0.9894322847464595</v>
+        <v>0.99416973031683098</v>
       </c>
       <c r="AB34">
-        <v>193.74144631490861</v>
+        <v>106.88827752476594</v>
       </c>
       <c r="AD34" t="s">
         <v>534</v>
@@ -13464,16 +13464,16 @@
         <v>921</v>
       </c>
       <c r="AM34" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AN34" t="s">
         <v>1058</v>
       </c>
-      <c r="AN34" t="s">
-        <v>1059</v>
-      </c>
       <c r="AO34">
-        <v>0.98589595763902149</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP34">
-        <v>258.57410995127316</v>
+        <v>58.751500348127372</v>
       </c>
       <c r="AR34" t="s">
         <v>534</v>
@@ -13506,10 +13506,10 @@
         <v>1254</v>
       </c>
       <c r="BC34">
-        <v>0.9959052853503485</v>
+        <v>0.98815917778868734</v>
       </c>
       <c r="BD34">
-        <v>75.06976857694373</v>
+        <v>217.08174054073277</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13574,16 +13574,16 @@
         <v>585</v>
       </c>
       <c r="Y35" t="s">
-        <v>519</v>
+        <v>452</v>
       </c>
       <c r="Z35" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AA35">
-        <v>0.99558181127270129</v>
+        <v>0.99726809134187266</v>
       </c>
       <c r="AB35">
-        <v>81.000126667143434</v>
+        <v>50.0849920656675</v>
       </c>
       <c r="AD35" t="s">
         <v>534</v>
@@ -13610,16 +13610,16 @@
         <v>923</v>
       </c>
       <c r="AM35" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AN35" t="s">
         <v>1060</v>
       </c>
-      <c r="AN35" t="s">
-        <v>1061</v>
-      </c>
       <c r="AO35">
-        <v>0.98853129699420972</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP35">
-        <v>210.2595551061562</v>
+        <v>151.17817104385733</v>
       </c>
       <c r="AR35" t="s">
         <v>534</v>
@@ -13649,13 +13649,13 @@
         <v>1255</v>
       </c>
       <c r="BB35" t="s">
-        <v>1116</v>
+        <v>1256</v>
       </c>
       <c r="BC35">
-        <v>0.99418931598784899</v>
+        <v>0.98696067665321152</v>
       </c>
       <c r="BD35">
-        <v>106.52920688943452</v>
+        <v>239.0542613577889</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13720,16 +13720,16 @@
         <v>587</v>
       </c>
       <c r="Y36" t="s">
-        <v>503</v>
+        <v>462</v>
       </c>
       <c r="Z36" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AA36">
-        <v>0.99679428524771641</v>
+        <v>0.98092062608337349</v>
       </c>
       <c r="AB36">
-        <v>58.771437125198602</v>
+        <v>349.78852180481954</v>
       </c>
       <c r="AD36" t="s">
         <v>534</v>
@@ -13756,16 +13756,16 @@
         <v>925</v>
       </c>
       <c r="AM36" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AN36" t="s">
         <v>1062</v>
       </c>
-      <c r="AN36" t="s">
-        <v>1063</v>
-      </c>
       <c r="AO36">
-        <v>0.9976320377495026</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP36">
-        <v>43.412641259119624</v>
+        <v>85.270745539791065</v>
       </c>
       <c r="AR36" t="s">
         <v>534</v>
@@ -13792,16 +13792,16 @@
         <v>1198</v>
       </c>
       <c r="BA36" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="BB36" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="BC36">
-        <v>0.96863461872110523</v>
+        <v>0.99027261546287559</v>
       </c>
       <c r="BD36">
-        <v>575.0319901130714</v>
+        <v>178.33538318061403</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13866,16 +13866,16 @@
         <v>589</v>
       </c>
       <c r="Y37" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="Z37" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AA37">
-        <v>0.98823673546715696</v>
+        <v>0.99311062188734656</v>
       </c>
       <c r="AB37">
-        <v>215.65984976878829</v>
+        <v>126.30526539864729</v>
       </c>
       <c r="AD37" t="s">
         <v>534</v>
@@ -13902,16 +13902,16 @@
         <v>927</v>
       </c>
       <c r="AM37" t="s">
+        <v>1063</v>
+      </c>
+      <c r="AN37" t="s">
         <v>1064</v>
       </c>
-      <c r="AN37" t="s">
-        <v>1065</v>
-      </c>
       <c r="AO37">
-        <v>0.99274560110857168</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP37">
-        <v>132.99731300951822</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR37" t="s">
         <v>534</v>
@@ -13938,16 +13938,16 @@
         <v>1200</v>
       </c>
       <c r="BA37" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="BB37" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="BC37">
-        <v>0.99282464000221371</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD37">
-        <v>131.54826662608204</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -14012,16 +14012,16 @@
         <v>591</v>
       </c>
       <c r="Y38" t="s">
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="Z38" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="AA38">
-        <v>0.97910116787740509</v>
+        <v>0.9968232244405717</v>
       </c>
       <c r="AB38">
-        <v>383.14525558090747</v>
+        <v>58.240885256184697</v>
       </c>
       <c r="AD38" t="s">
         <v>534</v>
@@ -14048,16 +14048,16 @@
         <v>929</v>
       </c>
       <c r="AM38" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AN38" t="s">
         <v>1066</v>
       </c>
-      <c r="AN38" t="s">
-        <v>1067</v>
-      </c>
       <c r="AO38">
-        <v>0.99626625046628881</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP38">
-        <v>68.452074784704692</v>
+        <v>42.750927651225993</v>
       </c>
       <c r="AR38" t="s">
         <v>534</v>
@@ -14090,10 +14090,10 @@
         <v>1261</v>
       </c>
       <c r="BC38">
-        <v>0.98926566233528401</v>
+        <v>0.99282464000221371</v>
       </c>
       <c r="BD38">
-        <v>196.79619051979324</v>
+        <v>131.54826662608204</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14158,16 +14158,16 @@
         <v>593</v>
       </c>
       <c r="Y39" t="s">
-        <v>427</v>
+        <v>518</v>
       </c>
       <c r="Z39" t="s">
         <v>796</v>
       </c>
       <c r="AA39">
-        <v>0.99053217900479729</v>
+        <v>0.99268906851994998</v>
       </c>
       <c r="AB39">
-        <v>173.5767182453834</v>
+        <v>134.03374380091802</v>
       </c>
       <c r="AD39" t="s">
         <v>534</v>
@@ -14194,16 +14194,16 @@
         <v>931</v>
       </c>
       <c r="AM39" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AN39" t="s">
         <v>1068</v>
       </c>
-      <c r="AN39" t="s">
-        <v>1069</v>
-      </c>
       <c r="AO39">
-        <v>0.99727528327537784</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP39">
-        <v>49.953139951405952</v>
+        <v>114.668395037126</v>
       </c>
       <c r="AR39" t="s">
         <v>534</v>
@@ -14236,10 +14236,10 @@
         <v>1263</v>
       </c>
       <c r="BC39">
-        <v>0.99053278045305837</v>
+        <v>0.99043684613816729</v>
       </c>
       <c r="BD39">
-        <v>173.56569169392964</v>
+        <v>175.324487466932</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14304,16 +14304,16 @@
         <v>595</v>
       </c>
       <c r="Y40" t="s">
-        <v>466</v>
+        <v>516</v>
       </c>
       <c r="Z40" t="s">
         <v>797</v>
       </c>
       <c r="AA40">
-        <v>0.98938039552710522</v>
+        <v>0.99380566729635134</v>
       </c>
       <c r="AB40">
-        <v>194.69274866973731</v>
+        <v>113.56276623355811</v>
       </c>
       <c r="AD40" t="s">
         <v>534</v>
@@ -14340,16 +14340,16 @@
         <v>933</v>
       </c>
       <c r="AM40" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AN40" t="s">
         <v>1070</v>
       </c>
-      <c r="AN40" t="s">
-        <v>1071</v>
-      </c>
       <c r="AO40">
-        <v>0.99644815774097173</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP40">
-        <v>65.117108082185538</v>
+        <v>101.57889622275951</v>
       </c>
       <c r="AR40" t="s">
         <v>534</v>
@@ -14382,10 +14382,10 @@
         <v>1265</v>
       </c>
       <c r="BC40">
-        <v>0.98879241442000787</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD40">
-        <v>205.47240229985658</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14450,16 +14450,16 @@
         <v>597</v>
       </c>
       <c r="Y41" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Z41" t="s">
         <v>798</v>
       </c>
       <c r="AA41">
-        <v>0.99104477607780261</v>
+        <v>0.97765566056164599</v>
       </c>
       <c r="AB41">
-        <v>164.17910524028503</v>
+        <v>409.64622303649065</v>
       </c>
       <c r="AD41" t="s">
         <v>534</v>
@@ -14486,16 +14486,16 @@
         <v>935</v>
       </c>
       <c r="AM41" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AN41" t="s">
         <v>1072</v>
       </c>
-      <c r="AN41" t="s">
-        <v>1073</v>
-      </c>
       <c r="AO41">
-        <v>0.99453968761366496</v>
+        <v>0.99664818772595598</v>
       </c>
       <c r="AP41">
-        <v>100.10572708280816</v>
+        <v>61.449891690807455</v>
       </c>
       <c r="AR41" t="s">
         <v>534</v>
@@ -14528,10 +14528,10 @@
         <v>1267</v>
       </c>
       <c r="BC41">
-        <v>0.99542890407822671</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD41">
-        <v>83.803425232511387</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14596,16 +14596,16 @@
         <v>599</v>
       </c>
       <c r="Y42" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="Z42" t="s">
         <v>799</v>
       </c>
       <c r="AA42">
-        <v>0.99850371228061685</v>
+        <v>0.99505763323061869</v>
       </c>
       <c r="AB42">
-        <v>27.431941522024111</v>
+        <v>90.610057438657108</v>
       </c>
       <c r="AD42" t="s">
         <v>534</v>
@@ -14632,16 +14632,16 @@
         <v>937</v>
       </c>
       <c r="AM42" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AN42" t="s">
         <v>1074</v>
       </c>
-      <c r="AN42" t="s">
-        <v>1075</v>
-      </c>
       <c r="AO42">
-        <v>0.99675446210163643</v>
+        <v>0.9819559893726687</v>
       </c>
       <c r="AP42">
-        <v>59.501528136664533</v>
+        <v>330.80686150107323</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14706,16 +14706,16 @@
         <v>601</v>
       </c>
       <c r="Y43" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="Z43" t="s">
         <v>800</v>
       </c>
       <c r="AA43">
-        <v>0.99570852190480352</v>
+        <v>0.9956126565071991</v>
       </c>
       <c r="AB43">
-        <v>78.677098411934551</v>
+        <v>80.434630701349718</v>
       </c>
       <c r="AD43" t="s">
         <v>534</v>
@@ -14742,16 +14742,16 @@
         <v>939</v>
       </c>
       <c r="AM43" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AN43" t="s">
         <v>1076</v>
       </c>
-      <c r="AN43" t="s">
-        <v>1077</v>
-      </c>
       <c r="AO43">
-        <v>0.99589340828485295</v>
+        <v>0.99758444956716208</v>
       </c>
       <c r="AP43">
-        <v>75.287514777696231</v>
+        <v>44.285091268695631</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14816,16 +14816,16 @@
         <v>603</v>
       </c>
       <c r="Y44" t="s">
-        <v>451</v>
+        <v>525</v>
       </c>
       <c r="Z44" t="s">
         <v>801</v>
       </c>
       <c r="AA44">
-        <v>0.99344074878931121</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB44">
-        <v>120.25293886262826</v>
+        <v>92.674656500591539</v>
       </c>
       <c r="AD44" t="s">
         <v>534</v>
@@ -14852,16 +14852,16 @@
         <v>941</v>
       </c>
       <c r="AM44" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AN44" t="s">
         <v>1078</v>
       </c>
-      <c r="AN44" t="s">
-        <v>1079</v>
-      </c>
       <c r="AO44">
-        <v>0.99766813121902409</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP44">
-        <v>42.750927651225993</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14926,16 +14926,16 @@
         <v>605</v>
       </c>
       <c r="Y45" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="Z45" t="s">
         <v>802</v>
       </c>
       <c r="AA45">
-        <v>0.9799951654300354</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB45">
-        <v>366.75530044935078</v>
+        <v>146.8618143486346</v>
       </c>
       <c r="AD45" t="s">
         <v>534</v>
@@ -14962,16 +14962,16 @@
         <v>943</v>
       </c>
       <c r="AM45" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AN45" t="s">
         <v>1080</v>
       </c>
-      <c r="AN45" t="s">
-        <v>1081</v>
-      </c>
       <c r="AO45">
-        <v>0.99374536027070226</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP45">
-        <v>114.668395037126</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -15036,16 +15036,16 @@
         <v>607</v>
       </c>
       <c r="Y46" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="Z46" t="s">
         <v>803</v>
       </c>
       <c r="AA46">
-        <v>0.99703673025664319</v>
+        <v>0.99525157031553801</v>
       </c>
       <c r="AB46">
-        <v>54.326611961541836</v>
+        <v>87.054544215136644</v>
       </c>
       <c r="AD46" t="s">
         <v>534</v>
@@ -15072,16 +15072,16 @@
         <v>945</v>
       </c>
       <c r="AM46" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AN46" t="s">
         <v>1082</v>
       </c>
-      <c r="AN46" t="s">
-        <v>1083</v>
-      </c>
       <c r="AO46">
-        <v>0.99445933293330402</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP46">
-        <v>101.57889622275951</v>
+        <v>109.31605592223302</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -15146,16 +15146,16 @@
         <v>609</v>
       </c>
       <c r="Y47" t="s">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="Z47" t="s">
         <v>804</v>
       </c>
       <c r="AA47">
-        <v>0.99516037587595307</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB47">
-        <v>88.726442274192678</v>
+        <v>307.49900901993823</v>
       </c>
       <c r="AD47" t="s">
         <v>534</v>
@@ -15182,16 +15182,16 @@
         <v>947</v>
       </c>
       <c r="AM47" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AN47" t="s">
         <v>1084</v>
       </c>
-      <c r="AN47" t="s">
-        <v>1085</v>
-      </c>
       <c r="AO47">
-        <v>0.99664818772595598</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP47">
-        <v>61.449891690807455</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15256,16 +15256,16 @@
         <v>611</v>
       </c>
       <c r="Y48" t="s">
-        <v>433</v>
+        <v>513</v>
       </c>
       <c r="Z48" t="s">
         <v>805</v>
       </c>
       <c r="AA48">
-        <v>0.99772567527055689</v>
+        <v>0.99147725599972802</v>
       </c>
       <c r="AB48">
-        <v>41.695953373122713</v>
+        <v>156.25030667165251</v>
       </c>
       <c r="AD48" t="s">
         <v>534</v>
@@ -15292,16 +15292,16 @@
         <v>949</v>
       </c>
       <c r="AM48" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AN48" t="s">
         <v>1086</v>
       </c>
-      <c r="AN48" t="s">
-        <v>1087</v>
-      </c>
       <c r="AO48">
-        <v>0.99601995941081189</v>
+        <v>0.99564187507480328</v>
       </c>
       <c r="AP48">
-        <v>72.967410801782407</v>
+        <v>79.898956961940044</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15366,16 +15366,16 @@
         <v>613</v>
       </c>
       <c r="Y49" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="Z49" t="s">
         <v>806</v>
       </c>
       <c r="AA49">
-        <v>0.99156821305535681</v>
+        <v>0.99489602087782958</v>
       </c>
       <c r="AB49">
-        <v>154.58276065179118</v>
+        <v>93.572950573123947</v>
       </c>
       <c r="AD49" t="s">
         <v>534</v>
@@ -15402,16 +15402,16 @@
         <v>951</v>
       </c>
       <c r="AM49" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AN49" t="s">
         <v>1088</v>
       </c>
-      <c r="AN49" t="s">
-        <v>1089</v>
-      </c>
       <c r="AO49">
-        <v>0.99478775228549088</v>
+        <v>0.99724271030877243</v>
       </c>
       <c r="AP49">
-        <v>95.557874766001078</v>
+        <v>50.550311005838999</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15476,16 +15476,16 @@
         <v>615</v>
       </c>
       <c r="Y50" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="Z50" t="s">
         <v>807</v>
       </c>
       <c r="AA50">
-        <v>0.99187818425781349</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB50">
-        <v>148.89995527341952</v>
+        <v>92.048872319688599</v>
       </c>
       <c r="AD50" t="s">
         <v>534</v>
@@ -15512,16 +15512,16 @@
         <v>953</v>
       </c>
       <c r="AM50" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AN50" t="s">
         <v>1090</v>
       </c>
-      <c r="AN50" t="s">
-        <v>1091</v>
-      </c>
       <c r="AO50">
-        <v>0.99562494976668181</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP50">
-        <v>80.209254277501145</v>
+        <v>138.50582323297994</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15586,16 +15586,16 @@
         <v>617</v>
       </c>
       <c r="Y51" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="Z51" t="s">
         <v>808</v>
       </c>
       <c r="AA51">
-        <v>0.9565626086601956</v>
+        <v>0.99539217974285599</v>
       </c>
       <c r="AB51">
-        <v>796.35217456308078</v>
+        <v>84.476704714307601</v>
       </c>
       <c r="AD51" t="s">
         <v>534</v>
@@ -15622,16 +15622,16 @@
         <v>955</v>
       </c>
       <c r="AM51" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AN51" t="s">
         <v>1092</v>
       </c>
-      <c r="AN51" t="s">
-        <v>1093</v>
-      </c>
       <c r="AO51">
-        <v>0.9917253583369573</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP51">
-        <v>151.70176382244892</v>
+        <v>121.72426728897108</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15696,16 +15696,16 @@
         <v>619</v>
       </c>
       <c r="Y52" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="Z52" t="s">
         <v>809</v>
       </c>
       <c r="AA52">
-        <v>0.98644915759239105</v>
+        <v>0.9955587546015936</v>
       </c>
       <c r="AB52">
-        <v>248.43211080616339</v>
+        <v>81.422832304117264</v>
       </c>
       <c r="AD52" t="s">
         <v>534</v>
@@ -15732,16 +15732,16 @@
         <v>957</v>
       </c>
       <c r="AM52" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AN52" t="s">
         <v>1094</v>
       </c>
-      <c r="AN52" t="s">
-        <v>1095</v>
-      </c>
       <c r="AO52">
-        <v>0.99244513691456471</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP52">
-        <v>138.50582323297994</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15806,16 +15806,16 @@
         <v>621</v>
       </c>
       <c r="Y53" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="Z53" t="s">
         <v>810</v>
       </c>
       <c r="AA53">
-        <v>0.9946911823559148</v>
+        <v>0.99543850973825376</v>
       </c>
       <c r="AB53">
-        <v>97.32832347489618</v>
+        <v>83.627321465346881</v>
       </c>
       <c r="AD53" t="s">
         <v>534</v>
@@ -15842,16 +15842,16 @@
         <v>959</v>
       </c>
       <c r="AM53" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AN53" t="s">
         <v>1096</v>
       </c>
-      <c r="AN53" t="s">
-        <v>1097</v>
-      </c>
       <c r="AO53">
-        <v>0.99336049451151065</v>
+        <v>0.99503347605638859</v>
       </c>
       <c r="AP53">
-        <v>121.72426728897108</v>
+        <v>91.052938966209936</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15916,16 +15916,16 @@
         <v>623</v>
       </c>
       <c r="Y54" t="s">
-        <v>512</v>
+        <v>467</v>
       </c>
       <c r="Z54" t="s">
-        <v>811</v>
+        <v>776</v>
       </c>
       <c r="AA54">
-        <v>0.99040896044606685</v>
+        <v>0.99463967358156791</v>
       </c>
       <c r="AB54">
-        <v>175.83572515544165</v>
+        <v>98.272651004588909</v>
       </c>
       <c r="AD54" t="s">
         <v>534</v>
@@ -15952,16 +15952,16 @@
         <v>961</v>
       </c>
       <c r="AM54" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AN54" t="s">
         <v>1098</v>
       </c>
-      <c r="AN54" t="s">
-        <v>1099</v>
-      </c>
       <c r="AO54">
-        <v>0.99681385284485569</v>
+        <v>0.99500949727727495</v>
       </c>
       <c r="AP54">
-        <v>58.41269784431158</v>
+        <v>91.492549916626857</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -16026,16 +16026,16 @@
         <v>625</v>
       </c>
       <c r="Y55" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="Z55" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AA55">
-        <v>0.9946350729064154</v>
+        <v>0.99485953599356114</v>
       </c>
       <c r="AB55">
-        <v>98.356996715718111</v>
+        <v>94.241840118045246</v>
       </c>
       <c r="AD55" t="s">
         <v>534</v>
@@ -16062,16 +16062,16 @@
         <v>963</v>
       </c>
       <c r="AM55" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AN55" t="s">
         <v>1100</v>
       </c>
-      <c r="AN55" t="s">
-        <v>1101</v>
-      </c>
       <c r="AO55">
-        <v>0.99503347605638859</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP55">
-        <v>91.052938966209936</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -16136,16 +16136,16 @@
         <v>627</v>
       </c>
       <c r="Y56" t="s">
-        <v>494</v>
+        <v>437</v>
       </c>
       <c r="Z56" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AA56">
-        <v>0.99431447054153432</v>
+        <v>0.99114422924909706</v>
       </c>
       <c r="AB56">
-        <v>104.23470673853728</v>
+        <v>162.3557970998875</v>
       </c>
       <c r="AD56" t="s">
         <v>534</v>
@@ -16172,16 +16172,16 @@
         <v>965</v>
       </c>
       <c r="AM56" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AN56" t="s">
         <v>1102</v>
       </c>
-      <c r="AN56" t="s">
-        <v>1103</v>
-      </c>
       <c r="AO56">
-        <v>0.98030817163892847</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP56">
-        <v>361.01685328631117</v>
+        <v>85.716830221163534</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16246,16 +16246,16 @@
         <v>629</v>
       </c>
       <c r="Y57" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="Z57" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AA57">
-        <v>0.99726809134187266</v>
+        <v>0.9894322847464595</v>
       </c>
       <c r="AB57">
-        <v>50.0849920656675</v>
+        <v>193.74144631490861</v>
       </c>
       <c r="AD57" t="s">
         <v>534</v>
@@ -16282,16 +16282,16 @@
         <v>967</v>
       </c>
       <c r="AM57" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AN57" t="s">
         <v>1104</v>
       </c>
-      <c r="AN57" t="s">
-        <v>1105</v>
-      </c>
       <c r="AO57">
-        <v>0.99429886321911398</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP57">
-        <v>104.52084098291034</v>
+        <v>214.50192763901472</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16356,16 +16356,16 @@
         <v>631</v>
       </c>
       <c r="Y58" t="s">
-        <v>462</v>
+        <v>519</v>
       </c>
       <c r="Z58" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AA58">
-        <v>0.98092062608337349</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB58">
-        <v>349.78852180481954</v>
+        <v>81.000126667143434</v>
       </c>
       <c r="AD58" t="s">
         <v>534</v>
@@ -16392,16 +16392,16 @@
         <v>969</v>
       </c>
       <c r="AM58" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AN58" t="s">
         <v>1106</v>
       </c>
-      <c r="AN58" t="s">
-        <v>791</v>
-      </c>
       <c r="AO58">
-        <v>0.99406127396234245</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP58">
-        <v>108.87664402372108</v>
+        <v>184.02231422223667</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16466,16 +16466,16 @@
         <v>633</v>
       </c>
       <c r="Y59" t="s">
-        <v>456</v>
+        <v>503</v>
       </c>
       <c r="Z59" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AA59">
-        <v>0.99311062188734656</v>
+        <v>0.99679428524771641</v>
       </c>
       <c r="AB59">
-        <v>126.30526539864729</v>
+        <v>58.771437125198602</v>
       </c>
       <c r="AD59" t="s">
         <v>534</v>
@@ -16508,10 +16508,10 @@
         <v>1108</v>
       </c>
       <c r="AO59">
-        <v>0.99314072847128088</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP59">
-        <v>125.75331135985151</v>
+        <v>258.57410995127316</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16576,16 +16576,16 @@
         <v>635</v>
       </c>
       <c r="Y60" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="Z60" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="AA60">
-        <v>0.9968232244405717</v>
+        <v>0.99168183433195056</v>
       </c>
       <c r="AB60">
-        <v>58.240885256184697</v>
+        <v>152.49970391424031</v>
       </c>
       <c r="AD60" t="s">
         <v>534</v>
@@ -16618,10 +16618,10 @@
         <v>1110</v>
       </c>
       <c r="AO60">
-        <v>0.99554924619735208</v>
+        <v>0.98853129699420972</v>
       </c>
       <c r="AP60">
-        <v>81.597153048545437</v>
+        <v>210.2595551061562</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16686,16 +16686,16 @@
         <v>637</v>
       </c>
       <c r="Y61" t="s">
-        <v>518</v>
+        <v>478</v>
       </c>
       <c r="Z61" t="s">
-        <v>818</v>
+        <v>776</v>
       </c>
       <c r="AA61">
-        <v>0.99268906851994998</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB61">
-        <v>134.03374380091802</v>
+        <v>675.25867642804383</v>
       </c>
       <c r="AD61" t="s">
         <v>534</v>
@@ -16728,10 +16728,10 @@
         <v>1112</v>
       </c>
       <c r="AO61">
-        <v>0.99760247912344124</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP61">
-        <v>43.95454940357709</v>
+        <v>43.412641259119624</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16796,16 +16796,16 @@
         <v>639</v>
       </c>
       <c r="Y62" t="s">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="Z62" t="s">
-        <v>819</v>
+        <v>776</v>
       </c>
       <c r="AA62">
-        <v>0.99380566729635134</v>
+        <v>0.97267890273247193</v>
       </c>
       <c r="AB62">
-        <v>113.56276623355811</v>
+        <v>500.88678323801429</v>
       </c>
       <c r="AD62" t="s">
         <v>534</v>
@@ -16838,10 +16838,10 @@
         <v>1114</v>
       </c>
       <c r="AO62">
-        <v>0.99083036293819104</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP62">
-        <v>168.11001279983091</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16906,16 +16906,16 @@
         <v>641</v>
       </c>
       <c r="Y63" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="Z63" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="AA63">
-        <v>0.97765566056164599</v>
+        <v>0.98996675113795696</v>
       </c>
       <c r="AB63">
-        <v>409.64622303649065</v>
+        <v>183.94289580412195</v>
       </c>
       <c r="AD63" t="s">
         <v>534</v>
@@ -16948,10 +16948,10 @@
         <v>1116</v>
       </c>
       <c r="AO63">
-        <v>0.99729205446773184</v>
+        <v>0.99626625046628881</v>
       </c>
       <c r="AP63">
-        <v>49.645668091582088</v>
+        <v>68.452074784704692</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -17016,16 +17016,16 @@
         <v>643</v>
       </c>
       <c r="Y64" t="s">
-        <v>514</v>
+        <v>431</v>
       </c>
       <c r="Z64" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="AA64">
-        <v>0.99505763323061869</v>
+        <v>0.98775929894003411</v>
       </c>
       <c r="AB64">
-        <v>90.610057438657108</v>
+        <v>224.41285276604052</v>
       </c>
       <c r="AD64" t="s">
         <v>534</v>
@@ -17058,10 +17058,10 @@
         <v>1118</v>
       </c>
       <c r="AO64">
-        <v>0.99776348189506514</v>
+        <v>0.99727528327537784</v>
       </c>
       <c r="AP64">
-        <v>41.002831923804749</v>
+        <v>49.953139951405952</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -17126,16 +17126,16 @@
         <v>645</v>
       </c>
       <c r="Y65" t="s">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="Z65" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="AA65">
-        <v>0.9956126565071991</v>
+        <v>0.99558768376711515</v>
       </c>
       <c r="AB65">
-        <v>80.434630701349718</v>
+        <v>80.892464269556413</v>
       </c>
       <c r="AD65" t="s">
         <v>534</v>
@@ -17168,10 +17168,10 @@
         <v>1120</v>
       </c>
       <c r="AO65">
-        <v>0.99279821853131744</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP65">
-        <v>132.03266025918069</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17236,16 +17236,16 @@
         <v>647</v>
       </c>
       <c r="Y66" t="s">
-        <v>525</v>
+        <v>421</v>
       </c>
       <c r="Z66" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="AA66">
-        <v>0.99494501873633134</v>
+        <v>0.99458514459095504</v>
       </c>
       <c r="AB66">
-        <v>92.674656500591539</v>
+        <v>99.272349165823911</v>
       </c>
       <c r="AD66" t="s">
         <v>534</v>
@@ -17278,10 +17278,10 @@
         <v>1122</v>
       </c>
       <c r="AO66">
-        <v>0.99567626923235475</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP66">
-        <v>79.268397406829976</v>
+        <v>105.47547991621673</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17346,16 +17346,16 @@
         <v>649</v>
       </c>
       <c r="Y67" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="Z67" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="AA67">
-        <v>0.99198935558098356</v>
+        <v>0.99799095183376552</v>
       </c>
       <c r="AB67">
-        <v>146.8618143486346</v>
+        <v>36.832549714298302</v>
       </c>
       <c r="AD67" t="s">
         <v>534</v>
@@ -17388,10 +17388,10 @@
         <v>1124</v>
       </c>
       <c r="AO67">
-        <v>0.99721018800165706</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP67">
-        <v>51.146553302954146</v>
+        <v>57.146786340912868</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17456,16 +17456,16 @@
         <v>651</v>
       </c>
       <c r="Y68" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="Z68" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="AA68">
-        <v>0.96279893744053135</v>
+        <v>0.99344074878931121</v>
       </c>
       <c r="AB68">
-        <v>682.01948025692582</v>
+        <v>120.25293886262826</v>
       </c>
       <c r="AD68" t="s">
         <v>534</v>
@@ -17498,10 +17498,10 @@
         <v>1126</v>
       </c>
       <c r="AO68">
-        <v>0.9959346869215373</v>
+        <v>0.99568455481208962</v>
       </c>
       <c r="AP68">
-        <v>74.530739771815789</v>
+        <v>79.11649511169017</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17566,16 +17566,16 @@
         <v>653</v>
       </c>
       <c r="Y69" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="Z69" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="AA69">
-        <v>0.97166110802369898</v>
+        <v>0.9799951654300354</v>
       </c>
       <c r="AB69">
-        <v>519.54635289885152</v>
+        <v>366.75530044935078</v>
       </c>
       <c r="AD69" t="s">
         <v>534</v>
@@ -17608,10 +17608,10 @@
         <v>1128</v>
       </c>
       <c r="AO69">
-        <v>0.9961850470371636</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP69">
-        <v>69.94080431866837</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17676,16 +17676,16 @@
         <v>655</v>
       </c>
       <c r="Y70" t="s">
-        <v>529</v>
+        <v>439</v>
       </c>
       <c r="Z70" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="AA70">
-        <v>0.99632140393460755</v>
+        <v>0.99703673025664319</v>
       </c>
       <c r="AB70">
-        <v>67.440927865527755</v>
+        <v>54.326611961541836</v>
       </c>
       <c r="AD70" t="s">
         <v>534</v>
@@ -17715,13 +17715,13 @@
         <v>1129</v>
       </c>
       <c r="AN70" t="s">
-        <v>808</v>
+        <v>1130</v>
       </c>
       <c r="AO70">
-        <v>0.95532613069733086</v>
+        <v>0.99279821853131744</v>
       </c>
       <c r="AP70">
-        <v>819.02093721560016</v>
+        <v>132.03266025918069</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17786,16 +17786,16 @@
         <v>657</v>
       </c>
       <c r="Y71" t="s">
-        <v>531</v>
+        <v>470</v>
       </c>
       <c r="Z71" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="AA71">
-        <v>0.99478593896263345</v>
+        <v>0.99516037587595307</v>
       </c>
       <c r="AB71">
-        <v>95.59111901838736</v>
+        <v>88.726442274192678</v>
       </c>
       <c r="AD71" t="s">
         <v>534</v>
@@ -17822,16 +17822,16 @@
         <v>995</v>
       </c>
       <c r="AM71" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="AN71" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AO71">
-        <v>0.99723686803477207</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP71">
-        <v>50.657419362511995</v>
+        <v>79.268397406829976</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17896,16 +17896,16 @@
         <v>659</v>
       </c>
       <c r="Y72" t="s">
-        <v>502</v>
+        <v>433</v>
       </c>
       <c r="Z72" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="AA72">
-        <v>0.99598444160375343</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB72">
-        <v>73.6185705978545</v>
+        <v>41.695953373122713</v>
       </c>
       <c r="AD72" t="s">
         <v>534</v>
@@ -17932,16 +17932,16 @@
         <v>997</v>
       </c>
       <c r="AM72" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AN72" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="AO72">
-        <v>0.996795372708284</v>
+        <v>0.99721018800165706</v>
       </c>
       <c r="AP72">
-        <v>58.751500348127372</v>
+        <v>51.146553302954146</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -18006,16 +18006,16 @@
         <v>661</v>
       </c>
       <c r="Y73" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="Z73" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="AA73">
-        <v>0.99704166323096854</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB73">
-        <v>54.23617409891024</v>
+        <v>154.58276065179118</v>
       </c>
       <c r="AD73" t="s">
         <v>534</v>
@@ -18042,16 +18042,16 @@
         <v>999</v>
       </c>
       <c r="AM73" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="AN73" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="AO73">
-        <v>0.99175391794306234</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP73">
-        <v>151.17817104385733</v>
+        <v>74.530739771815789</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -18116,16 +18116,16 @@
         <v>663</v>
       </c>
       <c r="Y74" t="s">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="Z74" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="AA74">
-        <v>0.99764423102316024</v>
+        <v>0.99187818425781349</v>
       </c>
       <c r="AB74">
-        <v>43.189097908729714</v>
+        <v>148.89995527341952</v>
       </c>
       <c r="AD74" t="s">
         <v>534</v>
@@ -18152,16 +18152,16 @@
         <v>1001</v>
       </c>
       <c r="AM74" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AN74" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AO74">
-        <v>0.99534886842510228</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP74">
-        <v>85.270745539791065</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18226,16 +18226,16 @@
         <v>665</v>
       </c>
       <c r="Y75" t="s">
-        <v>523</v>
+        <v>460</v>
       </c>
       <c r="Z75" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="AA75">
-        <v>0.99729259940965764</v>
+        <v>0.98283227092255654</v>
       </c>
       <c r="AB75">
-        <v>49.635677489608995</v>
+        <v>314.74169975312947</v>
       </c>
       <c r="AD75" t="s">
         <v>534</v>
@@ -18262,16 +18262,16 @@
         <v>1003</v>
       </c>
       <c r="AM75" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="AN75" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AO75">
-        <v>0.99433447571906541</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP75">
-        <v>103.86794515046822</v>
+        <v>546.30069964051177</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18336,16 +18336,16 @@
         <v>667</v>
       </c>
       <c r="Y76" t="s">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="Z76" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="AA76">
-        <v>0.99299389066598753</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB76">
-        <v>128.44533779022913</v>
+        <v>106.82211818572355</v>
       </c>
       <c r="AD76" t="s">
         <v>534</v>
@@ -18372,16 +18372,16 @@
         <v>1005</v>
       </c>
       <c r="AM76" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="AN76" t="s">
-        <v>1141</v>
+        <v>812</v>
       </c>
       <c r="AO76">
-        <v>0.99500949727727495</v>
+        <v>0.98461822034848479</v>
       </c>
       <c r="AP76">
-        <v>91.492549916626857</v>
+        <v>281.99929361111151</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18446,16 +18446,16 @@
         <v>669</v>
       </c>
       <c r="Y77" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Z77" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="AA77">
-        <v>0.99536976316228409</v>
+        <v>0.99519314522306834</v>
       </c>
       <c r="AB77">
-        <v>84.887675358125122</v>
+        <v>88.125670910414172</v>
       </c>
       <c r="AD77" t="s">
         <v>534</v>
@@ -18488,10 +18488,10 @@
         <v>1143</v>
       </c>
       <c r="AO77">
-        <v>0.99679967385551038</v>
+        <v>0.99732946028719993</v>
       </c>
       <c r="AP77">
-        <v>58.672645982308907</v>
+        <v>48.959894734666925</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18556,16 +18556,16 @@
         <v>671</v>
       </c>
       <c r="Y78" t="s">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="Z78" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="AA78">
-        <v>0.99549782242326257</v>
+        <v>0.99508465148544945</v>
       </c>
       <c r="AB78">
-        <v>82.539922240185263</v>
+        <v>90.11472276676038</v>
       </c>
       <c r="AD78" t="s">
         <v>534</v>
@@ -18598,10 +18598,10 @@
         <v>1145</v>
       </c>
       <c r="AO78">
-        <v>0.99532453653339104</v>
+        <v>0.9976383201876905</v>
       </c>
       <c r="AP78">
-        <v>85.716830221163534</v>
+        <v>43.297463225673241</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18666,16 +18666,16 @@
         <v>673</v>
       </c>
       <c r="Y79" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="Z79" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="AA79">
-        <v>0.99657689065782151</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB79">
-        <v>62.757004606605378</v>
+        <v>153.20678909592235</v>
       </c>
       <c r="AD79" t="s">
         <v>534</v>
@@ -18708,10 +18708,10 @@
         <v>1147</v>
       </c>
       <c r="AO79">
-        <v>0.98829989485605374</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP79">
-        <v>214.50192763901472</v>
+        <v>83.589016951479763</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18776,16 +18776,16 @@
         <v>675</v>
       </c>
       <c r="Y80" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="Z80" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="AA80">
-        <v>0.96184233910767591</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB80">
-        <v>699.55711635927571</v>
+        <v>62.251070203636829</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18850,16 +18850,16 @@
         <v>677</v>
       </c>
       <c r="Y81" t="s">
-        <v>449</v>
+        <v>524</v>
       </c>
       <c r="Z81" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="AA81">
-        <v>0.9751195525863231</v>
+        <v>0.99711280774432032</v>
       </c>
       <c r="AB81">
-        <v>456.14153591741012</v>
+        <v>52.931858020794202</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18924,16 +18924,16 @@
         <v>679</v>
       </c>
       <c r="Y82" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
       <c r="Z82" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="AA82">
-        <v>0.9922188892109014</v>
+        <v>0.99277811726114784</v>
       </c>
       <c r="AB82">
-        <v>142.65369780014009</v>
+        <v>132.40118354562273</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -18998,16 +18998,16 @@
         <v>681</v>
       </c>
       <c r="Y83" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="Z83" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="AA83">
-        <v>0.993866858424726</v>
+        <v>0.96988338866662871</v>
       </c>
       <c r="AB83">
-        <v>112.44092888002339</v>
+        <v>552.13787444514003</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -19072,16 +19072,16 @@
         <v>683</v>
       </c>
       <c r="Y84" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="Z84" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AA84">
-        <v>0.97539876358704702</v>
+        <v>0.98061830542009054</v>
       </c>
       <c r="AB84">
-        <v>451.02266757080491</v>
+        <v>355.3310672983406</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -19146,16 +19146,16 @@
         <v>685</v>
       </c>
       <c r="Y85" t="s">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="Z85" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="AA85">
-        <v>0.99462766772169342</v>
+        <v>0.99621118265687969</v>
       </c>
       <c r="AB85">
-        <v>98.492758435621411</v>
+        <v>69.461651290538995</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19220,16 +19220,16 @@
         <v>687</v>
       </c>
       <c r="Y86" t="s">
-        <v>505</v>
+        <v>429</v>
       </c>
       <c r="Z86" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="AA86">
-        <v>0.99572841681824009</v>
+        <v>0.99720399169001062</v>
       </c>
       <c r="AB86">
-        <v>78.312358332265575</v>
+        <v>51.260152349805715</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19294,16 +19294,16 @@
         <v>689</v>
       </c>
       <c r="Y87" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="Z87" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="AA87">
-        <v>0.98283227092255654</v>
+        <v>0.99546059111776786</v>
       </c>
       <c r="AB87">
-        <v>314.74169975312947</v>
+        <v>83.222496174256221</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19368,16 +19368,16 @@
         <v>691</v>
       </c>
       <c r="Y88" t="s">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="Z88" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="AA88">
-        <v>0.99417333900805149</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB88">
-        <v>106.82211818572355</v>
+        <v>123.82892298254488</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19442,16 +19442,16 @@
         <v>693</v>
       </c>
       <c r="Y89" t="s">
-        <v>528</v>
+        <v>489</v>
       </c>
       <c r="Z89" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="AA89">
-        <v>0.99519314522306834</v>
+        <v>0.99337606666931988</v>
       </c>
       <c r="AB89">
-        <v>88.125670910414172</v>
+        <v>121.43877772913534</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19516,16 +19516,16 @@
         <v>695</v>
       </c>
       <c r="Y90" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="Z90" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="AA90">
-        <v>0.99508465148544945</v>
+        <v>0.99373081730832413</v>
       </c>
       <c r="AB90">
-        <v>90.11472276676038</v>
+        <v>114.93501601405842</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19590,16 +19590,16 @@
         <v>697</v>
       </c>
       <c r="Y91" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="Z91" t="s">
-        <v>787</v>
+        <v>844</v>
       </c>
       <c r="AA91">
-        <v>0.99168183433195056</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB91">
-        <v>152.49970391424031</v>
+        <v>637.85920701836687</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19664,16 +19664,16 @@
         <v>699</v>
       </c>
       <c r="Y92" t="s">
-        <v>478</v>
+        <v>440</v>
       </c>
       <c r="Z92" t="s">
-        <v>789</v>
+        <v>845</v>
       </c>
       <c r="AA92">
-        <v>0.96316770855847034</v>
+        <v>0.98451942937510906</v>
       </c>
       <c r="AB92">
-        <v>675.25867642804383</v>
+        <v>283.810461456334</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19738,16 +19738,16 @@
         <v>701</v>
       </c>
       <c r="Y93" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="Z93" t="s">
-        <v>789</v>
+        <v>846</v>
       </c>
       <c r="AA93">
-        <v>0.97267890273247193</v>
+        <v>0.97762911532019692</v>
       </c>
       <c r="AB93">
-        <v>500.88678323801429</v>
+        <v>410.13288579638987</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19812,16 +19812,16 @@
         <v>703</v>
       </c>
       <c r="Y94" t="s">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="Z94" t="s">
-        <v>826</v>
+        <v>847</v>
       </c>
       <c r="AA94">
-        <v>0.98996675113795696</v>
+        <v>0.99197266581296062</v>
       </c>
       <c r="AB94">
-        <v>183.94289580412195</v>
+        <v>147.16779342905627</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19886,16 +19886,16 @@
         <v>705</v>
       </c>
       <c r="Y95" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="Z95" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="AA95">
-        <v>0.98775929894003411</v>
+        <v>0.98707909035546004</v>
       </c>
       <c r="AB95">
-        <v>224.41285276604052</v>
+        <v>236.88334348323221</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19960,16 +19960,16 @@
         <v>707</v>
       </c>
       <c r="Y96" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="Z96" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="AA96">
-        <v>0.99558768376711515</v>
+        <v>0.98908992153232178</v>
       </c>
       <c r="AB96">
-        <v>80.892464269556413</v>
+        <v>200.01810524076683</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -20034,16 +20034,16 @@
         <v>709</v>
       </c>
       <c r="Y97" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="Z97" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="AA97">
-        <v>0.99458514459095504</v>
+        <v>0.99669256432701525</v>
       </c>
       <c r="AB97">
-        <v>99.272349165823911</v>
+        <v>60.636320671386301</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -20108,16 +20108,16 @@
         <v>711</v>
       </c>
       <c r="Y98" t="s">
-        <v>484</v>
+        <v>432</v>
       </c>
       <c r="Z98" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="AA98">
-        <v>0.99799095183376552</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB98">
-        <v>36.832549714298302</v>
+        <v>62.664876956210314</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20182,16 +20182,16 @@
         <v>713</v>
       </c>
       <c r="Y99" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="Z99" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="AA99">
-        <v>0.9916432660493133</v>
+        <v>0.99591694828752353</v>
       </c>
       <c r="AB99">
-        <v>153.20678909592235</v>
+        <v>74.855948062068691</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20256,16 +20256,16 @@
         <v>715</v>
       </c>
       <c r="Y100" t="s">
-        <v>434</v>
+        <v>493</v>
       </c>
       <c r="Z100" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="AA100">
-        <v>0.99660448707980165</v>
+        <v>0.99521933495260839</v>
       </c>
       <c r="AB100">
-        <v>62.251070203636829</v>
+        <v>87.645525868847031</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20330,16 +20330,16 @@
         <v>717</v>
       </c>
       <c r="Y101" t="s">
-        <v>524</v>
+        <v>445</v>
       </c>
       <c r="Z101" t="s">
-        <v>852</v>
+        <v>782</v>
       </c>
       <c r="AA101">
-        <v>0.99711280774432032</v>
+        <v>0.96279893744053135</v>
       </c>
       <c r="AB101">
-        <v>52.931858020794202</v>
+        <v>682.01948025692582</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20404,16 +20404,16 @@
         <v>719</v>
       </c>
       <c r="Y102" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="Z102" t="s">
-        <v>853</v>
+        <v>816</v>
       </c>
       <c r="AA102">
-        <v>0.99277811726114784</v>
+        <v>0.97166110802369898</v>
       </c>
       <c r="AB102">
-        <v>132.40118354562273</v>
+        <v>519.54635289885152</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20478,16 +20478,16 @@
         <v>721</v>
       </c>
       <c r="Y103" t="s">
-        <v>479</v>
+        <v>529</v>
       </c>
       <c r="Z103" t="s">
         <v>854</v>
       </c>
       <c r="AA103">
-        <v>0.96520767961718001</v>
+        <v>0.99632140393460755</v>
       </c>
       <c r="AB103">
-        <v>637.85920701836687</v>
+        <v>67.440927865527755</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20552,16 +20552,16 @@
         <v>723</v>
       </c>
       <c r="Y104" t="s">
-        <v>440</v>
+        <v>531</v>
       </c>
       <c r="Z104" t="s">
         <v>855</v>
       </c>
       <c r="AA104">
-        <v>0.98451942937510906</v>
+        <v>0.99478593896263345</v>
       </c>
       <c r="AB104">
-        <v>283.810461456334</v>
+        <v>95.59111901838736</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20626,16 +20626,16 @@
         <v>725</v>
       </c>
       <c r="Y105" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="Z105" t="s">
         <v>856</v>
       </c>
       <c r="AA105">
-        <v>0.97762911532019692</v>
+        <v>0.99598444160375343</v>
       </c>
       <c r="AB105">
-        <v>410.13288579638987</v>
+        <v>73.6185705978545</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20700,16 +20700,16 @@
         <v>727</v>
       </c>
       <c r="Y106" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="Z106" t="s">
-        <v>857</v>
+        <v>782</v>
       </c>
       <c r="AA106">
-        <v>0.99197266581296062</v>
+        <v>0.97158859079583204</v>
       </c>
       <c r="AB106">
-        <v>147.16779342905627</v>
+        <v>520.87583540974583</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20774,16 +20774,16 @@
         <v>729</v>
       </c>
       <c r="Y107" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="Z107" t="s">
-        <v>858</v>
+        <v>776</v>
       </c>
       <c r="AA107">
-        <v>0.98707909035546004</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB107">
-        <v>236.88334348323221</v>
+        <v>1103.617804666449</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20848,16 +20848,16 @@
         <v>731</v>
       </c>
       <c r="Y108" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="Z108" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="AA108">
-        <v>0.98908992153232178</v>
+        <v>0.98205098401701585</v>
       </c>
       <c r="AB108">
-        <v>200.01810524076683</v>
+        <v>329.06529302137608</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20922,16 +20922,16 @@
         <v>733</v>
       </c>
       <c r="Y109" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="Z109" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="AA109">
-        <v>0.99669256432701525</v>
+        <v>0.979429443890801</v>
       </c>
       <c r="AB109">
-        <v>60.636320671386301</v>
+        <v>377.12686200198209</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20996,16 +20996,16 @@
         <v>735</v>
       </c>
       <c r="Y110" t="s">
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="Z110" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="AA110">
-        <v>0.99658191580238853</v>
+        <v>0.995907010043938</v>
       </c>
       <c r="AB110">
-        <v>62.664876956210314</v>
+        <v>75.038149194470606</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -21070,16 +21070,16 @@
         <v>737</v>
       </c>
       <c r="Y111" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="Z111" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="AA111">
-        <v>0.99591694828752353</v>
+        <v>0.98589287668661407</v>
       </c>
       <c r="AB111">
-        <v>74.855948062068691</v>
+        <v>258.6305940787426</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -21144,16 +21144,16 @@
         <v>739</v>
       </c>
       <c r="Y112" t="s">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="Z112" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="AA112">
-        <v>0.99521933495260839</v>
+        <v>0.99334528001303357</v>
       </c>
       <c r="AB112">
-        <v>87.645525868847031</v>
+        <v>122.0031997610503</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21218,16 +21218,16 @@
         <v>741</v>
       </c>
       <c r="Y113" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="Z113" t="s">
-        <v>825</v>
+        <v>862</v>
       </c>
       <c r="AA113">
-        <v>0.97158859079583204</v>
+        <v>0.99669478302557901</v>
       </c>
       <c r="AB113">
-        <v>520.87583540974583</v>
+        <v>60.595644531051299</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21292,16 +21292,16 @@
         <v>743</v>
       </c>
       <c r="Y114" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="Z114" t="s">
-        <v>789</v>
+        <v>863</v>
       </c>
       <c r="AA114">
-        <v>0.93980266520001188</v>
+        <v>0.99339186524799883</v>
       </c>
       <c r="AB114">
-        <v>1103.617804666449</v>
+        <v>121.14913712002206</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21366,16 +21366,16 @@
         <v>745</v>
       </c>
       <c r="Y115" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Z115" t="s">
         <v>864</v>
       </c>
       <c r="AA115">
-        <v>0.98205098401701585</v>
+        <v>0.99662919663728466</v>
       </c>
       <c r="AB115">
-        <v>329.06529302137608</v>
+        <v>61.798061649780351</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21440,16 +21440,16 @@
         <v>747</v>
       </c>
       <c r="Y116" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="Z116" t="s">
         <v>865</v>
       </c>
       <c r="AA116">
-        <v>0.979429443890801</v>
+        <v>0.99410803309779372</v>
       </c>
       <c r="AB116">
-        <v>377.12686200198209</v>
+        <v>108.019393207116</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21514,16 +21514,16 @@
         <v>749</v>
       </c>
       <c r="Y117" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="Z117" t="s">
         <v>866</v>
       </c>
       <c r="AA117">
-        <v>0.995907010043938</v>
+        <v>0.99649132983250632</v>
       </c>
       <c r="AB117">
-        <v>75.038149194470606</v>
+        <v>64.325619737385011</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21588,16 +21588,16 @@
         <v>751</v>
       </c>
       <c r="Y118" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="Z118" t="s">
         <v>867</v>
       </c>
       <c r="AA118">
-        <v>0.98589287668661407</v>
+        <v>0.99460824242158252</v>
       </c>
       <c r="AB118">
-        <v>258.6305940787426</v>
+        <v>98.848888937653527</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21662,16 +21662,16 @@
         <v>753</v>
       </c>
       <c r="Y119" t="s">
-        <v>471</v>
+        <v>520</v>
       </c>
       <c r="Z119" t="s">
         <v>868</v>
       </c>
       <c r="AA119">
-        <v>0.99334528001303357</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB119">
-        <v>122.0031997610503</v>
+        <v>54.23617409891024</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21736,16 +21736,16 @@
         <v>755</v>
       </c>
       <c r="Y120" t="s">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="Z120" t="s">
         <v>869</v>
       </c>
       <c r="AA120">
-        <v>0.99669478302557901</v>
+        <v>0.99764423102316024</v>
       </c>
       <c r="AB120">
-        <v>60.595644531051299</v>
+        <v>43.189097908729714</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21810,16 +21810,16 @@
         <v>757</v>
       </c>
       <c r="Y121" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="Z121" t="s">
         <v>870</v>
       </c>
       <c r="AA121">
-        <v>0.99339186524799883</v>
+        <v>0.99729259940965764</v>
       </c>
       <c r="AB121">
-        <v>121.14913712002206</v>
+        <v>49.635677489608995</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21884,16 +21884,16 @@
         <v>759</v>
       </c>
       <c r="Y122" t="s">
-        <v>430</v>
+        <v>488</v>
       </c>
       <c r="Z122" t="s">
         <v>871</v>
       </c>
       <c r="AA122">
-        <v>0.99662919663728466</v>
+        <v>0.99299389066598753</v>
       </c>
       <c r="AB122">
-        <v>61.798061649780351</v>
+        <v>128.44533779022913</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21958,16 +21958,16 @@
         <v>761</v>
       </c>
       <c r="Y123" t="s">
-        <v>486</v>
+        <v>530</v>
       </c>
       <c r="Z123" t="s">
         <v>872</v>
       </c>
       <c r="AA123">
-        <v>0.99410803309779372</v>
+        <v>0.99536976316228409</v>
       </c>
       <c r="AB123">
-        <v>108.019393207116</v>
+        <v>84.887675358125122</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -22032,16 +22032,16 @@
         <v>763</v>
       </c>
       <c r="Y124" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="Z124" t="s">
         <v>873</v>
       </c>
       <c r="AA124">
-        <v>0.99649132983250632</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB124">
-        <v>64.325619737385011</v>
+        <v>82.539922240185263</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -22106,16 +22106,16 @@
         <v>765</v>
       </c>
       <c r="Y125" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="Z125" t="s">
         <v>874</v>
       </c>
       <c r="AA125">
-        <v>0.99460824242158252</v>
+        <v>0.99657689065782151</v>
       </c>
       <c r="AB125">
-        <v>98.848888937653527</v>
+        <v>62.757004606605378</v>
       </c>
     </row>
   </sheetData>
@@ -22124,7 +22124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB0F6FC-1E34-486F-9F7B-E4902BACDA3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC4F0832-6924-4CDD-B564-7FC3890C4CCD}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22236,7 +22236,7 @@
         <v>1268</v>
       </c>
       <c r="K11" t="s">
-        <v>1074</v>
+        <v>1015</v>
       </c>
       <c r="L11">
         <v>2.2424312957699906</v>
@@ -22269,7 +22269,7 @@
         <v>1406</v>
       </c>
       <c r="X11" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="Y11">
         <v>40.677</v>
@@ -22304,7 +22304,7 @@
         <v>1270</v>
       </c>
       <c r="K12" t="s">
-        <v>1111</v>
+        <v>1028</v>
       </c>
       <c r="L12">
         <v>0.39959553615654331</v>
@@ -22337,7 +22337,7 @@
         <v>1408</v>
       </c>
       <c r="X12" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="Y12">
         <v>55.56</v>
@@ -22372,7 +22372,7 @@
         <v>1272</v>
       </c>
       <c r="K13" t="s">
-        <v>1033</v>
+        <v>1075</v>
       </c>
       <c r="L13">
         <v>1.6391158162780219</v>
@@ -22405,7 +22405,7 @@
         <v>1410</v>
       </c>
       <c r="X13" t="s">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="Y13">
         <v>60.140999999999998</v>
@@ -22440,7 +22440,7 @@
         <v>1274</v>
       </c>
       <c r="K14" t="s">
-        <v>1127</v>
+        <v>1137</v>
       </c>
       <c r="L14">
         <v>0.35051099632091098</v>
@@ -22473,7 +22473,7 @@
         <v>1412</v>
       </c>
       <c r="X14" t="s">
-        <v>1260</v>
+        <v>1229</v>
       </c>
       <c r="Y14">
         <v>41.4405</v>
@@ -22508,7 +22508,7 @@
         <v>1276</v>
       </c>
       <c r="K15" t="s">
-        <v>1138</v>
+        <v>1063</v>
       </c>
       <c r="L15">
         <v>5.5005105319204732</v>
@@ -22541,7 +22541,7 @@
         <v>1414</v>
       </c>
       <c r="X15" t="s">
-        <v>1217</v>
+        <v>1262</v>
       </c>
       <c r="Y15">
         <v>43.819499999999998</v>
@@ -22576,7 +22576,7 @@
         <v>1278</v>
       </c>
       <c r="K16" t="s">
-        <v>1078</v>
+        <v>1065</v>
       </c>
       <c r="L16">
         <v>0.5190595734350465</v>
@@ -22609,7 +22609,7 @@
         <v>1416</v>
       </c>
       <c r="X16" t="s">
-        <v>1262</v>
+        <v>1231</v>
       </c>
       <c r="Y16">
         <v>27.66375</v>
@@ -22644,7 +22644,7 @@
         <v>1280</v>
       </c>
       <c r="K17" t="s">
-        <v>1052</v>
+        <v>1144</v>
       </c>
       <c r="L17">
         <v>0.56392905291701501</v>
@@ -22677,7 +22677,7 @@
         <v>1418</v>
       </c>
       <c r="X17" t="s">
-        <v>1239</v>
+        <v>1259</v>
       </c>
       <c r="Y17">
         <v>21.581250000000001</v>
@@ -22712,7 +22712,7 @@
         <v>1282</v>
       </c>
       <c r="K18" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="L18">
         <v>5.5304311809856452</v>
@@ -22745,7 +22745,7 @@
         <v>1420</v>
       </c>
       <c r="X18" t="s">
-        <v>1225</v>
+        <v>1253</v>
       </c>
       <c r="Y18">
         <v>25.759499999999999</v>
@@ -22780,7 +22780,7 @@
         <v>1284</v>
       </c>
       <c r="K19" t="s">
-        <v>1121</v>
+        <v>1131</v>
       </c>
       <c r="L19">
         <v>3.7614311754340659</v>
@@ -22813,7 +22813,7 @@
         <v>1422</v>
       </c>
       <c r="X19" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="Y19">
         <v>60.146250000000002</v>
@@ -22848,7 +22848,7 @@
         <v>1286</v>
       </c>
       <c r="K20" t="s">
-        <v>1140</v>
+        <v>1097</v>
       </c>
       <c r="L20">
         <v>1.9040172385939969</v>
@@ -22881,7 +22881,7 @@
         <v>1424</v>
       </c>
       <c r="X20" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="Y20">
         <v>44.461500000000001</v>
@@ -22916,7 +22916,7 @@
         <v>1288</v>
       </c>
       <c r="K21" t="s">
-        <v>1130</v>
+        <v>1055</v>
       </c>
       <c r="L21">
         <v>1.2379257959384389</v>
@@ -22949,7 +22949,7 @@
         <v>1426</v>
       </c>
       <c r="X21" t="s">
-        <v>1253</v>
+        <v>1241</v>
       </c>
       <c r="Y21">
         <v>19.922999999999998</v>
@@ -22984,7 +22984,7 @@
         <v>1290</v>
       </c>
       <c r="K22" t="s">
-        <v>1123</v>
+        <v>1133</v>
       </c>
       <c r="L22">
         <v>3.8533296682560416</v>
@@ -23017,7 +23017,7 @@
         <v>1428</v>
       </c>
       <c r="X22" t="s">
-        <v>1264</v>
+        <v>1233</v>
       </c>
       <c r="Y22">
         <v>29.15625</v>
@@ -23052,7 +23052,7 @@
         <v>1292</v>
       </c>
       <c r="K23" t="s">
-        <v>1039</v>
+        <v>1121</v>
       </c>
       <c r="L23">
         <v>11.884376191048085</v>
@@ -23085,7 +23085,7 @@
         <v>1430</v>
       </c>
       <c r="X23" t="s">
-        <v>1212</v>
+        <v>1257</v>
       </c>
       <c r="Y23">
         <v>18.1815</v>
@@ -23120,7 +23120,7 @@
         <v>1294</v>
       </c>
       <c r="K24" t="s">
-        <v>1104</v>
+        <v>1021</v>
       </c>
       <c r="L24">
         <v>10.042628949933583</v>
@@ -23153,7 +23153,7 @@
         <v>1432</v>
       </c>
       <c r="X24" t="s">
-        <v>1227</v>
+        <v>1255</v>
       </c>
       <c r="Y24">
         <v>60.111750000000001</v>
@@ -23188,7 +23188,7 @@
         <v>1296</v>
       </c>
       <c r="K25" t="s">
-        <v>1015</v>
+        <v>1048</v>
       </c>
       <c r="L25">
         <v>11.221871479411517</v>
@@ -23221,7 +23221,7 @@
         <v>1434</v>
       </c>
       <c r="X25" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="Y25">
         <v>56.094749999999998</v>
@@ -23256,7 +23256,7 @@
         <v>1298</v>
       </c>
       <c r="K26" t="s">
-        <v>1023</v>
+        <v>1081</v>
       </c>
       <c r="L26">
         <v>7.6463375414566821</v>
@@ -23289,7 +23289,7 @@
         <v>1436</v>
       </c>
       <c r="X26" t="s">
-        <v>1256</v>
+        <v>1227</v>
       </c>
       <c r="Y26">
         <v>43.631999999999998</v>
@@ -23324,7 +23324,7 @@
         <v>1300</v>
       </c>
       <c r="K27" t="s">
-        <v>1056</v>
+        <v>1105</v>
       </c>
       <c r="L27">
         <v>49.086666974214374</v>
@@ -23357,7 +23357,7 @@
         <v>1438</v>
       </c>
       <c r="X27" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="Y27">
         <v>3.4402499999999998</v>
@@ -23392,7 +23392,7 @@
         <v>1302</v>
       </c>
       <c r="K28" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="L28">
         <v>4.7713910333636482</v>
@@ -23425,7 +23425,7 @@
         <v>1440</v>
       </c>
       <c r="X28" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="Y28">
         <v>13.389749999999999</v>
@@ -23460,7 +23460,7 @@
         <v>1304</v>
       </c>
       <c r="K29" t="s">
-        <v>1047</v>
+        <v>1139</v>
       </c>
       <c r="L29">
         <v>10.563746678268352</v>
@@ -23493,7 +23493,7 @@
         <v>1442</v>
       </c>
       <c r="X29" t="s">
-        <v>1255</v>
+        <v>1243</v>
       </c>
       <c r="Y29">
         <v>6.9757499999999997</v>
@@ -23528,7 +23528,7 @@
         <v>1306</v>
       </c>
       <c r="K30" t="s">
-        <v>1021</v>
+        <v>1044</v>
       </c>
       <c r="L30">
         <v>9.1089937926910061</v>
@@ -23561,7 +23561,7 @@
         <v>1444</v>
       </c>
       <c r="X30" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="Y30">
         <v>38.154000000000003</v>
@@ -23596,7 +23596,7 @@
         <v>1308</v>
       </c>
       <c r="K31" t="s">
-        <v>1102</v>
+        <v>1019</v>
       </c>
       <c r="L31">
         <v>9.5926767059877864</v>
@@ -23629,7 +23629,7 @@
         <v>1446</v>
       </c>
       <c r="X31" t="s">
-        <v>1223</v>
+        <v>1237</v>
       </c>
       <c r="Y31">
         <v>43.858499999999999</v>
@@ -23664,7 +23664,7 @@
         <v>1310</v>
       </c>
       <c r="K32" t="s">
-        <v>1013</v>
+        <v>1046</v>
       </c>
       <c r="L32">
         <v>7.4816578037471135</v>
@@ -23697,7 +23697,7 @@
         <v>1448</v>
       </c>
       <c r="X32" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="Y32">
         <v>26.765999999999998</v>
@@ -23732,7 +23732,7 @@
         <v>1312</v>
       </c>
       <c r="K33" t="s">
-        <v>1050</v>
+        <v>1142</v>
       </c>
       <c r="L33">
         <v>0.42921323534771355</v>
@@ -23765,7 +23765,7 @@
         <v>1450</v>
       </c>
       <c r="X33" t="s">
-        <v>1221</v>
+        <v>1266</v>
       </c>
       <c r="Y33">
         <v>35.325000000000003</v>
@@ -23800,7 +23800,7 @@
         <v>1314</v>
       </c>
       <c r="K34" t="s">
-        <v>1066</v>
+        <v>1115</v>
       </c>
       <c r="L34">
         <v>2.5791573409383797</v>
@@ -23833,7 +23833,7 @@
         <v>1452</v>
       </c>
       <c r="X34" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="Y34">
         <v>38.589750000000002</v>
@@ -23868,7 +23868,7 @@
         <v>1316</v>
       </c>
       <c r="K35" t="s">
-        <v>1086</v>
+        <v>1036</v>
       </c>
       <c r="L35">
         <v>4.5447948235000659</v>
@@ -23936,7 +23936,7 @@
         <v>1318</v>
       </c>
       <c r="K36" t="s">
-        <v>1049</v>
+        <v>1141</v>
       </c>
       <c r="L36">
         <v>2.5512484974479288</v>
@@ -23969,7 +23969,7 @@
         <v>1456</v>
       </c>
       <c r="X36" t="s">
-        <v>1235</v>
+        <v>1219</v>
       </c>
       <c r="Y36">
         <v>2.6655000000000002</v>
@@ -24004,7 +24004,7 @@
         <v>1320</v>
       </c>
       <c r="K37" t="s">
-        <v>1106</v>
+        <v>1023</v>
       </c>
       <c r="L37">
         <v>2.1398112854340741</v>
@@ -24037,7 +24037,7 @@
         <v>1458</v>
       </c>
       <c r="X37" t="s">
-        <v>1266</v>
+        <v>1235</v>
       </c>
       <c r="Y37">
         <v>11.651999999999999</v>
@@ -24072,7 +24072,7 @@
         <v>1322</v>
       </c>
       <c r="K38" t="s">
-        <v>1107</v>
+        <v>1024</v>
       </c>
       <c r="L38">
         <v>0.49924773862749328</v>
@@ -24105,7 +24105,7 @@
         <v>1460</v>
       </c>
       <c r="X38" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="Y38">
         <v>10.619249999999999</v>
@@ -24140,7 +24140,7 @@
         <v>1324</v>
       </c>
       <c r="K39" t="s">
-        <v>1072</v>
+        <v>1013</v>
       </c>
       <c r="L39">
         <v>0.38370105604163202</v>
@@ -24173,7 +24173,7 @@
         <v>1462</v>
       </c>
       <c r="X39" t="s">
-        <v>1219</v>
+        <v>1264</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24208,7 +24208,7 @@
         <v>1326</v>
       </c>
       <c r="K40" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="L40">
         <v>0.90968527564022184</v>
@@ -24241,7 +24241,7 @@
         <v>1464</v>
       </c>
       <c r="X40" t="s">
-        <v>1237</v>
+        <v>1221</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24276,7 +24276,7 @@
         <v>1328</v>
       </c>
       <c r="K41" t="s">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="L41">
         <v>0.29505146981926272</v>
@@ -24309,7 +24309,7 @@
         <v>1466</v>
       </c>
       <c r="X41" t="s">
-        <v>1249</v>
+        <v>1215</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24344,7 +24344,7 @@
         <v>1330</v>
       </c>
       <c r="K42" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="L42">
         <v>0.28737649325389003</v>
@@ -24379,7 +24379,7 @@
         <v>1332</v>
       </c>
       <c r="K43" t="s">
-        <v>1060</v>
+        <v>1109</v>
       </c>
       <c r="L43">
         <v>2.6969209295416086</v>
@@ -24414,7 +24414,7 @@
         <v>1334</v>
       </c>
       <c r="K44" t="s">
-        <v>1031</v>
+        <v>1073</v>
       </c>
       <c r="L44">
         <v>2.107226923411055</v>
@@ -24449,7 +24449,7 @@
         <v>1336</v>
       </c>
       <c r="K45" t="s">
-        <v>1068</v>
+        <v>1117</v>
       </c>
       <c r="L45">
         <v>30.801184751503769</v>
@@ -24484,7 +24484,7 @@
         <v>1338</v>
       </c>
       <c r="K46" t="s">
-        <v>1037</v>
+        <v>1079</v>
       </c>
       <c r="L46">
         <v>1.4999429400795936</v>
@@ -24519,7 +24519,7 @@
         <v>1340</v>
       </c>
       <c r="K47" t="s">
-        <v>1027</v>
+        <v>1085</v>
       </c>
       <c r="L47">
         <v>48.163447907404631</v>
@@ -24554,7 +24554,7 @@
         <v>1342</v>
       </c>
       <c r="K48" t="s">
-        <v>1043</v>
+        <v>1125</v>
       </c>
       <c r="L48">
         <v>6.2631430584646317</v>
@@ -24589,7 +24589,7 @@
         <v>1344</v>
       </c>
       <c r="K49" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="L49">
         <v>10.805661861658292</v>
@@ -24624,7 +24624,7 @@
         <v>1346</v>
       </c>
       <c r="K50" t="s">
-        <v>1029</v>
+        <v>1087</v>
       </c>
       <c r="L50">
         <v>5.3278771181664615</v>
@@ -24659,7 +24659,7 @@
         <v>1348</v>
       </c>
       <c r="K51" t="s">
-        <v>1076</v>
+        <v>1017</v>
       </c>
       <c r="L51">
         <v>21.113356105805089</v>
@@ -24694,7 +24694,7 @@
         <v>1350</v>
       </c>
       <c r="K52" t="s">
-        <v>1058</v>
+        <v>1107</v>
       </c>
       <c r="L52">
         <v>2.3372365278937242</v>
@@ -24729,7 +24729,7 @@
         <v>1352</v>
       </c>
       <c r="K53" t="s">
-        <v>1113</v>
+        <v>1030</v>
       </c>
       <c r="L53">
         <v>4.2648673086521249</v>
@@ -24764,7 +24764,7 @@
         <v>1354</v>
       </c>
       <c r="K54" t="s">
-        <v>1041</v>
+        <v>1123</v>
       </c>
       <c r="L54">
         <v>2.8571480649629004</v>
@@ -24799,7 +24799,7 @@
         <v>1356</v>
       </c>
       <c r="K55" t="s">
-        <v>1084</v>
+        <v>1071</v>
       </c>
       <c r="L55">
         <v>31.544159267579381</v>
@@ -24834,7 +24834,7 @@
         <v>1358</v>
       </c>
       <c r="K56" t="s">
-        <v>1092</v>
+        <v>1042</v>
       </c>
       <c r="L56">
         <v>15.478330347836801</v>
@@ -24869,7 +24869,7 @@
         <v>1360</v>
       </c>
       <c r="K57" t="s">
-        <v>1117</v>
+        <v>1034</v>
       </c>
       <c r="L57">
         <v>18.772499167970881</v>
@@ -24904,7 +24904,7 @@
         <v>1362</v>
       </c>
       <c r="K58" t="s">
-        <v>1070</v>
+        <v>1119</v>
       </c>
       <c r="L58">
         <v>18.904558868579112</v>
@@ -24939,7 +24939,7 @@
         <v>1364</v>
       </c>
       <c r="K59" t="s">
-        <v>1129</v>
+        <v>1054</v>
       </c>
       <c r="L59">
         <v>14.176079891703212</v>
@@ -24974,7 +24974,7 @@
         <v>1366</v>
       </c>
       <c r="K60" t="s">
-        <v>1146</v>
+        <v>1103</v>
       </c>
       <c r="L60">
         <v>0.80973624203950822</v>
@@ -25009,7 +25009,7 @@
         <v>1368</v>
       </c>
       <c r="K61" t="s">
-        <v>1064</v>
+        <v>1113</v>
       </c>
       <c r="L61">
         <v>3.2067222321080848</v>
@@ -25044,7 +25044,7 @@
         <v>1370</v>
       </c>
       <c r="K62" t="s">
-        <v>1115</v>
+        <v>1032</v>
       </c>
       <c r="L62">
         <v>0.66271354737797783</v>
@@ -25079,7 +25079,7 @@
         <v>1372</v>
       </c>
       <c r="K63" t="s">
-        <v>1045</v>
+        <v>1127</v>
       </c>
       <c r="L63">
         <v>1.8183767824138508</v>
@@ -25114,7 +25114,7 @@
         <v>1374</v>
       </c>
       <c r="K64" t="s">
-        <v>1142</v>
+        <v>1099</v>
       </c>
       <c r="L64">
         <v>0.24904319237866104</v>
@@ -25149,7 +25149,7 @@
         <v>1376</v>
       </c>
       <c r="K65" t="s">
-        <v>1062</v>
+        <v>1111</v>
       </c>
       <c r="L65">
         <v>8.2047875916663029E-2</v>
@@ -25184,7 +25184,7 @@
         <v>1378</v>
       </c>
       <c r="K66" t="s">
-        <v>1134</v>
+        <v>1059</v>
       </c>
       <c r="L66">
         <v>11.861012832193515</v>
@@ -25219,7 +25219,7 @@
         <v>1380</v>
       </c>
       <c r="K67" t="s">
-        <v>1025</v>
+        <v>1083</v>
       </c>
       <c r="L67">
         <v>0.74143826937354373</v>
@@ -25254,7 +25254,7 @@
         <v>1382</v>
       </c>
       <c r="K68" t="s">
-        <v>1080</v>
+        <v>1067</v>
       </c>
       <c r="L68">
         <v>5.5201095579611916</v>
@@ -25289,7 +25289,7 @@
         <v>1384</v>
       </c>
       <c r="K69" t="s">
-        <v>1136</v>
+        <v>1061</v>
       </c>
       <c r="L69">
         <v>6.8285247240880329</v>
@@ -25324,7 +25324,7 @@
         <v>1386</v>
       </c>
       <c r="K70" t="s">
-        <v>1088</v>
+        <v>1038</v>
       </c>
       <c r="L70">
         <v>14.065249575687433</v>
@@ -25359,7 +25359,7 @@
         <v>1388</v>
       </c>
       <c r="K71" t="s">
-        <v>1035</v>
+        <v>1077</v>
       </c>
       <c r="L71">
         <v>9.3799037679336319</v>
@@ -25394,7 +25394,7 @@
         <v>1390</v>
       </c>
       <c r="K72" t="s">
-        <v>1054</v>
+        <v>1146</v>
       </c>
       <c r="L72">
         <v>42.785830383290261</v>
@@ -25429,7 +25429,7 @@
         <v>1392</v>
       </c>
       <c r="K73" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="L73">
         <v>7.8693705940085819</v>
@@ -25464,7 +25464,7 @@
         <v>1394</v>
       </c>
       <c r="K74" t="s">
-        <v>1082</v>
+        <v>1069</v>
       </c>
       <c r="L74">
         <v>19.787589902082505</v>
@@ -25499,7 +25499,7 @@
         <v>1396</v>
       </c>
       <c r="K75" t="s">
-        <v>1090</v>
+        <v>1040</v>
       </c>
       <c r="L75">
         <v>18.646888343565813</v>
@@ -25534,7 +25534,7 @@
         <v>1398</v>
       </c>
       <c r="K76" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="L76">
         <v>6.7551756478058005</v>
@@ -25569,7 +25569,7 @@
         <v>1400</v>
       </c>
       <c r="K77" t="s">
-        <v>1109</v>
+        <v>1026</v>
       </c>
       <c r="L77">
         <v>3.5275797249830152</v>
@@ -25604,7 +25604,7 @@
         <v>1402</v>
       </c>
       <c r="K78" t="s">
-        <v>1144</v>
+        <v>1101</v>
       </c>
       <c r="L78">
         <v>0.89663971235601181</v>
@@ -25639,7 +25639,7 @@
         <v>1404</v>
       </c>
       <c r="K79" t="s">
-        <v>1132</v>
+        <v>1057</v>
       </c>
       <c r="L79">
         <v>5.9305458091691294</v>
@@ -25654,7 +25654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC5D12F-748F-43BC-9EB6-D19F3BD2D487}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D9E0F5A-65AA-430A-AF4C-9B006DA8A0AA}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -27123,7 +27123,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836D0950-7765-4CC8-A3FB-95297D345327}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FF17A3A-5174-423B-A3DD-2CEAEF655FBA}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D11160EB-1178-49DC-AADB-B113DA12DCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8103245A-7D7C-45E3-AD29-A8CE92BEEE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1705,24 +1705,612 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_100</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 100</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_114</t>
   </si>
   <si>
@@ -1771,540 +2359,6 @@
     <t>connecting solar to buses in cluster 34</t>
   </si>
   <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_072</t>
   </si>
   <si>
@@ -2347,72 +2401,288 @@
     <t>connecting solar to buses in cluster 51</t>
   </si>
   <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_BR347-500,e_BR290-500,e_BR283-500,e_BR371-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_BR515-500,e_w302931307-440,e_BR544-500,e_BR632-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_r6844204-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR141-500,e_BR61-500,e_BR125-500</t>
+  </si>
+  <si>
+    <t>e_BR437-500,e_BR373-500,e_w953014442-500,e_BR309-500,e_BR220-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
     <t>e_w168904844-230,e_w168664395-500,e_BR626-440</t>
   </si>
   <si>
     <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
   </si>
   <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230,e_BR283-500,e_BR290-500</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR41-500,e_BR37-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>e_BR487-500,e_BR446-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR294-500,e_BR236-500,e_BR296-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR305-230,e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR363-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR293-500,e_BR282-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR657-440,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_w271191830-500,e_BR310-500,e_BR300-500,e_BR171-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR587-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w206109551-500,e_BR662-440,e_BR732-500,e_BR673-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR626-440,e_w302901044-440,e_BR673-440,e_BR624-440,e_BR676-440,e_BR676-500,e_BR632-440,e_w174017677-440,e_BR646-440,e_BR663-440</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR483-500,e_BR571-500,e_BR558-500,e_BR535-500,e_w954122148-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR371-500,e_BR353-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w225181494-500,e_w172071437-440,e_BR666-440,e_BR764-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR499-500,e_BR462-500,e_BR439-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_w201470687-500,e_BR273-230,e_BR270-230,e_BR315-230,e_BR327-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR283-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR459-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR878-500,e_w188465343-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR515-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR535-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_w286006777-440</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR221-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR209-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR80-500,e_BR148-500,e_BR120-500,e_BR187-500,e_BR114-500,e_BR164-500,e_BR142-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w453724535-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR525-500,e_BR500-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_BR387-500,e_BR354-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
     <t>e_BR270-230,e_BR342-230,e_BR327-230,e_BR283-500</t>
   </si>
   <si>
@@ -2437,249 +2707,6 @@
     <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR337-500,e_BR264-500</t>
   </si>
   <si>
-    <t>e_BR347-500,e_BR290-500,e_BR283-500,e_BR371-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_BR515-500,e_w302931307-440,e_BR544-500,e_BR632-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_r6844204-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR141-500,e_BR61-500,e_BR125-500</t>
-  </si>
-  <si>
-    <t>e_BR437-500,e_BR373-500,e_w953014442-500,e_BR309-500,e_BR220-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_w286006777-440</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR221-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR209-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR80-500,e_BR148-500,e_BR120-500,e_BR187-500,e_BR114-500,e_BR164-500,e_BR142-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR305-230,e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR483-500,e_BR571-500,e_BR558-500,e_BR535-500,e_w954122148-500</t>
-  </si>
-  <si>
-    <t>e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR363-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR293-500,e_BR282-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR371-500,e_BR353-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w225181494-500,e_w172071437-440,e_BR666-440,e_BR764-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR499-500,e_BR462-500,e_BR439-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230,e_BR283-500,e_BR290-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR41-500,e_BR37-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR878-500,e_w188465343-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR515-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR535-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>e_BR487-500,e_BR446-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR294-500,e_BR236-500,e_BR296-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_w201470687-500,e_BR273-230,e_BR270-230,e_BR315-230,e_BR327-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR283-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR459-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR657-440,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_w271191830-500,e_BR310-500,e_BR300-500,e_BR171-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR587-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w206109551-500,e_BR662-440,e_BR732-500,e_BR673-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR626-440,e_w302901044-440,e_BR673-440,e_BR624-440,e_BR676-440,e_BR676-500,e_BR632-440,e_w174017677-440,e_BR646-440,e_BR663-440</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
     <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
   </si>
   <si>
@@ -2698,31 +2725,250 @@
     <t>e_BR282-500,e_BR209-500,e_BR302-500,e_BR190-500,e_BR340-500,e_w603494578-500,e_BR194-500,e_BR292-500,e_BR204-500,e_BR187-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
   </si>
   <si>
-    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w453724535-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR525-500,e_BR500-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
-  </si>
-  <si>
-    <t>e_BR387-500,e_BR354-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
   </si>
   <si>
     <t>distr_wonelc_won_004</t>
@@ -2803,34 +3049,16 @@
     <t>connecting wind onshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
   </si>
   <si>
     <t>distr_wonelc_won_026</t>
@@ -2851,6 +3079,36 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_031</t>
   </si>
   <si>
@@ -2881,262 +3139,247 @@
     <t>connecting wind onshore to buses in cluster 50</t>
   </si>
   <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR344-500,e_BR340-500,e_BR302-500,e_w603494578-500,e_BR292-500,e_w532354815-500,e_BR204-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
   </si>
   <si>
     <t>elc_won_004</t>
@@ -3214,34 +3457,16 @@
     <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR302-500</t>
   </si>
   <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
   </si>
   <si>
     <t>elc_won_026</t>
@@ -3262,6 +3487,36 @@
     <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
   </si>
   <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
     <t>elc_won_031</t>
   </si>
   <si>
@@ -3292,261 +3547,6 @@
     <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
   </si>
   <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR344-500,e_BR340-500,e_BR302-500,e_w603494578-500,e_BR292-500,e_w532354815-500,e_BR204-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_won_069</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_028</t>
   </si>
   <si>
@@ -3559,6 +3559,72 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_003</t>
   </si>
   <si>
@@ -3577,6 +3643,78 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
@@ -3589,150 +3727,12 @@
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_017</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
     <t>elc_wof_028</t>
   </si>
   <si>
@@ -3745,6 +3745,66 @@
     <t>e_BR652-500,e_BR644-500</t>
   </si>
   <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR764-440,e_BR758-440</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
     <t>elc_wof_003</t>
   </si>
   <si>
@@ -3763,142 +3823,82 @@
     <t>e_BR851-500,e_BR764-440,e_BR758-440,e_BR755-500</t>
   </si>
   <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_BR1014-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
     <t>elc_wof_004</t>
   </si>
   <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
     <t>elc_wof_024</t>
   </si>
   <si>
     <t>e_BR15-500</t>
   </si>
   <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_BR992-525</t>
-  </si>
-  <si>
     <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_BR1014-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9646,7 +9646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BFFBBFF-8FBA-4127-9EC0-457B2CF2AD26}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B22B921C-7F59-49A7-BEA3-76749909B382}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9884,16 +9884,16 @@
         <v>525</v>
       </c>
       <c r="Y11" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="Z11" t="s">
         <v>759</v>
       </c>
       <c r="AA11">
-        <v>0.98578060748142671</v>
+        <v>0.99356258288761645</v>
       </c>
       <c r="AB11">
-        <v>260.68886284051109</v>
+        <v>118.01931372703181</v>
       </c>
       <c r="AD11" t="s">
         <v>524</v>
@@ -9926,10 +9926,10 @@
         <v>1004</v>
       </c>
       <c r="AO11">
-        <v>0.98134982200735632</v>
+        <v>0.99664818772595598</v>
       </c>
       <c r="AP11">
-        <v>341.91992986513412</v>
+        <v>61.449891690807455</v>
       </c>
       <c r="AR11" t="s">
         <v>524</v>
@@ -10030,16 +10030,16 @@
         <v>529</v>
       </c>
       <c r="Y12" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="Z12" t="s">
         <v>760</v>
       </c>
       <c r="AA12">
-        <v>0.9946911823559148</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB12">
-        <v>97.32832347489618</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD12" t="s">
         <v>524</v>
@@ -10069,13 +10069,13 @@
         <v>1005</v>
       </c>
       <c r="AN12" t="s">
-        <v>806</v>
+        <v>1006</v>
       </c>
       <c r="AO12">
-        <v>0.98674094240398891</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP12">
-        <v>243.0827225935364</v>
+        <v>105.47547991621673</v>
       </c>
       <c r="AR12" t="s">
         <v>524</v>
@@ -10176,16 +10176,16 @@
         <v>531</v>
       </c>
       <c r="Y13" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="Z13" t="s">
         <v>761</v>
       </c>
       <c r="AA13">
-        <v>0.9866640001482827</v>
+        <v>0.99652977687804423</v>
       </c>
       <c r="AB13">
-        <v>244.49333061481801</v>
+        <v>63.62075723585545</v>
       </c>
       <c r="AD13" t="s">
         <v>524</v>
@@ -10212,16 +10212,16 @@
         <v>869</v>
       </c>
       <c r="AM13" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="AN13" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="AO13">
-        <v>0.9959346869215373</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP13">
-        <v>74.530739771815789</v>
+        <v>43.581147571379539</v>
       </c>
       <c r="AR13" t="s">
         <v>524</v>
@@ -10254,10 +10254,10 @@
         <v>1206</v>
       </c>
       <c r="BC13">
-        <v>0.98935994634927737</v>
+        <v>0.99120104792145036</v>
       </c>
       <c r="BD13">
-        <v>195.06765026324791</v>
+        <v>161.31412144007655</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10322,16 +10322,16 @@
         <v>533</v>
       </c>
       <c r="Y14" t="s">
-        <v>480</v>
+        <v>446</v>
       </c>
       <c r="Z14" t="s">
         <v>762</v>
       </c>
       <c r="AA14">
-        <v>0.97166110802369898</v>
+        <v>0.99356282906984039</v>
       </c>
       <c r="AB14">
-        <v>519.54635289885152</v>
+        <v>118.01480038625972</v>
       </c>
       <c r="AD14" t="s">
         <v>524</v>
@@ -10358,16 +10358,16 @@
         <v>871</v>
       </c>
       <c r="AM14" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="AN14" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="AO14">
-        <v>0.9976320377495026</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP14">
-        <v>43.412641259119624</v>
+        <v>64.433996023258757</v>
       </c>
       <c r="AR14" t="s">
         <v>524</v>
@@ -10400,10 +10400,10 @@
         <v>1208</v>
       </c>
       <c r="BC14">
-        <v>0.95713629889852414</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD14">
-        <v>785.83452019372396</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10468,16 +10468,16 @@
         <v>535</v>
       </c>
       <c r="Y15" t="s">
-        <v>510</v>
+        <v>442</v>
       </c>
       <c r="Z15" t="s">
         <v>763</v>
       </c>
       <c r="AA15">
-        <v>0.99353270322428533</v>
+        <v>0.99482380895087164</v>
       </c>
       <c r="AB15">
-        <v>118.56710755476936</v>
+        <v>94.896835900686696</v>
       </c>
       <c r="AD15" t="s">
         <v>524</v>
@@ -10504,16 +10504,16 @@
         <v>873</v>
       </c>
       <c r="AM15" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="AN15" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="AO15">
-        <v>0.99433447571906541</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP15">
-        <v>103.86794515046822</v>
+        <v>101.57889622275951</v>
       </c>
       <c r="AR15" t="s">
         <v>524</v>
@@ -10546,10 +10546,10 @@
         <v>1210</v>
       </c>
       <c r="BC15">
-        <v>0.98529820518310829</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD15">
-        <v>269.5329049763485</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10614,16 +10614,16 @@
         <v>537</v>
       </c>
       <c r="Y16" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="Z16" t="s">
         <v>764</v>
       </c>
       <c r="AA16">
-        <v>0.99729259940965764</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB16">
-        <v>49.635677489608995</v>
+        <v>121.27899510281891</v>
       </c>
       <c r="AD16" t="s">
         <v>524</v>
@@ -10650,16 +10650,16 @@
         <v>875</v>
       </c>
       <c r="AM16" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="AN16" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="AO16">
-        <v>0.99688290256322298</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP16">
-        <v>57.146786340912868</v>
+        <v>546.30069964051177</v>
       </c>
       <c r="AR16" t="s">
         <v>524</v>
@@ -10692,10 +10692,10 @@
         <v>1212</v>
       </c>
       <c r="BC16">
-        <v>0.99357050471442732</v>
+        <v>0.99542890407822671</v>
       </c>
       <c r="BD16">
-        <v>117.87408023549864</v>
+        <v>83.803425232511387</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10760,16 +10760,16 @@
         <v>539</v>
       </c>
       <c r="Y17" t="s">
-        <v>436</v>
+        <v>507</v>
       </c>
       <c r="Z17" t="s">
         <v>765</v>
       </c>
       <c r="AA17">
-        <v>0.99591694828752353</v>
+        <v>0.98578060748142671</v>
       </c>
       <c r="AB17">
-        <v>74.855948062068691</v>
+        <v>260.68886284051109</v>
       </c>
       <c r="AD17" t="s">
         <v>524</v>
@@ -10796,16 +10796,16 @@
         <v>877</v>
       </c>
       <c r="AM17" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="AN17" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="AO17">
-        <v>0.99724271030877243</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP17">
-        <v>50.550311005838999</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR17" t="s">
         <v>524</v>
@@ -10838,10 +10838,10 @@
         <v>1214</v>
       </c>
       <c r="BC17">
-        <v>0.9807271101910352</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD17">
-        <v>353.33631316435549</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -10906,16 +10906,16 @@
         <v>541</v>
       </c>
       <c r="Y18" t="s">
-        <v>448</v>
+        <v>408</v>
       </c>
       <c r="Z18" t="s">
         <v>766</v>
       </c>
       <c r="AA18">
-        <v>0.99335306489036745</v>
+        <v>0.9946911823559148</v>
       </c>
       <c r="AB18">
-        <v>121.86047700993024</v>
+        <v>97.32832347489618</v>
       </c>
       <c r="AD18" t="s">
         <v>524</v>
@@ -10942,16 +10942,16 @@
         <v>879</v>
       </c>
       <c r="AM18" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="AN18" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="AO18">
-        <v>0.99473480482648013</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP18">
-        <v>96.528578181196991</v>
+        <v>85.716830221163534</v>
       </c>
       <c r="AR18" t="s">
         <v>524</v>
@@ -10981,13 +10981,13 @@
         <v>1215</v>
       </c>
       <c r="BB18" t="s">
-        <v>1216</v>
+        <v>1032</v>
       </c>
       <c r="BC18">
-        <v>0.99232494426983575</v>
+        <v>0.99119386580545066</v>
       </c>
       <c r="BD18">
-        <v>140.70935505301131</v>
+        <v>161.44579356673827</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11052,16 +11052,16 @@
         <v>543</v>
       </c>
       <c r="Y19" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="Z19" t="s">
         <v>767</v>
       </c>
       <c r="AA19">
-        <v>0.99619719802293027</v>
+        <v>0.98028549885826644</v>
       </c>
       <c r="AB19">
-        <v>69.718036246277634</v>
+        <v>361.43252093178171</v>
       </c>
       <c r="AD19" t="s">
         <v>524</v>
@@ -11088,16 +11088,16 @@
         <v>881</v>
       </c>
       <c r="AM19" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AN19" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AO19">
-        <v>0.99760255773158468</v>
+        <v>0.9964556860892605</v>
       </c>
       <c r="AP19">
-        <v>43.953108254279897</v>
+        <v>64.979088363557494</v>
       </c>
       <c r="AR19" t="s">
         <v>524</v>
@@ -11124,16 +11124,16 @@
         <v>1155</v>
       </c>
       <c r="BA19" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="BB19" t="s">
-        <v>1218</v>
+        <v>817</v>
       </c>
       <c r="BC19">
-        <v>0.99375410727160951</v>
+        <v>0.9924080998261412</v>
       </c>
       <c r="BD19">
-        <v>114.50803335382533</v>
+        <v>139.18483652074559</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11198,16 +11198,16 @@
         <v>545</v>
       </c>
       <c r="Y20" t="s">
-        <v>441</v>
+        <v>518</v>
       </c>
       <c r="Z20" t="s">
         <v>768</v>
       </c>
       <c r="AA20">
-        <v>0.99557851591679303</v>
+        <v>0.99144230757194385</v>
       </c>
       <c r="AB20">
-        <v>81.06054152546038</v>
+        <v>156.89102784769577</v>
       </c>
       <c r="AD20" t="s">
         <v>524</v>
@@ -11234,16 +11234,16 @@
         <v>883</v>
       </c>
       <c r="AM20" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AN20" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AO20">
-        <v>0.99766813121902409</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP20">
-        <v>42.750927651225993</v>
+        <v>195.31167947327185</v>
       </c>
       <c r="AR20" t="s">
         <v>524</v>
@@ -11270,16 +11270,16 @@
         <v>1157</v>
       </c>
       <c r="BA20" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="BB20" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="BC20">
-        <v>0.99538398111052984</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD20">
-        <v>84.627012973619784</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11344,16 +11344,16 @@
         <v>547</v>
       </c>
       <c r="Y21" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z21" t="s">
         <v>769</v>
       </c>
       <c r="AA21">
-        <v>0.99356258288761645</v>
+        <v>0.98863909075879119</v>
       </c>
       <c r="AB21">
-        <v>118.01931372703181</v>
+        <v>208.2833360888277</v>
       </c>
       <c r="AD21" t="s">
         <v>524</v>
@@ -11380,16 +11380,16 @@
         <v>885</v>
       </c>
       <c r="AM21" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="AN21" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AO21">
-        <v>0.99544059907537386</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP21">
-        <v>83.589016951479763</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR21" t="s">
         <v>524</v>
@@ -11416,16 +11416,16 @@
         <v>1159</v>
       </c>
       <c r="BA21" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="BB21" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="BC21">
-        <v>0.99196968319234669</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD21">
-        <v>147.22247480697732</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11490,16 +11490,16 @@
         <v>549</v>
       </c>
       <c r="Y22" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="Z22" t="s">
         <v>770</v>
       </c>
       <c r="AA22">
-        <v>0.99658191580238853</v>
+        <v>0.99503418876282002</v>
       </c>
       <c r="AB22">
-        <v>62.664876956210314</v>
+        <v>91.039872681632787</v>
       </c>
       <c r="AD22" t="s">
         <v>524</v>
@@ -11526,16 +11526,16 @@
         <v>887</v>
       </c>
       <c r="AM22" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AN22" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="AO22">
-        <v>0.99527237968252791</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP22">
-        <v>86.673039153654699</v>
+        <v>80.747827133859133</v>
       </c>
       <c r="AR22" t="s">
         <v>524</v>
@@ -11562,16 +11562,16 @@
         <v>1161</v>
       </c>
       <c r="BA22" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="BB22" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="BC22">
-        <v>0.96816761985420574</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD22">
-        <v>583.5936360062276</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11636,16 +11636,16 @@
         <v>551</v>
       </c>
       <c r="Y23" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="Z23" t="s">
         <v>771</v>
       </c>
       <c r="AA23">
-        <v>0.99652977687804423</v>
+        <v>0.99237710954614877</v>
       </c>
       <c r="AB23">
-        <v>63.62075723585545</v>
+        <v>139.75299165393855</v>
       </c>
       <c r="AD23" t="s">
         <v>524</v>
@@ -11672,16 +11672,16 @@
         <v>889</v>
       </c>
       <c r="AM23" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AN23" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="AO23">
-        <v>0.99589340828485295</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP23">
-        <v>75.287514777696231</v>
+        <v>53.069246900976879</v>
       </c>
       <c r="AR23" t="s">
         <v>524</v>
@@ -11708,16 +11708,16 @@
         <v>1163</v>
       </c>
       <c r="BA23" t="s">
+        <v>1223</v>
+      </c>
+      <c r="BB23" t="s">
         <v>1224</v>
       </c>
-      <c r="BB23" t="s">
-        <v>803</v>
-      </c>
       <c r="BC23">
-        <v>0.97821242976023937</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD23">
-        <v>399.43878772894504</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11782,16 +11782,16 @@
         <v>553</v>
       </c>
       <c r="Y24" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="Z24" t="s">
         <v>772</v>
       </c>
       <c r="AA24">
-        <v>0.99356282906984039</v>
+        <v>0.99680369125279411</v>
       </c>
       <c r="AB24">
-        <v>118.01480038625972</v>
+        <v>58.598993698774343</v>
       </c>
       <c r="AD24" t="s">
         <v>524</v>
@@ -11818,16 +11818,16 @@
         <v>891</v>
       </c>
       <c r="AM24" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="AN24" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="AO24">
-        <v>0.9964556860892605</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP24">
-        <v>64.979088363557494</v>
+        <v>57.905423216266421</v>
       </c>
       <c r="AR24" t="s">
         <v>524</v>
@@ -11860,10 +11860,10 @@
         <v>1226</v>
       </c>
       <c r="BC24">
-        <v>0.99120104792145036</v>
+        <v>0.98935994634927737</v>
       </c>
       <c r="BD24">
-        <v>161.31412144007655</v>
+        <v>195.06765026324791</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -11928,16 +11928,16 @@
         <v>555</v>
       </c>
       <c r="Y25" t="s">
-        <v>442</v>
+        <v>511</v>
       </c>
       <c r="Z25" t="s">
         <v>773</v>
       </c>
       <c r="AA25">
-        <v>0.99482380895087164</v>
+        <v>0.99321000417798277</v>
       </c>
       <c r="AB25">
-        <v>94.896835900686696</v>
+        <v>124.48325673698231</v>
       </c>
       <c r="AD25" t="s">
         <v>524</v>
@@ -11964,16 +11964,16 @@
         <v>893</v>
       </c>
       <c r="AM25" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AN25" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AO25">
-        <v>0.98934663566509429</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP25">
-        <v>195.31167947327185</v>
+        <v>58.672645982308907</v>
       </c>
       <c r="AR25" t="s">
         <v>524</v>
@@ -12006,10 +12006,10 @@
         <v>1228</v>
       </c>
       <c r="BC25">
-        <v>0.98946506962487613</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD25">
-        <v>193.14039021060518</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12074,16 +12074,16 @@
         <v>557</v>
       </c>
       <c r="Y26" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="Z26" t="s">
         <v>774</v>
       </c>
       <c r="AA26">
-        <v>0.99338478208530079</v>
+        <v>0.99519804750325769</v>
       </c>
       <c r="AB26">
-        <v>121.27899510281891</v>
+        <v>88.03579577360874</v>
       </c>
       <c r="AD26" t="s">
         <v>524</v>
@@ -12110,16 +12110,16 @@
         <v>895</v>
       </c>
       <c r="AM26" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="AN26" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="AO26">
-        <v>0.99503039970536677</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP26">
-        <v>91.109338734942796</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR26" t="s">
         <v>524</v>
@@ -12152,10 +12152,10 @@
         <v>1230</v>
       </c>
       <c r="BC26">
-        <v>0.9959052853503485</v>
+        <v>0.98529820518310829</v>
       </c>
       <c r="BD26">
-        <v>75.06976857694373</v>
+        <v>269.5329049763485</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>559</v>
       </c>
       <c r="Y27" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="Z27" t="s">
         <v>775</v>
       </c>
       <c r="AA27">
-        <v>0.95375321856768847</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB27">
-        <v>847.85765959237779</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD27" t="s">
         <v>524</v>
@@ -12256,16 +12256,16 @@
         <v>897</v>
       </c>
       <c r="AM27" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AN27" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AO27">
-        <v>0.9955955730654259</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP27">
-        <v>80.747827133859133</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR27" t="s">
         <v>524</v>
@@ -12295,13 +12295,13 @@
         <v>1231</v>
       </c>
       <c r="BB27" t="s">
-        <v>1232</v>
+        <v>789</v>
       </c>
       <c r="BC27">
-        <v>0.99542890407822671</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD27">
-        <v>83.803425232511387</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12366,16 +12366,16 @@
         <v>561</v>
       </c>
       <c r="Y28" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="Z28" t="s">
         <v>776</v>
       </c>
       <c r="AA28">
-        <v>0.99223209876176832</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB28">
-        <v>142.4115227009143</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD28" t="s">
         <v>524</v>
@@ -12402,16 +12402,16 @@
         <v>899</v>
       </c>
       <c r="AM28" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AN28" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AO28">
-        <v>0.99710531380540124</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP28">
-        <v>53.069246900976879</v>
+        <v>430.61202751883985</v>
       </c>
       <c r="AR28" t="s">
         <v>524</v>
@@ -12438,16 +12438,16 @@
         <v>1173</v>
       </c>
       <c r="BA28" t="s">
+        <v>1232</v>
+      </c>
+      <c r="BB28" t="s">
         <v>1233</v>
       </c>
-      <c r="BB28" t="s">
-        <v>1234</v>
-      </c>
       <c r="BC28">
-        <v>0.98879241442000787</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD28">
-        <v>205.47240229985658</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12512,16 +12512,16 @@
         <v>563</v>
       </c>
       <c r="Y29" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="Z29" t="s">
         <v>777</v>
       </c>
       <c r="AA29">
-        <v>0.98547237448299074</v>
+        <v>0.99034341169653584</v>
       </c>
       <c r="AB29">
-        <v>266.33980114516959</v>
+        <v>177.03745223017594</v>
       </c>
       <c r="AD29" t="s">
         <v>524</v>
@@ -12548,16 +12548,16 @@
         <v>901</v>
       </c>
       <c r="AM29" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AN29" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AO29">
-        <v>0.98452519237182756</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP29">
-        <v>283.70480651649393</v>
+        <v>79.268397406829976</v>
       </c>
       <c r="AR29" t="s">
         <v>524</v>
@@ -12584,16 +12584,16 @@
         <v>1175</v>
       </c>
       <c r="BA29" t="s">
+        <v>1234</v>
+      </c>
+      <c r="BB29" t="s">
         <v>1235</v>
       </c>
-      <c r="BB29" t="s">
-        <v>1236</v>
-      </c>
       <c r="BC29">
-        <v>0.98574436213546524</v>
+        <v>0.99375410727160951</v>
       </c>
       <c r="BD29">
-        <v>261.35336084980423</v>
+        <v>114.50803335382533</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12658,16 +12658,16 @@
         <v>565</v>
       </c>
       <c r="Y30" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="Z30" t="s">
         <v>778</v>
       </c>
       <c r="AA30">
-        <v>0.98775140142897844</v>
+        <v>0.97804554015715406</v>
       </c>
       <c r="AB30">
-        <v>224.55764046872929</v>
+        <v>402.49843045217517</v>
       </c>
       <c r="AD30" t="s">
         <v>524</v>
@@ -12694,16 +12694,16 @@
         <v>903</v>
       </c>
       <c r="AM30" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="AN30" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AO30">
-        <v>0.99398479997386135</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP30">
-        <v>110.27866714587458</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR30" t="s">
         <v>524</v>
@@ -12730,16 +12730,16 @@
         <v>1177</v>
       </c>
       <c r="BA30" t="s">
+        <v>1236</v>
+      </c>
+      <c r="BB30" t="s">
         <v>1237</v>
       </c>
-      <c r="BB30" t="s">
-        <v>1238</v>
-      </c>
       <c r="BC30">
-        <v>0.98097706415899455</v>
+        <v>0.99538398111052984</v>
       </c>
       <c r="BD30">
-        <v>348.75382375176576</v>
+        <v>84.627012973619784</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12804,16 +12804,16 @@
         <v>567</v>
       </c>
       <c r="Y31" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="Z31" t="s">
         <v>779</v>
       </c>
       <c r="AA31">
-        <v>0.99660448707980165</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB31">
-        <v>62.251070203636829</v>
+        <v>226.88936094280919</v>
       </c>
       <c r="AD31" t="s">
         <v>524</v>
@@ -12840,16 +12840,16 @@
         <v>905</v>
       </c>
       <c r="AM31" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AN31" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AO31">
-        <v>0.99403730604060547</v>
+        <v>0.99694661611560498</v>
       </c>
       <c r="AP31">
-        <v>109.31605592223302</v>
+        <v>55.978704547242401</v>
       </c>
       <c r="AR31" t="s">
         <v>524</v>
@@ -12876,16 +12876,16 @@
         <v>1179</v>
       </c>
       <c r="BA31" t="s">
+        <v>1238</v>
+      </c>
+      <c r="BB31" t="s">
         <v>1239</v>
       </c>
-      <c r="BB31" t="s">
-        <v>1212</v>
-      </c>
       <c r="BC31">
-        <v>0.98806872821788805</v>
+        <v>0.98734189460869326</v>
       </c>
       <c r="BD31">
-        <v>218.73998267205184</v>
+        <v>232.06526550729092</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -12950,16 +12950,16 @@
         <v>569</v>
       </c>
       <c r="Y32" t="s">
-        <v>487</v>
+        <v>417</v>
       </c>
       <c r="Z32" t="s">
         <v>780</v>
       </c>
       <c r="AA32">
-        <v>0.99363093646241407</v>
+        <v>0.97627448840453657</v>
       </c>
       <c r="AB32">
-        <v>116.76616485574142</v>
+        <v>434.96771258349719</v>
       </c>
       <c r="AD32" t="s">
         <v>524</v>
@@ -12986,16 +12986,16 @@
         <v>907</v>
       </c>
       <c r="AM32" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="AN32" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AO32">
-        <v>0.99620534810300254</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP32">
-        <v>69.568618111619969</v>
+        <v>151.17817104385733</v>
       </c>
       <c r="AR32" t="s">
         <v>524</v>
@@ -13025,13 +13025,13 @@
         <v>1240</v>
       </c>
       <c r="BB32" t="s">
-        <v>1057</v>
+        <v>1241</v>
       </c>
       <c r="BC32">
-        <v>0.99119386580545066</v>
+        <v>0.98097706415899455</v>
       </c>
       <c r="BD32">
-        <v>161.44579356673827</v>
+        <v>348.75382375176576</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13096,16 +13096,16 @@
         <v>571</v>
       </c>
       <c r="Y33" t="s">
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="Z33" t="s">
         <v>781</v>
       </c>
       <c r="AA33">
-        <v>0.99519314522306834</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB33">
-        <v>88.125670910414172</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD33" t="s">
         <v>524</v>
@@ -13132,16 +13132,16 @@
         <v>909</v>
       </c>
       <c r="AM33" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AN33" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AO33">
-        <v>0.9961850470371636</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP33">
-        <v>69.94080431866837</v>
+        <v>107.39028514481463</v>
       </c>
       <c r="AR33" t="s">
         <v>524</v>
@@ -13168,16 +13168,16 @@
         <v>1183</v>
       </c>
       <c r="BA33" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="BB33" t="s">
-        <v>808</v>
+        <v>1243</v>
       </c>
       <c r="BC33">
-        <v>0.9924080998261412</v>
+        <v>0.9884421166583558</v>
       </c>
       <c r="BD33">
-        <v>139.18483652074559</v>
+        <v>211.89452793014343</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13242,16 +13242,16 @@
         <v>573</v>
       </c>
       <c r="Y34" t="s">
-        <v>432</v>
+        <v>492</v>
       </c>
       <c r="Z34" t="s">
         <v>782</v>
       </c>
       <c r="AA34">
-        <v>0.99494501873633134</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB34">
-        <v>92.674656500591539</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD34" t="s">
         <v>524</v>
@@ -13278,16 +13278,16 @@
         <v>911</v>
       </c>
       <c r="AM34" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="AN34" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AO34">
-        <v>0.99681385284485569</v>
+        <v>0.99776348189506514</v>
       </c>
       <c r="AP34">
-        <v>58.41269784431158</v>
+        <v>41.002831923804749</v>
       </c>
       <c r="AR34" t="s">
         <v>524</v>
@@ -13314,16 +13314,16 @@
         <v>1185</v>
       </c>
       <c r="BA34" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="BB34" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="BC34">
-        <v>0.99314574070258299</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD34">
-        <v>125.66142045264445</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13388,16 +13388,16 @@
         <v>575</v>
       </c>
       <c r="Y35" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="Z35" t="s">
         <v>783</v>
       </c>
       <c r="AA35">
-        <v>0.99327397587413557</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB35">
-        <v>123.31044230751543</v>
+        <v>49.309812409870183</v>
       </c>
       <c r="AD35" t="s">
         <v>524</v>
@@ -13424,16 +13424,16 @@
         <v>913</v>
       </c>
       <c r="AM35" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="AN35" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="AO35">
-        <v>0.9917253583369573</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP35">
-        <v>151.70176382244892</v>
+        <v>79.007487588415231</v>
       </c>
       <c r="AR35" t="s">
         <v>524</v>
@@ -13460,16 +13460,16 @@
         <v>1187</v>
       </c>
       <c r="BA35" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="BB35" t="s">
-        <v>1245</v>
+        <v>1128</v>
       </c>
       <c r="BC35">
-        <v>0.98163861082146986</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD35">
-        <v>336.62546827305243</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13534,16 +13534,16 @@
         <v>577</v>
       </c>
       <c r="Y36" t="s">
-        <v>457</v>
+        <v>519</v>
       </c>
       <c r="Z36" t="s">
         <v>784</v>
       </c>
       <c r="AA36">
-        <v>0.99588617410922531</v>
+        <v>0.99681364926860017</v>
       </c>
       <c r="AB36">
-        <v>75.420141330869626</v>
+        <v>58.416430075664103</v>
       </c>
       <c r="AD36" t="s">
         <v>524</v>
@@ -13570,16 +13570,16 @@
         <v>915</v>
       </c>
       <c r="AM36" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AN36" t="s">
-        <v>1053</v>
+        <v>859</v>
       </c>
       <c r="AO36">
-        <v>0.99274560110857168</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP36">
-        <v>132.99731300951822</v>
+        <v>819.02093721560016</v>
       </c>
       <c r="AR36" t="s">
         <v>524</v>
@@ -13606,16 +13606,16 @@
         <v>1189</v>
       </c>
       <c r="BA36" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="BB36" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="BC36">
-        <v>0.99665799830099</v>
+        <v>0.99196968319234669</v>
       </c>
       <c r="BD36">
-        <v>61.270031148516708</v>
+        <v>147.22247480697732</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13680,16 +13680,16 @@
         <v>579</v>
       </c>
       <c r="Y37" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="Z37" t="s">
         <v>785</v>
       </c>
       <c r="AA37">
-        <v>0.96942910386940295</v>
+        <v>0.99527450819743701</v>
       </c>
       <c r="AB37">
-        <v>560.46642906094564</v>
+        <v>86.634016380320446</v>
       </c>
       <c r="AD37" t="s">
         <v>524</v>
@@ -13722,10 +13722,10 @@
         <v>1055</v>
       </c>
       <c r="AO37">
-        <v>0.99684152237002188</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP37">
-        <v>57.905423216266421</v>
+        <v>56.159977027506663</v>
       </c>
       <c r="AR37" t="s">
         <v>524</v>
@@ -13752,16 +13752,16 @@
         <v>1191</v>
       </c>
       <c r="BA37" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="BB37" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="BC37">
-        <v>0.98125520899414764</v>
+        <v>0.98879241442000787</v>
       </c>
       <c r="BD37">
-        <v>343.65450177395917</v>
+        <v>205.47240229985658</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -13826,16 +13826,16 @@
         <v>581</v>
       </c>
       <c r="Y38" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="Z38" t="s">
         <v>786</v>
       </c>
       <c r="AA38">
-        <v>0.93980266520001188</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB38">
-        <v>1103.617804666449</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD38" t="s">
         <v>524</v>
@@ -13868,10 +13868,10 @@
         <v>1057</v>
       </c>
       <c r="AO38">
-        <v>0.99679967385551038</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP38">
-        <v>58.672645982308907</v>
+        <v>58.751500348127372</v>
       </c>
       <c r="AR38" t="s">
         <v>524</v>
@@ -13898,16 +13898,16 @@
         <v>1193</v>
       </c>
       <c r="BA38" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="BB38" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="BC38">
-        <v>0.98734189460869326</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD38">
-        <v>232.06526550729092</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -13972,16 +13972,16 @@
         <v>583</v>
       </c>
       <c r="Y39" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="Z39" t="s">
         <v>787</v>
       </c>
       <c r="AA39">
-        <v>0.99034341169653584</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB39">
-        <v>177.03745223017594</v>
+        <v>121.57987025257442</v>
       </c>
       <c r="AD39" t="s">
         <v>524</v>
@@ -14014,10 +14014,10 @@
         <v>1059</v>
       </c>
       <c r="AO39">
-        <v>0.99083036293819104</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP39">
-        <v>168.11001279983091</v>
+        <v>114.668395037126</v>
       </c>
       <c r="AR39" t="s">
         <v>524</v>
@@ -14044,16 +14044,16 @@
         <v>1195</v>
       </c>
       <c r="BA39" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="BB39" t="s">
-        <v>1253</v>
+        <v>1214</v>
       </c>
       <c r="BC39">
-        <v>0.9884421166583558</v>
+        <v>0.99357050471442732</v>
       </c>
       <c r="BD39">
-        <v>211.89452793014343</v>
+        <v>117.87408023549864</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14118,16 +14118,16 @@
         <v>585</v>
       </c>
       <c r="Y40" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="Z40" t="s">
         <v>788</v>
       </c>
       <c r="AA40">
-        <v>0.97804554015715406</v>
+        <v>0.99394598112170862</v>
       </c>
       <c r="AB40">
-        <v>402.49843045217517</v>
+        <v>110.99034610200921</v>
       </c>
       <c r="AD40" t="s">
         <v>524</v>
@@ -14160,10 +14160,10 @@
         <v>1061</v>
       </c>
       <c r="AO40">
-        <v>0.98829989485605374</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP40">
-        <v>214.50192763901472</v>
+        <v>43.009723520953628</v>
       </c>
       <c r="AR40" t="s">
         <v>524</v>
@@ -14196,10 +14196,10 @@
         <v>1255</v>
       </c>
       <c r="BC40">
-        <v>0.99420451954813838</v>
+        <v>0.9807271101910352</v>
       </c>
       <c r="BD40">
-        <v>106.25047495079694</v>
+        <v>353.33631316435549</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14264,16 +14264,16 @@
         <v>587</v>
       </c>
       <c r="Y41" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="Z41" t="s">
         <v>789</v>
       </c>
       <c r="AA41">
-        <v>0.98762421667584677</v>
+        <v>0.99199345857785914</v>
       </c>
       <c r="AB41">
-        <v>226.88936094280919</v>
+        <v>146.78659273924956</v>
       </c>
       <c r="AD41" t="s">
         <v>524</v>
@@ -14306,10 +14306,10 @@
         <v>1063</v>
       </c>
       <c r="AO41">
-        <v>0.97651207122624506</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP41">
-        <v>430.61202751883985</v>
+        <v>256.69809569401372</v>
       </c>
       <c r="AR41" t="s">
         <v>524</v>
@@ -14339,13 +14339,13 @@
         <v>1256</v>
       </c>
       <c r="BB41" t="s">
-        <v>1087</v>
+        <v>1255</v>
       </c>
       <c r="BC41">
-        <v>0.99418931598784899</v>
+        <v>0.96816761985420574</v>
       </c>
       <c r="BD41">
-        <v>106.52920688943452</v>
+        <v>583.5936360062276</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14410,16 +14410,16 @@
         <v>589</v>
       </c>
       <c r="Y42" t="s">
-        <v>417</v>
+        <v>462</v>
       </c>
       <c r="Z42" t="s">
         <v>790</v>
       </c>
       <c r="AA42">
-        <v>0.97627448840453657</v>
+        <v>0.99615640242349235</v>
       </c>
       <c r="AB42">
-        <v>434.96771258349719</v>
+        <v>70.465955569306928</v>
       </c>
       <c r="AD42" t="s">
         <v>524</v>
@@ -14452,10 +14452,10 @@
         <v>1065</v>
       </c>
       <c r="AO42">
-        <v>0.99567626923235475</v>
+        <v>0.99500949727727495</v>
       </c>
       <c r="AP42">
-        <v>79.268397406829976</v>
+        <v>91.492549916626857</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14520,16 +14520,16 @@
         <v>591</v>
       </c>
       <c r="Y43" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
       <c r="Z43" t="s">
         <v>791</v>
       </c>
       <c r="AA43">
-        <v>0.98289281118622185</v>
+        <v>0.99288391401638731</v>
       </c>
       <c r="AB43">
-        <v>313.63179491926536</v>
+        <v>130.46157636623229</v>
       </c>
       <c r="AD43" t="s">
         <v>524</v>
@@ -14562,10 +14562,10 @@
         <v>1067</v>
       </c>
       <c r="AO43">
-        <v>0.9974675531234084</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP43">
-        <v>46.428192737512276</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14630,16 +14630,16 @@
         <v>593</v>
       </c>
       <c r="Y44" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="Z44" t="s">
         <v>792</v>
       </c>
       <c r="AA44">
-        <v>0.99563792883070867</v>
+        <v>0.99146050371560923</v>
       </c>
       <c r="AB44">
-        <v>79.971304770340467</v>
+        <v>156.55743188049695</v>
       </c>
       <c r="AD44" t="s">
         <v>524</v>
@@ -14672,10 +14672,10 @@
         <v>1069</v>
       </c>
       <c r="AO44">
-        <v>0.99694661611560498</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP44">
-        <v>55.978704547242401</v>
+        <v>258.57410995127316</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14740,16 +14740,16 @@
         <v>595</v>
       </c>
       <c r="Y45" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="Z45" t="s">
         <v>793</v>
       </c>
       <c r="AA45">
-        <v>0.99731037386855248</v>
+        <v>0.98077679482096181</v>
       </c>
       <c r="AB45">
-        <v>49.309812409870183</v>
+        <v>352.42542828236634</v>
       </c>
       <c r="AD45" t="s">
         <v>524</v>
@@ -14782,10 +14782,10 @@
         <v>1071</v>
       </c>
       <c r="AO45">
-        <v>0.99175391794306234</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP45">
-        <v>151.17817104385733</v>
+        <v>81.597153048545437</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -14850,16 +14850,16 @@
         <v>597</v>
       </c>
       <c r="Y46" t="s">
-        <v>499</v>
+        <v>418</v>
       </c>
       <c r="Z46" t="s">
-        <v>785</v>
+        <v>794</v>
       </c>
       <c r="AA46">
-        <v>0.96258244503784818</v>
+        <v>0.98976542300352621</v>
       </c>
       <c r="AB46">
-        <v>685.98850763945075</v>
+        <v>187.63391160201948</v>
       </c>
       <c r="AD46" t="s">
         <v>524</v>
@@ -14892,10 +14892,10 @@
         <v>1073</v>
       </c>
       <c r="AO46">
-        <v>0.99414234808301016</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP46">
-        <v>107.39028514481463</v>
+        <v>85.270745539791065</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -14960,16 +14960,16 @@
         <v>599</v>
       </c>
       <c r="Y47" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="Z47" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AA47">
-        <v>0.991015135510805</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB47">
-        <v>164.72251563524117</v>
+        <v>645.26520366712316</v>
       </c>
       <c r="AD47" t="s">
         <v>524</v>
@@ -15002,10 +15002,10 @@
         <v>1075</v>
       </c>
       <c r="AO47">
-        <v>0.99776348189506514</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP47">
-        <v>41.002831923804749</v>
+        <v>184.02231422223667</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15070,16 +15070,16 @@
         <v>601</v>
       </c>
       <c r="Y48" t="s">
-        <v>425</v>
+        <v>490</v>
       </c>
       <c r="Z48" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AA48">
-        <v>0.99653079856255411</v>
+        <v>0.99372086165616802</v>
       </c>
       <c r="AB48">
-        <v>63.602026353175077</v>
+        <v>115.11753630358729</v>
       </c>
       <c r="AD48" t="s">
         <v>524</v>
@@ -15112,10 +15112,10 @@
         <v>1077</v>
       </c>
       <c r="AO48">
-        <v>0.99569050067699549</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP48">
-        <v>79.007487588415231</v>
+        <v>473.60023862765331</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15180,16 +15180,16 @@
         <v>603</v>
       </c>
       <c r="Y49" t="s">
-        <v>497</v>
+        <v>434</v>
       </c>
       <c r="Z49" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AA49">
-        <v>0.98304101862012738</v>
+        <v>0.99478593896263345</v>
       </c>
       <c r="AB49">
-        <v>310.91465863099842</v>
+        <v>95.59111901838736</v>
       </c>
       <c r="AD49" t="s">
         <v>524</v>
@@ -15222,10 +15222,10 @@
         <v>1079</v>
       </c>
       <c r="AO49">
-        <v>0.99244513691456471</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP49">
-        <v>138.50582323297994</v>
+        <v>163.93514059684662</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15290,16 +15290,16 @@
         <v>605</v>
       </c>
       <c r="Y50" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="Z50" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AA50">
-        <v>0.99313763810995603</v>
+        <v>0.99480158385008166</v>
       </c>
       <c r="AB50">
-        <v>125.80996798414014</v>
+        <v>95.304296081836526</v>
       </c>
       <c r="AD50" t="s">
         <v>524</v>
@@ -15332,10 +15332,10 @@
         <v>1081</v>
       </c>
       <c r="AO50">
-        <v>0.99729761494442914</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP50">
-        <v>49.543726018799653</v>
+        <v>40.90273458067751</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15400,16 +15400,16 @@
         <v>607</v>
       </c>
       <c r="Y51" t="s">
-        <v>519</v>
+        <v>450</v>
       </c>
       <c r="Z51" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AA51">
-        <v>0.99681364926860017</v>
+        <v>0.99503505617325061</v>
       </c>
       <c r="AB51">
-        <v>58.416430075664103</v>
+        <v>91.023970157072284</v>
       </c>
       <c r="AD51" t="s">
         <v>524</v>
@@ -15442,10 +15442,10 @@
         <v>1083</v>
       </c>
       <c r="AO51">
-        <v>0.99478775228549088</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP51">
-        <v>95.557874766001078</v>
+        <v>121.72426728897108</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15510,16 +15510,16 @@
         <v>609</v>
       </c>
       <c r="Y52" t="s">
-        <v>472</v>
+        <v>431</v>
       </c>
       <c r="Z52" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AA52">
-        <v>0.99527450819743701</v>
+        <v>0.99549887366825363</v>
       </c>
       <c r="AB52">
-        <v>86.634016380320446</v>
+        <v>82.52064941535015</v>
       </c>
       <c r="AD52" t="s">
         <v>524</v>
@@ -15552,10 +15552,10 @@
         <v>1085</v>
       </c>
       <c r="AO52">
-        <v>0.99593828267147511</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP52">
-        <v>74.464817689622748</v>
+        <v>341.91992986513412</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15620,16 +15620,16 @@
         <v>611</v>
       </c>
       <c r="Y53" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="Z53" t="s">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="AA53">
-        <v>0.99136196456122894</v>
+        <v>0.96192701971480499</v>
       </c>
       <c r="AB53">
-        <v>158.36398304413572</v>
+        <v>698.00463856190902</v>
       </c>
       <c r="AD53" t="s">
         <v>524</v>
@@ -15659,13 +15659,13 @@
         <v>1086</v>
       </c>
       <c r="AN53" t="s">
-        <v>1087</v>
+        <v>815</v>
       </c>
       <c r="AO53">
-        <v>0.99729205446773184</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP53">
-        <v>49.645668091582088</v>
+        <v>243.0827225935364</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15730,16 +15730,16 @@
         <v>613</v>
       </c>
       <c r="Y54" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="Z54" t="s">
-        <v>801</v>
+        <v>776</v>
       </c>
       <c r="AA54">
-        <v>0.99336837071349593</v>
+        <v>0.96219171780159551</v>
       </c>
       <c r="AB54">
-        <v>121.57987025257442</v>
+        <v>693.1518403040825</v>
       </c>
       <c r="AD54" t="s">
         <v>524</v>
@@ -15766,16 +15766,16 @@
         <v>951</v>
       </c>
       <c r="AM54" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AN54" t="s">
         <v>1088</v>
       </c>
-      <c r="AN54" t="s">
-        <v>1089</v>
-      </c>
       <c r="AO54">
-        <v>0.98589595763902149</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP54">
-        <v>258.57410995127316</v>
+        <v>74.530739771815789</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -15840,16 +15840,16 @@
         <v>615</v>
       </c>
       <c r="Y55" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="Z55" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AA55">
-        <v>0.99394598112170862</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB55">
-        <v>110.99034610200921</v>
+        <v>64.274570700309781</v>
       </c>
       <c r="AD55" t="s">
         <v>524</v>
@@ -15876,16 +15876,16 @@
         <v>953</v>
       </c>
       <c r="AM55" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AN55" t="s">
         <v>1090</v>
       </c>
-      <c r="AN55" t="s">
-        <v>1091</v>
-      </c>
       <c r="AO55">
-        <v>0.99554924619735208</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP55">
-        <v>81.597153048545437</v>
+        <v>43.412641259119624</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -15950,16 +15950,16 @@
         <v>617</v>
       </c>
       <c r="Y56" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="Z56" t="s">
-        <v>803</v>
+        <v>776</v>
       </c>
       <c r="AA56">
-        <v>0.99199345857785914</v>
+        <v>0.99463967358156791</v>
       </c>
       <c r="AB56">
-        <v>146.78659273924956</v>
+        <v>98.272651004588909</v>
       </c>
       <c r="AD56" t="s">
         <v>524</v>
@@ -15986,16 +15986,16 @@
         <v>955</v>
       </c>
       <c r="AM56" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AN56" t="s">
         <v>1092</v>
       </c>
-      <c r="AN56" t="s">
-        <v>1093</v>
-      </c>
       <c r="AO56">
-        <v>0.99534886842510228</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP56">
-        <v>85.270745539791065</v>
+        <v>103.86794515046822</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16060,16 +16060,16 @@
         <v>619</v>
       </c>
       <c r="Y57" t="s">
-        <v>462</v>
+        <v>508</v>
       </c>
       <c r="Z57" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AA57">
-        <v>0.99615640242349235</v>
+        <v>0.9919888686303644</v>
       </c>
       <c r="AB57">
-        <v>70.465955569306928</v>
+        <v>146.87074177665352</v>
       </c>
       <c r="AD57" t="s">
         <v>524</v>
@@ -16096,16 +16096,16 @@
         <v>957</v>
       </c>
       <c r="AM57" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AN57" t="s">
         <v>1094</v>
       </c>
-      <c r="AN57" t="s">
-        <v>1095</v>
-      </c>
       <c r="AO57">
-        <v>0.99664818772595598</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP57">
-        <v>61.449891690807455</v>
+        <v>57.146786340912868</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16170,16 +16170,16 @@
         <v>621</v>
       </c>
       <c r="Y58" t="s">
-        <v>475</v>
+        <v>415</v>
       </c>
       <c r="Z58" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="AA58">
-        <v>0.96725161865330156</v>
+        <v>0.97183849711184567</v>
       </c>
       <c r="AB58">
-        <v>600.38699135613854</v>
+        <v>516.29421961616231</v>
       </c>
       <c r="AD58" t="s">
         <v>524</v>
@@ -16206,16 +16206,16 @@
         <v>959</v>
       </c>
       <c r="AM58" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AN58" t="s">
         <v>1096</v>
       </c>
-      <c r="AN58" t="s">
-        <v>1097</v>
-      </c>
       <c r="AO58">
-        <v>0.98996241922424166</v>
+        <v>0.99724271030877243</v>
       </c>
       <c r="AP58">
-        <v>184.02231422223667</v>
+        <v>50.550311005838999</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16280,16 +16280,16 @@
         <v>623</v>
       </c>
       <c r="Y59" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Z59" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="AA59">
-        <v>0.98625376775139273</v>
+        <v>0.99315026975482257</v>
       </c>
       <c r="AB59">
-        <v>252.01425789113298</v>
+        <v>125.578387828252</v>
       </c>
       <c r="AD59" t="s">
         <v>524</v>
@@ -16316,16 +16316,16 @@
         <v>961</v>
       </c>
       <c r="AM59" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AN59" t="s">
         <v>1098</v>
       </c>
-      <c r="AN59" t="s">
-        <v>1099</v>
-      </c>
       <c r="AO59">
-        <v>0.97416725971121887</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP59">
-        <v>473.60023862765331</v>
+        <v>96.528578181196991</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16390,16 +16390,16 @@
         <v>625</v>
       </c>
       <c r="Y60" t="s">
-        <v>483</v>
+        <v>424</v>
       </c>
       <c r="Z60" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="AA60">
-        <v>0.99260874818585765</v>
+        <v>0.99638114444190684</v>
       </c>
       <c r="AB60">
-        <v>135.50628325927707</v>
+        <v>66.345685231708771</v>
       </c>
       <c r="AD60" t="s">
         <v>524</v>
@@ -16426,16 +16426,16 @@
         <v>963</v>
       </c>
       <c r="AM60" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AN60" t="s">
         <v>1100</v>
       </c>
-      <c r="AN60" t="s">
-        <v>1101</v>
-      </c>
       <c r="AO60">
-        <v>0.99105808324017197</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP60">
-        <v>163.93514059684662</v>
+        <v>43.953108254279897</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16500,16 +16500,16 @@
         <v>627</v>
       </c>
       <c r="Y61" t="s">
-        <v>427</v>
+        <v>484</v>
       </c>
       <c r="Z61" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="AA61">
-        <v>0.99704166323096854</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB61">
-        <v>54.23617409891024</v>
+        <v>307.49900901993823</v>
       </c>
       <c r="AD61" t="s">
         <v>524</v>
@@ -16536,16 +16536,16 @@
         <v>965</v>
       </c>
       <c r="AM61" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AN61" t="s">
         <v>1102</v>
       </c>
-      <c r="AN61" t="s">
-        <v>1103</v>
-      </c>
       <c r="AO61">
-        <v>0.99776894175014486</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP61">
-        <v>40.90273458067751</v>
+        <v>42.750927651225993</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16610,16 +16610,16 @@
         <v>629</v>
       </c>
       <c r="Y62" t="s">
-        <v>428</v>
+        <v>494</v>
       </c>
       <c r="Z62" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AA62">
-        <v>0.99781963473721114</v>
+        <v>0.99649199193483273</v>
       </c>
       <c r="AB62">
-        <v>39.973363151129654</v>
+        <v>64.313481194734194</v>
       </c>
       <c r="AD62" t="s">
         <v>524</v>
@@ -16646,16 +16646,16 @@
         <v>967</v>
       </c>
       <c r="AM62" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AN62" t="s">
         <v>1104</v>
       </c>
-      <c r="AN62" t="s">
-        <v>1105</v>
-      </c>
       <c r="AO62">
-        <v>0.99336049451151065</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP62">
-        <v>121.72426728897108</v>
+        <v>83.589016951479763</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16720,16 +16720,16 @@
         <v>631</v>
       </c>
       <c r="Y63" t="s">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="Z63" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="AA63">
-        <v>0.99134608634204613</v>
+        <v>0.99716560649644992</v>
       </c>
       <c r="AB63">
-        <v>158.65508372915352</v>
+        <v>51.96388089841895</v>
       </c>
       <c r="AD63" t="s">
         <v>524</v>
@@ -16756,16 +16756,16 @@
         <v>969</v>
       </c>
       <c r="AM63" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AN63" t="s">
         <v>1106</v>
       </c>
-      <c r="AN63" t="s">
-        <v>1107</v>
-      </c>
       <c r="AO63">
-        <v>0.9972012891192491</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP63">
-        <v>51.309699480432613</v>
+        <v>86.673039153654699</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -16830,16 +16830,16 @@
         <v>633</v>
       </c>
       <c r="Y64" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="Z64" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="AA64">
-        <v>0.99500961501774632</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB64">
-        <v>91.490391341317391</v>
+        <v>98.356996715718111</v>
       </c>
       <c r="AD64" t="s">
         <v>524</v>
@@ -16866,16 +16866,16 @@
         <v>971</v>
       </c>
       <c r="AM64" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AN64" t="s">
         <v>1108</v>
       </c>
-      <c r="AN64" t="s">
-        <v>1109</v>
-      </c>
       <c r="AO64">
-        <v>0.99644815774097173</v>
+        <v>0.99589340828485295</v>
       </c>
       <c r="AP64">
-        <v>65.117108082185538</v>
+        <v>75.287514777696231</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16940,16 +16940,16 @@
         <v>635</v>
       </c>
       <c r="Y65" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="Z65" t="s">
-        <v>812</v>
+        <v>775</v>
       </c>
       <c r="AA65">
-        <v>0.98028549885826644</v>
+        <v>0.96258244503784818</v>
       </c>
       <c r="AB65">
-        <v>361.43252093178171</v>
+        <v>685.98850763945075</v>
       </c>
       <c r="AD65" t="s">
         <v>524</v>
@@ -16976,16 +16976,16 @@
         <v>973</v>
       </c>
       <c r="AM65" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AN65" t="s">
         <v>1110</v>
       </c>
-      <c r="AN65" t="s">
-        <v>1111</v>
-      </c>
       <c r="AO65">
-        <v>0.97020178001960844</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP65">
-        <v>546.30069964051177</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17050,16 +17050,16 @@
         <v>637</v>
       </c>
       <c r="Y66" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Z66" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="AA66">
-        <v>0.99144230757194385</v>
+        <v>0.991015135510805</v>
       </c>
       <c r="AB66">
-        <v>156.89102784769577</v>
+        <v>164.72251563524117</v>
       </c>
       <c r="AD66" t="s">
         <v>524</v>
@@ -17086,16 +17086,16 @@
         <v>975</v>
       </c>
       <c r="AM66" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AN66" t="s">
         <v>1112</v>
       </c>
-      <c r="AN66" t="s">
-        <v>1113</v>
-      </c>
       <c r="AO66">
-        <v>0.99352359657507616</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP66">
-        <v>118.7340627902709</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17160,16 +17160,16 @@
         <v>639</v>
       </c>
       <c r="Y67" t="s">
-        <v>517</v>
+        <v>425</v>
       </c>
       <c r="Z67" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="AA67">
-        <v>0.98863909075879119</v>
+        <v>0.99653079856255411</v>
       </c>
       <c r="AB67">
-        <v>208.2833360888277</v>
+        <v>63.602026353175077</v>
       </c>
       <c r="AD67" t="s">
         <v>524</v>
@@ -17196,16 +17196,16 @@
         <v>977</v>
       </c>
       <c r="AM67" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AN67" t="s">
         <v>1114</v>
       </c>
-      <c r="AN67" t="s">
-        <v>1115</v>
-      </c>
       <c r="AO67">
-        <v>0.99532453653339104</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP67">
-        <v>85.716830221163534</v>
+        <v>283.70480651649393</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17270,16 +17270,16 @@
         <v>641</v>
       </c>
       <c r="Y68" t="s">
-        <v>443</v>
+        <v>497</v>
       </c>
       <c r="Z68" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="AA68">
-        <v>0.99503418876282002</v>
+        <v>0.98304101862012738</v>
       </c>
       <c r="AB68">
-        <v>91.039872681632787</v>
+        <v>310.91465863099842</v>
       </c>
       <c r="AD68" t="s">
         <v>524</v>
@@ -17306,16 +17306,16 @@
         <v>979</v>
       </c>
       <c r="AM68" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AN68" t="s">
         <v>1116</v>
       </c>
-      <c r="AN68" t="s">
-        <v>850</v>
-      </c>
       <c r="AO68">
-        <v>0.95532613069733086</v>
+        <v>0.99398479997386135</v>
       </c>
       <c r="AP68">
-        <v>819.02093721560016</v>
+        <v>110.27866714587458</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17380,16 +17380,16 @@
         <v>643</v>
       </c>
       <c r="Y69" t="s">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="Z69" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="AA69">
-        <v>0.99506672623055659</v>
+        <v>0.99313763810995603</v>
       </c>
       <c r="AB69">
-        <v>90.443352439796072</v>
+        <v>125.80996798414014</v>
       </c>
       <c r="AD69" t="s">
         <v>524</v>
@@ -17422,10 +17422,10 @@
         <v>1118</v>
       </c>
       <c r="AO69">
-        <v>0.99693672852577231</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP69">
-        <v>56.159977027506663</v>
+        <v>109.31605592223302</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17490,16 +17490,16 @@
         <v>645</v>
       </c>
       <c r="Y70" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="Z70" t="s">
-        <v>786</v>
+        <v>814</v>
       </c>
       <c r="AA70">
-        <v>0.98064868322652787</v>
+        <v>0.96725161865330156</v>
       </c>
       <c r="AB70">
-        <v>354.77414084698938</v>
+        <v>600.38699135613854</v>
       </c>
       <c r="AD70" t="s">
         <v>524</v>
@@ -17532,10 +17532,10 @@
         <v>1120</v>
       </c>
       <c r="AO70">
-        <v>0.996795372708284</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP70">
-        <v>58.751500348127372</v>
+        <v>138.50582323297994</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17600,16 +17600,16 @@
         <v>647</v>
       </c>
       <c r="Y71" t="s">
-        <v>481</v>
+        <v>414</v>
       </c>
       <c r="Z71" t="s">
-        <v>786</v>
+        <v>815</v>
       </c>
       <c r="AA71">
-        <v>0.97267890273247193</v>
+        <v>0.98625376775139273</v>
       </c>
       <c r="AB71">
-        <v>500.88678323801429</v>
+        <v>252.01425789113298</v>
       </c>
       <c r="AD71" t="s">
         <v>524</v>
@@ -17642,10 +17642,10 @@
         <v>1122</v>
       </c>
       <c r="AO71">
-        <v>0.99374536027070226</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP71">
-        <v>114.668395037126</v>
+        <v>49.543726018799653</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17710,16 +17710,16 @@
         <v>649</v>
       </c>
       <c r="Y72" t="s">
-        <v>409</v>
+        <v>483</v>
       </c>
       <c r="Z72" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="AA72">
-        <v>0.9951188973511842</v>
+        <v>0.99260874818585765</v>
       </c>
       <c r="AB72">
-        <v>89.486881894956255</v>
+        <v>135.50628325927707</v>
       </c>
       <c r="AD72" t="s">
         <v>524</v>
@@ -17752,10 +17752,10 @@
         <v>1124</v>
       </c>
       <c r="AO72">
-        <v>0.9976540150806753</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP72">
-        <v>43.009723520953628</v>
+        <v>95.557874766001078</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17820,16 +17820,16 @@
         <v>651</v>
       </c>
       <c r="Y73" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="Z73" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AA73">
-        <v>0.99570118415007625</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB73">
-        <v>78.81162391526847</v>
+        <v>54.23617409891024</v>
       </c>
       <c r="AD73" t="s">
         <v>524</v>
@@ -17862,10 +17862,10 @@
         <v>1126</v>
       </c>
       <c r="AO73">
-        <v>0.99424679200457</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP73">
-        <v>105.47547991621673</v>
+        <v>74.464817689622748</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17930,16 +17930,16 @@
         <v>653</v>
       </c>
       <c r="Y74" t="s">
-        <v>488</v>
+        <v>428</v>
       </c>
       <c r="Z74" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AA74">
-        <v>0.98419413291291158</v>
+        <v>0.99781963473721114</v>
       </c>
       <c r="AB74">
-        <v>289.77422992995491</v>
+        <v>39.973363151129654</v>
       </c>
       <c r="AD74" t="s">
         <v>524</v>
@@ -17972,10 +17972,10 @@
         <v>1128</v>
       </c>
       <c r="AO74">
-        <v>0.99762284649610655</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP74">
-        <v>43.581147571379539</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18040,16 +18040,16 @@
         <v>655</v>
       </c>
       <c r="Y75" t="s">
-        <v>489</v>
+        <v>445</v>
       </c>
       <c r="Z75" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AA75">
-        <v>0.98563153879963317</v>
+        <v>0.99134608634204613</v>
       </c>
       <c r="AB75">
-        <v>263.42178867339101</v>
+        <v>158.65508372915352</v>
       </c>
       <c r="AD75" t="s">
         <v>524</v>
@@ -18082,10 +18082,10 @@
         <v>1130</v>
       </c>
       <c r="AO75">
-        <v>0.99648541839873139</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP75">
-        <v>64.433996023258757</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18150,16 +18150,16 @@
         <v>657</v>
       </c>
       <c r="Y76" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="Z76" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AA76">
-        <v>0.99394085749709427</v>
+        <v>0.99500961501774632</v>
       </c>
       <c r="AB76">
-        <v>111.08427921993857</v>
+        <v>91.490391341317391</v>
       </c>
       <c r="AD76" t="s">
         <v>524</v>
@@ -18192,10 +18192,10 @@
         <v>1132</v>
       </c>
       <c r="AO76">
-        <v>0.99445933293330402</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP76">
-        <v>101.57889622275951</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18260,16 +18260,16 @@
         <v>659</v>
       </c>
       <c r="Y77" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="Z77" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
       <c r="AA77">
-        <v>0.99237710954614877</v>
+        <v>0.97410572590752698</v>
       </c>
       <c r="AB77">
-        <v>139.75299165393855</v>
+        <v>474.72835836200494</v>
       </c>
       <c r="AD77" t="s">
         <v>524</v>
@@ -18302,10 +18302,10 @@
         <v>1134</v>
       </c>
       <c r="AO77">
-        <v>0.98599828568941739</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP77">
-        <v>256.69809569401372</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18370,16 +18370,16 @@
         <v>661</v>
       </c>
       <c r="Y78" t="s">
-        <v>422</v>
+        <v>522</v>
       </c>
       <c r="Z78" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AA78">
-        <v>0.99680369125279411</v>
+        <v>0.9934351357667861</v>
       </c>
       <c r="AB78">
-        <v>58.598993698774343</v>
+        <v>120.35584427558737</v>
       </c>
       <c r="AD78" t="s">
         <v>524</v>
@@ -18412,10 +18412,10 @@
         <v>1136</v>
       </c>
       <c r="AO78">
-        <v>0.99500949727727495</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP78">
-        <v>91.492549916626857</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18480,16 +18480,16 @@
         <v>663</v>
       </c>
       <c r="Y79" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="Z79" t="s">
-        <v>824</v>
+        <v>776</v>
       </c>
       <c r="AA79">
-        <v>0.99321000417798277</v>
+        <v>0.97910116787740509</v>
       </c>
       <c r="AB79">
-        <v>124.48325673698231</v>
+        <v>383.14525558090747</v>
       </c>
       <c r="AD79" t="s">
         <v>524</v>
@@ -18522,10 +18522,10 @@
         <v>1138</v>
       </c>
       <c r="AO79">
-        <v>0.99760247912344124</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP79">
-        <v>43.95454940357709</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18590,16 +18590,16 @@
         <v>665</v>
       </c>
       <c r="Y80" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="Z80" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="AA80">
-        <v>0.99519804750325769</v>
+        <v>0.98797270203083642</v>
       </c>
       <c r="AB80">
-        <v>88.03579577360874</v>
+        <v>220.50046276799787</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18664,16 +18664,16 @@
         <v>667</v>
       </c>
       <c r="Y81" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="Z81" t="s">
-        <v>785</v>
+        <v>823</v>
       </c>
       <c r="AA81">
-        <v>0.97410572590752698</v>
+        <v>0.9923817726751798</v>
       </c>
       <c r="AB81">
-        <v>474.72835836200494</v>
+        <v>139.66750095503775</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18738,16 +18738,16 @@
         <v>669</v>
       </c>
       <c r="Y82" t="s">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="Z82" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AA82">
-        <v>0.9934351357667861</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB82">
-        <v>120.35584427558737</v>
+        <v>174.28740880058183</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -18812,16 +18812,16 @@
         <v>671</v>
       </c>
       <c r="Y83" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="Z83" t="s">
-        <v>786</v>
+        <v>825</v>
       </c>
       <c r="AA83">
-        <v>0.97910116787740509</v>
+        <v>0.99523006105909662</v>
       </c>
       <c r="AB83">
-        <v>383.14525558090747</v>
+        <v>87.448880583228942</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -18886,16 +18886,16 @@
         <v>673</v>
       </c>
       <c r="Y84" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="Z84" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AA84">
-        <v>0.98797270203083642</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB84">
-        <v>220.50046276799787</v>
+        <v>90.443352439796072</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -18960,16 +18960,16 @@
         <v>675</v>
       </c>
       <c r="Y85" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="Z85" t="s">
-        <v>828</v>
+        <v>776</v>
       </c>
       <c r="AA85">
-        <v>0.9923817726751798</v>
+        <v>0.98064868322652787</v>
       </c>
       <c r="AB85">
-        <v>139.66750095503775</v>
+        <v>354.77414084698938</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19034,16 +19034,16 @@
         <v>677</v>
       </c>
       <c r="Y86" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="Z86" t="s">
-        <v>829</v>
+        <v>776</v>
       </c>
       <c r="AA86">
-        <v>0.99049341406542279</v>
+        <v>0.97267890273247193</v>
       </c>
       <c r="AB86">
-        <v>174.28740880058183</v>
+        <v>500.88678323801429</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19108,16 +19108,16 @@
         <v>679</v>
       </c>
       <c r="Y87" t="s">
-        <v>459</v>
+        <v>409</v>
       </c>
       <c r="Z87" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="AA87">
-        <v>0.99523006105909662</v>
+        <v>0.9951188973511842</v>
       </c>
       <c r="AB87">
-        <v>87.448880583228942</v>
+        <v>89.486881894956255</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19182,16 +19182,16 @@
         <v>681</v>
       </c>
       <c r="Y88" t="s">
-        <v>506</v>
+        <v>410</v>
       </c>
       <c r="Z88" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="AA88">
-        <v>0.99288391401638731</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB88">
-        <v>130.46157636623229</v>
+        <v>78.81162391526847</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19256,16 +19256,16 @@
         <v>683</v>
       </c>
       <c r="Y89" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="Z89" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="AA89">
-        <v>0.99146050371560923</v>
+        <v>0.98419413291291158</v>
       </c>
       <c r="AB89">
-        <v>156.55743188049695</v>
+        <v>289.77422992995491</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19330,16 +19330,16 @@
         <v>685</v>
       </c>
       <c r="Y90" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="Z90" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="AA90">
-        <v>0.98077679482096181</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB90">
-        <v>352.42542828236634</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19404,16 +19404,16 @@
         <v>687</v>
       </c>
       <c r="Y91" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="Z91" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AA91">
-        <v>0.98976542300352621</v>
+        <v>0.99394085749709427</v>
       </c>
       <c r="AB91">
-        <v>187.63391160201948</v>
+        <v>111.08427921993857</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19478,16 +19478,16 @@
         <v>689</v>
       </c>
       <c r="Y92" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="Z92" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="AA92">
-        <v>0.96480371616361149</v>
+        <v>0.95375321856768847</v>
       </c>
       <c r="AB92">
-        <v>645.26520366712316</v>
+        <v>847.85765959237779</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19552,16 +19552,16 @@
         <v>691</v>
       </c>
       <c r="Y93" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="Z93" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="AA93">
-        <v>0.99372086165616802</v>
+        <v>0.99223209876176832</v>
       </c>
       <c r="AB93">
-        <v>115.11753630358729</v>
+        <v>142.4115227009143</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19626,16 +19626,16 @@
         <v>693</v>
       </c>
       <c r="Y94" t="s">
-        <v>434</v>
+        <v>512</v>
       </c>
       <c r="Z94" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="AA94">
-        <v>0.99478593896263345</v>
+        <v>0.98547237448299074</v>
       </c>
       <c r="AB94">
-        <v>95.59111901838736</v>
+        <v>266.33980114516959</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19700,16 +19700,16 @@
         <v>695</v>
       </c>
       <c r="Y95" t="s">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="Z95" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="AA95">
-        <v>0.99480158385008166</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB95">
-        <v>95.304296081836526</v>
+        <v>224.55764046872929</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19774,16 +19774,16 @@
         <v>697</v>
       </c>
       <c r="Y96" t="s">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="Z96" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="AA96">
-        <v>0.99503505617325061</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB96">
-        <v>91.023970157072284</v>
+        <v>62.251070203636829</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -19848,16 +19848,16 @@
         <v>699</v>
       </c>
       <c r="Y97" t="s">
-        <v>431</v>
+        <v>487</v>
       </c>
       <c r="Z97" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="AA97">
-        <v>0.99549887366825363</v>
+        <v>0.99363093646241407</v>
       </c>
       <c r="AB97">
-        <v>82.52064941535015</v>
+        <v>116.76616485574142</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -19922,16 +19922,16 @@
         <v>701</v>
       </c>
       <c r="Y98" t="s">
-        <v>500</v>
+        <v>433</v>
       </c>
       <c r="Z98" t="s">
-        <v>785</v>
+        <v>838</v>
       </c>
       <c r="AA98">
-        <v>0.96192701971480499</v>
+        <v>0.99519314522306834</v>
       </c>
       <c r="AB98">
-        <v>698.00463856190902</v>
+        <v>88.125670910414172</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -19996,16 +19996,16 @@
         <v>703</v>
       </c>
       <c r="Y99" t="s">
-        <v>476</v>
+        <v>432</v>
       </c>
       <c r="Z99" t="s">
-        <v>786</v>
+        <v>839</v>
       </c>
       <c r="AA99">
-        <v>0.96219171780159551</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB99">
-        <v>693.1518403040825</v>
+        <v>92.674656500591539</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20070,16 +20070,16 @@
         <v>705</v>
       </c>
       <c r="Y100" t="s">
-        <v>502</v>
+        <v>444</v>
       </c>
       <c r="Z100" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AA100">
-        <v>0.99649411432543766</v>
+        <v>0.99327397587413557</v>
       </c>
       <c r="AB100">
-        <v>64.274570700309781</v>
+        <v>123.31044230751543</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20144,16 +20144,16 @@
         <v>707</v>
       </c>
       <c r="Y101" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="Z101" t="s">
-        <v>786</v>
+        <v>841</v>
       </c>
       <c r="AA101">
-        <v>0.99463967358156791</v>
+        <v>0.99588617410922531</v>
       </c>
       <c r="AB101">
-        <v>98.272651004588909</v>
+        <v>75.420141330869626</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20218,16 +20218,16 @@
         <v>709</v>
       </c>
       <c r="Y102" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="Z102" t="s">
         <v>842</v>
       </c>
       <c r="AA102">
-        <v>0.9919888686303644</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB102">
-        <v>146.87074177665352</v>
+        <v>443.37880474956393</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20292,16 +20292,16 @@
         <v>711</v>
       </c>
       <c r="Y103" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="Z103" t="s">
         <v>843</v>
       </c>
       <c r="AA103">
-        <v>0.97183849711184567</v>
+        <v>0.98907176997397894</v>
       </c>
       <c r="AB103">
-        <v>516.29421961616231</v>
+        <v>200.35088381038645</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20366,16 +20366,16 @@
         <v>713</v>
       </c>
       <c r="Y104" t="s">
-        <v>413</v>
+        <v>471</v>
       </c>
       <c r="Z104" t="s">
         <v>844</v>
       </c>
       <c r="AA104">
-        <v>0.99315026975482257</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB104">
-        <v>125.578387828252</v>
+        <v>409.70769939155917</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20440,16 +20440,16 @@
         <v>715</v>
       </c>
       <c r="Y105" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="Z105" t="s">
         <v>845</v>
       </c>
       <c r="AA105">
-        <v>0.99638114444190684</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB105">
-        <v>66.345685231708771</v>
+        <v>67.023399161603095</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20514,16 +20514,16 @@
         <v>717</v>
       </c>
       <c r="Y106" t="s">
-        <v>484</v>
+        <v>426</v>
       </c>
       <c r="Z106" t="s">
         <v>846</v>
       </c>
       <c r="AA106">
-        <v>0.98322732678073066</v>
+        <v>0.99521210903869584</v>
       </c>
       <c r="AB106">
-        <v>307.49900901993823</v>
+        <v>87.778000957242412</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20588,16 +20588,16 @@
         <v>719</v>
       </c>
       <c r="Y107" t="s">
-        <v>494</v>
+        <v>437</v>
       </c>
       <c r="Z107" t="s">
         <v>847</v>
       </c>
       <c r="AA107">
-        <v>0.99649199193483273</v>
+        <v>0.99623432132689671</v>
       </c>
       <c r="AB107">
-        <v>64.313481194734194</v>
+        <v>69.037442340226178</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20662,16 +20662,16 @@
         <v>721</v>
       </c>
       <c r="Y108" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="Z108" t="s">
         <v>848</v>
       </c>
       <c r="AA108">
-        <v>0.99716560649644992</v>
+        <v>0.99476627594399158</v>
       </c>
       <c r="AB108">
-        <v>51.96388089841895</v>
+        <v>95.951607693487446</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20736,16 +20736,16 @@
         <v>723</v>
       </c>
       <c r="Y109" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="Z109" t="s">
         <v>849</v>
       </c>
       <c r="AA109">
-        <v>0.9946350729064154</v>
+        <v>0.99678217534817648</v>
       </c>
       <c r="AB109">
-        <v>98.356996715718111</v>
+        <v>58.99345195009743</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20810,16 +20810,16 @@
         <v>725</v>
       </c>
       <c r="Y110" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
       <c r="Z110" t="s">
         <v>850</v>
       </c>
       <c r="AA110">
-        <v>0.9565626086601956</v>
+        <v>0.99649132983250632</v>
       </c>
       <c r="AB110">
-        <v>796.35217456308078</v>
+        <v>64.325619737385011</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -20884,16 +20884,16 @@
         <v>727</v>
       </c>
       <c r="Y111" t="s">
-        <v>464</v>
+        <v>521</v>
       </c>
       <c r="Z111" t="s">
-        <v>786</v>
+        <v>851</v>
       </c>
       <c r="AA111">
-        <v>0.98848870678765</v>
+        <v>0.9866640001482827</v>
       </c>
       <c r="AB111">
-        <v>211.04037555975037</v>
+        <v>244.49333061481801</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -20958,16 +20958,16 @@
         <v>729</v>
       </c>
       <c r="Y112" t="s">
-        <v>515</v>
+        <v>480</v>
       </c>
       <c r="Z112" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AA112">
-        <v>0.99412748637108239</v>
+        <v>0.97166110802369898</v>
       </c>
       <c r="AB112">
-        <v>107.66274986349015</v>
+        <v>519.54635289885152</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21032,16 +21032,16 @@
         <v>731</v>
       </c>
       <c r="Y113" t="s">
-        <v>419</v>
+        <v>510</v>
       </c>
       <c r="Z113" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AA113">
-        <v>0.99772567527055689</v>
+        <v>0.99353270322428533</v>
       </c>
       <c r="AB113">
-        <v>41.695953373122713</v>
+        <v>118.56710755476936</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21106,16 +21106,16 @@
         <v>733</v>
       </c>
       <c r="Y114" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="Z114" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AA114">
-        <v>0.99382195819286057</v>
+        <v>0.99729259940965764</v>
       </c>
       <c r="AB114">
-        <v>113.26409979755675</v>
+        <v>49.635677489608995</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21180,16 +21180,16 @@
         <v>735</v>
       </c>
       <c r="Y115" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="Z115" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AA115">
-        <v>0.99529226044395613</v>
+        <v>0.99591694828752353</v>
       </c>
       <c r="AB115">
-        <v>86.308558527470979</v>
+        <v>74.855948062068691</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21254,16 +21254,16 @@
         <v>737</v>
       </c>
       <c r="Y116" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="Z116" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AA116">
-        <v>0.9964859002508345</v>
+        <v>0.99335306489036745</v>
       </c>
       <c r="AB116">
-        <v>64.425162068034254</v>
+        <v>121.86047700993024</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21328,16 +21328,16 @@
         <v>739</v>
       </c>
       <c r="Y117" t="s">
-        <v>503</v>
+        <v>453</v>
       </c>
       <c r="Z117" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AA117">
-        <v>0.97581570155911468</v>
+        <v>0.99619719802293027</v>
       </c>
       <c r="AB117">
-        <v>443.37880474956393</v>
+        <v>69.718036246277634</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21402,16 +21402,16 @@
         <v>741</v>
       </c>
       <c r="Y118" t="s">
-        <v>470</v>
+        <v>441</v>
       </c>
       <c r="Z118" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AA118">
-        <v>0.98907176997397894</v>
+        <v>0.99557851591679303</v>
       </c>
       <c r="AB118">
-        <v>200.35088381038645</v>
+        <v>81.06054152546038</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21476,16 +21476,16 @@
         <v>743</v>
       </c>
       <c r="Y119" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="Z119" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AA119">
-        <v>0.9776523073059149</v>
+        <v>0.9565626086601956</v>
       </c>
       <c r="AB119">
-        <v>409.70769939155917</v>
+        <v>796.35217456308078</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21550,16 +21550,16 @@
         <v>745</v>
       </c>
       <c r="Y120" t="s">
-        <v>411</v>
+        <v>464</v>
       </c>
       <c r="Z120" t="s">
-        <v>859</v>
+        <v>776</v>
       </c>
       <c r="AA120">
-        <v>0.99634417822754895</v>
+        <v>0.98848870678765</v>
       </c>
       <c r="AB120">
-        <v>67.023399161603095</v>
+        <v>211.04037555975037</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21624,16 +21624,16 @@
         <v>747</v>
       </c>
       <c r="Y121" t="s">
-        <v>426</v>
+        <v>515</v>
       </c>
       <c r="Z121" t="s">
         <v>860</v>
       </c>
       <c r="AA121">
-        <v>0.99521210903869584</v>
+        <v>0.99412748637108239</v>
       </c>
       <c r="AB121">
-        <v>87.778000957242412</v>
+        <v>107.66274986349015</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21698,16 +21698,16 @@
         <v>749</v>
       </c>
       <c r="Y122" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="Z122" t="s">
         <v>861</v>
       </c>
       <c r="AA122">
-        <v>0.99623432132689671</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB122">
-        <v>69.037442340226178</v>
+        <v>41.695953373122713</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21772,16 +21772,16 @@
         <v>751</v>
       </c>
       <c r="Y123" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Z123" t="s">
         <v>862</v>
       </c>
       <c r="AA123">
-        <v>0.99476627594399158</v>
+        <v>0.99382195819286057</v>
       </c>
       <c r="AB123">
-        <v>95.951607693487446</v>
+        <v>113.26409979755675</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -21846,16 +21846,16 @@
         <v>753</v>
       </c>
       <c r="Y124" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="Z124" t="s">
         <v>863</v>
       </c>
       <c r="AA124">
-        <v>0.99678217534817648</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB124">
-        <v>58.99345195009743</v>
+        <v>86.308558527470979</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -21920,16 +21920,16 @@
         <v>755</v>
       </c>
       <c r="Y125" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Z125" t="s">
         <v>864</v>
       </c>
       <c r="AA125">
-        <v>0.99649132983250632</v>
+        <v>0.9964859002508345</v>
       </c>
       <c r="AB125">
-        <v>64.325619737385011</v>
+        <v>64.425162068034254</v>
       </c>
     </row>
   </sheetData>
@@ -21938,7 +21938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B820BB-E94A-4E3A-9298-EB27655B5333}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5559CD3A-92F0-4F04-BEBA-094EF0BBD915}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22050,7 +22050,7 @@
         <v>1257</v>
       </c>
       <c r="K11" t="s">
-        <v>1110</v>
+        <v>1013</v>
       </c>
       <c r="L11">
         <v>10.563746678268352</v>
@@ -22083,7 +22083,7 @@
         <v>1395</v>
       </c>
       <c r="X11" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="Y11">
         <v>47.240250000000003</v>
@@ -22118,7 +22118,7 @@
         <v>1259</v>
       </c>
       <c r="K12" t="s">
-        <v>1098</v>
+        <v>1076</v>
       </c>
       <c r="L12">
         <v>7.4816578037471135</v>
@@ -22151,7 +22151,7 @@
         <v>1397</v>
       </c>
       <c r="X12" t="s">
-        <v>1250</v>
+        <v>1238</v>
       </c>
       <c r="Y12">
         <v>38.134500000000003</v>
@@ -22186,7 +22186,7 @@
         <v>1261</v>
       </c>
       <c r="K13" t="s">
-        <v>1078</v>
+        <v>1119</v>
       </c>
       <c r="L13">
         <v>4.7713910333636482</v>
@@ -22219,7 +22219,7 @@
         <v>1399</v>
       </c>
       <c r="X13" t="s">
-        <v>1205</v>
+        <v>1225</v>
       </c>
       <c r="Y13">
         <v>46.530749999999998</v>
@@ -22254,7 +22254,7 @@
         <v>1263</v>
       </c>
       <c r="K14" t="s">
-        <v>1003</v>
+        <v>1084</v>
       </c>
       <c r="L14">
         <v>12.404103898825962</v>
@@ -22287,7 +22287,7 @@
         <v>1401</v>
       </c>
       <c r="X14" t="s">
-        <v>1211</v>
+        <v>1253</v>
       </c>
       <c r="Y14">
         <v>21.307500000000001</v>
@@ -22322,7 +22322,7 @@
         <v>1265</v>
       </c>
       <c r="K15" t="s">
-        <v>1133</v>
+        <v>1062</v>
       </c>
       <c r="L15">
         <v>6.1276234637439133</v>
@@ -22355,7 +22355,7 @@
         <v>1403</v>
       </c>
       <c r="X15" t="s">
-        <v>1221</v>
+        <v>1247</v>
       </c>
       <c r="Y15">
         <v>47.747999999999998</v>
@@ -22390,7 +22390,7 @@
         <v>1267</v>
       </c>
       <c r="K16" t="s">
-        <v>1068</v>
+        <v>1043</v>
       </c>
       <c r="L16">
         <v>2.2195844391122765</v>
@@ -22423,7 +22423,7 @@
         <v>1405</v>
       </c>
       <c r="X16" t="s">
-        <v>1239</v>
+        <v>1213</v>
       </c>
       <c r="Y16">
         <v>40.677</v>
@@ -22458,7 +22458,7 @@
         <v>1269</v>
       </c>
       <c r="K17" t="s">
-        <v>1064</v>
+        <v>1039</v>
       </c>
       <c r="L17">
         <v>3.7614311754340659</v>
@@ -22491,7 +22491,7 @@
         <v>1407</v>
       </c>
       <c r="X17" t="s">
-        <v>1240</v>
+        <v>1215</v>
       </c>
       <c r="Y17">
         <v>53.033999999999999</v>
@@ -22526,7 +22526,7 @@
         <v>1271</v>
       </c>
       <c r="K18" t="s">
-        <v>1127</v>
+        <v>1007</v>
       </c>
       <c r="L18">
         <v>2.5731779960501728</v>
@@ -22559,7 +22559,7 @@
         <v>1409</v>
       </c>
       <c r="X18" t="s">
-        <v>1227</v>
+        <v>1207</v>
       </c>
       <c r="Y18">
         <v>39.273000000000003</v>
@@ -22594,7 +22594,7 @@
         <v>1273</v>
       </c>
       <c r="K19" t="s">
-        <v>1135</v>
+        <v>1064</v>
       </c>
       <c r="L19">
         <v>1.9040172385939969</v>
@@ -22627,7 +22627,7 @@
         <v>1411</v>
       </c>
       <c r="X19" t="s">
-        <v>1209</v>
+        <v>1229</v>
       </c>
       <c r="Y19">
         <v>32.054250000000003</v>
@@ -22662,7 +22662,7 @@
         <v>1275</v>
       </c>
       <c r="K20" t="s">
-        <v>1125</v>
+        <v>1005</v>
       </c>
       <c r="L20">
         <v>11.884376191048085</v>
@@ -22695,7 +22695,7 @@
         <v>1413</v>
       </c>
       <c r="X20" t="s">
-        <v>1252</v>
+        <v>1242</v>
       </c>
       <c r="Y20">
         <v>32.871749999999999</v>
@@ -22730,7 +22730,7 @@
         <v>1277</v>
       </c>
       <c r="K21" t="s">
-        <v>1016</v>
+        <v>1097</v>
       </c>
       <c r="L21">
         <v>12.246676572623375</v>
@@ -22763,7 +22763,7 @@
         <v>1415</v>
       </c>
       <c r="X21" t="s">
-        <v>1241</v>
+        <v>1216</v>
       </c>
       <c r="Y21">
         <v>49.244999999999997</v>
@@ -22798,7 +22798,7 @@
         <v>1279</v>
       </c>
       <c r="K22" t="s">
-        <v>1117</v>
+        <v>1054</v>
       </c>
       <c r="L22">
         <v>11.221871479411517</v>
@@ -22831,7 +22831,7 @@
         <v>1417</v>
       </c>
       <c r="X22" t="s">
-        <v>1242</v>
+        <v>1217</v>
       </c>
       <c r="Y22">
         <v>43.858499999999999</v>
@@ -22866,7 +22866,7 @@
         <v>1281</v>
       </c>
       <c r="K23" t="s">
-        <v>1042</v>
+        <v>1117</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -22899,7 +22899,7 @@
         <v>1419</v>
       </c>
       <c r="X23" t="s">
-        <v>1215</v>
+        <v>1232</v>
       </c>
       <c r="Y23">
         <v>51.427500000000002</v>
@@ -22934,7 +22934,7 @@
         <v>1283</v>
       </c>
       <c r="K24" t="s">
-        <v>1096</v>
+        <v>1074</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -22967,7 +22967,7 @@
         <v>1421</v>
       </c>
       <c r="X24" t="s">
-        <v>1229</v>
+        <v>1209</v>
       </c>
       <c r="Y24">
         <v>19.922999999999998</v>
@@ -23002,7 +23002,7 @@
         <v>1285</v>
       </c>
       <c r="K25" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="L25">
         <v>1.6757541426674882</v>
@@ -23035,7 +23035,7 @@
         <v>1423</v>
       </c>
       <c r="X25" t="s">
-        <v>1233</v>
+        <v>1249</v>
       </c>
       <c r="Y25">
         <v>29.15625</v>
@@ -23070,7 +23070,7 @@
         <v>1287</v>
       </c>
       <c r="K26" t="s">
-        <v>1137</v>
+        <v>1066</v>
       </c>
       <c r="L26">
         <v>0.39959553615654331</v>
@@ -23103,7 +23103,7 @@
         <v>1425</v>
       </c>
       <c r="X26" t="s">
-        <v>1207</v>
+        <v>1227</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23138,7 +23138,7 @@
         <v>1289</v>
       </c>
       <c r="K27" t="s">
-        <v>1080</v>
+        <v>1121</v>
       </c>
       <c r="L27">
         <v>1.7832075556426605</v>
@@ -23171,7 +23171,7 @@
         <v>1427</v>
       </c>
       <c r="X27" t="s">
-        <v>1223</v>
+        <v>1256</v>
       </c>
       <c r="Y27">
         <v>41.647500000000001</v>
@@ -23206,7 +23206,7 @@
         <v>1291</v>
       </c>
       <c r="K28" t="s">
-        <v>1046</v>
+        <v>1131</v>
       </c>
       <c r="L28">
         <v>0.35051099632091098</v>
@@ -23239,7 +23239,7 @@
         <v>1429</v>
       </c>
       <c r="X28" t="s">
-        <v>1244</v>
+        <v>1219</v>
       </c>
       <c r="Y28">
         <v>3.4402499999999998</v>
@@ -23274,7 +23274,7 @@
         <v>1293</v>
       </c>
       <c r="K29" t="s">
-        <v>1010</v>
+        <v>1091</v>
       </c>
       <c r="L29">
         <v>5.5005105319204732</v>
@@ -23307,7 +23307,7 @@
         <v>1431</v>
       </c>
       <c r="X29" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="Y29">
         <v>13.389749999999999</v>
@@ -23342,7 +23342,7 @@
         <v>1295</v>
       </c>
       <c r="K30" t="s">
-        <v>1102</v>
+        <v>1080</v>
       </c>
       <c r="L30">
         <v>0.34625959029864795</v>
@@ -23375,7 +23375,7 @@
         <v>1433</v>
       </c>
       <c r="X30" t="s">
-        <v>1256</v>
+        <v>1246</v>
       </c>
       <c r="Y30">
         <v>6.9757499999999997</v>
@@ -23410,7 +23410,7 @@
         <v>1297</v>
       </c>
       <c r="K31" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
       <c r="L31">
         <v>0.65440271382024695</v>
@@ -23443,7 +23443,7 @@
         <v>1435</v>
       </c>
       <c r="X31" t="s">
-        <v>1235</v>
+        <v>1251</v>
       </c>
       <c r="Y31">
         <v>38.154000000000003</v>
@@ -23478,7 +23478,7 @@
         <v>1299</v>
       </c>
       <c r="K32" t="s">
-        <v>1020</v>
+        <v>1101</v>
       </c>
       <c r="L32">
         <v>0.5190595734350465</v>
@@ -23511,7 +23511,7 @@
         <v>1437</v>
       </c>
       <c r="X32" t="s">
-        <v>1254</v>
+        <v>1244</v>
       </c>
       <c r="Y32">
         <v>26.765999999999998</v>
@@ -23546,7 +23546,7 @@
         <v>1301</v>
       </c>
       <c r="K33" t="s">
-        <v>1006</v>
+        <v>1087</v>
       </c>
       <c r="L33">
         <v>0.29505146981926272</v>
@@ -23614,7 +23614,7 @@
         <v>1303</v>
       </c>
       <c r="K34" t="s">
-        <v>1018</v>
+        <v>1099</v>
       </c>
       <c r="L34">
         <v>0.28737649325389003</v>
@@ -23647,7 +23647,7 @@
         <v>1441</v>
       </c>
       <c r="X34" t="s">
-        <v>1213</v>
+        <v>1254</v>
       </c>
       <c r="Y34">
         <v>21.510750000000002</v>
@@ -23682,7 +23682,7 @@
         <v>1305</v>
       </c>
       <c r="K35" t="s">
-        <v>1062</v>
+        <v>1037</v>
       </c>
       <c r="L35">
         <v>0.85621181691755843</v>
@@ -23715,7 +23715,7 @@
         <v>1443</v>
       </c>
       <c r="X35" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="Y35">
         <v>38.088000000000001</v>
@@ -23750,7 +23750,7 @@
         <v>1307</v>
       </c>
       <c r="K36" t="s">
-        <v>1038</v>
+        <v>1113</v>
       </c>
       <c r="L36">
         <v>2.2628760328229185</v>
@@ -23783,7 +23783,7 @@
         <v>1445</v>
       </c>
       <c r="X36" t="s">
-        <v>1246</v>
+        <v>1221</v>
       </c>
       <c r="Y36">
         <v>2.6655000000000002</v>
@@ -23818,7 +23818,7 @@
         <v>1309</v>
       </c>
       <c r="K37" t="s">
-        <v>1100</v>
+        <v>1078</v>
       </c>
       <c r="L37">
         <v>0.43370118574988076</v>
@@ -23851,7 +23851,7 @@
         <v>1447</v>
       </c>
       <c r="X37" t="s">
-        <v>1231</v>
+        <v>1211</v>
       </c>
       <c r="Y37">
         <v>11.651999999999999</v>
@@ -23886,7 +23886,7 @@
         <v>1311</v>
       </c>
       <c r="K38" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="L38">
         <v>2.5150267058852811</v>
@@ -23954,7 +23954,7 @@
         <v>1313</v>
       </c>
       <c r="K39" t="s">
-        <v>1066</v>
+        <v>1041</v>
       </c>
       <c r="L39">
         <v>2.2677057834637031</v>
@@ -23987,7 +23987,7 @@
         <v>1451</v>
       </c>
       <c r="X39" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="Y39">
         <v>10.619249999999999</v>
@@ -24022,7 +24022,7 @@
         <v>1315</v>
       </c>
       <c r="K40" t="s">
-        <v>1054</v>
+        <v>1029</v>
       </c>
       <c r="L40">
         <v>4.0509443596880574</v>
@@ -24055,7 +24055,7 @@
         <v>1453</v>
       </c>
       <c r="X40" t="s">
-        <v>1248</v>
+        <v>1223</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24090,7 +24090,7 @@
         <v>1317</v>
       </c>
       <c r="K41" t="s">
-        <v>1044</v>
+        <v>1129</v>
       </c>
       <c r="L41">
         <v>2.4836923620575391</v>
@@ -24123,7 +24123,7 @@
         <v>1455</v>
       </c>
       <c r="X41" t="s">
-        <v>1217</v>
+        <v>1234</v>
       </c>
       <c r="Y41">
         <v>35.486249999999998</v>
@@ -24158,7 +24158,7 @@
         <v>1319</v>
       </c>
       <c r="K42" t="s">
-        <v>1005</v>
+        <v>1086</v>
       </c>
       <c r="L42">
         <v>2.885493974180005</v>
@@ -24193,7 +24193,7 @@
         <v>1321</v>
       </c>
       <c r="K43" t="s">
-        <v>1040</v>
+        <v>1115</v>
       </c>
       <c r="L43">
         <v>1.5541104167331323</v>
@@ -24228,7 +24228,7 @@
         <v>1323</v>
       </c>
       <c r="K44" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="L44">
         <v>2.5222218440883255</v>
@@ -24263,7 +24263,7 @@
         <v>1325</v>
       </c>
       <c r="K45" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="L45">
         <v>23.427729543154012</v>
@@ -24298,7 +24298,7 @@
         <v>1327</v>
       </c>
       <c r="K46" t="s">
-        <v>1076</v>
+        <v>1051</v>
       </c>
       <c r="L46">
         <v>1.4999429400795936</v>
@@ -24333,7 +24333,7 @@
         <v>1329</v>
       </c>
       <c r="K47" t="s">
-        <v>1084</v>
+        <v>1125</v>
       </c>
       <c r="L47">
         <v>55.863958629218203</v>
@@ -24368,7 +24368,7 @@
         <v>1331</v>
       </c>
       <c r="K48" t="s">
-        <v>1024</v>
+        <v>1105</v>
       </c>
       <c r="L48">
         <v>17.068804920122925</v>
@@ -24403,7 +24403,7 @@
         <v>1333</v>
       </c>
       <c r="K49" t="s">
-        <v>1014</v>
+        <v>1095</v>
       </c>
       <c r="L49">
         <v>5.3278771181664615</v>
@@ -24438,7 +24438,7 @@
         <v>1335</v>
       </c>
       <c r="K50" t="s">
-        <v>1026</v>
+        <v>1107</v>
       </c>
       <c r="L50">
         <v>21.113356105805089</v>
@@ -24473,7 +24473,7 @@
         <v>1337</v>
       </c>
       <c r="K51" t="s">
-        <v>1088</v>
+        <v>1068</v>
       </c>
       <c r="L51">
         <v>2.3372365278937242</v>
@@ -24508,7 +24508,7 @@
         <v>1339</v>
       </c>
       <c r="K52" t="s">
-        <v>1058</v>
+        <v>1033</v>
       </c>
       <c r="L52">
         <v>4.2648673086521249</v>
@@ -24543,7 +24543,7 @@
         <v>1341</v>
       </c>
       <c r="K53" t="s">
-        <v>1012</v>
+        <v>1093</v>
       </c>
       <c r="L53">
         <v>2.8571480649629004</v>
@@ -24578,7 +24578,7 @@
         <v>1343</v>
       </c>
       <c r="K54" t="s">
-        <v>1094</v>
+        <v>1003</v>
       </c>
       <c r="L54">
         <v>31.544159267579381</v>
@@ -24613,7 +24613,7 @@
         <v>1345</v>
       </c>
       <c r="K55" t="s">
-        <v>1050</v>
+        <v>1135</v>
       </c>
       <c r="L55">
         <v>15.478330347836801</v>
@@ -24648,7 +24648,7 @@
         <v>1347</v>
       </c>
       <c r="K56" t="s">
-        <v>1074</v>
+        <v>1049</v>
       </c>
       <c r="L56">
         <v>18.772499167970881</v>
@@ -24683,7 +24683,7 @@
         <v>1349</v>
       </c>
       <c r="K57" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="L57">
         <v>18.904558868579112</v>
@@ -24718,7 +24718,7 @@
         <v>1351</v>
       </c>
       <c r="K58" t="s">
-        <v>1116</v>
+        <v>1053</v>
       </c>
       <c r="L58">
         <v>14.176079891703212</v>
@@ -24753,7 +24753,7 @@
         <v>1353</v>
       </c>
       <c r="K59" t="s">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="L59">
         <v>0.80973624203950822</v>
@@ -24788,7 +24788,7 @@
         <v>1355</v>
       </c>
       <c r="K60" t="s">
-        <v>1052</v>
+        <v>1137</v>
       </c>
       <c r="L60">
         <v>3.2067222321080848</v>
@@ -24823,7 +24823,7 @@
         <v>1357</v>
       </c>
       <c r="K61" t="s">
-        <v>1086</v>
+        <v>1127</v>
       </c>
       <c r="L61">
         <v>0.66271354737797783</v>
@@ -24858,7 +24858,7 @@
         <v>1359</v>
       </c>
       <c r="K62" t="s">
-        <v>1123</v>
+        <v>1060</v>
       </c>
       <c r="L62">
         <v>1.8183767824138508</v>
@@ -24893,7 +24893,7 @@
         <v>1361</v>
       </c>
       <c r="K63" t="s">
-        <v>1056</v>
+        <v>1031</v>
       </c>
       <c r="L63">
         <v>0.24904319237866104</v>
@@ -24928,7 +24928,7 @@
         <v>1363</v>
       </c>
       <c r="K64" t="s">
-        <v>1008</v>
+        <v>1089</v>
       </c>
       <c r="L64">
         <v>8.2047875916663029E-2</v>
@@ -24963,7 +24963,7 @@
         <v>1365</v>
       </c>
       <c r="K65" t="s">
-        <v>1070</v>
+        <v>1045</v>
       </c>
       <c r="L65">
         <v>11.861012832193515</v>
@@ -24998,7 +24998,7 @@
         <v>1367</v>
       </c>
       <c r="K66" t="s">
-        <v>1129</v>
+        <v>1009</v>
       </c>
       <c r="L66">
         <v>0.74143826937354373</v>
@@ -25033,7 +25033,7 @@
         <v>1369</v>
       </c>
       <c r="K67" t="s">
-        <v>1121</v>
+        <v>1058</v>
       </c>
       <c r="L67">
         <v>5.5201095579611916</v>
@@ -25068,7 +25068,7 @@
         <v>1371</v>
       </c>
       <c r="K68" t="s">
-        <v>1092</v>
+        <v>1072</v>
       </c>
       <c r="L68">
         <v>6.8285247240880329</v>
@@ -25103,7 +25103,7 @@
         <v>1373</v>
       </c>
       <c r="K69" t="s">
-        <v>1082</v>
+        <v>1123</v>
       </c>
       <c r="L69">
         <v>14.065249575687433</v>
@@ -25138,7 +25138,7 @@
         <v>1375</v>
       </c>
       <c r="K70" t="s">
-        <v>1072</v>
+        <v>1047</v>
       </c>
       <c r="L70">
         <v>9.3799037679336319</v>
@@ -25173,7 +25173,7 @@
         <v>1377</v>
       </c>
       <c r="K71" t="s">
-        <v>1022</v>
+        <v>1103</v>
       </c>
       <c r="L71">
         <v>42.785830383290261</v>
@@ -25208,7 +25208,7 @@
         <v>1379</v>
       </c>
       <c r="K72" t="s">
-        <v>1104</v>
+        <v>1082</v>
       </c>
       <c r="L72">
         <v>7.8693705940085819</v>
@@ -25243,7 +25243,7 @@
         <v>1381</v>
       </c>
       <c r="K73" t="s">
-        <v>1131</v>
+        <v>1011</v>
       </c>
       <c r="L73">
         <v>19.787589902082505</v>
@@ -25278,7 +25278,7 @@
         <v>1383</v>
       </c>
       <c r="K74" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
       <c r="L74">
         <v>18.319832830101969</v>
@@ -25313,7 +25313,7 @@
         <v>1385</v>
       </c>
       <c r="K75" t="s">
-        <v>1048</v>
+        <v>1133</v>
       </c>
       <c r="L75">
         <v>6.7551756478058005</v>
@@ -25348,7 +25348,7 @@
         <v>1387</v>
       </c>
       <c r="K76" t="s">
-        <v>1112</v>
+        <v>1015</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25383,7 +25383,7 @@
         <v>1389</v>
       </c>
       <c r="K77" t="s">
-        <v>1090</v>
+        <v>1070</v>
       </c>
       <c r="L77">
         <v>3.5275797249830152</v>
@@ -25418,7 +25418,7 @@
         <v>1391</v>
       </c>
       <c r="K78" t="s">
-        <v>1114</v>
+        <v>1017</v>
       </c>
       <c r="L78">
         <v>0.89663971235601181</v>
@@ -25453,7 +25453,7 @@
         <v>1393</v>
       </c>
       <c r="K79" t="s">
-        <v>1119</v>
+        <v>1056</v>
       </c>
       <c r="L79">
         <v>5.9305458091691294</v>
@@ -25468,7 +25468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E268577-1A5D-496C-B6E3-525909055A1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959BEAF7-BD9E-4883-8767-4FFE54B9909D}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26937,7 +26937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD84EAD-6B54-4E4C-BDF0-50E96F89B522}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E1AD51-8367-496D-A243-384ACCF0C803}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8103245A-7D7C-45E3-AD29-A8CE92BEEE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80033F3E-92CA-4DB8-918F-872BFC35BC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1705,18 +1705,150 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_100</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 100</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_109</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 109</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_016</t>
   </si>
   <si>
@@ -1747,64 +1879,106 @@
     <t>connecting solar to buses in cluster 33</t>
   </si>
   <si>
-    <t>distr_solelc_spv_100</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 100</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
   </si>
   <si>
     <t>distr_solelc_spv_091</t>
@@ -1861,48 +2035,6 @@
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_099</t>
   </si>
   <si>
@@ -1963,6 +2095,186 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_093</t>
   </si>
   <si>
@@ -2035,228 +2347,6 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_096</t>
   </si>
   <si>
@@ -2311,102 +2401,78 @@
     <t>connecting solar to buses in cluster 49</t>
   </si>
   <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w168904844-230,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230,e_BR283-500,e_BR290-500</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR41-500,e_BR37-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR483-500,e_BR571-500,e_BR558-500,e_BR535-500,e_w954122148-500</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>e_BR487-500,e_BR446-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR294-500,e_BR236-500,e_BR296-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR363-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR293-500,e_BR282-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
     <t>e_BR347-500,e_BR290-500,e_BR283-500,e_BR371-500,e_w453724535-500</t>
   </si>
   <si>
@@ -2425,37 +2491,55 @@
     <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
   </si>
   <si>
-    <t>e_w168904844-230,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230,e_BR283-500,e_BR290-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR41-500,e_BR37-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>e_BR487-500,e_BR446-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR294-500,e_BR236-500,e_BR296-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_w286006777-440</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR221-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR209-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR80-500,e_BR148-500,e_BR120-500,e_BR187-500,e_BR114-500,e_BR164-500,e_BR142-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR371-500,e_BR353-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w225181494-500,e_w172071437-440,e_BR666-440,e_BR764-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR499-500,e_BR462-500,e_BR439-500,e_BR430-500,e_BR459-500</t>
   </si>
   <si>
     <t>e_w304646981-500</t>
@@ -2482,27 +2566,6 @@
     <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
   </si>
   <si>
-    <t>e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR363-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR293-500,e_BR282-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
     <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
   </si>
   <si>
@@ -2533,6 +2596,81 @@
     <t>e_BR652-500,e_BR643-500,e_BR587-500,e_BR627-500,e_BR644-500</t>
   </si>
   <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR878-500,e_w188465343-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR515-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR535-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR487-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR300-500,e_BR433-500,e_BR437-500,e_w953014442-500,e_BR309-500</t>
+  </si>
+  <si>
+    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR282-500,e_BR209-500,e_BR302-500,e_BR190-500,e_BR340-500,e_w603494578-500,e_BR194-500,e_BR292-500,e_BR204-500,e_BR187-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR342-230,e_BR327-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
+  </si>
+  <si>
+    <t>e_BR300-500,e_w271191830-500,e_BR310-500,e_BR184-500,e_BR309-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR528-500,e_BR558-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR337-500,e_BR264-500</t>
+  </si>
+  <si>
+    <t>e_w201470687-500,e_BR273-230,e_BR270-230,e_BR315-230,e_BR327-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR283-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR459-500,e_BR412-500</t>
+  </si>
+  <si>
     <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
   </si>
   <si>
@@ -2560,102 +2698,6 @@
     <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
   </si>
   <si>
-    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR483-500,e_BR571-500,e_BR558-500,e_BR535-500,e_w954122148-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR371-500,e_BR353-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w225181494-500,e_w172071437-440,e_BR666-440,e_BR764-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR499-500,e_BR462-500,e_BR439-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_w201470687-500,e_BR273-230,e_BR270-230,e_BR315-230,e_BR327-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR283-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR459-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR878-500,e_w188465343-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR515-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR535-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_w286006777-440</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR221-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR209-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR80-500,e_BR148-500,e_BR120-500,e_BR187-500,e_BR114-500,e_BR164-500,e_BR142-500</t>
-  </si>
-  <si>
     <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
   </si>
   <si>
@@ -2683,46 +2725,340 @@
     <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
   </si>
   <si>
-    <t>e_BR270-230,e_BR342-230,e_BR327-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
-  </si>
-  <si>
-    <t>e_BR300-500,e_w271191830-500,e_BR310-500,e_BR184-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR528-500,e_BR558-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR337-500,e_BR264-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR487-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR300-500,e_BR433-500,e_BR437-500,e_w953014442-500,e_BR309-500</t>
-  </si>
-  <si>
-    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR282-500,e_BR209-500,e_BR302-500,e_BR190-500,e_BR340-500,e_w603494578-500,e_BR194-500,e_BR292-500,e_BR204-500,e_BR187-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
   </si>
   <si>
     <t>distr_wonelc_won_044</t>
@@ -2731,6 +3067,24 @@
     <t>connecting wind onshore to buses in cluster 44</t>
   </si>
   <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_010</t>
   </si>
   <si>
@@ -2755,126 +3109,6 @@
     <t>connecting wind onshore to buses in cluster 63</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_048</t>
   </si>
   <si>
@@ -2905,238 +3139,337 @@
     <t>connecting wind onshore to buses in cluster 52</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR302-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR400-500,e_BR360-500</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
   </si>
   <si>
     <t>elc_won_044</t>
@@ -3145,6 +3478,24 @@
     <t>e_BR400-500,e_BR360-500,e_BR344-500,e_BR340-500,e_BR302-500,e_w603494578-500,e_BR292-500,e_w532354815-500,e_BR204-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500</t>
   </si>
   <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
+  </si>
+  <si>
     <t>elc_won_010</t>
   </si>
   <si>
@@ -3169,126 +3520,6 @@
     <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
     <t>elc_won_048</t>
   </si>
   <si>
@@ -3316,235 +3547,94 @@
     <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR400-500,e_BR360-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR302-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_BR787-525,e_BR777-500,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR662-440</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_BR580-500,e_BR596-500,e_BR583-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR464-500,e_BR428-500,e_BR382-500,e_BR333-500,e_BR354-500,e_BR387-500</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
   </si>
   <si>
     <t>distr_wofelc_wof_028</t>
@@ -3583,46 +3673,22 @@
     <t>connecting wind offshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wofelc_wof_003</t>
@@ -3643,12 +3709,6 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_013</t>
   </si>
   <si>
@@ -3673,64 +3733,79 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
   </si>
   <si>
     <t>elc_wof_028</t>
@@ -3769,40 +3844,19 @@
     <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
   </si>
   <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
   </si>
   <si>
     <t>elc_wof_003</t>
@@ -3823,9 +3877,6 @@
     <t>e_BR851-500,e_BR764-440,e_BR758-440,e_BR755-500</t>
   </si>
   <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
     <t>elc_wof_013</t>
   </si>
   <si>
@@ -3848,57 +3899,6 @@
   </si>
   <si>
     <t>e_BR1014-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9646,7 +9646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B22B921C-7F59-49A7-BEA3-76749909B382}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D37A34C-1B0F-49A4-A4D1-5817DD65E2D2}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9884,16 +9884,16 @@
         <v>525</v>
       </c>
       <c r="Y11" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="Z11" t="s">
         <v>759</v>
       </c>
       <c r="AA11">
-        <v>0.99356258288761645</v>
+        <v>0.98578060748142671</v>
       </c>
       <c r="AB11">
-        <v>118.01931372703181</v>
+        <v>260.68886284051109</v>
       </c>
       <c r="AD11" t="s">
         <v>524</v>
@@ -9926,10 +9926,10 @@
         <v>1004</v>
       </c>
       <c r="AO11">
-        <v>0.99664818772595598</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP11">
-        <v>61.449891690807455</v>
+        <v>546.30069964051177</v>
       </c>
       <c r="AR11" t="s">
         <v>524</v>
@@ -9962,10 +9962,10 @@
         <v>1202</v>
       </c>
       <c r="BC11">
-        <v>0.99227438811018465</v>
+        <v>0.9884421166583558</v>
       </c>
       <c r="BD11">
-        <v>141.63621797994898</v>
+        <v>211.89452793014343</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10030,16 +10030,16 @@
         <v>529</v>
       </c>
       <c r="Y12" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="Z12" t="s">
         <v>760</v>
       </c>
       <c r="AA12">
-        <v>0.99658191580238853</v>
+        <v>0.9946911823559148</v>
       </c>
       <c r="AB12">
-        <v>62.664876956210314</v>
+        <v>97.32832347489618</v>
       </c>
       <c r="AD12" t="s">
         <v>524</v>
@@ -10072,10 +10072,10 @@
         <v>1006</v>
       </c>
       <c r="AO12">
-        <v>0.99424679200457</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP12">
-        <v>105.47547991621673</v>
+        <v>118.7340627902709</v>
       </c>
       <c r="AR12" t="s">
         <v>524</v>
@@ -10108,10 +10108,10 @@
         <v>1204</v>
       </c>
       <c r="BC12">
-        <v>0.9933934749176847</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD12">
-        <v>121.11962650911367</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10176,16 +10176,16 @@
         <v>531</v>
       </c>
       <c r="Y13" t="s">
-        <v>513</v>
+        <v>467</v>
       </c>
       <c r="Z13" t="s">
         <v>761</v>
       </c>
       <c r="AA13">
-        <v>0.99652977687804423</v>
+        <v>0.98028549885826644</v>
       </c>
       <c r="AB13">
-        <v>63.62075723585545</v>
+        <v>361.43252093178171</v>
       </c>
       <c r="AD13" t="s">
         <v>524</v>
@@ -10218,10 +10218,10 @@
         <v>1008</v>
       </c>
       <c r="AO13">
-        <v>0.99762284649610655</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP13">
-        <v>43.581147571379539</v>
+        <v>85.716830221163534</v>
       </c>
       <c r="AR13" t="s">
         <v>524</v>
@@ -10251,13 +10251,13 @@
         <v>1205</v>
       </c>
       <c r="BB13" t="s">
-        <v>1206</v>
+        <v>1113</v>
       </c>
       <c r="BC13">
-        <v>0.99120104792145036</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD13">
-        <v>161.31412144007655</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10322,16 +10322,16 @@
         <v>533</v>
       </c>
       <c r="Y14" t="s">
-        <v>446</v>
+        <v>518</v>
       </c>
       <c r="Z14" t="s">
         <v>762</v>
       </c>
       <c r="AA14">
-        <v>0.99356282906984039</v>
+        <v>0.99144230757194385</v>
       </c>
       <c r="AB14">
-        <v>118.01480038625972</v>
+        <v>156.89102784769577</v>
       </c>
       <c r="AD14" t="s">
         <v>524</v>
@@ -10364,10 +10364,10 @@
         <v>1010</v>
       </c>
       <c r="AO14">
-        <v>0.99648541839873139</v>
+        <v>0.9964556860892605</v>
       </c>
       <c r="AP14">
-        <v>64.433996023258757</v>
+        <v>64.979088363557494</v>
       </c>
       <c r="AR14" t="s">
         <v>524</v>
@@ -10394,16 +10394,16 @@
         <v>1145</v>
       </c>
       <c r="BA14" t="s">
+        <v>1206</v>
+      </c>
+      <c r="BB14" t="s">
         <v>1207</v>
       </c>
-      <c r="BB14" t="s">
-        <v>1208</v>
-      </c>
       <c r="BC14">
-        <v>0.98946506962487613</v>
+        <v>0.99196968319234669</v>
       </c>
       <c r="BD14">
-        <v>193.14039021060518</v>
+        <v>147.22247480697732</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10468,16 +10468,16 @@
         <v>535</v>
       </c>
       <c r="Y15" t="s">
-        <v>442</v>
+        <v>517</v>
       </c>
       <c r="Z15" t="s">
         <v>763</v>
       </c>
       <c r="AA15">
-        <v>0.99482380895087164</v>
+        <v>0.98863909075879119</v>
       </c>
       <c r="AB15">
-        <v>94.896835900686696</v>
+        <v>208.2833360888277</v>
       </c>
       <c r="AD15" t="s">
         <v>524</v>
@@ -10510,10 +10510,10 @@
         <v>1012</v>
       </c>
       <c r="AO15">
-        <v>0.99445933293330402</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP15">
-        <v>101.57889622275951</v>
+        <v>195.31167947327185</v>
       </c>
       <c r="AR15" t="s">
         <v>524</v>
@@ -10540,16 +10540,16 @@
         <v>1147</v>
       </c>
       <c r="BA15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="BB15" t="s">
         <v>1209</v>
       </c>
-      <c r="BB15" t="s">
-        <v>1210</v>
-      </c>
       <c r="BC15">
-        <v>0.9959052853503485</v>
+        <v>0.99357050471442732</v>
       </c>
       <c r="BD15">
-        <v>75.06976857694373</v>
+        <v>117.87408023549864</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10614,16 +10614,16 @@
         <v>537</v>
       </c>
       <c r="Y16" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Z16" t="s">
         <v>764</v>
       </c>
       <c r="AA16">
-        <v>0.99338478208530079</v>
+        <v>0.99503418876282002</v>
       </c>
       <c r="AB16">
-        <v>121.27899510281891</v>
+        <v>91.039872681632787</v>
       </c>
       <c r="AD16" t="s">
         <v>524</v>
@@ -10656,10 +10656,10 @@
         <v>1014</v>
       </c>
       <c r="AO16">
-        <v>0.97020178001960844</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP16">
-        <v>546.30069964051177</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR16" t="s">
         <v>524</v>
@@ -10686,16 +10686,16 @@
         <v>1149</v>
       </c>
       <c r="BA16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="BB16" t="s">
         <v>1211</v>
       </c>
-      <c r="BB16" t="s">
-        <v>1212</v>
-      </c>
       <c r="BC16">
-        <v>0.99542890407822671</v>
+        <v>0.9807271101910352</v>
       </c>
       <c r="BD16">
-        <v>83.803425232511387</v>
+        <v>353.33631316435549</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10760,16 +10760,16 @@
         <v>539</v>
       </c>
       <c r="Y17" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="Z17" t="s">
         <v>765</v>
       </c>
       <c r="AA17">
-        <v>0.98578060748142671</v>
+        <v>0.96258244503784818</v>
       </c>
       <c r="AB17">
-        <v>260.68886284051109</v>
+        <v>685.98850763945075</v>
       </c>
       <c r="AD17" t="s">
         <v>524</v>
@@ -10802,10 +10802,10 @@
         <v>1016</v>
       </c>
       <c r="AO17">
-        <v>0.99352359657507616</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP17">
-        <v>118.7340627902709</v>
+        <v>80.747827133859133</v>
       </c>
       <c r="AR17" t="s">
         <v>524</v>
@@ -10832,16 +10832,16 @@
         <v>1151</v>
       </c>
       <c r="BA17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="BB17" t="s">
         <v>1213</v>
       </c>
-      <c r="BB17" t="s">
-        <v>1214</v>
-      </c>
       <c r="BC17">
-        <v>0.98806872821788805</v>
+        <v>0.98097706415899455</v>
       </c>
       <c r="BD17">
-        <v>218.73998267205184</v>
+        <v>348.75382375176576</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -10906,16 +10906,16 @@
         <v>541</v>
       </c>
       <c r="Y18" t="s">
-        <v>408</v>
+        <v>520</v>
       </c>
       <c r="Z18" t="s">
         <v>766</v>
       </c>
       <c r="AA18">
-        <v>0.9946911823559148</v>
+        <v>0.991015135510805</v>
       </c>
       <c r="AB18">
-        <v>97.32832347489618</v>
+        <v>164.72251563524117</v>
       </c>
       <c r="AD18" t="s">
         <v>524</v>
@@ -10948,10 +10948,10 @@
         <v>1018</v>
       </c>
       <c r="AO18">
-        <v>0.99532453653339104</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP18">
-        <v>85.716830221163534</v>
+        <v>53.069246900976879</v>
       </c>
       <c r="AR18" t="s">
         <v>524</v>
@@ -10978,16 +10978,16 @@
         <v>1153</v>
       </c>
       <c r="BA18" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="BB18" t="s">
-        <v>1032</v>
+        <v>779</v>
       </c>
       <c r="BC18">
-        <v>0.99119386580545066</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD18">
-        <v>161.44579356673827</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11052,16 +11052,16 @@
         <v>543</v>
       </c>
       <c r="Y19" t="s">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="Z19" t="s">
         <v>767</v>
       </c>
       <c r="AA19">
-        <v>0.98028549885826644</v>
+        <v>0.99653079856255411</v>
       </c>
       <c r="AB19">
-        <v>361.43252093178171</v>
+        <v>63.602026353175077</v>
       </c>
       <c r="AD19" t="s">
         <v>524</v>
@@ -11094,10 +11094,10 @@
         <v>1020</v>
       </c>
       <c r="AO19">
-        <v>0.9964556860892605</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP19">
-        <v>64.979088363557494</v>
+        <v>96.528578181196991</v>
       </c>
       <c r="AR19" t="s">
         <v>524</v>
@@ -11124,16 +11124,16 @@
         <v>1155</v>
       </c>
       <c r="BA19" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="BB19" t="s">
-        <v>817</v>
+        <v>1209</v>
       </c>
       <c r="BC19">
-        <v>0.9924080998261412</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD19">
-        <v>139.18483652074559</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11198,16 +11198,16 @@
         <v>545</v>
       </c>
       <c r="Y20" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="Z20" t="s">
         <v>768</v>
       </c>
       <c r="AA20">
-        <v>0.99144230757194385</v>
+        <v>0.98304101862012738</v>
       </c>
       <c r="AB20">
-        <v>156.89102784769577</v>
+        <v>310.91465863099842</v>
       </c>
       <c r="AD20" t="s">
         <v>524</v>
@@ -11240,10 +11240,10 @@
         <v>1022</v>
       </c>
       <c r="AO20">
-        <v>0.98934663566509429</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP20">
-        <v>195.31167947327185</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR20" t="s">
         <v>524</v>
@@ -11270,16 +11270,16 @@
         <v>1157</v>
       </c>
       <c r="BA20" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="BB20" t="s">
-        <v>1218</v>
+        <v>1047</v>
       </c>
       <c r="BC20">
-        <v>0.99314574070258299</v>
+        <v>0.99119386580545066</v>
       </c>
       <c r="BD20">
-        <v>125.66142045264445</v>
+        <v>161.44579356673827</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11344,16 +11344,16 @@
         <v>547</v>
       </c>
       <c r="Y21" t="s">
-        <v>517</v>
+        <v>454</v>
       </c>
       <c r="Z21" t="s">
         <v>769</v>
       </c>
       <c r="AA21">
-        <v>0.98863909075879119</v>
+        <v>0.99313763810995603</v>
       </c>
       <c r="AB21">
-        <v>208.2833360888277</v>
+        <v>125.80996798414014</v>
       </c>
       <c r="AD21" t="s">
         <v>524</v>
@@ -11386,10 +11386,10 @@
         <v>1024</v>
       </c>
       <c r="AO21">
-        <v>0.99503039970536677</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP21">
-        <v>91.109338734942796</v>
+        <v>42.750927651225993</v>
       </c>
       <c r="AR21" t="s">
         <v>524</v>
@@ -11416,16 +11416,16 @@
         <v>1159</v>
       </c>
       <c r="BA21" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="BB21" t="s">
-        <v>1220</v>
+        <v>800</v>
       </c>
       <c r="BC21">
-        <v>0.98163861082146986</v>
+        <v>0.9924080998261412</v>
       </c>
       <c r="BD21">
-        <v>336.62546827305243</v>
+        <v>139.18483652074559</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11490,16 +11490,16 @@
         <v>549</v>
       </c>
       <c r="Y22" t="s">
-        <v>443</v>
+        <v>509</v>
       </c>
       <c r="Z22" t="s">
         <v>770</v>
       </c>
       <c r="AA22">
-        <v>0.99503418876282002</v>
+        <v>0.99237710954614877</v>
       </c>
       <c r="AB22">
-        <v>91.039872681632787</v>
+        <v>139.75299165393855</v>
       </c>
       <c r="AD22" t="s">
         <v>524</v>
@@ -11532,10 +11532,10 @@
         <v>1026</v>
       </c>
       <c r="AO22">
-        <v>0.9955955730654259</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP22">
-        <v>80.747827133859133</v>
+        <v>83.589016951479763</v>
       </c>
       <c r="AR22" t="s">
         <v>524</v>
@@ -11562,16 +11562,16 @@
         <v>1161</v>
       </c>
       <c r="BA22" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="BB22" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="BC22">
-        <v>0.99665799830099</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD22">
-        <v>61.270031148516708</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11636,16 +11636,16 @@
         <v>551</v>
       </c>
       <c r="Y23" t="s">
-        <v>509</v>
+        <v>422</v>
       </c>
       <c r="Z23" t="s">
         <v>771</v>
       </c>
       <c r="AA23">
-        <v>0.99237710954614877</v>
+        <v>0.99680369125279411</v>
       </c>
       <c r="AB23">
-        <v>139.75299165393855</v>
+        <v>58.598993698774343</v>
       </c>
       <c r="AD23" t="s">
         <v>524</v>
@@ -11678,10 +11678,10 @@
         <v>1028</v>
       </c>
       <c r="AO23">
-        <v>0.99710531380540124</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP23">
-        <v>53.069246900976879</v>
+        <v>86.673039153654699</v>
       </c>
       <c r="AR23" t="s">
         <v>524</v>
@@ -11708,16 +11708,16 @@
         <v>1163</v>
       </c>
       <c r="BA23" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="BB23" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="BC23">
-        <v>0.98125520899414764</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD23">
-        <v>343.65450177395917</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11782,16 +11782,16 @@
         <v>553</v>
       </c>
       <c r="Y24" t="s">
-        <v>422</v>
+        <v>511</v>
       </c>
       <c r="Z24" t="s">
         <v>772</v>
       </c>
       <c r="AA24">
-        <v>0.99680369125279411</v>
+        <v>0.99321000417798277</v>
       </c>
       <c r="AB24">
-        <v>58.598993698774343</v>
+        <v>124.48325673698231</v>
       </c>
       <c r="AD24" t="s">
         <v>524</v>
@@ -11824,10 +11824,10 @@
         <v>1030</v>
       </c>
       <c r="AO24">
-        <v>0.99684152237002188</v>
+        <v>0.99589340828485295</v>
       </c>
       <c r="AP24">
-        <v>57.905423216266421</v>
+        <v>75.287514777696231</v>
       </c>
       <c r="AR24" t="s">
         <v>524</v>
@@ -11854,16 +11854,16 @@
         <v>1165</v>
       </c>
       <c r="BA24" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="BB24" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="BC24">
-        <v>0.98935994634927737</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD24">
-        <v>195.06765026324791</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -11928,16 +11928,16 @@
         <v>555</v>
       </c>
       <c r="Y25" t="s">
-        <v>511</v>
+        <v>461</v>
       </c>
       <c r="Z25" t="s">
         <v>773</v>
       </c>
       <c r="AA25">
-        <v>0.99321000417798277</v>
+        <v>0.99519804750325769</v>
       </c>
       <c r="AB25">
-        <v>124.48325673698231</v>
+        <v>88.03579577360874</v>
       </c>
       <c r="AD25" t="s">
         <v>524</v>
@@ -11970,10 +11970,10 @@
         <v>1032</v>
       </c>
       <c r="AO25">
-        <v>0.99679967385551038</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP25">
-        <v>58.672645982308907</v>
+        <v>341.91992986513412</v>
       </c>
       <c r="AR25" t="s">
         <v>524</v>
@@ -12000,16 +12000,16 @@
         <v>1167</v>
       </c>
       <c r="BA25" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="BB25" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="BC25">
-        <v>0.95713629889852414</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD25">
-        <v>785.83452019372396</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12074,16 +12074,16 @@
         <v>557</v>
       </c>
       <c r="Y26" t="s">
-        <v>461</v>
+        <v>519</v>
       </c>
       <c r="Z26" t="s">
         <v>774</v>
       </c>
       <c r="AA26">
-        <v>0.99519804750325769</v>
+        <v>0.99681364926860017</v>
       </c>
       <c r="AB26">
-        <v>88.03579577360874</v>
+        <v>58.416430075664103</v>
       </c>
       <c r="AD26" t="s">
         <v>524</v>
@@ -12113,13 +12113,13 @@
         <v>1033</v>
       </c>
       <c r="AN26" t="s">
-        <v>1034</v>
+        <v>798</v>
       </c>
       <c r="AO26">
-        <v>0.99083036293819104</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP26">
-        <v>168.11001279983091</v>
+        <v>243.0827225935364</v>
       </c>
       <c r="AR26" t="s">
         <v>524</v>
@@ -12146,16 +12146,16 @@
         <v>1169</v>
       </c>
       <c r="BA26" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="BB26" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="BC26">
-        <v>0.98529820518310829</v>
+        <v>0.99227438811018465</v>
       </c>
       <c r="BD26">
-        <v>269.5329049763485</v>
+        <v>141.63621797994898</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>559</v>
       </c>
       <c r="Y27" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="Z27" t="s">
         <v>775</v>
       </c>
       <c r="AA27">
-        <v>0.96942910386940295</v>
+        <v>0.99527450819743701</v>
       </c>
       <c r="AB27">
-        <v>560.46642906094564</v>
+        <v>86.634016380320446</v>
       </c>
       <c r="AD27" t="s">
         <v>524</v>
@@ -12256,16 +12256,16 @@
         <v>897</v>
       </c>
       <c r="AM27" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AN27" t="s">
         <v>1035</v>
       </c>
-      <c r="AN27" t="s">
-        <v>1036</v>
-      </c>
       <c r="AO27">
-        <v>0.98829989485605374</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP27">
-        <v>214.50192763901472</v>
+        <v>74.530739771815789</v>
       </c>
       <c r="AR27" t="s">
         <v>524</v>
@@ -12292,16 +12292,16 @@
         <v>1171</v>
       </c>
       <c r="BA27" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="BB27" t="s">
-        <v>789</v>
+        <v>1229</v>
       </c>
       <c r="BC27">
-        <v>0.97821242976023937</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD27">
-        <v>399.43878772894504</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12366,16 +12366,16 @@
         <v>561</v>
       </c>
       <c r="Y28" t="s">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="Z28" t="s">
         <v>776</v>
       </c>
       <c r="AA28">
-        <v>0.93980266520001188</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB28">
-        <v>1103.617804666449</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD28" t="s">
         <v>524</v>
@@ -12402,16 +12402,16 @@
         <v>899</v>
       </c>
       <c r="AM28" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AN28" t="s">
         <v>1037</v>
       </c>
-      <c r="AN28" t="s">
-        <v>1038</v>
-      </c>
       <c r="AO28">
-        <v>0.97651207122624506</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP28">
-        <v>430.61202751883985</v>
+        <v>43.412641259119624</v>
       </c>
       <c r="AR28" t="s">
         <v>524</v>
@@ -12438,16 +12438,16 @@
         <v>1173</v>
       </c>
       <c r="BA28" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="BB28" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="BC28">
-        <v>0.99232494426983575</v>
+        <v>0.99120104792145036</v>
       </c>
       <c r="BD28">
-        <v>140.70935505301131</v>
+        <v>161.31412144007655</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12512,16 +12512,16 @@
         <v>563</v>
       </c>
       <c r="Y29" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="Z29" t="s">
         <v>777</v>
       </c>
       <c r="AA29">
-        <v>0.99034341169653584</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB29">
-        <v>177.03745223017594</v>
+        <v>121.57987025257442</v>
       </c>
       <c r="AD29" t="s">
         <v>524</v>
@@ -12548,16 +12548,16 @@
         <v>901</v>
       </c>
       <c r="AM29" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AN29" t="s">
         <v>1039</v>
       </c>
-      <c r="AN29" t="s">
-        <v>1040</v>
-      </c>
       <c r="AO29">
-        <v>0.99567626923235475</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP29">
-        <v>79.268397406829976</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR29" t="s">
         <v>524</v>
@@ -12584,16 +12584,16 @@
         <v>1175</v>
       </c>
       <c r="BA29" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="BB29" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="BC29">
-        <v>0.99375410727160951</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD29">
-        <v>114.50803335382533</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12658,16 +12658,16 @@
         <v>565</v>
       </c>
       <c r="Y30" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="Z30" t="s">
         <v>778</v>
       </c>
       <c r="AA30">
-        <v>0.97804554015715406</v>
+        <v>0.99394598112170862</v>
       </c>
       <c r="AB30">
-        <v>402.49843045217517</v>
+        <v>110.99034610200921</v>
       </c>
       <c r="AD30" t="s">
         <v>524</v>
@@ -12694,16 +12694,16 @@
         <v>903</v>
       </c>
       <c r="AM30" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AN30" t="s">
         <v>1041</v>
       </c>
-      <c r="AN30" t="s">
-        <v>1042</v>
-      </c>
       <c r="AO30">
-        <v>0.9974675531234084</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP30">
-        <v>46.428192737512276</v>
+        <v>57.146786340912868</v>
       </c>
       <c r="AR30" t="s">
         <v>524</v>
@@ -12730,16 +12730,16 @@
         <v>1177</v>
       </c>
       <c r="BA30" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="BB30" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="BC30">
-        <v>0.99538398111052984</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD30">
-        <v>84.627012973619784</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12804,16 +12804,16 @@
         <v>567</v>
       </c>
       <c r="Y31" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="Z31" t="s">
         <v>779</v>
       </c>
       <c r="AA31">
-        <v>0.98762421667584677</v>
+        <v>0.99199345857785914</v>
       </c>
       <c r="AB31">
-        <v>226.88936094280919</v>
+        <v>146.78659273924956</v>
       </c>
       <c r="AD31" t="s">
         <v>524</v>
@@ -12840,16 +12840,16 @@
         <v>905</v>
       </c>
       <c r="AM31" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AN31" t="s">
         <v>1043</v>
       </c>
-      <c r="AN31" t="s">
-        <v>1044</v>
-      </c>
       <c r="AO31">
-        <v>0.99694661611560498</v>
+        <v>0.99724271030877243</v>
       </c>
       <c r="AP31">
-        <v>55.978704547242401</v>
+        <v>50.550311005838999</v>
       </c>
       <c r="AR31" t="s">
         <v>524</v>
@@ -12876,16 +12876,16 @@
         <v>1179</v>
       </c>
       <c r="BA31" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="BB31" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="BC31">
-        <v>0.98734189460869326</v>
+        <v>0.99542890407822671</v>
       </c>
       <c r="BD31">
-        <v>232.06526550729092</v>
+        <v>83.803425232511387</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -12950,16 +12950,16 @@
         <v>569</v>
       </c>
       <c r="Y32" t="s">
-        <v>417</v>
+        <v>462</v>
       </c>
       <c r="Z32" t="s">
         <v>780</v>
       </c>
       <c r="AA32">
-        <v>0.97627448840453657</v>
+        <v>0.99615640242349235</v>
       </c>
       <c r="AB32">
-        <v>434.96771258349719</v>
+        <v>70.465955569306928</v>
       </c>
       <c r="AD32" t="s">
         <v>524</v>
@@ -12986,16 +12986,16 @@
         <v>907</v>
       </c>
       <c r="AM32" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AN32" t="s">
         <v>1045</v>
       </c>
-      <c r="AN32" t="s">
-        <v>1046</v>
-      </c>
       <c r="AO32">
-        <v>0.99175391794306234</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP32">
-        <v>151.17817104385733</v>
+        <v>57.905423216266421</v>
       </c>
       <c r="AR32" t="s">
         <v>524</v>
@@ -13022,16 +13022,16 @@
         <v>1181</v>
       </c>
       <c r="BA32" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="BB32" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="BC32">
-        <v>0.98097706415899455</v>
+        <v>0.98879241442000787</v>
       </c>
       <c r="BD32">
-        <v>348.75382375176576</v>
+        <v>205.47240229985658</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13096,16 +13096,16 @@
         <v>571</v>
       </c>
       <c r="Y33" t="s">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="Z33" t="s">
         <v>781</v>
       </c>
       <c r="AA33">
-        <v>0.98289281118622185</v>
+        <v>0.99356258288761645</v>
       </c>
       <c r="AB33">
-        <v>313.63179491926536</v>
+        <v>118.01931372703181</v>
       </c>
       <c r="AD33" t="s">
         <v>524</v>
@@ -13132,16 +13132,16 @@
         <v>909</v>
       </c>
       <c r="AM33" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AN33" t="s">
         <v>1047</v>
       </c>
-      <c r="AN33" t="s">
-        <v>1048</v>
-      </c>
       <c r="AO33">
-        <v>0.99414234808301016</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP33">
-        <v>107.39028514481463</v>
+        <v>58.672645982308907</v>
       </c>
       <c r="AR33" t="s">
         <v>524</v>
@@ -13168,16 +13168,16 @@
         <v>1183</v>
       </c>
       <c r="BA33" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="BB33" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="BC33">
-        <v>0.9884421166583558</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD33">
-        <v>211.89452793014343</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13242,16 +13242,16 @@
         <v>573</v>
       </c>
       <c r="Y34" t="s">
-        <v>492</v>
+        <v>423</v>
       </c>
       <c r="Z34" t="s">
         <v>782</v>
       </c>
       <c r="AA34">
-        <v>0.99563792883070867</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB34">
-        <v>79.971304770340467</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD34" t="s">
         <v>524</v>
@@ -13278,16 +13278,16 @@
         <v>911</v>
       </c>
       <c r="AM34" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AN34" t="s">
         <v>1049</v>
       </c>
-      <c r="AN34" t="s">
-        <v>1050</v>
-      </c>
       <c r="AO34">
-        <v>0.99776348189506514</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP34">
-        <v>41.002831923804749</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR34" t="s">
         <v>524</v>
@@ -13314,16 +13314,16 @@
         <v>1185</v>
       </c>
       <c r="BA34" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="BB34" t="s">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="BC34">
-        <v>0.99420451954813838</v>
+        <v>0.96816761985420574</v>
       </c>
       <c r="BD34">
-        <v>106.25047495079694</v>
+        <v>583.5936360062276</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13388,16 +13388,16 @@
         <v>575</v>
       </c>
       <c r="Y35" t="s">
-        <v>430</v>
+        <v>513</v>
       </c>
       <c r="Z35" t="s">
         <v>783</v>
       </c>
       <c r="AA35">
-        <v>0.99731037386855248</v>
+        <v>0.99652977687804423</v>
       </c>
       <c r="AB35">
-        <v>49.309812409870183</v>
+        <v>63.62075723585545</v>
       </c>
       <c r="AD35" t="s">
         <v>524</v>
@@ -13424,16 +13424,16 @@
         <v>913</v>
       </c>
       <c r="AM35" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AN35" t="s">
         <v>1051</v>
       </c>
-      <c r="AN35" t="s">
-        <v>1052</v>
-      </c>
       <c r="AO35">
-        <v>0.99569050067699549</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP35">
-        <v>79.007487588415231</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR35" t="s">
         <v>524</v>
@@ -13460,16 +13460,16 @@
         <v>1187</v>
       </c>
       <c r="BA35" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="BB35" t="s">
-        <v>1128</v>
+        <v>1244</v>
       </c>
       <c r="BC35">
-        <v>0.99418931598784899</v>
+        <v>0.98935994634927737</v>
       </c>
       <c r="BD35">
-        <v>106.52920688943452</v>
+        <v>195.06765026324791</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13534,16 +13534,16 @@
         <v>577</v>
       </c>
       <c r="Y36" t="s">
-        <v>519</v>
+        <v>446</v>
       </c>
       <c r="Z36" t="s">
         <v>784</v>
       </c>
       <c r="AA36">
-        <v>0.99681364926860017</v>
+        <v>0.99356282906984039</v>
       </c>
       <c r="AB36">
-        <v>58.416430075664103</v>
+        <v>118.01480038625972</v>
       </c>
       <c r="AD36" t="s">
         <v>524</v>
@@ -13570,16 +13570,16 @@
         <v>915</v>
       </c>
       <c r="AM36" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AN36" t="s">
         <v>1053</v>
       </c>
-      <c r="AN36" t="s">
-        <v>859</v>
-      </c>
       <c r="AO36">
-        <v>0.95532613069733086</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP36">
-        <v>819.02093721560016</v>
+        <v>258.57410995127316</v>
       </c>
       <c r="AR36" t="s">
         <v>524</v>
@@ -13606,16 +13606,16 @@
         <v>1189</v>
       </c>
       <c r="BA36" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="BB36" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="BC36">
-        <v>0.99196968319234669</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD36">
-        <v>147.22247480697732</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13680,16 +13680,16 @@
         <v>579</v>
       </c>
       <c r="Y37" t="s">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="Z37" t="s">
         <v>785</v>
       </c>
       <c r="AA37">
-        <v>0.99527450819743701</v>
+        <v>0.99482380895087164</v>
       </c>
       <c r="AB37">
-        <v>86.634016380320446</v>
+        <v>94.896835900686696</v>
       </c>
       <c r="AD37" t="s">
         <v>524</v>
@@ -13722,10 +13722,10 @@
         <v>1055</v>
       </c>
       <c r="AO37">
-        <v>0.99693672852577231</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP37">
-        <v>56.159977027506663</v>
+        <v>81.597153048545437</v>
       </c>
       <c r="AR37" t="s">
         <v>524</v>
@@ -13752,16 +13752,16 @@
         <v>1191</v>
       </c>
       <c r="BA37" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="BB37" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="BC37">
-        <v>0.98879241442000787</v>
+        <v>0.98529820518310829</v>
       </c>
       <c r="BD37">
-        <v>205.47240229985658</v>
+        <v>269.5329049763485</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -13826,16 +13826,16 @@
         <v>581</v>
       </c>
       <c r="Y38" t="s">
-        <v>493</v>
+        <v>440</v>
       </c>
       <c r="Z38" t="s">
         <v>786</v>
       </c>
       <c r="AA38">
-        <v>0.99136196456122894</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB38">
-        <v>158.36398304413572</v>
+        <v>121.27899510281891</v>
       </c>
       <c r="AD38" t="s">
         <v>524</v>
@@ -13868,10 +13868,10 @@
         <v>1057</v>
       </c>
       <c r="AO38">
-        <v>0.996795372708284</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP38">
-        <v>58.751500348127372</v>
+        <v>85.270745539791065</v>
       </c>
       <c r="AR38" t="s">
         <v>524</v>
@@ -13898,16 +13898,16 @@
         <v>1193</v>
       </c>
       <c r="BA38" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="BB38" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="BC38">
-        <v>0.98574436213546524</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD38">
-        <v>261.35336084980423</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -13972,16 +13972,16 @@
         <v>583</v>
       </c>
       <c r="Y39" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="Z39" t="s">
         <v>787</v>
       </c>
       <c r="AA39">
-        <v>0.99336837071349593</v>
+        <v>0.95375321856768847</v>
       </c>
       <c r="AB39">
-        <v>121.57987025257442</v>
+        <v>847.85765959237779</v>
       </c>
       <c r="AD39" t="s">
         <v>524</v>
@@ -14014,10 +14014,10 @@
         <v>1059</v>
       </c>
       <c r="AO39">
-        <v>0.99374536027070226</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP39">
-        <v>114.668395037126</v>
+        <v>430.61202751883985</v>
       </c>
       <c r="AR39" t="s">
         <v>524</v>
@@ -14044,16 +14044,16 @@
         <v>1195</v>
       </c>
       <c r="BA39" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="BB39" t="s">
-        <v>1214</v>
+        <v>1252</v>
       </c>
       <c r="BC39">
-        <v>0.99357050471442732</v>
+        <v>0.99375410727160951</v>
       </c>
       <c r="BD39">
-        <v>117.87408023549864</v>
+        <v>114.50803335382533</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14118,16 +14118,16 @@
         <v>585</v>
       </c>
       <c r="Y40" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="Z40" t="s">
         <v>788</v>
       </c>
       <c r="AA40">
-        <v>0.99394598112170862</v>
+        <v>0.99223209876176832</v>
       </c>
       <c r="AB40">
-        <v>110.99034610200921</v>
+        <v>142.4115227009143</v>
       </c>
       <c r="AD40" t="s">
         <v>524</v>
@@ -14160,10 +14160,10 @@
         <v>1061</v>
       </c>
       <c r="AO40">
-        <v>0.9976540150806753</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP40">
-        <v>43.009723520953628</v>
+        <v>79.268397406829976</v>
       </c>
       <c r="AR40" t="s">
         <v>524</v>
@@ -14190,16 +14190,16 @@
         <v>1197</v>
       </c>
       <c r="BA40" t="s">
+        <v>1253</v>
+      </c>
+      <c r="BB40" t="s">
         <v>1254</v>
       </c>
-      <c r="BB40" t="s">
-        <v>1255</v>
-      </c>
       <c r="BC40">
-        <v>0.9807271101910352</v>
+        <v>0.99538398111052984</v>
       </c>
       <c r="BD40">
-        <v>353.33631316435549</v>
+        <v>84.627012973619784</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14264,16 +14264,16 @@
         <v>587</v>
       </c>
       <c r="Y41" t="s">
-        <v>451</v>
+        <v>512</v>
       </c>
       <c r="Z41" t="s">
         <v>789</v>
       </c>
       <c r="AA41">
-        <v>0.99199345857785914</v>
+        <v>0.98547237448299074</v>
       </c>
       <c r="AB41">
-        <v>146.78659273924956</v>
+        <v>266.33980114516959</v>
       </c>
       <c r="AD41" t="s">
         <v>524</v>
@@ -14306,10 +14306,10 @@
         <v>1063</v>
       </c>
       <c r="AO41">
-        <v>0.98599828568941739</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP41">
-        <v>256.69809569401372</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR41" t="s">
         <v>524</v>
@@ -14336,16 +14336,16 @@
         <v>1199</v>
       </c>
       <c r="BA41" t="s">
+        <v>1255</v>
+      </c>
+      <c r="BB41" t="s">
         <v>1256</v>
       </c>
-      <c r="BB41" t="s">
-        <v>1255</v>
-      </c>
       <c r="BC41">
-        <v>0.96816761985420574</v>
+        <v>0.98734189460869326</v>
       </c>
       <c r="BD41">
-        <v>583.5936360062276</v>
+        <v>232.06526550729092</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14410,16 +14410,16 @@
         <v>589</v>
       </c>
       <c r="Y42" t="s">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="Z42" t="s">
         <v>790</v>
       </c>
       <c r="AA42">
-        <v>0.99615640242349235</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB42">
-        <v>70.465955569306928</v>
+        <v>224.55764046872929</v>
       </c>
       <c r="AD42" t="s">
         <v>524</v>
@@ -14452,10 +14452,10 @@
         <v>1065</v>
       </c>
       <c r="AO42">
-        <v>0.99500949727727495</v>
+        <v>0.99694661611560498</v>
       </c>
       <c r="AP42">
-        <v>91.492549916626857</v>
+        <v>55.978704547242401</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14520,16 +14520,16 @@
         <v>591</v>
       </c>
       <c r="Y43" t="s">
-        <v>506</v>
+        <v>420</v>
       </c>
       <c r="Z43" t="s">
         <v>791</v>
       </c>
       <c r="AA43">
-        <v>0.99288391401638731</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB43">
-        <v>130.46157636623229</v>
+        <v>62.251070203636829</v>
       </c>
       <c r="AD43" t="s">
         <v>524</v>
@@ -14562,10 +14562,10 @@
         <v>1067</v>
       </c>
       <c r="AO43">
-        <v>0.99760247912344124</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP43">
-        <v>43.95454940357709</v>
+        <v>151.17817104385733</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14630,16 +14630,16 @@
         <v>593</v>
       </c>
       <c r="Y44" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="Z44" t="s">
         <v>792</v>
       </c>
       <c r="AA44">
-        <v>0.99146050371560923</v>
+        <v>0.99363093646241407</v>
       </c>
       <c r="AB44">
-        <v>156.55743188049695</v>
+        <v>116.76616485574142</v>
       </c>
       <c r="AD44" t="s">
         <v>524</v>
@@ -14672,10 +14672,10 @@
         <v>1069</v>
       </c>
       <c r="AO44">
-        <v>0.98589595763902149</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP44">
-        <v>258.57410995127316</v>
+        <v>107.39028514481463</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14740,16 +14740,16 @@
         <v>595</v>
       </c>
       <c r="Y45" t="s">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="Z45" t="s">
         <v>793</v>
       </c>
       <c r="AA45">
-        <v>0.98077679482096181</v>
+        <v>0.99519314522306834</v>
       </c>
       <c r="AB45">
-        <v>352.42542828236634</v>
+        <v>88.125670910414172</v>
       </c>
       <c r="AD45" t="s">
         <v>524</v>
@@ -14782,10 +14782,10 @@
         <v>1071</v>
       </c>
       <c r="AO45">
-        <v>0.99554924619735208</v>
+        <v>0.99776348189506514</v>
       </c>
       <c r="AP45">
-        <v>81.597153048545437</v>
+        <v>41.002831923804749</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -14850,16 +14850,16 @@
         <v>597</v>
       </c>
       <c r="Y46" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="Z46" t="s">
         <v>794</v>
       </c>
       <c r="AA46">
-        <v>0.98976542300352621</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB46">
-        <v>187.63391160201948</v>
+        <v>92.674656500591539</v>
       </c>
       <c r="AD46" t="s">
         <v>524</v>
@@ -14892,10 +14892,10 @@
         <v>1073</v>
       </c>
       <c r="AO46">
-        <v>0.99534886842510228</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP46">
-        <v>85.270745539791065</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -14960,16 +14960,16 @@
         <v>599</v>
       </c>
       <c r="Y47" t="s">
-        <v>496</v>
+        <v>444</v>
       </c>
       <c r="Z47" t="s">
         <v>795</v>
       </c>
       <c r="AA47">
-        <v>0.96480371616361149</v>
+        <v>0.99327397587413557</v>
       </c>
       <c r="AB47">
-        <v>645.26520366712316</v>
+        <v>123.31044230751543</v>
       </c>
       <c r="AD47" t="s">
         <v>524</v>
@@ -15070,16 +15070,16 @@
         <v>601</v>
       </c>
       <c r="Y48" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="Z48" t="s">
         <v>796</v>
       </c>
       <c r="AA48">
-        <v>0.99372086165616802</v>
+        <v>0.99588617410922531</v>
       </c>
       <c r="AB48">
-        <v>115.11753630358729</v>
+        <v>75.420141330869626</v>
       </c>
       <c r="AD48" t="s">
         <v>524</v>
@@ -15180,16 +15180,16 @@
         <v>603</v>
       </c>
       <c r="Y49" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="Z49" t="s">
         <v>797</v>
       </c>
       <c r="AA49">
-        <v>0.99478593896263345</v>
+        <v>0.96725161865330156</v>
       </c>
       <c r="AB49">
-        <v>95.59111901838736</v>
+        <v>600.38699135613854</v>
       </c>
       <c r="AD49" t="s">
         <v>524</v>
@@ -15290,16 +15290,16 @@
         <v>605</v>
       </c>
       <c r="Y50" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="Z50" t="s">
         <v>798</v>
       </c>
       <c r="AA50">
-        <v>0.99480158385008166</v>
+        <v>0.98625376775139273</v>
       </c>
       <c r="AB50">
-        <v>95.304296081836526</v>
+        <v>252.01425789113298</v>
       </c>
       <c r="AD50" t="s">
         <v>524</v>
@@ -15400,16 +15400,16 @@
         <v>607</v>
       </c>
       <c r="Y51" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="Z51" t="s">
         <v>799</v>
       </c>
       <c r="AA51">
-        <v>0.99503505617325061</v>
+        <v>0.99260874818585765</v>
       </c>
       <c r="AB51">
-        <v>91.023970157072284</v>
+        <v>135.50628325927707</v>
       </c>
       <c r="AD51" t="s">
         <v>524</v>
@@ -15510,16 +15510,16 @@
         <v>609</v>
       </c>
       <c r="Y52" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="Z52" t="s">
         <v>800</v>
       </c>
       <c r="AA52">
-        <v>0.99549887366825363</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB52">
-        <v>82.52064941535015</v>
+        <v>54.23617409891024</v>
       </c>
       <c r="AD52" t="s">
         <v>524</v>
@@ -15552,10 +15552,10 @@
         <v>1085</v>
       </c>
       <c r="AO52">
-        <v>0.98134982200735632</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP52">
-        <v>341.91992986513412</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15620,16 +15620,16 @@
         <v>611</v>
       </c>
       <c r="Y53" t="s">
-        <v>500</v>
+        <v>428</v>
       </c>
       <c r="Z53" t="s">
-        <v>775</v>
+        <v>801</v>
       </c>
       <c r="AA53">
-        <v>0.96192701971480499</v>
+        <v>0.99781963473721114</v>
       </c>
       <c r="AB53">
-        <v>698.00463856190902</v>
+        <v>39.973363151129654</v>
       </c>
       <c r="AD53" t="s">
         <v>524</v>
@@ -15659,13 +15659,13 @@
         <v>1086</v>
       </c>
       <c r="AN53" t="s">
-        <v>815</v>
+        <v>1087</v>
       </c>
       <c r="AO53">
-        <v>0.98674094240398891</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP53">
-        <v>243.0827225935364</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15730,16 +15730,16 @@
         <v>613</v>
       </c>
       <c r="Y54" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="Z54" t="s">
-        <v>776</v>
+        <v>802</v>
       </c>
       <c r="AA54">
-        <v>0.96219171780159551</v>
+        <v>0.99134608634204613</v>
       </c>
       <c r="AB54">
-        <v>693.1518403040825</v>
+        <v>158.65508372915352</v>
       </c>
       <c r="AD54" t="s">
         <v>524</v>
@@ -15766,16 +15766,16 @@
         <v>951</v>
       </c>
       <c r="AM54" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="AN54" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="AO54">
-        <v>0.9959346869215373</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP54">
-        <v>74.530739771815789</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -15840,16 +15840,16 @@
         <v>615</v>
       </c>
       <c r="Y55" t="s">
-        <v>502</v>
+        <v>452</v>
       </c>
       <c r="Z55" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AA55">
-        <v>0.99649411432543766</v>
+        <v>0.99500961501774632</v>
       </c>
       <c r="AB55">
-        <v>64.274570700309781</v>
+        <v>91.490391341317391</v>
       </c>
       <c r="AD55" t="s">
         <v>524</v>
@@ -15876,16 +15876,16 @@
         <v>953</v>
       </c>
       <c r="AM55" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AN55" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AO55">
-        <v>0.9976320377495026</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP55">
-        <v>43.412641259119624</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -15950,16 +15950,16 @@
         <v>617</v>
       </c>
       <c r="Y56" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="Z56" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="AA56">
-        <v>0.99463967358156791</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB56">
-        <v>98.272651004588909</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD56" t="s">
         <v>524</v>
@@ -15986,16 +15986,16 @@
         <v>955</v>
       </c>
       <c r="AM56" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AN56" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AO56">
-        <v>0.99433447571906541</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP56">
-        <v>103.86794515046822</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16060,16 +16060,16 @@
         <v>619</v>
       </c>
       <c r="Y57" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="Z57" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AA57">
-        <v>0.9919888686303644</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB57">
-        <v>146.87074177665352</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD57" t="s">
         <v>524</v>
@@ -16096,16 +16096,16 @@
         <v>957</v>
       </c>
       <c r="AM57" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AN57" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AO57">
-        <v>0.99688290256322298</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP57">
-        <v>57.146786340912868</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16170,16 +16170,16 @@
         <v>621</v>
       </c>
       <c r="Y58" t="s">
-        <v>415</v>
+        <v>505</v>
       </c>
       <c r="Z58" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="AA58">
-        <v>0.97183849711184567</v>
+        <v>0.99034341169653584</v>
       </c>
       <c r="AB58">
-        <v>516.29421961616231</v>
+        <v>177.03745223017594</v>
       </c>
       <c r="AD58" t="s">
         <v>524</v>
@@ -16206,16 +16206,16 @@
         <v>959</v>
       </c>
       <c r="AM58" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AN58" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AO58">
-        <v>0.99724271030877243</v>
+        <v>0.99500949727727495</v>
       </c>
       <c r="AP58">
-        <v>50.550311005838999</v>
+        <v>91.492549916626857</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16280,16 +16280,16 @@
         <v>623</v>
       </c>
       <c r="Y59" t="s">
-        <v>413</v>
+        <v>465</v>
       </c>
       <c r="Z59" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="AA59">
-        <v>0.99315026975482257</v>
+        <v>0.97804554015715406</v>
       </c>
       <c r="AB59">
-        <v>125.578387828252</v>
+        <v>402.49843045217517</v>
       </c>
       <c r="AD59" t="s">
         <v>524</v>
@@ -16316,16 +16316,16 @@
         <v>961</v>
       </c>
       <c r="AM59" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AN59" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="AO59">
-        <v>0.99473480482648013</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP59">
-        <v>96.528578181196991</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16390,16 +16390,16 @@
         <v>625</v>
       </c>
       <c r="Y60" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="Z60" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="AA60">
-        <v>0.99638114444190684</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB60">
-        <v>66.345685231708771</v>
+        <v>226.88936094280919</v>
       </c>
       <c r="AD60" t="s">
         <v>524</v>
@@ -16426,16 +16426,16 @@
         <v>963</v>
       </c>
       <c r="AM60" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AN60" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="AO60">
-        <v>0.99760255773158468</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP60">
-        <v>43.953108254279897</v>
+        <v>51.309699480432613</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16500,16 +16500,16 @@
         <v>627</v>
       </c>
       <c r="Y61" t="s">
-        <v>484</v>
+        <v>417</v>
       </c>
       <c r="Z61" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AA61">
-        <v>0.98322732678073066</v>
+        <v>0.97627448840453657</v>
       </c>
       <c r="AB61">
-        <v>307.49900901993823</v>
+        <v>434.96771258349719</v>
       </c>
       <c r="AD61" t="s">
         <v>524</v>
@@ -16536,16 +16536,16 @@
         <v>965</v>
       </c>
       <c r="AM61" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AN61" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AO61">
-        <v>0.99766813121902409</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP61">
-        <v>42.750927651225993</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16610,16 +16610,16 @@
         <v>629</v>
       </c>
       <c r="Y62" t="s">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="Z62" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AA62">
-        <v>0.99649199193483273</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB62">
-        <v>64.313481194734194</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD62" t="s">
         <v>524</v>
@@ -16646,16 +16646,16 @@
         <v>967</v>
       </c>
       <c r="AM62" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AN62" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="AO62">
-        <v>0.99544059907537386</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP62">
-        <v>83.589016951479763</v>
+        <v>138.50582323297994</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16720,16 +16720,16 @@
         <v>631</v>
       </c>
       <c r="Y63" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="Z63" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AA63">
-        <v>0.99716560649644992</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB63">
-        <v>51.96388089841895</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD63" t="s">
         <v>524</v>
@@ -16756,16 +16756,16 @@
         <v>969</v>
       </c>
       <c r="AM63" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="AN63" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AO63">
-        <v>0.99527237968252791</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP63">
-        <v>86.673039153654699</v>
+        <v>49.543726018799653</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -16830,16 +16830,16 @@
         <v>633</v>
       </c>
       <c r="Y64" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="Z64" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AA64">
-        <v>0.9946350729064154</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB64">
-        <v>98.356996715718111</v>
+        <v>49.309812409870183</v>
       </c>
       <c r="AD64" t="s">
         <v>524</v>
@@ -16866,16 +16866,16 @@
         <v>971</v>
       </c>
       <c r="AM64" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AN64" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AO64">
-        <v>0.99589340828485295</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP64">
-        <v>75.287514777696231</v>
+        <v>95.557874766001078</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16940,16 +16940,16 @@
         <v>635</v>
       </c>
       <c r="Y65" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="Z65" t="s">
-        <v>775</v>
+        <v>812</v>
       </c>
       <c r="AA65">
-        <v>0.96258244503784818</v>
+        <v>0.99288391401638731</v>
       </c>
       <c r="AB65">
-        <v>685.98850763945075</v>
+        <v>130.46157636623229</v>
       </c>
       <c r="AD65" t="s">
         <v>524</v>
@@ -16976,16 +16976,16 @@
         <v>973</v>
       </c>
       <c r="AM65" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AN65" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="AO65">
-        <v>0.9972012891192491</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP65">
-        <v>51.309699480432613</v>
+        <v>74.464817689622748</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17050,16 +17050,16 @@
         <v>637</v>
       </c>
       <c r="Y66" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="Z66" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="AA66">
-        <v>0.991015135510805</v>
+        <v>0.99146050371560923</v>
       </c>
       <c r="AB66">
-        <v>164.72251563524117</v>
+        <v>156.55743188049695</v>
       </c>
       <c r="AD66" t="s">
         <v>524</v>
@@ -17086,16 +17086,16 @@
         <v>975</v>
       </c>
       <c r="AM66" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="AN66" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="AO66">
-        <v>0.99644815774097173</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP66">
-        <v>65.117108082185538</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17160,16 +17160,16 @@
         <v>639</v>
       </c>
       <c r="Y67" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="Z67" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="AA67">
-        <v>0.99653079856255411</v>
+        <v>0.98077679482096181</v>
       </c>
       <c r="AB67">
-        <v>63.602026353175077</v>
+        <v>352.42542828236634</v>
       </c>
       <c r="AD67" t="s">
         <v>524</v>
@@ -17196,16 +17196,16 @@
         <v>977</v>
       </c>
       <c r="AM67" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="AN67" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AO67">
-        <v>0.98452519237182756</v>
+        <v>0.99664818772595598</v>
       </c>
       <c r="AP67">
-        <v>283.70480651649393</v>
+        <v>61.449891690807455</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17270,16 +17270,16 @@
         <v>641</v>
       </c>
       <c r="Y68" t="s">
-        <v>497</v>
+        <v>418</v>
       </c>
       <c r="Z68" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="AA68">
-        <v>0.98304101862012738</v>
+        <v>0.98976542300352621</v>
       </c>
       <c r="AB68">
-        <v>310.91465863099842</v>
+        <v>187.63391160201948</v>
       </c>
       <c r="AD68" t="s">
         <v>524</v>
@@ -17306,16 +17306,16 @@
         <v>979</v>
       </c>
       <c r="AM68" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="AN68" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="AO68">
-        <v>0.99398479997386135</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP68">
-        <v>110.27866714587458</v>
+        <v>283.70480651649393</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17380,16 +17380,16 @@
         <v>643</v>
       </c>
       <c r="Y69" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="Z69" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="AA69">
-        <v>0.99313763810995603</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB69">
-        <v>125.80996798414014</v>
+        <v>645.26520366712316</v>
       </c>
       <c r="AD69" t="s">
         <v>524</v>
@@ -17416,16 +17416,16 @@
         <v>981</v>
       </c>
       <c r="AM69" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AN69" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AO69">
-        <v>0.99403730604060547</v>
+        <v>0.99398479997386135</v>
       </c>
       <c r="AP69">
-        <v>109.31605592223302</v>
+        <v>110.27866714587458</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17490,16 +17490,16 @@
         <v>645</v>
       </c>
       <c r="Y70" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="Z70" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="AA70">
-        <v>0.96725161865330156</v>
+        <v>0.99372086165616802</v>
       </c>
       <c r="AB70">
-        <v>600.38699135613854</v>
+        <v>115.11753630358729</v>
       </c>
       <c r="AD70" t="s">
         <v>524</v>
@@ -17526,16 +17526,16 @@
         <v>983</v>
       </c>
       <c r="AM70" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AN70" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="AO70">
-        <v>0.99244513691456471</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP70">
-        <v>138.50582323297994</v>
+        <v>109.31605592223302</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17600,16 +17600,16 @@
         <v>647</v>
       </c>
       <c r="Y71" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="Z71" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="AA71">
-        <v>0.98625376775139273</v>
+        <v>0.99478593896263345</v>
       </c>
       <c r="AB71">
-        <v>252.01425789113298</v>
+        <v>95.59111901838736</v>
       </c>
       <c r="AD71" t="s">
         <v>524</v>
@@ -17636,16 +17636,16 @@
         <v>985</v>
       </c>
       <c r="AM71" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="AN71" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AO71">
-        <v>0.99729761494442914</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP71">
-        <v>49.543726018799653</v>
+        <v>105.47547991621673</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17710,16 +17710,16 @@
         <v>649</v>
       </c>
       <c r="Y72" t="s">
-        <v>483</v>
+        <v>435</v>
       </c>
       <c r="Z72" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="AA72">
-        <v>0.99260874818585765</v>
+        <v>0.99480158385008166</v>
       </c>
       <c r="AB72">
-        <v>135.50628325927707</v>
+        <v>95.304296081836526</v>
       </c>
       <c r="AD72" t="s">
         <v>524</v>
@@ -17746,16 +17746,16 @@
         <v>987</v>
       </c>
       <c r="AM72" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="AN72" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="AO72">
-        <v>0.99478775228549088</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP72">
-        <v>95.557874766001078</v>
+        <v>43.581147571379539</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17820,16 +17820,16 @@
         <v>651</v>
       </c>
       <c r="Y73" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="Z73" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="AA73">
-        <v>0.99704166323096854</v>
+        <v>0.99503505617325061</v>
       </c>
       <c r="AB73">
-        <v>54.23617409891024</v>
+        <v>91.023970157072284</v>
       </c>
       <c r="AD73" t="s">
         <v>524</v>
@@ -17856,16 +17856,16 @@
         <v>989</v>
       </c>
       <c r="AM73" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="AN73" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="AO73">
-        <v>0.99593828267147511</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP73">
-        <v>74.464817689622748</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17930,16 +17930,16 @@
         <v>653</v>
       </c>
       <c r="Y74" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="Z74" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="AA74">
-        <v>0.99781963473721114</v>
+        <v>0.99549887366825363</v>
       </c>
       <c r="AB74">
-        <v>39.973363151129654</v>
+        <v>82.52064941535015</v>
       </c>
       <c r="AD74" t="s">
         <v>524</v>
@@ -17966,16 +17966,16 @@
         <v>991</v>
       </c>
       <c r="AM74" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="AN74" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="AO74">
-        <v>0.99729205446773184</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP74">
-        <v>49.645668091582088</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18040,16 +18040,16 @@
         <v>655</v>
       </c>
       <c r="Y75" t="s">
-        <v>445</v>
+        <v>504</v>
       </c>
       <c r="Z75" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="AA75">
-        <v>0.99134608634204613</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB75">
-        <v>158.65508372915352</v>
+        <v>90.443352439796072</v>
       </c>
       <c r="AD75" t="s">
         <v>524</v>
@@ -18076,16 +18076,16 @@
         <v>993</v>
       </c>
       <c r="AM75" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="AN75" t="s">
-        <v>1130</v>
+        <v>828</v>
       </c>
       <c r="AO75">
-        <v>0.99620534810300254</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP75">
-        <v>69.568618111619969</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18150,16 +18150,16 @@
         <v>657</v>
       </c>
       <c r="Y76" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="Z76" t="s">
-        <v>820</v>
+        <v>804</v>
       </c>
       <c r="AA76">
-        <v>0.99500961501774632</v>
+        <v>0.98064868322652787</v>
       </c>
       <c r="AB76">
-        <v>91.490391341317391</v>
+        <v>354.77414084698938</v>
       </c>
       <c r="AD76" t="s">
         <v>524</v>
@@ -18192,10 +18192,10 @@
         <v>1132</v>
       </c>
       <c r="AO76">
-        <v>0.9961850470371636</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP76">
-        <v>69.94080431866837</v>
+        <v>56.159977027506663</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18260,16 +18260,16 @@
         <v>659</v>
       </c>
       <c r="Y77" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="Z77" t="s">
-        <v>775</v>
+        <v>804</v>
       </c>
       <c r="AA77">
-        <v>0.97410572590752698</v>
+        <v>0.97267890273247193</v>
       </c>
       <c r="AB77">
-        <v>474.72835836200494</v>
+        <v>500.88678323801429</v>
       </c>
       <c r="AD77" t="s">
         <v>524</v>
@@ -18302,10 +18302,10 @@
         <v>1134</v>
       </c>
       <c r="AO77">
-        <v>0.99681385284485569</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP77">
-        <v>58.41269784431158</v>
+        <v>58.751500348127372</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18370,16 +18370,16 @@
         <v>661</v>
       </c>
       <c r="Y78" t="s">
-        <v>522</v>
+        <v>409</v>
       </c>
       <c r="Z78" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AA78">
-        <v>0.9934351357667861</v>
+        <v>0.9951188973511842</v>
       </c>
       <c r="AB78">
-        <v>120.35584427558737</v>
+        <v>89.486881894956255</v>
       </c>
       <c r="AD78" t="s">
         <v>524</v>
@@ -18412,10 +18412,10 @@
         <v>1136</v>
       </c>
       <c r="AO78">
-        <v>0.9917253583369573</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP78">
-        <v>151.70176382244892</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18480,16 +18480,16 @@
         <v>663</v>
       </c>
       <c r="Y79" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="Z79" t="s">
-        <v>776</v>
+        <v>824</v>
       </c>
       <c r="AA79">
-        <v>0.97910116787740509</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB79">
-        <v>383.14525558090747</v>
+        <v>78.81162391526847</v>
       </c>
       <c r="AD79" t="s">
         <v>524</v>
@@ -18522,10 +18522,10 @@
         <v>1138</v>
       </c>
       <c r="AO79">
-        <v>0.99274560110857168</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP79">
-        <v>132.99731300951822</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18590,16 +18590,16 @@
         <v>665</v>
       </c>
       <c r="Y80" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="Z80" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="AA80">
-        <v>0.98797270203083642</v>
+        <v>0.98419413291291158</v>
       </c>
       <c r="AB80">
-        <v>220.50046276799787</v>
+        <v>289.77422992995491</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18664,16 +18664,16 @@
         <v>667</v>
       </c>
       <c r="Y81" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="Z81" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="AA81">
-        <v>0.9923817726751798</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB81">
-        <v>139.66750095503775</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18738,16 +18738,16 @@
         <v>669</v>
       </c>
       <c r="Y82" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="Z82" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="AA82">
-        <v>0.99049341406542279</v>
+        <v>0.99394085749709427</v>
       </c>
       <c r="AB82">
-        <v>174.28740880058183</v>
+        <v>111.08427921993857</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -18812,16 +18812,16 @@
         <v>671</v>
       </c>
       <c r="Y83" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="Z83" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AA83">
-        <v>0.99523006105909662</v>
+        <v>0.9565626086601956</v>
       </c>
       <c r="AB83">
-        <v>87.448880583228942</v>
+        <v>796.35217456308078</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -18886,16 +18886,16 @@
         <v>673</v>
       </c>
       <c r="Y84" t="s">
-        <v>504</v>
+        <v>464</v>
       </c>
       <c r="Z84" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="AA84">
-        <v>0.99506672623055659</v>
+        <v>0.98848870678765</v>
       </c>
       <c r="AB84">
-        <v>90.443352439796072</v>
+        <v>211.04037555975037</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -18960,16 +18960,16 @@
         <v>675</v>
       </c>
       <c r="Y85" t="s">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="Z85" t="s">
-        <v>776</v>
+        <v>829</v>
       </c>
       <c r="AA85">
-        <v>0.98064868322652787</v>
+        <v>0.99412748637108239</v>
       </c>
       <c r="AB85">
-        <v>354.77414084698938</v>
+        <v>107.66274986349015</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19034,16 +19034,16 @@
         <v>677</v>
       </c>
       <c r="Y86" t="s">
-        <v>481</v>
+        <v>419</v>
       </c>
       <c r="Z86" t="s">
-        <v>776</v>
+        <v>830</v>
       </c>
       <c r="AA86">
-        <v>0.97267890273247193</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB86">
-        <v>500.88678323801429</v>
+        <v>41.695953373122713</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19108,16 +19108,16 @@
         <v>679</v>
       </c>
       <c r="Y87" t="s">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="Z87" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="AA87">
-        <v>0.9951188973511842</v>
+        <v>0.99382195819286057</v>
       </c>
       <c r="AB87">
-        <v>89.486881894956255</v>
+        <v>113.26409979755675</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19182,16 +19182,16 @@
         <v>681</v>
       </c>
       <c r="Y88" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
       <c r="Z88" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="AA88">
-        <v>0.99570118415007625</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB88">
-        <v>78.81162391526847</v>
+        <v>86.308558527470979</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19256,16 +19256,16 @@
         <v>683</v>
       </c>
       <c r="Y89" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
       <c r="Z89" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="AA89">
-        <v>0.98419413291291158</v>
+        <v>0.9964859002508345</v>
       </c>
       <c r="AB89">
-        <v>289.77422992995491</v>
+        <v>64.425162068034254</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19330,16 +19330,16 @@
         <v>685</v>
       </c>
       <c r="Y90" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="Z90" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="AA90">
-        <v>0.98563153879963317</v>
+        <v>0.9866640001482827</v>
       </c>
       <c r="AB90">
-        <v>263.42178867339101</v>
+        <v>244.49333061481801</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19404,16 +19404,16 @@
         <v>687</v>
       </c>
       <c r="Y91" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="Z91" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AA91">
-        <v>0.99394085749709427</v>
+        <v>0.97166110802369898</v>
       </c>
       <c r="AB91">
-        <v>111.08427921993857</v>
+        <v>519.54635289885152</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19478,16 +19478,16 @@
         <v>689</v>
       </c>
       <c r="Y92" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="Z92" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="AA92">
-        <v>0.95375321856768847</v>
+        <v>0.99353270322428533</v>
       </c>
       <c r="AB92">
-        <v>847.85765959237779</v>
+        <v>118.56710755476936</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19552,16 +19552,16 @@
         <v>691</v>
       </c>
       <c r="Y93" t="s">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="Z93" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="AA93">
-        <v>0.99223209876176832</v>
+        <v>0.99729259940965764</v>
       </c>
       <c r="AB93">
-        <v>142.4115227009143</v>
+        <v>49.635677489608995</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19626,16 +19626,16 @@
         <v>693</v>
       </c>
       <c r="Y94" t="s">
-        <v>512</v>
+        <v>436</v>
       </c>
       <c r="Z94" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="AA94">
-        <v>0.98547237448299074</v>
+        <v>0.99591694828752353</v>
       </c>
       <c r="AB94">
-        <v>266.33980114516959</v>
+        <v>74.855948062068691</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19700,16 +19700,16 @@
         <v>695</v>
       </c>
       <c r="Y95" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="Z95" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="AA95">
-        <v>0.98775140142897844</v>
+        <v>0.99335306489036745</v>
       </c>
       <c r="AB95">
-        <v>224.55764046872929</v>
+        <v>121.86047700993024</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19774,16 +19774,16 @@
         <v>697</v>
       </c>
       <c r="Y96" t="s">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="Z96" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="AA96">
-        <v>0.99660448707980165</v>
+        <v>0.99619719802293027</v>
       </c>
       <c r="AB96">
-        <v>62.251070203636829</v>
+        <v>69.718036246277634</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -19848,16 +19848,16 @@
         <v>699</v>
       </c>
       <c r="Y97" t="s">
-        <v>487</v>
+        <v>441</v>
       </c>
       <c r="Z97" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="AA97">
-        <v>0.99363093646241407</v>
+        <v>0.99557851591679303</v>
       </c>
       <c r="AB97">
-        <v>116.76616485574142</v>
+        <v>81.06054152546038</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -19922,16 +19922,16 @@
         <v>701</v>
       </c>
       <c r="Y98" t="s">
-        <v>433</v>
+        <v>501</v>
       </c>
       <c r="Z98" t="s">
-        <v>838</v>
+        <v>765</v>
       </c>
       <c r="AA98">
-        <v>0.99519314522306834</v>
+        <v>0.97410572590752698</v>
       </c>
       <c r="AB98">
-        <v>88.125670910414172</v>
+        <v>474.72835836200494</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -19996,16 +19996,16 @@
         <v>703</v>
       </c>
       <c r="Y99" t="s">
-        <v>432</v>
+        <v>522</v>
       </c>
       <c r="Z99" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="AA99">
-        <v>0.99494501873633134</v>
+        <v>0.9934351357667861</v>
       </c>
       <c r="AB99">
-        <v>92.674656500591539</v>
+        <v>120.35584427558737</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20070,16 +20070,16 @@
         <v>705</v>
       </c>
       <c r="Y100" t="s">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="Z100" t="s">
-        <v>840</v>
+        <v>804</v>
       </c>
       <c r="AA100">
-        <v>0.99327397587413557</v>
+        <v>0.97910116787740509</v>
       </c>
       <c r="AB100">
-        <v>123.31044230751543</v>
+        <v>383.14525558090747</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20144,16 +20144,16 @@
         <v>707</v>
       </c>
       <c r="Y101" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="Z101" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="AA101">
-        <v>0.99588617410922531</v>
+        <v>0.98797270203083642</v>
       </c>
       <c r="AB101">
-        <v>75.420141330869626</v>
+        <v>220.50046276799787</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20218,16 +20218,16 @@
         <v>709</v>
       </c>
       <c r="Y102" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="Z102" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="AA102">
-        <v>0.97581570155911468</v>
+        <v>0.9923817726751798</v>
       </c>
       <c r="AB102">
-        <v>443.37880474956393</v>
+        <v>139.66750095503775</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20292,16 +20292,16 @@
         <v>711</v>
       </c>
       <c r="Y103" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="Z103" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="AA103">
-        <v>0.98907176997397894</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB103">
-        <v>200.35088381038645</v>
+        <v>174.28740880058183</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20366,16 +20366,16 @@
         <v>713</v>
       </c>
       <c r="Y104" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="Z104" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="AA104">
-        <v>0.9776523073059149</v>
+        <v>0.99523006105909662</v>
       </c>
       <c r="AB104">
-        <v>409.70769939155917</v>
+        <v>87.448880583228942</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20440,16 +20440,16 @@
         <v>715</v>
       </c>
       <c r="Y105" t="s">
-        <v>411</v>
+        <v>500</v>
       </c>
       <c r="Z105" t="s">
-        <v>845</v>
+        <v>765</v>
       </c>
       <c r="AA105">
-        <v>0.99634417822754895</v>
+        <v>0.96192701971480499</v>
       </c>
       <c r="AB105">
-        <v>67.023399161603095</v>
+        <v>698.00463856190902</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20514,16 +20514,16 @@
         <v>717</v>
       </c>
       <c r="Y106" t="s">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="Z106" t="s">
-        <v>846</v>
+        <v>804</v>
       </c>
       <c r="AA106">
-        <v>0.99521210903869584</v>
+        <v>0.96219171780159551</v>
       </c>
       <c r="AB106">
-        <v>87.778000957242412</v>
+        <v>693.1518403040825</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20588,16 +20588,16 @@
         <v>719</v>
       </c>
       <c r="Y107" t="s">
-        <v>437</v>
+        <v>502</v>
       </c>
       <c r="Z107" t="s">
         <v>847</v>
       </c>
       <c r="AA107">
-        <v>0.99623432132689671</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB107">
-        <v>69.037442340226178</v>
+        <v>64.274570700309781</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20662,16 +20662,16 @@
         <v>721</v>
       </c>
       <c r="Y108" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="Z108" t="s">
-        <v>848</v>
+        <v>804</v>
       </c>
       <c r="AA108">
-        <v>0.99476627594399158</v>
+        <v>0.99463967358156791</v>
       </c>
       <c r="AB108">
-        <v>95.951607693487446</v>
+        <v>98.272651004588909</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20736,16 +20736,16 @@
         <v>723</v>
       </c>
       <c r="Y109" t="s">
-        <v>460</v>
+        <v>508</v>
       </c>
       <c r="Z109" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AA109">
-        <v>0.99678217534817648</v>
+        <v>0.9919888686303644</v>
       </c>
       <c r="AB109">
-        <v>58.99345195009743</v>
+        <v>146.87074177665352</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20810,16 +20810,16 @@
         <v>725</v>
       </c>
       <c r="Y110" t="s">
-        <v>456</v>
+        <v>415</v>
       </c>
       <c r="Z110" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AA110">
-        <v>0.99649132983250632</v>
+        <v>0.97183849711184567</v>
       </c>
       <c r="AB110">
-        <v>64.325619737385011</v>
+        <v>516.29421961616231</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -20884,16 +20884,16 @@
         <v>727</v>
       </c>
       <c r="Y111" t="s">
-        <v>521</v>
+        <v>413</v>
       </c>
       <c r="Z111" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AA111">
-        <v>0.9866640001482827</v>
+        <v>0.99315026975482257</v>
       </c>
       <c r="AB111">
-        <v>244.49333061481801</v>
+        <v>125.578387828252</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -20958,16 +20958,16 @@
         <v>729</v>
       </c>
       <c r="Y112" t="s">
-        <v>480</v>
+        <v>424</v>
       </c>
       <c r="Z112" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AA112">
-        <v>0.97166110802369898</v>
+        <v>0.99638114444190684</v>
       </c>
       <c r="AB112">
-        <v>519.54635289885152</v>
+        <v>66.345685231708771</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21032,16 +21032,16 @@
         <v>731</v>
       </c>
       <c r="Y113" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="Z113" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AA113">
-        <v>0.99353270322428533</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB113">
-        <v>118.56710755476936</v>
+        <v>307.49900901993823</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21106,16 +21106,16 @@
         <v>733</v>
       </c>
       <c r="Y114" t="s">
-        <v>429</v>
+        <v>494</v>
       </c>
       <c r="Z114" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AA114">
-        <v>0.99729259940965764</v>
+        <v>0.99649199193483273</v>
       </c>
       <c r="AB114">
-        <v>49.635677489608995</v>
+        <v>64.313481194734194</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21180,16 +21180,16 @@
         <v>735</v>
       </c>
       <c r="Y115" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="Z115" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AA115">
-        <v>0.99591694828752353</v>
+        <v>0.99716560649644992</v>
       </c>
       <c r="AB115">
-        <v>74.855948062068691</v>
+        <v>51.96388089841895</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21254,16 +21254,16 @@
         <v>737</v>
       </c>
       <c r="Y116" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="Z116" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AA116">
-        <v>0.99335306489036745</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB116">
-        <v>121.86047700993024</v>
+        <v>98.356996715718111</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21328,16 +21328,16 @@
         <v>739</v>
       </c>
       <c r="Y117" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="Z117" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AA117">
-        <v>0.99619719802293027</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB117">
-        <v>69.718036246277634</v>
+        <v>443.37880474956393</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21402,16 +21402,16 @@
         <v>741</v>
       </c>
       <c r="Y118" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="Z118" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AA118">
-        <v>0.99557851591679303</v>
+        <v>0.98907176997397894</v>
       </c>
       <c r="AB118">
-        <v>81.06054152546038</v>
+        <v>200.35088381038645</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21476,16 +21476,16 @@
         <v>743</v>
       </c>
       <c r="Y119" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="Z119" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AA119">
-        <v>0.9565626086601956</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB119">
-        <v>796.35217456308078</v>
+        <v>409.70769939155917</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21550,16 +21550,16 @@
         <v>745</v>
       </c>
       <c r="Y120" t="s">
-        <v>464</v>
+        <v>411</v>
       </c>
       <c r="Z120" t="s">
-        <v>776</v>
+        <v>859</v>
       </c>
       <c r="AA120">
-        <v>0.98848870678765</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB120">
-        <v>211.04037555975037</v>
+        <v>67.023399161603095</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21624,16 +21624,16 @@
         <v>747</v>
       </c>
       <c r="Y121" t="s">
-        <v>515</v>
+        <v>426</v>
       </c>
       <c r="Z121" t="s">
         <v>860</v>
       </c>
       <c r="AA121">
-        <v>0.99412748637108239</v>
+        <v>0.99521210903869584</v>
       </c>
       <c r="AB121">
-        <v>107.66274986349015</v>
+        <v>87.778000957242412</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21698,16 +21698,16 @@
         <v>749</v>
       </c>
       <c r="Y122" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="Z122" t="s">
         <v>861</v>
       </c>
       <c r="AA122">
-        <v>0.99772567527055689</v>
+        <v>0.99623432132689671</v>
       </c>
       <c r="AB122">
-        <v>41.695953373122713</v>
+        <v>69.037442340226178</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21772,16 +21772,16 @@
         <v>751</v>
       </c>
       <c r="Y123" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Z123" t="s">
         <v>862</v>
       </c>
       <c r="AA123">
-        <v>0.99382195819286057</v>
+        <v>0.99476627594399158</v>
       </c>
       <c r="AB123">
-        <v>113.26409979755675</v>
+        <v>95.951607693487446</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -21846,16 +21846,16 @@
         <v>753</v>
       </c>
       <c r="Y124" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="Z124" t="s">
         <v>863</v>
       </c>
       <c r="AA124">
-        <v>0.99529226044395613</v>
+        <v>0.99678217534817648</v>
       </c>
       <c r="AB124">
-        <v>86.308558527470979</v>
+        <v>58.99345195009743</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -21920,16 +21920,16 @@
         <v>755</v>
       </c>
       <c r="Y125" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Z125" t="s">
         <v>864</v>
       </c>
       <c r="AA125">
-        <v>0.9964859002508345</v>
+        <v>0.99649132983250632</v>
       </c>
       <c r="AB125">
-        <v>64.425162068034254</v>
+        <v>64.325619737385011</v>
       </c>
     </row>
   </sheetData>
@@ -21938,7 +21938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5559CD3A-92F0-4F04-BEBA-094EF0BBD915}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C488B657-61E2-4614-9928-44C27903CB06}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22050,7 +22050,7 @@
         <v>1257</v>
       </c>
       <c r="K11" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="L11">
         <v>10.563746678268352</v>
@@ -22083,7 +22083,7 @@
         <v>1395</v>
       </c>
       <c r="X11" t="s">
-        <v>1205</v>
+        <v>1230</v>
       </c>
       <c r="Y11">
         <v>47.240250000000003</v>
@@ -22151,7 +22151,7 @@
         <v>1397</v>
       </c>
       <c r="X12" t="s">
-        <v>1238</v>
+        <v>1255</v>
       </c>
       <c r="Y12">
         <v>38.134500000000003</v>
@@ -22186,7 +22186,7 @@
         <v>1261</v>
       </c>
       <c r="K13" t="s">
-        <v>1119</v>
+        <v>1104</v>
       </c>
       <c r="L13">
         <v>4.7713910333636482</v>
@@ -22219,7 +22219,7 @@
         <v>1399</v>
       </c>
       <c r="X13" t="s">
-        <v>1225</v>
+        <v>1243</v>
       </c>
       <c r="Y13">
         <v>46.530749999999998</v>
@@ -22254,7 +22254,7 @@
         <v>1263</v>
       </c>
       <c r="K14" t="s">
-        <v>1084</v>
+        <v>1031</v>
       </c>
       <c r="L14">
         <v>12.404103898825962</v>
@@ -22287,7 +22287,7 @@
         <v>1401</v>
       </c>
       <c r="X14" t="s">
-        <v>1253</v>
+        <v>1208</v>
       </c>
       <c r="Y14">
         <v>21.307500000000001</v>
@@ -22322,7 +22322,7 @@
         <v>1265</v>
       </c>
       <c r="K15" t="s">
-        <v>1062</v>
+        <v>1094</v>
       </c>
       <c r="L15">
         <v>6.1276234637439133</v>
@@ -22355,7 +22355,7 @@
         <v>1403</v>
       </c>
       <c r="X15" t="s">
-        <v>1247</v>
+        <v>1206</v>
       </c>
       <c r="Y15">
         <v>47.747999999999998</v>
@@ -22390,7 +22390,7 @@
         <v>1267</v>
       </c>
       <c r="K16" t="s">
-        <v>1043</v>
+        <v>1064</v>
       </c>
       <c r="L16">
         <v>2.2195844391122765</v>
@@ -22423,7 +22423,7 @@
         <v>1405</v>
       </c>
       <c r="X16" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="Y16">
         <v>40.677</v>
@@ -22458,7 +22458,7 @@
         <v>1269</v>
       </c>
       <c r="K17" t="s">
-        <v>1039</v>
+        <v>1060</v>
       </c>
       <c r="L17">
         <v>3.7614311754340659</v>
@@ -22491,7 +22491,7 @@
         <v>1407</v>
       </c>
       <c r="X17" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="Y17">
         <v>53.033999999999999</v>
@@ -22526,7 +22526,7 @@
         <v>1271</v>
       </c>
       <c r="K18" t="s">
-        <v>1007</v>
+        <v>1124</v>
       </c>
       <c r="L18">
         <v>2.5731779960501728</v>
@@ -22559,7 +22559,7 @@
         <v>1409</v>
       </c>
       <c r="X18" t="s">
-        <v>1207</v>
+        <v>1232</v>
       </c>
       <c r="Y18">
         <v>39.273000000000003</v>
@@ -22594,7 +22594,7 @@
         <v>1273</v>
       </c>
       <c r="K19" t="s">
-        <v>1064</v>
+        <v>1096</v>
       </c>
       <c r="L19">
         <v>1.9040172385939969</v>
@@ -22627,7 +22627,7 @@
         <v>1411</v>
       </c>
       <c r="X19" t="s">
-        <v>1229</v>
+        <v>1247</v>
       </c>
       <c r="Y19">
         <v>32.054250000000003</v>
@@ -22662,7 +22662,7 @@
         <v>1275</v>
       </c>
       <c r="K20" t="s">
-        <v>1005</v>
+        <v>1122</v>
       </c>
       <c r="L20">
         <v>11.884376191048085</v>
@@ -22695,7 +22695,7 @@
         <v>1413</v>
       </c>
       <c r="X20" t="s">
-        <v>1242</v>
+        <v>1201</v>
       </c>
       <c r="Y20">
         <v>32.871749999999999</v>
@@ -22730,7 +22730,7 @@
         <v>1277</v>
       </c>
       <c r="K21" t="s">
-        <v>1097</v>
+        <v>1019</v>
       </c>
       <c r="L21">
         <v>12.246676572623375</v>
@@ -22763,7 +22763,7 @@
         <v>1415</v>
       </c>
       <c r="X21" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="Y21">
         <v>49.244999999999997</v>
@@ -22798,7 +22798,7 @@
         <v>1279</v>
       </c>
       <c r="K22" t="s">
-        <v>1054</v>
+        <v>1131</v>
       </c>
       <c r="L22">
         <v>11.221871479411517</v>
@@ -22831,7 +22831,7 @@
         <v>1417</v>
       </c>
       <c r="X22" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="Y22">
         <v>43.858499999999999</v>
@@ -22866,7 +22866,7 @@
         <v>1281</v>
       </c>
       <c r="K23" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -22899,7 +22899,7 @@
         <v>1419</v>
       </c>
       <c r="X23" t="s">
-        <v>1232</v>
+        <v>1249</v>
       </c>
       <c r="Y23">
         <v>51.427500000000002</v>
@@ -22967,7 +22967,7 @@
         <v>1421</v>
       </c>
       <c r="X24" t="s">
-        <v>1209</v>
+        <v>1234</v>
       </c>
       <c r="Y24">
         <v>19.922999999999998</v>
@@ -23002,7 +23002,7 @@
         <v>1285</v>
       </c>
       <c r="K25" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="L25">
         <v>1.6757541426674882</v>
@@ -23035,7 +23035,7 @@
         <v>1423</v>
       </c>
       <c r="X25" t="s">
-        <v>1249</v>
+        <v>1238</v>
       </c>
       <c r="Y25">
         <v>29.15625</v>
@@ -23070,7 +23070,7 @@
         <v>1287</v>
       </c>
       <c r="K26" t="s">
-        <v>1066</v>
+        <v>1098</v>
       </c>
       <c r="L26">
         <v>0.39959553615654331</v>
@@ -23103,7 +23103,7 @@
         <v>1425</v>
       </c>
       <c r="X26" t="s">
-        <v>1227</v>
+        <v>1245</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23138,7 +23138,7 @@
         <v>1289</v>
       </c>
       <c r="K27" t="s">
-        <v>1121</v>
+        <v>1106</v>
       </c>
       <c r="L27">
         <v>1.7832075556426605</v>
@@ -23171,7 +23171,7 @@
         <v>1427</v>
       </c>
       <c r="X27" t="s">
-        <v>1256</v>
+        <v>1242</v>
       </c>
       <c r="Y27">
         <v>41.647500000000001</v>
@@ -23206,7 +23206,7 @@
         <v>1291</v>
       </c>
       <c r="K28" t="s">
-        <v>1131</v>
+        <v>1086</v>
       </c>
       <c r="L28">
         <v>0.35051099632091098</v>
@@ -23239,7 +23239,7 @@
         <v>1429</v>
       </c>
       <c r="X28" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="Y28">
         <v>3.4402499999999998</v>
@@ -23274,7 +23274,7 @@
         <v>1293</v>
       </c>
       <c r="K29" t="s">
-        <v>1091</v>
+        <v>1038</v>
       </c>
       <c r="L29">
         <v>5.5005105319204732</v>
@@ -23307,7 +23307,7 @@
         <v>1431</v>
       </c>
       <c r="X29" t="s">
-        <v>1231</v>
+        <v>1214</v>
       </c>
       <c r="Y29">
         <v>13.389749999999999</v>
@@ -23375,7 +23375,7 @@
         <v>1433</v>
       </c>
       <c r="X30" t="s">
-        <v>1246</v>
+        <v>1205</v>
       </c>
       <c r="Y30">
         <v>6.9757499999999997</v>
@@ -23410,7 +23410,7 @@
         <v>1297</v>
       </c>
       <c r="K31" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="L31">
         <v>0.65440271382024695</v>
@@ -23443,7 +23443,7 @@
         <v>1435</v>
       </c>
       <c r="X31" t="s">
-        <v>1251</v>
+        <v>1240</v>
       </c>
       <c r="Y31">
         <v>38.154000000000003</v>
@@ -23478,7 +23478,7 @@
         <v>1299</v>
       </c>
       <c r="K32" t="s">
-        <v>1101</v>
+        <v>1023</v>
       </c>
       <c r="L32">
         <v>0.5190595734350465</v>
@@ -23511,7 +23511,7 @@
         <v>1437</v>
       </c>
       <c r="X32" t="s">
-        <v>1244</v>
+        <v>1203</v>
       </c>
       <c r="Y32">
         <v>26.765999999999998</v>
@@ -23546,7 +23546,7 @@
         <v>1301</v>
       </c>
       <c r="K33" t="s">
-        <v>1087</v>
+        <v>1034</v>
       </c>
       <c r="L33">
         <v>0.29505146981926272</v>
@@ -23579,7 +23579,7 @@
         <v>1439</v>
       </c>
       <c r="X33" t="s">
-        <v>1203</v>
+        <v>1228</v>
       </c>
       <c r="Y33">
         <v>35.325000000000003</v>
@@ -23614,7 +23614,7 @@
         <v>1303</v>
       </c>
       <c r="K34" t="s">
-        <v>1099</v>
+        <v>1021</v>
       </c>
       <c r="L34">
         <v>0.28737649325389003</v>
@@ -23647,7 +23647,7 @@
         <v>1441</v>
       </c>
       <c r="X34" t="s">
-        <v>1254</v>
+        <v>1210</v>
       </c>
       <c r="Y34">
         <v>21.510750000000002</v>
@@ -23682,7 +23682,7 @@
         <v>1305</v>
       </c>
       <c r="K35" t="s">
-        <v>1037</v>
+        <v>1058</v>
       </c>
       <c r="L35">
         <v>0.85621181691755843</v>
@@ -23715,7 +23715,7 @@
         <v>1443</v>
       </c>
       <c r="X35" t="s">
-        <v>1240</v>
+        <v>1212</v>
       </c>
       <c r="Y35">
         <v>38.088000000000001</v>
@@ -23750,7 +23750,7 @@
         <v>1307</v>
       </c>
       <c r="K36" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="L36">
         <v>2.2628760328229185</v>
@@ -23783,7 +23783,7 @@
         <v>1445</v>
       </c>
       <c r="X36" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="Y36">
         <v>2.6655000000000002</v>
@@ -23851,7 +23851,7 @@
         <v>1447</v>
       </c>
       <c r="X37" t="s">
-        <v>1211</v>
+        <v>1236</v>
       </c>
       <c r="Y37">
         <v>11.651999999999999</v>
@@ -23886,7 +23886,7 @@
         <v>1311</v>
       </c>
       <c r="K38" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="L38">
         <v>2.5150267058852811</v>
@@ -23919,7 +23919,7 @@
         <v>1449</v>
       </c>
       <c r="X38" t="s">
-        <v>1201</v>
+        <v>1226</v>
       </c>
       <c r="Y38">
         <v>22.338000000000001</v>
@@ -23954,7 +23954,7 @@
         <v>1313</v>
       </c>
       <c r="K39" t="s">
-        <v>1041</v>
+        <v>1062</v>
       </c>
       <c r="L39">
         <v>2.2677057834637031</v>
@@ -23987,7 +23987,7 @@
         <v>1451</v>
       </c>
       <c r="X39" t="s">
-        <v>1236</v>
+        <v>1253</v>
       </c>
       <c r="Y39">
         <v>10.619249999999999</v>
@@ -24022,7 +24022,7 @@
         <v>1315</v>
       </c>
       <c r="K40" t="s">
-        <v>1029</v>
+        <v>1044</v>
       </c>
       <c r="L40">
         <v>4.0509443596880574</v>
@@ -24055,7 +24055,7 @@
         <v>1453</v>
       </c>
       <c r="X40" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24090,7 +24090,7 @@
         <v>1317</v>
       </c>
       <c r="K41" t="s">
-        <v>1129</v>
+        <v>1084</v>
       </c>
       <c r="L41">
         <v>2.4836923620575391</v>
@@ -24123,7 +24123,7 @@
         <v>1455</v>
       </c>
       <c r="X41" t="s">
-        <v>1234</v>
+        <v>1251</v>
       </c>
       <c r="Y41">
         <v>35.486249999999998</v>
@@ -24158,7 +24158,7 @@
         <v>1319</v>
       </c>
       <c r="K42" t="s">
-        <v>1086</v>
+        <v>1033</v>
       </c>
       <c r="L42">
         <v>2.885493974180005</v>
@@ -24193,7 +24193,7 @@
         <v>1321</v>
       </c>
       <c r="K43" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="L43">
         <v>1.5541104167331323</v>
@@ -24228,7 +24228,7 @@
         <v>1323</v>
       </c>
       <c r="K44" t="s">
-        <v>1019</v>
+        <v>1009</v>
       </c>
       <c r="L44">
         <v>2.5222218440883255</v>
@@ -24263,7 +24263,7 @@
         <v>1325</v>
       </c>
       <c r="K45" t="s">
-        <v>1027</v>
+        <v>1017</v>
       </c>
       <c r="L45">
         <v>23.427729543154012</v>
@@ -24298,7 +24298,7 @@
         <v>1327</v>
       </c>
       <c r="K46" t="s">
-        <v>1051</v>
+        <v>1072</v>
       </c>
       <c r="L46">
         <v>1.4999429400795936</v>
@@ -24333,7 +24333,7 @@
         <v>1329</v>
       </c>
       <c r="K47" t="s">
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="L47">
         <v>55.863958629218203</v>
@@ -24368,7 +24368,7 @@
         <v>1331</v>
       </c>
       <c r="K48" t="s">
-        <v>1105</v>
+        <v>1027</v>
       </c>
       <c r="L48">
         <v>17.068804920122925</v>
@@ -24403,7 +24403,7 @@
         <v>1333</v>
       </c>
       <c r="K49" t="s">
-        <v>1095</v>
+        <v>1042</v>
       </c>
       <c r="L49">
         <v>5.3278771181664615</v>
@@ -24438,7 +24438,7 @@
         <v>1335</v>
       </c>
       <c r="K50" t="s">
-        <v>1107</v>
+        <v>1029</v>
       </c>
       <c r="L50">
         <v>21.113356105805089</v>
@@ -24473,7 +24473,7 @@
         <v>1337</v>
       </c>
       <c r="K51" t="s">
-        <v>1068</v>
+        <v>1052</v>
       </c>
       <c r="L51">
         <v>2.3372365278937242</v>
@@ -24508,7 +24508,7 @@
         <v>1339</v>
       </c>
       <c r="K52" t="s">
-        <v>1033</v>
+        <v>1048</v>
       </c>
       <c r="L52">
         <v>4.2648673086521249</v>
@@ -24543,7 +24543,7 @@
         <v>1341</v>
       </c>
       <c r="K53" t="s">
-        <v>1093</v>
+        <v>1040</v>
       </c>
       <c r="L53">
         <v>2.8571480649629004</v>
@@ -24578,7 +24578,7 @@
         <v>1343</v>
       </c>
       <c r="K54" t="s">
-        <v>1003</v>
+        <v>1114</v>
       </c>
       <c r="L54">
         <v>31.544159267579381</v>
@@ -24613,7 +24613,7 @@
         <v>1345</v>
       </c>
       <c r="K55" t="s">
-        <v>1135</v>
+        <v>1090</v>
       </c>
       <c r="L55">
         <v>15.478330347836801</v>
@@ -24648,7 +24648,7 @@
         <v>1347</v>
       </c>
       <c r="K56" t="s">
-        <v>1049</v>
+        <v>1070</v>
       </c>
       <c r="L56">
         <v>18.772499167970881</v>
@@ -24683,7 +24683,7 @@
         <v>1349</v>
       </c>
       <c r="K57" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
       <c r="L57">
         <v>18.904558868579112</v>
@@ -24718,7 +24718,7 @@
         <v>1351</v>
       </c>
       <c r="K58" t="s">
-        <v>1053</v>
+        <v>1130</v>
       </c>
       <c r="L58">
         <v>14.176079891703212</v>
@@ -24753,7 +24753,7 @@
         <v>1353</v>
       </c>
       <c r="K59" t="s">
-        <v>1035</v>
+        <v>1050</v>
       </c>
       <c r="L59">
         <v>0.80973624203950822</v>
@@ -24788,7 +24788,7 @@
         <v>1355</v>
       </c>
       <c r="K60" t="s">
-        <v>1137</v>
+        <v>1092</v>
       </c>
       <c r="L60">
         <v>3.2067222321080848</v>
@@ -24823,7 +24823,7 @@
         <v>1357</v>
       </c>
       <c r="K61" t="s">
-        <v>1127</v>
+        <v>1112</v>
       </c>
       <c r="L61">
         <v>0.66271354737797783</v>
@@ -24858,7 +24858,7 @@
         <v>1359</v>
       </c>
       <c r="K62" t="s">
-        <v>1060</v>
+        <v>1137</v>
       </c>
       <c r="L62">
         <v>1.8183767824138508</v>
@@ -24893,7 +24893,7 @@
         <v>1361</v>
       </c>
       <c r="K63" t="s">
-        <v>1031</v>
+        <v>1046</v>
       </c>
       <c r="L63">
         <v>0.24904319237866104</v>
@@ -24928,7 +24928,7 @@
         <v>1363</v>
       </c>
       <c r="K64" t="s">
-        <v>1089</v>
+        <v>1036</v>
       </c>
       <c r="L64">
         <v>8.2047875916663029E-2</v>
@@ -24963,7 +24963,7 @@
         <v>1365</v>
       </c>
       <c r="K65" t="s">
-        <v>1045</v>
+        <v>1066</v>
       </c>
       <c r="L65">
         <v>11.861012832193515</v>
@@ -24998,7 +24998,7 @@
         <v>1367</v>
       </c>
       <c r="K66" t="s">
-        <v>1009</v>
+        <v>1126</v>
       </c>
       <c r="L66">
         <v>0.74143826937354373</v>
@@ -25033,7 +25033,7 @@
         <v>1369</v>
       </c>
       <c r="K67" t="s">
-        <v>1058</v>
+        <v>1135</v>
       </c>
       <c r="L67">
         <v>5.5201095579611916</v>
@@ -25068,7 +25068,7 @@
         <v>1371</v>
       </c>
       <c r="K68" t="s">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="L68">
         <v>6.8285247240880329</v>
@@ -25103,7 +25103,7 @@
         <v>1373</v>
       </c>
       <c r="K69" t="s">
-        <v>1123</v>
+        <v>1108</v>
       </c>
       <c r="L69">
         <v>14.065249575687433</v>
@@ -25138,7 +25138,7 @@
         <v>1375</v>
       </c>
       <c r="K70" t="s">
-        <v>1047</v>
+        <v>1068</v>
       </c>
       <c r="L70">
         <v>9.3799037679336319</v>
@@ -25173,7 +25173,7 @@
         <v>1377</v>
       </c>
       <c r="K71" t="s">
-        <v>1103</v>
+        <v>1025</v>
       </c>
       <c r="L71">
         <v>42.785830383290261</v>
@@ -25243,7 +25243,7 @@
         <v>1381</v>
       </c>
       <c r="K73" t="s">
-        <v>1011</v>
+        <v>1128</v>
       </c>
       <c r="L73">
         <v>19.787589902082505</v>
@@ -25278,7 +25278,7 @@
         <v>1383</v>
       </c>
       <c r="K74" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
       <c r="L74">
         <v>18.319832830101969</v>
@@ -25313,7 +25313,7 @@
         <v>1385</v>
       </c>
       <c r="K75" t="s">
-        <v>1133</v>
+        <v>1088</v>
       </c>
       <c r="L75">
         <v>6.7551756478058005</v>
@@ -25348,7 +25348,7 @@
         <v>1387</v>
       </c>
       <c r="K76" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25383,7 +25383,7 @@
         <v>1389</v>
       </c>
       <c r="K77" t="s">
-        <v>1070</v>
+        <v>1054</v>
       </c>
       <c r="L77">
         <v>3.5275797249830152</v>
@@ -25418,7 +25418,7 @@
         <v>1391</v>
       </c>
       <c r="K78" t="s">
-        <v>1017</v>
+        <v>1007</v>
       </c>
       <c r="L78">
         <v>0.89663971235601181</v>
@@ -25453,7 +25453,7 @@
         <v>1393</v>
       </c>
       <c r="K79" t="s">
-        <v>1056</v>
+        <v>1133</v>
       </c>
       <c r="L79">
         <v>5.9305458091691294</v>
@@ -25468,7 +25468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959BEAF7-BD9E-4883-8767-4FFE54B9909D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4C76F6-371E-4500-8AA4-562DF27CC81E}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26937,7 +26937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E1AD51-8367-496D-A243-384ACCF0C803}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524F87C-08BA-4F94-9759-A6691D340AD1}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80033F3E-92CA-4DB8-918F-872BFC35BC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{217A0814-0D56-407D-929D-EE4E3B21B02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1705,1026 +1705,1026 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_102</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 102</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_112</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 112</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_100</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 100</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_110</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 110</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_102</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 102</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_112</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 112</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_098</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 98</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_081</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 81</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_115</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 115</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_079</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 79</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>e_BR487-500,e_BR446-500,e_BR515-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR294-500,e_BR236-500,e_BR296-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_w286006777-440</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR221-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR209-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR80-500,e_BR148-500,e_BR120-500,e_BR187-500,e_BR114-500,e_BR164-500,e_BR142-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR305-230,e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w453724535-500,e_BR347-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
+    <t>e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR525-500,e_BR500-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_BR387-500,e_BR354-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR304-500</t>
+  </si>
+  <si>
+    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR246-500,e_BR185-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR363-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR293-500,e_BR282-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
+  </si>
+  <si>
+    <t>e_w201470687-500,e_BR273-230,e_BR270-230,e_BR315-230,e_BR327-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR283-500,e_BR24-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR459-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_BR347-500,e_BR290-500,e_BR283-500,e_BR371-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_BR515-500,e_w302931307-440,e_BR544-500,e_BR632-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_r6844204-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR141-500,e_BR61-500,e_BR125-500</t>
+  </si>
+  <si>
+    <t>e_BR437-500,e_BR373-500,e_w953014442-500,e_BR309-500,e_BR220-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR487-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR300-500,e_BR433-500,e_BR437-500,e_w953014442-500,e_BR309-500</t>
+  </si>
+  <si>
+    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR282-500,e_BR209-500,e_BR302-500,e_BR190-500,e_BR340-500,e_w603494578-500,e_BR194-500,e_BR292-500,e_BR204-500,e_BR187-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR342-230,e_BR327-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
+  </si>
+  <si>
+    <t>e_BR300-500,e_w271191830-500,e_BR310-500,e_BR184-500,e_BR309-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR528-500,e_BR558-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR337-500,e_BR264-500</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w206109551-500,e_BR662-440,e_BR732-500,e_BR673-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR626-440,e_w302901044-440,e_BR673-440,e_BR624-440,e_BR676-440,e_BR676-500,e_BR632-440,e_w174017677-440,e_BR646-440,e_BR663-440</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR371-500,e_BR353-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w225181494-500,e_w172071437-440,e_BR666-440,e_BR764-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR499-500,e_BR462-500,e_BR439-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR657-440,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_w271191830-500,e_BR310-500,e_BR300-500,e_BR171-500</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR587-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR878-500,e_w188465343-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR515-500,e_BR435-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR535-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w307168542-230,e_BR342-230,e_BR411-230,e_BR283-500,e_BR290-500</t>
+  </si>
+  <si>
+    <t>e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR41-500,e_BR37-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR483-500,e_BR571-500,e_BR558-500,e_BR535-500,e_w954122148-500</t>
+  </si>
+  <si>
     <t>e_w168904844-230,e_w168664395-500,e_BR626-440</t>
   </si>
   <si>
     <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
   </si>
   <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w307168542-230,e_BR342-230,e_BR411-230,e_BR283-500,e_BR290-500</t>
-  </si>
-  <si>
-    <t>e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR41-500,e_BR37-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
-  </si>
-  <si>
-    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR483-500,e_BR571-500,e_BR558-500,e_BR535-500,e_w954122148-500</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>e_BR487-500,e_BR446-500,e_BR515-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR294-500,e_BR236-500,e_BR296-500,e_BR321-500,e_BR282-500,e_BR209-500</t>
-  </si>
-  <si>
-    <t>e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_BR52-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR246-500,e_BR185-500,e_BR248-500,e_BR221-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR363-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR293-500,e_BR282-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
-  </si>
-  <si>
-    <t>e_BR347-500,e_BR290-500,e_BR283-500,e_BR371-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_BR515-500,e_w302931307-440,e_BR544-500,e_BR632-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_r6844204-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR119-500,e_BR77-500,e_BR102-500,e_BR141-500,e_BR61-500,e_BR125-500</t>
-  </si>
-  <si>
-    <t>e_BR437-500,e_BR373-500,e_w953014442-500,e_BR309-500,e_BR220-500,e_BR382-500,e_BR333-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w302901044-440,e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_w286006777-440</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_w306104018-500,e_r6844204-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR221-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR209-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR80-500,e_BR148-500,e_BR120-500,e_BR187-500,e_BR114-500,e_BR164-500,e_BR142-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR371-500,e_BR353-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w225181494-500,e_w172071437-440,e_BR666-440,e_BR764-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR499-500,e_BR462-500,e_BR439-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR305-230,e_w284868411-230,e_BR327-230,e_BR315-230,e_BR285-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500,e_BR52-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR642-500,e_BR697-500,e_BR656-500,e_BR685-500,e_BR669-500,e_w287393618-500,e_BR659-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR371-500,e_w168664395-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR657-440,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_w271191830-500,e_BR310-500,e_BR300-500,e_BR171-500</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR528-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR587-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR878-500,e_w188465343-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_w521542011-500,e_BR904-500,e_BR947-525,e_w247684836-500,e_BR903-500,e_BR866-500,e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR367-500,e_BR515-500,e_BR435-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR300-500,e_w271191830-500</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR535-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR487-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR300-500,e_BR433-500,e_BR437-500,e_w953014442-500,e_BR309-500</t>
-  </si>
-  <si>
-    <t>e_BR184-500,e_BR143-500,e_BR119-500,e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR282-500,e_BR209-500,e_BR302-500,e_BR190-500,e_BR340-500,e_w603494578-500,e_BR194-500,e_BR292-500,e_BR204-500,e_BR187-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR342-230,e_BR327-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
-  </si>
-  <si>
-    <t>e_BR300-500,e_w271191830-500,e_BR310-500,e_BR184-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR528-500,e_BR558-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR337-500,e_BR264-500</t>
-  </si>
-  <si>
-    <t>e_w201470687-500,e_BR273-230,e_BR270-230,e_BR315-230,e_BR327-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR283-500,e_BR24-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR459-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500,e_BR285-500,e_w201470687-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w206109551-500,e_BR662-440,e_BR732-500,e_BR673-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR52-500,e_w515552863-500,e_w215284729-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR626-440,e_w302901044-440,e_BR673-440,e_BR624-440,e_BR676-440,e_BR676-500,e_BR632-440,e_w174017677-440,e_BR646-440,e_BR663-440</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w453724535-500,e_BR347-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR525-500,e_BR500-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
-  </si>
-  <si>
-    <t>e_BR387-500,e_BR354-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR304-500</t>
-  </si>
-  <si>
-    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_001</t>
   </si>
   <si>
@@ -2743,6 +2743,156 @@
     <t>connecting wind onshore to buses in cluster 68</t>
   </si>
   <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_034</t>
   </si>
   <si>
@@ -2773,6 +2923,156 @@
     <t>connecting wind onshore to buses in cluster 35</t>
   </si>
   <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_069</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_011</t>
   </si>
   <si>
@@ -2809,168 +3109,6 @@
     <t>connecting wind onshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_031</t>
   </si>
   <si>
@@ -3001,144 +3139,6 @@
     <t>connecting wind onshore to buses in cluster 50</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_069</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
     <t>elc_won_001</t>
   </si>
   <si>
@@ -3157,6 +3157,153 @@
     <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
   </si>
   <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR876-500,e_BR820-500,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR360-500,e_BR344-500,e_BR340-500,e_BR302-500,e_w603494578-500,e_BR292-500,e_w532354815-500,e_BR204-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR400-500,e_BR360-500</t>
+  </si>
+  <si>
     <t>elc_won_034</t>
   </si>
   <si>
@@ -3187,6 +3334,153 @@
     <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
   </si>
   <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
+  </si>
+  <si>
     <t>elc_won_011</t>
   </si>
   <si>
@@ -3223,165 +3517,6 @@
     <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR302-500</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR400-500,e_BR360-500</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_BR159-500,e_BR135-500,e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500,e_BR227-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
     <t>elc_won_031</t>
   </si>
   <si>
@@ -3412,139 +3547,52 @@
     <t>e_BR579-500,e_BR535-500,e_BR499-500</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR866-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR360-500,e_BR344-500,e_BR340-500,e_BR302-500,e_w603494578-500,e_BR292-500,e_w532354815-500,e_BR204-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR876-500,e_BR820-500,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w521542011-500,e_BR838-500,e_BR866-500,e_BR837-500</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_BR381-500,e_BR367-500,e_BR384-500</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_BR1013-525,e_w466973262-525,e_w969586211-525,e_BR984-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_won_069</t>
-  </si>
-  <si>
-    <t>e_BR525-500,e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR500-500</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_BR437-500,e_BR373-500</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR643-500,e_BR627-500,e_BR644-500</t>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wofelc_wof_010</t>
@@ -3565,88 +3613,100 @@
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -3673,64 +3733,46 @@
     <t>connecting wind offshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w108224468-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
   </si>
   <si>
     <t>elc_wof_010</t>
@@ -3748,76 +3790,91 @@
     <t>elc_wof_020</t>
   </si>
   <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_BR37-500,e_BR42-500,e_BR51-500,e_BR46-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_BR1014-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
     <t>elc_wof_005</t>
   </si>
   <si>
     <t>e_BR992-525</t>
   </si>
   <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_025</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w108224468-500,e_BR652-500</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_BR37-500,e_BR42-500,e_BR51-500,e_BR46-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR644-500</t>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w466973262-525,e_BR992-525</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_BR764-440,e_BR758-440,e_BR755-500</t>
   </si>
   <si>
     <t>elc_wof_001</t>
@@ -3842,63 +3899,6 @@
   </si>
   <si>
     <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_BR764-440,e_BR758-440,e_BR755-500</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_BR1014-525,e_BR1013-525,e_w466973262-525</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9646,7 +9646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D37A34C-1B0F-49A4-A4D1-5817DD65E2D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7846EF71-824A-422C-BB10-C639EF945D6F}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9884,16 +9884,16 @@
         <v>525</v>
       </c>
       <c r="Y11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Z11" t="s">
         <v>759</v>
       </c>
       <c r="AA11">
-        <v>0.98578060748142671</v>
+        <v>0.99237710954614877</v>
       </c>
       <c r="AB11">
-        <v>260.68886284051109</v>
+        <v>139.75299165393855</v>
       </c>
       <c r="AD11" t="s">
         <v>524</v>
@@ -9962,10 +9962,10 @@
         <v>1202</v>
       </c>
       <c r="BC11">
-        <v>0.9884421166583558</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD11">
-        <v>211.89452793014343</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10030,16 +10030,16 @@
         <v>529</v>
       </c>
       <c r="Y12" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="Z12" t="s">
         <v>760</v>
       </c>
       <c r="AA12">
-        <v>0.9946911823559148</v>
+        <v>0.99680369125279411</v>
       </c>
       <c r="AB12">
-        <v>97.32832347489618</v>
+        <v>58.598993698774343</v>
       </c>
       <c r="AD12" t="s">
         <v>524</v>
@@ -10105,13 +10105,13 @@
         <v>1203</v>
       </c>
       <c r="BB12" t="s">
-        <v>1204</v>
+        <v>1040</v>
       </c>
       <c r="BC12">
-        <v>0.99420451954813838</v>
+        <v>0.99119386580545066</v>
       </c>
       <c r="BD12">
-        <v>106.25047495079694</v>
+        <v>161.44579356673827</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10176,16 +10176,16 @@
         <v>531</v>
       </c>
       <c r="Y13" t="s">
-        <v>467</v>
+        <v>511</v>
       </c>
       <c r="Z13" t="s">
         <v>761</v>
       </c>
       <c r="AA13">
-        <v>0.98028549885826644</v>
+        <v>0.99321000417798277</v>
       </c>
       <c r="AB13">
-        <v>361.43252093178171</v>
+        <v>124.48325673698231</v>
       </c>
       <c r="AD13" t="s">
         <v>524</v>
@@ -10248,16 +10248,16 @@
         <v>1143</v>
       </c>
       <c r="BA13" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="BB13" t="s">
-        <v>1113</v>
+        <v>835</v>
       </c>
       <c r="BC13">
-        <v>0.99418931598784899</v>
+        <v>0.9924080998261412</v>
       </c>
       <c r="BD13">
-        <v>106.52920688943452</v>
+        <v>139.18483652074559</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10322,16 +10322,16 @@
         <v>533</v>
       </c>
       <c r="Y14" t="s">
-        <v>518</v>
+        <v>461</v>
       </c>
       <c r="Z14" t="s">
         <v>762</v>
       </c>
       <c r="AA14">
-        <v>0.99144230757194385</v>
+        <v>0.99519804750325769</v>
       </c>
       <c r="AB14">
-        <v>156.89102784769577</v>
+        <v>88.03579577360874</v>
       </c>
       <c r="AD14" t="s">
         <v>524</v>
@@ -10364,10 +10364,10 @@
         <v>1010</v>
       </c>
       <c r="AO14">
-        <v>0.9964556860892605</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP14">
-        <v>64.979088363557494</v>
+        <v>430.61202751883985</v>
       </c>
       <c r="AR14" t="s">
         <v>524</v>
@@ -10394,16 +10394,16 @@
         <v>1145</v>
       </c>
       <c r="BA14" t="s">
+        <v>1205</v>
+      </c>
+      <c r="BB14" t="s">
         <v>1206</v>
       </c>
-      <c r="BB14" t="s">
-        <v>1207</v>
-      </c>
       <c r="BC14">
-        <v>0.99196968319234669</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD14">
-        <v>147.22247480697732</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10468,16 +10468,16 @@
         <v>535</v>
       </c>
       <c r="Y15" t="s">
-        <v>517</v>
+        <v>478</v>
       </c>
       <c r="Z15" t="s">
         <v>763</v>
       </c>
       <c r="AA15">
-        <v>0.98863909075879119</v>
+        <v>0.95375321856768847</v>
       </c>
       <c r="AB15">
-        <v>208.2833360888277</v>
+        <v>847.85765959237779</v>
       </c>
       <c r="AD15" t="s">
         <v>524</v>
@@ -10510,10 +10510,10 @@
         <v>1012</v>
       </c>
       <c r="AO15">
-        <v>0.98934663566509429</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP15">
-        <v>195.31167947327185</v>
+        <v>79.268397406829976</v>
       </c>
       <c r="AR15" t="s">
         <v>524</v>
@@ -10540,16 +10540,16 @@
         <v>1147</v>
       </c>
       <c r="BA15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="BB15" t="s">
         <v>1208</v>
       </c>
-      <c r="BB15" t="s">
-        <v>1209</v>
-      </c>
       <c r="BC15">
-        <v>0.99357050471442732</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD15">
-        <v>117.87408023549864</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10614,16 +10614,16 @@
         <v>537</v>
       </c>
       <c r="Y16" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="Z16" t="s">
         <v>764</v>
       </c>
       <c r="AA16">
-        <v>0.99503418876282002</v>
+        <v>0.99223209876176832</v>
       </c>
       <c r="AB16">
-        <v>91.039872681632787</v>
+        <v>142.4115227009143</v>
       </c>
       <c r="AD16" t="s">
         <v>524</v>
@@ -10656,10 +10656,10 @@
         <v>1014</v>
       </c>
       <c r="AO16">
-        <v>0.99503039970536677</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP16">
-        <v>91.109338734942796</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR16" t="s">
         <v>524</v>
@@ -10686,16 +10686,16 @@
         <v>1149</v>
       </c>
       <c r="BA16" t="s">
+        <v>1209</v>
+      </c>
+      <c r="BB16" t="s">
         <v>1210</v>
       </c>
-      <c r="BB16" t="s">
-        <v>1211</v>
-      </c>
       <c r="BC16">
-        <v>0.9807271101910352</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD16">
-        <v>353.33631316435549</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10760,16 +10760,16 @@
         <v>539</v>
       </c>
       <c r="Y17" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="Z17" t="s">
         <v>765</v>
       </c>
       <c r="AA17">
-        <v>0.96258244503784818</v>
+        <v>0.98547237448299074</v>
       </c>
       <c r="AB17">
-        <v>685.98850763945075</v>
+        <v>266.33980114516959</v>
       </c>
       <c r="AD17" t="s">
         <v>524</v>
@@ -10802,10 +10802,10 @@
         <v>1016</v>
       </c>
       <c r="AO17">
-        <v>0.9955955730654259</v>
+        <v>0.99694661611560498</v>
       </c>
       <c r="AP17">
-        <v>80.747827133859133</v>
+        <v>55.978704547242401</v>
       </c>
       <c r="AR17" t="s">
         <v>524</v>
@@ -10832,16 +10832,16 @@
         <v>1151</v>
       </c>
       <c r="BA17" t="s">
+        <v>1211</v>
+      </c>
+      <c r="BB17" t="s">
         <v>1212</v>
       </c>
-      <c r="BB17" t="s">
-        <v>1213</v>
-      </c>
       <c r="BC17">
-        <v>0.98097706415899455</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD17">
-        <v>348.75382375176576</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -10906,16 +10906,16 @@
         <v>541</v>
       </c>
       <c r="Y18" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="Z18" t="s">
         <v>766</v>
       </c>
       <c r="AA18">
-        <v>0.991015135510805</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB18">
-        <v>164.72251563524117</v>
+        <v>224.55764046872929</v>
       </c>
       <c r="AD18" t="s">
         <v>524</v>
@@ -10948,10 +10948,10 @@
         <v>1018</v>
       </c>
       <c r="AO18">
-        <v>0.99710531380540124</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP18">
-        <v>53.069246900976879</v>
+        <v>151.17817104385733</v>
       </c>
       <c r="AR18" t="s">
         <v>524</v>
@@ -10978,16 +10978,16 @@
         <v>1153</v>
       </c>
       <c r="BA18" t="s">
+        <v>1213</v>
+      </c>
+      <c r="BB18" t="s">
         <v>1214</v>
       </c>
-      <c r="BB18" t="s">
-        <v>779</v>
-      </c>
       <c r="BC18">
-        <v>0.97821242976023937</v>
+        <v>0.98097706415899455</v>
       </c>
       <c r="BD18">
-        <v>399.43878772894504</v>
+        <v>348.75382375176576</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11052,16 +11052,16 @@
         <v>543</v>
       </c>
       <c r="Y19" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="Z19" t="s">
         <v>767</v>
       </c>
       <c r="AA19">
-        <v>0.99653079856255411</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB19">
-        <v>63.602026353175077</v>
+        <v>62.251070203636829</v>
       </c>
       <c r="AD19" t="s">
         <v>524</v>
@@ -11094,10 +11094,10 @@
         <v>1020</v>
       </c>
       <c r="AO19">
-        <v>0.99473480482648013</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP19">
-        <v>96.528578181196991</v>
+        <v>107.39028514481463</v>
       </c>
       <c r="AR19" t="s">
         <v>524</v>
@@ -11127,13 +11127,13 @@
         <v>1215</v>
       </c>
       <c r="BB19" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="BC19">
-        <v>0.98806872821788805</v>
+        <v>0.9884421166583558</v>
       </c>
       <c r="BD19">
-        <v>218.73998267205184</v>
+        <v>211.89452793014343</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11198,16 +11198,16 @@
         <v>545</v>
       </c>
       <c r="Y20" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="Z20" t="s">
         <v>768</v>
       </c>
       <c r="AA20">
-        <v>0.98304101862012738</v>
+        <v>0.99363093646241407</v>
       </c>
       <c r="AB20">
-        <v>310.91465863099842</v>
+        <v>116.76616485574142</v>
       </c>
       <c r="AD20" t="s">
         <v>524</v>
@@ -11240,10 +11240,10 @@
         <v>1022</v>
       </c>
       <c r="AO20">
-        <v>0.99760255773158468</v>
+        <v>0.99776348189506514</v>
       </c>
       <c r="AP20">
-        <v>43.953108254279897</v>
+        <v>41.002831923804749</v>
       </c>
       <c r="AR20" t="s">
         <v>524</v>
@@ -11270,16 +11270,16 @@
         <v>1157</v>
       </c>
       <c r="BA20" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="BB20" t="s">
-        <v>1047</v>
+        <v>1218</v>
       </c>
       <c r="BC20">
-        <v>0.99119386580545066</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD20">
-        <v>161.44579356673827</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11344,16 +11344,16 @@
         <v>547</v>
       </c>
       <c r="Y21" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="Z21" t="s">
         <v>769</v>
       </c>
       <c r="AA21">
-        <v>0.99313763810995603</v>
+        <v>0.99519314522306834</v>
       </c>
       <c r="AB21">
-        <v>125.80996798414014</v>
+        <v>88.125670910414172</v>
       </c>
       <c r="AD21" t="s">
         <v>524</v>
@@ -11386,10 +11386,10 @@
         <v>1024</v>
       </c>
       <c r="AO21">
-        <v>0.99766813121902409</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP21">
-        <v>42.750927651225993</v>
+        <v>79.007487588415231</v>
       </c>
       <c r="AR21" t="s">
         <v>524</v>
@@ -11416,16 +11416,16 @@
         <v>1159</v>
       </c>
       <c r="BA21" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="BB21" t="s">
-        <v>800</v>
+        <v>1077</v>
       </c>
       <c r="BC21">
-        <v>0.9924080998261412</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD21">
-        <v>139.18483652074559</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11490,16 +11490,16 @@
         <v>549</v>
       </c>
       <c r="Y22" t="s">
-        <v>509</v>
+        <v>432</v>
       </c>
       <c r="Z22" t="s">
         <v>770</v>
       </c>
       <c r="AA22">
-        <v>0.99237710954614877</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB22">
-        <v>139.75299165393855</v>
+        <v>92.674656500591539</v>
       </c>
       <c r="AD22" t="s">
         <v>524</v>
@@ -11532,10 +11532,10 @@
         <v>1026</v>
       </c>
       <c r="AO22">
-        <v>0.99544059907537386</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP22">
-        <v>83.589016951479763</v>
+        <v>283.70480651649393</v>
       </c>
       <c r="AR22" t="s">
         <v>524</v>
@@ -11562,16 +11562,16 @@
         <v>1161</v>
       </c>
       <c r="BA22" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="BB22" t="s">
-        <v>1219</v>
+        <v>796</v>
       </c>
       <c r="BC22">
-        <v>0.99314574070258299</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD22">
-        <v>125.66142045264445</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11636,16 +11636,16 @@
         <v>551</v>
       </c>
       <c r="Y23" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="Z23" t="s">
         <v>771</v>
       </c>
       <c r="AA23">
-        <v>0.99680369125279411</v>
+        <v>0.99327397587413557</v>
       </c>
       <c r="AB23">
-        <v>58.598993698774343</v>
+        <v>123.31044230751543</v>
       </c>
       <c r="AD23" t="s">
         <v>524</v>
@@ -11678,10 +11678,10 @@
         <v>1028</v>
       </c>
       <c r="AO23">
-        <v>0.99527237968252791</v>
+        <v>0.99398479997386135</v>
       </c>
       <c r="AP23">
-        <v>86.673039153654699</v>
+        <v>110.27866714587458</v>
       </c>
       <c r="AR23" t="s">
         <v>524</v>
@@ -11708,16 +11708,16 @@
         <v>1163</v>
       </c>
       <c r="BA23" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="BB23" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="BC23">
-        <v>0.98163861082146986</v>
+        <v>0.99227438811018465</v>
       </c>
       <c r="BD23">
-        <v>336.62546827305243</v>
+        <v>141.63621797994898</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11782,16 +11782,16 @@
         <v>553</v>
       </c>
       <c r="Y24" t="s">
-        <v>511</v>
+        <v>457</v>
       </c>
       <c r="Z24" t="s">
         <v>772</v>
       </c>
       <c r="AA24">
-        <v>0.99321000417798277</v>
+        <v>0.99588617410922531</v>
       </c>
       <c r="AB24">
-        <v>124.48325673698231</v>
+        <v>75.420141330869626</v>
       </c>
       <c r="AD24" t="s">
         <v>524</v>
@@ -11824,10 +11824,10 @@
         <v>1030</v>
       </c>
       <c r="AO24">
-        <v>0.99589340828485295</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP24">
-        <v>75.287514777696231</v>
+        <v>109.31605592223302</v>
       </c>
       <c r="AR24" t="s">
         <v>524</v>
@@ -11854,16 +11854,16 @@
         <v>1165</v>
       </c>
       <c r="BA24" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="BB24" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="BC24">
-        <v>0.99665799830099</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD24">
-        <v>61.270031148516708</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -11928,16 +11928,16 @@
         <v>555</v>
       </c>
       <c r="Y25" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="Z25" t="s">
         <v>773</v>
       </c>
       <c r="AA25">
-        <v>0.99519804750325769</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB25">
-        <v>88.03579577360874</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD25" t="s">
         <v>524</v>
@@ -11970,10 +11970,10 @@
         <v>1032</v>
       </c>
       <c r="AO25">
-        <v>0.98134982200735632</v>
+        <v>0.99664818772595598</v>
       </c>
       <c r="AP25">
-        <v>341.91992986513412</v>
+        <v>61.449891690807455</v>
       </c>
       <c r="AR25" t="s">
         <v>524</v>
@@ -12000,16 +12000,16 @@
         <v>1167</v>
       </c>
       <c r="BA25" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="BB25" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="BC25">
-        <v>0.98125520899414764</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD25">
-        <v>343.65450177395917</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12074,16 +12074,16 @@
         <v>557</v>
       </c>
       <c r="Y26" t="s">
-        <v>519</v>
+        <v>477</v>
       </c>
       <c r="Z26" t="s">
         <v>774</v>
       </c>
       <c r="AA26">
-        <v>0.99681364926860017</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB26">
-        <v>58.416430075664103</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD26" t="s">
         <v>524</v>
@@ -12113,13 +12113,13 @@
         <v>1033</v>
       </c>
       <c r="AN26" t="s">
-        <v>798</v>
+        <v>1034</v>
       </c>
       <c r="AO26">
-        <v>0.98674094240398891</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP26">
-        <v>243.0827225935364</v>
+        <v>51.309699480432613</v>
       </c>
       <c r="AR26" t="s">
         <v>524</v>
@@ -12146,16 +12146,16 @@
         <v>1169</v>
       </c>
       <c r="BA26" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="BB26" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="BC26">
-        <v>0.99227438811018465</v>
+        <v>0.99375410727160951</v>
       </c>
       <c r="BD26">
-        <v>141.63621797994898</v>
+        <v>114.50803335382533</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12220,16 +12220,16 @@
         <v>559</v>
       </c>
       <c r="Y27" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="Z27" t="s">
         <v>775</v>
       </c>
       <c r="AA27">
-        <v>0.99527450819743701</v>
+        <v>0.99034341169653584</v>
       </c>
       <c r="AB27">
-        <v>86.634016380320446</v>
+        <v>177.03745223017594</v>
       </c>
       <c r="AD27" t="s">
         <v>524</v>
@@ -12256,16 +12256,16 @@
         <v>897</v>
       </c>
       <c r="AM27" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="AN27" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AO27">
-        <v>0.9959346869215373</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP27">
-        <v>74.530739771815789</v>
+        <v>65.117108082185538</v>
       </c>
       <c r="AR27" t="s">
         <v>524</v>
@@ -12292,16 +12292,16 @@
         <v>1171</v>
       </c>
       <c r="BA27" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="BB27" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="BC27">
-        <v>0.9933934749176847</v>
+        <v>0.99538398111052984</v>
       </c>
       <c r="BD27">
-        <v>121.11962650911367</v>
+        <v>84.627012973619784</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12366,16 +12366,16 @@
         <v>561</v>
       </c>
       <c r="Y28" t="s">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="Z28" t="s">
         <v>776</v>
       </c>
       <c r="AA28">
-        <v>0.99136196456122894</v>
+        <v>0.97804554015715406</v>
       </c>
       <c r="AB28">
-        <v>158.36398304413572</v>
+        <v>402.49843045217517</v>
       </c>
       <c r="AD28" t="s">
         <v>524</v>
@@ -12402,16 +12402,16 @@
         <v>899</v>
       </c>
       <c r="AM28" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AN28" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AO28">
-        <v>0.9976320377495026</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP28">
-        <v>43.412641259119624</v>
+        <v>57.905423216266421</v>
       </c>
       <c r="AR28" t="s">
         <v>524</v>
@@ -12438,16 +12438,16 @@
         <v>1173</v>
       </c>
       <c r="BA28" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="BB28" t="s">
-        <v>1231</v>
+        <v>1202</v>
       </c>
       <c r="BC28">
-        <v>0.99120104792145036</v>
+        <v>0.99357050471442732</v>
       </c>
       <c r="BD28">
-        <v>161.31412144007655</v>
+        <v>117.87408023549864</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12512,16 +12512,16 @@
         <v>563</v>
       </c>
       <c r="Y29" t="s">
-        <v>495</v>
+        <v>412</v>
       </c>
       <c r="Z29" t="s">
         <v>777</v>
       </c>
       <c r="AA29">
-        <v>0.99336837071349593</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB29">
-        <v>121.57987025257442</v>
+        <v>226.88936094280919</v>
       </c>
       <c r="AD29" t="s">
         <v>524</v>
@@ -12548,16 +12548,16 @@
         <v>901</v>
       </c>
       <c r="AM29" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AN29" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="AO29">
-        <v>0.99433447571906541</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP29">
-        <v>103.86794515046822</v>
+        <v>58.672645982308907</v>
       </c>
       <c r="AR29" t="s">
         <v>524</v>
@@ -12590,10 +12590,10 @@
         <v>1233</v>
       </c>
       <c r="BC29">
-        <v>0.98946506962487613</v>
+        <v>0.9807271101910352</v>
       </c>
       <c r="BD29">
-        <v>193.14039021060518</v>
+        <v>353.33631316435549</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12658,16 +12658,16 @@
         <v>565</v>
       </c>
       <c r="Y30" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="Z30" t="s">
         <v>778</v>
       </c>
       <c r="AA30">
-        <v>0.99394598112170862</v>
+        <v>0.97627448840453657</v>
       </c>
       <c r="AB30">
-        <v>110.99034610200921</v>
+        <v>434.96771258349719</v>
       </c>
       <c r="AD30" t="s">
         <v>524</v>
@@ -12694,16 +12694,16 @@
         <v>903</v>
       </c>
       <c r="AM30" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="AN30" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AO30">
-        <v>0.99688290256322298</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP30">
-        <v>57.146786340912868</v>
+        <v>168.11001279983091</v>
       </c>
       <c r="AR30" t="s">
         <v>524</v>
@@ -12736,10 +12736,10 @@
         <v>1235</v>
       </c>
       <c r="BC30">
-        <v>0.9959052853503485</v>
+        <v>0.98734189460869326</v>
       </c>
       <c r="BD30">
-        <v>75.06976857694373</v>
+        <v>232.06526550729092</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12804,16 +12804,16 @@
         <v>567</v>
       </c>
       <c r="Y31" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="Z31" t="s">
         <v>779</v>
       </c>
       <c r="AA31">
-        <v>0.99199345857785914</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB31">
-        <v>146.78659273924956</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD31" t="s">
         <v>524</v>
@@ -12840,16 +12840,16 @@
         <v>905</v>
       </c>
       <c r="AM31" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AN31" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AO31">
-        <v>0.99724271030877243</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP31">
-        <v>50.550311005838999</v>
+        <v>214.50192763901472</v>
       </c>
       <c r="AR31" t="s">
         <v>524</v>
@@ -12882,10 +12882,10 @@
         <v>1237</v>
       </c>
       <c r="BC31">
-        <v>0.99542890407822671</v>
+        <v>0.98879241442000787</v>
       </c>
       <c r="BD31">
-        <v>83.803425232511387</v>
+        <v>205.47240229985658</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -12950,16 +12950,16 @@
         <v>569</v>
       </c>
       <c r="Y32" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="Z32" t="s">
         <v>780</v>
       </c>
       <c r="AA32">
-        <v>0.99615640242349235</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB32">
-        <v>70.465955569306928</v>
+        <v>79.971304770340467</v>
       </c>
       <c r="AD32" t="s">
         <v>524</v>
@@ -12986,16 +12986,16 @@
         <v>907</v>
       </c>
       <c r="AM32" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="AN32" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AO32">
-        <v>0.99684152237002188</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP32">
-        <v>57.905423216266421</v>
+        <v>341.91992986513412</v>
       </c>
       <c r="AR32" t="s">
         <v>524</v>
@@ -13028,10 +13028,10 @@
         <v>1239</v>
       </c>
       <c r="BC32">
-        <v>0.98879241442000787</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD32">
-        <v>205.47240229985658</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13096,16 +13096,16 @@
         <v>571</v>
       </c>
       <c r="Y33" t="s">
-        <v>516</v>
+        <v>430</v>
       </c>
       <c r="Z33" t="s">
         <v>781</v>
       </c>
       <c r="AA33">
-        <v>0.99356258288761645</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB33">
-        <v>118.01931372703181</v>
+        <v>49.309812409870183</v>
       </c>
       <c r="AD33" t="s">
         <v>524</v>
@@ -13132,16 +13132,16 @@
         <v>909</v>
       </c>
       <c r="AM33" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AN33" t="s">
-        <v>1047</v>
+        <v>833</v>
       </c>
       <c r="AO33">
-        <v>0.99679967385551038</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP33">
-        <v>58.672645982308907</v>
+        <v>243.0827225935364</v>
       </c>
       <c r="AR33" t="s">
         <v>524</v>
@@ -13171,13 +13171,13 @@
         <v>1240</v>
       </c>
       <c r="BB33" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="BC33">
-        <v>0.98574436213546524</v>
+        <v>0.96816761985420574</v>
       </c>
       <c r="BD33">
-        <v>261.35336084980423</v>
+        <v>583.5936360062276</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13242,16 +13242,16 @@
         <v>573</v>
       </c>
       <c r="Y34" t="s">
-        <v>423</v>
+        <v>503</v>
       </c>
       <c r="Z34" t="s">
         <v>782</v>
       </c>
       <c r="AA34">
-        <v>0.99658191580238853</v>
+        <v>0.97581570155911468</v>
       </c>
       <c r="AB34">
-        <v>62.664876956210314</v>
+        <v>443.37880474956393</v>
       </c>
       <c r="AD34" t="s">
         <v>524</v>
@@ -13284,10 +13284,10 @@
         <v>1049</v>
       </c>
       <c r="AO34">
-        <v>0.99083036293819104</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP34">
-        <v>168.11001279983091</v>
+        <v>74.530739771815789</v>
       </c>
       <c r="AR34" t="s">
         <v>524</v>
@@ -13314,16 +13314,16 @@
         <v>1185</v>
       </c>
       <c r="BA34" t="s">
+        <v>1241</v>
+      </c>
+      <c r="BB34" t="s">
         <v>1242</v>
       </c>
-      <c r="BB34" t="s">
-        <v>1211</v>
-      </c>
       <c r="BC34">
-        <v>0.96816761985420574</v>
+        <v>0.99196968319234669</v>
       </c>
       <c r="BD34">
-        <v>583.5936360062276</v>
+        <v>147.22247480697732</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13388,16 +13388,16 @@
         <v>575</v>
       </c>
       <c r="Y35" t="s">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="Z35" t="s">
         <v>783</v>
       </c>
       <c r="AA35">
-        <v>0.99652977687804423</v>
+        <v>0.98907176997397894</v>
       </c>
       <c r="AB35">
-        <v>63.62075723585545</v>
+        <v>200.35088381038645</v>
       </c>
       <c r="AD35" t="s">
         <v>524</v>
@@ -13430,10 +13430,10 @@
         <v>1051</v>
       </c>
       <c r="AO35">
-        <v>0.98829989485605374</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP35">
-        <v>214.50192763901472</v>
+        <v>43.412641259119624</v>
       </c>
       <c r="AR35" t="s">
         <v>524</v>
@@ -13534,16 +13534,16 @@
         <v>577</v>
       </c>
       <c r="Y36" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="Z36" t="s">
         <v>784</v>
       </c>
       <c r="AA36">
-        <v>0.99356282906984039</v>
+        <v>0.9776523073059149</v>
       </c>
       <c r="AB36">
-        <v>118.01480038625972</v>
+        <v>409.70769939155917</v>
       </c>
       <c r="AD36" t="s">
         <v>524</v>
@@ -13576,10 +13576,10 @@
         <v>1053</v>
       </c>
       <c r="AO36">
-        <v>0.98589595763902149</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP36">
-        <v>258.57410995127316</v>
+        <v>103.86794515046822</v>
       </c>
       <c r="AR36" t="s">
         <v>524</v>
@@ -13680,16 +13680,16 @@
         <v>579</v>
       </c>
       <c r="Y37" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="Z37" t="s">
         <v>785</v>
       </c>
       <c r="AA37">
-        <v>0.99482380895087164</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB37">
-        <v>94.896835900686696</v>
+        <v>67.023399161603095</v>
       </c>
       <c r="AD37" t="s">
         <v>524</v>
@@ -13722,10 +13722,10 @@
         <v>1055</v>
       </c>
       <c r="AO37">
-        <v>0.99554924619735208</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP37">
-        <v>81.597153048545437</v>
+        <v>57.146786340912868</v>
       </c>
       <c r="AR37" t="s">
         <v>524</v>
@@ -13826,16 +13826,16 @@
         <v>581</v>
       </c>
       <c r="Y38" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="Z38" t="s">
         <v>786</v>
       </c>
       <c r="AA38">
-        <v>0.99338478208530079</v>
+        <v>0.99521210903869584</v>
       </c>
       <c r="AB38">
-        <v>121.27899510281891</v>
+        <v>87.778000957242412</v>
       </c>
       <c r="AD38" t="s">
         <v>524</v>
@@ -13868,10 +13868,10 @@
         <v>1057</v>
       </c>
       <c r="AO38">
-        <v>0.99534886842510228</v>
+        <v>0.99724271030877243</v>
       </c>
       <c r="AP38">
-        <v>85.270745539791065</v>
+        <v>50.550311005838999</v>
       </c>
       <c r="AR38" t="s">
         <v>524</v>
@@ -13904,10 +13904,10 @@
         <v>1250</v>
       </c>
       <c r="BC38">
-        <v>0.99232494426983575</v>
+        <v>0.99120104792145036</v>
       </c>
       <c r="BD38">
-        <v>140.70935505301131</v>
+        <v>161.31412144007655</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -13972,16 +13972,16 @@
         <v>583</v>
       </c>
       <c r="Y39" t="s">
-        <v>478</v>
+        <v>437</v>
       </c>
       <c r="Z39" t="s">
         <v>787</v>
       </c>
       <c r="AA39">
-        <v>0.95375321856768847</v>
+        <v>0.99623432132689671</v>
       </c>
       <c r="AB39">
-        <v>847.85765959237779</v>
+        <v>69.037442340226178</v>
       </c>
       <c r="AD39" t="s">
         <v>524</v>
@@ -14014,10 +14014,10 @@
         <v>1059</v>
       </c>
       <c r="AO39">
-        <v>0.97651207122624506</v>
+        <v>0.9964556860892605</v>
       </c>
       <c r="AP39">
-        <v>430.61202751883985</v>
+        <v>64.979088363557494</v>
       </c>
       <c r="AR39" t="s">
         <v>524</v>
@@ -14050,10 +14050,10 @@
         <v>1252</v>
       </c>
       <c r="BC39">
-        <v>0.99375410727160951</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD39">
-        <v>114.50803335382533</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14118,16 +14118,16 @@
         <v>585</v>
       </c>
       <c r="Y40" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="Z40" t="s">
         <v>788</v>
       </c>
       <c r="AA40">
-        <v>0.99223209876176832</v>
+        <v>0.99476627594399158</v>
       </c>
       <c r="AB40">
-        <v>142.4115227009143</v>
+        <v>95.951607693487446</v>
       </c>
       <c r="AD40" t="s">
         <v>524</v>
@@ -14160,10 +14160,10 @@
         <v>1061</v>
       </c>
       <c r="AO40">
-        <v>0.99567626923235475</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP40">
-        <v>79.268397406829976</v>
+        <v>195.31167947327185</v>
       </c>
       <c r="AR40" t="s">
         <v>524</v>
@@ -14196,10 +14196,10 @@
         <v>1254</v>
       </c>
       <c r="BC40">
-        <v>0.99538398111052984</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD40">
-        <v>84.627012973619784</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14264,16 +14264,16 @@
         <v>587</v>
       </c>
       <c r="Y41" t="s">
-        <v>512</v>
+        <v>460</v>
       </c>
       <c r="Z41" t="s">
         <v>789</v>
       </c>
       <c r="AA41">
-        <v>0.98547237448299074</v>
+        <v>0.99678217534817648</v>
       </c>
       <c r="AB41">
-        <v>266.33980114516959</v>
+        <v>58.99345195009743</v>
       </c>
       <c r="AD41" t="s">
         <v>524</v>
@@ -14306,10 +14306,10 @@
         <v>1063</v>
       </c>
       <c r="AO41">
-        <v>0.9974675531234084</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP41">
-        <v>46.428192737512276</v>
+        <v>91.109338734942796</v>
       </c>
       <c r="AR41" t="s">
         <v>524</v>
@@ -14342,10 +14342,10 @@
         <v>1256</v>
       </c>
       <c r="BC41">
-        <v>0.98734189460869326</v>
+        <v>0.99542890407822671</v>
       </c>
       <c r="BD41">
-        <v>232.06526550729092</v>
+        <v>83.803425232511387</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14410,16 +14410,16 @@
         <v>589</v>
       </c>
       <c r="Y42" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
       <c r="Z42" t="s">
         <v>790</v>
       </c>
       <c r="AA42">
-        <v>0.98775140142897844</v>
+        <v>0.99649132983250632</v>
       </c>
       <c r="AB42">
-        <v>224.55764046872929</v>
+        <v>64.325619737385011</v>
       </c>
       <c r="AD42" t="s">
         <v>524</v>
@@ -14452,10 +14452,10 @@
         <v>1065</v>
       </c>
       <c r="AO42">
-        <v>0.99694661611560498</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP42">
-        <v>55.978704547242401</v>
+        <v>80.747827133859133</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14520,16 +14520,16 @@
         <v>591</v>
       </c>
       <c r="Y43" t="s">
-        <v>420</v>
+        <v>519</v>
       </c>
       <c r="Z43" t="s">
         <v>791</v>
       </c>
       <c r="AA43">
-        <v>0.99660448707980165</v>
+        <v>0.99681364926860017</v>
       </c>
       <c r="AB43">
-        <v>62.251070203636829</v>
+        <v>58.416430075664103</v>
       </c>
       <c r="AD43" t="s">
         <v>524</v>
@@ -14562,10 +14562,10 @@
         <v>1067</v>
       </c>
       <c r="AO43">
-        <v>0.99175391794306234</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP43">
-        <v>151.17817104385733</v>
+        <v>53.069246900976879</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14630,16 +14630,16 @@
         <v>593</v>
       </c>
       <c r="Y44" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="Z44" t="s">
         <v>792</v>
       </c>
       <c r="AA44">
-        <v>0.99363093646241407</v>
+        <v>0.99527450819743701</v>
       </c>
       <c r="AB44">
-        <v>116.76616485574142</v>
+        <v>86.634016380320446</v>
       </c>
       <c r="AD44" t="s">
         <v>524</v>
@@ -14672,10 +14672,10 @@
         <v>1069</v>
       </c>
       <c r="AO44">
-        <v>0.99414234808301016</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP44">
-        <v>107.39028514481463</v>
+        <v>138.50582323297994</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14740,16 +14740,16 @@
         <v>595</v>
       </c>
       <c r="Y45" t="s">
-        <v>433</v>
+        <v>493</v>
       </c>
       <c r="Z45" t="s">
         <v>793</v>
       </c>
       <c r="AA45">
-        <v>0.99519314522306834</v>
+        <v>0.99136196456122894</v>
       </c>
       <c r="AB45">
-        <v>88.125670910414172</v>
+        <v>158.36398304413572</v>
       </c>
       <c r="AD45" t="s">
         <v>524</v>
@@ -14782,10 +14782,10 @@
         <v>1071</v>
       </c>
       <c r="AO45">
-        <v>0.99776348189506514</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP45">
-        <v>41.002831923804749</v>
+        <v>49.543726018799653</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -14850,16 +14850,16 @@
         <v>597</v>
       </c>
       <c r="Y46" t="s">
-        <v>432</v>
+        <v>495</v>
       </c>
       <c r="Z46" t="s">
         <v>794</v>
       </c>
       <c r="AA46">
-        <v>0.99494501873633134</v>
+        <v>0.99336837071349593</v>
       </c>
       <c r="AB46">
-        <v>92.674656500591539</v>
+        <v>121.57987025257442</v>
       </c>
       <c r="AD46" t="s">
         <v>524</v>
@@ -14892,10 +14892,10 @@
         <v>1073</v>
       </c>
       <c r="AO46">
-        <v>0.99569050067699549</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP46">
-        <v>79.007487588415231</v>
+        <v>95.557874766001078</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -14960,16 +14960,16 @@
         <v>599</v>
       </c>
       <c r="Y47" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="Z47" t="s">
         <v>795</v>
       </c>
       <c r="AA47">
-        <v>0.99327397587413557</v>
+        <v>0.99394598112170862</v>
       </c>
       <c r="AB47">
-        <v>123.31044230751543</v>
+        <v>110.99034610200921</v>
       </c>
       <c r="AD47" t="s">
         <v>524</v>
@@ -15002,10 +15002,10 @@
         <v>1075</v>
       </c>
       <c r="AO47">
-        <v>0.98996241922424166</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP47">
-        <v>184.02231422223667</v>
+        <v>74.464817689622748</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15070,16 +15070,16 @@
         <v>601</v>
       </c>
       <c r="Y48" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="Z48" t="s">
         <v>796</v>
       </c>
       <c r="AA48">
-        <v>0.99588617410922531</v>
+        <v>0.99199345857785914</v>
       </c>
       <c r="AB48">
-        <v>75.420141330869626</v>
+        <v>146.78659273924956</v>
       </c>
       <c r="AD48" t="s">
         <v>524</v>
@@ -15112,10 +15112,10 @@
         <v>1077</v>
       </c>
       <c r="AO48">
-        <v>0.97416725971121887</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP48">
-        <v>473.60023862765331</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15180,16 +15180,16 @@
         <v>603</v>
       </c>
       <c r="Y49" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="Z49" t="s">
         <v>797</v>
       </c>
       <c r="AA49">
-        <v>0.96725161865330156</v>
+        <v>0.99615640242349235</v>
       </c>
       <c r="AB49">
-        <v>600.38699135613854</v>
+        <v>70.465955569306928</v>
       </c>
       <c r="AD49" t="s">
         <v>524</v>
@@ -15222,10 +15222,10 @@
         <v>1079</v>
       </c>
       <c r="AO49">
-        <v>0.99105808324017197</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP49">
-        <v>163.93514059684662</v>
+        <v>258.57410995127316</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15290,16 +15290,16 @@
         <v>605</v>
       </c>
       <c r="Y50" t="s">
-        <v>414</v>
+        <v>501</v>
       </c>
       <c r="Z50" t="s">
-        <v>798</v>
+        <v>773</v>
       </c>
       <c r="AA50">
-        <v>0.98625376775139273</v>
+        <v>0.97410572590752698</v>
       </c>
       <c r="AB50">
-        <v>252.01425789113298</v>
+        <v>474.72835836200494</v>
       </c>
       <c r="AD50" t="s">
         <v>524</v>
@@ -15332,10 +15332,10 @@
         <v>1081</v>
       </c>
       <c r="AO50">
-        <v>0.99776894175014486</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP50">
-        <v>40.90273458067751</v>
+        <v>81.597153048545437</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15400,16 +15400,16 @@
         <v>607</v>
       </c>
       <c r="Y51" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="Z51" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AA51">
-        <v>0.99260874818585765</v>
+        <v>0.9934351357667861</v>
       </c>
       <c r="AB51">
-        <v>135.50628325927707</v>
+        <v>120.35584427558737</v>
       </c>
       <c r="AD51" t="s">
         <v>524</v>
@@ -15442,10 +15442,10 @@
         <v>1083</v>
       </c>
       <c r="AO51">
-        <v>0.99336049451151065</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP51">
-        <v>121.72426728897108</v>
+        <v>85.270745539791065</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15510,16 +15510,16 @@
         <v>609</v>
       </c>
       <c r="Y52" t="s">
-        <v>427</v>
+        <v>482</v>
       </c>
       <c r="Z52" t="s">
-        <v>800</v>
+        <v>774</v>
       </c>
       <c r="AA52">
-        <v>0.99704166323096854</v>
+        <v>0.97910116787740509</v>
       </c>
       <c r="AB52">
-        <v>54.23617409891024</v>
+        <v>383.14525558090747</v>
       </c>
       <c r="AD52" t="s">
         <v>524</v>
@@ -15552,10 +15552,10 @@
         <v>1085</v>
       </c>
       <c r="AO52">
-        <v>0.99620534810300254</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP52">
-        <v>69.568618111619969</v>
+        <v>105.47547991621673</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15620,16 +15620,16 @@
         <v>611</v>
       </c>
       <c r="Y53" t="s">
-        <v>428</v>
+        <v>474</v>
       </c>
       <c r="Z53" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="AA53">
-        <v>0.99781963473721114</v>
+        <v>0.98797270203083642</v>
       </c>
       <c r="AB53">
-        <v>39.973363151129654</v>
+        <v>220.50046276799787</v>
       </c>
       <c r="AD53" t="s">
         <v>524</v>
@@ -15662,10 +15662,10 @@
         <v>1087</v>
       </c>
       <c r="AO53">
-        <v>0.9961850470371636</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP53">
-        <v>69.94080431866837</v>
+        <v>43.581147571379539</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15730,16 +15730,16 @@
         <v>613</v>
       </c>
       <c r="Y54" t="s">
-        <v>445</v>
+        <v>485</v>
       </c>
       <c r="Z54" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AA54">
-        <v>0.99134608634204613</v>
+        <v>0.9923817726751798</v>
       </c>
       <c r="AB54">
-        <v>158.65508372915352</v>
+        <v>139.66750095503775</v>
       </c>
       <c r="AD54" t="s">
         <v>524</v>
@@ -15772,10 +15772,10 @@
         <v>1089</v>
       </c>
       <c r="AO54">
-        <v>0.99681385284485569</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP54">
-        <v>58.41269784431158</v>
+        <v>64.433996023258757</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -15840,16 +15840,16 @@
         <v>615</v>
       </c>
       <c r="Y55" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="Z55" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="AA55">
-        <v>0.99500961501774632</v>
+        <v>0.99049341406542279</v>
       </c>
       <c r="AB55">
-        <v>91.490391341317391</v>
+        <v>174.28740880058183</v>
       </c>
       <c r="AD55" t="s">
         <v>524</v>
@@ -15882,10 +15882,10 @@
         <v>1091</v>
       </c>
       <c r="AO55">
-        <v>0.9917253583369573</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP55">
-        <v>151.70176382244892</v>
+        <v>101.57889622275951</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -15950,16 +15950,16 @@
         <v>617</v>
       </c>
       <c r="Y56" t="s">
-        <v>498</v>
+        <v>459</v>
       </c>
       <c r="Z56" t="s">
-        <v>765</v>
+        <v>802</v>
       </c>
       <c r="AA56">
-        <v>0.96942910386940295</v>
+        <v>0.99523006105909662</v>
       </c>
       <c r="AB56">
-        <v>560.46642906094564</v>
+        <v>87.448880583228942</v>
       </c>
       <c r="AD56" t="s">
         <v>524</v>
@@ -15989,13 +15989,13 @@
         <v>1092</v>
       </c>
       <c r="AN56" t="s">
-        <v>1093</v>
+        <v>809</v>
       </c>
       <c r="AO56">
-        <v>0.99274560110857168</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP56">
-        <v>132.99731300951822</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16060,16 +16060,16 @@
         <v>619</v>
       </c>
       <c r="Y57" t="s">
-        <v>477</v>
+        <v>516</v>
       </c>
       <c r="Z57" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AA57">
-        <v>0.93980266520001188</v>
+        <v>0.99356258288761645</v>
       </c>
       <c r="AB57">
-        <v>1103.617804666449</v>
+        <v>118.01931372703181</v>
       </c>
       <c r="AD57" t="s">
         <v>524</v>
@@ -16096,16 +16096,16 @@
         <v>957</v>
       </c>
       <c r="AM57" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AN57" t="s">
         <v>1094</v>
       </c>
-      <c r="AN57" t="s">
-        <v>1095</v>
-      </c>
       <c r="AO57">
-        <v>0.98599828568941739</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP57">
-        <v>256.69809569401372</v>
+        <v>56.159977027506663</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16170,16 +16170,16 @@
         <v>621</v>
       </c>
       <c r="Y58" t="s">
-        <v>505</v>
+        <v>423</v>
       </c>
       <c r="Z58" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AA58">
-        <v>0.99034341169653584</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB58">
-        <v>177.03745223017594</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD58" t="s">
         <v>524</v>
@@ -16206,16 +16206,16 @@
         <v>959</v>
       </c>
       <c r="AM58" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AN58" t="s">
         <v>1096</v>
       </c>
-      <c r="AN58" t="s">
-        <v>1097</v>
-      </c>
       <c r="AO58">
-        <v>0.99500949727727495</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP58">
-        <v>91.492549916626857</v>
+        <v>58.751500348127372</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16280,16 +16280,16 @@
         <v>623</v>
       </c>
       <c r="Y59" t="s">
-        <v>465</v>
+        <v>513</v>
       </c>
       <c r="Z59" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AA59">
-        <v>0.97804554015715406</v>
+        <v>0.99652977687804423</v>
       </c>
       <c r="AB59">
-        <v>402.49843045217517</v>
+        <v>63.62075723585545</v>
       </c>
       <c r="AD59" t="s">
         <v>524</v>
@@ -16316,16 +16316,16 @@
         <v>961</v>
       </c>
       <c r="AM59" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AN59" t="s">
         <v>1098</v>
       </c>
-      <c r="AN59" t="s">
-        <v>1099</v>
-      </c>
       <c r="AO59">
-        <v>0.99760247912344124</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP59">
-        <v>43.95454940357709</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16390,16 +16390,16 @@
         <v>625</v>
       </c>
       <c r="Y60" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="Z60" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AA60">
-        <v>0.98762421667584677</v>
+        <v>0.99356282906984039</v>
       </c>
       <c r="AB60">
-        <v>226.88936094280919</v>
+        <v>118.01480038625972</v>
       </c>
       <c r="AD60" t="s">
         <v>524</v>
@@ -16426,16 +16426,16 @@
         <v>963</v>
       </c>
       <c r="AM60" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AN60" t="s">
         <v>1100</v>
       </c>
-      <c r="AN60" t="s">
-        <v>1101</v>
-      </c>
       <c r="AO60">
-        <v>0.9972012891192491</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP60">
-        <v>51.309699480432613</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16500,16 +16500,16 @@
         <v>627</v>
       </c>
       <c r="Y61" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="Z61" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AA61">
-        <v>0.97627448840453657</v>
+        <v>0.99482380895087164</v>
       </c>
       <c r="AB61">
-        <v>434.96771258349719</v>
+        <v>94.896835900686696</v>
       </c>
       <c r="AD61" t="s">
         <v>524</v>
@@ -16536,16 +16536,16 @@
         <v>965</v>
       </c>
       <c r="AM61" t="s">
+        <v>1101</v>
+      </c>
+      <c r="AN61" t="s">
         <v>1102</v>
       </c>
-      <c r="AN61" t="s">
-        <v>1103</v>
-      </c>
       <c r="AO61">
-        <v>0.99644815774097173</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP61">
-        <v>65.117108082185538</v>
+        <v>184.02231422223667</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16610,16 +16610,16 @@
         <v>629</v>
       </c>
       <c r="Y62" t="s">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="Z62" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AA62">
-        <v>0.98289281118622185</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB62">
-        <v>313.63179491926536</v>
+        <v>121.27899510281891</v>
       </c>
       <c r="AD62" t="s">
         <v>524</v>
@@ -16646,16 +16646,16 @@
         <v>967</v>
       </c>
       <c r="AM62" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AN62" t="s">
         <v>1104</v>
       </c>
-      <c r="AN62" t="s">
-        <v>1105</v>
-      </c>
       <c r="AO62">
-        <v>0.99244513691456471</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP62">
-        <v>138.50582323297994</v>
+        <v>473.60023862765331</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16720,16 +16720,16 @@
         <v>631</v>
       </c>
       <c r="Y63" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="Z63" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AA63">
-        <v>0.99563792883070867</v>
+        <v>0.9565626086601956</v>
       </c>
       <c r="AB63">
-        <v>79.971304770340467</v>
+        <v>796.35217456308078</v>
       </c>
       <c r="AD63" t="s">
         <v>524</v>
@@ -16756,16 +16756,16 @@
         <v>969</v>
       </c>
       <c r="AM63" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AN63" t="s">
         <v>1106</v>
       </c>
-      <c r="AN63" t="s">
-        <v>1107</v>
-      </c>
       <c r="AO63">
-        <v>0.99729761494442914</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP63">
-        <v>49.543726018799653</v>
+        <v>163.93514059684662</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -16830,16 +16830,16 @@
         <v>633</v>
       </c>
       <c r="Y64" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="Z64" t="s">
-        <v>811</v>
+        <v>774</v>
       </c>
       <c r="AA64">
-        <v>0.99731037386855248</v>
+        <v>0.98848870678765</v>
       </c>
       <c r="AB64">
-        <v>49.309812409870183</v>
+        <v>211.04037555975037</v>
       </c>
       <c r="AD64" t="s">
         <v>524</v>
@@ -16866,16 +16866,16 @@
         <v>971</v>
       </c>
       <c r="AM64" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AN64" t="s">
         <v>1108</v>
       </c>
-      <c r="AN64" t="s">
-        <v>1109</v>
-      </c>
       <c r="AO64">
-        <v>0.99478775228549088</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP64">
-        <v>95.557874766001078</v>
+        <v>40.90273458067751</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16940,16 +16940,16 @@
         <v>635</v>
       </c>
       <c r="Y65" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="Z65" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="AA65">
-        <v>0.99288391401638731</v>
+        <v>0.99412748637108239</v>
       </c>
       <c r="AB65">
-        <v>130.46157636623229</v>
+        <v>107.66274986349015</v>
       </c>
       <c r="AD65" t="s">
         <v>524</v>
@@ -16976,16 +16976,16 @@
         <v>973</v>
       </c>
       <c r="AM65" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AN65" t="s">
         <v>1110</v>
       </c>
-      <c r="AN65" t="s">
-        <v>1111</v>
-      </c>
       <c r="AO65">
-        <v>0.99593828267147511</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP65">
-        <v>74.464817689622748</v>
+        <v>121.72426728897108</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17050,16 +17050,16 @@
         <v>637</v>
       </c>
       <c r="Y66" t="s">
-        <v>514</v>
+        <v>419</v>
       </c>
       <c r="Z66" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="AA66">
-        <v>0.99146050371560923</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB66">
-        <v>156.55743188049695</v>
+        <v>41.695953373122713</v>
       </c>
       <c r="AD66" t="s">
         <v>524</v>
@@ -17086,16 +17086,16 @@
         <v>975</v>
       </c>
       <c r="AM66" t="s">
+        <v>1111</v>
+      </c>
+      <c r="AN66" t="s">
         <v>1112</v>
       </c>
-      <c r="AN66" t="s">
-        <v>1113</v>
-      </c>
       <c r="AO66">
-        <v>0.99729205446773184</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP66">
-        <v>49.645668091582088</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17160,16 +17160,16 @@
         <v>639</v>
       </c>
       <c r="Y67" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="Z67" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="AA67">
-        <v>0.98077679482096181</v>
+        <v>0.99382195819286057</v>
       </c>
       <c r="AB67">
-        <v>352.42542828236634</v>
+        <v>113.26409979755675</v>
       </c>
       <c r="AD67" t="s">
         <v>524</v>
@@ -17196,16 +17196,16 @@
         <v>977</v>
       </c>
       <c r="AM67" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AN67" t="s">
         <v>1114</v>
       </c>
-      <c r="AN67" t="s">
-        <v>1115</v>
-      </c>
       <c r="AO67">
-        <v>0.99664818772595598</v>
+        <v>0.99500949727727495</v>
       </c>
       <c r="AP67">
-        <v>61.449891690807455</v>
+        <v>91.492549916626857</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17270,16 +17270,16 @@
         <v>641</v>
       </c>
       <c r="Y68" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
       <c r="Z68" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="AA68">
-        <v>0.98976542300352621</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB68">
-        <v>187.63391160201948</v>
+        <v>86.308558527470979</v>
       </c>
       <c r="AD68" t="s">
         <v>524</v>
@@ -17306,16 +17306,16 @@
         <v>979</v>
       </c>
       <c r="AM68" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AN68" t="s">
         <v>1116</v>
       </c>
-      <c r="AN68" t="s">
-        <v>1117</v>
-      </c>
       <c r="AO68">
-        <v>0.98452519237182756</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP68">
-        <v>283.70480651649393</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17380,16 +17380,16 @@
         <v>643</v>
       </c>
       <c r="Y69" t="s">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="Z69" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="AA69">
-        <v>0.96480371616361149</v>
+        <v>0.9964859002508345</v>
       </c>
       <c r="AB69">
-        <v>645.26520366712316</v>
+        <v>64.425162068034254</v>
       </c>
       <c r="AD69" t="s">
         <v>524</v>
@@ -17416,16 +17416,16 @@
         <v>981</v>
       </c>
       <c r="AM69" t="s">
+        <v>1117</v>
+      </c>
+      <c r="AN69" t="s">
         <v>1118</v>
       </c>
-      <c r="AN69" t="s">
-        <v>1119</v>
-      </c>
       <c r="AO69">
-        <v>0.99398479997386135</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP69">
-        <v>110.27866714587458</v>
+        <v>96.528578181196991</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17490,16 +17490,16 @@
         <v>645</v>
       </c>
       <c r="Y70" t="s">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="Z70" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="AA70">
-        <v>0.99372086165616802</v>
+        <v>0.9866640001482827</v>
       </c>
       <c r="AB70">
-        <v>115.11753630358729</v>
+        <v>244.49333061481801</v>
       </c>
       <c r="AD70" t="s">
         <v>524</v>
@@ -17526,16 +17526,16 @@
         <v>983</v>
       </c>
       <c r="AM70" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AN70" t="s">
         <v>1120</v>
       </c>
-      <c r="AN70" t="s">
-        <v>1121</v>
-      </c>
       <c r="AO70">
-        <v>0.99403730604060547</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP70">
-        <v>109.31605592223302</v>
+        <v>43.953108254279897</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17600,16 +17600,16 @@
         <v>647</v>
       </c>
       <c r="Y71" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
       <c r="Z71" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="AA71">
-        <v>0.99478593896263345</v>
+        <v>0.97166110802369898</v>
       </c>
       <c r="AB71">
-        <v>95.59111901838736</v>
+        <v>519.54635289885152</v>
       </c>
       <c r="AD71" t="s">
         <v>524</v>
@@ -17636,16 +17636,16 @@
         <v>985</v>
       </c>
       <c r="AM71" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AN71" t="s">
         <v>1122</v>
       </c>
-      <c r="AN71" t="s">
-        <v>1123</v>
-      </c>
       <c r="AO71">
-        <v>0.99424679200457</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP71">
-        <v>105.47547991621673</v>
+        <v>42.750927651225993</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17710,16 +17710,16 @@
         <v>649</v>
       </c>
       <c r="Y72" t="s">
-        <v>435</v>
+        <v>510</v>
       </c>
       <c r="Z72" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="AA72">
-        <v>0.99480158385008166</v>
+        <v>0.99353270322428533</v>
       </c>
       <c r="AB72">
-        <v>95.304296081836526</v>
+        <v>118.56710755476936</v>
       </c>
       <c r="AD72" t="s">
         <v>524</v>
@@ -17746,16 +17746,16 @@
         <v>987</v>
       </c>
       <c r="AM72" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AN72" t="s">
         <v>1124</v>
       </c>
-      <c r="AN72" t="s">
-        <v>1125</v>
-      </c>
       <c r="AO72">
-        <v>0.99762284649610655</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP72">
-        <v>43.581147571379539</v>
+        <v>83.589016951479763</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17820,16 +17820,16 @@
         <v>651</v>
       </c>
       <c r="Y73" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="Z73" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="AA73">
-        <v>0.99503505617325061</v>
+        <v>0.99729259940965764</v>
       </c>
       <c r="AB73">
-        <v>91.023970157072284</v>
+        <v>49.635677489608995</v>
       </c>
       <c r="AD73" t="s">
         <v>524</v>
@@ -17856,16 +17856,16 @@
         <v>989</v>
       </c>
       <c r="AM73" t="s">
+        <v>1125</v>
+      </c>
+      <c r="AN73" t="s">
         <v>1126</v>
       </c>
-      <c r="AN73" t="s">
-        <v>1127</v>
-      </c>
       <c r="AO73">
-        <v>0.99648541839873139</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP73">
-        <v>64.433996023258757</v>
+        <v>86.673039153654699</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17930,16 +17930,16 @@
         <v>653</v>
       </c>
       <c r="Y74" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="Z74" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AA74">
-        <v>0.99549887366825363</v>
+        <v>0.99591694828752353</v>
       </c>
       <c r="AB74">
-        <v>82.52064941535015</v>
+        <v>74.855948062068691</v>
       </c>
       <c r="AD74" t="s">
         <v>524</v>
@@ -17966,16 +17966,16 @@
         <v>991</v>
       </c>
       <c r="AM74" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AN74" t="s">
         <v>1128</v>
       </c>
-      <c r="AN74" t="s">
-        <v>1129</v>
-      </c>
       <c r="AO74">
-        <v>0.99445933293330402</v>
+        <v>0.99589340828485295</v>
       </c>
       <c r="AP74">
-        <v>101.57889622275951</v>
+        <v>75.287514777696231</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18040,16 +18040,16 @@
         <v>655</v>
       </c>
       <c r="Y75" t="s">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="Z75" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AA75">
-        <v>0.99506672623055659</v>
+        <v>0.99335306489036745</v>
       </c>
       <c r="AB75">
-        <v>90.443352439796072</v>
+        <v>121.86047700993024</v>
       </c>
       <c r="AD75" t="s">
         <v>524</v>
@@ -18076,16 +18076,16 @@
         <v>993</v>
       </c>
       <c r="AM75" t="s">
+        <v>1129</v>
+      </c>
+      <c r="AN75" t="s">
         <v>1130</v>
       </c>
-      <c r="AN75" t="s">
-        <v>828</v>
-      </c>
       <c r="AO75">
-        <v>0.95532613069733086</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP75">
-        <v>819.02093721560016</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18150,16 +18150,16 @@
         <v>657</v>
       </c>
       <c r="Y76" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="Z76" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
       <c r="AA76">
-        <v>0.98064868322652787</v>
+        <v>0.99619719802293027</v>
       </c>
       <c r="AB76">
-        <v>354.77414084698938</v>
+        <v>69.718036246277634</v>
       </c>
       <c r="AD76" t="s">
         <v>524</v>
@@ -18192,10 +18192,10 @@
         <v>1132</v>
       </c>
       <c r="AO76">
-        <v>0.99693672852577231</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP76">
-        <v>56.159977027506663</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18260,16 +18260,16 @@
         <v>659</v>
       </c>
       <c r="Y77" t="s">
-        <v>481</v>
+        <v>441</v>
       </c>
       <c r="Z77" t="s">
-        <v>804</v>
+        <v>822</v>
       </c>
       <c r="AA77">
-        <v>0.97267890273247193</v>
+        <v>0.99557851591679303</v>
       </c>
       <c r="AB77">
-        <v>500.88678323801429</v>
+        <v>81.06054152546038</v>
       </c>
       <c r="AD77" t="s">
         <v>524</v>
@@ -18302,10 +18302,10 @@
         <v>1134</v>
       </c>
       <c r="AO77">
-        <v>0.996795372708284</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP77">
-        <v>58.751500348127372</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18370,16 +18370,16 @@
         <v>661</v>
       </c>
       <c r="Y78" t="s">
-        <v>409</v>
+        <v>500</v>
       </c>
       <c r="Z78" t="s">
-        <v>823</v>
+        <v>773</v>
       </c>
       <c r="AA78">
-        <v>0.9951188973511842</v>
+        <v>0.96192701971480499</v>
       </c>
       <c r="AB78">
-        <v>89.486881894956255</v>
+        <v>698.00463856190902</v>
       </c>
       <c r="AD78" t="s">
         <v>524</v>
@@ -18412,10 +18412,10 @@
         <v>1136</v>
       </c>
       <c r="AO78">
-        <v>0.99374536027070226</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP78">
-        <v>114.668395037126</v>
+        <v>151.70176382244892</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18480,16 +18480,16 @@
         <v>663</v>
       </c>
       <c r="Y79" t="s">
-        <v>410</v>
+        <v>476</v>
       </c>
       <c r="Z79" t="s">
-        <v>824</v>
+        <v>774</v>
       </c>
       <c r="AA79">
-        <v>0.99570118415007625</v>
+        <v>0.96219171780159551</v>
       </c>
       <c r="AB79">
-        <v>78.81162391526847</v>
+        <v>693.1518403040825</v>
       </c>
       <c r="AD79" t="s">
         <v>524</v>
@@ -18522,10 +18522,10 @@
         <v>1138</v>
       </c>
       <c r="AO79">
-        <v>0.9976540150806753</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP79">
-        <v>43.009723520953628</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18590,16 +18590,16 @@
         <v>665</v>
       </c>
       <c r="Y80" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="Z80" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AA80">
-        <v>0.98419413291291158</v>
+        <v>0.99649411432543766</v>
       </c>
       <c r="AB80">
-        <v>289.77422992995491</v>
+        <v>64.274570700309781</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18664,16 +18664,16 @@
         <v>667</v>
       </c>
       <c r="Y81" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="Z81" t="s">
-        <v>826</v>
+        <v>774</v>
       </c>
       <c r="AA81">
-        <v>0.98563153879963317</v>
+        <v>0.99463967358156791</v>
       </c>
       <c r="AB81">
-        <v>263.42178867339101</v>
+        <v>98.272651004588909</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18738,16 +18738,16 @@
         <v>669</v>
       </c>
       <c r="Y82" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="Z82" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="AA82">
-        <v>0.99394085749709427</v>
+        <v>0.9919888686303644</v>
       </c>
       <c r="AB82">
-        <v>111.08427921993857</v>
+        <v>146.87074177665352</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -18812,16 +18812,16 @@
         <v>671</v>
       </c>
       <c r="Y83" t="s">
-        <v>479</v>
+        <v>415</v>
       </c>
       <c r="Z83" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="AA83">
-        <v>0.9565626086601956</v>
+        <v>0.97183849711184567</v>
       </c>
       <c r="AB83">
-        <v>796.35217456308078</v>
+        <v>516.29421961616231</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -18886,16 +18886,16 @@
         <v>673</v>
       </c>
       <c r="Y84" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="Z84" t="s">
-        <v>804</v>
+        <v>826</v>
       </c>
       <c r="AA84">
-        <v>0.98848870678765</v>
+        <v>0.99315026975482257</v>
       </c>
       <c r="AB84">
-        <v>211.04037555975037</v>
+        <v>125.578387828252</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -18960,16 +18960,16 @@
         <v>675</v>
       </c>
       <c r="Y85" t="s">
-        <v>515</v>
+        <v>424</v>
       </c>
       <c r="Z85" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AA85">
-        <v>0.99412748637108239</v>
+        <v>0.99638114444190684</v>
       </c>
       <c r="AB85">
-        <v>107.66274986349015</v>
+        <v>66.345685231708771</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19034,16 +19034,16 @@
         <v>677</v>
       </c>
       <c r="Y86" t="s">
-        <v>419</v>
+        <v>484</v>
       </c>
       <c r="Z86" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="AA86">
-        <v>0.99772567527055689</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB86">
-        <v>41.695953373122713</v>
+        <v>307.49900901993823</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19108,16 +19108,16 @@
         <v>679</v>
       </c>
       <c r="Y87" t="s">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="Z87" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="AA87">
-        <v>0.99382195819286057</v>
+        <v>0.99649199193483273</v>
       </c>
       <c r="AB87">
-        <v>113.26409979755675</v>
+        <v>64.313481194734194</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19182,16 +19182,16 @@
         <v>681</v>
       </c>
       <c r="Y88" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="Z88" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="AA88">
-        <v>0.99529226044395613</v>
+        <v>0.99716560649644992</v>
       </c>
       <c r="AB88">
-        <v>86.308558527470979</v>
+        <v>51.96388089841895</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19256,16 +19256,16 @@
         <v>683</v>
       </c>
       <c r="Y89" t="s">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="Z89" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="AA89">
-        <v>0.9964859002508345</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB89">
-        <v>64.425162068034254</v>
+        <v>98.356996715718111</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19330,16 +19330,16 @@
         <v>685</v>
       </c>
       <c r="Y90" t="s">
-        <v>521</v>
+        <v>475</v>
       </c>
       <c r="Z90" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AA90">
-        <v>0.9866640001482827</v>
+        <v>0.96725161865330156</v>
       </c>
       <c r="AB90">
-        <v>244.49333061481801</v>
+        <v>600.38699135613854</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19404,16 +19404,16 @@
         <v>687</v>
       </c>
       <c r="Y91" t="s">
-        <v>480</v>
+        <v>414</v>
       </c>
       <c r="Z91" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="AA91">
-        <v>0.97166110802369898</v>
+        <v>0.98625376775139273</v>
       </c>
       <c r="AB91">
-        <v>519.54635289885152</v>
+        <v>252.01425789113298</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19478,16 +19478,16 @@
         <v>689</v>
       </c>
       <c r="Y92" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="Z92" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="AA92">
-        <v>0.99353270322428533</v>
+        <v>0.99260874818585765</v>
       </c>
       <c r="AB92">
-        <v>118.56710755476936</v>
+        <v>135.50628325927707</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19552,16 +19552,16 @@
         <v>691</v>
       </c>
       <c r="Y93" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Z93" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="AA93">
-        <v>0.99729259940965764</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB93">
-        <v>49.635677489608995</v>
+        <v>54.23617409891024</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19626,16 +19626,16 @@
         <v>693</v>
       </c>
       <c r="Y94" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="Z94" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="AA94">
-        <v>0.99591694828752353</v>
+        <v>0.99781963473721114</v>
       </c>
       <c r="AB94">
-        <v>74.855948062068691</v>
+        <v>39.973363151129654</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19700,16 +19700,16 @@
         <v>695</v>
       </c>
       <c r="Y95" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="Z95" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AA95">
-        <v>0.99335306489036745</v>
+        <v>0.99134608634204613</v>
       </c>
       <c r="AB95">
-        <v>121.86047700993024</v>
+        <v>158.65508372915352</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19774,16 +19774,16 @@
         <v>697</v>
       </c>
       <c r="Y96" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Z96" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="AA96">
-        <v>0.99619719802293027</v>
+        <v>0.99500961501774632</v>
       </c>
       <c r="AB96">
-        <v>69.718036246277634</v>
+        <v>91.490391341317391</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -19848,16 +19848,16 @@
         <v>699</v>
       </c>
       <c r="Y97" t="s">
-        <v>441</v>
+        <v>506</v>
       </c>
       <c r="Z97" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="AA97">
-        <v>0.99557851591679303</v>
+        <v>0.99288391401638731</v>
       </c>
       <c r="AB97">
-        <v>81.06054152546038</v>
+        <v>130.46157636623229</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -19922,16 +19922,16 @@
         <v>701</v>
       </c>
       <c r="Y98" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="Z98" t="s">
-        <v>765</v>
+        <v>840</v>
       </c>
       <c r="AA98">
-        <v>0.97410572590752698</v>
+        <v>0.99146050371560923</v>
       </c>
       <c r="AB98">
-        <v>474.72835836200494</v>
+        <v>156.55743188049695</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -19996,16 +19996,16 @@
         <v>703</v>
       </c>
       <c r="Y99" t="s">
-        <v>522</v>
+        <v>469</v>
       </c>
       <c r="Z99" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AA99">
-        <v>0.9934351357667861</v>
+        <v>0.98077679482096181</v>
       </c>
       <c r="AB99">
-        <v>120.35584427558737</v>
+        <v>352.42542828236634</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20070,16 +20070,16 @@
         <v>705</v>
       </c>
       <c r="Y100" t="s">
-        <v>482</v>
+        <v>418</v>
       </c>
       <c r="Z100" t="s">
-        <v>804</v>
+        <v>842</v>
       </c>
       <c r="AA100">
-        <v>0.97910116787740509</v>
+        <v>0.98976542300352621</v>
       </c>
       <c r="AB100">
-        <v>383.14525558090747</v>
+        <v>187.63391160201948</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20144,16 +20144,16 @@
         <v>707</v>
       </c>
       <c r="Y101" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="Z101" t="s">
         <v>843</v>
       </c>
       <c r="AA101">
-        <v>0.98797270203083642</v>
+        <v>0.96480371616361149</v>
       </c>
       <c r="AB101">
-        <v>220.50046276799787</v>
+        <v>645.26520366712316</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20218,16 +20218,16 @@
         <v>709</v>
       </c>
       <c r="Y102" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="Z102" t="s">
         <v>844</v>
       </c>
       <c r="AA102">
-        <v>0.9923817726751798</v>
+        <v>0.99372086165616802</v>
       </c>
       <c r="AB102">
-        <v>139.66750095503775</v>
+        <v>115.11753630358729</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20292,16 +20292,16 @@
         <v>711</v>
       </c>
       <c r="Y103" t="s">
-        <v>486</v>
+        <v>434</v>
       </c>
       <c r="Z103" t="s">
         <v>845</v>
       </c>
       <c r="AA103">
-        <v>0.99049341406542279</v>
+        <v>0.99478593896263345</v>
       </c>
       <c r="AB103">
-        <v>174.28740880058183</v>
+        <v>95.59111901838736</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20366,16 +20366,16 @@
         <v>713</v>
       </c>
       <c r="Y104" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="Z104" t="s">
         <v>846</v>
       </c>
       <c r="AA104">
-        <v>0.99523006105909662</v>
+        <v>0.99480158385008166</v>
       </c>
       <c r="AB104">
-        <v>87.448880583228942</v>
+        <v>95.304296081836526</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20440,16 +20440,16 @@
         <v>715</v>
       </c>
       <c r="Y105" t="s">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="Z105" t="s">
-        <v>765</v>
+        <v>847</v>
       </c>
       <c r="AA105">
-        <v>0.96192701971480499</v>
+        <v>0.99503505617325061</v>
       </c>
       <c r="AB105">
-        <v>698.00463856190902</v>
+        <v>91.023970157072284</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20514,16 +20514,16 @@
         <v>717</v>
       </c>
       <c r="Y106" t="s">
-        <v>476</v>
+        <v>431</v>
       </c>
       <c r="Z106" t="s">
-        <v>804</v>
+        <v>848</v>
       </c>
       <c r="AA106">
-        <v>0.96219171780159551</v>
+        <v>0.99549887366825363</v>
       </c>
       <c r="AB106">
-        <v>693.1518403040825</v>
+        <v>82.52064941535015</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20588,16 +20588,16 @@
         <v>719</v>
       </c>
       <c r="Y107" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Z107" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="AA107">
-        <v>0.99649411432543766</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB107">
-        <v>64.274570700309781</v>
+        <v>90.443352439796072</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20662,16 +20662,16 @@
         <v>721</v>
       </c>
       <c r="Y108" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="Z108" t="s">
-        <v>804</v>
+        <v>774</v>
       </c>
       <c r="AA108">
-        <v>0.99463967358156791</v>
+        <v>0.98064868322652787</v>
       </c>
       <c r="AB108">
-        <v>98.272651004588909</v>
+        <v>354.77414084698938</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20736,16 +20736,16 @@
         <v>723</v>
       </c>
       <c r="Y109" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="Z109" t="s">
-        <v>848</v>
+        <v>774</v>
       </c>
       <c r="AA109">
-        <v>0.9919888686303644</v>
+        <v>0.97267890273247193</v>
       </c>
       <c r="AB109">
-        <v>146.87074177665352</v>
+        <v>500.88678323801429</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20810,16 +20810,16 @@
         <v>725</v>
       </c>
       <c r="Y110" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="Z110" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AA110">
-        <v>0.97183849711184567</v>
+        <v>0.9951188973511842</v>
       </c>
       <c r="AB110">
-        <v>516.29421961616231</v>
+        <v>89.486881894956255</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -20884,16 +20884,16 @@
         <v>727</v>
       </c>
       <c r="Y111" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="Z111" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AA111">
-        <v>0.99315026975482257</v>
+        <v>0.99570118415007625</v>
       </c>
       <c r="AB111">
-        <v>125.578387828252</v>
+        <v>78.81162391526847</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -20958,16 +20958,16 @@
         <v>729</v>
       </c>
       <c r="Y112" t="s">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="Z112" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AA112">
-        <v>0.99638114444190684</v>
+        <v>0.98419413291291158</v>
       </c>
       <c r="AB112">
-        <v>66.345685231708771</v>
+        <v>289.77422992995491</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21032,16 +21032,16 @@
         <v>731</v>
       </c>
       <c r="Y113" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="Z113" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AA113">
-        <v>0.98322732678073066</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB113">
-        <v>307.49900901993823</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21106,16 +21106,16 @@
         <v>733</v>
       </c>
       <c r="Y114" t="s">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="Z114" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AA114">
-        <v>0.99649199193483273</v>
+        <v>0.99394085749709427</v>
       </c>
       <c r="AB114">
-        <v>64.313481194734194</v>
+        <v>111.08427921993857</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21180,16 +21180,16 @@
         <v>735</v>
       </c>
       <c r="Y115" t="s">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="Z115" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AA115">
-        <v>0.99716560649644992</v>
+        <v>0.98028549885826644</v>
       </c>
       <c r="AB115">
-        <v>51.96388089841895</v>
+        <v>361.43252093178171</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21254,16 +21254,16 @@
         <v>737</v>
       </c>
       <c r="Y116" t="s">
-        <v>421</v>
+        <v>518</v>
       </c>
       <c r="Z116" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AA116">
-        <v>0.9946350729064154</v>
+        <v>0.99144230757194385</v>
       </c>
       <c r="AB116">
-        <v>98.356996715718111</v>
+        <v>156.89102784769577</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21328,16 +21328,16 @@
         <v>739</v>
       </c>
       <c r="Y117" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="Z117" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AA117">
-        <v>0.97581570155911468</v>
+        <v>0.98863909075879119</v>
       </c>
       <c r="AB117">
-        <v>443.37880474956393</v>
+        <v>208.2833360888277</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21402,16 +21402,16 @@
         <v>741</v>
       </c>
       <c r="Y118" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="Z118" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AA118">
-        <v>0.98907176997397894</v>
+        <v>0.99503418876282002</v>
       </c>
       <c r="AB118">
-        <v>200.35088381038645</v>
+        <v>91.039872681632787</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21476,16 +21476,16 @@
         <v>743</v>
       </c>
       <c r="Y119" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="Z119" t="s">
-        <v>858</v>
+        <v>773</v>
       </c>
       <c r="AA119">
-        <v>0.9776523073059149</v>
+        <v>0.96258244503784818</v>
       </c>
       <c r="AB119">
-        <v>409.70769939155917</v>
+        <v>685.98850763945075</v>
       </c>
     </row>
     <row r="120" spans="2:28">
@@ -21550,16 +21550,16 @@
         <v>745</v>
       </c>
       <c r="Y120" t="s">
-        <v>411</v>
+        <v>520</v>
       </c>
       <c r="Z120" t="s">
         <v>859</v>
       </c>
       <c r="AA120">
-        <v>0.99634417822754895</v>
+        <v>0.991015135510805</v>
       </c>
       <c r="AB120">
-        <v>67.023399161603095</v>
+        <v>164.72251563524117</v>
       </c>
     </row>
     <row r="121" spans="2:28">
@@ -21624,16 +21624,16 @@
         <v>747</v>
       </c>
       <c r="Y121" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Z121" t="s">
         <v>860</v>
       </c>
       <c r="AA121">
-        <v>0.99521210903869584</v>
+        <v>0.99653079856255411</v>
       </c>
       <c r="AB121">
-        <v>87.778000957242412</v>
+        <v>63.602026353175077</v>
       </c>
     </row>
     <row r="122" spans="2:28">
@@ -21698,16 +21698,16 @@
         <v>749</v>
       </c>
       <c r="Y122" t="s">
-        <v>437</v>
+        <v>497</v>
       </c>
       <c r="Z122" t="s">
         <v>861</v>
       </c>
       <c r="AA122">
-        <v>0.99623432132689671</v>
+        <v>0.98304101862012738</v>
       </c>
       <c r="AB122">
-        <v>69.037442340226178</v>
+        <v>310.91465863099842</v>
       </c>
     </row>
     <row r="123" spans="2:28">
@@ -21772,16 +21772,16 @@
         <v>751</v>
       </c>
       <c r="Y123" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="Z123" t="s">
         <v>862</v>
       </c>
       <c r="AA123">
-        <v>0.99476627594399158</v>
+        <v>0.99313763810995603</v>
       </c>
       <c r="AB123">
-        <v>95.951607693487446</v>
+        <v>125.80996798414014</v>
       </c>
     </row>
     <row r="124" spans="2:28">
@@ -21846,16 +21846,16 @@
         <v>753</v>
       </c>
       <c r="Y124" t="s">
-        <v>460</v>
+        <v>507</v>
       </c>
       <c r="Z124" t="s">
         <v>863</v>
       </c>
       <c r="AA124">
-        <v>0.99678217534817648</v>
+        <v>0.98578060748142671</v>
       </c>
       <c r="AB124">
-        <v>58.99345195009743</v>
+        <v>260.68886284051109</v>
       </c>
     </row>
     <row r="125" spans="2:28">
@@ -21920,16 +21920,16 @@
         <v>755</v>
       </c>
       <c r="Y125" t="s">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="Z125" t="s">
         <v>864</v>
       </c>
       <c r="AA125">
-        <v>0.99649132983250632</v>
+        <v>0.9946911823559148</v>
       </c>
       <c r="AB125">
-        <v>64.325619737385011</v>
+        <v>97.32832347489618</v>
       </c>
     </row>
   </sheetData>
@@ -21938,7 +21938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C488B657-61E2-4614-9928-44C27903CB06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08D1DC8-F6E2-4AEE-82FF-02FFCD66449C}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22083,7 +22083,7 @@
         <v>1395</v>
       </c>
       <c r="X11" t="s">
-        <v>1230</v>
+        <v>1249</v>
       </c>
       <c r="Y11">
         <v>47.240250000000003</v>
@@ -22118,7 +22118,7 @@
         <v>1259</v>
       </c>
       <c r="K12" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
       <c r="L12">
         <v>7.4816578037471135</v>
@@ -22151,7 +22151,7 @@
         <v>1397</v>
       </c>
       <c r="X12" t="s">
-        <v>1255</v>
+        <v>1234</v>
       </c>
       <c r="Y12">
         <v>38.134500000000003</v>
@@ -22186,7 +22186,7 @@
         <v>1261</v>
       </c>
       <c r="K13" t="s">
-        <v>1104</v>
+        <v>1068</v>
       </c>
       <c r="L13">
         <v>4.7713910333636482</v>
@@ -22254,7 +22254,7 @@
         <v>1263</v>
       </c>
       <c r="K14" t="s">
-        <v>1031</v>
+        <v>1045</v>
       </c>
       <c r="L14">
         <v>12.404103898825962</v>
@@ -22287,7 +22287,7 @@
         <v>1401</v>
       </c>
       <c r="X14" t="s">
-        <v>1208</v>
+        <v>1231</v>
       </c>
       <c r="Y14">
         <v>21.307500000000001</v>
@@ -22322,7 +22322,7 @@
         <v>1265</v>
       </c>
       <c r="K15" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="L15">
         <v>6.1276234637439133</v>
@@ -22355,7 +22355,7 @@
         <v>1403</v>
       </c>
       <c r="X15" t="s">
-        <v>1206</v>
+        <v>1241</v>
       </c>
       <c r="Y15">
         <v>47.747999999999998</v>
@@ -22390,7 +22390,7 @@
         <v>1267</v>
       </c>
       <c r="K16" t="s">
-        <v>1064</v>
+        <v>1015</v>
       </c>
       <c r="L16">
         <v>2.2195844391122765</v>
@@ -22423,7 +22423,7 @@
         <v>1405</v>
       </c>
       <c r="X16" t="s">
-        <v>1215</v>
+        <v>1201</v>
       </c>
       <c r="Y16">
         <v>40.677</v>
@@ -22458,7 +22458,7 @@
         <v>1269</v>
       </c>
       <c r="K17" t="s">
-        <v>1060</v>
+        <v>1011</v>
       </c>
       <c r="L17">
         <v>3.7614311754340659</v>
@@ -22491,7 +22491,7 @@
         <v>1407</v>
       </c>
       <c r="X17" t="s">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="Y17">
         <v>53.033999999999999</v>
@@ -22526,7 +22526,7 @@
         <v>1271</v>
       </c>
       <c r="K18" t="s">
-        <v>1124</v>
+        <v>1086</v>
       </c>
       <c r="L18">
         <v>2.5731779960501728</v>
@@ -22559,7 +22559,7 @@
         <v>1409</v>
       </c>
       <c r="X18" t="s">
-        <v>1232</v>
+        <v>1251</v>
       </c>
       <c r="Y18">
         <v>39.273000000000003</v>
@@ -22594,7 +22594,7 @@
         <v>1273</v>
       </c>
       <c r="K19" t="s">
-        <v>1096</v>
+        <v>1113</v>
       </c>
       <c r="L19">
         <v>1.9040172385939969</v>
@@ -22662,7 +22662,7 @@
         <v>1275</v>
       </c>
       <c r="K20" t="s">
-        <v>1122</v>
+        <v>1084</v>
       </c>
       <c r="L20">
         <v>11.884376191048085</v>
@@ -22695,7 +22695,7 @@
         <v>1413</v>
       </c>
       <c r="X20" t="s">
-        <v>1201</v>
+        <v>1215</v>
       </c>
       <c r="Y20">
         <v>32.871749999999999</v>
@@ -22730,7 +22730,7 @@
         <v>1277</v>
       </c>
       <c r="K21" t="s">
-        <v>1019</v>
+        <v>1117</v>
       </c>
       <c r="L21">
         <v>12.246676572623375</v>
@@ -22763,7 +22763,7 @@
         <v>1415</v>
       </c>
       <c r="X21" t="s">
-        <v>1217</v>
+        <v>1204</v>
       </c>
       <c r="Y21">
         <v>49.244999999999997</v>
@@ -22798,7 +22798,7 @@
         <v>1279</v>
       </c>
       <c r="K22" t="s">
-        <v>1131</v>
+        <v>1093</v>
       </c>
       <c r="L22">
         <v>11.221871479411517</v>
@@ -22831,7 +22831,7 @@
         <v>1417</v>
       </c>
       <c r="X22" t="s">
-        <v>1218</v>
+        <v>1205</v>
       </c>
       <c r="Y22">
         <v>43.858499999999999</v>
@@ -22866,7 +22866,7 @@
         <v>1281</v>
       </c>
       <c r="K23" t="s">
-        <v>1120</v>
+        <v>1029</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -22899,7 +22899,7 @@
         <v>1419</v>
       </c>
       <c r="X23" t="s">
-        <v>1249</v>
+        <v>1225</v>
       </c>
       <c r="Y23">
         <v>51.427500000000002</v>
@@ -22934,7 +22934,7 @@
         <v>1283</v>
       </c>
       <c r="K24" t="s">
-        <v>1074</v>
+        <v>1101</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -22967,7 +22967,7 @@
         <v>1421</v>
       </c>
       <c r="X24" t="s">
-        <v>1234</v>
+        <v>1253</v>
       </c>
       <c r="Y24">
         <v>19.922999999999998</v>
@@ -23002,7 +23002,7 @@
         <v>1285</v>
       </c>
       <c r="K25" t="s">
-        <v>1100</v>
+        <v>1033</v>
       </c>
       <c r="L25">
         <v>1.6757541426674882</v>
@@ -23035,7 +23035,7 @@
         <v>1423</v>
       </c>
       <c r="X25" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="Y25">
         <v>29.15625</v>
@@ -23070,7 +23070,7 @@
         <v>1287</v>
       </c>
       <c r="K26" t="s">
-        <v>1098</v>
+        <v>1115</v>
       </c>
       <c r="L26">
         <v>0.39959553615654331</v>
@@ -23138,7 +23138,7 @@
         <v>1289</v>
       </c>
       <c r="K27" t="s">
-        <v>1106</v>
+        <v>1070</v>
       </c>
       <c r="L27">
         <v>1.7832075556426605</v>
@@ -23171,7 +23171,7 @@
         <v>1427</v>
       </c>
       <c r="X27" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="Y27">
         <v>41.647500000000001</v>
@@ -23206,7 +23206,7 @@
         <v>1291</v>
       </c>
       <c r="K28" t="s">
-        <v>1086</v>
+        <v>1131</v>
       </c>
       <c r="L28">
         <v>0.35051099632091098</v>
@@ -23239,7 +23239,7 @@
         <v>1429</v>
       </c>
       <c r="X28" t="s">
-        <v>1220</v>
+        <v>1207</v>
       </c>
       <c r="Y28">
         <v>3.4402499999999998</v>
@@ -23274,7 +23274,7 @@
         <v>1293</v>
       </c>
       <c r="K29" t="s">
-        <v>1038</v>
+        <v>1052</v>
       </c>
       <c r="L29">
         <v>5.5005105319204732</v>
@@ -23307,7 +23307,7 @@
         <v>1431</v>
       </c>
       <c r="X29" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="Y29">
         <v>13.389749999999999</v>
@@ -23342,7 +23342,7 @@
         <v>1295</v>
       </c>
       <c r="K30" t="s">
-        <v>1080</v>
+        <v>1107</v>
       </c>
       <c r="L30">
         <v>0.34625959029864795</v>
@@ -23375,7 +23375,7 @@
         <v>1433</v>
       </c>
       <c r="X30" t="s">
-        <v>1205</v>
+        <v>1219</v>
       </c>
       <c r="Y30">
         <v>6.9757499999999997</v>
@@ -23410,7 +23410,7 @@
         <v>1297</v>
       </c>
       <c r="K31" t="s">
-        <v>1013</v>
+        <v>1062</v>
       </c>
       <c r="L31">
         <v>0.65440271382024695</v>
@@ -23443,7 +23443,7 @@
         <v>1435</v>
       </c>
       <c r="X31" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="Y31">
         <v>38.154000000000003</v>
@@ -23478,7 +23478,7 @@
         <v>1299</v>
       </c>
       <c r="K32" t="s">
-        <v>1023</v>
+        <v>1121</v>
       </c>
       <c r="L32">
         <v>0.5190595734350465</v>
@@ -23511,7 +23511,7 @@
         <v>1437</v>
       </c>
       <c r="X32" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="Y32">
         <v>26.765999999999998</v>
@@ -23546,7 +23546,7 @@
         <v>1301</v>
       </c>
       <c r="K33" t="s">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="L33">
         <v>0.29505146981926272</v>
@@ -23579,7 +23579,7 @@
         <v>1439</v>
       </c>
       <c r="X33" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="Y33">
         <v>35.325000000000003</v>
@@ -23614,7 +23614,7 @@
         <v>1303</v>
       </c>
       <c r="K34" t="s">
-        <v>1021</v>
+        <v>1119</v>
       </c>
       <c r="L34">
         <v>0.28737649325389003</v>
@@ -23647,7 +23647,7 @@
         <v>1441</v>
       </c>
       <c r="X34" t="s">
-        <v>1210</v>
+        <v>1232</v>
       </c>
       <c r="Y34">
         <v>21.510750000000002</v>
@@ -23682,7 +23682,7 @@
         <v>1305</v>
       </c>
       <c r="K35" t="s">
-        <v>1058</v>
+        <v>1009</v>
       </c>
       <c r="L35">
         <v>0.85621181691755843</v>
@@ -23715,7 +23715,7 @@
         <v>1443</v>
       </c>
       <c r="X35" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="Y35">
         <v>38.088000000000001</v>
@@ -23750,7 +23750,7 @@
         <v>1307</v>
       </c>
       <c r="K36" t="s">
-        <v>1116</v>
+        <v>1025</v>
       </c>
       <c r="L36">
         <v>2.2628760328229185</v>
@@ -23783,7 +23783,7 @@
         <v>1445</v>
       </c>
       <c r="X36" t="s">
-        <v>1222</v>
+        <v>1209</v>
       </c>
       <c r="Y36">
         <v>2.6655000000000002</v>
@@ -23818,7 +23818,7 @@
         <v>1309</v>
       </c>
       <c r="K37" t="s">
-        <v>1078</v>
+        <v>1105</v>
       </c>
       <c r="L37">
         <v>0.43370118574988076</v>
@@ -23851,7 +23851,7 @@
         <v>1447</v>
       </c>
       <c r="X37" t="s">
-        <v>1236</v>
+        <v>1255</v>
       </c>
       <c r="Y37">
         <v>11.651999999999999</v>
@@ -23886,7 +23886,7 @@
         <v>1311</v>
       </c>
       <c r="K38" t="s">
-        <v>1011</v>
+        <v>1060</v>
       </c>
       <c r="L38">
         <v>2.5150267058852811</v>
@@ -23919,7 +23919,7 @@
         <v>1449</v>
       </c>
       <c r="X38" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="Y38">
         <v>22.338000000000001</v>
@@ -23954,7 +23954,7 @@
         <v>1313</v>
       </c>
       <c r="K39" t="s">
-        <v>1062</v>
+        <v>1013</v>
       </c>
       <c r="L39">
         <v>2.2677057834637031</v>
@@ -23987,7 +23987,7 @@
         <v>1451</v>
       </c>
       <c r="X39" t="s">
-        <v>1253</v>
+        <v>1229</v>
       </c>
       <c r="Y39">
         <v>10.619249999999999</v>
@@ -24022,7 +24022,7 @@
         <v>1315</v>
       </c>
       <c r="K40" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="L40">
         <v>4.0509443596880574</v>
@@ -24055,7 +24055,7 @@
         <v>1453</v>
       </c>
       <c r="X40" t="s">
-        <v>1224</v>
+        <v>1211</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24090,7 +24090,7 @@
         <v>1317</v>
       </c>
       <c r="K41" t="s">
-        <v>1084</v>
+        <v>1129</v>
       </c>
       <c r="L41">
         <v>2.4836923620575391</v>
@@ -24123,7 +24123,7 @@
         <v>1455</v>
       </c>
       <c r="X41" t="s">
-        <v>1251</v>
+        <v>1227</v>
       </c>
       <c r="Y41">
         <v>35.486249999999998</v>
@@ -24158,7 +24158,7 @@
         <v>1319</v>
       </c>
       <c r="K42" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="L42">
         <v>2.885493974180005</v>
@@ -24193,7 +24193,7 @@
         <v>1321</v>
       </c>
       <c r="K43" t="s">
-        <v>1118</v>
+        <v>1027</v>
       </c>
       <c r="L43">
         <v>1.5541104167331323</v>
@@ -24228,7 +24228,7 @@
         <v>1323</v>
       </c>
       <c r="K44" t="s">
-        <v>1009</v>
+        <v>1058</v>
       </c>
       <c r="L44">
         <v>2.5222218440883255</v>
@@ -24263,7 +24263,7 @@
         <v>1325</v>
       </c>
       <c r="K45" t="s">
-        <v>1017</v>
+        <v>1066</v>
       </c>
       <c r="L45">
         <v>23.427729543154012</v>
@@ -24298,7 +24298,7 @@
         <v>1327</v>
       </c>
       <c r="K46" t="s">
-        <v>1072</v>
+        <v>1023</v>
       </c>
       <c r="L46">
         <v>1.4999429400795936</v>
@@ -24333,7 +24333,7 @@
         <v>1329</v>
       </c>
       <c r="K47" t="s">
-        <v>1110</v>
+        <v>1074</v>
       </c>
       <c r="L47">
         <v>55.863958629218203</v>
@@ -24368,7 +24368,7 @@
         <v>1331</v>
       </c>
       <c r="K48" t="s">
-        <v>1027</v>
+        <v>1125</v>
       </c>
       <c r="L48">
         <v>17.068804920122925</v>
@@ -24403,7 +24403,7 @@
         <v>1333</v>
       </c>
       <c r="K49" t="s">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="L49">
         <v>5.3278771181664615</v>
@@ -24438,7 +24438,7 @@
         <v>1335</v>
       </c>
       <c r="K50" t="s">
-        <v>1029</v>
+        <v>1127</v>
       </c>
       <c r="L50">
         <v>21.113356105805089</v>
@@ -24473,7 +24473,7 @@
         <v>1337</v>
       </c>
       <c r="K51" t="s">
-        <v>1052</v>
+        <v>1078</v>
       </c>
       <c r="L51">
         <v>2.3372365278937242</v>
@@ -24508,7 +24508,7 @@
         <v>1339</v>
       </c>
       <c r="K52" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="L52">
         <v>4.2648673086521249</v>
@@ -24543,7 +24543,7 @@
         <v>1341</v>
       </c>
       <c r="K53" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="L53">
         <v>2.8571480649629004</v>
@@ -24578,7 +24578,7 @@
         <v>1343</v>
       </c>
       <c r="K54" t="s">
-        <v>1114</v>
+        <v>1031</v>
       </c>
       <c r="L54">
         <v>31.544159267579381</v>
@@ -24613,7 +24613,7 @@
         <v>1345</v>
       </c>
       <c r="K55" t="s">
-        <v>1090</v>
+        <v>1135</v>
       </c>
       <c r="L55">
         <v>15.478330347836801</v>
@@ -24648,7 +24648,7 @@
         <v>1347</v>
       </c>
       <c r="K56" t="s">
-        <v>1070</v>
+        <v>1021</v>
       </c>
       <c r="L56">
         <v>18.772499167970881</v>
@@ -24683,7 +24683,7 @@
         <v>1349</v>
       </c>
       <c r="K57" t="s">
-        <v>1102</v>
+        <v>1035</v>
       </c>
       <c r="L57">
         <v>18.904558868579112</v>
@@ -24718,7 +24718,7 @@
         <v>1351</v>
       </c>
       <c r="K58" t="s">
-        <v>1130</v>
+        <v>1092</v>
       </c>
       <c r="L58">
         <v>14.176079891703212</v>
@@ -24753,7 +24753,7 @@
         <v>1353</v>
       </c>
       <c r="K59" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="L59">
         <v>0.80973624203950822</v>
@@ -24788,7 +24788,7 @@
         <v>1355</v>
       </c>
       <c r="K60" t="s">
-        <v>1092</v>
+        <v>1137</v>
       </c>
       <c r="L60">
         <v>3.2067222321080848</v>
@@ -24823,7 +24823,7 @@
         <v>1357</v>
       </c>
       <c r="K61" t="s">
-        <v>1112</v>
+        <v>1076</v>
       </c>
       <c r="L61">
         <v>0.66271354737797783</v>
@@ -24858,7 +24858,7 @@
         <v>1359</v>
       </c>
       <c r="K62" t="s">
-        <v>1137</v>
+        <v>1099</v>
       </c>
       <c r="L62">
         <v>1.8183767824138508</v>
@@ -24893,7 +24893,7 @@
         <v>1361</v>
       </c>
       <c r="K63" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="L63">
         <v>0.24904319237866104</v>
@@ -24928,7 +24928,7 @@
         <v>1363</v>
       </c>
       <c r="K64" t="s">
-        <v>1036</v>
+        <v>1050</v>
       </c>
       <c r="L64">
         <v>8.2047875916663029E-2</v>
@@ -24963,7 +24963,7 @@
         <v>1365</v>
       </c>
       <c r="K65" t="s">
-        <v>1066</v>
+        <v>1017</v>
       </c>
       <c r="L65">
         <v>11.861012832193515</v>
@@ -24998,7 +24998,7 @@
         <v>1367</v>
       </c>
       <c r="K66" t="s">
-        <v>1126</v>
+        <v>1088</v>
       </c>
       <c r="L66">
         <v>0.74143826937354373</v>
@@ -25033,7 +25033,7 @@
         <v>1369</v>
       </c>
       <c r="K67" t="s">
-        <v>1135</v>
+        <v>1097</v>
       </c>
       <c r="L67">
         <v>5.5201095579611916</v>
@@ -25068,7 +25068,7 @@
         <v>1371</v>
       </c>
       <c r="K68" t="s">
-        <v>1056</v>
+        <v>1082</v>
       </c>
       <c r="L68">
         <v>6.8285247240880329</v>
@@ -25103,7 +25103,7 @@
         <v>1373</v>
       </c>
       <c r="K69" t="s">
-        <v>1108</v>
+        <v>1072</v>
       </c>
       <c r="L69">
         <v>14.065249575687433</v>
@@ -25138,7 +25138,7 @@
         <v>1375</v>
       </c>
       <c r="K70" t="s">
-        <v>1068</v>
+        <v>1019</v>
       </c>
       <c r="L70">
         <v>9.3799037679336319</v>
@@ -25173,7 +25173,7 @@
         <v>1377</v>
       </c>
       <c r="K71" t="s">
-        <v>1025</v>
+        <v>1123</v>
       </c>
       <c r="L71">
         <v>42.785830383290261</v>
@@ -25208,7 +25208,7 @@
         <v>1379</v>
       </c>
       <c r="K72" t="s">
-        <v>1082</v>
+        <v>1109</v>
       </c>
       <c r="L72">
         <v>7.8693705940085819</v>
@@ -25243,7 +25243,7 @@
         <v>1381</v>
       </c>
       <c r="K73" t="s">
-        <v>1128</v>
+        <v>1090</v>
       </c>
       <c r="L73">
         <v>19.787589902082505</v>
@@ -25278,7 +25278,7 @@
         <v>1383</v>
       </c>
       <c r="K74" t="s">
-        <v>1015</v>
+        <v>1064</v>
       </c>
       <c r="L74">
         <v>18.319832830101969</v>
@@ -25313,7 +25313,7 @@
         <v>1385</v>
       </c>
       <c r="K75" t="s">
-        <v>1088</v>
+        <v>1133</v>
       </c>
       <c r="L75">
         <v>6.7551756478058005</v>
@@ -25383,7 +25383,7 @@
         <v>1389</v>
       </c>
       <c r="K77" t="s">
-        <v>1054</v>
+        <v>1080</v>
       </c>
       <c r="L77">
         <v>3.5275797249830152</v>
@@ -25453,7 +25453,7 @@
         <v>1393</v>
       </c>
       <c r="K79" t="s">
-        <v>1133</v>
+        <v>1095</v>
       </c>
       <c r="L79">
         <v>5.9305458091691294</v>
@@ -25468,7 +25468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4C76F6-371E-4500-8AA4-562DF27CC81E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25F685F9-D153-407C-8D97-874426005E31}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26937,7 +26937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524F87C-08BA-4F94-9759-A6691D340AD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019FA833-AEE6-4184-8185-C3E77CF732D8}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{217A0814-0D56-407D-929D-EE4E3B21B02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E45BC1DF-73FC-4322-8114-9FAE5819F1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1705,18 +1705,360 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_081</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 81</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_084</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 84</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_080</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 80</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_098</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 98</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_110</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 110</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_115</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 115</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_079</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 79</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_102</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 102</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_015</t>
   </si>
   <si>
@@ -1735,118 +2077,64 @@
     <t>connecting solar to buses in cluster 54</t>
   </si>
   <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_084</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 84</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_080</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 80</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-   